--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:T37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1872,6 +1872,1062 @@
         <v>19</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_00-13-52</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I22" t="n">
+        <v>20</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>10</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M22" t="n">
+        <v>50</v>
+      </c>
+      <c r="N22" t="n">
+        <v>28</v>
+      </c>
+      <c r="O22" t="n">
+        <v>29</v>
+      </c>
+      <c r="P22" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>29</v>
+      </c>
+      <c r="S22" t="n">
+        <v>50.86900424344039</v>
+      </c>
+      <c r="T22" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_00-13-52</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="I23" t="n">
+        <v>20</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>10</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M23" t="n">
+        <v>50</v>
+      </c>
+      <c r="N23" t="n">
+        <v>5</v>
+      </c>
+      <c r="O23" t="n">
+        <v>5</v>
+      </c>
+      <c r="P23" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>31</v>
+      </c>
+      <c r="R23" t="n">
+        <v>5</v>
+      </c>
+      <c r="S23" t="n">
+        <v>51.16019157575869</v>
+      </c>
+      <c r="T23" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_00-13-52</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="I24" t="n">
+        <v>20</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>10</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M24" t="n">
+        <v>50</v>
+      </c>
+      <c r="N24" t="n">
+        <v>27</v>
+      </c>
+      <c r="O24" t="n">
+        <v>28</v>
+      </c>
+      <c r="P24" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>12</v>
+      </c>
+      <c r="R24" t="n">
+        <v>27</v>
+      </c>
+      <c r="S24" t="n">
+        <v>50.86900424344032</v>
+      </c>
+      <c r="T24" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_00-13-52</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="I25" t="n">
+        <v>20</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>10</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M25" t="n">
+        <v>50</v>
+      </c>
+      <c r="N25" t="n">
+        <v>15</v>
+      </c>
+      <c r="O25" t="n">
+        <v>12</v>
+      </c>
+      <c r="P25" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>15</v>
+      </c>
+      <c r="R25" t="n">
+        <v>17</v>
+      </c>
+      <c r="S25" t="n">
+        <v>53.08295539600383</v>
+      </c>
+      <c r="T25" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_00-36-14</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I26" t="n">
+        <v>20</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>10</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M26" t="n">
+        <v>50</v>
+      </c>
+      <c r="N26" t="n">
+        <v>14</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2</v>
+      </c>
+      <c r="P26" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>14</v>
+      </c>
+      <c r="R26" t="n">
+        <v>19</v>
+      </c>
+      <c r="S26" t="n">
+        <v>64.79856402114055</v>
+      </c>
+      <c r="T26" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_00-36-14</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" t="n">
+        <v>5</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I27" t="n">
+        <v>20</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>10</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M27" t="n">
+        <v>50</v>
+      </c>
+      <c r="N27" t="n">
+        <v>8</v>
+      </c>
+      <c r="O27" t="n">
+        <v>5</v>
+      </c>
+      <c r="P27" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>8</v>
+      </c>
+      <c r="R27" t="n">
+        <v>10</v>
+      </c>
+      <c r="S27" t="n">
+        <v>54.87286459635793</v>
+      </c>
+      <c r="T27" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_00-36-14</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I28" t="n">
+        <v>20</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>10</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M28" t="n">
+        <v>50</v>
+      </c>
+      <c r="N28" t="n">
+        <v>24</v>
+      </c>
+      <c r="O28" t="n">
+        <v>24</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>10</v>
+      </c>
+      <c r="S28" t="n">
+        <v>63.83482549079477</v>
+      </c>
+      <c r="T28" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_00-36-14</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="I29" t="n">
+        <v>20</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>10</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M29" t="n">
+        <v>50</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3</v>
+      </c>
+      <c r="P29" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3</v>
+      </c>
+      <c r="R29" t="n">
+        <v>16</v>
+      </c>
+      <c r="S29" t="n">
+        <v>54.61464970018736</v>
+      </c>
+      <c r="T29" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_00-36-14</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="I30" t="n">
+        <v>20</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>10</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M30" t="n">
+        <v>50</v>
+      </c>
+      <c r="N30" t="n">
+        <v>15</v>
+      </c>
+      <c r="O30" t="n">
+        <v>31</v>
+      </c>
+      <c r="P30" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>13</v>
+      </c>
+      <c r="R30" t="n">
+        <v>15</v>
+      </c>
+      <c r="S30" t="n">
+        <v>60.68754662879635</v>
+      </c>
+      <c r="T30" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_00-36-14</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" t="n">
+        <v>5</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="I31" t="n">
+        <v>20</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>10</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M31" t="n">
+        <v>50</v>
+      </c>
+      <c r="N31" t="n">
+        <v>30</v>
+      </c>
+      <c r="O31" t="n">
+        <v>23</v>
+      </c>
+      <c r="P31" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>9</v>
+      </c>
+      <c r="R31" t="n">
+        <v>15</v>
+      </c>
+      <c r="S31" t="n">
+        <v>65.18885482373847</v>
+      </c>
+      <c r="T31" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_00-36-14</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I32" t="n">
+        <v>20</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>10</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M32" t="n">
+        <v>50</v>
+      </c>
+      <c r="N32" t="n">
+        <v>21</v>
+      </c>
+      <c r="O32" t="n">
+        <v>22</v>
+      </c>
+      <c r="P32" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>28</v>
+      </c>
+      <c r="R32" t="n">
+        <v>28</v>
+      </c>
+      <c r="S32" t="n">
+        <v>53.10155470235578</v>
+      </c>
+      <c r="T32" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_00-36-14</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" t="n">
+        <v>5</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I33" t="n">
+        <v>20</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>10</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M33" t="n">
+        <v>50</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3</v>
+      </c>
+      <c r="P33" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3</v>
+      </c>
+      <c r="R33" t="n">
+        <v>23</v>
+      </c>
+      <c r="S33" t="n">
+        <v>66.51582444758002</v>
+      </c>
+      <c r="T33" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_00-36-14</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" t="n">
+        <v>5</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I34" t="n">
+        <v>20</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>10</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M34" t="n">
+        <v>50</v>
+      </c>
+      <c r="N34" t="n">
+        <v>11</v>
+      </c>
+      <c r="O34" t="n">
+        <v>6</v>
+      </c>
+      <c r="P34" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>20</v>
+      </c>
+      <c r="R34" t="n">
+        <v>13</v>
+      </c>
+      <c r="S34" t="n">
+        <v>52.95821507321003</v>
+      </c>
+      <c r="T34" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_00-36-14</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" t="n">
+        <v>5</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="I35" t="n">
+        <v>20</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>10</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M35" t="n">
+        <v>50</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>21</v>
+      </c>
+      <c r="P35" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>20</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1</v>
+      </c>
+      <c r="S35" t="n">
+        <v>52.36820530346569</v>
+      </c>
+      <c r="T35" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_00-36-14</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>4</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" t="n">
+        <v>5</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="I36" t="n">
+        <v>20</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>10</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M36" t="n">
+        <v>50</v>
+      </c>
+      <c r="N36" t="n">
+        <v>13</v>
+      </c>
+      <c r="O36" t="n">
+        <v>14</v>
+      </c>
+      <c r="P36" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>31</v>
+      </c>
+      <c r="R36" t="n">
+        <v>13</v>
+      </c>
+      <c r="S36" t="n">
+        <v>51.16019157575857</v>
+      </c>
+      <c r="T36" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_00-36-14</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" t="n">
+        <v>4</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" t="n">
+        <v>5</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="I37" t="n">
+        <v>20</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>10</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M37" t="n">
+        <v>50</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" t="n">
+        <v>2</v>
+      </c>
+      <c r="P37" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>29</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2</v>
+      </c>
+      <c r="S37" t="n">
+        <v>51.16019157575864</v>
+      </c>
+      <c r="T37" t="n">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -515,7 +515,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
         <v>0.9</v>
       </c>
       <c r="I2" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -556,14 +556,14 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>[23, 3, 23, 23, 4]</t>
+          <t>[1, 27, 1, 1, 7]</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>49.13545004407975</v>
+        <v>40.49047096288854</v>
       </c>
       <c r="P2" t="n">
-        <v>99</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -571,7 +571,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -612,11 +612,11 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>[25, 0, 25, 25, 1]</t>
+          <t>[15, 23, 15, 30, 23]</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>40.49047096288852</v>
+        <v>50.57577825945861</v>
       </c>
       <c r="P3" t="n">
         <v>99</v>
@@ -627,7 +627,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
         <v>0.9</v>
       </c>
       <c r="I4" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -668,14 +668,14 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>[15, 23, 15, 30, 23]</t>
+          <t>[15, 29, 15, 9, 21]</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>50.57577825945861</v>
+        <v>51.65845840858613</v>
       </c>
       <c r="P4" t="n">
-        <v>99</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -683,7 +683,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -724,11 +724,11 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>[15, 29, 15, 9, 21]</t>
+          <t>[12, 24, 12, 1, 8]</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>51.65845840858613</v>
+        <v>51.02421332433351</v>
       </c>
       <c r="P5" t="n">
         <v>19</v>
@@ -736,7 +736,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6" t="n">
         <v>5</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="I6" t="n">
         <v>20</v>
@@ -780,11 +780,11 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>[1, 27, 1, 1, 7]</t>
+          <t>[24, 2, 24, 8, 15]</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>40.49047096288854</v>
+        <v>53.48536225359509</v>
       </c>
       <c r="P6" t="n">
         <v>19</v>
@@ -795,7 +795,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>0.9</v>
       </c>
       <c r="I7" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -836,22 +836,22 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>[12, 24, 12, 1, 8]</t>
+          <t>[25, 0, 25, 25, 1]</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>51.02421332433351</v>
+        <v>40.49047096288852</v>
       </c>
       <c r="P7" t="n">
-        <v>19</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="I8" t="n">
         <v>20</v>
@@ -892,11 +892,11 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>[11, 0, 11, 11, 5]</t>
+          <t>[20, 28, 20, 0, 7]</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>49.58388510895465</v>
+        <v>50.57577825945862</v>
       </c>
       <c r="P8" t="n">
         <v>19</v>
@@ -907,7 +907,7 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -948,11 +948,11 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>[3, 30, 3, 3, 9]</t>
+          <t>[1, 7, 1, 1, 8]</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>40.49047096288854</v>
+        <v>40.49047096288852</v>
       </c>
       <c r="P9" t="n">
         <v>99</v>
@@ -963,7 +963,7 @@
         <v>2</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="I10" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1004,22 +1004,22 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>[1, 7, 1, 1, 8]</t>
+          <t>[6, 0, 6, 25, 1]</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>40.49047096288852</v>
+        <v>51.04032529934361</v>
       </c>
       <c r="P10" t="n">
-        <v>99</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="I11" t="n">
         <v>100</v>
@@ -1060,11 +1060,11 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>[23, 29, 23, 23, 13]</t>
+          <t>[8, 0, 8, 8, 19]</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>49.13545004407976</v>
+        <v>41.61301147209003</v>
       </c>
       <c r="P11" t="n">
         <v>99</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I12" t="n">
         <v>20</v>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>[13, 30, 13, 13, 9]</t>
+          <t>[11, 0, 11, 11, 5]</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -1131,7 +1131,7 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="I13" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1172,14 +1172,14 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>[24, 2, 24, 8, 15]</t>
+          <t>[3, 30, 3, 3, 9]</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>53.48536225359509</v>
+        <v>40.49047096288854</v>
       </c>
       <c r="P13" t="n">
-        <v>19</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1187,7 +1187,7 @@
         <v>2</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1228,11 +1228,11 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>[20, 28, 20, 0, 7]</t>
+          <t>[13, 30, 13, 13, 9]</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>50.57577825945862</v>
+        <v>49.58388510895465</v>
       </c>
       <c r="P14" t="n">
         <v>19</v>
@@ -1243,7 +1243,7 @@
         <v>2</v>
       </c>
       <c r="B15" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="I15" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -1284,14 +1284,14 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>[6, 0, 6, 25, 1]</t>
+          <t>[23, 29, 23, 23, 13]</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>51.04032529934361</v>
+        <v>49.13545004407976</v>
       </c>
       <c r="P15" t="n">
-        <v>19</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,45 +425,67 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:T11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>pasta_run</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>configuracao</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>execucao</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>config_num</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>exec_num</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>param_ARRAY_VAR</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>param_CROSSOVER</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>param_DELTA_MIN</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>param_IND_SIZE</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>param_LIMITE_VAR</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>param_MUTACAO</t>
@@ -496,802 +518,698 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>best_variables</t>
+          <t>best_var_1</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>best_var_2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>best_var_3</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>best_var_4</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>best_var_5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
           <t>best_fitness</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>best_gen_idx</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 15]</t>
-        </is>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_22-11-53</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
       </c>
       <c r="H2" t="n">
         <v>0.9</v>
       </c>
       <c r="I2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M2" t="n">
         <v>50</v>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>[1, 27, 1, 1, 7]</t>
-        </is>
+      <c r="N2" t="n">
+        <v>16</v>
       </c>
       <c r="O2" t="n">
-        <v>40.49047096288854</v>
+        <v>17</v>
       </c>
       <c r="P2" t="n">
-        <v>19</v>
+        <v>16</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>27</v>
+      </c>
+      <c r="S2" t="n">
+        <v>54.45241486626857</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 15]</t>
-        </is>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_22-11-53</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
       </c>
       <c r="H3" t="n">
         <v>0.9</v>
       </c>
       <c r="I3" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M3" t="n">
         <v>50</v>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>[15, 23, 15, 30, 23]</t>
-        </is>
+      <c r="N3" t="n">
+        <v>23</v>
       </c>
       <c r="O3" t="n">
-        <v>50.57577825945861</v>
+        <v>31</v>
       </c>
       <c r="P3" t="n">
-        <v>99</v>
+        <v>10</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>10</v>
+      </c>
+      <c r="R3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S3" t="n">
+        <v>61.09729891301109</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 15]</t>
-        </is>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_22-11-53</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5</v>
       </c>
       <c r="H4" t="n">
         <v>0.9</v>
       </c>
       <c r="I4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M4" t="n">
         <v>50</v>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>[15, 29, 15, 9, 21]</t>
-        </is>
+      <c r="N4" t="n">
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>51.65845840858613</v>
+        <v>23</v>
       </c>
       <c r="P4" t="n">
-        <v>19</v>
+        <v>14</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>29</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>63.26315549340273</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 15]</t>
-        </is>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_22-11-53</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5</v>
       </c>
       <c r="H5" t="n">
         <v>0.9</v>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M5" t="n">
         <v>50</v>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>[12, 24, 12, 1, 8]</t>
-        </is>
+      <c r="N5" t="n">
+        <v>10</v>
       </c>
       <c r="O5" t="n">
-        <v>51.02421332433351</v>
+        <v>30</v>
       </c>
       <c r="P5" t="n">
-        <v>19</v>
+        <v>24</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>10</v>
+      </c>
+      <c r="R5" t="n">
+        <v>18</v>
+      </c>
+      <c r="S5" t="n">
+        <v>53.89148964378263</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 15]</t>
-        </is>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_22-11-53</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I6" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M6" t="n">
         <v>50</v>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>[24, 2, 24, 8, 15]</t>
-        </is>
+      <c r="N6" t="n">
+        <v>7</v>
       </c>
       <c r="O6" t="n">
-        <v>53.48536225359509</v>
+        <v>6</v>
       </c>
       <c r="P6" t="n">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>22</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7</v>
+      </c>
+      <c r="S6" t="n">
+        <v>60.99743812844282</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 15]</t>
-        </is>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_22-11-53</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9</v>
+        <v>0.77</v>
       </c>
       <c r="I7" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M7" t="n">
         <v>50</v>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>[25, 0, 25, 25, 1]</t>
-        </is>
+      <c r="N7" t="n">
+        <v>17</v>
       </c>
       <c r="O7" t="n">
-        <v>40.49047096288852</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>99</v>
+        <v>10</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>25</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6</v>
+      </c>
+      <c r="S7" t="n">
+        <v>64.46103088747418</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" t="n">
-        <v>6</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 15]</t>
-        </is>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_22-11-53</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="I8" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M8" t="n">
         <v>50</v>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>[20, 28, 20, 0, 7]</t>
-        </is>
+      <c r="N8" t="n">
+        <v>7</v>
       </c>
       <c r="O8" t="n">
-        <v>50.57577825945862</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>19</v>
+        <v>7</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>29</v>
+      </c>
+      <c r="R8" t="n">
+        <v>15</v>
+      </c>
+      <c r="S8" t="n">
+        <v>51.6519701753148</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 15]</t>
-        </is>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_22-11-53</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5</v>
+        <v>0.77</v>
       </c>
       <c r="I9" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M9" t="n">
         <v>50</v>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>[1, 7, 1, 1, 8]</t>
-        </is>
+      <c r="N9" t="n">
+        <v>4</v>
       </c>
       <c r="O9" t="n">
-        <v>40.49047096288852</v>
+        <v>10</v>
       </c>
       <c r="P9" t="n">
-        <v>99</v>
+        <v>25</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>17</v>
+      </c>
+      <c r="S9" t="n">
+        <v>53.89148964378268</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" t="n">
-        <v>7</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 15]</t>
-        </is>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_22-11-53</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="I10" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M10" t="n">
         <v>50</v>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>[6, 0, 6, 25, 1]</t>
-        </is>
+      <c r="N10" t="n">
+        <v>18</v>
       </c>
       <c r="O10" t="n">
-        <v>51.04032529934361</v>
+        <v>7</v>
       </c>
       <c r="P10" t="n">
-        <v>19</v>
+        <v>18</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>30</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50.92435253976517</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 15]</t>
-        </is>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_22-11-53</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9</v>
+        <v>0.77</v>
       </c>
       <c r="I11" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M11" t="n">
         <v>50</v>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>[8, 0, 8, 8, 19]</t>
-        </is>
+      <c r="N11" t="n">
+        <v>16</v>
       </c>
       <c r="O11" t="n">
-        <v>41.61301147209003</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>1</v>
-      </c>
-      <c r="B12" t="n">
-        <v>7</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 15]</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" t="n">
-        <v>5</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I12" t="n">
-        <v>20</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>10</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M12" t="n">
-        <v>50</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>[11, 0, 11, 11, 5]</t>
-        </is>
-      </c>
-      <c r="O12" t="n">
-        <v>49.58388510895465</v>
-      </c>
-      <c r="P12" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 15]</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" t="n">
-        <v>5</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I13" t="n">
-        <v>100</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>10</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M13" t="n">
-        <v>50</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>[3, 30, 3, 3, 9]</t>
-        </is>
-      </c>
-      <c r="O13" t="n">
-        <v>40.49047096288854</v>
-      </c>
-      <c r="P13" t="n">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>2</v>
-      </c>
-      <c r="B14" t="n">
-        <v>4</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 15]</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" t="n">
-        <v>5</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I14" t="n">
-        <v>20</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>10</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M14" t="n">
-        <v>50</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>[13, 30, 13, 13, 9]</t>
-        </is>
-      </c>
-      <c r="O14" t="n">
-        <v>49.58388510895465</v>
-      </c>
-      <c r="P14" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>2</v>
-      </c>
-      <c r="B15" t="n">
-        <v>3</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 15]</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" t="n">
-        <v>5</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I15" t="n">
-        <v>100</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>10</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M15" t="n">
-        <v>50</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>[23, 29, 23, 23, 13]</t>
-        </is>
-      </c>
-      <c r="O15" t="n">
-        <v>49.13545004407976</v>
-      </c>
-      <c r="P15" t="n">
-        <v>99</v>
+        <v>23</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>30</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6</v>
+      </c>
+      <c r="S11" t="n">
+        <v>63.21030899695449</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:T34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -555,7 +555,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>run_2025-08-21_22-11-53</t>
+          <t>run_2025-08-21_22-49-32</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -579,10 +579,10 @@
         <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9</v>
+        <v>0.77</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -597,31 +597,31 @@
         <v>50</v>
       </c>
       <c r="N2" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="O2" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="P2" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="R2" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S2" t="n">
-        <v>54.45241486626857</v>
+        <v>51.16019157575857</v>
       </c>
       <c r="T2" t="n">
-        <v>4</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>run_2025-08-21_22-11-53</t>
+          <t>run_2025-08-21_22-49-32</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -645,10 +645,10 @@
         <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9</v>
+        <v>0.77</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -663,31 +663,31 @@
         <v>50</v>
       </c>
       <c r="N3" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="O3" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="P3" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="Q3" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="S3" t="n">
-        <v>61.09729891301109</v>
+        <v>51.66787779075111</v>
       </c>
       <c r="T3" t="n">
-        <v>4</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>run_2025-08-21_22-11-53</t>
+          <t>run_2025-08-21_22-49-32</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -711,10 +711,10 @@
         <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9</v>
+        <v>0.77</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -729,31 +729,31 @@
         <v>50</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="P4" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="Q4" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="S4" t="n">
-        <v>63.26315549340273</v>
+        <v>50.70603867431607</v>
       </c>
       <c r="T4" t="n">
-        <v>4</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>run_2025-08-21_22-11-53</t>
+          <t>run_2025-08-21_22-49-32</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -762,64 +762,64 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I5" t="n">
+        <v>100</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>50</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I5" t="n">
-        <v>5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>5</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>50</v>
-      </c>
-      <c r="N5" t="n">
-        <v>10</v>
-      </c>
-      <c r="O5" t="n">
-        <v>30</v>
-      </c>
       <c r="P5" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="Q5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="R5" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
-        <v>53.89148964378263</v>
+        <v>50.86900424344032</v>
       </c>
       <c r="T5" t="n">
-        <v>4</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>run_2025-08-21_22-11-53</t>
+          <t>run_2025-08-21_22-23-33</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -843,10 +843,10 @@
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9</v>
+        <v>0.77</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -861,43 +861,43 @@
         <v>50</v>
       </c>
       <c r="N6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O6" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="P6" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="Q6" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="R6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="S6" t="n">
-        <v>60.99743812844282</v>
+        <v>52.22303357638416</v>
       </c>
       <c r="T6" t="n">
-        <v>4</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>run_2025-08-21_22-11-53</t>
+          <t>run_2025-08-21_22-23-33</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>config_2</t>
+          <t>config_1</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>0.9</v>
@@ -912,7 +912,7 @@
         <v>0.77</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -927,43 +927,43 @@
         <v>50</v>
       </c>
       <c r="N7" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P7" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="Q7" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="R7" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="S7" t="n">
-        <v>64.46103088747418</v>
+        <v>37.35402933294379</v>
       </c>
       <c r="T7" t="n">
-        <v>4</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>run_2025-08-21_22-11-53</t>
+          <t>run_2025-08-21_22-23-33</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>config_2</t>
+          <t>config_1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0.9</v>
@@ -978,7 +978,7 @@
         <v>0.77</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -993,43 +993,43 @@
         <v>50</v>
       </c>
       <c r="N8" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="P8" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="Q8" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="R8" t="n">
         <v>15</v>
       </c>
       <c r="S8" t="n">
-        <v>51.6519701753148</v>
+        <v>37.45559271642123</v>
       </c>
       <c r="T8" t="n">
-        <v>4</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>run_2025-08-21_22-11-53</t>
+          <t>run_2025-08-21_22-23-33</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>config_2</t>
+          <t>config_1</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0.9</v>
@@ -1044,7 +1044,7 @@
         <v>0.77</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1059,43 +1059,43 @@
         <v>50</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O9" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="P9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
         <v>17</v>
       </c>
       <c r="S9" t="n">
-        <v>53.89148964378268</v>
+        <v>38.5189038855434</v>
       </c>
       <c r="T9" t="n">
-        <v>4</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>run_2025-08-21_22-11-53</t>
+          <t>run_2025-08-21_22-23-33</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>config_2</t>
+          <t>config_1</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0.9</v>
@@ -1110,7 +1110,7 @@
         <v>0.77</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1125,90 +1125,1608 @@
         <v>50</v>
       </c>
       <c r="N10" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="O10" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="P10" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="Q10" t="n">
         <v>30</v>
       </c>
       <c r="R10" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="S10" t="n">
-        <v>50.92435253976517</v>
+        <v>37.35402933294375</v>
       </c>
       <c r="T10" t="n">
-        <v>4</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>run_2025-08-21_22-23-33</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>100</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>50</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>20</v>
+      </c>
+      <c r="R11" t="n">
+        <v>16</v>
+      </c>
+      <c r="S11" t="n">
+        <v>52.7841926773345</v>
+      </c>
+      <c r="T11" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_22-23-33</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>100</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>50</v>
+      </c>
+      <c r="N12" t="n">
+        <v>9</v>
+      </c>
+      <c r="O12" t="n">
+        <v>11</v>
+      </c>
+      <c r="P12" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>9</v>
+      </c>
+      <c r="R12" t="n">
+        <v>5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>52.36433802573944</v>
+      </c>
+      <c r="T12" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_22-23-33</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>100</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>50</v>
+      </c>
+      <c r="N13" t="n">
+        <v>13</v>
+      </c>
+      <c r="O13" t="n">
+        <v>22</v>
+      </c>
+      <c r="P13" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>21</v>
+      </c>
+      <c r="R13" t="n">
+        <v>21</v>
+      </c>
+      <c r="S13" t="n">
+        <v>52.32727973261093</v>
+      </c>
+      <c r="T13" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_22-23-33</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>100</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>50</v>
+      </c>
+      <c r="N14" t="n">
+        <v>16</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2</v>
+      </c>
+      <c r="P14" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>16</v>
+      </c>
+      <c r="R14" t="n">
+        <v>3</v>
+      </c>
+      <c r="S14" t="n">
+        <v>38.63626557759999</v>
+      </c>
+      <c r="T14" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_22-23-33</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>100</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>50</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3</v>
+      </c>
+      <c r="P15" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>20</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50.86900424344025</v>
+      </c>
+      <c r="T15" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_22-23-33</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>90</v>
+      </c>
+      <c r="I16" t="n">
+        <v>100</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>50</v>
+      </c>
+      <c r="N16" t="n">
+        <v>9</v>
+      </c>
+      <c r="O16" t="n">
+        <v>21</v>
+      </c>
+      <c r="P16" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>9</v>
+      </c>
+      <c r="R16" t="n">
+        <v>11</v>
+      </c>
+      <c r="S16" t="n">
+        <v>37.35402933294375</v>
+      </c>
+      <c r="T16" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_22-23-33</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>90</v>
+      </c>
+      <c r="I17" t="n">
+        <v>100</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>50</v>
+      </c>
+      <c r="N17" t="n">
+        <v>7</v>
+      </c>
+      <c r="O17" t="n">
+        <v>8</v>
+      </c>
+      <c r="P17" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>7</v>
+      </c>
+      <c r="R17" t="n">
+        <v>9</v>
+      </c>
+      <c r="S17" t="n">
+        <v>51.90529650881621</v>
+      </c>
+      <c r="T17" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_22-23-33</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>90</v>
+      </c>
+      <c r="I18" t="n">
+        <v>100</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>50</v>
+      </c>
+      <c r="N18" t="n">
+        <v>24</v>
+      </c>
+      <c r="O18" t="n">
+        <v>24</v>
+      </c>
+      <c r="P18" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>6</v>
+      </c>
+      <c r="R18" t="n">
+        <v>26</v>
+      </c>
+      <c r="S18" t="n">
+        <v>50.86900424344032</v>
+      </c>
+      <c r="T18" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_22-23-33</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>90</v>
+      </c>
+      <c r="I19" t="n">
+        <v>100</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>50</v>
+      </c>
+      <c r="N19" t="n">
+        <v>13</v>
+      </c>
+      <c r="O19" t="n">
+        <v>14</v>
+      </c>
+      <c r="P19" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>27</v>
+      </c>
+      <c r="R19" t="n">
+        <v>13</v>
+      </c>
+      <c r="S19" t="n">
+        <v>51.16019157575857</v>
+      </c>
+      <c r="T19" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_22-23-33</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>90</v>
+      </c>
+      <c r="I20" t="n">
+        <v>100</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>50</v>
+      </c>
+      <c r="N20" t="n">
+        <v>8</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3</v>
+      </c>
+      <c r="P20" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4</v>
+      </c>
+      <c r="R20" t="n">
+        <v>4</v>
+      </c>
+      <c r="S20" t="n">
+        <v>50.62046726902084</v>
+      </c>
+      <c r="T20" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_22-11-13</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I21" t="n">
+        <v>100</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>50</v>
+      </c>
+      <c r="N21" t="n">
+        <v>13</v>
+      </c>
+      <c r="O21" t="n">
+        <v>19</v>
+      </c>
+      <c r="P21" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>13</v>
+      </c>
+      <c r="R21" t="n">
+        <v>13</v>
+      </c>
+      <c r="S21" t="n">
+        <v>37.35402933294375</v>
+      </c>
+      <c r="T21" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_22-11-13</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I22" t="n">
+        <v>100</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M22" t="n">
+        <v>50</v>
+      </c>
+      <c r="N22" t="n">
+        <v>27</v>
+      </c>
+      <c r="O22" t="n">
+        <v>22</v>
+      </c>
+      <c r="P22" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>22</v>
+      </c>
+      <c r="R22" t="n">
+        <v>27</v>
+      </c>
+      <c r="S22" t="n">
+        <v>50.19952857273991</v>
+      </c>
+      <c r="T22" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_22-11-13</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I23" t="n">
+        <v>100</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>5</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M23" t="n">
+        <v>50</v>
+      </c>
+      <c r="N23" t="n">
+        <v>29</v>
+      </c>
+      <c r="O23" t="n">
+        <v>29</v>
+      </c>
+      <c r="P23" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>29</v>
+      </c>
+      <c r="R23" t="n">
+        <v>30</v>
+      </c>
+      <c r="S23" t="n">
+        <v>45.51200429701026</v>
+      </c>
+      <c r="T23" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_22-11-13</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I24" t="n">
+        <v>100</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>5</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M24" t="n">
+        <v>50</v>
+      </c>
+      <c r="N24" t="n">
+        <v>10</v>
+      </c>
+      <c r="O24" t="n">
+        <v>16</v>
+      </c>
+      <c r="P24" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>10</v>
+      </c>
+      <c r="R24" t="n">
+        <v>10</v>
+      </c>
+      <c r="S24" t="n">
+        <v>37.35402933294375</v>
+      </c>
+      <c r="T24" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>run_2025-08-21_22-11-53</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I25" t="n">
+        <v>5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>5</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M25" t="n">
+        <v>50</v>
+      </c>
+      <c r="N25" t="n">
+        <v>7</v>
+      </c>
+      <c r="O25" t="n">
+        <v>6</v>
+      </c>
+      <c r="P25" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>22</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7</v>
+      </c>
+      <c r="S25" t="n">
+        <v>60.99743812844282</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_22-11-53</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I26" t="n">
+        <v>5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>5</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M26" t="n">
+        <v>50</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>23</v>
+      </c>
+      <c r="P26" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>29</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2</v>
+      </c>
+      <c r="S26" t="n">
+        <v>63.26315549340273</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_22-11-53</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" t="n">
+        <v>5</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I27" t="n">
+        <v>5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M27" t="n">
+        <v>50</v>
+      </c>
+      <c r="N27" t="n">
+        <v>10</v>
+      </c>
+      <c r="O27" t="n">
+        <v>30</v>
+      </c>
+      <c r="P27" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>10</v>
+      </c>
+      <c r="R27" t="n">
+        <v>18</v>
+      </c>
+      <c r="S27" t="n">
+        <v>53.89148964378263</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_22-11-53</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I28" t="n">
+        <v>5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>5</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M28" t="n">
+        <v>50</v>
+      </c>
+      <c r="N28" t="n">
+        <v>23</v>
+      </c>
+      <c r="O28" t="n">
+        <v>31</v>
+      </c>
+      <c r="P28" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>10</v>
+      </c>
+      <c r="R28" t="n">
+        <v>3</v>
+      </c>
+      <c r="S28" t="n">
+        <v>61.09729891301109</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_22-11-53</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I29" t="n">
+        <v>5</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>5</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M29" t="n">
+        <v>50</v>
+      </c>
+      <c r="N29" t="n">
+        <v>16</v>
+      </c>
+      <c r="O29" t="n">
+        <v>17</v>
+      </c>
+      <c r="P29" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>27</v>
+      </c>
+      <c r="S29" t="n">
+        <v>54.45241486626857</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_22-11-53</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
         <is>
           <t>config_2</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G11" t="n">
-        <v>5</v>
-      </c>
-      <c r="H11" t="n">
+      <c r="C30" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5</v>
+      </c>
+      <c r="H30" t="n">
         <v>0.77</v>
       </c>
-      <c r="I11" t="n">
-        <v>5</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>5</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>50</v>
-      </c>
-      <c r="N11" t="n">
+      <c r="I30" t="n">
+        <v>5</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>5</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M30" t="n">
+        <v>50</v>
+      </c>
+      <c r="N30" t="n">
         <v>16</v>
       </c>
-      <c r="O11" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" t="n">
+      <c r="O30" t="n">
+        <v>1</v>
+      </c>
+      <c r="P30" t="n">
         <v>23</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q30" t="n">
         <v>30</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R30" t="n">
         <v>6</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S30" t="n">
         <v>63.21030899695449</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T30" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_22-11-53</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" t="n">
+        <v>5</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I31" t="n">
+        <v>5</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>5</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M31" t="n">
+        <v>50</v>
+      </c>
+      <c r="N31" t="n">
+        <v>7</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2</v>
+      </c>
+      <c r="P31" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>29</v>
+      </c>
+      <c r="R31" t="n">
+        <v>15</v>
+      </c>
+      <c r="S31" t="n">
+        <v>51.6519701753148</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_22-11-53</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>5</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M32" t="n">
+        <v>50</v>
+      </c>
+      <c r="N32" t="n">
+        <v>17</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>25</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6</v>
+      </c>
+      <c r="S32" t="n">
+        <v>64.46103088747418</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_22-11-53</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" t="n">
+        <v>5</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I33" t="n">
+        <v>5</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>5</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M33" t="n">
+        <v>50</v>
+      </c>
+      <c r="N33" t="n">
+        <v>18</v>
+      </c>
+      <c r="O33" t="n">
+        <v>7</v>
+      </c>
+      <c r="P33" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>30</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7</v>
+      </c>
+      <c r="S33" t="n">
+        <v>50.92435253976517</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>run_2025-08-21_22-11-53</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" t="n">
+        <v>5</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I34" t="n">
+        <v>5</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>5</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M34" t="n">
+        <v>50</v>
+      </c>
+      <c r="N34" t="n">
+        <v>4</v>
+      </c>
+      <c r="O34" t="n">
+        <v>10</v>
+      </c>
+      <c r="P34" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>4</v>
+      </c>
+      <c r="R34" t="n">
+        <v>17</v>
+      </c>
+      <c r="S34" t="n">
+        <v>53.89148964378268</v>
+      </c>
+      <c r="T34" t="n">
         <v>4</v>
       </c>
     </row>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T108"/>
+  <dimension ref="A1:T109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D53" t="n">
         <v>4</v>
@@ -3963,22 +3963,22 @@
         <v>50</v>
       </c>
       <c r="N53" t="n">
+        <v>15</v>
+      </c>
+      <c r="O53" t="n">
         <v>22</v>
       </c>
-      <c r="O53" t="n">
-        <v>5</v>
-      </c>
       <c r="P53" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="Q53" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="R53" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="S53" t="n">
-        <v>52.33167472531786</v>
+        <v>37.35402933294375</v>
       </c>
       <c r="T53" t="n">
         <v>99</v>
@@ -3996,7 +3996,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
         <v>4</v>
@@ -4029,22 +4029,22 @@
         <v>50</v>
       </c>
       <c r="N54" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="O54" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P54" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="Q54" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="R54" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="S54" t="n">
-        <v>37.35402933294375</v>
+        <v>52.33167472531786</v>
       </c>
       <c r="T54" t="n">
         <v>99</v>
@@ -4058,17 +4058,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>config_2</t>
+          <t>config_4</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E55" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="F55" t="n">
         <v>2</v>
@@ -4095,22 +4095,22 @@
         <v>50</v>
       </c>
       <c r="N55" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="O55" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="P55" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="Q55" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="R55" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="S55" t="n">
-        <v>37.35402933294379</v>
+        <v>37.35402933294375</v>
       </c>
       <c r="T55" t="n">
         <v>99</v>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D56" t="n">
         <v>2</v>
@@ -4161,22 +4161,22 @@
         <v>50</v>
       </c>
       <c r="N56" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="O56" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="P56" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="Q56" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="R56" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="S56" t="n">
-        <v>37.35402933294375</v>
+        <v>37.35402933294379</v>
       </c>
       <c r="T56" t="n">
         <v>99</v>
@@ -4194,7 +4194,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57" t="n">
         <v>2</v>
@@ -4227,22 +4227,22 @@
         <v>50</v>
       </c>
       <c r="N57" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="O57" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="P57" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="Q57" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="R57" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="S57" t="n">
-        <v>37.35402933294379</v>
+        <v>37.35402933294375</v>
       </c>
       <c r="T57" t="n">
         <v>99</v>
@@ -4260,7 +4260,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D58" t="n">
         <v>2</v>
@@ -4293,22 +4293,22 @@
         <v>50</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="O58" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="S58" t="n">
-        <v>37.35402933294375</v>
+        <v>37.35402933294379</v>
       </c>
       <c r="T58" t="n">
         <v>99</v>
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D59" t="n">
         <v>2</v>
@@ -4359,22 +4359,22 @@
         <v>50</v>
       </c>
       <c r="N59" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="P59" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>37.35402933294379</v>
+        <v>37.35402933294375</v>
       </c>
       <c r="T59" t="n">
         <v>99</v>
@@ -4383,22 +4383,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>run_2025-08-21_22-23-33</t>
+          <t>run_2025-08-22_12-50-07</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>config_1</t>
+          <t>config_2</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F60" t="n">
         <v>2</v>
@@ -4407,7 +4407,7 @@
         <v>5</v>
       </c>
       <c r="H60" t="n">
-        <v>0.77</v>
+        <v>0.9</v>
       </c>
       <c r="I60" t="n">
         <v>100</v>
@@ -4416,7 +4416,7 @@
         <v>1</v>
       </c>
       <c r="K60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L60" t="n">
         <v>0.2</v>
@@ -4425,22 +4425,22 @@
         <v>50</v>
       </c>
       <c r="N60" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="O60" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="P60" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="Q60" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="R60" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="S60" t="n">
-        <v>52.22303357638416</v>
+        <v>37.35402933294379</v>
       </c>
       <c r="T60" t="n">
         <v>99</v>
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D61" t="n">
         <v>1</v>
@@ -4491,22 +4491,22 @@
         <v>50</v>
       </c>
       <c r="N61" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="O61" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="P61" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="Q61" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="R61" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="S61" t="n">
-        <v>37.35402933294379</v>
+        <v>52.22303357638416</v>
       </c>
       <c r="T61" t="n">
         <v>99</v>
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D62" t="n">
         <v>1</v>
@@ -4557,22 +4557,22 @@
         <v>50</v>
       </c>
       <c r="N62" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="O62" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="P62" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="Q62" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="R62" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="S62" t="n">
-        <v>37.45559271642123</v>
+        <v>37.35402933294379</v>
       </c>
       <c r="T62" t="n">
         <v>99</v>
@@ -4590,7 +4590,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D63" t="n">
         <v>1</v>
@@ -4623,22 +4623,22 @@
         <v>50</v>
       </c>
       <c r="N63" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="O63" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="P63" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="Q63" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="R63" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="S63" t="n">
-        <v>38.5189038855434</v>
+        <v>37.45559271642123</v>
       </c>
       <c r="T63" t="n">
         <v>99</v>
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D64" t="n">
         <v>1</v>
@@ -4689,22 +4689,22 @@
         <v>50</v>
       </c>
       <c r="N64" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="O64" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="P64" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="Q64" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="R64" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="S64" t="n">
-        <v>37.35402933294375</v>
+        <v>38.5189038855434</v>
       </c>
       <c r="T64" t="n">
         <v>99</v>
@@ -4718,14 +4718,14 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>config_3</t>
+          <t>config_1</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E65" t="n">
         <v>0.9</v>
@@ -4737,7 +4737,7 @@
         <v>5</v>
       </c>
       <c r="H65" t="n">
-        <v>0.5</v>
+        <v>0.77</v>
       </c>
       <c r="I65" t="n">
         <v>100</v>
@@ -4755,22 +4755,22 @@
         <v>50</v>
       </c>
       <c r="N65" t="n">
+        <v>30</v>
+      </c>
+      <c r="O65" t="n">
         <v>20</v>
       </c>
-      <c r="O65" t="n">
-        <v>2</v>
-      </c>
       <c r="P65" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="Q65" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="R65" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="S65" t="n">
-        <v>52.7841926773345</v>
+        <v>37.35402933294375</v>
       </c>
       <c r="T65" t="n">
         <v>99</v>
@@ -4788,7 +4788,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D66" t="n">
         <v>3</v>
@@ -4821,22 +4821,22 @@
         <v>50</v>
       </c>
       <c r="N66" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="O66" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="P66" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="Q66" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="R66" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="S66" t="n">
-        <v>52.36433802573944</v>
+        <v>52.7841926773345</v>
       </c>
       <c r="T66" t="n">
         <v>99</v>
@@ -4854,7 +4854,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D67" t="n">
         <v>3</v>
@@ -4887,22 +4887,22 @@
         <v>50</v>
       </c>
       <c r="N67" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="O67" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="P67" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="Q67" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="R67" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="S67" t="n">
-        <v>52.32727973261093</v>
+        <v>52.36433802573944</v>
       </c>
       <c r="T67" t="n">
         <v>99</v>
@@ -4920,7 +4920,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D68" t="n">
         <v>3</v>
@@ -4953,22 +4953,22 @@
         <v>50</v>
       </c>
       <c r="N68" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="O68" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="P68" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="Q68" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="R68" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="S68" t="n">
-        <v>38.63626557759999</v>
+        <v>52.32727973261093</v>
       </c>
       <c r="T68" t="n">
         <v>99</v>
@@ -4986,7 +4986,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D69" t="n">
         <v>3</v>
@@ -5019,22 +5019,22 @@
         <v>50</v>
       </c>
       <c r="N69" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="O69" t="n">
+        <v>2</v>
+      </c>
+      <c r="P69" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>16</v>
+      </c>
+      <c r="R69" t="n">
         <v>3</v>
       </c>
-      <c r="P69" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>20</v>
-      </c>
-      <c r="R69" t="n">
-        <v>2</v>
-      </c>
       <c r="S69" t="n">
-        <v>50.86900424344025</v>
+        <v>38.63626557759999</v>
       </c>
       <c r="T69" t="n">
         <v>99</v>
@@ -5048,14 +5048,14 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>config_2</t>
+          <t>config_3</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E70" t="n">
         <v>0.9</v>
@@ -5067,7 +5067,7 @@
         <v>5</v>
       </c>
       <c r="H70" t="n">
-        <v>90</v>
+        <v>0.5</v>
       </c>
       <c r="I70" t="n">
         <v>100</v>
@@ -5085,22 +5085,22 @@
         <v>50</v>
       </c>
       <c r="N70" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O70" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="P70" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="Q70" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="R70" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="S70" t="n">
-        <v>37.35402933294375</v>
+        <v>50.86900424344025</v>
       </c>
       <c r="T70" t="n">
         <v>99</v>
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D71" t="n">
         <v>2</v>
@@ -5151,22 +5151,22 @@
         <v>50</v>
       </c>
       <c r="N71" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O71" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="P71" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="Q71" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R71" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S71" t="n">
-        <v>51.90529650881621</v>
+        <v>37.35402933294375</v>
       </c>
       <c r="T71" t="n">
         <v>99</v>
@@ -5184,7 +5184,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D72" t="n">
         <v>2</v>
@@ -5217,22 +5217,22 @@
         <v>50</v>
       </c>
       <c r="N72" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="O72" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="P72" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="Q72" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R72" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="S72" t="n">
-        <v>50.86900424344032</v>
+        <v>51.90529650881621</v>
       </c>
       <c r="T72" t="n">
         <v>99</v>
@@ -5250,7 +5250,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D73" t="n">
         <v>2</v>
@@ -5283,22 +5283,22 @@
         <v>50</v>
       </c>
       <c r="N73" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="O73" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="P73" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="Q73" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="R73" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S73" t="n">
-        <v>51.16019157575857</v>
+        <v>50.86900424344032</v>
       </c>
       <c r="T73" t="n">
         <v>99</v>
@@ -5316,7 +5316,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D74" t="n">
         <v>2</v>
@@ -5349,22 +5349,22 @@
         <v>50</v>
       </c>
       <c r="N74" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="O74" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="P74" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="Q74" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="R74" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="S74" t="n">
-        <v>50.62046726902084</v>
+        <v>51.16019157575857</v>
       </c>
       <c r="T74" t="n">
         <v>99</v>
@@ -5373,19 +5373,19 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>run_2025-08-21_22-11-13</t>
+          <t>run_2025-08-21_22-23-33</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>config_1</t>
+          <t>config_2</t>
         </is>
       </c>
       <c r="C75" t="n">
         <v>3</v>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75" t="n">
         <v>0.9</v>
@@ -5397,7 +5397,7 @@
         <v>5</v>
       </c>
       <c r="H75" t="n">
-        <v>0.77</v>
+        <v>90</v>
       </c>
       <c r="I75" t="n">
         <v>100</v>
@@ -5415,22 +5415,22 @@
         <v>50</v>
       </c>
       <c r="N75" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O75" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="P75" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Q75" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="R75" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="S75" t="n">
-        <v>37.35402933294375</v>
+        <v>50.62046726902084</v>
       </c>
       <c r="T75" t="n">
         <v>99</v>
@@ -5448,7 +5448,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D76" t="n">
         <v>1</v>
@@ -5481,22 +5481,22 @@
         <v>50</v>
       </c>
       <c r="N76" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="O76" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="P76" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="Q76" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="R76" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="S76" t="n">
-        <v>50.19952857273991</v>
+        <v>37.35402933294375</v>
       </c>
       <c r="T76" t="n">
         <v>99</v>
@@ -5514,7 +5514,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D77" t="n">
         <v>1</v>
@@ -5547,22 +5547,22 @@
         <v>50</v>
       </c>
       <c r="N77" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="O77" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="P77" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="Q77" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="R77" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="S77" t="n">
-        <v>45.51200429701026</v>
+        <v>50.19952857273991</v>
       </c>
       <c r="T77" t="n">
         <v>99</v>
@@ -5580,7 +5580,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D78" t="n">
         <v>1</v>
@@ -5613,22 +5613,22 @@
         <v>50</v>
       </c>
       <c r="N78" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="O78" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="P78" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="Q78" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="R78" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="S78" t="n">
-        <v>37.35402933294375</v>
+        <v>45.51200429701026</v>
       </c>
       <c r="T78" t="n">
         <v>99</v>
@@ -5637,7 +5637,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>run_2025-08-21_22-11-53</t>
+          <t>run_2025-08-21_22-11-13</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5646,7 +5646,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D79" t="n">
         <v>1</v>
@@ -5661,10 +5661,10 @@
         <v>5</v>
       </c>
       <c r="H79" t="n">
-        <v>0.9</v>
+        <v>0.77</v>
       </c>
       <c r="I79" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="J79" t="n">
         <v>1</v>
@@ -5679,25 +5679,25 @@
         <v>50</v>
       </c>
       <c r="N79" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O79" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="P79" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="Q79" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="R79" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S79" t="n">
-        <v>60.99743812844282</v>
+        <v>37.35402933294375</v>
       </c>
       <c r="T79" t="n">
-        <v>4</v>
+        <v>99</v>
       </c>
     </row>
     <row r="80">
@@ -5712,7 +5712,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D80" t="n">
         <v>1</v>
@@ -5745,22 +5745,22 @@
         <v>50</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O80" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="P80" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="Q80" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="R80" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S80" t="n">
-        <v>63.26315549340273</v>
+        <v>60.99743812844282</v>
       </c>
       <c r="T80" t="n">
         <v>4</v>
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D81" t="n">
         <v>1</v>
@@ -5811,22 +5811,22 @@
         <v>50</v>
       </c>
       <c r="N81" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="P81" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="Q81" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="R81" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="S81" t="n">
-        <v>53.89148964378263</v>
+        <v>63.26315549340273</v>
       </c>
       <c r="T81" t="n">
         <v>4</v>
@@ -5844,7 +5844,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D82" t="n">
         <v>1</v>
@@ -5877,22 +5877,22 @@
         <v>50</v>
       </c>
       <c r="N82" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="O82" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P82" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="Q82" t="n">
         <v>10</v>
       </c>
       <c r="R82" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="S82" t="n">
-        <v>61.09729891301109</v>
+        <v>53.89148964378263</v>
       </c>
       <c r="T82" t="n">
         <v>4</v>
@@ -5910,7 +5910,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D83" t="n">
         <v>1</v>
@@ -5943,22 +5943,22 @@
         <v>50</v>
       </c>
       <c r="N83" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="O83" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="P83" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="Q83" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R83" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="S83" t="n">
-        <v>54.45241486626857</v>
+        <v>61.09729891301109</v>
       </c>
       <c r="T83" t="n">
         <v>4</v>
@@ -5972,14 +5972,14 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>config_2</t>
+          <t>config_1</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84" t="n">
         <v>0.9</v>
@@ -5991,7 +5991,7 @@
         <v>5</v>
       </c>
       <c r="H84" t="n">
-        <v>0.77</v>
+        <v>0.9</v>
       </c>
       <c r="I84" t="n">
         <v>5</v>
@@ -6012,19 +6012,19 @@
         <v>16</v>
       </c>
       <c r="O84" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="P84" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="Q84" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="R84" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="S84" t="n">
-        <v>63.21030899695449</v>
+        <v>54.45241486626857</v>
       </c>
       <c r="T84" t="n">
         <v>4</v>
@@ -6042,7 +6042,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D85" t="n">
         <v>2</v>
@@ -6075,22 +6075,22 @@
         <v>50</v>
       </c>
       <c r="N85" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="O85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P85" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="Q85" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R85" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="S85" t="n">
-        <v>51.6519701753148</v>
+        <v>63.21030899695449</v>
       </c>
       <c r="T85" t="n">
         <v>4</v>
@@ -6108,7 +6108,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D86" t="n">
         <v>2</v>
@@ -6141,22 +6141,22 @@
         <v>50</v>
       </c>
       <c r="N86" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P86" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q86" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="R86" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="S86" t="n">
-        <v>64.46103088747418</v>
+        <v>51.6519701753148</v>
       </c>
       <c r="T86" t="n">
         <v>4</v>
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
         <v>2</v>
@@ -6207,22 +6207,22 @@
         <v>50</v>
       </c>
       <c r="N87" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O87" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="Q87" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="R87" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S87" t="n">
-        <v>50.92435253976517</v>
+        <v>64.46103088747418</v>
       </c>
       <c r="T87" t="n">
         <v>4</v>
@@ -6240,7 +6240,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D88" t="n">
         <v>2</v>
@@ -6273,22 +6273,22 @@
         <v>50</v>
       </c>
       <c r="N88" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="O88" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P88" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="Q88" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="R88" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="S88" t="n">
-        <v>53.89148964378268</v>
+        <v>50.92435253976517</v>
       </c>
       <c r="T88" t="n">
         <v>4</v>
@@ -6297,19 +6297,19 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>run_2025-08-22_11-06-39</t>
+          <t>run_2025-08-21_22-11-53</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>config_1</t>
+          <t>config_2</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E89" t="n">
         <v>0.9</v>
@@ -6321,43 +6321,43 @@
         <v>5</v>
       </c>
       <c r="H89" t="n">
-        <v>0.9</v>
+        <v>0.77</v>
       </c>
       <c r="I89" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="J89" t="n">
         <v>1</v>
       </c>
       <c r="K89" t="n">
+        <v>5</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M89" t="n">
+        <v>50</v>
+      </c>
+      <c r="N89" t="n">
+        <v>4</v>
+      </c>
+      <c r="O89" t="n">
         <v>10</v>
       </c>
-      <c r="L89" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M89" t="n">
-        <v>50</v>
-      </c>
-      <c r="N89" t="n">
-        <v>20</v>
-      </c>
-      <c r="O89" t="n">
-        <v>0</v>
-      </c>
       <c r="P89" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="Q89" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="R89" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="S89" t="n">
-        <v>37.35402933294375</v>
+        <v>53.89148964378268</v>
       </c>
       <c r="T89" t="n">
-        <v>99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D90" t="n">
         <v>1</v>
@@ -6405,22 +6405,22 @@
         <v>50</v>
       </c>
       <c r="N90" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O90" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q90" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="R90" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="S90" t="n">
-        <v>37.38888331705508</v>
+        <v>37.35402933294375</v>
       </c>
       <c r="T90" t="n">
         <v>99</v>
@@ -6438,7 +6438,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D91" t="n">
         <v>1</v>
@@ -6471,22 +6471,22 @@
         <v>50</v>
       </c>
       <c r="N91" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="O91" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="P91" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="Q91" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="R91" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="S91" t="n">
-        <v>37.45559271642127</v>
+        <v>37.38888331705508</v>
       </c>
       <c r="T91" t="n">
         <v>99</v>
@@ -6504,7 +6504,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D92" t="n">
         <v>1</v>
@@ -6537,22 +6537,22 @@
         <v>50</v>
       </c>
       <c r="N92" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="O92" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R92" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="S92" t="n">
-        <v>50.86900424344032</v>
+        <v>37.45559271642127</v>
       </c>
       <c r="T92" t="n">
         <v>99</v>
@@ -6570,7 +6570,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D93" t="n">
         <v>1</v>
@@ -6603,22 +6603,22 @@
         <v>50</v>
       </c>
       <c r="N93" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O93" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="P93" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="Q93" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="R93" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="S93" t="n">
-        <v>37.35402933294379</v>
+        <v>50.86900424344032</v>
       </c>
       <c r="T93" t="n">
         <v>99</v>
@@ -6632,17 +6632,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>config_3</t>
+          <t>config_1</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="F94" t="n">
         <v>2</v>
@@ -6669,22 +6669,22 @@
         <v>50</v>
       </c>
       <c r="N94" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O94" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="P94" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="Q94" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="R94" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="S94" t="n">
-        <v>50.86900424344032</v>
+        <v>37.35402933294379</v>
       </c>
       <c r="T94" t="n">
         <v>99</v>
@@ -6702,7 +6702,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D95" t="n">
         <v>3</v>
@@ -6735,22 +6735,22 @@
         <v>50</v>
       </c>
       <c r="N95" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="P95" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="Q95" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="R95" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="S95" t="n">
-        <v>37.38888331705508</v>
+        <v>50.86900424344032</v>
       </c>
       <c r="T95" t="n">
         <v>99</v>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D96" t="n">
         <v>3</v>
@@ -6801,22 +6801,22 @@
         <v>50</v>
       </c>
       <c r="N96" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="O96" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q96" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R96" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="S96" t="n">
-        <v>50.86900424344025</v>
+        <v>37.38888331705508</v>
       </c>
       <c r="T96" t="n">
         <v>99</v>
@@ -6834,7 +6834,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D97" t="n">
         <v>3</v>
@@ -6867,22 +6867,22 @@
         <v>50</v>
       </c>
       <c r="N97" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="O97" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="P97" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q97" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R97" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="S97" t="n">
-        <v>37.35402933294375</v>
+        <v>50.86900424344025</v>
       </c>
       <c r="T97" t="n">
         <v>99</v>
@@ -6900,7 +6900,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D98" t="n">
         <v>3</v>
@@ -6933,22 +6933,22 @@
         <v>50</v>
       </c>
       <c r="N98" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="O98" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P98" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="Q98" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="R98" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="S98" t="n">
-        <v>38.62046726902093</v>
+        <v>37.35402933294375</v>
       </c>
       <c r="T98" t="n">
         <v>99</v>
@@ -6962,17 +6962,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>config_4</t>
+          <t>config_3</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E99" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="F99" t="n">
         <v>2</v>
@@ -6999,22 +6999,22 @@
         <v>50</v>
       </c>
       <c r="N99" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="O99" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Q99" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R99" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="S99" t="n">
-        <v>37.35402933294375</v>
+        <v>38.62046726902093</v>
       </c>
       <c r="T99" t="n">
         <v>99</v>
@@ -7032,7 +7032,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D100" t="n">
         <v>4</v>
@@ -7068,7 +7068,7 @@
         <v>28</v>
       </c>
       <c r="O100" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P100" t="n">
         <v>28</v>
@@ -7077,10 +7077,10 @@
         <v>28</v>
       </c>
       <c r="R100" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S100" t="n">
-        <v>37.35402933294379</v>
+        <v>37.35402933294375</v>
       </c>
       <c r="T100" t="n">
         <v>99</v>
@@ -7098,7 +7098,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D101" t="n">
         <v>4</v>
@@ -7131,19 +7131,19 @@
         <v>50</v>
       </c>
       <c r="N101" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O101" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P101" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q101" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="R101" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S101" t="n">
         <v>37.35402933294379</v>
@@ -7164,7 +7164,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D102" t="n">
         <v>4</v>
@@ -7197,22 +7197,22 @@
         <v>50</v>
       </c>
       <c r="N102" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="O102" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="P102" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Q102" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="R102" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="S102" t="n">
-        <v>37.35402933294375</v>
+        <v>37.35402933294379</v>
       </c>
       <c r="T102" t="n">
         <v>99</v>
@@ -7230,7 +7230,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D103" t="n">
         <v>4</v>
@@ -7263,22 +7263,22 @@
         <v>50</v>
       </c>
       <c r="N103" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="O103" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P103" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Q103" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="R103" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="S103" t="n">
-        <v>37.35402933294379</v>
+        <v>37.35402933294375</v>
       </c>
       <c r="T103" t="n">
         <v>99</v>
@@ -7292,17 +7292,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>config_2</t>
+          <t>config_4</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D104" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E104" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="F104" t="n">
         <v>2</v>
@@ -7329,22 +7329,22 @@
         <v>50</v>
       </c>
       <c r="N104" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="O104" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="P104" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="Q104" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="R104" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="S104" t="n">
-        <v>37.35402933294375</v>
+        <v>37.35402933294379</v>
       </c>
       <c r="T104" t="n">
         <v>99</v>
@@ -7362,7 +7362,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D105" t="n">
         <v>2</v>
@@ -7395,19 +7395,19 @@
         <v>50</v>
       </c>
       <c r="N105" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="O105" t="n">
         <v>14</v>
       </c>
       <c r="P105" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="Q105" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="R105" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="S105" t="n">
         <v>37.35402933294375</v>
@@ -7428,7 +7428,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D106" t="n">
         <v>2</v>
@@ -7461,19 +7461,19 @@
         <v>50</v>
       </c>
       <c r="N106" t="n">
+        <v>6</v>
+      </c>
+      <c r="O106" t="n">
         <v>14</v>
       </c>
-      <c r="O106" t="n">
-        <v>20</v>
-      </c>
       <c r="P106" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Q106" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="R106" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="S106" t="n">
         <v>37.35402933294375</v>
@@ -7494,7 +7494,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D107" t="n">
         <v>2</v>
@@ -7527,22 +7527,22 @@
         <v>50</v>
       </c>
       <c r="N107" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="O107" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P107" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="Q107" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="R107" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="S107" t="n">
-        <v>37.35402933294379</v>
+        <v>37.35402933294375</v>
       </c>
       <c r="T107" t="n">
         <v>99</v>
@@ -7560,7 +7560,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D108" t="n">
         <v>2</v>
@@ -7593,24 +7593,90 @@
         <v>50</v>
       </c>
       <c r="N108" t="n">
+        <v>26</v>
+      </c>
+      <c r="O108" t="n">
+        <v>21</v>
+      </c>
+      <c r="P108" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>26</v>
+      </c>
+      <c r="R108" t="n">
+        <v>28</v>
+      </c>
+      <c r="S108" t="n">
+        <v>37.35402933294379</v>
+      </c>
+      <c r="T108" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>run_2025-08-22_11-06-39</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>3</v>
+      </c>
+      <c r="D109" t="n">
+        <v>2</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F109" t="n">
+        <v>2</v>
+      </c>
+      <c r="G109" t="n">
+        <v>5</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I109" t="n">
+        <v>100</v>
+      </c>
+      <c r="J109" t="n">
+        <v>1</v>
+      </c>
+      <c r="K109" t="n">
+        <v>10</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M109" t="n">
+        <v>50</v>
+      </c>
+      <c r="N109" t="n">
         <v>0</v>
       </c>
-      <c r="O108" t="n">
+      <c r="O109" t="n">
         <v>22</v>
       </c>
-      <c r="P108" t="n">
+      <c r="P109" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
+      <c r="Q109" t="n">
         <v>0</v>
       </c>
-      <c r="R108" t="n">
+      <c r="R109" t="n">
         <v>0</v>
       </c>
-      <c r="S108" t="n">
+      <c r="S109" t="n">
         <v>37.35402933294375</v>
       </c>
-      <c r="T108" t="n">
+      <c r="T109" t="n">
         <v>99</v>
       </c>
     </row>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T422"/>
+  <dimension ref="A1:T518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -28338,6 +28338,6342 @@
         <v>19</v>
       </c>
     </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_10-42-29</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C423" t="n">
+        <v>3</v>
+      </c>
+      <c r="D423" t="n">
+        <v>1</v>
+      </c>
+      <c r="E423" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F423" t="n">
+        <v>2</v>
+      </c>
+      <c r="G423" t="n">
+        <v>5</v>
+      </c>
+      <c r="H423" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I423" t="n">
+        <v>20</v>
+      </c>
+      <c r="J423" t="n">
+        <v>1</v>
+      </c>
+      <c r="K423" t="n">
+        <v>5</v>
+      </c>
+      <c r="L423" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M423" t="n">
+        <v>50</v>
+      </c>
+      <c r="N423" t="n">
+        <v>1</v>
+      </c>
+      <c r="O423" t="n">
+        <v>11</v>
+      </c>
+      <c r="P423" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q423" t="n">
+        <v>22</v>
+      </c>
+      <c r="R423" t="n">
+        <v>1</v>
+      </c>
+      <c r="S423" t="n">
+        <v>52.9233610890987</v>
+      </c>
+      <c r="T423" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_10-42-29</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C424" t="n">
+        <v>4</v>
+      </c>
+      <c r="D424" t="n">
+        <v>1</v>
+      </c>
+      <c r="E424" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F424" t="n">
+        <v>2</v>
+      </c>
+      <c r="G424" t="n">
+        <v>5</v>
+      </c>
+      <c r="H424" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I424" t="n">
+        <v>20</v>
+      </c>
+      <c r="J424" t="n">
+        <v>1</v>
+      </c>
+      <c r="K424" t="n">
+        <v>5</v>
+      </c>
+      <c r="L424" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M424" t="n">
+        <v>50</v>
+      </c>
+      <c r="N424" t="n">
+        <v>4</v>
+      </c>
+      <c r="O424" t="n">
+        <v>9</v>
+      </c>
+      <c r="P424" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q424" t="n">
+        <v>3</v>
+      </c>
+      <c r="R424" t="n">
+        <v>10</v>
+      </c>
+      <c r="S424" t="n">
+        <v>51.62473861564388</v>
+      </c>
+      <c r="T424" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_10-42-29</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C425" t="n">
+        <v>5</v>
+      </c>
+      <c r="D425" t="n">
+        <v>1</v>
+      </c>
+      <c r="E425" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F425" t="n">
+        <v>2</v>
+      </c>
+      <c r="G425" t="n">
+        <v>5</v>
+      </c>
+      <c r="H425" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I425" t="n">
+        <v>20</v>
+      </c>
+      <c r="J425" t="n">
+        <v>1</v>
+      </c>
+      <c r="K425" t="n">
+        <v>5</v>
+      </c>
+      <c r="L425" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M425" t="n">
+        <v>50</v>
+      </c>
+      <c r="N425" t="n">
+        <v>29</v>
+      </c>
+      <c r="O425" t="n">
+        <v>20</v>
+      </c>
+      <c r="P425" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q425" t="n">
+        <v>29</v>
+      </c>
+      <c r="R425" t="n">
+        <v>29</v>
+      </c>
+      <c r="S425" t="n">
+        <v>53.8483132662859</v>
+      </c>
+      <c r="T425" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_10-42-29</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C426" t="n">
+        <v>1</v>
+      </c>
+      <c r="D426" t="n">
+        <v>2</v>
+      </c>
+      <c r="E426" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F426" t="n">
+        <v>2</v>
+      </c>
+      <c r="G426" t="n">
+        <v>5</v>
+      </c>
+      <c r="H426" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I426" t="n">
+        <v>20</v>
+      </c>
+      <c r="J426" t="n">
+        <v>1</v>
+      </c>
+      <c r="K426" t="n">
+        <v>5</v>
+      </c>
+      <c r="L426" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M426" t="n">
+        <v>50</v>
+      </c>
+      <c r="N426" t="n">
+        <v>26</v>
+      </c>
+      <c r="O426" t="n">
+        <v>3</v>
+      </c>
+      <c r="P426" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q426" t="n">
+        <v>26</v>
+      </c>
+      <c r="R426" t="n">
+        <v>3</v>
+      </c>
+      <c r="S426" t="n">
+        <v>54.59141343352625</v>
+      </c>
+      <c r="T426" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_10-42-29</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C427" t="n">
+        <v>2</v>
+      </c>
+      <c r="D427" t="n">
+        <v>2</v>
+      </c>
+      <c r="E427" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F427" t="n">
+        <v>2</v>
+      </c>
+      <c r="G427" t="n">
+        <v>5</v>
+      </c>
+      <c r="H427" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I427" t="n">
+        <v>20</v>
+      </c>
+      <c r="J427" t="n">
+        <v>1</v>
+      </c>
+      <c r="K427" t="n">
+        <v>5</v>
+      </c>
+      <c r="L427" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M427" t="n">
+        <v>50</v>
+      </c>
+      <c r="N427" t="n">
+        <v>17</v>
+      </c>
+      <c r="O427" t="n">
+        <v>28</v>
+      </c>
+      <c r="P427" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q427" t="n">
+        <v>3</v>
+      </c>
+      <c r="R427" t="n">
+        <v>28</v>
+      </c>
+      <c r="S427" t="n">
+        <v>53.65552547448785</v>
+      </c>
+      <c r="T427" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_10-42-29</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C428" t="n">
+        <v>3</v>
+      </c>
+      <c r="D428" t="n">
+        <v>2</v>
+      </c>
+      <c r="E428" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F428" t="n">
+        <v>2</v>
+      </c>
+      <c r="G428" t="n">
+        <v>5</v>
+      </c>
+      <c r="H428" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I428" t="n">
+        <v>20</v>
+      </c>
+      <c r="J428" t="n">
+        <v>1</v>
+      </c>
+      <c r="K428" t="n">
+        <v>5</v>
+      </c>
+      <c r="L428" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M428" t="n">
+        <v>50</v>
+      </c>
+      <c r="N428" t="n">
+        <v>1</v>
+      </c>
+      <c r="O428" t="n">
+        <v>10</v>
+      </c>
+      <c r="P428" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q428" t="n">
+        <v>23</v>
+      </c>
+      <c r="R428" t="n">
+        <v>10</v>
+      </c>
+      <c r="S428" t="n">
+        <v>60.70721345836029</v>
+      </c>
+      <c r="T428" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_10-45-32</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C429" t="n">
+        <v>1</v>
+      </c>
+      <c r="D429" t="n">
+        <v>1</v>
+      </c>
+      <c r="E429" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F429" t="n">
+        <v>2</v>
+      </c>
+      <c r="G429" t="n">
+        <v>5</v>
+      </c>
+      <c r="H429" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I429" t="n">
+        <v>20</v>
+      </c>
+      <c r="J429" t="n">
+        <v>1</v>
+      </c>
+      <c r="K429" t="n">
+        <v>5</v>
+      </c>
+      <c r="L429" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M429" t="n">
+        <v>50</v>
+      </c>
+      <c r="N429" t="n">
+        <v>14</v>
+      </c>
+      <c r="O429" t="n">
+        <v>11</v>
+      </c>
+      <c r="P429" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q429" t="n">
+        <v>27</v>
+      </c>
+      <c r="R429" t="n">
+        <v>16</v>
+      </c>
+      <c r="S429" t="n">
+        <v>52.54907489281376</v>
+      </c>
+      <c r="T429" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_10-45-32</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C430" t="n">
+        <v>2</v>
+      </c>
+      <c r="D430" t="n">
+        <v>1</v>
+      </c>
+      <c r="E430" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F430" t="n">
+        <v>2</v>
+      </c>
+      <c r="G430" t="n">
+        <v>5</v>
+      </c>
+      <c r="H430" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I430" t="n">
+        <v>20</v>
+      </c>
+      <c r="J430" t="n">
+        <v>1</v>
+      </c>
+      <c r="K430" t="n">
+        <v>5</v>
+      </c>
+      <c r="L430" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M430" t="n">
+        <v>50</v>
+      </c>
+      <c r="N430" t="n">
+        <v>27</v>
+      </c>
+      <c r="O430" t="n">
+        <v>2</v>
+      </c>
+      <c r="P430" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q430" t="n">
+        <v>16</v>
+      </c>
+      <c r="R430" t="n">
+        <v>3</v>
+      </c>
+      <c r="S430" t="n">
+        <v>53.5052698210404</v>
+      </c>
+      <c r="T430" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_10-45-32</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C431" t="n">
+        <v>3</v>
+      </c>
+      <c r="D431" t="n">
+        <v>1</v>
+      </c>
+      <c r="E431" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F431" t="n">
+        <v>2</v>
+      </c>
+      <c r="G431" t="n">
+        <v>5</v>
+      </c>
+      <c r="H431" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I431" t="n">
+        <v>20</v>
+      </c>
+      <c r="J431" t="n">
+        <v>1</v>
+      </c>
+      <c r="K431" t="n">
+        <v>5</v>
+      </c>
+      <c r="L431" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M431" t="n">
+        <v>50</v>
+      </c>
+      <c r="N431" t="n">
+        <v>12</v>
+      </c>
+      <c r="O431" t="n">
+        <v>23</v>
+      </c>
+      <c r="P431" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q431" t="n">
+        <v>5</v>
+      </c>
+      <c r="R431" t="n">
+        <v>24</v>
+      </c>
+      <c r="S431" t="n">
+        <v>61.88321685297359</v>
+      </c>
+      <c r="T431" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_10-45-32</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C432" t="n">
+        <v>4</v>
+      </c>
+      <c r="D432" t="n">
+        <v>1</v>
+      </c>
+      <c r="E432" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F432" t="n">
+        <v>2</v>
+      </c>
+      <c r="G432" t="n">
+        <v>5</v>
+      </c>
+      <c r="H432" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I432" t="n">
+        <v>20</v>
+      </c>
+      <c r="J432" t="n">
+        <v>1</v>
+      </c>
+      <c r="K432" t="n">
+        <v>5</v>
+      </c>
+      <c r="L432" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M432" t="n">
+        <v>50</v>
+      </c>
+      <c r="N432" t="n">
+        <v>18</v>
+      </c>
+      <c r="O432" t="n">
+        <v>24</v>
+      </c>
+      <c r="P432" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q432" t="n">
+        <v>1</v>
+      </c>
+      <c r="R432" t="n">
+        <v>25</v>
+      </c>
+      <c r="S432" t="n">
+        <v>61.98478023645107</v>
+      </c>
+      <c r="T432" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_10-45-32</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C433" t="n">
+        <v>5</v>
+      </c>
+      <c r="D433" t="n">
+        <v>1</v>
+      </c>
+      <c r="E433" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F433" t="n">
+        <v>2</v>
+      </c>
+      <c r="G433" t="n">
+        <v>5</v>
+      </c>
+      <c r="H433" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I433" t="n">
+        <v>20</v>
+      </c>
+      <c r="J433" t="n">
+        <v>1</v>
+      </c>
+      <c r="K433" t="n">
+        <v>5</v>
+      </c>
+      <c r="L433" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M433" t="n">
+        <v>50</v>
+      </c>
+      <c r="N433" t="n">
+        <v>2</v>
+      </c>
+      <c r="O433" t="n">
+        <v>23</v>
+      </c>
+      <c r="P433" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q433" t="n">
+        <v>20</v>
+      </c>
+      <c r="R433" t="n">
+        <v>22</v>
+      </c>
+      <c r="S433" t="n">
+        <v>74.49979099684903</v>
+      </c>
+      <c r="T433" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_10-45-32</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C434" t="n">
+        <v>1</v>
+      </c>
+      <c r="D434" t="n">
+        <v>2</v>
+      </c>
+      <c r="E434" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F434" t="n">
+        <v>2</v>
+      </c>
+      <c r="G434" t="n">
+        <v>5</v>
+      </c>
+      <c r="H434" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I434" t="n">
+        <v>20</v>
+      </c>
+      <c r="J434" t="n">
+        <v>1</v>
+      </c>
+      <c r="K434" t="n">
+        <v>5</v>
+      </c>
+      <c r="L434" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M434" t="n">
+        <v>50</v>
+      </c>
+      <c r="N434" t="n">
+        <v>2</v>
+      </c>
+      <c r="O434" t="n">
+        <v>2</v>
+      </c>
+      <c r="P434" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q434" t="n">
+        <v>2</v>
+      </c>
+      <c r="R434" t="n">
+        <v>3</v>
+      </c>
+      <c r="S434" t="n">
+        <v>51.2049689961018</v>
+      </c>
+      <c r="T434" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_10-45-32</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C435" t="n">
+        <v>2</v>
+      </c>
+      <c r="D435" t="n">
+        <v>2</v>
+      </c>
+      <c r="E435" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F435" t="n">
+        <v>2</v>
+      </c>
+      <c r="G435" t="n">
+        <v>5</v>
+      </c>
+      <c r="H435" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I435" t="n">
+        <v>20</v>
+      </c>
+      <c r="J435" t="n">
+        <v>1</v>
+      </c>
+      <c r="K435" t="n">
+        <v>5</v>
+      </c>
+      <c r="L435" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M435" t="n">
+        <v>50</v>
+      </c>
+      <c r="N435" t="n">
+        <v>1</v>
+      </c>
+      <c r="O435" t="n">
+        <v>25</v>
+      </c>
+      <c r="P435" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q435" t="n">
+        <v>25</v>
+      </c>
+      <c r="R435" t="n">
+        <v>3</v>
+      </c>
+      <c r="S435" t="n">
+        <v>61.71657403989328</v>
+      </c>
+      <c r="T435" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_10-45-32</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C436" t="n">
+        <v>3</v>
+      </c>
+      <c r="D436" t="n">
+        <v>2</v>
+      </c>
+      <c r="E436" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F436" t="n">
+        <v>2</v>
+      </c>
+      <c r="G436" t="n">
+        <v>5</v>
+      </c>
+      <c r="H436" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I436" t="n">
+        <v>20</v>
+      </c>
+      <c r="J436" t="n">
+        <v>1</v>
+      </c>
+      <c r="K436" t="n">
+        <v>5</v>
+      </c>
+      <c r="L436" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M436" t="n">
+        <v>50</v>
+      </c>
+      <c r="N436" t="n">
+        <v>30</v>
+      </c>
+      <c r="O436" t="n">
+        <v>13</v>
+      </c>
+      <c r="P436" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q436" t="n">
+        <v>30</v>
+      </c>
+      <c r="R436" t="n">
+        <v>30</v>
+      </c>
+      <c r="S436" t="n">
+        <v>37.35402933294375</v>
+      </c>
+      <c r="T436" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_10-45-32</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C437" t="n">
+        <v>4</v>
+      </c>
+      <c r="D437" t="n">
+        <v>2</v>
+      </c>
+      <c r="E437" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F437" t="n">
+        <v>2</v>
+      </c>
+      <c r="G437" t="n">
+        <v>5</v>
+      </c>
+      <c r="H437" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I437" t="n">
+        <v>20</v>
+      </c>
+      <c r="J437" t="n">
+        <v>1</v>
+      </c>
+      <c r="K437" t="n">
+        <v>5</v>
+      </c>
+      <c r="L437" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M437" t="n">
+        <v>50</v>
+      </c>
+      <c r="N437" t="n">
+        <v>20</v>
+      </c>
+      <c r="O437" t="n">
+        <v>21</v>
+      </c>
+      <c r="P437" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q437" t="n">
+        <v>3</v>
+      </c>
+      <c r="R437" t="n">
+        <v>22</v>
+      </c>
+      <c r="S437" t="n">
+        <v>75.83729011460709</v>
+      </c>
+      <c r="T437" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_10-45-32</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C438" t="n">
+        <v>5</v>
+      </c>
+      <c r="D438" t="n">
+        <v>2</v>
+      </c>
+      <c r="E438" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F438" t="n">
+        <v>2</v>
+      </c>
+      <c r="G438" t="n">
+        <v>5</v>
+      </c>
+      <c r="H438" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I438" t="n">
+        <v>20</v>
+      </c>
+      <c r="J438" t="n">
+        <v>1</v>
+      </c>
+      <c r="K438" t="n">
+        <v>5</v>
+      </c>
+      <c r="L438" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M438" t="n">
+        <v>50</v>
+      </c>
+      <c r="N438" t="n">
+        <v>29</v>
+      </c>
+      <c r="O438" t="n">
+        <v>23</v>
+      </c>
+      <c r="P438" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q438" t="n">
+        <v>29</v>
+      </c>
+      <c r="R438" t="n">
+        <v>13</v>
+      </c>
+      <c r="S438" t="n">
+        <v>66.50100684737578</v>
+      </c>
+      <c r="T438" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_10-55-09</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C439" t="n">
+        <v>1</v>
+      </c>
+      <c r="D439" t="n">
+        <v>1</v>
+      </c>
+      <c r="E439" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F439" t="n">
+        <v>2</v>
+      </c>
+      <c r="G439" t="n">
+        <v>5</v>
+      </c>
+      <c r="H439" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I439" t="n">
+        <v>20</v>
+      </c>
+      <c r="J439" t="n">
+        <v>1</v>
+      </c>
+      <c r="K439" t="n">
+        <v>5</v>
+      </c>
+      <c r="L439" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M439" t="n">
+        <v>50</v>
+      </c>
+      <c r="N439" t="n">
+        <v>13</v>
+      </c>
+      <c r="O439" t="n">
+        <v>8</v>
+      </c>
+      <c r="P439" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q439" t="n">
+        <v>8</v>
+      </c>
+      <c r="R439" t="n">
+        <v>23</v>
+      </c>
+      <c r="S439" t="n">
+        <v>62.03029149361637</v>
+      </c>
+      <c r="T439" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_10-55-09</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C440" t="n">
+        <v>2</v>
+      </c>
+      <c r="D440" t="n">
+        <v>1</v>
+      </c>
+      <c r="E440" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F440" t="n">
+        <v>2</v>
+      </c>
+      <c r="G440" t="n">
+        <v>5</v>
+      </c>
+      <c r="H440" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I440" t="n">
+        <v>20</v>
+      </c>
+      <c r="J440" t="n">
+        <v>1</v>
+      </c>
+      <c r="K440" t="n">
+        <v>5</v>
+      </c>
+      <c r="L440" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M440" t="n">
+        <v>50</v>
+      </c>
+      <c r="N440" t="n">
+        <v>0</v>
+      </c>
+      <c r="O440" t="n">
+        <v>21</v>
+      </c>
+      <c r="P440" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q440" t="n">
+        <v>24</v>
+      </c>
+      <c r="R440" t="n">
+        <v>26</v>
+      </c>
+      <c r="S440" t="n">
+        <v>53.23540479125701</v>
+      </c>
+      <c r="T440" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_10-55-09</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C441" t="n">
+        <v>3</v>
+      </c>
+      <c r="D441" t="n">
+        <v>1</v>
+      </c>
+      <c r="E441" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F441" t="n">
+        <v>2</v>
+      </c>
+      <c r="G441" t="n">
+        <v>5</v>
+      </c>
+      <c r="H441" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I441" t="n">
+        <v>20</v>
+      </c>
+      <c r="J441" t="n">
+        <v>1</v>
+      </c>
+      <c r="K441" t="n">
+        <v>5</v>
+      </c>
+      <c r="L441" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M441" t="n">
+        <v>50</v>
+      </c>
+      <c r="N441" t="n">
+        <v>8</v>
+      </c>
+      <c r="O441" t="n">
+        <v>27</v>
+      </c>
+      <c r="P441" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q441" t="n">
+        <v>8</v>
+      </c>
+      <c r="R441" t="n">
+        <v>27</v>
+      </c>
+      <c r="S441" t="n">
+        <v>38.75282632407595</v>
+      </c>
+      <c r="T441" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_10-55-09</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C442" t="n">
+        <v>4</v>
+      </c>
+      <c r="D442" t="n">
+        <v>1</v>
+      </c>
+      <c r="E442" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F442" t="n">
+        <v>2</v>
+      </c>
+      <c r="G442" t="n">
+        <v>5</v>
+      </c>
+      <c r="H442" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I442" t="n">
+        <v>20</v>
+      </c>
+      <c r="J442" t="n">
+        <v>1</v>
+      </c>
+      <c r="K442" t="n">
+        <v>5</v>
+      </c>
+      <c r="L442" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M442" t="n">
+        <v>50</v>
+      </c>
+      <c r="N442" t="n">
+        <v>27</v>
+      </c>
+      <c r="O442" t="n">
+        <v>7</v>
+      </c>
+      <c r="P442" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q442" t="n">
+        <v>29</v>
+      </c>
+      <c r="R442" t="n">
+        <v>29</v>
+      </c>
+      <c r="S442" t="n">
+        <v>52.32343788272181</v>
+      </c>
+      <c r="T442" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_10-55-09</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C443" t="n">
+        <v>5</v>
+      </c>
+      <c r="D443" t="n">
+        <v>1</v>
+      </c>
+      <c r="E443" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F443" t="n">
+        <v>2</v>
+      </c>
+      <c r="G443" t="n">
+        <v>5</v>
+      </c>
+      <c r="H443" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I443" t="n">
+        <v>20</v>
+      </c>
+      <c r="J443" t="n">
+        <v>1</v>
+      </c>
+      <c r="K443" t="n">
+        <v>5</v>
+      </c>
+      <c r="L443" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M443" t="n">
+        <v>50</v>
+      </c>
+      <c r="N443" t="n">
+        <v>0</v>
+      </c>
+      <c r="O443" t="n">
+        <v>6</v>
+      </c>
+      <c r="P443" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q443" t="n">
+        <v>0</v>
+      </c>
+      <c r="R443" t="n">
+        <v>7</v>
+      </c>
+      <c r="S443" t="n">
+        <v>54.54156208641643</v>
+      </c>
+      <c r="T443" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_10-55-09</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C444" t="n">
+        <v>1</v>
+      </c>
+      <c r="D444" t="n">
+        <v>2</v>
+      </c>
+      <c r="E444" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F444" t="n">
+        <v>2</v>
+      </c>
+      <c r="G444" t="n">
+        <v>5</v>
+      </c>
+      <c r="H444" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I444" t="n">
+        <v>20</v>
+      </c>
+      <c r="J444" t="n">
+        <v>1</v>
+      </c>
+      <c r="K444" t="n">
+        <v>5</v>
+      </c>
+      <c r="L444" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M444" t="n">
+        <v>50</v>
+      </c>
+      <c r="N444" t="n">
+        <v>6</v>
+      </c>
+      <c r="O444" t="n">
+        <v>30</v>
+      </c>
+      <c r="P444" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q444" t="n">
+        <v>22</v>
+      </c>
+      <c r="R444" t="n">
+        <v>13</v>
+      </c>
+      <c r="S444" t="n">
+        <v>65.19001390087831</v>
+      </c>
+      <c r="T444" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_10-55-09</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C445" t="n">
+        <v>2</v>
+      </c>
+      <c r="D445" t="n">
+        <v>2</v>
+      </c>
+      <c r="E445" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F445" t="n">
+        <v>2</v>
+      </c>
+      <c r="G445" t="n">
+        <v>5</v>
+      </c>
+      <c r="H445" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I445" t="n">
+        <v>20</v>
+      </c>
+      <c r="J445" t="n">
+        <v>1</v>
+      </c>
+      <c r="K445" t="n">
+        <v>5</v>
+      </c>
+      <c r="L445" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M445" t="n">
+        <v>50</v>
+      </c>
+      <c r="N445" t="n">
+        <v>0</v>
+      </c>
+      <c r="O445" t="n">
+        <v>29</v>
+      </c>
+      <c r="P445" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q445" t="n">
+        <v>8</v>
+      </c>
+      <c r="R445" t="n">
+        <v>10</v>
+      </c>
+      <c r="S445" t="n">
+        <v>67.48337751143566</v>
+      </c>
+      <c r="T445" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_10-55-09</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C446" t="n">
+        <v>3</v>
+      </c>
+      <c r="D446" t="n">
+        <v>2</v>
+      </c>
+      <c r="E446" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F446" t="n">
+        <v>2</v>
+      </c>
+      <c r="G446" t="n">
+        <v>5</v>
+      </c>
+      <c r="H446" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I446" t="n">
+        <v>20</v>
+      </c>
+      <c r="J446" t="n">
+        <v>1</v>
+      </c>
+      <c r="K446" t="n">
+        <v>5</v>
+      </c>
+      <c r="L446" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M446" t="n">
+        <v>50</v>
+      </c>
+      <c r="N446" t="n">
+        <v>9</v>
+      </c>
+      <c r="O446" t="n">
+        <v>3</v>
+      </c>
+      <c r="P446" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q446" t="n">
+        <v>9</v>
+      </c>
+      <c r="R446" t="n">
+        <v>11</v>
+      </c>
+      <c r="S446" t="n">
+        <v>37.45559271642123</v>
+      </c>
+      <c r="T446" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_10-55-09</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C447" t="n">
+        <v>4</v>
+      </c>
+      <c r="D447" t="n">
+        <v>2</v>
+      </c>
+      <c r="E447" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F447" t="n">
+        <v>2</v>
+      </c>
+      <c r="G447" t="n">
+        <v>5</v>
+      </c>
+      <c r="H447" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I447" t="n">
+        <v>20</v>
+      </c>
+      <c r="J447" t="n">
+        <v>1</v>
+      </c>
+      <c r="K447" t="n">
+        <v>5</v>
+      </c>
+      <c r="L447" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M447" t="n">
+        <v>50</v>
+      </c>
+      <c r="N447" t="n">
+        <v>5</v>
+      </c>
+      <c r="O447" t="n">
+        <v>13</v>
+      </c>
+      <c r="P447" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q447" t="n">
+        <v>21</v>
+      </c>
+      <c r="R447" t="n">
+        <v>5</v>
+      </c>
+      <c r="S447" t="n">
+        <v>52.9233610890987</v>
+      </c>
+      <c r="T447" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_10-55-09</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C448" t="n">
+        <v>5</v>
+      </c>
+      <c r="D448" t="n">
+        <v>2</v>
+      </c>
+      <c r="E448" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F448" t="n">
+        <v>2</v>
+      </c>
+      <c r="G448" t="n">
+        <v>5</v>
+      </c>
+      <c r="H448" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I448" t="n">
+        <v>20</v>
+      </c>
+      <c r="J448" t="n">
+        <v>1</v>
+      </c>
+      <c r="K448" t="n">
+        <v>5</v>
+      </c>
+      <c r="L448" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M448" t="n">
+        <v>50</v>
+      </c>
+      <c r="N448" t="n">
+        <v>0</v>
+      </c>
+      <c r="O448" t="n">
+        <v>26</v>
+      </c>
+      <c r="P448" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q448" t="n">
+        <v>31</v>
+      </c>
+      <c r="R448" t="n">
+        <v>0</v>
+      </c>
+      <c r="S448" t="n">
+        <v>76.14137479386967</v>
+      </c>
+      <c r="T448" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-02-09</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C449" t="n">
+        <v>1</v>
+      </c>
+      <c r="D449" t="n">
+        <v>1</v>
+      </c>
+      <c r="E449" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F449" t="n">
+        <v>2</v>
+      </c>
+      <c r="G449" t="n">
+        <v>5</v>
+      </c>
+      <c r="H449" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I449" t="n">
+        <v>20</v>
+      </c>
+      <c r="J449" t="n">
+        <v>1</v>
+      </c>
+      <c r="K449" t="n">
+        <v>5</v>
+      </c>
+      <c r="L449" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M449" t="n">
+        <v>50</v>
+      </c>
+      <c r="N449" t="n">
+        <v>17</v>
+      </c>
+      <c r="O449" t="n">
+        <v>12</v>
+      </c>
+      <c r="P449" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q449" t="n">
+        <v>17</v>
+      </c>
+      <c r="R449" t="n">
+        <v>17</v>
+      </c>
+      <c r="S449" t="n">
+        <v>51.1237412789847</v>
+      </c>
+      <c r="T449" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-02-09</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C450" t="n">
+        <v>2</v>
+      </c>
+      <c r="D450" t="n">
+        <v>1</v>
+      </c>
+      <c r="E450" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F450" t="n">
+        <v>2</v>
+      </c>
+      <c r="G450" t="n">
+        <v>5</v>
+      </c>
+      <c r="H450" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I450" t="n">
+        <v>20</v>
+      </c>
+      <c r="J450" t="n">
+        <v>1</v>
+      </c>
+      <c r="K450" t="n">
+        <v>5</v>
+      </c>
+      <c r="L450" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M450" t="n">
+        <v>50</v>
+      </c>
+      <c r="N450" t="n">
+        <v>20</v>
+      </c>
+      <c r="O450" t="n">
+        <v>5</v>
+      </c>
+      <c r="P450" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q450" t="n">
+        <v>10</v>
+      </c>
+      <c r="R450" t="n">
+        <v>20</v>
+      </c>
+      <c r="S450" t="n">
+        <v>52.95821507321003</v>
+      </c>
+      <c r="T450" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-02-09</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C451" t="n">
+        <v>3</v>
+      </c>
+      <c r="D451" t="n">
+        <v>1</v>
+      </c>
+      <c r="E451" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F451" t="n">
+        <v>2</v>
+      </c>
+      <c r="G451" t="n">
+        <v>5</v>
+      </c>
+      <c r="H451" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I451" t="n">
+        <v>20</v>
+      </c>
+      <c r="J451" t="n">
+        <v>1</v>
+      </c>
+      <c r="K451" t="n">
+        <v>5</v>
+      </c>
+      <c r="L451" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M451" t="n">
+        <v>50</v>
+      </c>
+      <c r="N451" t="n">
+        <v>5</v>
+      </c>
+      <c r="O451" t="n">
+        <v>6</v>
+      </c>
+      <c r="P451" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q451" t="n">
+        <v>14</v>
+      </c>
+      <c r="R451" t="n">
+        <v>6</v>
+      </c>
+      <c r="S451" t="n">
+        <v>59.4085478460318</v>
+      </c>
+      <c r="T451" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-02-09</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C452" t="n">
+        <v>4</v>
+      </c>
+      <c r="D452" t="n">
+        <v>1</v>
+      </c>
+      <c r="E452" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F452" t="n">
+        <v>2</v>
+      </c>
+      <c r="G452" t="n">
+        <v>5</v>
+      </c>
+      <c r="H452" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I452" t="n">
+        <v>20</v>
+      </c>
+      <c r="J452" t="n">
+        <v>1</v>
+      </c>
+      <c r="K452" t="n">
+        <v>5</v>
+      </c>
+      <c r="L452" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M452" t="n">
+        <v>50</v>
+      </c>
+      <c r="N452" t="n">
+        <v>25</v>
+      </c>
+      <c r="O452" t="n">
+        <v>10</v>
+      </c>
+      <c r="P452" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q452" t="n">
+        <v>10</v>
+      </c>
+      <c r="R452" t="n">
+        <v>25</v>
+      </c>
+      <c r="S452" t="n">
+        <v>59.52452060561028</v>
+      </c>
+      <c r="T452" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-02-09</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C453" t="n">
+        <v>5</v>
+      </c>
+      <c r="D453" t="n">
+        <v>1</v>
+      </c>
+      <c r="E453" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F453" t="n">
+        <v>2</v>
+      </c>
+      <c r="G453" t="n">
+        <v>5</v>
+      </c>
+      <c r="H453" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I453" t="n">
+        <v>20</v>
+      </c>
+      <c r="J453" t="n">
+        <v>1</v>
+      </c>
+      <c r="K453" t="n">
+        <v>5</v>
+      </c>
+      <c r="L453" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M453" t="n">
+        <v>50</v>
+      </c>
+      <c r="N453" t="n">
+        <v>0</v>
+      </c>
+      <c r="O453" t="n">
+        <v>27</v>
+      </c>
+      <c r="P453" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q453" t="n">
+        <v>0</v>
+      </c>
+      <c r="R453" t="n">
+        <v>14</v>
+      </c>
+      <c r="S453" t="n">
+        <v>50.3210096574379</v>
+      </c>
+      <c r="T453" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-02-09</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C454" t="n">
+        <v>1</v>
+      </c>
+      <c r="D454" t="n">
+        <v>2</v>
+      </c>
+      <c r="E454" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F454" t="n">
+        <v>2</v>
+      </c>
+      <c r="G454" t="n">
+        <v>5</v>
+      </c>
+      <c r="H454" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I454" t="n">
+        <v>20</v>
+      </c>
+      <c r="J454" t="n">
+        <v>1</v>
+      </c>
+      <c r="K454" t="n">
+        <v>5</v>
+      </c>
+      <c r="L454" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M454" t="n">
+        <v>50</v>
+      </c>
+      <c r="N454" t="n">
+        <v>28</v>
+      </c>
+      <c r="O454" t="n">
+        <v>21</v>
+      </c>
+      <c r="P454" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q454" t="n">
+        <v>28</v>
+      </c>
+      <c r="R454" t="n">
+        <v>21</v>
+      </c>
+      <c r="S454" t="n">
+        <v>54.52576377783733</v>
+      </c>
+      <c r="T454" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-02-09</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C455" t="n">
+        <v>2</v>
+      </c>
+      <c r="D455" t="n">
+        <v>2</v>
+      </c>
+      <c r="E455" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F455" t="n">
+        <v>2</v>
+      </c>
+      <c r="G455" t="n">
+        <v>5</v>
+      </c>
+      <c r="H455" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I455" t="n">
+        <v>20</v>
+      </c>
+      <c r="J455" t="n">
+        <v>1</v>
+      </c>
+      <c r="K455" t="n">
+        <v>5</v>
+      </c>
+      <c r="L455" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M455" t="n">
+        <v>50</v>
+      </c>
+      <c r="N455" t="n">
+        <v>2</v>
+      </c>
+      <c r="O455" t="n">
+        <v>30</v>
+      </c>
+      <c r="P455" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q455" t="n">
+        <v>2</v>
+      </c>
+      <c r="R455" t="n">
+        <v>30</v>
+      </c>
+      <c r="S455" t="n">
+        <v>54.59141343352621</v>
+      </c>
+      <c r="T455" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-02-09</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C456" t="n">
+        <v>3</v>
+      </c>
+      <c r="D456" t="n">
+        <v>2</v>
+      </c>
+      <c r="E456" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F456" t="n">
+        <v>2</v>
+      </c>
+      <c r="G456" t="n">
+        <v>5</v>
+      </c>
+      <c r="H456" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I456" t="n">
+        <v>20</v>
+      </c>
+      <c r="J456" t="n">
+        <v>1</v>
+      </c>
+      <c r="K456" t="n">
+        <v>5</v>
+      </c>
+      <c r="L456" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M456" t="n">
+        <v>50</v>
+      </c>
+      <c r="N456" t="n">
+        <v>26</v>
+      </c>
+      <c r="O456" t="n">
+        <v>18</v>
+      </c>
+      <c r="P456" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q456" t="n">
+        <v>26</v>
+      </c>
+      <c r="R456" t="n">
+        <v>27</v>
+      </c>
+      <c r="S456" t="n">
+        <v>49.35402933294385</v>
+      </c>
+      <c r="T456" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-02-09</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C457" t="n">
+        <v>4</v>
+      </c>
+      <c r="D457" t="n">
+        <v>2</v>
+      </c>
+      <c r="E457" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F457" t="n">
+        <v>2</v>
+      </c>
+      <c r="G457" t="n">
+        <v>5</v>
+      </c>
+      <c r="H457" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I457" t="n">
+        <v>20</v>
+      </c>
+      <c r="J457" t="n">
+        <v>1</v>
+      </c>
+      <c r="K457" t="n">
+        <v>5</v>
+      </c>
+      <c r="L457" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M457" t="n">
+        <v>50</v>
+      </c>
+      <c r="N457" t="n">
+        <v>21</v>
+      </c>
+      <c r="O457" t="n">
+        <v>15</v>
+      </c>
+      <c r="P457" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q457" t="n">
+        <v>21</v>
+      </c>
+      <c r="R457" t="n">
+        <v>15</v>
+      </c>
+      <c r="S457" t="n">
+        <v>38.5347021941225</v>
+      </c>
+      <c r="T457" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-02-09</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C458" t="n">
+        <v>5</v>
+      </c>
+      <c r="D458" t="n">
+        <v>2</v>
+      </c>
+      <c r="E458" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F458" t="n">
+        <v>2</v>
+      </c>
+      <c r="G458" t="n">
+        <v>5</v>
+      </c>
+      <c r="H458" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I458" t="n">
+        <v>20</v>
+      </c>
+      <c r="J458" t="n">
+        <v>1</v>
+      </c>
+      <c r="K458" t="n">
+        <v>5</v>
+      </c>
+      <c r="L458" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M458" t="n">
+        <v>50</v>
+      </c>
+      <c r="N458" t="n">
+        <v>4</v>
+      </c>
+      <c r="O458" t="n">
+        <v>9</v>
+      </c>
+      <c r="P458" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q458" t="n">
+        <v>3</v>
+      </c>
+      <c r="R458" t="n">
+        <v>10</v>
+      </c>
+      <c r="S458" t="n">
+        <v>61.52943925112034</v>
+      </c>
+      <c r="T458" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-09-00</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C459" t="n">
+        <v>1</v>
+      </c>
+      <c r="D459" t="n">
+        <v>1</v>
+      </c>
+      <c r="E459" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F459" t="n">
+        <v>2</v>
+      </c>
+      <c r="G459" t="n">
+        <v>5</v>
+      </c>
+      <c r="H459" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I459" t="n">
+        <v>20</v>
+      </c>
+      <c r="J459" t="n">
+        <v>1</v>
+      </c>
+      <c r="K459" t="n">
+        <v>5</v>
+      </c>
+      <c r="L459" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M459" t="n">
+        <v>50</v>
+      </c>
+      <c r="N459" t="n">
+        <v>19</v>
+      </c>
+      <c r="O459" t="n">
+        <v>4</v>
+      </c>
+      <c r="P459" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q459" t="n">
+        <v>19</v>
+      </c>
+      <c r="R459" t="n">
+        <v>19</v>
+      </c>
+      <c r="S459" t="n">
+        <v>54.10889308894615</v>
+      </c>
+      <c r="T459" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-09-00</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C460" t="n">
+        <v>2</v>
+      </c>
+      <c r="D460" t="n">
+        <v>1</v>
+      </c>
+      <c r="E460" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F460" t="n">
+        <v>2</v>
+      </c>
+      <c r="G460" t="n">
+        <v>5</v>
+      </c>
+      <c r="H460" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I460" t="n">
+        <v>20</v>
+      </c>
+      <c r="J460" t="n">
+        <v>1</v>
+      </c>
+      <c r="K460" t="n">
+        <v>5</v>
+      </c>
+      <c r="L460" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M460" t="n">
+        <v>50</v>
+      </c>
+      <c r="N460" t="n">
+        <v>20</v>
+      </c>
+      <c r="O460" t="n">
+        <v>18</v>
+      </c>
+      <c r="P460" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q460" t="n">
+        <v>14</v>
+      </c>
+      <c r="R460" t="n">
+        <v>14</v>
+      </c>
+      <c r="S460" t="n">
+        <v>51.57128449758621</v>
+      </c>
+      <c r="T460" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-09-00</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C461" t="n">
+        <v>3</v>
+      </c>
+      <c r="D461" t="n">
+        <v>1</v>
+      </c>
+      <c r="E461" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F461" t="n">
+        <v>2</v>
+      </c>
+      <c r="G461" t="n">
+        <v>5</v>
+      </c>
+      <c r="H461" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I461" t="n">
+        <v>20</v>
+      </c>
+      <c r="J461" t="n">
+        <v>1</v>
+      </c>
+      <c r="K461" t="n">
+        <v>5</v>
+      </c>
+      <c r="L461" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M461" t="n">
+        <v>50</v>
+      </c>
+      <c r="N461" t="n">
+        <v>29</v>
+      </c>
+      <c r="O461" t="n">
+        <v>0</v>
+      </c>
+      <c r="P461" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q461" t="n">
+        <v>11</v>
+      </c>
+      <c r="R461" t="n">
+        <v>31</v>
+      </c>
+      <c r="S461" t="n">
+        <v>59.74852937006577</v>
+      </c>
+      <c r="T461" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-09-00</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C462" t="n">
+        <v>4</v>
+      </c>
+      <c r="D462" t="n">
+        <v>1</v>
+      </c>
+      <c r="E462" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F462" t="n">
+        <v>2</v>
+      </c>
+      <c r="G462" t="n">
+        <v>5</v>
+      </c>
+      <c r="H462" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I462" t="n">
+        <v>20</v>
+      </c>
+      <c r="J462" t="n">
+        <v>1</v>
+      </c>
+      <c r="K462" t="n">
+        <v>5</v>
+      </c>
+      <c r="L462" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M462" t="n">
+        <v>50</v>
+      </c>
+      <c r="N462" t="n">
+        <v>30</v>
+      </c>
+      <c r="O462" t="n">
+        <v>22</v>
+      </c>
+      <c r="P462" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q462" t="n">
+        <v>30</v>
+      </c>
+      <c r="R462" t="n">
+        <v>23</v>
+      </c>
+      <c r="S462" t="n">
+        <v>38.51890388554344</v>
+      </c>
+      <c r="T462" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-09-00</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C463" t="n">
+        <v>5</v>
+      </c>
+      <c r="D463" t="n">
+        <v>1</v>
+      </c>
+      <c r="E463" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F463" t="n">
+        <v>2</v>
+      </c>
+      <c r="G463" t="n">
+        <v>5</v>
+      </c>
+      <c r="H463" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I463" t="n">
+        <v>20</v>
+      </c>
+      <c r="J463" t="n">
+        <v>1</v>
+      </c>
+      <c r="K463" t="n">
+        <v>5</v>
+      </c>
+      <c r="L463" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M463" t="n">
+        <v>50</v>
+      </c>
+      <c r="N463" t="n">
+        <v>23</v>
+      </c>
+      <c r="O463" t="n">
+        <v>18</v>
+      </c>
+      <c r="P463" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q463" t="n">
+        <v>23</v>
+      </c>
+      <c r="R463" t="n">
+        <v>22</v>
+      </c>
+      <c r="S463" t="n">
+        <v>67.25328500124057</v>
+      </c>
+      <c r="T463" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-09-00</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C464" t="n">
+        <v>1</v>
+      </c>
+      <c r="D464" t="n">
+        <v>2</v>
+      </c>
+      <c r="E464" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F464" t="n">
+        <v>2</v>
+      </c>
+      <c r="G464" t="n">
+        <v>5</v>
+      </c>
+      <c r="H464" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I464" t="n">
+        <v>20</v>
+      </c>
+      <c r="J464" t="n">
+        <v>1</v>
+      </c>
+      <c r="K464" t="n">
+        <v>5</v>
+      </c>
+      <c r="L464" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M464" t="n">
+        <v>50</v>
+      </c>
+      <c r="N464" t="n">
+        <v>25</v>
+      </c>
+      <c r="O464" t="n">
+        <v>31</v>
+      </c>
+      <c r="P464" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q464" t="n">
+        <v>30</v>
+      </c>
+      <c r="R464" t="n">
+        <v>25</v>
+      </c>
+      <c r="S464" t="n">
+        <v>66.47082608684525</v>
+      </c>
+      <c r="T464" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-09-00</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C465" t="n">
+        <v>2</v>
+      </c>
+      <c r="D465" t="n">
+        <v>2</v>
+      </c>
+      <c r="E465" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F465" t="n">
+        <v>2</v>
+      </c>
+      <c r="G465" t="n">
+        <v>5</v>
+      </c>
+      <c r="H465" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I465" t="n">
+        <v>20</v>
+      </c>
+      <c r="J465" t="n">
+        <v>1</v>
+      </c>
+      <c r="K465" t="n">
+        <v>5</v>
+      </c>
+      <c r="L465" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M465" t="n">
+        <v>50</v>
+      </c>
+      <c r="N465" t="n">
+        <v>19</v>
+      </c>
+      <c r="O465" t="n">
+        <v>14</v>
+      </c>
+      <c r="P465" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q465" t="n">
+        <v>19</v>
+      </c>
+      <c r="R465" t="n">
+        <v>20</v>
+      </c>
+      <c r="S465" t="n">
+        <v>49.38888331705514</v>
+      </c>
+      <c r="T465" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-09-00</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C466" t="n">
+        <v>3</v>
+      </c>
+      <c r="D466" t="n">
+        <v>2</v>
+      </c>
+      <c r="E466" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F466" t="n">
+        <v>2</v>
+      </c>
+      <c r="G466" t="n">
+        <v>5</v>
+      </c>
+      <c r="H466" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I466" t="n">
+        <v>20</v>
+      </c>
+      <c r="J466" t="n">
+        <v>1</v>
+      </c>
+      <c r="K466" t="n">
+        <v>5</v>
+      </c>
+      <c r="L466" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M466" t="n">
+        <v>50</v>
+      </c>
+      <c r="N466" t="n">
+        <v>10</v>
+      </c>
+      <c r="O466" t="n">
+        <v>18</v>
+      </c>
+      <c r="P466" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q466" t="n">
+        <v>23</v>
+      </c>
+      <c r="R466" t="n">
+        <v>10</v>
+      </c>
+      <c r="S466" t="n">
+        <v>52.9233610890987</v>
+      </c>
+      <c r="T466" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-09-00</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C467" t="n">
+        <v>4</v>
+      </c>
+      <c r="D467" t="n">
+        <v>2</v>
+      </c>
+      <c r="E467" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F467" t="n">
+        <v>2</v>
+      </c>
+      <c r="G467" t="n">
+        <v>5</v>
+      </c>
+      <c r="H467" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I467" t="n">
+        <v>20</v>
+      </c>
+      <c r="J467" t="n">
+        <v>1</v>
+      </c>
+      <c r="K467" t="n">
+        <v>5</v>
+      </c>
+      <c r="L467" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M467" t="n">
+        <v>50</v>
+      </c>
+      <c r="N467" t="n">
+        <v>24</v>
+      </c>
+      <c r="O467" t="n">
+        <v>25</v>
+      </c>
+      <c r="P467" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q467" t="n">
+        <v>2</v>
+      </c>
+      <c r="R467" t="n">
+        <v>24</v>
+      </c>
+      <c r="S467" t="n">
+        <v>50.86900424344032</v>
+      </c>
+      <c r="T467" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-09-00</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C468" t="n">
+        <v>5</v>
+      </c>
+      <c r="D468" t="n">
+        <v>2</v>
+      </c>
+      <c r="E468" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F468" t="n">
+        <v>2</v>
+      </c>
+      <c r="G468" t="n">
+        <v>5</v>
+      </c>
+      <c r="H468" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I468" t="n">
+        <v>20</v>
+      </c>
+      <c r="J468" t="n">
+        <v>1</v>
+      </c>
+      <c r="K468" t="n">
+        <v>5</v>
+      </c>
+      <c r="L468" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M468" t="n">
+        <v>50</v>
+      </c>
+      <c r="N468" t="n">
+        <v>10</v>
+      </c>
+      <c r="O468" t="n">
+        <v>25</v>
+      </c>
+      <c r="P468" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q468" t="n">
+        <v>10</v>
+      </c>
+      <c r="R468" t="n">
+        <v>26</v>
+      </c>
+      <c r="S468" t="n">
+        <v>56.40323383063933</v>
+      </c>
+      <c r="T468" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-15-57</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C469" t="n">
+        <v>1</v>
+      </c>
+      <c r="D469" t="n">
+        <v>1</v>
+      </c>
+      <c r="E469" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F469" t="n">
+        <v>2</v>
+      </c>
+      <c r="G469" t="n">
+        <v>5</v>
+      </c>
+      <c r="H469" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I469" t="n">
+        <v>20</v>
+      </c>
+      <c r="J469" t="n">
+        <v>1</v>
+      </c>
+      <c r="K469" t="n">
+        <v>5</v>
+      </c>
+      <c r="L469" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M469" t="n">
+        <v>50</v>
+      </c>
+      <c r="N469" t="n">
+        <v>20</v>
+      </c>
+      <c r="O469" t="n">
+        <v>3</v>
+      </c>
+      <c r="P469" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q469" t="n">
+        <v>2</v>
+      </c>
+      <c r="R469" t="n">
+        <v>22</v>
+      </c>
+      <c r="S469" t="n">
+        <v>52.65939263578401</v>
+      </c>
+      <c r="T469" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-15-57</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C470" t="n">
+        <v>2</v>
+      </c>
+      <c r="D470" t="n">
+        <v>1</v>
+      </c>
+      <c r="E470" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F470" t="n">
+        <v>2</v>
+      </c>
+      <c r="G470" t="n">
+        <v>5</v>
+      </c>
+      <c r="H470" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I470" t="n">
+        <v>20</v>
+      </c>
+      <c r="J470" t="n">
+        <v>1</v>
+      </c>
+      <c r="K470" t="n">
+        <v>5</v>
+      </c>
+      <c r="L470" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M470" t="n">
+        <v>50</v>
+      </c>
+      <c r="N470" t="n">
+        <v>15</v>
+      </c>
+      <c r="O470" t="n">
+        <v>17</v>
+      </c>
+      <c r="P470" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q470" t="n">
+        <v>29</v>
+      </c>
+      <c r="R470" t="n">
+        <v>17</v>
+      </c>
+      <c r="S470" t="n">
+        <v>52.51422090870241</v>
+      </c>
+      <c r="T470" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-15-57</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C471" t="n">
+        <v>3</v>
+      </c>
+      <c r="D471" t="n">
+        <v>1</v>
+      </c>
+      <c r="E471" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F471" t="n">
+        <v>2</v>
+      </c>
+      <c r="G471" t="n">
+        <v>5</v>
+      </c>
+      <c r="H471" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I471" t="n">
+        <v>20</v>
+      </c>
+      <c r="J471" t="n">
+        <v>1</v>
+      </c>
+      <c r="K471" t="n">
+        <v>5</v>
+      </c>
+      <c r="L471" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M471" t="n">
+        <v>50</v>
+      </c>
+      <c r="N471" t="n">
+        <v>31</v>
+      </c>
+      <c r="O471" t="n">
+        <v>21</v>
+      </c>
+      <c r="P471" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q471" t="n">
+        <v>20</v>
+      </c>
+      <c r="R471" t="n">
+        <v>20</v>
+      </c>
+      <c r="S471" t="n">
+        <v>52.32727973261095</v>
+      </c>
+      <c r="T471" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-15-57</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C472" t="n">
+        <v>4</v>
+      </c>
+      <c r="D472" t="n">
+        <v>1</v>
+      </c>
+      <c r="E472" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F472" t="n">
+        <v>2</v>
+      </c>
+      <c r="G472" t="n">
+        <v>5</v>
+      </c>
+      <c r="H472" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I472" t="n">
+        <v>20</v>
+      </c>
+      <c r="J472" t="n">
+        <v>1</v>
+      </c>
+      <c r="K472" t="n">
+        <v>5</v>
+      </c>
+      <c r="L472" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M472" t="n">
+        <v>50</v>
+      </c>
+      <c r="N472" t="n">
+        <v>17</v>
+      </c>
+      <c r="O472" t="n">
+        <v>29</v>
+      </c>
+      <c r="P472" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q472" t="n">
+        <v>29</v>
+      </c>
+      <c r="R472" t="n">
+        <v>17</v>
+      </c>
+      <c r="S472" t="n">
+        <v>60.39682846497484</v>
+      </c>
+      <c r="T472" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-15-57</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C473" t="n">
+        <v>5</v>
+      </c>
+      <c r="D473" t="n">
+        <v>1</v>
+      </c>
+      <c r="E473" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F473" t="n">
+        <v>2</v>
+      </c>
+      <c r="G473" t="n">
+        <v>5</v>
+      </c>
+      <c r="H473" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I473" t="n">
+        <v>20</v>
+      </c>
+      <c r="J473" t="n">
+        <v>1</v>
+      </c>
+      <c r="K473" t="n">
+        <v>5</v>
+      </c>
+      <c r="L473" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M473" t="n">
+        <v>50</v>
+      </c>
+      <c r="N473" t="n">
+        <v>1</v>
+      </c>
+      <c r="O473" t="n">
+        <v>22</v>
+      </c>
+      <c r="P473" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q473" t="n">
+        <v>22</v>
+      </c>
+      <c r="R473" t="n">
+        <v>23</v>
+      </c>
+      <c r="S473" t="n">
+        <v>52.65939263578407</v>
+      </c>
+      <c r="T473" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-15-57</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C474" t="n">
+        <v>1</v>
+      </c>
+      <c r="D474" t="n">
+        <v>2</v>
+      </c>
+      <c r="E474" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F474" t="n">
+        <v>2</v>
+      </c>
+      <c r="G474" t="n">
+        <v>5</v>
+      </c>
+      <c r="H474" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I474" t="n">
+        <v>20</v>
+      </c>
+      <c r="J474" t="n">
+        <v>1</v>
+      </c>
+      <c r="K474" t="n">
+        <v>5</v>
+      </c>
+      <c r="L474" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M474" t="n">
+        <v>50</v>
+      </c>
+      <c r="N474" t="n">
+        <v>27</v>
+      </c>
+      <c r="O474" t="n">
+        <v>28</v>
+      </c>
+      <c r="P474" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q474" t="n">
+        <v>2</v>
+      </c>
+      <c r="R474" t="n">
+        <v>29</v>
+      </c>
+      <c r="S474" t="n">
+        <v>50.86900424344039</v>
+      </c>
+      <c r="T474" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-15-57</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C475" t="n">
+        <v>2</v>
+      </c>
+      <c r="D475" t="n">
+        <v>2</v>
+      </c>
+      <c r="E475" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F475" t="n">
+        <v>2</v>
+      </c>
+      <c r="G475" t="n">
+        <v>5</v>
+      </c>
+      <c r="H475" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I475" t="n">
+        <v>20</v>
+      </c>
+      <c r="J475" t="n">
+        <v>1</v>
+      </c>
+      <c r="K475" t="n">
+        <v>5</v>
+      </c>
+      <c r="L475" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M475" t="n">
+        <v>50</v>
+      </c>
+      <c r="N475" t="n">
+        <v>5</v>
+      </c>
+      <c r="O475" t="n">
+        <v>13</v>
+      </c>
+      <c r="P475" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q475" t="n">
+        <v>14</v>
+      </c>
+      <c r="R475" t="n">
+        <v>20</v>
+      </c>
+      <c r="S475" t="n">
+        <v>68.13211530446605</v>
+      </c>
+      <c r="T475" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-15-57</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C476" t="n">
+        <v>3</v>
+      </c>
+      <c r="D476" t="n">
+        <v>2</v>
+      </c>
+      <c r="E476" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F476" t="n">
+        <v>2</v>
+      </c>
+      <c r="G476" t="n">
+        <v>5</v>
+      </c>
+      <c r="H476" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I476" t="n">
+        <v>20</v>
+      </c>
+      <c r="J476" t="n">
+        <v>1</v>
+      </c>
+      <c r="K476" t="n">
+        <v>5</v>
+      </c>
+      <c r="L476" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M476" t="n">
+        <v>50</v>
+      </c>
+      <c r="N476" t="n">
+        <v>15</v>
+      </c>
+      <c r="O476" t="n">
+        <v>1</v>
+      </c>
+      <c r="P476" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q476" t="n">
+        <v>15</v>
+      </c>
+      <c r="R476" t="n">
+        <v>1</v>
+      </c>
+      <c r="S476" t="n">
+        <v>56.33652443127318</v>
+      </c>
+      <c r="T476" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-15-57</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C477" t="n">
+        <v>4</v>
+      </c>
+      <c r="D477" t="n">
+        <v>2</v>
+      </c>
+      <c r="E477" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F477" t="n">
+        <v>2</v>
+      </c>
+      <c r="G477" t="n">
+        <v>5</v>
+      </c>
+      <c r="H477" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I477" t="n">
+        <v>20</v>
+      </c>
+      <c r="J477" t="n">
+        <v>1</v>
+      </c>
+      <c r="K477" t="n">
+        <v>5</v>
+      </c>
+      <c r="L477" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M477" t="n">
+        <v>50</v>
+      </c>
+      <c r="N477" t="n">
+        <v>5</v>
+      </c>
+      <c r="O477" t="n">
+        <v>23</v>
+      </c>
+      <c r="P477" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q477" t="n">
+        <v>5</v>
+      </c>
+      <c r="R477" t="n">
+        <v>5</v>
+      </c>
+      <c r="S477" t="n">
+        <v>53.14798575357145</v>
+      </c>
+      <c r="T477" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-15-57</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C478" t="n">
+        <v>5</v>
+      </c>
+      <c r="D478" t="n">
+        <v>2</v>
+      </c>
+      <c r="E478" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F478" t="n">
+        <v>2</v>
+      </c>
+      <c r="G478" t="n">
+        <v>5</v>
+      </c>
+      <c r="H478" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I478" t="n">
+        <v>20</v>
+      </c>
+      <c r="J478" t="n">
+        <v>1</v>
+      </c>
+      <c r="K478" t="n">
+        <v>5</v>
+      </c>
+      <c r="L478" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M478" t="n">
+        <v>50</v>
+      </c>
+      <c r="N478" t="n">
+        <v>9</v>
+      </c>
+      <c r="O478" t="n">
+        <v>22</v>
+      </c>
+      <c r="P478" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q478" t="n">
+        <v>9</v>
+      </c>
+      <c r="R478" t="n">
+        <v>16</v>
+      </c>
+      <c r="S478" t="n">
+        <v>50.21944627396041</v>
+      </c>
+      <c r="T478" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-22-54</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C479" t="n">
+        <v>1</v>
+      </c>
+      <c r="D479" t="n">
+        <v>1</v>
+      </c>
+      <c r="E479" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F479" t="n">
+        <v>2</v>
+      </c>
+      <c r="G479" t="n">
+        <v>5</v>
+      </c>
+      <c r="H479" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I479" t="n">
+        <v>20</v>
+      </c>
+      <c r="J479" t="n">
+        <v>1</v>
+      </c>
+      <c r="K479" t="n">
+        <v>5</v>
+      </c>
+      <c r="L479" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M479" t="n">
+        <v>50</v>
+      </c>
+      <c r="N479" t="n">
+        <v>28</v>
+      </c>
+      <c r="O479" t="n">
+        <v>28</v>
+      </c>
+      <c r="P479" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q479" t="n">
+        <v>1</v>
+      </c>
+      <c r="R479" t="n">
+        <v>30</v>
+      </c>
+      <c r="S479" t="n">
+        <v>50.86900424344032</v>
+      </c>
+      <c r="T479" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-22-54</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C480" t="n">
+        <v>2</v>
+      </c>
+      <c r="D480" t="n">
+        <v>1</v>
+      </c>
+      <c r="E480" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F480" t="n">
+        <v>2</v>
+      </c>
+      <c r="G480" t="n">
+        <v>5</v>
+      </c>
+      <c r="H480" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I480" t="n">
+        <v>20</v>
+      </c>
+      <c r="J480" t="n">
+        <v>1</v>
+      </c>
+      <c r="K480" t="n">
+        <v>5</v>
+      </c>
+      <c r="L480" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M480" t="n">
+        <v>50</v>
+      </c>
+      <c r="N480" t="n">
+        <v>7</v>
+      </c>
+      <c r="O480" t="n">
+        <v>7</v>
+      </c>
+      <c r="P480" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q480" t="n">
+        <v>3</v>
+      </c>
+      <c r="R480" t="n">
+        <v>9</v>
+      </c>
+      <c r="S480" t="n">
+        <v>76.26986120733696</v>
+      </c>
+      <c r="T480" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-22-54</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C481" t="n">
+        <v>3</v>
+      </c>
+      <c r="D481" t="n">
+        <v>1</v>
+      </c>
+      <c r="E481" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F481" t="n">
+        <v>2</v>
+      </c>
+      <c r="G481" t="n">
+        <v>5</v>
+      </c>
+      <c r="H481" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I481" t="n">
+        <v>20</v>
+      </c>
+      <c r="J481" t="n">
+        <v>1</v>
+      </c>
+      <c r="K481" t="n">
+        <v>5</v>
+      </c>
+      <c r="L481" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M481" t="n">
+        <v>50</v>
+      </c>
+      <c r="N481" t="n">
+        <v>0</v>
+      </c>
+      <c r="O481" t="n">
+        <v>15</v>
+      </c>
+      <c r="P481" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q481" t="n">
+        <v>14</v>
+      </c>
+      <c r="R481" t="n">
+        <v>2</v>
+      </c>
+      <c r="S481" t="n">
+        <v>52.46860960980335</v>
+      </c>
+      <c r="T481" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-22-54</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C482" t="n">
+        <v>4</v>
+      </c>
+      <c r="D482" t="n">
+        <v>1</v>
+      </c>
+      <c r="E482" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F482" t="n">
+        <v>2</v>
+      </c>
+      <c r="G482" t="n">
+        <v>5</v>
+      </c>
+      <c r="H482" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I482" t="n">
+        <v>20</v>
+      </c>
+      <c r="J482" t="n">
+        <v>1</v>
+      </c>
+      <c r="K482" t="n">
+        <v>5</v>
+      </c>
+      <c r="L482" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M482" t="n">
+        <v>50</v>
+      </c>
+      <c r="N482" t="n">
+        <v>15</v>
+      </c>
+      <c r="O482" t="n">
+        <v>1</v>
+      </c>
+      <c r="P482" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q482" t="n">
+        <v>6</v>
+      </c>
+      <c r="R482" t="n">
+        <v>1</v>
+      </c>
+      <c r="S482" t="n">
+        <v>76.54749786282919</v>
+      </c>
+      <c r="T482" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-22-54</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C483" t="n">
+        <v>5</v>
+      </c>
+      <c r="D483" t="n">
+        <v>1</v>
+      </c>
+      <c r="E483" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F483" t="n">
+        <v>2</v>
+      </c>
+      <c r="G483" t="n">
+        <v>5</v>
+      </c>
+      <c r="H483" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I483" t="n">
+        <v>20</v>
+      </c>
+      <c r="J483" t="n">
+        <v>1</v>
+      </c>
+      <c r="K483" t="n">
+        <v>5</v>
+      </c>
+      <c r="L483" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M483" t="n">
+        <v>50</v>
+      </c>
+      <c r="N483" t="n">
+        <v>29</v>
+      </c>
+      <c r="O483" t="n">
+        <v>1</v>
+      </c>
+      <c r="P483" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q483" t="n">
+        <v>20</v>
+      </c>
+      <c r="R483" t="n">
+        <v>2</v>
+      </c>
+      <c r="S483" t="n">
+        <v>53.48947151246131</v>
+      </c>
+      <c r="T483" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-22-54</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C484" t="n">
+        <v>1</v>
+      </c>
+      <c r="D484" t="n">
+        <v>2</v>
+      </c>
+      <c r="E484" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F484" t="n">
+        <v>2</v>
+      </c>
+      <c r="G484" t="n">
+        <v>5</v>
+      </c>
+      <c r="H484" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I484" t="n">
+        <v>20</v>
+      </c>
+      <c r="J484" t="n">
+        <v>1</v>
+      </c>
+      <c r="K484" t="n">
+        <v>5</v>
+      </c>
+      <c r="L484" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M484" t="n">
+        <v>50</v>
+      </c>
+      <c r="N484" t="n">
+        <v>4</v>
+      </c>
+      <c r="O484" t="n">
+        <v>21</v>
+      </c>
+      <c r="P484" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q484" t="n">
+        <v>0</v>
+      </c>
+      <c r="R484" t="n">
+        <v>0</v>
+      </c>
+      <c r="S484" t="n">
+        <v>58.21539595024683</v>
+      </c>
+      <c r="T484" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-22-54</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C485" t="n">
+        <v>2</v>
+      </c>
+      <c r="D485" t="n">
+        <v>2</v>
+      </c>
+      <c r="E485" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F485" t="n">
+        <v>2</v>
+      </c>
+      <c r="G485" t="n">
+        <v>5</v>
+      </c>
+      <c r="H485" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I485" t="n">
+        <v>20</v>
+      </c>
+      <c r="J485" t="n">
+        <v>1</v>
+      </c>
+      <c r="K485" t="n">
+        <v>5</v>
+      </c>
+      <c r="L485" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M485" t="n">
+        <v>50</v>
+      </c>
+      <c r="N485" t="n">
+        <v>26</v>
+      </c>
+      <c r="O485" t="n">
+        <v>21</v>
+      </c>
+      <c r="P485" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q485" t="n">
+        <v>26</v>
+      </c>
+      <c r="R485" t="n">
+        <v>26</v>
+      </c>
+      <c r="S485" t="n">
+        <v>53.84831326628594</v>
+      </c>
+      <c r="T485" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-22-54</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C486" t="n">
+        <v>3</v>
+      </c>
+      <c r="D486" t="n">
+        <v>2</v>
+      </c>
+      <c r="E486" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F486" t="n">
+        <v>2</v>
+      </c>
+      <c r="G486" t="n">
+        <v>5</v>
+      </c>
+      <c r="H486" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I486" t="n">
+        <v>20</v>
+      </c>
+      <c r="J486" t="n">
+        <v>1</v>
+      </c>
+      <c r="K486" t="n">
+        <v>5</v>
+      </c>
+      <c r="L486" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M486" t="n">
+        <v>50</v>
+      </c>
+      <c r="N486" t="n">
+        <v>25</v>
+      </c>
+      <c r="O486" t="n">
+        <v>24</v>
+      </c>
+      <c r="P486" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q486" t="n">
+        <v>24</v>
+      </c>
+      <c r="R486" t="n">
+        <v>25</v>
+      </c>
+      <c r="S486" t="n">
+        <v>55.29040839476545</v>
+      </c>
+      <c r="T486" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-22-54</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C487" t="n">
+        <v>4</v>
+      </c>
+      <c r="D487" t="n">
+        <v>2</v>
+      </c>
+      <c r="E487" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F487" t="n">
+        <v>2</v>
+      </c>
+      <c r="G487" t="n">
+        <v>5</v>
+      </c>
+      <c r="H487" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I487" t="n">
+        <v>20</v>
+      </c>
+      <c r="J487" t="n">
+        <v>1</v>
+      </c>
+      <c r="K487" t="n">
+        <v>5</v>
+      </c>
+      <c r="L487" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M487" t="n">
+        <v>50</v>
+      </c>
+      <c r="N487" t="n">
+        <v>30</v>
+      </c>
+      <c r="O487" t="n">
+        <v>31</v>
+      </c>
+      <c r="P487" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q487" t="n">
+        <v>30</v>
+      </c>
+      <c r="R487" t="n">
+        <v>19</v>
+      </c>
+      <c r="S487" t="n">
+        <v>54.61464970018741</v>
+      </c>
+      <c r="T487" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-22-54</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C488" t="n">
+        <v>5</v>
+      </c>
+      <c r="D488" t="n">
+        <v>2</v>
+      </c>
+      <c r="E488" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F488" t="n">
+        <v>2</v>
+      </c>
+      <c r="G488" t="n">
+        <v>5</v>
+      </c>
+      <c r="H488" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I488" t="n">
+        <v>20</v>
+      </c>
+      <c r="J488" t="n">
+        <v>1</v>
+      </c>
+      <c r="K488" t="n">
+        <v>5</v>
+      </c>
+      <c r="L488" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M488" t="n">
+        <v>50</v>
+      </c>
+      <c r="N488" t="n">
+        <v>31</v>
+      </c>
+      <c r="O488" t="n">
+        <v>2</v>
+      </c>
+      <c r="P488" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q488" t="n">
+        <v>31</v>
+      </c>
+      <c r="R488" t="n">
+        <v>13</v>
+      </c>
+      <c r="S488" t="n">
+        <v>50.25430025807179</v>
+      </c>
+      <c r="T488" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-29-49</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C489" t="n">
+        <v>1</v>
+      </c>
+      <c r="D489" t="n">
+        <v>1</v>
+      </c>
+      <c r="E489" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F489" t="n">
+        <v>2</v>
+      </c>
+      <c r="G489" t="n">
+        <v>5</v>
+      </c>
+      <c r="H489" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I489" t="n">
+        <v>20</v>
+      </c>
+      <c r="J489" t="n">
+        <v>1</v>
+      </c>
+      <c r="K489" t="n">
+        <v>5</v>
+      </c>
+      <c r="L489" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M489" t="n">
+        <v>50</v>
+      </c>
+      <c r="N489" t="n">
+        <v>17</v>
+      </c>
+      <c r="O489" t="n">
+        <v>23</v>
+      </c>
+      <c r="P489" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q489" t="n">
+        <v>1</v>
+      </c>
+      <c r="R489" t="n">
+        <v>1</v>
+      </c>
+      <c r="S489" t="n">
+        <v>54.45558403529955</v>
+      </c>
+      <c r="T489" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-29-49</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C490" t="n">
+        <v>2</v>
+      </c>
+      <c r="D490" t="n">
+        <v>1</v>
+      </c>
+      <c r="E490" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F490" t="n">
+        <v>2</v>
+      </c>
+      <c r="G490" t="n">
+        <v>5</v>
+      </c>
+      <c r="H490" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I490" t="n">
+        <v>20</v>
+      </c>
+      <c r="J490" t="n">
+        <v>1</v>
+      </c>
+      <c r="K490" t="n">
+        <v>5</v>
+      </c>
+      <c r="L490" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M490" t="n">
+        <v>50</v>
+      </c>
+      <c r="N490" t="n">
+        <v>28</v>
+      </c>
+      <c r="O490" t="n">
+        <v>1</v>
+      </c>
+      <c r="P490" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q490" t="n">
+        <v>28</v>
+      </c>
+      <c r="R490" t="n">
+        <v>28</v>
+      </c>
+      <c r="S490" t="n">
+        <v>37.35402933294375</v>
+      </c>
+      <c r="T490" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-29-49</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C491" t="n">
+        <v>3</v>
+      </c>
+      <c r="D491" t="n">
+        <v>1</v>
+      </c>
+      <c r="E491" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F491" t="n">
+        <v>2</v>
+      </c>
+      <c r="G491" t="n">
+        <v>5</v>
+      </c>
+      <c r="H491" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I491" t="n">
+        <v>20</v>
+      </c>
+      <c r="J491" t="n">
+        <v>1</v>
+      </c>
+      <c r="K491" t="n">
+        <v>5</v>
+      </c>
+      <c r="L491" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M491" t="n">
+        <v>50</v>
+      </c>
+      <c r="N491" t="n">
+        <v>14</v>
+      </c>
+      <c r="O491" t="n">
+        <v>23</v>
+      </c>
+      <c r="P491" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q491" t="n">
+        <v>14</v>
+      </c>
+      <c r="R491" t="n">
+        <v>15</v>
+      </c>
+      <c r="S491" t="n">
+        <v>49.35402933294376</v>
+      </c>
+      <c r="T491" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-29-49</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C492" t="n">
+        <v>4</v>
+      </c>
+      <c r="D492" t="n">
+        <v>1</v>
+      </c>
+      <c r="E492" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F492" t="n">
+        <v>2</v>
+      </c>
+      <c r="G492" t="n">
+        <v>5</v>
+      </c>
+      <c r="H492" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I492" t="n">
+        <v>20</v>
+      </c>
+      <c r="J492" t="n">
+        <v>1</v>
+      </c>
+      <c r="K492" t="n">
+        <v>5</v>
+      </c>
+      <c r="L492" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M492" t="n">
+        <v>50</v>
+      </c>
+      <c r="N492" t="n">
+        <v>30</v>
+      </c>
+      <c r="O492" t="n">
+        <v>31</v>
+      </c>
+      <c r="P492" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q492" t="n">
+        <v>7</v>
+      </c>
+      <c r="R492" t="n">
+        <v>9</v>
+      </c>
+      <c r="S492" t="n">
+        <v>53.03791448991957</v>
+      </c>
+      <c r="T492" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-29-49</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C493" t="n">
+        <v>5</v>
+      </c>
+      <c r="D493" t="n">
+        <v>1</v>
+      </c>
+      <c r="E493" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F493" t="n">
+        <v>2</v>
+      </c>
+      <c r="G493" t="n">
+        <v>5</v>
+      </c>
+      <c r="H493" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I493" t="n">
+        <v>20</v>
+      </c>
+      <c r="J493" t="n">
+        <v>1</v>
+      </c>
+      <c r="K493" t="n">
+        <v>5</v>
+      </c>
+      <c r="L493" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M493" t="n">
+        <v>50</v>
+      </c>
+      <c r="N493" t="n">
+        <v>14</v>
+      </c>
+      <c r="O493" t="n">
+        <v>15</v>
+      </c>
+      <c r="P493" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q493" t="n">
+        <v>14</v>
+      </c>
+      <c r="R493" t="n">
+        <v>15</v>
+      </c>
+      <c r="S493" t="n">
+        <v>52.28156057341502</v>
+      </c>
+      <c r="T493" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-29-49</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C494" t="n">
+        <v>1</v>
+      </c>
+      <c r="D494" t="n">
+        <v>2</v>
+      </c>
+      <c r="E494" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F494" t="n">
+        <v>2</v>
+      </c>
+      <c r="G494" t="n">
+        <v>5</v>
+      </c>
+      <c r="H494" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I494" t="n">
+        <v>20</v>
+      </c>
+      <c r="J494" t="n">
+        <v>1</v>
+      </c>
+      <c r="K494" t="n">
+        <v>5</v>
+      </c>
+      <c r="L494" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M494" t="n">
+        <v>50</v>
+      </c>
+      <c r="N494" t="n">
+        <v>5</v>
+      </c>
+      <c r="O494" t="n">
+        <v>28</v>
+      </c>
+      <c r="P494" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q494" t="n">
+        <v>15</v>
+      </c>
+      <c r="R494" t="n">
+        <v>28</v>
+      </c>
+      <c r="S494" t="n">
+        <v>60.85862818894759</v>
+      </c>
+      <c r="T494" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-29-49</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C495" t="n">
+        <v>2</v>
+      </c>
+      <c r="D495" t="n">
+        <v>2</v>
+      </c>
+      <c r="E495" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F495" t="n">
+        <v>2</v>
+      </c>
+      <c r="G495" t="n">
+        <v>5</v>
+      </c>
+      <c r="H495" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I495" t="n">
+        <v>20</v>
+      </c>
+      <c r="J495" t="n">
+        <v>1</v>
+      </c>
+      <c r="K495" t="n">
+        <v>5</v>
+      </c>
+      <c r="L495" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M495" t="n">
+        <v>50</v>
+      </c>
+      <c r="N495" t="n">
+        <v>26</v>
+      </c>
+      <c r="O495" t="n">
+        <v>0</v>
+      </c>
+      <c r="P495" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q495" t="n">
+        <v>26</v>
+      </c>
+      <c r="R495" t="n">
+        <v>28</v>
+      </c>
+      <c r="S495" t="n">
+        <v>53.63558990635911</v>
+      </c>
+      <c r="T495" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-29-49</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C496" t="n">
+        <v>3</v>
+      </c>
+      <c r="D496" t="n">
+        <v>2</v>
+      </c>
+      <c r="E496" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F496" t="n">
+        <v>2</v>
+      </c>
+      <c r="G496" t="n">
+        <v>5</v>
+      </c>
+      <c r="H496" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I496" t="n">
+        <v>20</v>
+      </c>
+      <c r="J496" t="n">
+        <v>1</v>
+      </c>
+      <c r="K496" t="n">
+        <v>5</v>
+      </c>
+      <c r="L496" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M496" t="n">
+        <v>50</v>
+      </c>
+      <c r="N496" t="n">
+        <v>2</v>
+      </c>
+      <c r="O496" t="n">
+        <v>7</v>
+      </c>
+      <c r="P496" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q496" t="n">
+        <v>2</v>
+      </c>
+      <c r="R496" t="n">
+        <v>8</v>
+      </c>
+      <c r="S496" t="n">
+        <v>53.08596936999517</v>
+      </c>
+      <c r="T496" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-29-49</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C497" t="n">
+        <v>4</v>
+      </c>
+      <c r="D497" t="n">
+        <v>2</v>
+      </c>
+      <c r="E497" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F497" t="n">
+        <v>2</v>
+      </c>
+      <c r="G497" t="n">
+        <v>5</v>
+      </c>
+      <c r="H497" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I497" t="n">
+        <v>20</v>
+      </c>
+      <c r="J497" t="n">
+        <v>1</v>
+      </c>
+      <c r="K497" t="n">
+        <v>5</v>
+      </c>
+      <c r="L497" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M497" t="n">
+        <v>50</v>
+      </c>
+      <c r="N497" t="n">
+        <v>1</v>
+      </c>
+      <c r="O497" t="n">
+        <v>8</v>
+      </c>
+      <c r="P497" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q497" t="n">
+        <v>1</v>
+      </c>
+      <c r="R497" t="n">
+        <v>2</v>
+      </c>
+      <c r="S497" t="n">
+        <v>66.24351323907793</v>
+      </c>
+      <c r="T497" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-29-49</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C498" t="n">
+        <v>5</v>
+      </c>
+      <c r="D498" t="n">
+        <v>2</v>
+      </c>
+      <c r="E498" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F498" t="n">
+        <v>2</v>
+      </c>
+      <c r="G498" t="n">
+        <v>5</v>
+      </c>
+      <c r="H498" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I498" t="n">
+        <v>20</v>
+      </c>
+      <c r="J498" t="n">
+        <v>1</v>
+      </c>
+      <c r="K498" t="n">
+        <v>5</v>
+      </c>
+      <c r="L498" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M498" t="n">
+        <v>50</v>
+      </c>
+      <c r="N498" t="n">
+        <v>1</v>
+      </c>
+      <c r="O498" t="n">
+        <v>17</v>
+      </c>
+      <c r="P498" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q498" t="n">
+        <v>18</v>
+      </c>
+      <c r="R498" t="n">
+        <v>18</v>
+      </c>
+      <c r="S498" t="n">
+        <v>52.9582150732101</v>
+      </c>
+      <c r="T498" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-38-26</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C499" t="n">
+        <v>1</v>
+      </c>
+      <c r="D499" t="n">
+        <v>1</v>
+      </c>
+      <c r="E499" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F499" t="n">
+        <v>2</v>
+      </c>
+      <c r="G499" t="n">
+        <v>5</v>
+      </c>
+      <c r="H499" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I499" t="n">
+        <v>20</v>
+      </c>
+      <c r="J499" t="n">
+        <v>1</v>
+      </c>
+      <c r="K499" t="n">
+        <v>5</v>
+      </c>
+      <c r="L499" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M499" t="n">
+        <v>50</v>
+      </c>
+      <c r="N499" t="n">
+        <v>23</v>
+      </c>
+      <c r="O499" t="n">
+        <v>31</v>
+      </c>
+      <c r="P499" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q499" t="n">
+        <v>0</v>
+      </c>
+      <c r="R499" t="n">
+        <v>2</v>
+      </c>
+      <c r="S499" t="n">
+        <v>54.49350720634074</v>
+      </c>
+      <c r="T499" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-38-26</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C500" t="n">
+        <v>2</v>
+      </c>
+      <c r="D500" t="n">
+        <v>1</v>
+      </c>
+      <c r="E500" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F500" t="n">
+        <v>2</v>
+      </c>
+      <c r="G500" t="n">
+        <v>5</v>
+      </c>
+      <c r="H500" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I500" t="n">
+        <v>20</v>
+      </c>
+      <c r="J500" t="n">
+        <v>1</v>
+      </c>
+      <c r="K500" t="n">
+        <v>5</v>
+      </c>
+      <c r="L500" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M500" t="n">
+        <v>50</v>
+      </c>
+      <c r="N500" t="n">
+        <v>3</v>
+      </c>
+      <c r="O500" t="n">
+        <v>3</v>
+      </c>
+      <c r="P500" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q500" t="n">
+        <v>3</v>
+      </c>
+      <c r="R500" t="n">
+        <v>4</v>
+      </c>
+      <c r="S500" t="n">
+        <v>51.90529650881621</v>
+      </c>
+      <c r="T500" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-38-26</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C501" t="n">
+        <v>3</v>
+      </c>
+      <c r="D501" t="n">
+        <v>1</v>
+      </c>
+      <c r="E501" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F501" t="n">
+        <v>2</v>
+      </c>
+      <c r="G501" t="n">
+        <v>5</v>
+      </c>
+      <c r="H501" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I501" t="n">
+        <v>20</v>
+      </c>
+      <c r="J501" t="n">
+        <v>1</v>
+      </c>
+      <c r="K501" t="n">
+        <v>5</v>
+      </c>
+      <c r="L501" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M501" t="n">
+        <v>50</v>
+      </c>
+      <c r="N501" t="n">
+        <v>9</v>
+      </c>
+      <c r="O501" t="n">
+        <v>9</v>
+      </c>
+      <c r="P501" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q501" t="n">
+        <v>14</v>
+      </c>
+      <c r="R501" t="n">
+        <v>16</v>
+      </c>
+      <c r="S501" t="n">
+        <v>52.14680395122429</v>
+      </c>
+      <c r="T501" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-38-26</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C502" t="n">
+        <v>4</v>
+      </c>
+      <c r="D502" t="n">
+        <v>1</v>
+      </c>
+      <c r="E502" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F502" t="n">
+        <v>2</v>
+      </c>
+      <c r="G502" t="n">
+        <v>5</v>
+      </c>
+      <c r="H502" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I502" t="n">
+        <v>20</v>
+      </c>
+      <c r="J502" t="n">
+        <v>1</v>
+      </c>
+      <c r="K502" t="n">
+        <v>5</v>
+      </c>
+      <c r="L502" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M502" t="n">
+        <v>50</v>
+      </c>
+      <c r="N502" t="n">
+        <v>29</v>
+      </c>
+      <c r="O502" t="n">
+        <v>18</v>
+      </c>
+      <c r="P502" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q502" t="n">
+        <v>17</v>
+      </c>
+      <c r="R502" t="n">
+        <v>17</v>
+      </c>
+      <c r="S502" t="n">
+        <v>52.27161201030091</v>
+      </c>
+      <c r="T502" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-38-26</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C503" t="n">
+        <v>5</v>
+      </c>
+      <c r="D503" t="n">
+        <v>1</v>
+      </c>
+      <c r="E503" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F503" t="n">
+        <v>2</v>
+      </c>
+      <c r="G503" t="n">
+        <v>5</v>
+      </c>
+      <c r="H503" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I503" t="n">
+        <v>20</v>
+      </c>
+      <c r="J503" t="n">
+        <v>1</v>
+      </c>
+      <c r="K503" t="n">
+        <v>5</v>
+      </c>
+      <c r="L503" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M503" t="n">
+        <v>50</v>
+      </c>
+      <c r="N503" t="n">
+        <v>10</v>
+      </c>
+      <c r="O503" t="n">
+        <v>26</v>
+      </c>
+      <c r="P503" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q503" t="n">
+        <v>12</v>
+      </c>
+      <c r="R503" t="n">
+        <v>11</v>
+      </c>
+      <c r="S503" t="n">
+        <v>77.02492447257622</v>
+      </c>
+      <c r="T503" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-38-26</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C504" t="n">
+        <v>1</v>
+      </c>
+      <c r="D504" t="n">
+        <v>2</v>
+      </c>
+      <c r="E504" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F504" t="n">
+        <v>2</v>
+      </c>
+      <c r="G504" t="n">
+        <v>5</v>
+      </c>
+      <c r="H504" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I504" t="n">
+        <v>20</v>
+      </c>
+      <c r="J504" t="n">
+        <v>1</v>
+      </c>
+      <c r="K504" t="n">
+        <v>5</v>
+      </c>
+      <c r="L504" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M504" t="n">
+        <v>50</v>
+      </c>
+      <c r="N504" t="n">
+        <v>28</v>
+      </c>
+      <c r="O504" t="n">
+        <v>9</v>
+      </c>
+      <c r="P504" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q504" t="n">
+        <v>30</v>
+      </c>
+      <c r="R504" t="n">
+        <v>28</v>
+      </c>
+      <c r="S504" t="n">
+        <v>64.32343788272175</v>
+      </c>
+      <c r="T504" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-38-26</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C505" t="n">
+        <v>2</v>
+      </c>
+      <c r="D505" t="n">
+        <v>2</v>
+      </c>
+      <c r="E505" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F505" t="n">
+        <v>2</v>
+      </c>
+      <c r="G505" t="n">
+        <v>5</v>
+      </c>
+      <c r="H505" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I505" t="n">
+        <v>20</v>
+      </c>
+      <c r="J505" t="n">
+        <v>1</v>
+      </c>
+      <c r="K505" t="n">
+        <v>5</v>
+      </c>
+      <c r="L505" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M505" t="n">
+        <v>50</v>
+      </c>
+      <c r="N505" t="n">
+        <v>15</v>
+      </c>
+      <c r="O505" t="n">
+        <v>19</v>
+      </c>
+      <c r="P505" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q505" t="n">
+        <v>15</v>
+      </c>
+      <c r="R505" t="n">
+        <v>15</v>
+      </c>
+      <c r="S505" t="n">
+        <v>53.44131238598635</v>
+      </c>
+      <c r="T505" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-38-26</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C506" t="n">
+        <v>3</v>
+      </c>
+      <c r="D506" t="n">
+        <v>2</v>
+      </c>
+      <c r="E506" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F506" t="n">
+        <v>2</v>
+      </c>
+      <c r="G506" t="n">
+        <v>5</v>
+      </c>
+      <c r="H506" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I506" t="n">
+        <v>20</v>
+      </c>
+      <c r="J506" t="n">
+        <v>1</v>
+      </c>
+      <c r="K506" t="n">
+        <v>5</v>
+      </c>
+      <c r="L506" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M506" t="n">
+        <v>50</v>
+      </c>
+      <c r="N506" t="n">
+        <v>1</v>
+      </c>
+      <c r="O506" t="n">
+        <v>16</v>
+      </c>
+      <c r="P506" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q506" t="n">
+        <v>1</v>
+      </c>
+      <c r="R506" t="n">
+        <v>3</v>
+      </c>
+      <c r="S506" t="n">
+        <v>37.35402933294379</v>
+      </c>
+      <c r="T506" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-38-26</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C507" t="n">
+        <v>4</v>
+      </c>
+      <c r="D507" t="n">
+        <v>2</v>
+      </c>
+      <c r="E507" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F507" t="n">
+        <v>2</v>
+      </c>
+      <c r="G507" t="n">
+        <v>5</v>
+      </c>
+      <c r="H507" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I507" t="n">
+        <v>20</v>
+      </c>
+      <c r="J507" t="n">
+        <v>1</v>
+      </c>
+      <c r="K507" t="n">
+        <v>5</v>
+      </c>
+      <c r="L507" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M507" t="n">
+        <v>50</v>
+      </c>
+      <c r="N507" t="n">
+        <v>19</v>
+      </c>
+      <c r="O507" t="n">
+        <v>14</v>
+      </c>
+      <c r="P507" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q507" t="n">
+        <v>19</v>
+      </c>
+      <c r="R507" t="n">
+        <v>19</v>
+      </c>
+      <c r="S507" t="n">
+        <v>54.10889308894615</v>
+      </c>
+      <c r="T507" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-38-26</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C508" t="n">
+        <v>5</v>
+      </c>
+      <c r="D508" t="n">
+        <v>2</v>
+      </c>
+      <c r="E508" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F508" t="n">
+        <v>2</v>
+      </c>
+      <c r="G508" t="n">
+        <v>5</v>
+      </c>
+      <c r="H508" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I508" t="n">
+        <v>20</v>
+      </c>
+      <c r="J508" t="n">
+        <v>1</v>
+      </c>
+      <c r="K508" t="n">
+        <v>5</v>
+      </c>
+      <c r="L508" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M508" t="n">
+        <v>50</v>
+      </c>
+      <c r="N508" t="n">
+        <v>14</v>
+      </c>
+      <c r="O508" t="n">
+        <v>24</v>
+      </c>
+      <c r="P508" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q508" t="n">
+        <v>6</v>
+      </c>
+      <c r="R508" t="n">
+        <v>14</v>
+      </c>
+      <c r="S508" t="n">
+        <v>53.1253287789138</v>
+      </c>
+      <c r="T508" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-46-54</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C509" t="n">
+        <v>1</v>
+      </c>
+      <c r="D509" t="n">
+        <v>1</v>
+      </c>
+      <c r="E509" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F509" t="n">
+        <v>2</v>
+      </c>
+      <c r="G509" t="n">
+        <v>5</v>
+      </c>
+      <c r="H509" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I509" t="n">
+        <v>20</v>
+      </c>
+      <c r="J509" t="n">
+        <v>1</v>
+      </c>
+      <c r="K509" t="n">
+        <v>5</v>
+      </c>
+      <c r="L509" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M509" t="n">
+        <v>50</v>
+      </c>
+      <c r="N509" t="n">
+        <v>31</v>
+      </c>
+      <c r="O509" t="n">
+        <v>20</v>
+      </c>
+      <c r="P509" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q509" t="n">
+        <v>5</v>
+      </c>
+      <c r="R509" t="n">
+        <v>31</v>
+      </c>
+      <c r="S509" t="n">
+        <v>52.9233610890987</v>
+      </c>
+      <c r="T509" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-46-54</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C510" t="n">
+        <v>2</v>
+      </c>
+      <c r="D510" t="n">
+        <v>1</v>
+      </c>
+      <c r="E510" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F510" t="n">
+        <v>2</v>
+      </c>
+      <c r="G510" t="n">
+        <v>5</v>
+      </c>
+      <c r="H510" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I510" t="n">
+        <v>20</v>
+      </c>
+      <c r="J510" t="n">
+        <v>1</v>
+      </c>
+      <c r="K510" t="n">
+        <v>5</v>
+      </c>
+      <c r="L510" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M510" t="n">
+        <v>50</v>
+      </c>
+      <c r="N510" t="n">
+        <v>14</v>
+      </c>
+      <c r="O510" t="n">
+        <v>4</v>
+      </c>
+      <c r="P510" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q510" t="n">
+        <v>26</v>
+      </c>
+      <c r="R510" t="n">
+        <v>16</v>
+      </c>
+      <c r="S510" t="n">
+        <v>53.24940240552836</v>
+      </c>
+      <c r="T510" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-46-54</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C511" t="n">
+        <v>3</v>
+      </c>
+      <c r="D511" t="n">
+        <v>1</v>
+      </c>
+      <c r="E511" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F511" t="n">
+        <v>2</v>
+      </c>
+      <c r="G511" t="n">
+        <v>5</v>
+      </c>
+      <c r="H511" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I511" t="n">
+        <v>20</v>
+      </c>
+      <c r="J511" t="n">
+        <v>1</v>
+      </c>
+      <c r="K511" t="n">
+        <v>5</v>
+      </c>
+      <c r="L511" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M511" t="n">
+        <v>50</v>
+      </c>
+      <c r="N511" t="n">
+        <v>28</v>
+      </c>
+      <c r="O511" t="n">
+        <v>16</v>
+      </c>
+      <c r="P511" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q511" t="n">
+        <v>2</v>
+      </c>
+      <c r="R511" t="n">
+        <v>28</v>
+      </c>
+      <c r="S511" t="n">
+        <v>53.02376539543634</v>
+      </c>
+      <c r="T511" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-46-54</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C512" t="n">
+        <v>4</v>
+      </c>
+      <c r="D512" t="n">
+        <v>1</v>
+      </c>
+      <c r="E512" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F512" t="n">
+        <v>2</v>
+      </c>
+      <c r="G512" t="n">
+        <v>5</v>
+      </c>
+      <c r="H512" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I512" t="n">
+        <v>20</v>
+      </c>
+      <c r="J512" t="n">
+        <v>1</v>
+      </c>
+      <c r="K512" t="n">
+        <v>5</v>
+      </c>
+      <c r="L512" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M512" t="n">
+        <v>50</v>
+      </c>
+      <c r="N512" t="n">
+        <v>29</v>
+      </c>
+      <c r="O512" t="n">
+        <v>31</v>
+      </c>
+      <c r="P512" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q512" t="n">
+        <v>29</v>
+      </c>
+      <c r="R512" t="n">
+        <v>25</v>
+      </c>
+      <c r="S512" t="n">
+        <v>52.39919200985083</v>
+      </c>
+      <c r="T512" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-46-54</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C513" t="n">
+        <v>5</v>
+      </c>
+      <c r="D513" t="n">
+        <v>1</v>
+      </c>
+      <c r="E513" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F513" t="n">
+        <v>2</v>
+      </c>
+      <c r="G513" t="n">
+        <v>5</v>
+      </c>
+      <c r="H513" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I513" t="n">
+        <v>20</v>
+      </c>
+      <c r="J513" t="n">
+        <v>1</v>
+      </c>
+      <c r="K513" t="n">
+        <v>5</v>
+      </c>
+      <c r="L513" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M513" t="n">
+        <v>50</v>
+      </c>
+      <c r="N513" t="n">
+        <v>9</v>
+      </c>
+      <c r="O513" t="n">
+        <v>16</v>
+      </c>
+      <c r="P513" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q513" t="n">
+        <v>9</v>
+      </c>
+      <c r="R513" t="n">
+        <v>16</v>
+      </c>
+      <c r="S513" t="n">
+        <v>54.37936415945754</v>
+      </c>
+      <c r="T513" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-46-54</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C514" t="n">
+        <v>1</v>
+      </c>
+      <c r="D514" t="n">
+        <v>2</v>
+      </c>
+      <c r="E514" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F514" t="n">
+        <v>2</v>
+      </c>
+      <c r="G514" t="n">
+        <v>5</v>
+      </c>
+      <c r="H514" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I514" t="n">
+        <v>20</v>
+      </c>
+      <c r="J514" t="n">
+        <v>1</v>
+      </c>
+      <c r="K514" t="n">
+        <v>5</v>
+      </c>
+      <c r="L514" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M514" t="n">
+        <v>50</v>
+      </c>
+      <c r="N514" t="n">
+        <v>10</v>
+      </c>
+      <c r="O514" t="n">
+        <v>20</v>
+      </c>
+      <c r="P514" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q514" t="n">
+        <v>10</v>
+      </c>
+      <c r="R514" t="n">
+        <v>4</v>
+      </c>
+      <c r="S514" t="n">
+        <v>56.63152725534878</v>
+      </c>
+      <c r="T514" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-46-54</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C515" t="n">
+        <v>2</v>
+      </c>
+      <c r="D515" t="n">
+        <v>2</v>
+      </c>
+      <c r="E515" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F515" t="n">
+        <v>2</v>
+      </c>
+      <c r="G515" t="n">
+        <v>5</v>
+      </c>
+      <c r="H515" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I515" t="n">
+        <v>20</v>
+      </c>
+      <c r="J515" t="n">
+        <v>1</v>
+      </c>
+      <c r="K515" t="n">
+        <v>5</v>
+      </c>
+      <c r="L515" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M515" t="n">
+        <v>50</v>
+      </c>
+      <c r="N515" t="n">
+        <v>13</v>
+      </c>
+      <c r="O515" t="n">
+        <v>2</v>
+      </c>
+      <c r="P515" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q515" t="n">
+        <v>13</v>
+      </c>
+      <c r="R515" t="n">
+        <v>13</v>
+      </c>
+      <c r="S515" t="n">
+        <v>53.78585847440731</v>
+      </c>
+      <c r="T515" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-46-54</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C516" t="n">
+        <v>3</v>
+      </c>
+      <c r="D516" t="n">
+        <v>2</v>
+      </c>
+      <c r="E516" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F516" t="n">
+        <v>2</v>
+      </c>
+      <c r="G516" t="n">
+        <v>5</v>
+      </c>
+      <c r="H516" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I516" t="n">
+        <v>20</v>
+      </c>
+      <c r="J516" t="n">
+        <v>1</v>
+      </c>
+      <c r="K516" t="n">
+        <v>5</v>
+      </c>
+      <c r="L516" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M516" t="n">
+        <v>50</v>
+      </c>
+      <c r="N516" t="n">
+        <v>26</v>
+      </c>
+      <c r="O516" t="n">
+        <v>16</v>
+      </c>
+      <c r="P516" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q516" t="n">
+        <v>26</v>
+      </c>
+      <c r="R516" t="n">
+        <v>17</v>
+      </c>
+      <c r="S516" t="n">
+        <v>38.55375786965478</v>
+      </c>
+      <c r="T516" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-46-54</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C517" t="n">
+        <v>4</v>
+      </c>
+      <c r="D517" t="n">
+        <v>2</v>
+      </c>
+      <c r="E517" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F517" t="n">
+        <v>2</v>
+      </c>
+      <c r="G517" t="n">
+        <v>5</v>
+      </c>
+      <c r="H517" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I517" t="n">
+        <v>20</v>
+      </c>
+      <c r="J517" t="n">
+        <v>1</v>
+      </c>
+      <c r="K517" t="n">
+        <v>5</v>
+      </c>
+      <c r="L517" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M517" t="n">
+        <v>50</v>
+      </c>
+      <c r="N517" t="n">
+        <v>31</v>
+      </c>
+      <c r="O517" t="n">
+        <v>29</v>
+      </c>
+      <c r="P517" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q517" t="n">
+        <v>18</v>
+      </c>
+      <c r="R517" t="n">
+        <v>31</v>
+      </c>
+      <c r="S517" t="n">
+        <v>73.08661512257319</v>
+      </c>
+      <c r="T517" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_11-46-54</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C518" t="n">
+        <v>5</v>
+      </c>
+      <c r="D518" t="n">
+        <v>2</v>
+      </c>
+      <c r="E518" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F518" t="n">
+        <v>2</v>
+      </c>
+      <c r="G518" t="n">
+        <v>5</v>
+      </c>
+      <c r="H518" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I518" t="n">
+        <v>20</v>
+      </c>
+      <c r="J518" t="n">
+        <v>1</v>
+      </c>
+      <c r="K518" t="n">
+        <v>5</v>
+      </c>
+      <c r="L518" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M518" t="n">
+        <v>50</v>
+      </c>
+      <c r="N518" t="n">
+        <v>29</v>
+      </c>
+      <c r="O518" t="n">
+        <v>4</v>
+      </c>
+      <c r="P518" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q518" t="n">
+        <v>22</v>
+      </c>
+      <c r="R518" t="n">
+        <v>5</v>
+      </c>
+      <c r="S518" t="n">
+        <v>60.98011332203151</v>
+      </c>
+      <c r="T518" t="n">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T17"/>
+  <dimension ref="A1:T49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1608,6 +1608,2118 @@
         <v>19</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-51-18</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I18" t="n">
+        <v>20</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>50</v>
+      </c>
+      <c r="N18" t="n">
+        <v>20</v>
+      </c>
+      <c r="O18" t="n">
+        <v>12</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>20</v>
+      </c>
+      <c r="R18" t="n">
+        <v>4</v>
+      </c>
+      <c r="S18" t="n">
+        <v>57.76426193419481</v>
+      </c>
+      <c r="T18" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-51-18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I19" t="n">
+        <v>20</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>50</v>
+      </c>
+      <c r="N19" t="n">
+        <v>25</v>
+      </c>
+      <c r="O19" t="n">
+        <v>29</v>
+      </c>
+      <c r="P19" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>25</v>
+      </c>
+      <c r="R19" t="n">
+        <v>27</v>
+      </c>
+      <c r="S19" t="n">
+        <v>65.94987664976328</v>
+      </c>
+      <c r="T19" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-51-18</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I20" t="n">
+        <v>20</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>50</v>
+      </c>
+      <c r="N20" t="n">
+        <v>9</v>
+      </c>
+      <c r="O20" t="n">
+        <v>18</v>
+      </c>
+      <c r="P20" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>9</v>
+      </c>
+      <c r="R20" t="n">
+        <v>10</v>
+      </c>
+      <c r="S20" t="n">
+        <v>68.22518568836949</v>
+      </c>
+      <c r="T20" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-51-18</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I21" t="n">
+        <v>20</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>50</v>
+      </c>
+      <c r="N21" t="n">
+        <v>31</v>
+      </c>
+      <c r="O21" t="n">
+        <v>20</v>
+      </c>
+      <c r="P21" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>3</v>
+      </c>
+      <c r="S21" t="n">
+        <v>85.34295803277705</v>
+      </c>
+      <c r="T21" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-51-18</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I22" t="n">
+        <v>20</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M22" t="n">
+        <v>50</v>
+      </c>
+      <c r="N22" t="n">
+        <v>31</v>
+      </c>
+      <c r="O22" t="n">
+        <v>4</v>
+      </c>
+      <c r="P22" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4</v>
+      </c>
+      <c r="R22" t="n">
+        <v>4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>68.33617160072384</v>
+      </c>
+      <c r="T22" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-51-18</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I23" t="n">
+        <v>20</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>5</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M23" t="n">
+        <v>50</v>
+      </c>
+      <c r="N23" t="n">
+        <v>26</v>
+      </c>
+      <c r="O23" t="n">
+        <v>9</v>
+      </c>
+      <c r="P23" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>26</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>68.90817668935779</v>
+      </c>
+      <c r="T23" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-51-18</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I24" t="n">
+        <v>20</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>5</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M24" t="n">
+        <v>50</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>15</v>
+      </c>
+      <c r="P24" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>24</v>
+      </c>
+      <c r="S24" t="n">
+        <v>58.02911687610892</v>
+      </c>
+      <c r="T24" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-51-18</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I25" t="n">
+        <v>20</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>5</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M25" t="n">
+        <v>50</v>
+      </c>
+      <c r="N25" t="n">
+        <v>31</v>
+      </c>
+      <c r="O25" t="n">
+        <v>31</v>
+      </c>
+      <c r="P25" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>31</v>
+      </c>
+      <c r="R25" t="n">
+        <v>21</v>
+      </c>
+      <c r="S25" t="n">
+        <v>64.77071344983304</v>
+      </c>
+      <c r="T25" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-51-18</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I26" t="n">
+        <v>20</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>5</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M26" t="n">
+        <v>50</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2</v>
+      </c>
+      <c r="O26" t="n">
+        <v>25</v>
+      </c>
+      <c r="P26" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2</v>
+      </c>
+      <c r="R26" t="n">
+        <v>25</v>
+      </c>
+      <c r="S26" t="n">
+        <v>55.74821109260589</v>
+      </c>
+      <c r="T26" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-51-18</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" t="n">
+        <v>5</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I27" t="n">
+        <v>20</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M27" t="n">
+        <v>50</v>
+      </c>
+      <c r="N27" t="n">
+        <v>29</v>
+      </c>
+      <c r="O27" t="n">
+        <v>29</v>
+      </c>
+      <c r="P27" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>20</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>71.53151837560355</v>
+      </c>
+      <c r="T27" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-51-18</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I28" t="n">
+        <v>20</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>5</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M28" t="n">
+        <v>50</v>
+      </c>
+      <c r="N28" t="n">
+        <v>17</v>
+      </c>
+      <c r="O28" t="n">
+        <v>16</v>
+      </c>
+      <c r="P28" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>21</v>
+      </c>
+      <c r="R28" t="n">
+        <v>23</v>
+      </c>
+      <c r="S28" t="n">
+        <v>72.26476864053073</v>
+      </c>
+      <c r="T28" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-51-18</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I29" t="n">
+        <v>20</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>5</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M29" t="n">
+        <v>50</v>
+      </c>
+      <c r="N29" t="n">
+        <v>7</v>
+      </c>
+      <c r="O29" t="n">
+        <v>16</v>
+      </c>
+      <c r="P29" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>21</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7</v>
+      </c>
+      <c r="S29" t="n">
+        <v>74.79074481341382</v>
+      </c>
+      <c r="T29" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-51-18</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I30" t="n">
+        <v>20</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>5</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M30" t="n">
+        <v>50</v>
+      </c>
+      <c r="N30" t="n">
+        <v>11</v>
+      </c>
+      <c r="O30" t="n">
+        <v>12</v>
+      </c>
+      <c r="P30" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>25</v>
+      </c>
+      <c r="R30" t="n">
+        <v>12</v>
+      </c>
+      <c r="S30" t="n">
+        <v>51.16019157575864</v>
+      </c>
+      <c r="T30" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-51-18</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" t="n">
+        <v>5</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I31" t="n">
+        <v>20</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>5</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M31" t="n">
+        <v>50</v>
+      </c>
+      <c r="N31" t="n">
+        <v>15</v>
+      </c>
+      <c r="O31" t="n">
+        <v>9</v>
+      </c>
+      <c r="P31" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>15</v>
+      </c>
+      <c r="R31" t="n">
+        <v>12</v>
+      </c>
+      <c r="S31" t="n">
+        <v>66.04963484198028</v>
+      </c>
+      <c r="T31" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-51-18</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I32" t="n">
+        <v>20</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>5</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M32" t="n">
+        <v>50</v>
+      </c>
+      <c r="N32" t="n">
+        <v>24</v>
+      </c>
+      <c r="O32" t="n">
+        <v>30</v>
+      </c>
+      <c r="P32" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>24</v>
+      </c>
+      <c r="R32" t="n">
+        <v>24</v>
+      </c>
+      <c r="S32" t="n">
+        <v>50.33821673026171</v>
+      </c>
+      <c r="T32" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-51-18</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" t="n">
+        <v>5</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I33" t="n">
+        <v>20</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>5</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M33" t="n">
+        <v>50</v>
+      </c>
+      <c r="N33" t="n">
+        <v>6</v>
+      </c>
+      <c r="O33" t="n">
+        <v>5</v>
+      </c>
+      <c r="P33" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>22</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6</v>
+      </c>
+      <c r="S33" t="n">
+        <v>60.67700577368011</v>
+      </c>
+      <c r="T33" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-03-46</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" t="n">
+        <v>5</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I34" t="n">
+        <v>20</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>5</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M34" t="n">
+        <v>50</v>
+      </c>
+      <c r="N34" t="n">
+        <v>7</v>
+      </c>
+      <c r="O34" t="n">
+        <v>9</v>
+      </c>
+      <c r="P34" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>22</v>
+      </c>
+      <c r="R34" t="n">
+        <v>9</v>
+      </c>
+      <c r="S34" t="n">
+        <v>88.17561135909651</v>
+      </c>
+      <c r="T34" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-03-46</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" t="n">
+        <v>5</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I35" t="n">
+        <v>20</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>5</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M35" t="n">
+        <v>50</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>27</v>
+      </c>
+      <c r="P35" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>17</v>
+      </c>
+      <c r="S35" t="n">
+        <v>79.6514720238746</v>
+      </c>
+      <c r="T35" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-03-46</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" t="n">
+        <v>5</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I36" t="n">
+        <v>20</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>5</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M36" t="n">
+        <v>50</v>
+      </c>
+      <c r="N36" t="n">
+        <v>13</v>
+      </c>
+      <c r="O36" t="n">
+        <v>8</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>13</v>
+      </c>
+      <c r="R36" t="n">
+        <v>10</v>
+      </c>
+      <c r="S36" t="n">
+        <v>68.72601367713909</v>
+      </c>
+      <c r="T36" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-03-46</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" t="n">
+        <v>5</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I37" t="n">
+        <v>20</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>5</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M37" t="n">
+        <v>50</v>
+      </c>
+      <c r="N37" t="n">
+        <v>26</v>
+      </c>
+      <c r="O37" t="n">
+        <v>23</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>10</v>
+      </c>
+      <c r="S37" t="n">
+        <v>77.18885482373848</v>
+      </c>
+      <c r="T37" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-03-46</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2</v>
+      </c>
+      <c r="G38" t="n">
+        <v>5</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I38" t="n">
+        <v>20</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>5</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M38" t="n">
+        <v>50</v>
+      </c>
+      <c r="N38" t="n">
+        <v>8</v>
+      </c>
+      <c r="O38" t="n">
+        <v>8</v>
+      </c>
+      <c r="P38" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>8</v>
+      </c>
+      <c r="R38" t="n">
+        <v>23</v>
+      </c>
+      <c r="S38" t="n">
+        <v>66.51582444758002</v>
+      </c>
+      <c r="T38" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-03-46</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" t="n">
+        <v>5</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I39" t="n">
+        <v>20</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" t="n">
+        <v>5</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M39" t="n">
+        <v>50</v>
+      </c>
+      <c r="N39" t="n">
+        <v>13</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>22</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>89.14018876236305</v>
+      </c>
+      <c r="T39" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-03-46</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" t="n">
+        <v>5</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I40" t="n">
+        <v>20</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>5</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M40" t="n">
+        <v>50</v>
+      </c>
+      <c r="N40" t="n">
+        <v>5</v>
+      </c>
+      <c r="O40" t="n">
+        <v>26</v>
+      </c>
+      <c r="P40" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>5</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7</v>
+      </c>
+      <c r="S40" t="n">
+        <v>53.86693921757954</v>
+      </c>
+      <c r="T40" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-03-46</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>4</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2</v>
+      </c>
+      <c r="G41" t="n">
+        <v>5</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I41" t="n">
+        <v>20</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="n">
+        <v>5</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M41" t="n">
+        <v>50</v>
+      </c>
+      <c r="N41" t="n">
+        <v>8</v>
+      </c>
+      <c r="O41" t="n">
+        <v>9</v>
+      </c>
+      <c r="P41" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>26</v>
+      </c>
+      <c r="R41" t="n">
+        <v>10</v>
+      </c>
+      <c r="S41" t="n">
+        <v>51.16019157575871</v>
+      </c>
+      <c r="T41" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-03-46</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" t="n">
+        <v>5</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I42" t="n">
+        <v>20</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" t="n">
+        <v>5</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M42" t="n">
+        <v>50</v>
+      </c>
+      <c r="N42" t="n">
+        <v>16</v>
+      </c>
+      <c r="O42" t="n">
+        <v>17</v>
+      </c>
+      <c r="P42" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>25</v>
+      </c>
+      <c r="R42" t="n">
+        <v>27</v>
+      </c>
+      <c r="S42" t="n">
+        <v>53.29233772833648</v>
+      </c>
+      <c r="T42" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-03-46</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" t="n">
+        <v>5</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I43" t="n">
+        <v>20</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" t="n">
+        <v>5</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M43" t="n">
+        <v>50</v>
+      </c>
+      <c r="N43" t="n">
+        <v>28</v>
+      </c>
+      <c r="O43" t="n">
+        <v>13</v>
+      </c>
+      <c r="P43" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>28</v>
+      </c>
+      <c r="R43" t="n">
+        <v>28</v>
+      </c>
+      <c r="S43" t="n">
+        <v>53.8483132662859</v>
+      </c>
+      <c r="T43" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-03-46</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2</v>
+      </c>
+      <c r="G44" t="n">
+        <v>5</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I44" t="n">
+        <v>20</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>5</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M44" t="n">
+        <v>50</v>
+      </c>
+      <c r="N44" t="n">
+        <v>20</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1</v>
+      </c>
+      <c r="P44" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>20</v>
+      </c>
+      <c r="R44" t="n">
+        <v>22</v>
+      </c>
+      <c r="S44" t="n">
+        <v>53.79933842371339</v>
+      </c>
+      <c r="T44" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-03-46</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>4</v>
+      </c>
+      <c r="D45" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2</v>
+      </c>
+      <c r="G45" t="n">
+        <v>5</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I45" t="n">
+        <v>20</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>5</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M45" t="n">
+        <v>50</v>
+      </c>
+      <c r="N45" t="n">
+        <v>11</v>
+      </c>
+      <c r="O45" t="n">
+        <v>23</v>
+      </c>
+      <c r="P45" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>29</v>
+      </c>
+      <c r="R45" t="n">
+        <v>31</v>
+      </c>
+      <c r="S45" t="n">
+        <v>54.64636706128023</v>
+      </c>
+      <c r="T45" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-03-46</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>4</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G46" t="n">
+        <v>5</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I46" t="n">
+        <v>20</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>5</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M46" t="n">
+        <v>50</v>
+      </c>
+      <c r="N46" t="n">
+        <v>25</v>
+      </c>
+      <c r="O46" t="n">
+        <v>21</v>
+      </c>
+      <c r="P46" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>21</v>
+      </c>
+      <c r="R46" t="n">
+        <v>27</v>
+      </c>
+      <c r="S46" t="n">
+        <v>52.73847979621706</v>
+      </c>
+      <c r="T46" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-03-46</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" t="n">
+        <v>4</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G47" t="n">
+        <v>5</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I47" t="n">
+        <v>20</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>5</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M47" t="n">
+        <v>50</v>
+      </c>
+      <c r="N47" t="n">
+        <v>10</v>
+      </c>
+      <c r="O47" t="n">
+        <v>19</v>
+      </c>
+      <c r="P47" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>4</v>
+      </c>
+      <c r="R47" t="n">
+        <v>10</v>
+      </c>
+      <c r="S47" t="n">
+        <v>53.02376539543634</v>
+      </c>
+      <c r="T47" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-03-46</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" t="n">
+        <v>4</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F48" t="n">
+        <v>2</v>
+      </c>
+      <c r="G48" t="n">
+        <v>5</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I48" t="n">
+        <v>20</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="n">
+        <v>5</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M48" t="n">
+        <v>50</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3</v>
+      </c>
+      <c r="O48" t="n">
+        <v>4</v>
+      </c>
+      <c r="P48" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>31</v>
+      </c>
+      <c r="R48" t="n">
+        <v>5</v>
+      </c>
+      <c r="S48" t="n">
+        <v>51.16019157575871</v>
+      </c>
+      <c r="T48" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-03-46</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>4</v>
+      </c>
+      <c r="D49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F49" t="n">
+        <v>2</v>
+      </c>
+      <c r="G49" t="n">
+        <v>5</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I49" t="n">
+        <v>20</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" t="n">
+        <v>5</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M49" t="n">
+        <v>50</v>
+      </c>
+      <c r="N49" t="n">
+        <v>12</v>
+      </c>
+      <c r="O49" t="n">
+        <v>18</v>
+      </c>
+      <c r="P49" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>8</v>
+      </c>
+      <c r="R49" t="n">
+        <v>14</v>
+      </c>
+      <c r="S49" t="n">
+        <v>60.58598324531882</v>
+      </c>
+      <c r="T49" t="n">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T49"/>
+  <dimension ref="A1:T65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -3720,6 +3720,1062 @@
         <v>19</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-15-35</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G50" t="n">
+        <v>5</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I50" t="n">
+        <v>20</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>5</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M50" t="n">
+        <v>50</v>
+      </c>
+      <c r="N50" t="n">
+        <v>26</v>
+      </c>
+      <c r="O50" t="n">
+        <v>20</v>
+      </c>
+      <c r="P50" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>13</v>
+      </c>
+      <c r="R50" t="n">
+        <v>28</v>
+      </c>
+      <c r="S50" t="n">
+        <v>52.9233610890987</v>
+      </c>
+      <c r="T50" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-15-35</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2</v>
+      </c>
+      <c r="G51" t="n">
+        <v>5</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I51" t="n">
+        <v>20</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
+        <v>5</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M51" t="n">
+        <v>50</v>
+      </c>
+      <c r="N51" t="n">
+        <v>3</v>
+      </c>
+      <c r="O51" t="n">
+        <v>9</v>
+      </c>
+      <c r="P51" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>8</v>
+      </c>
+      <c r="R51" t="n">
+        <v>5</v>
+      </c>
+      <c r="S51" t="n">
+        <v>66.27654856647256</v>
+      </c>
+      <c r="T51" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-15-35</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>3</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2</v>
+      </c>
+      <c r="G52" t="n">
+        <v>5</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I52" t="n">
+        <v>20</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" t="n">
+        <v>5</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M52" t="n">
+        <v>50</v>
+      </c>
+      <c r="N52" t="n">
+        <v>15</v>
+      </c>
+      <c r="O52" t="n">
+        <v>4</v>
+      </c>
+      <c r="P52" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>77.07990333732718</v>
+      </c>
+      <c r="T52" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-15-35</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>4</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2</v>
+      </c>
+      <c r="G53" t="n">
+        <v>5</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I53" t="n">
+        <v>20</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" t="n">
+        <v>5</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M53" t="n">
+        <v>50</v>
+      </c>
+      <c r="N53" t="n">
+        <v>18</v>
+      </c>
+      <c r="O53" t="n">
+        <v>31</v>
+      </c>
+      <c r="P53" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>18</v>
+      </c>
+      <c r="R53" t="n">
+        <v>2</v>
+      </c>
+      <c r="S53" t="n">
+        <v>73.37944954545732</v>
+      </c>
+      <c r="T53" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-15-35</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G54" t="n">
+        <v>5</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I54" t="n">
+        <v>20</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" t="n">
+        <v>5</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M54" t="n">
+        <v>50</v>
+      </c>
+      <c r="N54" t="n">
+        <v>2</v>
+      </c>
+      <c r="O54" t="n">
+        <v>28</v>
+      </c>
+      <c r="P54" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>11</v>
+      </c>
+      <c r="R54" t="n">
+        <v>23</v>
+      </c>
+      <c r="S54" t="n">
+        <v>72.4935209216757</v>
+      </c>
+      <c r="T54" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-15-35</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>2</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F55" t="n">
+        <v>2</v>
+      </c>
+      <c r="G55" t="n">
+        <v>5</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I55" t="n">
+        <v>20</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" t="n">
+        <v>5</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M55" t="n">
+        <v>50</v>
+      </c>
+      <c r="N55" t="n">
+        <v>11</v>
+      </c>
+      <c r="O55" t="n">
+        <v>13</v>
+      </c>
+      <c r="P55" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>19</v>
+      </c>
+      <c r="R55" t="n">
+        <v>19</v>
+      </c>
+      <c r="S55" t="n">
+        <v>66.1356104746563</v>
+      </c>
+      <c r="T55" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-15-35</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>3</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F56" t="n">
+        <v>2</v>
+      </c>
+      <c r="G56" t="n">
+        <v>5</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I56" t="n">
+        <v>20</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>5</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M56" t="n">
+        <v>50</v>
+      </c>
+      <c r="N56" t="n">
+        <v>24</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>11</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1</v>
+      </c>
+      <c r="S56" t="n">
+        <v>76.95856634709544</v>
+      </c>
+      <c r="T56" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-15-35</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>4</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F57" t="n">
+        <v>2</v>
+      </c>
+      <c r="G57" t="n">
+        <v>5</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I57" t="n">
+        <v>20</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="n">
+        <v>5</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M57" t="n">
+        <v>50</v>
+      </c>
+      <c r="N57" t="n">
+        <v>14</v>
+      </c>
+      <c r="O57" t="n">
+        <v>9</v>
+      </c>
+      <c r="P57" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>13</v>
+      </c>
+      <c r="R57" t="n">
+        <v>9</v>
+      </c>
+      <c r="S57" t="n">
+        <v>50.8779198761377</v>
+      </c>
+      <c r="T57" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-15-35</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>3</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2</v>
+      </c>
+      <c r="G58" t="n">
+        <v>5</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I58" t="n">
+        <v>20</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" t="n">
+        <v>5</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M58" t="n">
+        <v>50</v>
+      </c>
+      <c r="N58" t="n">
+        <v>26</v>
+      </c>
+      <c r="O58" t="n">
+        <v>20</v>
+      </c>
+      <c r="P58" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>8</v>
+      </c>
+      <c r="R58" t="n">
+        <v>21</v>
+      </c>
+      <c r="S58" t="n">
+        <v>53.38790812898382</v>
+      </c>
+      <c r="T58" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-15-35</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" t="n">
+        <v>3</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F59" t="n">
+        <v>2</v>
+      </c>
+      <c r="G59" t="n">
+        <v>5</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I59" t="n">
+        <v>20</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" t="n">
+        <v>5</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M59" t="n">
+        <v>50</v>
+      </c>
+      <c r="N59" t="n">
+        <v>7</v>
+      </c>
+      <c r="O59" t="n">
+        <v>22</v>
+      </c>
+      <c r="P59" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>13</v>
+      </c>
+      <c r="R59" t="n">
+        <v>22</v>
+      </c>
+      <c r="S59" t="n">
+        <v>53.48947151246131</v>
+      </c>
+      <c r="T59" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-15-35</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>3</v>
+      </c>
+      <c r="D60" t="n">
+        <v>3</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F60" t="n">
+        <v>2</v>
+      </c>
+      <c r="G60" t="n">
+        <v>5</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I60" t="n">
+        <v>20</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" t="n">
+        <v>5</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M60" t="n">
+        <v>50</v>
+      </c>
+      <c r="N60" t="n">
+        <v>9</v>
+      </c>
+      <c r="O60" t="n">
+        <v>19</v>
+      </c>
+      <c r="P60" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>2</v>
+      </c>
+      <c r="R60" t="n">
+        <v>9</v>
+      </c>
+      <c r="S60" t="n">
+        <v>53.21454842141702</v>
+      </c>
+      <c r="T60" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-15-35</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>4</v>
+      </c>
+      <c r="D61" t="n">
+        <v>3</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2</v>
+      </c>
+      <c r="G61" t="n">
+        <v>5</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I61" t="n">
+        <v>20</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="n">
+        <v>5</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M61" t="n">
+        <v>50</v>
+      </c>
+      <c r="N61" t="n">
+        <v>6</v>
+      </c>
+      <c r="O61" t="n">
+        <v>1</v>
+      </c>
+      <c r="P61" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>1</v>
+      </c>
+      <c r="R61" t="n">
+        <v>4</v>
+      </c>
+      <c r="S61" t="n">
+        <v>79.52436055125598</v>
+      </c>
+      <c r="T61" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-15-35</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="n">
+        <v>4</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F62" t="n">
+        <v>2</v>
+      </c>
+      <c r="G62" t="n">
+        <v>5</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I62" t="n">
+        <v>20</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" t="n">
+        <v>5</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M62" t="n">
+        <v>50</v>
+      </c>
+      <c r="N62" t="n">
+        <v>3</v>
+      </c>
+      <c r="O62" t="n">
+        <v>25</v>
+      </c>
+      <c r="P62" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>23</v>
+      </c>
+      <c r="R62" t="n">
+        <v>25</v>
+      </c>
+      <c r="S62" t="n">
+        <v>60.79297853325846</v>
+      </c>
+      <c r="T62" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-15-35</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" t="n">
+        <v>4</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F63" t="n">
+        <v>2</v>
+      </c>
+      <c r="G63" t="n">
+        <v>5</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I63" t="n">
+        <v>20</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" t="n">
+        <v>5</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M63" t="n">
+        <v>50</v>
+      </c>
+      <c r="N63" t="n">
+        <v>26</v>
+      </c>
+      <c r="O63" t="n">
+        <v>27</v>
+      </c>
+      <c r="P63" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>10</v>
+      </c>
+      <c r="R63" t="n">
+        <v>28</v>
+      </c>
+      <c r="S63" t="n">
+        <v>50.86900424344039</v>
+      </c>
+      <c r="T63" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-15-35</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>3</v>
+      </c>
+      <c r="D64" t="n">
+        <v>4</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F64" t="n">
+        <v>2</v>
+      </c>
+      <c r="G64" t="n">
+        <v>5</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I64" t="n">
+        <v>20</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" t="n">
+        <v>5</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M64" t="n">
+        <v>50</v>
+      </c>
+      <c r="N64" t="n">
+        <v>24</v>
+      </c>
+      <c r="O64" t="n">
+        <v>19</v>
+      </c>
+      <c r="P64" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>23</v>
+      </c>
+      <c r="R64" t="n">
+        <v>19</v>
+      </c>
+      <c r="S64" t="n">
+        <v>63.24843036576091</v>
+      </c>
+      <c r="T64" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-15-35</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>4</v>
+      </c>
+      <c r="D65" t="n">
+        <v>4</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F65" t="n">
+        <v>2</v>
+      </c>
+      <c r="G65" t="n">
+        <v>5</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I65" t="n">
+        <v>20</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" t="n">
+        <v>5</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M65" t="n">
+        <v>50</v>
+      </c>
+      <c r="N65" t="n">
+        <v>9</v>
+      </c>
+      <c r="O65" t="n">
+        <v>4</v>
+      </c>
+      <c r="P65" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>9</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6</v>
+      </c>
+      <c r="S65" t="n">
+        <v>50.78375975495094</v>
+      </c>
+      <c r="T65" t="n">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T65"/>
+  <dimension ref="A1:T97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -4776,6 +4776,2118 @@
         <v>19</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-26-42</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F66" t="n">
+        <v>2</v>
+      </c>
+      <c r="G66" t="n">
+        <v>5</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I66" t="n">
+        <v>20</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" t="n">
+        <v>5</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M66" t="n">
+        <v>50</v>
+      </c>
+      <c r="N66" t="n">
+        <v>5</v>
+      </c>
+      <c r="O66" t="n">
+        <v>12</v>
+      </c>
+      <c r="P66" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>23</v>
+      </c>
+      <c r="R66" t="n">
+        <v>19</v>
+      </c>
+      <c r="S66" t="n">
+        <v>65.12330450151217</v>
+      </c>
+      <c r="T66" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-26-42</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>2</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F67" t="n">
+        <v>2</v>
+      </c>
+      <c r="G67" t="n">
+        <v>5</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I67" t="n">
+        <v>20</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1</v>
+      </c>
+      <c r="K67" t="n">
+        <v>5</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M67" t="n">
+        <v>50</v>
+      </c>
+      <c r="N67" t="n">
+        <v>10</v>
+      </c>
+      <c r="O67" t="n">
+        <v>16</v>
+      </c>
+      <c r="P67" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>24</v>
+      </c>
+      <c r="R67" t="n">
+        <v>10</v>
+      </c>
+      <c r="S67" t="n">
+        <v>74.81412151697111</v>
+      </c>
+      <c r="T67" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-26-42</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>3</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F68" t="n">
+        <v>2</v>
+      </c>
+      <c r="G68" t="n">
+        <v>5</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I68" t="n">
+        <v>20</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1</v>
+      </c>
+      <c r="K68" t="n">
+        <v>5</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M68" t="n">
+        <v>50</v>
+      </c>
+      <c r="N68" t="n">
+        <v>25</v>
+      </c>
+      <c r="O68" t="n">
+        <v>17</v>
+      </c>
+      <c r="P68" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>6</v>
+      </c>
+      <c r="R68" t="n">
+        <v>27</v>
+      </c>
+      <c r="S68" t="n">
+        <v>60.77311803409181</v>
+      </c>
+      <c r="T68" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-26-42</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>4</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F69" t="n">
+        <v>2</v>
+      </c>
+      <c r="G69" t="n">
+        <v>5</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I69" t="n">
+        <v>20</v>
+      </c>
+      <c r="J69" t="n">
+        <v>1</v>
+      </c>
+      <c r="K69" t="n">
+        <v>5</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M69" t="n">
+        <v>50</v>
+      </c>
+      <c r="N69" t="n">
+        <v>5</v>
+      </c>
+      <c r="O69" t="n">
+        <v>25</v>
+      </c>
+      <c r="P69" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>3</v>
+      </c>
+      <c r="R69" t="n">
+        <v>5</v>
+      </c>
+      <c r="S69" t="n">
+        <v>78.31444134828412</v>
+      </c>
+      <c r="T69" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-26-42</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="n">
+        <v>2</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F70" t="n">
+        <v>2</v>
+      </c>
+      <c r="G70" t="n">
+        <v>5</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I70" t="n">
+        <v>20</v>
+      </c>
+      <c r="J70" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" t="n">
+        <v>5</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M70" t="n">
+        <v>50</v>
+      </c>
+      <c r="N70" t="n">
+        <v>28</v>
+      </c>
+      <c r="O70" t="n">
+        <v>17</v>
+      </c>
+      <c r="P70" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>5</v>
+      </c>
+      <c r="R70" t="n">
+        <v>28</v>
+      </c>
+      <c r="S70" t="n">
+        <v>60.58598324531898</v>
+      </c>
+      <c r="T70" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-26-42</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>2</v>
+      </c>
+      <c r="D71" t="n">
+        <v>2</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F71" t="n">
+        <v>2</v>
+      </c>
+      <c r="G71" t="n">
+        <v>5</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I71" t="n">
+        <v>20</v>
+      </c>
+      <c r="J71" t="n">
+        <v>1</v>
+      </c>
+      <c r="K71" t="n">
+        <v>5</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M71" t="n">
+        <v>50</v>
+      </c>
+      <c r="N71" t="n">
+        <v>17</v>
+      </c>
+      <c r="O71" t="n">
+        <v>16</v>
+      </c>
+      <c r="P71" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>7</v>
+      </c>
+      <c r="R71" t="n">
+        <v>17</v>
+      </c>
+      <c r="S71" t="n">
+        <v>78.28561607979958</v>
+      </c>
+      <c r="T71" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-26-42</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>3</v>
+      </c>
+      <c r="D72" t="n">
+        <v>2</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F72" t="n">
+        <v>2</v>
+      </c>
+      <c r="G72" t="n">
+        <v>5</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I72" t="n">
+        <v>20</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1</v>
+      </c>
+      <c r="K72" t="n">
+        <v>5</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M72" t="n">
+        <v>50</v>
+      </c>
+      <c r="N72" t="n">
+        <v>15</v>
+      </c>
+      <c r="O72" t="n">
+        <v>14</v>
+      </c>
+      <c r="P72" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>8</v>
+      </c>
+      <c r="R72" t="n">
+        <v>15</v>
+      </c>
+      <c r="S72" t="n">
+        <v>78.28561607979958</v>
+      </c>
+      <c r="T72" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-26-42</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>4</v>
+      </c>
+      <c r="D73" t="n">
+        <v>2</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F73" t="n">
+        <v>2</v>
+      </c>
+      <c r="G73" t="n">
+        <v>5</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I73" t="n">
+        <v>20</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1</v>
+      </c>
+      <c r="K73" t="n">
+        <v>5</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M73" t="n">
+        <v>50</v>
+      </c>
+      <c r="N73" t="n">
+        <v>8</v>
+      </c>
+      <c r="O73" t="n">
+        <v>14</v>
+      </c>
+      <c r="P73" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>9</v>
+      </c>
+      <c r="R73" t="n">
+        <v>5</v>
+      </c>
+      <c r="S73" t="n">
+        <v>78.22954009105359</v>
+      </c>
+      <c r="T73" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-26-42</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="n">
+        <v>3</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F74" t="n">
+        <v>2</v>
+      </c>
+      <c r="G74" t="n">
+        <v>5</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I74" t="n">
+        <v>20</v>
+      </c>
+      <c r="J74" t="n">
+        <v>1</v>
+      </c>
+      <c r="K74" t="n">
+        <v>5</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M74" t="n">
+        <v>50</v>
+      </c>
+      <c r="N74" t="n">
+        <v>11</v>
+      </c>
+      <c r="O74" t="n">
+        <v>6</v>
+      </c>
+      <c r="P74" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>24</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7</v>
+      </c>
+      <c r="S74" t="n">
+        <v>63.00083027612067</v>
+      </c>
+      <c r="T74" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-26-42</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2</v>
+      </c>
+      <c r="G75" t="n">
+        <v>5</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I75" t="n">
+        <v>20</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1</v>
+      </c>
+      <c r="K75" t="n">
+        <v>5</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M75" t="n">
+        <v>50</v>
+      </c>
+      <c r="N75" t="n">
+        <v>16</v>
+      </c>
+      <c r="O75" t="n">
+        <v>11</v>
+      </c>
+      <c r="P75" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>16</v>
+      </c>
+      <c r="S75" t="n">
+        <v>60.62083722943027</v>
+      </c>
+      <c r="T75" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-26-42</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>3</v>
+      </c>
+      <c r="D76" t="n">
+        <v>3</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F76" t="n">
+        <v>2</v>
+      </c>
+      <c r="G76" t="n">
+        <v>5</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I76" t="n">
+        <v>20</v>
+      </c>
+      <c r="J76" t="n">
+        <v>1</v>
+      </c>
+      <c r="K76" t="n">
+        <v>5</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M76" t="n">
+        <v>50</v>
+      </c>
+      <c r="N76" t="n">
+        <v>18</v>
+      </c>
+      <c r="O76" t="n">
+        <v>10</v>
+      </c>
+      <c r="P76" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>5</v>
+      </c>
+      <c r="R76" t="n">
+        <v>11</v>
+      </c>
+      <c r="S76" t="n">
+        <v>61.57750132615346</v>
+      </c>
+      <c r="T76" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-26-42</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>4</v>
+      </c>
+      <c r="D77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F77" t="n">
+        <v>2</v>
+      </c>
+      <c r="G77" t="n">
+        <v>5</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I77" t="n">
+        <v>20</v>
+      </c>
+      <c r="J77" t="n">
+        <v>1</v>
+      </c>
+      <c r="K77" t="n">
+        <v>5</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M77" t="n">
+        <v>50</v>
+      </c>
+      <c r="N77" t="n">
+        <v>22</v>
+      </c>
+      <c r="O77" t="n">
+        <v>3</v>
+      </c>
+      <c r="P77" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>11</v>
+      </c>
+      <c r="R77" t="n">
+        <v>24</v>
+      </c>
+      <c r="S77" t="n">
+        <v>52.95821507321001</v>
+      </c>
+      <c r="T77" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-26-42</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="n">
+        <v>4</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F78" t="n">
+        <v>2</v>
+      </c>
+      <c r="G78" t="n">
+        <v>5</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I78" t="n">
+        <v>20</v>
+      </c>
+      <c r="J78" t="n">
+        <v>1</v>
+      </c>
+      <c r="K78" t="n">
+        <v>5</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M78" t="n">
+        <v>50</v>
+      </c>
+      <c r="N78" t="n">
+        <v>25</v>
+      </c>
+      <c r="O78" t="n">
+        <v>18</v>
+      </c>
+      <c r="P78" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>19</v>
+      </c>
+      <c r="R78" t="n">
+        <v>19</v>
+      </c>
+      <c r="S78" t="n">
+        <v>65.57504291775645</v>
+      </c>
+      <c r="T78" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-26-42</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>2</v>
+      </c>
+      <c r="D79" t="n">
+        <v>4</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F79" t="n">
+        <v>2</v>
+      </c>
+      <c r="G79" t="n">
+        <v>5</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I79" t="n">
+        <v>20</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" t="n">
+        <v>5</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M79" t="n">
+        <v>50</v>
+      </c>
+      <c r="N79" t="n">
+        <v>4</v>
+      </c>
+      <c r="O79" t="n">
+        <v>22</v>
+      </c>
+      <c r="P79" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>27</v>
+      </c>
+      <c r="R79" t="n">
+        <v>4</v>
+      </c>
+      <c r="S79" t="n">
+        <v>53.214548421417</v>
+      </c>
+      <c r="T79" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-26-42</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>3</v>
+      </c>
+      <c r="D80" t="n">
+        <v>4</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F80" t="n">
+        <v>2</v>
+      </c>
+      <c r="G80" t="n">
+        <v>5</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I80" t="n">
+        <v>20</v>
+      </c>
+      <c r="J80" t="n">
+        <v>1</v>
+      </c>
+      <c r="K80" t="n">
+        <v>5</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M80" t="n">
+        <v>50</v>
+      </c>
+      <c r="N80" t="n">
+        <v>14</v>
+      </c>
+      <c r="O80" t="n">
+        <v>14</v>
+      </c>
+      <c r="P80" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>14</v>
+      </c>
+      <c r="R80" t="n">
+        <v>19</v>
+      </c>
+      <c r="S80" t="n">
+        <v>54.36714272975471</v>
+      </c>
+      <c r="T80" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-26-42</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>4</v>
+      </c>
+      <c r="D81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F81" t="n">
+        <v>2</v>
+      </c>
+      <c r="G81" t="n">
+        <v>5</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I81" t="n">
+        <v>20</v>
+      </c>
+      <c r="J81" t="n">
+        <v>1</v>
+      </c>
+      <c r="K81" t="n">
+        <v>5</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M81" t="n">
+        <v>50</v>
+      </c>
+      <c r="N81" t="n">
+        <v>19</v>
+      </c>
+      <c r="O81" t="n">
+        <v>12</v>
+      </c>
+      <c r="P81" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>11</v>
+      </c>
+      <c r="R81" t="n">
+        <v>19</v>
+      </c>
+      <c r="S81" t="n">
+        <v>52.66665556473693</v>
+      </c>
+      <c r="T81" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-37-33</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F82" t="n">
+        <v>2</v>
+      </c>
+      <c r="G82" t="n">
+        <v>5</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I82" t="n">
+        <v>20</v>
+      </c>
+      <c r="J82" t="n">
+        <v>1</v>
+      </c>
+      <c r="K82" t="n">
+        <v>5</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M82" t="n">
+        <v>50</v>
+      </c>
+      <c r="N82" t="n">
+        <v>7</v>
+      </c>
+      <c r="O82" t="n">
+        <v>30</v>
+      </c>
+      <c r="P82" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>21</v>
+      </c>
+      <c r="R82" t="n">
+        <v>9</v>
+      </c>
+      <c r="S82" t="n">
+        <v>53.02492447257619</v>
+      </c>
+      <c r="T82" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-37-33</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>2</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F83" t="n">
+        <v>2</v>
+      </c>
+      <c r="G83" t="n">
+        <v>5</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I83" t="n">
+        <v>20</v>
+      </c>
+      <c r="J83" t="n">
+        <v>1</v>
+      </c>
+      <c r="K83" t="n">
+        <v>5</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M83" t="n">
+        <v>50</v>
+      </c>
+      <c r="N83" t="n">
+        <v>17</v>
+      </c>
+      <c r="O83" t="n">
+        <v>16</v>
+      </c>
+      <c r="P83" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>4</v>
+      </c>
+      <c r="R83" t="n">
+        <v>18</v>
+      </c>
+      <c r="S83" t="n">
+        <v>87.78701154945981</v>
+      </c>
+      <c r="T83" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-37-33</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>3</v>
+      </c>
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F84" t="n">
+        <v>2</v>
+      </c>
+      <c r="G84" t="n">
+        <v>5</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I84" t="n">
+        <v>20</v>
+      </c>
+      <c r="J84" t="n">
+        <v>1</v>
+      </c>
+      <c r="K84" t="n">
+        <v>5</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M84" t="n">
+        <v>50</v>
+      </c>
+      <c r="N84" t="n">
+        <v>2</v>
+      </c>
+      <c r="O84" t="n">
+        <v>3</v>
+      </c>
+      <c r="P84" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>21</v>
+      </c>
+      <c r="R84" t="n">
+        <v>4</v>
+      </c>
+      <c r="S84" t="n">
+        <v>50.86900424344039</v>
+      </c>
+      <c r="T84" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-37-33</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>4</v>
+      </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F85" t="n">
+        <v>2</v>
+      </c>
+      <c r="G85" t="n">
+        <v>5</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I85" t="n">
+        <v>20</v>
+      </c>
+      <c r="J85" t="n">
+        <v>1</v>
+      </c>
+      <c r="K85" t="n">
+        <v>5</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M85" t="n">
+        <v>50</v>
+      </c>
+      <c r="N85" t="n">
+        <v>12</v>
+      </c>
+      <c r="O85" t="n">
+        <v>12</v>
+      </c>
+      <c r="P85" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>12</v>
+      </c>
+      <c r="R85" t="n">
+        <v>12</v>
+      </c>
+      <c r="S85" t="n">
+        <v>51.20496899610172</v>
+      </c>
+      <c r="T85" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-37-33</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="n">
+        <v>2</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F86" t="n">
+        <v>2</v>
+      </c>
+      <c r="G86" t="n">
+        <v>5</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I86" t="n">
+        <v>20</v>
+      </c>
+      <c r="J86" t="n">
+        <v>1</v>
+      </c>
+      <c r="K86" t="n">
+        <v>5</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M86" t="n">
+        <v>50</v>
+      </c>
+      <c r="N86" t="n">
+        <v>26</v>
+      </c>
+      <c r="O86" t="n">
+        <v>22</v>
+      </c>
+      <c r="P86" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>7</v>
+      </c>
+      <c r="R86" t="n">
+        <v>23</v>
+      </c>
+      <c r="S86" t="n">
+        <v>65.38790812898377</v>
+      </c>
+      <c r="T86" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-37-33</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>2</v>
+      </c>
+      <c r="D87" t="n">
+        <v>2</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F87" t="n">
+        <v>2</v>
+      </c>
+      <c r="G87" t="n">
+        <v>5</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I87" t="n">
+        <v>20</v>
+      </c>
+      <c r="J87" t="n">
+        <v>1</v>
+      </c>
+      <c r="K87" t="n">
+        <v>5</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M87" t="n">
+        <v>50</v>
+      </c>
+      <c r="N87" t="n">
+        <v>21</v>
+      </c>
+      <c r="O87" t="n">
+        <v>22</v>
+      </c>
+      <c r="P87" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>10</v>
+      </c>
+      <c r="R87" t="n">
+        <v>21</v>
+      </c>
+      <c r="S87" t="n">
+        <v>50.86900424344032</v>
+      </c>
+      <c r="T87" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-37-33</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>3</v>
+      </c>
+      <c r="D88" t="n">
+        <v>2</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F88" t="n">
+        <v>2</v>
+      </c>
+      <c r="G88" t="n">
+        <v>5</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I88" t="n">
+        <v>20</v>
+      </c>
+      <c r="J88" t="n">
+        <v>1</v>
+      </c>
+      <c r="K88" t="n">
+        <v>5</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M88" t="n">
+        <v>50</v>
+      </c>
+      <c r="N88" t="n">
+        <v>26</v>
+      </c>
+      <c r="O88" t="n">
+        <v>21</v>
+      </c>
+      <c r="P88" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>10</v>
+      </c>
+      <c r="R88" t="n">
+        <v>12</v>
+      </c>
+      <c r="S88" t="n">
+        <v>54.2011607968826</v>
+      </c>
+      <c r="T88" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-37-33</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>4</v>
+      </c>
+      <c r="D89" t="n">
+        <v>2</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F89" t="n">
+        <v>2</v>
+      </c>
+      <c r="G89" t="n">
+        <v>5</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I89" t="n">
+        <v>20</v>
+      </c>
+      <c r="J89" t="n">
+        <v>1</v>
+      </c>
+      <c r="K89" t="n">
+        <v>5</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M89" t="n">
+        <v>50</v>
+      </c>
+      <c r="N89" t="n">
+        <v>30</v>
+      </c>
+      <c r="O89" t="n">
+        <v>22</v>
+      </c>
+      <c r="P89" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>17</v>
+      </c>
+      <c r="R89" t="n">
+        <v>23</v>
+      </c>
+      <c r="S89" t="n">
+        <v>76.78382094285232</v>
+      </c>
+      <c r="T89" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-37-33</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" t="n">
+        <v>3</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F90" t="n">
+        <v>2</v>
+      </c>
+      <c r="G90" t="n">
+        <v>5</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I90" t="n">
+        <v>20</v>
+      </c>
+      <c r="J90" t="n">
+        <v>1</v>
+      </c>
+      <c r="K90" t="n">
+        <v>5</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M90" t="n">
+        <v>50</v>
+      </c>
+      <c r="N90" t="n">
+        <v>13</v>
+      </c>
+      <c r="O90" t="n">
+        <v>7</v>
+      </c>
+      <c r="P90" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>13</v>
+      </c>
+      <c r="R90" t="n">
+        <v>14</v>
+      </c>
+      <c r="S90" t="n">
+        <v>65.2941798258715</v>
+      </c>
+      <c r="T90" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-37-33</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>2</v>
+      </c>
+      <c r="D91" t="n">
+        <v>3</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F91" t="n">
+        <v>2</v>
+      </c>
+      <c r="G91" t="n">
+        <v>5</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I91" t="n">
+        <v>20</v>
+      </c>
+      <c r="J91" t="n">
+        <v>1</v>
+      </c>
+      <c r="K91" t="n">
+        <v>5</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M91" t="n">
+        <v>50</v>
+      </c>
+      <c r="N91" t="n">
+        <v>24</v>
+      </c>
+      <c r="O91" t="n">
+        <v>25</v>
+      </c>
+      <c r="P91" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>2</v>
+      </c>
+      <c r="R91" t="n">
+        <v>2</v>
+      </c>
+      <c r="S91" t="n">
+        <v>67.71460284066265</v>
+      </c>
+      <c r="T91" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-37-33</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>3</v>
+      </c>
+      <c r="D92" t="n">
+        <v>3</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F92" t="n">
+        <v>2</v>
+      </c>
+      <c r="G92" t="n">
+        <v>5</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I92" t="n">
+        <v>20</v>
+      </c>
+      <c r="J92" t="n">
+        <v>1</v>
+      </c>
+      <c r="K92" t="n">
+        <v>5</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M92" t="n">
+        <v>50</v>
+      </c>
+      <c r="N92" t="n">
+        <v>12</v>
+      </c>
+      <c r="O92" t="n">
+        <v>12</v>
+      </c>
+      <c r="P92" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>24</v>
+      </c>
+      <c r="R92" t="n">
+        <v>14</v>
+      </c>
+      <c r="S92" t="n">
+        <v>51.16019157575865</v>
+      </c>
+      <c r="T92" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-37-33</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>4</v>
+      </c>
+      <c r="D93" t="n">
+        <v>3</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F93" t="n">
+        <v>2</v>
+      </c>
+      <c r="G93" t="n">
+        <v>5</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I93" t="n">
+        <v>20</v>
+      </c>
+      <c r="J93" t="n">
+        <v>1</v>
+      </c>
+      <c r="K93" t="n">
+        <v>5</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M93" t="n">
+        <v>50</v>
+      </c>
+      <c r="N93" t="n">
+        <v>25</v>
+      </c>
+      <c r="O93" t="n">
+        <v>26</v>
+      </c>
+      <c r="P93" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>18</v>
+      </c>
+      <c r="R93" t="n">
+        <v>26</v>
+      </c>
+      <c r="S93" t="n">
+        <v>50.86900424344039</v>
+      </c>
+      <c r="T93" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-37-33</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" t="n">
+        <v>4</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F94" t="n">
+        <v>2</v>
+      </c>
+      <c r="G94" t="n">
+        <v>5</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I94" t="n">
+        <v>20</v>
+      </c>
+      <c r="J94" t="n">
+        <v>1</v>
+      </c>
+      <c r="K94" t="n">
+        <v>5</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M94" t="n">
+        <v>50</v>
+      </c>
+      <c r="N94" t="n">
+        <v>24</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>24</v>
+      </c>
+      <c r="R94" t="n">
+        <v>26</v>
+      </c>
+      <c r="S94" t="n">
+        <v>37.35402933294379</v>
+      </c>
+      <c r="T94" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-37-33</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>2</v>
+      </c>
+      <c r="D95" t="n">
+        <v>4</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F95" t="n">
+        <v>2</v>
+      </c>
+      <c r="G95" t="n">
+        <v>5</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I95" t="n">
+        <v>20</v>
+      </c>
+      <c r="J95" t="n">
+        <v>1</v>
+      </c>
+      <c r="K95" t="n">
+        <v>5</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M95" t="n">
+        <v>50</v>
+      </c>
+      <c r="N95" t="n">
+        <v>29</v>
+      </c>
+      <c r="O95" t="n">
+        <v>14</v>
+      </c>
+      <c r="P95" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>29</v>
+      </c>
+      <c r="R95" t="n">
+        <v>14</v>
+      </c>
+      <c r="S95" t="n">
+        <v>54.43999870293894</v>
+      </c>
+      <c r="T95" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-37-33</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>3</v>
+      </c>
+      <c r="D96" t="n">
+        <v>4</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F96" t="n">
+        <v>2</v>
+      </c>
+      <c r="G96" t="n">
+        <v>5</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I96" t="n">
+        <v>20</v>
+      </c>
+      <c r="J96" t="n">
+        <v>1</v>
+      </c>
+      <c r="K96" t="n">
+        <v>5</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M96" t="n">
+        <v>50</v>
+      </c>
+      <c r="N96" t="n">
+        <v>29</v>
+      </c>
+      <c r="O96" t="n">
+        <v>12</v>
+      </c>
+      <c r="P96" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>11</v>
+      </c>
+      <c r="R96" t="n">
+        <v>11</v>
+      </c>
+      <c r="S96" t="n">
+        <v>68.21884607629063</v>
+      </c>
+      <c r="T96" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-37-33</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>4</v>
+      </c>
+      <c r="D97" t="n">
+        <v>4</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F97" t="n">
+        <v>2</v>
+      </c>
+      <c r="G97" t="n">
+        <v>5</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I97" t="n">
+        <v>20</v>
+      </c>
+      <c r="J97" t="n">
+        <v>1</v>
+      </c>
+      <c r="K97" t="n">
+        <v>5</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M97" t="n">
+        <v>50</v>
+      </c>
+      <c r="N97" t="n">
+        <v>2</v>
+      </c>
+      <c r="O97" t="n">
+        <v>20</v>
+      </c>
+      <c r="P97" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>19</v>
+      </c>
+      <c r="R97" t="n">
+        <v>2</v>
+      </c>
+      <c r="S97" t="n">
+        <v>59.3373858168374</v>
+      </c>
+      <c r="T97" t="n">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,16 +425,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T97"/>
+  <dimension ref="A1:T113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
@@ -453,37 +453,37 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>pasta_run</t>
+          <t>config_num</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>configuracao</t>
+          <t>exec_num</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>execucao</t>
+          <t>param_ARRAY_VAR</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>config_num</t>
+          <t>param_CROSSOVER</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>param_CROSSOVER</t>
+          <t>param_DELTA_MIN</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>param_DELTA_MIN</t>
+          <t>param_IND_SIZE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>param_IND_SIZE</t>
+          <t>param_LIMITE_VAR</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -553,30 +553,30 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_20-39-32</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>config_1</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H2" t="n">
         <v>0.15</v>
@@ -619,30 +619,30 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_20-39-32</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>config_1</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H3" t="n">
         <v>0.15</v>
@@ -685,30 +685,30 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_20-39-32</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>config_1</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="n">
         <v>3</v>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H4" t="n">
         <v>0.15</v>
@@ -751,30 +751,30 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_20-39-32</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>config_1</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="n">
         <v>4</v>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H5" t="n">
         <v>0.15</v>
@@ -817,30 +817,30 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_20-39-32</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>config_2</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H6" t="n">
         <v>0.15</v>
@@ -883,30 +883,30 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_20-39-32</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>config_2</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H7" t="n">
         <v>0.15</v>
@@ -949,30 +949,30 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_20-39-32</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>config_2</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
+      <c r="A8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" t="n">
         <v>3</v>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H8" t="n">
         <v>0.15</v>
@@ -1015,30 +1015,30 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_20-39-32</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>config_2</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="n">
         <v>4</v>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H9" t="n">
         <v>0.15</v>
@@ -1081,30 +1081,30 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_20-39-32</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>config_3</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1</v>
+      <c r="A10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H10" t="n">
         <v>0.5</v>
@@ -1147,30 +1147,30 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_20-39-32</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>config_3</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2</v>
+      <c r="A11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G11" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H11" t="n">
         <v>0.5</v>
@@ -1213,30 +1213,30 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_20-39-32</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>config_3</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
+      <c r="A12" t="n">
         <v>3</v>
       </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G12" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H12" t="n">
         <v>0.5</v>
@@ -1279,30 +1279,30 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_20-39-32</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>config_3</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
         <v>4</v>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H13" t="n">
         <v>0.5</v>
@@ -1345,30 +1345,30 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_20-39-32</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>config_4</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>1</v>
+      <c r="A14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
-      </c>
-      <c r="G14" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H14" t="n">
         <v>0.5</v>
@@ -1411,30 +1411,30 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_20-39-32</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>config_4</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>2</v>
+      <c r="A15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G15" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H15" t="n">
         <v>0.5</v>
@@ -1477,30 +1477,30 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_20-39-32</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>config_4</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
+      <c r="A16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" t="n">
         <v>3</v>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
-      </c>
-      <c r="G16" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H16" t="n">
         <v>0.5</v>
@@ -1543,30 +1543,30 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_20-39-32</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>config_4</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
+      <c r="A17" t="n">
         <v>4</v>
       </c>
+      <c r="B17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
-      </c>
-      <c r="G17" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H17" t="n">
         <v>0.5</v>
@@ -1609,30 +1609,30 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_20-51-18</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>config_1</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
+      <c r="A18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H18" t="n">
         <v>0.15</v>
@@ -1675,30 +1675,30 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_20-51-18</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>config_1</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>2</v>
+      <c r="A19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
-      </c>
-      <c r="G19" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H19" t="n">
         <v>0.15</v>
@@ -1741,30 +1741,30 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_20-51-18</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>config_1</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
+      <c r="A20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" t="n">
         <v>3</v>
       </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
-      </c>
-      <c r="G20" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H20" t="n">
         <v>0.15</v>
@@ -1807,30 +1807,30 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_20-51-18</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>config_1</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
+      <c r="A21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" t="n">
         <v>4</v>
       </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
-      </c>
-      <c r="G21" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H21" t="n">
         <v>0.15</v>
@@ -1873,30 +1873,30 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_20-51-18</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>config_2</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
+      <c r="A22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
-      </c>
-      <c r="G22" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H22" t="n">
         <v>0.15</v>
@@ -1939,30 +1939,30 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_20-51-18</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>config_2</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>2</v>
+      <c r="A23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>2</v>
-      </c>
-      <c r="G23" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H23" t="n">
         <v>0.15</v>
@@ -2005,30 +2005,30 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_20-51-18</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>config_2</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
+      <c r="A24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" t="n">
         <v>3</v>
       </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
-      </c>
-      <c r="G24" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H24" t="n">
         <v>0.15</v>
@@ -2071,30 +2071,30 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_20-51-18</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>config_2</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
+      <c r="A25" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" t="n">
         <v>4</v>
       </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
-      </c>
-      <c r="G25" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H25" t="n">
         <v>0.15</v>
@@ -2137,30 +2137,30 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_20-51-18</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>config_3</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
+      <c r="A26" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
-      </c>
-      <c r="G26" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H26" t="n">
         <v>0.5</v>
@@ -2203,30 +2203,30 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_20-51-18</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>config_3</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>2</v>
+      <c r="A27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
-      </c>
-      <c r="G27" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H27" t="n">
         <v>0.5</v>
@@ -2269,30 +2269,30 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_20-51-18</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>config_3</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
+      <c r="A28" t="n">
         <v>3</v>
       </c>
+      <c r="B28" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
-      </c>
-      <c r="G28" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H28" t="n">
         <v>0.5</v>
@@ -2335,30 +2335,30 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_20-51-18</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>config_3</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
+      <c r="A29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" t="n">
         <v>4</v>
       </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
-      </c>
-      <c r="G29" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H29" t="n">
         <v>0.5</v>
@@ -2401,30 +2401,30 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_20-51-18</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>config_4</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>1</v>
+      <c r="A30" t="n">
+        <v>4</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
-      </c>
-      <c r="G30" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H30" t="n">
         <v>0.5</v>
@@ -2467,30 +2467,30 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_20-51-18</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>config_4</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>2</v>
+      <c r="A31" t="n">
+        <v>4</v>
+      </c>
+      <c r="B31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
-      </c>
-      <c r="G31" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H31" t="n">
         <v>0.5</v>
@@ -2533,30 +2533,30 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_20-51-18</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>config_4</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
+      <c r="A32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B32" t="n">
         <v>3</v>
       </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F32" t="n">
-        <v>2</v>
-      </c>
-      <c r="G32" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H32" t="n">
         <v>0.5</v>
@@ -2599,30 +2599,30 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_20-51-18</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>config_4</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
+      <c r="A33" t="n">
         <v>4</v>
       </c>
+      <c r="B33" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
-      </c>
-      <c r="G33" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H33" t="n">
         <v>0.5</v>
@@ -2665,30 +2665,30 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-03-46</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>config_1</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>1</v>
+      <c r="A34" t="n">
+        <v>1</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
-      </c>
-      <c r="G34" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H34" t="n">
         <v>0.15</v>
@@ -2731,30 +2731,30 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-03-46</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>config_1</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>2</v>
+      <c r="A35" t="n">
+        <v>1</v>
+      </c>
+      <c r="B35" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F35" t="n">
-        <v>2</v>
-      </c>
-      <c r="G35" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H35" t="n">
         <v>0.15</v>
@@ -2797,30 +2797,30 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-03-46</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>config_1</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
+      <c r="A36" t="n">
+        <v>1</v>
+      </c>
+      <c r="B36" t="n">
         <v>3</v>
       </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
-      </c>
-      <c r="G36" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H36" t="n">
         <v>0.15</v>
@@ -2863,30 +2863,30 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-03-46</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>config_1</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
+      <c r="A37" t="n">
+        <v>1</v>
+      </c>
+      <c r="B37" t="n">
         <v>4</v>
       </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
-      </c>
-      <c r="G37" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H37" t="n">
         <v>0.15</v>
@@ -2929,30 +2929,30 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-03-46</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>config_2</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>1</v>
+      <c r="A38" t="n">
+        <v>2</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
-      </c>
-      <c r="G38" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H38" t="n">
         <v>0.15</v>
@@ -2995,30 +2995,30 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-03-46</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>config_2</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>2</v>
+      <c r="A39" t="n">
+        <v>2</v>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F39" t="n">
-        <v>2</v>
-      </c>
-      <c r="G39" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H39" t="n">
         <v>0.15</v>
@@ -3061,30 +3061,30 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-03-46</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>config_2</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
+      <c r="A40" t="n">
+        <v>2</v>
+      </c>
+      <c r="B40" t="n">
         <v>3</v>
       </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F40" t="n">
-        <v>2</v>
-      </c>
-      <c r="G40" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H40" t="n">
         <v>0.15</v>
@@ -3127,30 +3127,30 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-03-46</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>config_2</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
+      <c r="A41" t="n">
+        <v>2</v>
+      </c>
+      <c r="B41" t="n">
         <v>4</v>
       </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
-      </c>
-      <c r="G41" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H41" t="n">
         <v>0.15</v>
@@ -3193,30 +3193,30 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-03-46</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>config_3</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>1</v>
+      <c r="A42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
-      </c>
-      <c r="G42" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H42" t="n">
         <v>0.5</v>
@@ -3259,30 +3259,30 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-03-46</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>config_3</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>2</v>
+      <c r="A43" t="n">
+        <v>3</v>
+      </c>
+      <c r="B43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
-        <v>2</v>
-      </c>
-      <c r="G43" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H43" t="n">
         <v>0.5</v>
@@ -3325,30 +3325,30 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-03-46</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>config_3</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
+      <c r="A44" t="n">
         <v>3</v>
       </c>
+      <c r="B44" t="n">
+        <v>3</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F44" t="n">
-        <v>2</v>
-      </c>
-      <c r="G44" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H44" t="n">
         <v>0.5</v>
@@ -3391,30 +3391,30 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-03-46</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>config_3</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
+      <c r="A45" t="n">
+        <v>3</v>
+      </c>
+      <c r="B45" t="n">
         <v>4</v>
       </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F45" t="n">
-        <v>2</v>
-      </c>
-      <c r="G45" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H45" t="n">
         <v>0.5</v>
@@ -3457,30 +3457,30 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-03-46</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>config_4</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>1</v>
+      <c r="A46" t="n">
+        <v>4</v>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G46" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H46" t="n">
         <v>0.5</v>
@@ -3523,30 +3523,30 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-03-46</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>config_4</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>2</v>
+      <c r="A47" t="n">
+        <v>4</v>
+      </c>
+      <c r="B47" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F47" t="n">
-        <v>2</v>
-      </c>
-      <c r="G47" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H47" t="n">
         <v>0.5</v>
@@ -3589,30 +3589,30 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-03-46</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>config_4</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
+      <c r="A48" t="n">
+        <v>4</v>
+      </c>
+      <c r="B48" t="n">
         <v>3</v>
       </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="E48" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F48" t="n">
-        <v>2</v>
-      </c>
-      <c r="G48" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H48" t="n">
         <v>0.5</v>
@@ -3655,30 +3655,30 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-03-46</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>config_4</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
+      <c r="A49" t="n">
         <v>4</v>
       </c>
+      <c r="B49" t="n">
+        <v>4</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
-      </c>
-      <c r="G49" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H49" t="n">
         <v>0.5</v>
@@ -3721,30 +3721,30 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-15-35</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>config_1</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>1</v>
+      <c r="A50" t="n">
+        <v>1</v>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E50" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F50" t="n">
-        <v>2</v>
-      </c>
-      <c r="G50" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H50" t="n">
         <v>0.15</v>
@@ -3787,30 +3787,30 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-15-35</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>config_1</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>2</v>
+      <c r="A51" t="n">
+        <v>1</v>
+      </c>
+      <c r="B51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E51" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F51" t="n">
-        <v>2</v>
-      </c>
-      <c r="G51" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H51" t="n">
         <v>0.15</v>
@@ -3853,30 +3853,30 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-15-35</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>config_1</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
+      <c r="A52" t="n">
+        <v>1</v>
+      </c>
+      <c r="B52" t="n">
         <v>3</v>
       </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E52" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F52" t="n">
-        <v>2</v>
-      </c>
-      <c r="G52" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H52" t="n">
         <v>0.15</v>
@@ -3919,30 +3919,30 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-15-35</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>config_1</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
+      <c r="A53" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" t="n">
         <v>4</v>
       </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E53" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F53" t="n">
-        <v>2</v>
-      </c>
-      <c r="G53" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H53" t="n">
         <v>0.15</v>
@@ -3985,30 +3985,30 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-15-35</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>config_2</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>1</v>
+      <c r="A54" t="n">
+        <v>2</v>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="E54" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F54" t="n">
-        <v>2</v>
-      </c>
-      <c r="G54" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H54" t="n">
         <v>0.15</v>
@@ -4051,30 +4051,30 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-15-35</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>config_2</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>2</v>
+      <c r="A55" t="n">
+        <v>2</v>
+      </c>
+      <c r="B55" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="E55" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F55" t="n">
-        <v>2</v>
-      </c>
-      <c r="G55" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H55" t="n">
         <v>0.15</v>
@@ -4117,30 +4117,30 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-15-35</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>config_2</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
+      <c r="A56" t="n">
+        <v>2</v>
+      </c>
+      <c r="B56" t="n">
         <v>3</v>
       </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="E56" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
-        <v>2</v>
-      </c>
-      <c r="G56" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H56" t="n">
         <v>0.15</v>
@@ -4183,30 +4183,30 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-15-35</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>config_2</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
+      <c r="A57" t="n">
+        <v>2</v>
+      </c>
+      <c r="B57" t="n">
         <v>4</v>
       </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="E57" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F57" t="n">
-        <v>2</v>
-      </c>
-      <c r="G57" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H57" t="n">
         <v>0.15</v>
@@ -4249,30 +4249,30 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-15-35</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>config_3</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>1</v>
+      <c r="A58" t="n">
+        <v>3</v>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="E58" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F58" t="n">
-        <v>2</v>
-      </c>
-      <c r="G58" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H58" t="n">
         <v>0.5</v>
@@ -4315,30 +4315,30 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-15-35</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>config_3</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>2</v>
+      <c r="A59" t="n">
+        <v>3</v>
+      </c>
+      <c r="B59" t="n">
+        <v>2</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="E59" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F59" t="n">
-        <v>2</v>
-      </c>
-      <c r="G59" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H59" t="n">
         <v>0.5</v>
@@ -4381,30 +4381,30 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-15-35</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>config_3</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
+      <c r="A60" t="n">
         <v>3</v>
       </c>
+      <c r="B60" t="n">
+        <v>3</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D60" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="E60" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F60" t="n">
-        <v>2</v>
-      </c>
-      <c r="G60" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H60" t="n">
         <v>0.5</v>
@@ -4447,30 +4447,30 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-15-35</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>config_3</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
+      <c r="A61" t="n">
+        <v>3</v>
+      </c>
+      <c r="B61" t="n">
         <v>4</v>
       </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D61" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="E61" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F61" t="n">
-        <v>2</v>
-      </c>
-      <c r="G61" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H61" t="n">
         <v>0.5</v>
@@ -4513,30 +4513,30 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-15-35</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>config_4</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>1</v>
+      <c r="A62" t="n">
+        <v>4</v>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D62" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="E62" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F62" t="n">
-        <v>2</v>
-      </c>
-      <c r="G62" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H62" t="n">
         <v>0.5</v>
@@ -4579,30 +4579,30 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-15-35</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>config_4</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>2</v>
+      <c r="A63" t="n">
+        <v>4</v>
+      </c>
+      <c r="B63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D63" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="E63" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F63" t="n">
-        <v>2</v>
-      </c>
-      <c r="G63" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H63" t="n">
         <v>0.5</v>
@@ -4645,30 +4645,30 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-15-35</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>config_4</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
+      <c r="A64" t="n">
+        <v>4</v>
+      </c>
+      <c r="B64" t="n">
         <v>3</v>
       </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D64" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="E64" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
-        <v>2</v>
-      </c>
-      <c r="G64" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H64" t="n">
         <v>0.5</v>
@@ -4711,30 +4711,30 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-15-35</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>config_4</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
+      <c r="A65" t="n">
         <v>4</v>
       </c>
+      <c r="B65" t="n">
+        <v>4</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D65" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="E65" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F65" t="n">
-        <v>2</v>
-      </c>
-      <c r="G65" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H65" t="n">
         <v>0.5</v>
@@ -4777,30 +4777,30 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-26-42</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>config_1</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>1</v>
+      <c r="A66" t="n">
+        <v>1</v>
+      </c>
+      <c r="B66" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E66" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F66" t="n">
-        <v>2</v>
-      </c>
-      <c r="G66" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H66" t="n">
         <v>0.15</v>
@@ -4843,30 +4843,30 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-26-42</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>config_1</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>2</v>
+      <c r="A67" t="n">
+        <v>1</v>
+      </c>
+      <c r="B67" t="n">
+        <v>2</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E67" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F67" t="n">
-        <v>2</v>
-      </c>
-      <c r="G67" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H67" t="n">
         <v>0.15</v>
@@ -4909,30 +4909,30 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-26-42</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>config_1</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
+      <c r="A68" t="n">
+        <v>1</v>
+      </c>
+      <c r="B68" t="n">
         <v>3</v>
       </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E68" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F68" t="n">
-        <v>2</v>
-      </c>
-      <c r="G68" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H68" t="n">
         <v>0.15</v>
@@ -4975,30 +4975,30 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-26-42</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>config_1</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
+      <c r="A69" t="n">
+        <v>1</v>
+      </c>
+      <c r="B69" t="n">
         <v>4</v>
       </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E69" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F69" t="n">
-        <v>2</v>
-      </c>
-      <c r="G69" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H69" t="n">
         <v>0.15</v>
@@ -5041,30 +5041,30 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-26-42</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>config_2</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>1</v>
+      <c r="A70" t="n">
+        <v>2</v>
+      </c>
+      <c r="B70" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D70" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="E70" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F70" t="n">
-        <v>2</v>
-      </c>
-      <c r="G70" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H70" t="n">
         <v>0.15</v>
@@ -5107,30 +5107,30 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-26-42</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>config_2</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>2</v>
+      <c r="A71" t="n">
+        <v>2</v>
+      </c>
+      <c r="B71" t="n">
+        <v>2</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="E71" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F71" t="n">
-        <v>2</v>
-      </c>
-      <c r="G71" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H71" t="n">
         <v>0.15</v>
@@ -5173,30 +5173,30 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-26-42</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>config_2</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
+      <c r="A72" t="n">
+        <v>2</v>
+      </c>
+      <c r="B72" t="n">
         <v>3</v>
       </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D72" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="E72" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F72" t="n">
-        <v>2</v>
-      </c>
-      <c r="G72" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H72" t="n">
         <v>0.15</v>
@@ -5239,30 +5239,30 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-26-42</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>config_2</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
+      <c r="A73" t="n">
+        <v>2</v>
+      </c>
+      <c r="B73" t="n">
         <v>4</v>
       </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D73" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="E73" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
-        <v>2</v>
-      </c>
-      <c r="G73" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H73" t="n">
         <v>0.15</v>
@@ -5305,30 +5305,30 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-26-42</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>config_3</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>1</v>
+      <c r="A74" t="n">
+        <v>3</v>
+      </c>
+      <c r="B74" t="n">
+        <v>1</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D74" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="E74" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F74" t="n">
-        <v>2</v>
-      </c>
-      <c r="G74" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H74" t="n">
         <v>0.5</v>
@@ -5371,30 +5371,30 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-26-42</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>config_3</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>2</v>
+      <c r="A75" t="n">
+        <v>3</v>
+      </c>
+      <c r="B75" t="n">
+        <v>2</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D75" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="E75" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F75" t="n">
-        <v>2</v>
-      </c>
-      <c r="G75" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H75" t="n">
         <v>0.5</v>
@@ -5437,30 +5437,30 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-26-42</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>config_3</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
+      <c r="A76" t="n">
         <v>3</v>
       </c>
+      <c r="B76" t="n">
+        <v>3</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D76" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="E76" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F76" t="n">
-        <v>2</v>
-      </c>
-      <c r="G76" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H76" t="n">
         <v>0.5</v>
@@ -5503,30 +5503,30 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-26-42</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>config_3</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
+      <c r="A77" t="n">
+        <v>3</v>
+      </c>
+      <c r="B77" t="n">
         <v>4</v>
       </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D77" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="E77" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F77" t="n">
-        <v>2</v>
-      </c>
-      <c r="G77" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H77" t="n">
         <v>0.5</v>
@@ -5569,30 +5569,30 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-26-42</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>config_4</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>1</v>
+      <c r="A78" t="n">
+        <v>4</v>
+      </c>
+      <c r="B78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D78" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="E78" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F78" t="n">
-        <v>2</v>
-      </c>
-      <c r="G78" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H78" t="n">
         <v>0.5</v>
@@ -5635,30 +5635,30 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-26-42</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>config_4</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>2</v>
+      <c r="A79" t="n">
+        <v>4</v>
+      </c>
+      <c r="B79" t="n">
+        <v>2</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D79" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="E79" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F79" t="n">
-        <v>2</v>
-      </c>
-      <c r="G79" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H79" t="n">
         <v>0.5</v>
@@ -5701,30 +5701,30 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-26-42</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>config_4</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
+      <c r="A80" t="n">
+        <v>4</v>
+      </c>
+      <c r="B80" t="n">
         <v>3</v>
       </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D80" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="E80" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F80" t="n">
-        <v>2</v>
-      </c>
-      <c r="G80" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H80" t="n">
         <v>0.5</v>
@@ -5767,30 +5767,30 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-26-42</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>config_4</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
+      <c r="A81" t="n">
         <v>4</v>
       </c>
+      <c r="B81" t="n">
+        <v>4</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D81" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="E81" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F81" t="n">
-        <v>2</v>
-      </c>
-      <c r="G81" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H81" t="n">
         <v>0.5</v>
@@ -5833,30 +5833,30 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-37-33</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>config_1</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>1</v>
+      <c r="A82" t="n">
+        <v>1</v>
+      </c>
+      <c r="B82" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E82" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
-        <v>2</v>
-      </c>
-      <c r="G82" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H82" t="n">
         <v>0.15</v>
@@ -5899,30 +5899,30 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-37-33</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>config_1</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>2</v>
+      <c r="A83" t="n">
+        <v>1</v>
+      </c>
+      <c r="B83" t="n">
+        <v>2</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E83" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F83" t="n">
-        <v>2</v>
-      </c>
-      <c r="G83" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H83" t="n">
         <v>0.15</v>
@@ -5965,30 +5965,30 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-37-33</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>config_1</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
+      <c r="A84" t="n">
+        <v>1</v>
+      </c>
+      <c r="B84" t="n">
         <v>3</v>
       </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E84" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F84" t="n">
-        <v>2</v>
-      </c>
-      <c r="G84" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H84" t="n">
         <v>0.15</v>
@@ -6031,30 +6031,30 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-37-33</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>config_1</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
+      <c r="A85" t="n">
+        <v>1</v>
+      </c>
+      <c r="B85" t="n">
         <v>4</v>
       </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E85" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F85" t="n">
-        <v>2</v>
-      </c>
-      <c r="G85" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H85" t="n">
         <v>0.15</v>
@@ -6097,30 +6097,30 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-37-33</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>config_2</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>1</v>
+      <c r="A86" t="n">
+        <v>2</v>
+      </c>
+      <c r="B86" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D86" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="E86" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F86" t="n">
-        <v>2</v>
-      </c>
-      <c r="G86" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H86" t="n">
         <v>0.15</v>
@@ -6163,30 +6163,30 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-37-33</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>config_2</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>2</v>
+      <c r="A87" t="n">
+        <v>2</v>
+      </c>
+      <c r="B87" t="n">
+        <v>2</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D87" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="E87" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F87" t="n">
-        <v>2</v>
-      </c>
-      <c r="G87" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H87" t="n">
         <v>0.15</v>
@@ -6229,30 +6229,30 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-37-33</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>config_2</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
+      <c r="A88" t="n">
+        <v>2</v>
+      </c>
+      <c r="B88" t="n">
         <v>3</v>
       </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D88" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="E88" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F88" t="n">
-        <v>2</v>
-      </c>
-      <c r="G88" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H88" t="n">
         <v>0.15</v>
@@ -6295,30 +6295,30 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-37-33</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>config_2</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
+      <c r="A89" t="n">
+        <v>2</v>
+      </c>
+      <c r="B89" t="n">
         <v>4</v>
       </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D89" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="E89" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F89" t="n">
-        <v>2</v>
-      </c>
-      <c r="G89" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H89" t="n">
         <v>0.15</v>
@@ -6361,30 +6361,30 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-37-33</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>config_3</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>1</v>
+      <c r="A90" t="n">
+        <v>3</v>
+      </c>
+      <c r="B90" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D90" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="E90" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F90" t="n">
-        <v>2</v>
-      </c>
-      <c r="G90" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H90" t="n">
         <v>0.5</v>
@@ -6427,30 +6427,30 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-37-33</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>config_3</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>2</v>
+      <c r="A91" t="n">
+        <v>3</v>
+      </c>
+      <c r="B91" t="n">
+        <v>2</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D91" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="E91" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F91" t="n">
-        <v>2</v>
-      </c>
-      <c r="G91" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H91" t="n">
         <v>0.5</v>
@@ -6493,30 +6493,30 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-37-33</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>config_3</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
+      <c r="A92" t="n">
         <v>3</v>
       </c>
+      <c r="B92" t="n">
+        <v>3</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D92" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="E92" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F92" t="n">
-        <v>2</v>
-      </c>
-      <c r="G92" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H92" t="n">
         <v>0.5</v>
@@ -6559,30 +6559,30 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-37-33</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>config_3</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
+      <c r="A93" t="n">
+        <v>3</v>
+      </c>
+      <c r="B93" t="n">
         <v>4</v>
       </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D93" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="E93" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="F93" t="n">
-        <v>2</v>
-      </c>
-      <c r="G93" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H93" t="n">
         <v>0.5</v>
@@ -6625,30 +6625,30 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-37-33</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>config_4</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>1</v>
+      <c r="A94" t="n">
+        <v>4</v>
+      </c>
+      <c r="B94" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D94" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="E94" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F94" t="n">
-        <v>2</v>
-      </c>
-      <c r="G94" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H94" t="n">
         <v>0.5</v>
@@ -6691,30 +6691,30 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-37-33</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>config_4</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>2</v>
+      <c r="A95" t="n">
+        <v>4</v>
+      </c>
+      <c r="B95" t="n">
+        <v>2</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
       </c>
       <c r="D95" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="E95" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F95" t="n">
-        <v>2</v>
-      </c>
-      <c r="G95" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H95" t="n">
         <v>0.5</v>
@@ -6757,30 +6757,30 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-37-33</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>config_4</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
+      <c r="A96" t="n">
+        <v>4</v>
+      </c>
+      <c r="B96" t="n">
         <v>3</v>
       </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D96" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="E96" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F96" t="n">
-        <v>2</v>
-      </c>
-      <c r="G96" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H96" t="n">
         <v>0.5</v>
@@ -6823,30 +6823,30 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>run_2025-08-25_21-37-33</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>config_4</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
+      <c r="A97" t="n">
         <v>4</v>
       </c>
+      <c r="B97" t="n">
+        <v>4</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
       <c r="D97" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="E97" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F97" t="n">
-        <v>2</v>
-      </c>
-      <c r="G97" t="n">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
       </c>
       <c r="H97" t="n">
         <v>0.5</v>
@@ -6885,6 +6885,1062 @@
         <v>59.3373858168374</v>
       </c>
       <c r="T97" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>1</v>
+      </c>
+      <c r="B98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E98" t="n">
+        <v>2</v>
+      </c>
+      <c r="F98" t="n">
+        <v>5</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I98" t="n">
+        <v>20</v>
+      </c>
+      <c r="J98" t="n">
+        <v>1</v>
+      </c>
+      <c r="K98" t="n">
+        <v>5</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M98" t="n">
+        <v>50</v>
+      </c>
+      <c r="N98" t="n">
+        <v>22</v>
+      </c>
+      <c r="O98" t="n">
+        <v>30</v>
+      </c>
+      <c r="P98" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>22</v>
+      </c>
+      <c r="R98" t="n">
+        <v>13</v>
+      </c>
+      <c r="S98" t="n">
+        <v>50.3210096574379</v>
+      </c>
+      <c r="T98" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>1</v>
+      </c>
+      <c r="B99" t="n">
+        <v>2</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E99" t="n">
+        <v>2</v>
+      </c>
+      <c r="F99" t="n">
+        <v>5</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I99" t="n">
+        <v>20</v>
+      </c>
+      <c r="J99" t="n">
+        <v>1</v>
+      </c>
+      <c r="K99" t="n">
+        <v>5</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M99" t="n">
+        <v>50</v>
+      </c>
+      <c r="N99" t="n">
+        <v>2</v>
+      </c>
+      <c r="O99" t="n">
+        <v>12</v>
+      </c>
+      <c r="P99" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>2</v>
+      </c>
+      <c r="R99" t="n">
+        <v>12</v>
+      </c>
+      <c r="S99" t="n">
+        <v>54.43999870293889</v>
+      </c>
+      <c r="T99" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>1</v>
+      </c>
+      <c r="B100" t="n">
+        <v>3</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E100" t="n">
+        <v>2</v>
+      </c>
+      <c r="F100" t="n">
+        <v>5</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I100" t="n">
+        <v>20</v>
+      </c>
+      <c r="J100" t="n">
+        <v>1</v>
+      </c>
+      <c r="K100" t="n">
+        <v>5</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M100" t="n">
+        <v>50</v>
+      </c>
+      <c r="N100" t="n">
+        <v>22</v>
+      </c>
+      <c r="O100" t="n">
+        <v>10</v>
+      </c>
+      <c r="P100" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>22</v>
+      </c>
+      <c r="R100" t="n">
+        <v>22</v>
+      </c>
+      <c r="S100" t="n">
+        <v>53.74700036815332</v>
+      </c>
+      <c r="T100" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>1</v>
+      </c>
+      <c r="B101" t="n">
+        <v>4</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E101" t="n">
+        <v>2</v>
+      </c>
+      <c r="F101" t="n">
+        <v>5</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I101" t="n">
+        <v>20</v>
+      </c>
+      <c r="J101" t="n">
+        <v>1</v>
+      </c>
+      <c r="K101" t="n">
+        <v>5</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M101" t="n">
+        <v>50</v>
+      </c>
+      <c r="N101" t="n">
+        <v>23</v>
+      </c>
+      <c r="O101" t="n">
+        <v>3</v>
+      </c>
+      <c r="P101" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>3</v>
+      </c>
+      <c r="R101" t="n">
+        <v>5</v>
+      </c>
+      <c r="S101" t="n">
+        <v>68.30712905157661</v>
+      </c>
+      <c r="T101" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>2</v>
+      </c>
+      <c r="B102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E102" t="n">
+        <v>2</v>
+      </c>
+      <c r="F102" t="n">
+        <v>5</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I102" t="n">
+        <v>20</v>
+      </c>
+      <c r="J102" t="n">
+        <v>1</v>
+      </c>
+      <c r="K102" t="n">
+        <v>5</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M102" t="n">
+        <v>50</v>
+      </c>
+      <c r="N102" t="n">
+        <v>31</v>
+      </c>
+      <c r="O102" t="n">
+        <v>25</v>
+      </c>
+      <c r="P102" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>14</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6</v>
+      </c>
+      <c r="S102" t="n">
+        <v>80.05270792571612</v>
+      </c>
+      <c r="T102" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>2</v>
+      </c>
+      <c r="B103" t="n">
+        <v>2</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E103" t="n">
+        <v>2</v>
+      </c>
+      <c r="F103" t="n">
+        <v>5</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I103" t="n">
+        <v>20</v>
+      </c>
+      <c r="J103" t="n">
+        <v>1</v>
+      </c>
+      <c r="K103" t="n">
+        <v>5</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M103" t="n">
+        <v>50</v>
+      </c>
+      <c r="N103" t="n">
+        <v>22</v>
+      </c>
+      <c r="O103" t="n">
+        <v>1</v>
+      </c>
+      <c r="P103" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>11</v>
+      </c>
+      <c r="R103" t="n">
+        <v>22</v>
+      </c>
+      <c r="S103" t="n">
+        <v>52.95821507321003</v>
+      </c>
+      <c r="T103" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>2</v>
+      </c>
+      <c r="B104" t="n">
+        <v>3</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E104" t="n">
+        <v>2</v>
+      </c>
+      <c r="F104" t="n">
+        <v>5</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I104" t="n">
+        <v>20</v>
+      </c>
+      <c r="J104" t="n">
+        <v>1</v>
+      </c>
+      <c r="K104" t="n">
+        <v>5</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M104" t="n">
+        <v>50</v>
+      </c>
+      <c r="N104" t="n">
+        <v>17</v>
+      </c>
+      <c r="O104" t="n">
+        <v>26</v>
+      </c>
+      <c r="P104" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>25</v>
+      </c>
+      <c r="R104" t="n">
+        <v>24</v>
+      </c>
+      <c r="S104" t="n">
+        <v>80.75688621642344</v>
+      </c>
+      <c r="T104" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>2</v>
+      </c>
+      <c r="B105" t="n">
+        <v>4</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E105" t="n">
+        <v>2</v>
+      </c>
+      <c r="F105" t="n">
+        <v>5</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I105" t="n">
+        <v>20</v>
+      </c>
+      <c r="J105" t="n">
+        <v>1</v>
+      </c>
+      <c r="K105" t="n">
+        <v>5</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M105" t="n">
+        <v>50</v>
+      </c>
+      <c r="N105" t="n">
+        <v>23</v>
+      </c>
+      <c r="O105" t="n">
+        <v>1</v>
+      </c>
+      <c r="P105" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>1</v>
+      </c>
+      <c r="R105" t="n">
+        <v>3</v>
+      </c>
+      <c r="S105" t="n">
+        <v>68.36719176659345</v>
+      </c>
+      <c r="T105" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>3</v>
+      </c>
+      <c r="B106" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E106" t="n">
+        <v>2</v>
+      </c>
+      <c r="F106" t="n">
+        <v>5</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I106" t="n">
+        <v>20</v>
+      </c>
+      <c r="J106" t="n">
+        <v>1</v>
+      </c>
+      <c r="K106" t="n">
+        <v>5</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M106" t="n">
+        <v>50</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>13</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
+        <v>2</v>
+      </c>
+      <c r="S106" t="n">
+        <v>37.35402933294379</v>
+      </c>
+      <c r="T106" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>3</v>
+      </c>
+      <c r="B107" t="n">
+        <v>2</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E107" t="n">
+        <v>2</v>
+      </c>
+      <c r="F107" t="n">
+        <v>5</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I107" t="n">
+        <v>20</v>
+      </c>
+      <c r="J107" t="n">
+        <v>1</v>
+      </c>
+      <c r="K107" t="n">
+        <v>5</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M107" t="n">
+        <v>50</v>
+      </c>
+      <c r="N107" t="n">
+        <v>7</v>
+      </c>
+      <c r="O107" t="n">
+        <v>28</v>
+      </c>
+      <c r="P107" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>8</v>
+      </c>
+      <c r="R107" t="n">
+        <v>10</v>
+      </c>
+      <c r="S107" t="n">
+        <v>68.25142359906067</v>
+      </c>
+      <c r="T107" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>3</v>
+      </c>
+      <c r="B108" t="n">
+        <v>3</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E108" t="n">
+        <v>2</v>
+      </c>
+      <c r="F108" t="n">
+        <v>5</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I108" t="n">
+        <v>20</v>
+      </c>
+      <c r="J108" t="n">
+        <v>1</v>
+      </c>
+      <c r="K108" t="n">
+        <v>5</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M108" t="n">
+        <v>50</v>
+      </c>
+      <c r="N108" t="n">
+        <v>29</v>
+      </c>
+      <c r="O108" t="n">
+        <v>30</v>
+      </c>
+      <c r="P108" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>3</v>
+      </c>
+      <c r="R108" t="n">
+        <v>31</v>
+      </c>
+      <c r="S108" t="n">
+        <v>74.07780777305416</v>
+      </c>
+      <c r="T108" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>3</v>
+      </c>
+      <c r="B109" t="n">
+        <v>4</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E109" t="n">
+        <v>2</v>
+      </c>
+      <c r="F109" t="n">
+        <v>5</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I109" t="n">
+        <v>20</v>
+      </c>
+      <c r="J109" t="n">
+        <v>1</v>
+      </c>
+      <c r="K109" t="n">
+        <v>5</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M109" t="n">
+        <v>50</v>
+      </c>
+      <c r="N109" t="n">
+        <v>4</v>
+      </c>
+      <c r="O109" t="n">
+        <v>26</v>
+      </c>
+      <c r="P109" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>26</v>
+      </c>
+      <c r="R109" t="n">
+        <v>26</v>
+      </c>
+      <c r="S109" t="n">
+        <v>52.9094208814944</v>
+      </c>
+      <c r="T109" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>4</v>
+      </c>
+      <c r="B110" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E110" t="n">
+        <v>2</v>
+      </c>
+      <c r="F110" t="n">
+        <v>5</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I110" t="n">
+        <v>20</v>
+      </c>
+      <c r="J110" t="n">
+        <v>1</v>
+      </c>
+      <c r="K110" t="n">
+        <v>5</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M110" t="n">
+        <v>50</v>
+      </c>
+      <c r="N110" t="n">
+        <v>7</v>
+      </c>
+      <c r="O110" t="n">
+        <v>28</v>
+      </c>
+      <c r="P110" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>18</v>
+      </c>
+      <c r="R110" t="n">
+        <v>20</v>
+      </c>
+      <c r="S110" t="n">
+        <v>66.23680007452545</v>
+      </c>
+      <c r="T110" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>4</v>
+      </c>
+      <c r="B111" t="n">
+        <v>2</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E111" t="n">
+        <v>2</v>
+      </c>
+      <c r="F111" t="n">
+        <v>5</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I111" t="n">
+        <v>20</v>
+      </c>
+      <c r="J111" t="n">
+        <v>1</v>
+      </c>
+      <c r="K111" t="n">
+        <v>5</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M111" t="n">
+        <v>50</v>
+      </c>
+      <c r="N111" t="n">
+        <v>24</v>
+      </c>
+      <c r="O111" t="n">
+        <v>15</v>
+      </c>
+      <c r="P111" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>24</v>
+      </c>
+      <c r="R111" t="n">
+        <v>16</v>
+      </c>
+      <c r="S111" t="n">
+        <v>54.49533691903626</v>
+      </c>
+      <c r="T111" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>4</v>
+      </c>
+      <c r="B112" t="n">
+        <v>3</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E112" t="n">
+        <v>2</v>
+      </c>
+      <c r="F112" t="n">
+        <v>5</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I112" t="n">
+        <v>20</v>
+      </c>
+      <c r="J112" t="n">
+        <v>1</v>
+      </c>
+      <c r="K112" t="n">
+        <v>5</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M112" t="n">
+        <v>50</v>
+      </c>
+      <c r="N112" t="n">
+        <v>5</v>
+      </c>
+      <c r="O112" t="n">
+        <v>23</v>
+      </c>
+      <c r="P112" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>23</v>
+      </c>
+      <c r="R112" t="n">
+        <v>25</v>
+      </c>
+      <c r="S112" t="n">
+        <v>52.33167472531786</v>
+      </c>
+      <c r="T112" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>4</v>
+      </c>
+      <c r="B113" t="n">
+        <v>4</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>[14, 15, 14, 18, 20]</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E113" t="n">
+        <v>2</v>
+      </c>
+      <c r="F113" t="n">
+        <v>5</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>[0, 31]</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I113" t="n">
+        <v>20</v>
+      </c>
+      <c r="J113" t="n">
+        <v>1</v>
+      </c>
+      <c r="K113" t="n">
+        <v>5</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M113" t="n">
+        <v>50</v>
+      </c>
+      <c r="N113" t="n">
+        <v>12</v>
+      </c>
+      <c r="O113" t="n">
+        <v>12</v>
+      </c>
+      <c r="P113" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>12</v>
+      </c>
+      <c r="R113" t="n">
+        <v>14</v>
+      </c>
+      <c r="S113" t="n">
+        <v>52.03405360298243</v>
+      </c>
+      <c r="T113" t="n">
         <v>19</v>
       </c>
     </row>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -422,6 +422,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001072BA"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -422,20 +422,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001072BA"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:T113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
@@ -454,39 +453,39 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>pasta_run</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>configuracao</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>execucao</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>config_num</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>exec_num</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>param_ARRAY_VAR</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>param_CROSSOVER</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>param_DELTA_MIN</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>param_IND_SIZE</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>param_LIMITE_VAR</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>param_MUTACAO</t>
@@ -554,30 +553,30 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-39-32</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
       </c>
       <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
         <v>0.1</v>
       </c>
-      <c r="E2" t="n">
-        <v>2</v>
-      </c>
       <c r="F2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
       </c>
       <c r="H2" t="n">
         <v>0.15</v>
@@ -620,30 +619,30 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-39-32</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
       </c>
       <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.1</v>
       </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
       <c r="F3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
       </c>
       <c r="H3" t="n">
         <v>0.15</v>
@@ -686,30 +685,30 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" t="n">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-39-32</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>3</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
       <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.1</v>
       </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
       <c r="F4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5</v>
       </c>
       <c r="H4" t="n">
         <v>0.15</v>
@@ -752,30 +751,30 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" t="n">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-39-32</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>4</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
       <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
         <v>0.1</v>
       </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
       <c r="F5" t="n">
-        <v>5</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5</v>
       </c>
       <c r="H5" t="n">
         <v>0.15</v>
@@ -818,30 +817,30 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-39-32</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
       </c>
       <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
         <v>0.9</v>
       </c>
-      <c r="E6" t="n">
-        <v>2</v>
-      </c>
       <c r="F6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5</v>
       </c>
       <c r="H6" t="n">
         <v>0.15</v>
@@ -884,30 +883,30 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-39-32</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
       </c>
       <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
         <v>0.9</v>
       </c>
-      <c r="E7" t="n">
-        <v>2</v>
-      </c>
       <c r="F7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5</v>
       </c>
       <c r="H7" t="n">
         <v>0.15</v>
@@ -950,30 +949,30 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" t="n">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-39-32</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>3</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
       <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
         <v>0.9</v>
       </c>
-      <c r="E8" t="n">
-        <v>2</v>
-      </c>
       <c r="F8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5</v>
       </c>
       <c r="H8" t="n">
         <v>0.15</v>
@@ -1016,30 +1015,30 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" t="n">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-39-32</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>4</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
       <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
         <v>0.9</v>
       </c>
-      <c r="E9" t="n">
-        <v>2</v>
-      </c>
       <c r="F9" t="n">
-        <v>5</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5</v>
       </c>
       <c r="H9" t="n">
         <v>0.15</v>
@@ -1082,30 +1081,30 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-39-32</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
         <v>3</v>
       </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>0.1</v>
       </c>
-      <c r="E10" t="n">
-        <v>2</v>
-      </c>
       <c r="F10" t="n">
-        <v>5</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
       </c>
       <c r="H10" t="n">
         <v>0.5</v>
@@ -1148,30 +1147,30 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-39-32</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
         <v>3</v>
       </c>
-      <c r="B11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>0.1</v>
       </c>
-      <c r="E11" t="n">
-        <v>2</v>
-      </c>
       <c r="F11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5</v>
       </c>
       <c r="H11" t="n">
         <v>0.5</v>
@@ -1214,30 +1213,30 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-39-32</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" t="n">
+      <c r="D12" t="n">
         <v>3</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>0.1</v>
       </c>
-      <c r="E12" t="n">
-        <v>2</v>
-      </c>
       <c r="F12" t="n">
-        <v>5</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5</v>
       </c>
       <c r="H12" t="n">
         <v>0.5</v>
@@ -1280,30 +1279,30 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-39-32</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
         <v>3</v>
       </c>
-      <c r="B13" t="n">
-        <v>4</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>0.1</v>
       </c>
-      <c r="E13" t="n">
-        <v>2</v>
-      </c>
       <c r="F13" t="n">
-        <v>5</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5</v>
       </c>
       <c r="H13" t="n">
         <v>0.5</v>
@@ -1346,30 +1345,30 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-39-32</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
         <v>4</v>
       </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>0.9</v>
       </c>
-      <c r="E14" t="n">
-        <v>2</v>
-      </c>
       <c r="F14" t="n">
-        <v>5</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5</v>
       </c>
       <c r="H14" t="n">
         <v>0.5</v>
@@ -1412,30 +1411,30 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-39-32</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
         <v>4</v>
       </c>
-      <c r="B15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>0.9</v>
       </c>
-      <c r="E15" t="n">
-        <v>2</v>
-      </c>
       <c r="F15" t="n">
-        <v>5</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5</v>
       </c>
       <c r="H15" t="n">
         <v>0.5</v>
@@ -1478,30 +1477,30 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-39-32</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
         <v>4</v>
       </c>
-      <c r="B16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>0.9</v>
       </c>
-      <c r="E16" t="n">
-        <v>2</v>
-      </c>
       <c r="F16" t="n">
-        <v>5</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5</v>
       </c>
       <c r="H16" t="n">
         <v>0.5</v>
@@ -1544,30 +1543,30 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-39-32</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
         <v>4</v>
       </c>
-      <c r="B17" t="n">
+      <c r="D17" t="n">
         <v>4</v>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>0.9</v>
       </c>
-      <c r="E17" t="n">
-        <v>2</v>
-      </c>
       <c r="F17" t="n">
-        <v>5</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5</v>
       </c>
       <c r="H17" t="n">
         <v>0.5</v>
@@ -1610,30 +1609,30 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>1</v>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-51-18</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
       </c>
       <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
         <v>0.1</v>
       </c>
-      <c r="E18" t="n">
-        <v>2</v>
-      </c>
       <c r="F18" t="n">
-        <v>5</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5</v>
       </c>
       <c r="H18" t="n">
         <v>0.15</v>
@@ -1676,30 +1675,30 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>1</v>
-      </c>
-      <c r="B19" t="n">
-        <v>2</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-51-18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
       </c>
       <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
         <v>0.1</v>
       </c>
-      <c r="E19" t="n">
-        <v>2</v>
-      </c>
       <c r="F19" t="n">
-        <v>5</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5</v>
       </c>
       <c r="H19" t="n">
         <v>0.15</v>
@@ -1742,30 +1741,30 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>1</v>
-      </c>
-      <c r="B20" t="n">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-51-18</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
         <v>3</v>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
       <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
         <v>0.1</v>
       </c>
-      <c r="E20" t="n">
-        <v>2</v>
-      </c>
       <c r="F20" t="n">
-        <v>5</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5</v>
       </c>
       <c r="H20" t="n">
         <v>0.15</v>
@@ -1808,30 +1807,30 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>1</v>
-      </c>
-      <c r="B21" t="n">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-51-18</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
         <v>4</v>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
       <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
         <v>0.1</v>
       </c>
-      <c r="E21" t="n">
-        <v>2</v>
-      </c>
       <c r="F21" t="n">
-        <v>5</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>5</v>
       </c>
       <c r="H21" t="n">
         <v>0.15</v>
@@ -1874,30 +1873,30 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>2</v>
-      </c>
-      <c r="B22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-51-18</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
       </c>
       <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
         <v>0.9</v>
       </c>
-      <c r="E22" t="n">
-        <v>2</v>
-      </c>
       <c r="F22" t="n">
-        <v>5</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5</v>
       </c>
       <c r="H22" t="n">
         <v>0.15</v>
@@ -1940,30 +1939,30 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>2</v>
-      </c>
-      <c r="B23" t="n">
-        <v>2</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-51-18</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
       </c>
       <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
         <v>0.9</v>
       </c>
-      <c r="E23" t="n">
-        <v>2</v>
-      </c>
       <c r="F23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5</v>
       </c>
       <c r="H23" t="n">
         <v>0.15</v>
@@ -2006,30 +2005,30 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>2</v>
-      </c>
-      <c r="B24" t="n">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-51-18</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
         <v>3</v>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
       <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
         <v>0.9</v>
       </c>
-      <c r="E24" t="n">
-        <v>2</v>
-      </c>
       <c r="F24" t="n">
-        <v>5</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5</v>
       </c>
       <c r="H24" t="n">
         <v>0.15</v>
@@ -2072,30 +2071,30 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>2</v>
-      </c>
-      <c r="B25" t="n">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-51-18</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
         <v>4</v>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
       <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
         <v>0.9</v>
       </c>
-      <c r="E25" t="n">
-        <v>2</v>
-      </c>
       <c r="F25" t="n">
-        <v>5</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5</v>
       </c>
       <c r="H25" t="n">
         <v>0.15</v>
@@ -2138,30 +2137,30 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-51-18</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
         <v>3</v>
       </c>
-      <c r="B26" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>0.1</v>
       </c>
-      <c r="E26" t="n">
-        <v>2</v>
-      </c>
       <c r="F26" t="n">
-        <v>5</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5</v>
       </c>
       <c r="H26" t="n">
         <v>0.5</v>
@@ -2204,30 +2203,30 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-51-18</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="n">
         <v>3</v>
       </c>
-      <c r="B27" t="n">
-        <v>2</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>0.1</v>
       </c>
-      <c r="E27" t="n">
-        <v>2</v>
-      </c>
       <c r="F27" t="n">
-        <v>5</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G27" t="n">
+        <v>5</v>
       </c>
       <c r="H27" t="n">
         <v>0.5</v>
@@ -2270,30 +2269,30 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-51-18</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
         <v>3</v>
       </c>
-      <c r="B28" t="n">
+      <c r="D28" t="n">
         <v>3</v>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>0.1</v>
       </c>
-      <c r="E28" t="n">
-        <v>2</v>
-      </c>
       <c r="F28" t="n">
-        <v>5</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G28" t="n">
+        <v>5</v>
       </c>
       <c r="H28" t="n">
         <v>0.5</v>
@@ -2336,30 +2335,30 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-51-18</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" t="n">
         <v>3</v>
       </c>
-      <c r="B29" t="n">
-        <v>4</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>0.1</v>
       </c>
-      <c r="E29" t="n">
-        <v>2</v>
-      </c>
       <c r="F29" t="n">
-        <v>5</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5</v>
       </c>
       <c r="H29" t="n">
         <v>0.5</v>
@@ -2402,30 +2401,30 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-51-18</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
         <v>4</v>
       </c>
-      <c r="B30" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
         <v>0.9</v>
       </c>
-      <c r="E30" t="n">
-        <v>2</v>
-      </c>
       <c r="F30" t="n">
-        <v>5</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5</v>
       </c>
       <c r="H30" t="n">
         <v>0.5</v>
@@ -2468,30 +2467,30 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-51-18</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="n">
         <v>4</v>
       </c>
-      <c r="B31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
         <v>0.9</v>
       </c>
-      <c r="E31" t="n">
-        <v>2</v>
-      </c>
       <c r="F31" t="n">
-        <v>5</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G31" t="n">
+        <v>5</v>
       </c>
       <c r="H31" t="n">
         <v>0.5</v>
@@ -2534,30 +2533,30 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-51-18</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="n">
         <v>4</v>
       </c>
-      <c r="B32" t="n">
-        <v>3</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
         <v>0.9</v>
       </c>
-      <c r="E32" t="n">
-        <v>2</v>
-      </c>
       <c r="F32" t="n">
-        <v>5</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G32" t="n">
+        <v>5</v>
       </c>
       <c r="H32" t="n">
         <v>0.5</v>
@@ -2600,30 +2599,30 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_20-51-18</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
         <v>4</v>
       </c>
-      <c r="B33" t="n">
+      <c r="D33" t="n">
         <v>4</v>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
+      <c r="E33" t="n">
         <v>0.9</v>
       </c>
-      <c r="E33" t="n">
-        <v>2</v>
-      </c>
       <c r="F33" t="n">
-        <v>5</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G33" t="n">
+        <v>5</v>
       </c>
       <c r="H33" t="n">
         <v>0.5</v>
@@ -2666,30 +2665,30 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>1</v>
-      </c>
-      <c r="B34" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-03-46</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
       </c>
       <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
         <v>0.1</v>
       </c>
-      <c r="E34" t="n">
-        <v>2</v>
-      </c>
       <c r="F34" t="n">
-        <v>5</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G34" t="n">
+        <v>5</v>
       </c>
       <c r="H34" t="n">
         <v>0.15</v>
@@ -2732,30 +2731,30 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>1</v>
-      </c>
-      <c r="B35" t="n">
-        <v>2</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-03-46</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
       </c>
       <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
         <v>0.1</v>
       </c>
-      <c r="E35" t="n">
-        <v>2</v>
-      </c>
       <c r="F35" t="n">
-        <v>5</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G35" t="n">
+        <v>5</v>
       </c>
       <c r="H35" t="n">
         <v>0.15</v>
@@ -2798,30 +2797,30 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>1</v>
-      </c>
-      <c r="B36" t="n">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-03-46</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
         <v>3</v>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
       <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
         <v>0.1</v>
       </c>
-      <c r="E36" t="n">
-        <v>2</v>
-      </c>
       <c r="F36" t="n">
-        <v>5</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G36" t="n">
+        <v>5</v>
       </c>
       <c r="H36" t="n">
         <v>0.15</v>
@@ -2864,30 +2863,30 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
-        <v>1</v>
-      </c>
-      <c r="B37" t="n">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-03-46</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
         <v>4</v>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
       <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
         <v>0.1</v>
       </c>
-      <c r="E37" t="n">
-        <v>2</v>
-      </c>
       <c r="F37" t="n">
-        <v>5</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G37" t="n">
+        <v>5</v>
       </c>
       <c r="H37" t="n">
         <v>0.15</v>
@@ -2930,30 +2929,30 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>2</v>
-      </c>
-      <c r="B38" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-03-46</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
       </c>
       <c r="D38" t="n">
+        <v>2</v>
+      </c>
+      <c r="E38" t="n">
         <v>0.9</v>
       </c>
-      <c r="E38" t="n">
-        <v>2</v>
-      </c>
       <c r="F38" t="n">
-        <v>5</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G38" t="n">
+        <v>5</v>
       </c>
       <c r="H38" t="n">
         <v>0.15</v>
@@ -2996,30 +2995,30 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
-        <v>2</v>
-      </c>
-      <c r="B39" t="n">
-        <v>2</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-03-46</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2</v>
       </c>
       <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="n">
         <v>0.9</v>
       </c>
-      <c r="E39" t="n">
-        <v>2</v>
-      </c>
       <c r="F39" t="n">
-        <v>5</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G39" t="n">
+        <v>5</v>
       </c>
       <c r="H39" t="n">
         <v>0.15</v>
@@ -3062,30 +3061,30 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
-        <v>2</v>
-      </c>
-      <c r="B40" t="n">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-03-46</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
         <v>3</v>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
       <c r="D40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" t="n">
         <v>0.9</v>
       </c>
-      <c r="E40" t="n">
-        <v>2</v>
-      </c>
       <c r="F40" t="n">
-        <v>5</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G40" t="n">
+        <v>5</v>
       </c>
       <c r="H40" t="n">
         <v>0.15</v>
@@ -3128,30 +3127,30 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
-        <v>2</v>
-      </c>
-      <c r="B41" t="n">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-03-46</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
         <v>4</v>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
       <c r="D41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" t="n">
         <v>0.9</v>
       </c>
-      <c r="E41" t="n">
-        <v>2</v>
-      </c>
       <c r="F41" t="n">
-        <v>5</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G41" t="n">
+        <v>5</v>
       </c>
       <c r="H41" t="n">
         <v>0.15</v>
@@ -3194,30 +3193,30 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-03-46</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
         <v>3</v>
       </c>
-      <c r="B42" t="n">
-        <v>1</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
+      <c r="E42" t="n">
         <v>0.1</v>
       </c>
-      <c r="E42" t="n">
-        <v>2</v>
-      </c>
       <c r="F42" t="n">
-        <v>5</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G42" t="n">
+        <v>5</v>
       </c>
       <c r="H42" t="n">
         <v>0.5</v>
@@ -3260,30 +3259,30 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-03-46</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="n">
         <v>3</v>
       </c>
-      <c r="B43" t="n">
-        <v>2</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
+      <c r="E43" t="n">
         <v>0.1</v>
       </c>
-      <c r="E43" t="n">
-        <v>2</v>
-      </c>
       <c r="F43" t="n">
-        <v>5</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G43" t="n">
+        <v>5</v>
       </c>
       <c r="H43" t="n">
         <v>0.5</v>
@@ -3326,30 +3325,30 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-03-46</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
         <v>3</v>
       </c>
-      <c r="B44" t="n">
+      <c r="D44" t="n">
         <v>3</v>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
+      <c r="E44" t="n">
         <v>0.1</v>
       </c>
-      <c r="E44" t="n">
-        <v>2</v>
-      </c>
       <c r="F44" t="n">
-        <v>5</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G44" t="n">
+        <v>5</v>
       </c>
       <c r="H44" t="n">
         <v>0.5</v>
@@ -3392,30 +3391,30 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-03-46</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>4</v>
+      </c>
+      <c r="D45" t="n">
         <v>3</v>
       </c>
-      <c r="B45" t="n">
-        <v>4</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
+      <c r="E45" t="n">
         <v>0.1</v>
       </c>
-      <c r="E45" t="n">
-        <v>2</v>
-      </c>
       <c r="F45" t="n">
-        <v>5</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G45" t="n">
+        <v>5</v>
       </c>
       <c r="H45" t="n">
         <v>0.5</v>
@@ -3458,30 +3457,30 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="n">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-03-46</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
         <v>4</v>
       </c>
-      <c r="B46" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
+      <c r="E46" t="n">
         <v>0.9</v>
       </c>
-      <c r="E46" t="n">
-        <v>2</v>
-      </c>
       <c r="F46" t="n">
-        <v>5</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G46" t="n">
+        <v>5</v>
       </c>
       <c r="H46" t="n">
         <v>0.5</v>
@@ -3524,30 +3523,30 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-03-46</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" t="n">
         <v>4</v>
       </c>
-      <c r="B47" t="n">
-        <v>2</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
+      <c r="E47" t="n">
         <v>0.9</v>
       </c>
-      <c r="E47" t="n">
-        <v>2</v>
-      </c>
       <c r="F47" t="n">
-        <v>5</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G47" t="n">
+        <v>5</v>
       </c>
       <c r="H47" t="n">
         <v>0.5</v>
@@ -3590,30 +3589,30 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-03-46</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" t="n">
         <v>4</v>
       </c>
-      <c r="B48" t="n">
-        <v>3</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
+      <c r="E48" t="n">
         <v>0.9</v>
       </c>
-      <c r="E48" t="n">
-        <v>2</v>
-      </c>
       <c r="F48" t="n">
-        <v>5</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G48" t="n">
+        <v>5</v>
       </c>
       <c r="H48" t="n">
         <v>0.5</v>
@@ -3656,30 +3655,30 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-03-46</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
         <v>4</v>
       </c>
-      <c r="B49" t="n">
+      <c r="D49" t="n">
         <v>4</v>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
+      <c r="E49" t="n">
         <v>0.9</v>
       </c>
-      <c r="E49" t="n">
-        <v>2</v>
-      </c>
       <c r="F49" t="n">
-        <v>5</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G49" t="n">
+        <v>5</v>
       </c>
       <c r="H49" t="n">
         <v>0.5</v>
@@ -3722,30 +3721,30 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
-        <v>1</v>
-      </c>
-      <c r="B50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-15-35</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
       </c>
       <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="n">
         <v>0.1</v>
       </c>
-      <c r="E50" t="n">
-        <v>2</v>
-      </c>
       <c r="F50" t="n">
-        <v>5</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G50" t="n">
+        <v>5</v>
       </c>
       <c r="H50" t="n">
         <v>0.15</v>
@@ -3788,30 +3787,30 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
-        <v>1</v>
-      </c>
-      <c r="B51" t="n">
-        <v>2</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-15-35</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>2</v>
       </c>
       <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
         <v>0.1</v>
       </c>
-      <c r="E51" t="n">
-        <v>2</v>
-      </c>
       <c r="F51" t="n">
-        <v>5</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G51" t="n">
+        <v>5</v>
       </c>
       <c r="H51" t="n">
         <v>0.15</v>
@@ -3854,30 +3853,30 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="n">
-        <v>1</v>
-      </c>
-      <c r="B52" t="n">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-15-35</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
         <v>3</v>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
       <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="n">
         <v>0.1</v>
       </c>
-      <c r="E52" t="n">
-        <v>2</v>
-      </c>
       <c r="F52" t="n">
-        <v>5</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G52" t="n">
+        <v>5</v>
       </c>
       <c r="H52" t="n">
         <v>0.15</v>
@@ -3920,30 +3919,30 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="n">
-        <v>1</v>
-      </c>
-      <c r="B53" t="n">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-15-35</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
         <v>4</v>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
       <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="n">
         <v>0.1</v>
       </c>
-      <c r="E53" t="n">
-        <v>2</v>
-      </c>
       <c r="F53" t="n">
-        <v>5</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G53" t="n">
+        <v>5</v>
       </c>
       <c r="H53" t="n">
         <v>0.15</v>
@@ -3986,30 +3985,30 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="n">
-        <v>2</v>
-      </c>
-      <c r="B54" t="n">
-        <v>1</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-15-35</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
       </c>
       <c r="D54" t="n">
+        <v>2</v>
+      </c>
+      <c r="E54" t="n">
         <v>0.9</v>
       </c>
-      <c r="E54" t="n">
-        <v>2</v>
-      </c>
       <c r="F54" t="n">
-        <v>5</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G54" t="n">
+        <v>5</v>
       </c>
       <c r="H54" t="n">
         <v>0.15</v>
@@ -4052,30 +4051,30 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="n">
-        <v>2</v>
-      </c>
-      <c r="B55" t="n">
-        <v>2</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-15-35</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>2</v>
       </c>
       <c r="D55" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" t="n">
         <v>0.9</v>
       </c>
-      <c r="E55" t="n">
-        <v>2</v>
-      </c>
       <c r="F55" t="n">
-        <v>5</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G55" t="n">
+        <v>5</v>
       </c>
       <c r="H55" t="n">
         <v>0.15</v>
@@ -4118,30 +4117,30 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="n">
-        <v>2</v>
-      </c>
-      <c r="B56" t="n">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-15-35</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
         <v>3</v>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
       <c r="D56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E56" t="n">
         <v>0.9</v>
       </c>
-      <c r="E56" t="n">
-        <v>2</v>
-      </c>
       <c r="F56" t="n">
-        <v>5</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G56" t="n">
+        <v>5</v>
       </c>
       <c r="H56" t="n">
         <v>0.15</v>
@@ -4184,30 +4183,30 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="n">
-        <v>2</v>
-      </c>
-      <c r="B57" t="n">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-15-35</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
         <v>4</v>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
       <c r="D57" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" t="n">
         <v>0.9</v>
       </c>
-      <c r="E57" t="n">
-        <v>2</v>
-      </c>
       <c r="F57" t="n">
-        <v>5</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G57" t="n">
+        <v>5</v>
       </c>
       <c r="H57" t="n">
         <v>0.15</v>
@@ -4250,30 +4249,30 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="n">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-15-35</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
         <v>3</v>
       </c>
-      <c r="B58" t="n">
-        <v>1</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
+      <c r="E58" t="n">
         <v>0.1</v>
       </c>
-      <c r="E58" t="n">
-        <v>2</v>
-      </c>
       <c r="F58" t="n">
-        <v>5</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G58" t="n">
+        <v>5</v>
       </c>
       <c r="H58" t="n">
         <v>0.5</v>
@@ -4316,30 +4315,30 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="n">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-15-35</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" t="n">
         <v>3</v>
       </c>
-      <c r="B59" t="n">
-        <v>2</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
+      <c r="E59" t="n">
         <v>0.1</v>
       </c>
-      <c r="E59" t="n">
-        <v>2</v>
-      </c>
       <c r="F59" t="n">
-        <v>5</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G59" t="n">
+        <v>5</v>
       </c>
       <c r="H59" t="n">
         <v>0.5</v>
@@ -4382,30 +4381,30 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="n">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-15-35</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
         <v>3</v>
       </c>
-      <c r="B60" t="n">
+      <c r="D60" t="n">
         <v>3</v>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
+      <c r="E60" t="n">
         <v>0.1</v>
       </c>
-      <c r="E60" t="n">
-        <v>2</v>
-      </c>
       <c r="F60" t="n">
-        <v>5</v>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G60" t="n">
+        <v>5</v>
       </c>
       <c r="H60" t="n">
         <v>0.5</v>
@@ -4448,30 +4447,30 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="n">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-15-35</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>4</v>
+      </c>
+      <c r="D61" t="n">
         <v>3</v>
       </c>
-      <c r="B61" t="n">
-        <v>4</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
+      <c r="E61" t="n">
         <v>0.1</v>
       </c>
-      <c r="E61" t="n">
-        <v>2</v>
-      </c>
       <c r="F61" t="n">
-        <v>5</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G61" t="n">
+        <v>5</v>
       </c>
       <c r="H61" t="n">
         <v>0.5</v>
@@ -4514,30 +4513,30 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="n">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-15-35</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="n">
         <v>4</v>
       </c>
-      <c r="B62" t="n">
-        <v>1</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
+      <c r="E62" t="n">
         <v>0.9</v>
       </c>
-      <c r="E62" t="n">
-        <v>2</v>
-      </c>
       <c r="F62" t="n">
-        <v>5</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G62" t="n">
+        <v>5</v>
       </c>
       <c r="H62" t="n">
         <v>0.5</v>
@@ -4580,30 +4579,30 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="n">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-15-35</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" t="n">
         <v>4</v>
       </c>
-      <c r="B63" t="n">
-        <v>2</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
+      <c r="E63" t="n">
         <v>0.9</v>
       </c>
-      <c r="E63" t="n">
-        <v>2</v>
-      </c>
       <c r="F63" t="n">
-        <v>5</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G63" t="n">
+        <v>5</v>
       </c>
       <c r="H63" t="n">
         <v>0.5</v>
@@ -4646,30 +4645,30 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="n">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-15-35</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>3</v>
+      </c>
+      <c r="D64" t="n">
         <v>4</v>
       </c>
-      <c r="B64" t="n">
-        <v>3</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
+      <c r="E64" t="n">
         <v>0.9</v>
       </c>
-      <c r="E64" t="n">
-        <v>2</v>
-      </c>
       <c r="F64" t="n">
-        <v>5</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G64" t="n">
+        <v>5</v>
       </c>
       <c r="H64" t="n">
         <v>0.5</v>
@@ -4712,30 +4711,30 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="n">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-15-35</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
         <v>4</v>
       </c>
-      <c r="B65" t="n">
+      <c r="D65" t="n">
         <v>4</v>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
+      <c r="E65" t="n">
         <v>0.9</v>
       </c>
-      <c r="E65" t="n">
-        <v>2</v>
-      </c>
       <c r="F65" t="n">
-        <v>5</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G65" t="n">
+        <v>5</v>
       </c>
       <c r="H65" t="n">
         <v>0.5</v>
@@ -4778,30 +4777,30 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="n">
-        <v>1</v>
-      </c>
-      <c r="B66" t="n">
-        <v>1</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-26-42</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
       </c>
       <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="n">
         <v>0.1</v>
       </c>
-      <c r="E66" t="n">
-        <v>2</v>
-      </c>
       <c r="F66" t="n">
-        <v>5</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G66" t="n">
+        <v>5</v>
       </c>
       <c r="H66" t="n">
         <v>0.15</v>
@@ -4844,30 +4843,30 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="n">
-        <v>1</v>
-      </c>
-      <c r="B67" t="n">
-        <v>2</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-26-42</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>2</v>
       </c>
       <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="n">
         <v>0.1</v>
       </c>
-      <c r="E67" t="n">
-        <v>2</v>
-      </c>
       <c r="F67" t="n">
-        <v>5</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G67" t="n">
+        <v>5</v>
       </c>
       <c r="H67" t="n">
         <v>0.15</v>
@@ -4910,30 +4909,30 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="n">
-        <v>1</v>
-      </c>
-      <c r="B68" t="n">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-26-42</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
         <v>3</v>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
       <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
         <v>0.1</v>
       </c>
-      <c r="E68" t="n">
-        <v>2</v>
-      </c>
       <c r="F68" t="n">
-        <v>5</v>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G68" t="n">
+        <v>5</v>
       </c>
       <c r="H68" t="n">
         <v>0.15</v>
@@ -4976,30 +4975,30 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
-        <v>1</v>
-      </c>
-      <c r="B69" t="n">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-26-42</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
         <v>4</v>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
       <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="n">
         <v>0.1</v>
       </c>
-      <c r="E69" t="n">
-        <v>2</v>
-      </c>
       <c r="F69" t="n">
-        <v>5</v>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G69" t="n">
+        <v>5</v>
       </c>
       <c r="H69" t="n">
         <v>0.15</v>
@@ -5042,30 +5041,30 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="n">
-        <v>2</v>
-      </c>
-      <c r="B70" t="n">
-        <v>1</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-26-42</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
       </c>
       <c r="D70" t="n">
+        <v>2</v>
+      </c>
+      <c r="E70" t="n">
         <v>0.9</v>
       </c>
-      <c r="E70" t="n">
-        <v>2</v>
-      </c>
       <c r="F70" t="n">
-        <v>5</v>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G70" t="n">
+        <v>5</v>
       </c>
       <c r="H70" t="n">
         <v>0.15</v>
@@ -5108,30 +5107,30 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="n">
-        <v>2</v>
-      </c>
-      <c r="B71" t="n">
-        <v>2</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-26-42</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>2</v>
       </c>
       <c r="D71" t="n">
+        <v>2</v>
+      </c>
+      <c r="E71" t="n">
         <v>0.9</v>
       </c>
-      <c r="E71" t="n">
-        <v>2</v>
-      </c>
       <c r="F71" t="n">
-        <v>5</v>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G71" t="n">
+        <v>5</v>
       </c>
       <c r="H71" t="n">
         <v>0.15</v>
@@ -5174,30 +5173,30 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="n">
-        <v>2</v>
-      </c>
-      <c r="B72" t="n">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-26-42</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
         <v>3</v>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
       <c r="D72" t="n">
+        <v>2</v>
+      </c>
+      <c r="E72" t="n">
         <v>0.9</v>
       </c>
-      <c r="E72" t="n">
-        <v>2</v>
-      </c>
       <c r="F72" t="n">
-        <v>5</v>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G72" t="n">
+        <v>5</v>
       </c>
       <c r="H72" t="n">
         <v>0.15</v>
@@ -5240,30 +5239,30 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="n">
-        <v>2</v>
-      </c>
-      <c r="B73" t="n">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-26-42</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
         <v>4</v>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
       <c r="D73" t="n">
+        <v>2</v>
+      </c>
+      <c r="E73" t="n">
         <v>0.9</v>
       </c>
-      <c r="E73" t="n">
-        <v>2</v>
-      </c>
       <c r="F73" t="n">
-        <v>5</v>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G73" t="n">
+        <v>5</v>
       </c>
       <c r="H73" t="n">
         <v>0.15</v>
@@ -5306,30 +5305,30 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="n">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-26-42</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="n">
         <v>3</v>
       </c>
-      <c r="B74" t="n">
-        <v>1</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
+      <c r="E74" t="n">
         <v>0.1</v>
       </c>
-      <c r="E74" t="n">
-        <v>2</v>
-      </c>
       <c r="F74" t="n">
-        <v>5</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G74" t="n">
+        <v>5</v>
       </c>
       <c r="H74" t="n">
         <v>0.5</v>
@@ -5372,30 +5371,30 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="n">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-26-42</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2</v>
+      </c>
+      <c r="D75" t="n">
         <v>3</v>
       </c>
-      <c r="B75" t="n">
-        <v>2</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
+      <c r="E75" t="n">
         <v>0.1</v>
       </c>
-      <c r="E75" t="n">
-        <v>2</v>
-      </c>
       <c r="F75" t="n">
-        <v>5</v>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G75" t="n">
+        <v>5</v>
       </c>
       <c r="H75" t="n">
         <v>0.5</v>
@@ -5438,30 +5437,30 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="n">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-26-42</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
         <v>3</v>
       </c>
-      <c r="B76" t="n">
+      <c r="D76" t="n">
         <v>3</v>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
+      <c r="E76" t="n">
         <v>0.1</v>
       </c>
-      <c r="E76" t="n">
-        <v>2</v>
-      </c>
       <c r="F76" t="n">
-        <v>5</v>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G76" t="n">
+        <v>5</v>
       </c>
       <c r="H76" t="n">
         <v>0.5</v>
@@ -5504,30 +5503,30 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="n">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-26-42</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>4</v>
+      </c>
+      <c r="D77" t="n">
         <v>3</v>
       </c>
-      <c r="B77" t="n">
-        <v>4</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
+      <c r="E77" t="n">
         <v>0.1</v>
       </c>
-      <c r="E77" t="n">
-        <v>2</v>
-      </c>
       <c r="F77" t="n">
-        <v>5</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G77" t="n">
+        <v>5</v>
       </c>
       <c r="H77" t="n">
         <v>0.5</v>
@@ -5570,30 +5569,30 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="n">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-26-42</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="n">
         <v>4</v>
       </c>
-      <c r="B78" t="n">
-        <v>1</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
+      <c r="E78" t="n">
         <v>0.9</v>
       </c>
-      <c r="E78" t="n">
-        <v>2</v>
-      </c>
       <c r="F78" t="n">
-        <v>5</v>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G78" t="n">
+        <v>5</v>
       </c>
       <c r="H78" t="n">
         <v>0.5</v>
@@ -5636,30 +5635,30 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="n">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-26-42</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>2</v>
+      </c>
+      <c r="D79" t="n">
         <v>4</v>
       </c>
-      <c r="B79" t="n">
-        <v>2</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
+      <c r="E79" t="n">
         <v>0.9</v>
       </c>
-      <c r="E79" t="n">
-        <v>2</v>
-      </c>
       <c r="F79" t="n">
-        <v>5</v>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G79" t="n">
+        <v>5</v>
       </c>
       <c r="H79" t="n">
         <v>0.5</v>
@@ -5702,30 +5701,30 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="n">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-26-42</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>3</v>
+      </c>
+      <c r="D80" t="n">
         <v>4</v>
       </c>
-      <c r="B80" t="n">
-        <v>3</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
+      <c r="E80" t="n">
         <v>0.9</v>
       </c>
-      <c r="E80" t="n">
-        <v>2</v>
-      </c>
       <c r="F80" t="n">
-        <v>5</v>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G80" t="n">
+        <v>5</v>
       </c>
       <c r="H80" t="n">
         <v>0.5</v>
@@ -5768,30 +5767,30 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="n">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-26-42</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
         <v>4</v>
       </c>
-      <c r="B81" t="n">
+      <c r="D81" t="n">
         <v>4</v>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
+      <c r="E81" t="n">
         <v>0.9</v>
       </c>
-      <c r="E81" t="n">
-        <v>2</v>
-      </c>
       <c r="F81" t="n">
-        <v>5</v>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G81" t="n">
+        <v>5</v>
       </c>
       <c r="H81" t="n">
         <v>0.5</v>
@@ -5834,30 +5833,30 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="n">
-        <v>1</v>
-      </c>
-      <c r="B82" t="n">
-        <v>1</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-37-33</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
       </c>
       <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="n">
         <v>0.1</v>
       </c>
-      <c r="E82" t="n">
-        <v>2</v>
-      </c>
       <c r="F82" t="n">
-        <v>5</v>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G82" t="n">
+        <v>5</v>
       </c>
       <c r="H82" t="n">
         <v>0.15</v>
@@ -5900,30 +5899,30 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="n">
-        <v>1</v>
-      </c>
-      <c r="B83" t="n">
-        <v>2</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-37-33</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>2</v>
       </c>
       <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="n">
         <v>0.1</v>
       </c>
-      <c r="E83" t="n">
-        <v>2</v>
-      </c>
       <c r="F83" t="n">
-        <v>5</v>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G83" t="n">
+        <v>5</v>
       </c>
       <c r="H83" t="n">
         <v>0.15</v>
@@ -5966,30 +5965,30 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="n">
-        <v>1</v>
-      </c>
-      <c r="B84" t="n">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-37-33</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
         <v>3</v>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
       <c r="D84" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" t="n">
         <v>0.1</v>
       </c>
-      <c r="E84" t="n">
-        <v>2</v>
-      </c>
       <c r="F84" t="n">
-        <v>5</v>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G84" t="n">
+        <v>5</v>
       </c>
       <c r="H84" t="n">
         <v>0.15</v>
@@ -6032,30 +6031,30 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="n">
-        <v>1</v>
-      </c>
-      <c r="B85" t="n">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-37-33</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
         <v>4</v>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
       <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="n">
         <v>0.1</v>
       </c>
-      <c r="E85" t="n">
-        <v>2</v>
-      </c>
       <c r="F85" t="n">
-        <v>5</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G85" t="n">
+        <v>5</v>
       </c>
       <c r="H85" t="n">
         <v>0.15</v>
@@ -6098,30 +6097,30 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="n">
-        <v>2</v>
-      </c>
-      <c r="B86" t="n">
-        <v>1</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-37-33</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
       </c>
       <c r="D86" t="n">
+        <v>2</v>
+      </c>
+      <c r="E86" t="n">
         <v>0.9</v>
       </c>
-      <c r="E86" t="n">
-        <v>2</v>
-      </c>
       <c r="F86" t="n">
-        <v>5</v>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G86" t="n">
+        <v>5</v>
       </c>
       <c r="H86" t="n">
         <v>0.15</v>
@@ -6164,30 +6163,30 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="n">
-        <v>2</v>
-      </c>
-      <c r="B87" t="n">
-        <v>2</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-37-33</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>2</v>
       </c>
       <c r="D87" t="n">
+        <v>2</v>
+      </c>
+      <c r="E87" t="n">
         <v>0.9</v>
       </c>
-      <c r="E87" t="n">
-        <v>2</v>
-      </c>
       <c r="F87" t="n">
-        <v>5</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G87" t="n">
+        <v>5</v>
       </c>
       <c r="H87" t="n">
         <v>0.15</v>
@@ -6230,30 +6229,30 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="n">
-        <v>2</v>
-      </c>
-      <c r="B88" t="n">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-37-33</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
         <v>3</v>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
       <c r="D88" t="n">
+        <v>2</v>
+      </c>
+      <c r="E88" t="n">
         <v>0.9</v>
       </c>
-      <c r="E88" t="n">
-        <v>2</v>
-      </c>
       <c r="F88" t="n">
-        <v>5</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G88" t="n">
+        <v>5</v>
       </c>
       <c r="H88" t="n">
         <v>0.15</v>
@@ -6296,30 +6295,30 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="n">
-        <v>2</v>
-      </c>
-      <c r="B89" t="n">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-37-33</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
         <v>4</v>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
       <c r="D89" t="n">
+        <v>2</v>
+      </c>
+      <c r="E89" t="n">
         <v>0.9</v>
       </c>
-      <c r="E89" t="n">
-        <v>2</v>
-      </c>
       <c r="F89" t="n">
-        <v>5</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G89" t="n">
+        <v>5</v>
       </c>
       <c r="H89" t="n">
         <v>0.15</v>
@@ -6362,30 +6361,30 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="n">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-37-33</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" t="n">
         <v>3</v>
       </c>
-      <c r="B90" t="n">
-        <v>1</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
+      <c r="E90" t="n">
         <v>0.1</v>
       </c>
-      <c r="E90" t="n">
-        <v>2</v>
-      </c>
       <c r="F90" t="n">
-        <v>5</v>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G90" t="n">
+        <v>5</v>
       </c>
       <c r="H90" t="n">
         <v>0.5</v>
@@ -6428,30 +6427,30 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="n">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-37-33</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>2</v>
+      </c>
+      <c r="D91" t="n">
         <v>3</v>
       </c>
-      <c r="B91" t="n">
-        <v>2</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
+      <c r="E91" t="n">
         <v>0.1</v>
       </c>
-      <c r="E91" t="n">
-        <v>2</v>
-      </c>
       <c r="F91" t="n">
-        <v>5</v>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G91" t="n">
+        <v>5</v>
       </c>
       <c r="H91" t="n">
         <v>0.5</v>
@@ -6494,30 +6493,30 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="n">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-37-33</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
         <v>3</v>
       </c>
-      <c r="B92" t="n">
+      <c r="D92" t="n">
         <v>3</v>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
+      <c r="E92" t="n">
         <v>0.1</v>
       </c>
-      <c r="E92" t="n">
-        <v>2</v>
-      </c>
       <c r="F92" t="n">
-        <v>5</v>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G92" t="n">
+        <v>5</v>
       </c>
       <c r="H92" t="n">
         <v>0.5</v>
@@ -6560,30 +6559,30 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="n">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-37-33</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>4</v>
+      </c>
+      <c r="D93" t="n">
         <v>3</v>
       </c>
-      <c r="B93" t="n">
-        <v>4</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
+      <c r="E93" t="n">
         <v>0.1</v>
       </c>
-      <c r="E93" t="n">
-        <v>2</v>
-      </c>
       <c r="F93" t="n">
-        <v>5</v>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G93" t="n">
+        <v>5</v>
       </c>
       <c r="H93" t="n">
         <v>0.5</v>
@@ -6626,30 +6625,30 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="n">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-37-33</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" t="n">
         <v>4</v>
       </c>
-      <c r="B94" t="n">
-        <v>1</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
+      <c r="E94" t="n">
         <v>0.9</v>
       </c>
-      <c r="E94" t="n">
-        <v>2</v>
-      </c>
       <c r="F94" t="n">
-        <v>5</v>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G94" t="n">
+        <v>5</v>
       </c>
       <c r="H94" t="n">
         <v>0.5</v>
@@ -6692,30 +6691,30 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="n">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-37-33</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>2</v>
+      </c>
+      <c r="D95" t="n">
         <v>4</v>
       </c>
-      <c r="B95" t="n">
-        <v>2</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
+      <c r="E95" t="n">
         <v>0.9</v>
       </c>
-      <c r="E95" t="n">
-        <v>2</v>
-      </c>
       <c r="F95" t="n">
-        <v>5</v>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G95" t="n">
+        <v>5</v>
       </c>
       <c r="H95" t="n">
         <v>0.5</v>
@@ -6758,30 +6757,30 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="n">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-37-33</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>3</v>
+      </c>
+      <c r="D96" t="n">
         <v>4</v>
       </c>
-      <c r="B96" t="n">
-        <v>3</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
+      <c r="E96" t="n">
         <v>0.9</v>
       </c>
-      <c r="E96" t="n">
-        <v>2</v>
-      </c>
       <c r="F96" t="n">
-        <v>5</v>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G96" t="n">
+        <v>5</v>
       </c>
       <c r="H96" t="n">
         <v>0.5</v>
@@ -6824,30 +6823,30 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="n">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-37-33</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
         <v>4</v>
       </c>
-      <c r="B97" t="n">
+      <c r="D97" t="n">
         <v>4</v>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
+      <c r="E97" t="n">
         <v>0.9</v>
       </c>
-      <c r="E97" t="n">
-        <v>2</v>
-      </c>
       <c r="F97" t="n">
-        <v>5</v>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G97" t="n">
+        <v>5</v>
       </c>
       <c r="H97" t="n">
         <v>0.5</v>
@@ -6890,30 +6889,30 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="n">
-        <v>1</v>
-      </c>
-      <c r="B98" t="n">
-        <v>1</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-46-02</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>1</v>
       </c>
       <c r="D98" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" t="n">
         <v>0.1</v>
       </c>
-      <c r="E98" t="n">
-        <v>2</v>
-      </c>
       <c r="F98" t="n">
-        <v>5</v>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G98" t="n">
+        <v>5</v>
       </c>
       <c r="H98" t="n">
         <v>0.15</v>
@@ -6956,30 +6955,30 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="n">
-        <v>1</v>
-      </c>
-      <c r="B99" t="n">
-        <v>2</v>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-46-02</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>2</v>
       </c>
       <c r="D99" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" t="n">
         <v>0.1</v>
       </c>
-      <c r="E99" t="n">
-        <v>2</v>
-      </c>
       <c r="F99" t="n">
-        <v>5</v>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G99" t="n">
+        <v>5</v>
       </c>
       <c r="H99" t="n">
         <v>0.15</v>
@@ -7022,30 +7021,30 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="n">
-        <v>1</v>
-      </c>
-      <c r="B100" t="n">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-46-02</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
         <v>3</v>
       </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
       <c r="D100" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" t="n">
         <v>0.1</v>
       </c>
-      <c r="E100" t="n">
-        <v>2</v>
-      </c>
       <c r="F100" t="n">
-        <v>5</v>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G100" t="n">
+        <v>5</v>
       </c>
       <c r="H100" t="n">
         <v>0.15</v>
@@ -7088,30 +7087,30 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="n">
-        <v>1</v>
-      </c>
-      <c r="B101" t="n">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-46-02</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
         <v>4</v>
       </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
       <c r="D101" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" t="n">
         <v>0.1</v>
       </c>
-      <c r="E101" t="n">
-        <v>2</v>
-      </c>
       <c r="F101" t="n">
-        <v>5</v>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G101" t="n">
+        <v>5</v>
       </c>
       <c r="H101" t="n">
         <v>0.15</v>
@@ -7154,30 +7153,30 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="n">
-        <v>2</v>
-      </c>
-      <c r="B102" t="n">
-        <v>1</v>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-46-02</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>1</v>
       </c>
       <c r="D102" t="n">
+        <v>2</v>
+      </c>
+      <c r="E102" t="n">
         <v>0.9</v>
       </c>
-      <c r="E102" t="n">
-        <v>2</v>
-      </c>
       <c r="F102" t="n">
-        <v>5</v>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G102" t="n">
+        <v>5</v>
       </c>
       <c r="H102" t="n">
         <v>0.15</v>
@@ -7220,30 +7219,30 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="n">
-        <v>2</v>
-      </c>
-      <c r="B103" t="n">
-        <v>2</v>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-46-02</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>2</v>
       </c>
       <c r="D103" t="n">
+        <v>2</v>
+      </c>
+      <c r="E103" t="n">
         <v>0.9</v>
       </c>
-      <c r="E103" t="n">
-        <v>2</v>
-      </c>
       <c r="F103" t="n">
-        <v>5</v>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G103" t="n">
+        <v>5</v>
       </c>
       <c r="H103" t="n">
         <v>0.15</v>
@@ -7286,30 +7285,30 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="n">
-        <v>2</v>
-      </c>
-      <c r="B104" t="n">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-46-02</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
         <v>3</v>
       </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
       <c r="D104" t="n">
+        <v>2</v>
+      </c>
+      <c r="E104" t="n">
         <v>0.9</v>
       </c>
-      <c r="E104" t="n">
-        <v>2</v>
-      </c>
       <c r="F104" t="n">
-        <v>5</v>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G104" t="n">
+        <v>5</v>
       </c>
       <c r="H104" t="n">
         <v>0.15</v>
@@ -7352,30 +7351,30 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="n">
-        <v>2</v>
-      </c>
-      <c r="B105" t="n">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-46-02</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
         <v>4</v>
       </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
       <c r="D105" t="n">
+        <v>2</v>
+      </c>
+      <c r="E105" t="n">
         <v>0.9</v>
       </c>
-      <c r="E105" t="n">
-        <v>2</v>
-      </c>
       <c r="F105" t="n">
-        <v>5</v>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G105" t="n">
+        <v>5</v>
       </c>
       <c r="H105" t="n">
         <v>0.15</v>
@@ -7418,30 +7417,30 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="n">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-46-02</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>1</v>
+      </c>
+      <c r="D106" t="n">
         <v>3</v>
       </c>
-      <c r="B106" t="n">
-        <v>1</v>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
+      <c r="E106" t="n">
         <v>0.1</v>
       </c>
-      <c r="E106" t="n">
-        <v>2</v>
-      </c>
       <c r="F106" t="n">
-        <v>5</v>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G106" t="n">
+        <v>5</v>
       </c>
       <c r="H106" t="n">
         <v>0.5</v>
@@ -7484,30 +7483,30 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="n">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-46-02</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>2</v>
+      </c>
+      <c r="D107" t="n">
         <v>3</v>
       </c>
-      <c r="B107" t="n">
-        <v>2</v>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
+      <c r="E107" t="n">
         <v>0.1</v>
       </c>
-      <c r="E107" t="n">
-        <v>2</v>
-      </c>
       <c r="F107" t="n">
-        <v>5</v>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G107" t="n">
+        <v>5</v>
       </c>
       <c r="H107" t="n">
         <v>0.5</v>
@@ -7550,30 +7549,30 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="n">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-46-02</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
         <v>3</v>
       </c>
-      <c r="B108" t="n">
+      <c r="D108" t="n">
         <v>3</v>
       </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
+      <c r="E108" t="n">
         <v>0.1</v>
       </c>
-      <c r="E108" t="n">
-        <v>2</v>
-      </c>
       <c r="F108" t="n">
-        <v>5</v>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G108" t="n">
+        <v>5</v>
       </c>
       <c r="H108" t="n">
         <v>0.5</v>
@@ -7616,30 +7615,30 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="n">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-46-02</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>4</v>
+      </c>
+      <c r="D109" t="n">
         <v>3</v>
       </c>
-      <c r="B109" t="n">
-        <v>4</v>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
+      <c r="E109" t="n">
         <v>0.1</v>
       </c>
-      <c r="E109" t="n">
-        <v>2</v>
-      </c>
       <c r="F109" t="n">
-        <v>5</v>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G109" t="n">
+        <v>5</v>
       </c>
       <c r="H109" t="n">
         <v>0.5</v>
@@ -7682,30 +7681,30 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="n">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-46-02</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>1</v>
+      </c>
+      <c r="D110" t="n">
         <v>4</v>
       </c>
-      <c r="B110" t="n">
-        <v>1</v>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
+      <c r="E110" t="n">
         <v>0.9</v>
       </c>
-      <c r="E110" t="n">
-        <v>2</v>
-      </c>
       <c r="F110" t="n">
-        <v>5</v>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G110" t="n">
+        <v>5</v>
       </c>
       <c r="H110" t="n">
         <v>0.5</v>
@@ -7748,30 +7747,30 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="n">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-46-02</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>2</v>
+      </c>
+      <c r="D111" t="n">
         <v>4</v>
       </c>
-      <c r="B111" t="n">
-        <v>2</v>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
+      <c r="E111" t="n">
         <v>0.9</v>
       </c>
-      <c r="E111" t="n">
-        <v>2</v>
-      </c>
       <c r="F111" t="n">
-        <v>5</v>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G111" t="n">
+        <v>5</v>
       </c>
       <c r="H111" t="n">
         <v>0.5</v>
@@ -7814,30 +7813,30 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="n">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-46-02</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>3</v>
+      </c>
+      <c r="D112" t="n">
         <v>4</v>
       </c>
-      <c r="B112" t="n">
-        <v>3</v>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
+      <c r="E112" t="n">
         <v>0.9</v>
       </c>
-      <c r="E112" t="n">
-        <v>2</v>
-      </c>
       <c r="F112" t="n">
-        <v>5</v>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G112" t="n">
+        <v>5</v>
       </c>
       <c r="H112" t="n">
         <v>0.5</v>
@@ -7880,30 +7879,30 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="n">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>run_2025-08-25_21-46-02</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
         <v>4</v>
       </c>
-      <c r="B113" t="n">
+      <c r="D113" t="n">
         <v>4</v>
       </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>[14, 15, 14, 18, 20]</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
+      <c r="E113" t="n">
         <v>0.9</v>
       </c>
-      <c r="E113" t="n">
-        <v>2</v>
-      </c>
       <c r="F113" t="n">
-        <v>5</v>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>[0, 31]</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G113" t="n">
+        <v>5</v>
       </c>
       <c r="H113" t="n">
         <v>0.5</v>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T113"/>
+  <dimension ref="A1:Y161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -442,12 +442,17 @@
     <col width="19" customWidth="1" min="12" max="12"/>
     <col width="36" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -523,30 +528,55 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>best_var_10</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>best_var_2</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>best_var_3</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>best_var_4</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>best_var_5</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>best_var_6</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>best_var_7</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>best_var_8</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>best_var_9</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>best_fitness</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>best_gen_idx</t>
         </is>
@@ -599,9 +629,7 @@
       <c r="N2" t="n">
         <v>2</v>
       </c>
-      <c r="O2" t="n">
-        <v>23</v>
-      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
         <v>23</v>
       </c>
@@ -609,12 +637,19 @@
         <v>23</v>
       </c>
       <c r="R2" t="n">
+        <v>23</v>
+      </c>
+      <c r="S2" t="n">
         <v>4</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="n">
         <v>52.65939263578403</v>
       </c>
-      <c r="T2" t="n">
+      <c r="Y2" t="n">
         <v>19</v>
       </c>
     </row>
@@ -665,22 +700,27 @@
       <c r="N3" t="n">
         <v>30</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
         <v>4</v>
-      </c>
-      <c r="P3" t="n">
-        <v>21</v>
       </c>
       <c r="Q3" t="n">
         <v>21</v>
       </c>
       <c r="R3" t="n">
+        <v>21</v>
+      </c>
+      <c r="S3" t="n">
         <v>4</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="n">
         <v>53.52026718403889</v>
       </c>
-      <c r="T3" t="n">
+      <c r="Y3" t="n">
         <v>19</v>
       </c>
     </row>
@@ -731,22 +771,27 @@
       <c r="N4" t="n">
         <v>7</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
         <v>21</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>14</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>7</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>14</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="n">
         <v>56.01915093644783</v>
       </c>
-      <c r="T4" t="n">
+      <c r="Y4" t="n">
         <v>19</v>
       </c>
     </row>
@@ -797,22 +842,27 @@
       <c r="N5" t="n">
         <v>26</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
         <v>27</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>28</v>
       </c>
-      <c r="Q5" t="n">
-        <v>2</v>
-      </c>
       <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
         <v>28</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="n">
         <v>75.61894639025262</v>
       </c>
-      <c r="T5" t="n">
+      <c r="Y5" t="n">
         <v>19</v>
       </c>
     </row>
@@ -863,22 +913,27 @@
       <c r="N6" t="n">
         <v>31</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
         <v>22</v>
-      </c>
-      <c r="P6" t="n">
-        <v>7</v>
       </c>
       <c r="Q6" t="n">
         <v>7</v>
       </c>
       <c r="R6" t="n">
+        <v>7</v>
+      </c>
+      <c r="S6" t="n">
         <v>27</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="n">
         <v>83.77718093279817</v>
       </c>
-      <c r="T6" t="n">
+      <c r="Y6" t="n">
         <v>19</v>
       </c>
     </row>
@@ -929,22 +984,27 @@
       <c r="N7" t="n">
         <v>23</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
         <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>26</v>
       </c>
       <c r="Q7" t="n">
         <v>26</v>
       </c>
       <c r="R7" t="n">
+        <v>26</v>
+      </c>
+      <c r="S7" t="n">
         <v>11</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="n">
         <v>77.41449183383052</v>
       </c>
-      <c r="T7" t="n">
+      <c r="Y7" t="n">
         <v>19</v>
       </c>
     </row>
@@ -995,22 +1055,27 @@
       <c r="N8" t="n">
         <v>1</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
         <v>7</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>26</v>
       </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
       <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
         <v>3</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="n">
         <v>55.60779560783896</v>
       </c>
-      <c r="T8" t="n">
+      <c r="Y8" t="n">
         <v>19</v>
       </c>
     </row>
@@ -1061,22 +1126,27 @@
       <c r="N9" t="n">
         <v>0</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
         <v>16</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
+        <v>19</v>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="n">
         <v>63.41917481067142</v>
       </c>
-      <c r="T9" t="n">
+      <c r="Y9" t="n">
         <v>19</v>
       </c>
     </row>
@@ -1127,22 +1197,27 @@
       <c r="N10" t="n">
         <v>28</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
         <v>9</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>28</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>22</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>28</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="n">
         <v>59.5265405971816</v>
       </c>
-      <c r="T10" t="n">
+      <c r="Y10" t="n">
         <v>19</v>
       </c>
     </row>
@@ -1193,22 +1268,27 @@
       <c r="N11" t="n">
         <v>11</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
         <v>11</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>21</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>13</v>
       </c>
       <c r="R11" t="n">
         <v>13</v>
       </c>
       <c r="S11" t="n">
+        <v>13</v>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="n">
         <v>73.8835302526813</v>
       </c>
-      <c r="T11" t="n">
+      <c r="Y11" t="n">
         <v>19</v>
       </c>
     </row>
@@ -1259,22 +1339,27 @@
       <c r="N12" t="n">
         <v>25</v>
       </c>
-      <c r="O12" t="n">
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="n">
         <v>24</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>29</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>12</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>25</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="n">
         <v>76.77969010708676</v>
       </c>
-      <c r="T12" t="n">
+      <c r="Y12" t="n">
         <v>19</v>
       </c>
     </row>
@@ -1325,22 +1410,27 @@
       <c r="N13" t="n">
         <v>30</v>
       </c>
-      <c r="O13" t="n">
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
         <v>11</v>
-      </c>
-      <c r="P13" t="n">
-        <v>21</v>
       </c>
       <c r="Q13" t="n">
         <v>21</v>
       </c>
       <c r="R13" t="n">
+        <v>21</v>
+      </c>
+      <c r="S13" t="n">
         <v>23</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="n">
         <v>54.10075649054495</v>
       </c>
-      <c r="T13" t="n">
+      <c r="Y13" t="n">
         <v>19</v>
       </c>
     </row>
@@ -1391,22 +1481,27 @@
       <c r="N14" t="n">
         <v>28</v>
       </c>
-      <c r="O14" t="n">
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
         <v>16</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>16</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>18</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="n">
         <v>73.22000577248077</v>
       </c>
-      <c r="T14" t="n">
+      <c r="Y14" t="n">
         <v>19</v>
       </c>
     </row>
@@ -1457,22 +1552,27 @@
       <c r="N15" t="n">
         <v>21</v>
       </c>
-      <c r="O15" t="n">
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
         <v>14</v>
-      </c>
-      <c r="P15" t="n">
-        <v>31</v>
       </c>
       <c r="Q15" t="n">
         <v>31</v>
       </c>
       <c r="R15" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="n">
         <v>78.0799653624337</v>
       </c>
-      <c r="T15" t="n">
+      <c r="Y15" t="n">
         <v>19</v>
       </c>
     </row>
@@ -1523,22 +1623,27 @@
       <c r="N16" t="n">
         <v>10</v>
       </c>
-      <c r="O16" t="n">
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
         <v>23</v>
-      </c>
-      <c r="P16" t="n">
-        <v>22</v>
       </c>
       <c r="Q16" t="n">
         <v>22</v>
       </c>
       <c r="R16" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="S16" t="n">
+        <v>19</v>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="n">
         <v>64.24234091520283</v>
       </c>
-      <c r="T16" t="n">
+      <c r="Y16" t="n">
         <v>19</v>
       </c>
     </row>
@@ -1589,22 +1694,27 @@
       <c r="N17" t="n">
         <v>28</v>
       </c>
-      <c r="O17" t="n">
-        <v>5</v>
-      </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q17" t="n">
         <v>28</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>17</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>28</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="n">
         <v>59.56139458129294</v>
       </c>
-      <c r="T17" t="n">
+      <c r="Y17" t="n">
         <v>19</v>
       </c>
     </row>
@@ -1655,22 +1765,27 @@
       <c r="N18" t="n">
         <v>20</v>
       </c>
-      <c r="O18" t="n">
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="n">
         <v>12</v>
       </c>
-      <c r="P18" t="n">
-        <v>2</v>
-      </c>
       <c r="Q18" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
+        <v>20</v>
+      </c>
+      <c r="S18" t="n">
         <v>4</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="n">
         <v>57.76426193419481</v>
       </c>
-      <c r="T18" t="n">
+      <c r="Y18" t="n">
         <v>19</v>
       </c>
     </row>
@@ -1721,22 +1836,27 @@
       <c r="N19" t="n">
         <v>25</v>
       </c>
-      <c r="O19" t="n">
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="n">
         <v>29</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>10</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>25</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>27</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="n">
         <v>65.94987664976328</v>
       </c>
-      <c r="T19" t="n">
+      <c r="Y19" t="n">
         <v>19</v>
       </c>
     </row>
@@ -1787,22 +1907,27 @@
       <c r="N20" t="n">
         <v>9</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="n">
         <v>18</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>27</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>9</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>10</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="n">
         <v>68.22518568836949</v>
       </c>
-      <c r="T20" t="n">
+      <c r="Y20" t="n">
         <v>19</v>
       </c>
     </row>
@@ -1853,22 +1978,27 @@
       <c r="N21" t="n">
         <v>31</v>
       </c>
-      <c r="O21" t="n">
-        <v>20</v>
-      </c>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q21" t="n">
         <v>14</v>
       </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
       <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
         <v>3</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="n">
         <v>85.34295803277705</v>
       </c>
-      <c r="T21" t="n">
+      <c r="Y21" t="n">
         <v>19</v>
       </c>
     </row>
@@ -1919,22 +2049,27 @@
       <c r="N22" t="n">
         <v>31</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="n">
         <v>4</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>8</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>4</v>
       </c>
       <c r="R22" t="n">
         <v>4</v>
       </c>
       <c r="S22" t="n">
+        <v>4</v>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="n">
         <v>68.33617160072384</v>
       </c>
-      <c r="T22" t="n">
+      <c r="Y22" t="n">
         <v>19</v>
       </c>
     </row>
@@ -1985,22 +2120,27 @@
       <c r="N23" t="n">
         <v>26</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="n">
         <v>9</v>
-      </c>
-      <c r="P23" t="n">
-        <v>26</v>
       </c>
       <c r="Q23" t="n">
         <v>26</v>
       </c>
       <c r="R23" t="n">
+        <v>26</v>
+      </c>
+      <c r="S23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="n">
         <v>68.90817668935779</v>
       </c>
-      <c r="T23" t="n">
+      <c r="Y23" t="n">
         <v>19</v>
       </c>
     </row>
@@ -2051,22 +2191,27 @@
       <c r="N24" t="n">
         <v>1</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
         <v>15</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>24</v>
       </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
       <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
         <v>24</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="n">
         <v>58.02911687610892</v>
       </c>
-      <c r="T24" t="n">
+      <c r="Y24" t="n">
         <v>19</v>
       </c>
     </row>
@@ -2117,22 +2262,27 @@
       <c r="N25" t="n">
         <v>31</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="n">
         <v>31</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>14</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>31</v>
       </c>
-      <c r="R25" t="n">
+      <c r="S25" t="n">
         <v>21</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="n">
         <v>64.77071344983304</v>
       </c>
-      <c r="T25" t="n">
+      <c r="Y25" t="n">
         <v>19</v>
       </c>
     </row>
@@ -2183,22 +2333,27 @@
       <c r="N26" t="n">
         <v>2</v>
       </c>
-      <c r="O26" t="n">
-        <v>25</v>
-      </c>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
         <v>25</v>
       </c>
       <c r="Q26" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="R26" t="n">
+        <v>2</v>
+      </c>
+      <c r="S26" t="n">
         <v>25</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="n">
         <v>55.74821109260589</v>
       </c>
-      <c r="T26" t="n">
+      <c r="Y26" t="n">
         <v>19</v>
       </c>
     </row>
@@ -2249,22 +2404,27 @@
       <c r="N27" t="n">
         <v>29</v>
       </c>
-      <c r="O27" t="n">
-        <v>29</v>
-      </c>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
         <v>29</v>
       </c>
       <c r="Q27" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="R27" t="n">
+        <v>20</v>
+      </c>
+      <c r="S27" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="n">
         <v>71.53151837560355</v>
       </c>
-      <c r="T27" t="n">
+      <c r="Y27" t="n">
         <v>19</v>
       </c>
     </row>
@@ -2315,22 +2475,27 @@
       <c r="N28" t="n">
         <v>17</v>
       </c>
-      <c r="O28" t="n">
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="n">
         <v>16</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>9</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>21</v>
       </c>
-      <c r="R28" t="n">
+      <c r="S28" t="n">
         <v>23</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="n">
         <v>72.26476864053073</v>
       </c>
-      <c r="T28" t="n">
+      <c r="Y28" t="n">
         <v>19</v>
       </c>
     </row>
@@ -2381,22 +2546,27 @@
       <c r="N29" t="n">
         <v>7</v>
       </c>
-      <c r="O29" t="n">
-        <v>16</v>
-      </c>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
         <v>16</v>
       </c>
       <c r="Q29" t="n">
+        <v>16</v>
+      </c>
+      <c r="R29" t="n">
         <v>21</v>
       </c>
-      <c r="R29" t="n">
+      <c r="S29" t="n">
         <v>7</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="n">
         <v>74.79074481341382</v>
       </c>
-      <c r="T29" t="n">
+      <c r="Y29" t="n">
         <v>19</v>
       </c>
     </row>
@@ -2447,22 +2617,27 @@
       <c r="N30" t="n">
         <v>11</v>
       </c>
-      <c r="O30" t="n">
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="n">
         <v>12</v>
-      </c>
-      <c r="P30" t="n">
-        <v>25</v>
       </c>
       <c r="Q30" t="n">
         <v>25</v>
       </c>
       <c r="R30" t="n">
+        <v>25</v>
+      </c>
+      <c r="S30" t="n">
         <v>12</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="n">
         <v>51.16019157575864</v>
       </c>
-      <c r="T30" t="n">
+      <c r="Y30" t="n">
         <v>19</v>
       </c>
     </row>
@@ -2513,22 +2688,27 @@
       <c r="N31" t="n">
         <v>15</v>
       </c>
-      <c r="O31" t="n">
-        <v>9</v>
-      </c>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
         <v>9</v>
       </c>
       <c r="Q31" t="n">
+        <v>9</v>
+      </c>
+      <c r="R31" t="n">
         <v>15</v>
       </c>
-      <c r="R31" t="n">
+      <c r="S31" t="n">
         <v>12</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="n">
         <v>66.04963484198028</v>
       </c>
-      <c r="T31" t="n">
+      <c r="Y31" t="n">
         <v>19</v>
       </c>
     </row>
@@ -2579,22 +2759,27 @@
       <c r="N32" t="n">
         <v>24</v>
       </c>
-      <c r="O32" t="n">
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="n">
         <v>30</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
         <v>29</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>24</v>
       </c>
       <c r="R32" t="n">
         <v>24</v>
       </c>
       <c r="S32" t="n">
+        <v>24</v>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="n">
         <v>50.33821673026171</v>
       </c>
-      <c r="T32" t="n">
+      <c r="Y32" t="n">
         <v>19</v>
       </c>
     </row>
@@ -2645,22 +2830,27 @@
       <c r="N33" t="n">
         <v>6</v>
       </c>
-      <c r="O33" t="n">
-        <v>5</v>
-      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q33" t="n">
         <v>6</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>22</v>
       </c>
-      <c r="R33" t="n">
+      <c r="S33" t="n">
         <v>6</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="n">
         <v>60.67700577368011</v>
       </c>
-      <c r="T33" t="n">
+      <c r="Y33" t="n">
         <v>19</v>
       </c>
     </row>
@@ -2711,22 +2901,27 @@
       <c r="N34" t="n">
         <v>7</v>
       </c>
-      <c r="O34" t="n">
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="n">
         <v>9</v>
       </c>
-      <c r="P34" t="n">
+      <c r="Q34" t="n">
         <v>11</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>22</v>
       </c>
-      <c r="R34" t="n">
+      <c r="S34" t="n">
         <v>9</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="n">
         <v>88.17561135909651</v>
       </c>
-      <c r="T34" t="n">
+      <c r="Y34" t="n">
         <v>19</v>
       </c>
     </row>
@@ -2777,22 +2972,27 @@
       <c r="N35" t="n">
         <v>0</v>
       </c>
-      <c r="O35" t="n">
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="n">
         <v>27</v>
       </c>
-      <c r="P35" t="n">
+      <c r="Q35" t="n">
         <v>31</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>0</v>
       </c>
-      <c r="R35" t="n">
+      <c r="S35" t="n">
         <v>17</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="n">
         <v>79.6514720238746</v>
       </c>
-      <c r="T35" t="n">
+      <c r="Y35" t="n">
         <v>19</v>
       </c>
     </row>
@@ -2843,22 +3043,27 @@
       <c r="N36" t="n">
         <v>13</v>
       </c>
-      <c r="O36" t="n">
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="n">
         <v>8</v>
       </c>
-      <c r="P36" t="n">
-        <v>1</v>
-      </c>
       <c r="Q36" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" t="n">
         <v>13</v>
       </c>
-      <c r="R36" t="n">
+      <c r="S36" t="n">
         <v>10</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="n">
         <v>68.72601367713909</v>
       </c>
-      <c r="T36" t="n">
+      <c r="Y36" t="n">
         <v>19</v>
       </c>
     </row>
@@ -2909,22 +3114,27 @@
       <c r="N37" t="n">
         <v>26</v>
       </c>
-      <c r="O37" t="n">
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="n">
         <v>23</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
         <v>10</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="n">
         <v>77.18885482373848</v>
       </c>
-      <c r="T37" t="n">
+      <c r="Y37" t="n">
         <v>19</v>
       </c>
     </row>
@@ -2975,22 +3185,27 @@
       <c r="N38" t="n">
         <v>8</v>
       </c>
-      <c r="O38" t="n">
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="n">
         <v>8</v>
       </c>
-      <c r="P38" t="n">
+      <c r="Q38" t="n">
         <v>28</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>8</v>
       </c>
-      <c r="R38" t="n">
+      <c r="S38" t="n">
         <v>23</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="n">
         <v>66.51582444758002</v>
       </c>
-      <c r="T38" t="n">
+      <c r="Y38" t="n">
         <v>19</v>
       </c>
     </row>
@@ -3041,22 +3256,27 @@
       <c r="N39" t="n">
         <v>13</v>
       </c>
-      <c r="O39" t="n">
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="n">
         <v>0</v>
       </c>
-      <c r="P39" t="n">
+      <c r="Q39" t="n">
         <v>11</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>22</v>
       </c>
-      <c r="R39" t="n">
+      <c r="S39" t="n">
         <v>0</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="n">
         <v>89.14018876236305</v>
       </c>
-      <c r="T39" t="n">
+      <c r="Y39" t="n">
         <v>19</v>
       </c>
     </row>
@@ -3107,22 +3327,27 @@
       <c r="N40" t="n">
         <v>5</v>
       </c>
-      <c r="O40" t="n">
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="n">
         <v>26</v>
       </c>
-      <c r="P40" t="n">
+      <c r="Q40" t="n">
         <v>16</v>
       </c>
-      <c r="Q40" t="n">
-        <v>5</v>
-      </c>
       <c r="R40" t="n">
+        <v>5</v>
+      </c>
+      <c r="S40" t="n">
         <v>7</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="n">
         <v>53.86693921757954</v>
       </c>
-      <c r="T40" t="n">
+      <c r="Y40" t="n">
         <v>19</v>
       </c>
     </row>
@@ -3173,22 +3398,27 @@
       <c r="N41" t="n">
         <v>8</v>
       </c>
-      <c r="O41" t="n">
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="n">
         <v>9</v>
-      </c>
-      <c r="P41" t="n">
-        <v>26</v>
       </c>
       <c r="Q41" t="n">
         <v>26</v>
       </c>
       <c r="R41" t="n">
+        <v>26</v>
+      </c>
+      <c r="S41" t="n">
         <v>10</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="n">
         <v>51.16019157575871</v>
       </c>
-      <c r="T41" t="n">
+      <c r="Y41" t="n">
         <v>19</v>
       </c>
     </row>
@@ -3239,22 +3469,27 @@
       <c r="N42" t="n">
         <v>16</v>
       </c>
-      <c r="O42" t="n">
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="n">
         <v>17</v>
-      </c>
-      <c r="P42" t="n">
-        <v>25</v>
       </c>
       <c r="Q42" t="n">
         <v>25</v>
       </c>
       <c r="R42" t="n">
+        <v>25</v>
+      </c>
+      <c r="S42" t="n">
         <v>27</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="n">
         <v>53.29233772833648</v>
       </c>
-      <c r="T42" t="n">
+      <c r="Y42" t="n">
         <v>19</v>
       </c>
     </row>
@@ -3305,22 +3540,27 @@
       <c r="N43" t="n">
         <v>28</v>
       </c>
-      <c r="O43" t="n">
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="n">
         <v>13</v>
       </c>
-      <c r="P43" t="n">
+      <c r="Q43" t="n">
         <v>22</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>28</v>
       </c>
       <c r="R43" t="n">
         <v>28</v>
       </c>
       <c r="S43" t="n">
+        <v>28</v>
+      </c>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="n">
         <v>53.8483132662859</v>
       </c>
-      <c r="T43" t="n">
+      <c r="Y43" t="n">
         <v>19</v>
       </c>
     </row>
@@ -3371,22 +3611,27 @@
       <c r="N44" t="n">
         <v>20</v>
       </c>
-      <c r="O44" t="n">
-        <v>1</v>
-      </c>
+      <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q44" t="n">
         <v>6</v>
       </c>
-      <c r="Q44" t="n">
-        <v>20</v>
-      </c>
       <c r="R44" t="n">
+        <v>20</v>
+      </c>
+      <c r="S44" t="n">
         <v>22</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="n">
         <v>53.79933842371339</v>
       </c>
-      <c r="T44" t="n">
+      <c r="Y44" t="n">
         <v>19</v>
       </c>
     </row>
@@ -3437,22 +3682,27 @@
       <c r="N45" t="n">
         <v>11</v>
       </c>
-      <c r="O45" t="n">
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="n">
         <v>23</v>
-      </c>
-      <c r="P45" t="n">
-        <v>29</v>
       </c>
       <c r="Q45" t="n">
         <v>29</v>
       </c>
       <c r="R45" t="n">
+        <v>29</v>
+      </c>
+      <c r="S45" t="n">
         <v>31</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="n">
         <v>54.64636706128023</v>
       </c>
-      <c r="T45" t="n">
+      <c r="Y45" t="n">
         <v>19</v>
       </c>
     </row>
@@ -3503,22 +3753,27 @@
       <c r="N46" t="n">
         <v>25</v>
       </c>
-      <c r="O46" t="n">
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="n">
         <v>21</v>
       </c>
-      <c r="P46" t="n">
+      <c r="Q46" t="n">
         <v>25</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="R46" t="n">
         <v>21</v>
       </c>
-      <c r="R46" t="n">
+      <c r="S46" t="n">
         <v>27</v>
       </c>
-      <c r="S46" t="n">
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="n">
         <v>52.73847979621706</v>
       </c>
-      <c r="T46" t="n">
+      <c r="Y46" t="n">
         <v>19</v>
       </c>
     </row>
@@ -3569,22 +3824,27 @@
       <c r="N47" t="n">
         <v>10</v>
       </c>
-      <c r="O47" t="n">
-        <v>19</v>
-      </c>
+      <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="Q47" t="n">
         <v>4</v>
       </c>
       <c r="R47" t="n">
+        <v>4</v>
+      </c>
+      <c r="S47" t="n">
         <v>10</v>
       </c>
-      <c r="S47" t="n">
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="n">
         <v>53.02376539543634</v>
       </c>
-      <c r="T47" t="n">
+      <c r="Y47" t="n">
         <v>19</v>
       </c>
     </row>
@@ -3635,22 +3895,27 @@
       <c r="N48" t="n">
         <v>3</v>
       </c>
-      <c r="O48" t="n">
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="n">
         <v>4</v>
-      </c>
-      <c r="P48" t="n">
-        <v>31</v>
       </c>
       <c r="Q48" t="n">
         <v>31</v>
       </c>
       <c r="R48" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="n">
         <v>51.16019157575871</v>
       </c>
-      <c r="T48" t="n">
+      <c r="Y48" t="n">
         <v>19</v>
       </c>
     </row>
@@ -3701,22 +3966,27 @@
       <c r="N49" t="n">
         <v>12</v>
       </c>
-      <c r="O49" t="n">
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="n">
         <v>18</v>
       </c>
-      <c r="P49" t="n">
+      <c r="Q49" t="n">
         <v>12</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="R49" t="n">
         <v>8</v>
       </c>
-      <c r="R49" t="n">
+      <c r="S49" t="n">
         <v>14</v>
       </c>
-      <c r="S49" t="n">
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="n">
         <v>60.58598324531882</v>
       </c>
-      <c r="T49" t="n">
+      <c r="Y49" t="n">
         <v>19</v>
       </c>
     </row>
@@ -3767,22 +4037,27 @@
       <c r="N50" t="n">
         <v>26</v>
       </c>
-      <c r="O50" t="n">
-        <v>20</v>
-      </c>
+      <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="Q50" t="n">
         <v>13</v>
       </c>
       <c r="R50" t="n">
+        <v>13</v>
+      </c>
+      <c r="S50" t="n">
         <v>28</v>
       </c>
-      <c r="S50" t="n">
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="n">
         <v>52.9233610890987</v>
       </c>
-      <c r="T50" t="n">
+      <c r="Y50" t="n">
         <v>19</v>
       </c>
     </row>
@@ -3833,22 +4108,27 @@
       <c r="N51" t="n">
         <v>3</v>
       </c>
-      <c r="O51" t="n">
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="n">
         <v>9</v>
       </c>
-      <c r="P51" t="n">
-        <v>19</v>
-      </c>
       <c r="Q51" t="n">
+        <v>19</v>
+      </c>
+      <c r="R51" t="n">
         <v>8</v>
       </c>
-      <c r="R51" t="n">
-        <v>5</v>
-      </c>
       <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="n">
         <v>66.27654856647256</v>
       </c>
-      <c r="T51" t="n">
+      <c r="Y51" t="n">
         <v>19</v>
       </c>
     </row>
@@ -3899,22 +4179,27 @@
       <c r="N52" t="n">
         <v>15</v>
       </c>
-      <c r="O52" t="n">
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="n">
         <v>4</v>
       </c>
-      <c r="P52" t="n">
+      <c r="Q52" t="n">
         <v>27</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>0</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
       <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="n">
         <v>77.07990333732718</v>
       </c>
-      <c r="T52" t="n">
+      <c r="Y52" t="n">
         <v>19</v>
       </c>
     </row>
@@ -3965,22 +4250,27 @@
       <c r="N53" t="n">
         <v>18</v>
       </c>
-      <c r="O53" t="n">
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="n">
         <v>31</v>
       </c>
-      <c r="P53" t="n">
+      <c r="Q53" t="n">
         <v>10</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="R53" t="n">
         <v>18</v>
       </c>
-      <c r="R53" t="n">
-        <v>2</v>
-      </c>
       <c r="S53" t="n">
+        <v>2</v>
+      </c>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="n">
         <v>73.37944954545732</v>
       </c>
-      <c r="T53" t="n">
+      <c r="Y53" t="n">
         <v>19</v>
       </c>
     </row>
@@ -4031,22 +4321,27 @@
       <c r="N54" t="n">
         <v>2</v>
       </c>
-      <c r="O54" t="n">
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="n">
         <v>28</v>
       </c>
-      <c r="P54" t="n">
-        <v>2</v>
-      </c>
       <c r="Q54" t="n">
+        <v>2</v>
+      </c>
+      <c r="R54" t="n">
         <v>11</v>
       </c>
-      <c r="R54" t="n">
+      <c r="S54" t="n">
         <v>23</v>
       </c>
-      <c r="S54" t="n">
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="n">
         <v>72.4935209216757</v>
       </c>
-      <c r="T54" t="n">
+      <c r="Y54" t="n">
         <v>19</v>
       </c>
     </row>
@@ -4097,12 +4392,10 @@
       <c r="N55" t="n">
         <v>11</v>
       </c>
-      <c r="O55" t="n">
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="n">
         <v>13</v>
       </c>
-      <c r="P55" t="n">
-        <v>19</v>
-      </c>
       <c r="Q55" t="n">
         <v>19</v>
       </c>
@@ -4110,9 +4403,16 @@
         <v>19</v>
       </c>
       <c r="S55" t="n">
+        <v>19</v>
+      </c>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="n">
         <v>66.1356104746563</v>
       </c>
-      <c r="T55" t="n">
+      <c r="Y55" t="n">
         <v>19</v>
       </c>
     </row>
@@ -4163,22 +4463,27 @@
       <c r="N56" t="n">
         <v>24</v>
       </c>
-      <c r="O56" t="n">
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="n">
         <v>0</v>
       </c>
-      <c r="P56" t="n">
-        <v>1</v>
-      </c>
       <c r="Q56" t="n">
+        <v>1</v>
+      </c>
+      <c r="R56" t="n">
         <v>11</v>
       </c>
-      <c r="R56" t="n">
-        <v>1</v>
-      </c>
       <c r="S56" t="n">
+        <v>1</v>
+      </c>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="n">
         <v>76.95856634709544</v>
       </c>
-      <c r="T56" t="n">
+      <c r="Y56" t="n">
         <v>19</v>
       </c>
     </row>
@@ -4229,22 +4534,27 @@
       <c r="N57" t="n">
         <v>14</v>
       </c>
-      <c r="O57" t="n">
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="n">
         <v>9</v>
-      </c>
-      <c r="P57" t="n">
-        <v>13</v>
       </c>
       <c r="Q57" t="n">
         <v>13</v>
       </c>
       <c r="R57" t="n">
+        <v>13</v>
+      </c>
+      <c r="S57" t="n">
         <v>9</v>
       </c>
-      <c r="S57" t="n">
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="n">
         <v>50.8779198761377</v>
       </c>
-      <c r="T57" t="n">
+      <c r="Y57" t="n">
         <v>19</v>
       </c>
     </row>
@@ -4295,22 +4605,27 @@
       <c r="N58" t="n">
         <v>26</v>
       </c>
-      <c r="O58" t="n">
-        <v>20</v>
-      </c>
+      <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="Q58" t="n">
         <v>8</v>
       </c>
       <c r="R58" t="n">
+        <v>8</v>
+      </c>
+      <c r="S58" t="n">
         <v>21</v>
       </c>
-      <c r="S58" t="n">
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="n">
         <v>53.38790812898382</v>
       </c>
-      <c r="T58" t="n">
+      <c r="Y58" t="n">
         <v>19</v>
       </c>
     </row>
@@ -4361,22 +4676,27 @@
       <c r="N59" t="n">
         <v>7</v>
       </c>
-      <c r="O59" t="n">
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="n">
         <v>22</v>
-      </c>
-      <c r="P59" t="n">
-        <v>13</v>
       </c>
       <c r="Q59" t="n">
         <v>13</v>
       </c>
       <c r="R59" t="n">
+        <v>13</v>
+      </c>
+      <c r="S59" t="n">
         <v>22</v>
       </c>
-      <c r="S59" t="n">
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
+      <c r="X59" t="n">
         <v>53.48947151246131</v>
       </c>
-      <c r="T59" t="n">
+      <c r="Y59" t="n">
         <v>19</v>
       </c>
     </row>
@@ -4427,22 +4747,27 @@
       <c r="N60" t="n">
         <v>9</v>
       </c>
-      <c r="O60" t="n">
-        <v>19</v>
-      </c>
+      <c r="O60" t="inlineStr"/>
       <c r="P60" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="Q60" t="n">
         <v>2</v>
       </c>
       <c r="R60" t="n">
+        <v>2</v>
+      </c>
+      <c r="S60" t="n">
         <v>9</v>
       </c>
-      <c r="S60" t="n">
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="n">
         <v>53.21454842141702</v>
       </c>
-      <c r="T60" t="n">
+      <c r="Y60" t="n">
         <v>19</v>
       </c>
     </row>
@@ -4493,22 +4818,27 @@
       <c r="N61" t="n">
         <v>6</v>
       </c>
-      <c r="O61" t="n">
-        <v>1</v>
-      </c>
+      <c r="O61" t="inlineStr"/>
       <c r="P61" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="R61" t="n">
+        <v>1</v>
+      </c>
+      <c r="S61" t="n">
         <v>4</v>
       </c>
-      <c r="S61" t="n">
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="n">
         <v>79.52436055125598</v>
       </c>
-      <c r="T61" t="n">
+      <c r="Y61" t="n">
         <v>19</v>
       </c>
     </row>
@@ -4559,22 +4889,27 @@
       <c r="N62" t="n">
         <v>3</v>
       </c>
-      <c r="O62" t="n">
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="n">
         <v>25</v>
       </c>
-      <c r="P62" t="n">
+      <c r="Q62" t="n">
         <v>3</v>
       </c>
-      <c r="Q62" t="n">
+      <c r="R62" t="n">
         <v>23</v>
       </c>
-      <c r="R62" t="n">
+      <c r="S62" t="n">
         <v>25</v>
       </c>
-      <c r="S62" t="n">
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="n">
         <v>60.79297853325846</v>
       </c>
-      <c r="T62" t="n">
+      <c r="Y62" t="n">
         <v>19</v>
       </c>
     </row>
@@ -4625,22 +4960,27 @@
       <c r="N63" t="n">
         <v>26</v>
       </c>
-      <c r="O63" t="n">
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="n">
         <v>27</v>
-      </c>
-      <c r="P63" t="n">
-        <v>10</v>
       </c>
       <c r="Q63" t="n">
         <v>10</v>
       </c>
       <c r="R63" t="n">
+        <v>10</v>
+      </c>
+      <c r="S63" t="n">
         <v>28</v>
       </c>
-      <c r="S63" t="n">
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
+      <c r="X63" t="n">
         <v>50.86900424344039</v>
       </c>
-      <c r="T63" t="n">
+      <c r="Y63" t="n">
         <v>19</v>
       </c>
     </row>
@@ -4691,22 +5031,27 @@
       <c r="N64" t="n">
         <v>24</v>
       </c>
-      <c r="O64" t="n">
-        <v>19</v>
-      </c>
+      <c r="O64" t="inlineStr"/>
       <c r="P64" t="n">
         <v>19</v>
       </c>
       <c r="Q64" t="n">
+        <v>19</v>
+      </c>
+      <c r="R64" t="n">
         <v>23</v>
       </c>
-      <c r="R64" t="n">
-        <v>19</v>
-      </c>
       <c r="S64" t="n">
+        <v>19</v>
+      </c>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
+      <c r="X64" t="n">
         <v>63.24843036576091</v>
       </c>
-      <c r="T64" t="n">
+      <c r="Y64" t="n">
         <v>19</v>
       </c>
     </row>
@@ -4757,22 +5102,27 @@
       <c r="N65" t="n">
         <v>9</v>
       </c>
-      <c r="O65" t="n">
-        <v>4</v>
-      </c>
+      <c r="O65" t="inlineStr"/>
       <c r="P65" t="n">
         <v>4</v>
       </c>
       <c r="Q65" t="n">
+        <v>4</v>
+      </c>
+      <c r="R65" t="n">
         <v>9</v>
       </c>
-      <c r="R65" t="n">
+      <c r="S65" t="n">
         <v>6</v>
       </c>
-      <c r="S65" t="n">
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="n">
         <v>50.78375975495094</v>
       </c>
-      <c r="T65" t="n">
+      <c r="Y65" t="n">
         <v>19</v>
       </c>
     </row>
@@ -4823,22 +5173,27 @@
       <c r="N66" t="n">
         <v>5</v>
       </c>
-      <c r="O66" t="n">
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="n">
         <v>12</v>
-      </c>
-      <c r="P66" t="n">
-        <v>23</v>
       </c>
       <c r="Q66" t="n">
         <v>23</v>
       </c>
       <c r="R66" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="S66" t="n">
+        <v>19</v>
+      </c>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="n">
         <v>65.12330450151217</v>
       </c>
-      <c r="T66" t="n">
+      <c r="Y66" t="n">
         <v>19</v>
       </c>
     </row>
@@ -4889,22 +5244,27 @@
       <c r="N67" t="n">
         <v>10</v>
       </c>
-      <c r="O67" t="n">
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="n">
         <v>16</v>
       </c>
-      <c r="P67" t="n">
+      <c r="Q67" t="n">
         <v>15</v>
       </c>
-      <c r="Q67" t="n">
+      <c r="R67" t="n">
         <v>24</v>
       </c>
-      <c r="R67" t="n">
+      <c r="S67" t="n">
         <v>10</v>
       </c>
-      <c r="S67" t="n">
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr"/>
+      <c r="X67" t="n">
         <v>74.81412151697111</v>
       </c>
-      <c r="T67" t="n">
+      <c r="Y67" t="n">
         <v>19</v>
       </c>
     </row>
@@ -4955,22 +5315,27 @@
       <c r="N68" t="n">
         <v>25</v>
       </c>
-      <c r="O68" t="n">
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="n">
         <v>17</v>
       </c>
-      <c r="P68" t="n">
+      <c r="Q68" t="n">
         <v>25</v>
       </c>
-      <c r="Q68" t="n">
+      <c r="R68" t="n">
         <v>6</v>
       </c>
-      <c r="R68" t="n">
+      <c r="S68" t="n">
         <v>27</v>
       </c>
-      <c r="S68" t="n">
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr"/>
+      <c r="X68" t="n">
         <v>60.77311803409181</v>
       </c>
-      <c r="T68" t="n">
+      <c r="Y68" t="n">
         <v>19</v>
       </c>
     </row>
@@ -5021,22 +5386,27 @@
       <c r="N69" t="n">
         <v>5</v>
       </c>
-      <c r="O69" t="n">
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="n">
         <v>25</v>
       </c>
-      <c r="P69" t="n">
+      <c r="Q69" t="n">
         <v>12</v>
       </c>
-      <c r="Q69" t="n">
+      <c r="R69" t="n">
         <v>3</v>
       </c>
-      <c r="R69" t="n">
-        <v>5</v>
-      </c>
       <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr"/>
+      <c r="X69" t="n">
         <v>78.31444134828412</v>
       </c>
-      <c r="T69" t="n">
+      <c r="Y69" t="n">
         <v>19</v>
       </c>
     </row>
@@ -5087,22 +5457,27 @@
       <c r="N70" t="n">
         <v>28</v>
       </c>
-      <c r="O70" t="n">
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="n">
         <v>17</v>
       </c>
-      <c r="P70" t="n">
+      <c r="Q70" t="n">
         <v>28</v>
       </c>
-      <c r="Q70" t="n">
-        <v>5</v>
-      </c>
       <c r="R70" t="n">
+        <v>5</v>
+      </c>
+      <c r="S70" t="n">
         <v>28</v>
       </c>
-      <c r="S70" t="n">
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr"/>
+      <c r="X70" t="n">
         <v>60.58598324531898</v>
       </c>
-      <c r="T70" t="n">
+      <c r="Y70" t="n">
         <v>19</v>
       </c>
     </row>
@@ -5153,22 +5528,27 @@
       <c r="N71" t="n">
         <v>17</v>
       </c>
-      <c r="O71" t="n">
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="n">
         <v>16</v>
       </c>
-      <c r="P71" t="n">
+      <c r="Q71" t="n">
         <v>31</v>
       </c>
-      <c r="Q71" t="n">
+      <c r="R71" t="n">
         <v>7</v>
       </c>
-      <c r="R71" t="n">
+      <c r="S71" t="n">
         <v>17</v>
       </c>
-      <c r="S71" t="n">
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr"/>
+      <c r="X71" t="n">
         <v>78.28561607979958</v>
       </c>
-      <c r="T71" t="n">
+      <c r="Y71" t="n">
         <v>19</v>
       </c>
     </row>
@@ -5219,22 +5599,27 @@
       <c r="N72" t="n">
         <v>15</v>
       </c>
-      <c r="O72" t="n">
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="n">
         <v>14</v>
       </c>
-      <c r="P72" t="n">
+      <c r="Q72" t="n">
         <v>24</v>
       </c>
-      <c r="Q72" t="n">
+      <c r="R72" t="n">
         <v>8</v>
       </c>
-      <c r="R72" t="n">
+      <c r="S72" t="n">
         <v>15</v>
       </c>
-      <c r="S72" t="n">
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr"/>
+      <c r="X72" t="n">
         <v>78.28561607979958</v>
       </c>
-      <c r="T72" t="n">
+      <c r="Y72" t="n">
         <v>19</v>
       </c>
     </row>
@@ -5285,22 +5670,27 @@
       <c r="N73" t="n">
         <v>8</v>
       </c>
-      <c r="O73" t="n">
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="n">
         <v>14</v>
       </c>
-      <c r="P73" t="n">
-        <v>5</v>
-      </c>
       <c r="Q73" t="n">
+        <v>5</v>
+      </c>
+      <c r="R73" t="n">
         <v>9</v>
       </c>
-      <c r="R73" t="n">
-        <v>5</v>
-      </c>
       <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr"/>
+      <c r="X73" t="n">
         <v>78.22954009105359</v>
       </c>
-      <c r="T73" t="n">
+      <c r="Y73" t="n">
         <v>19</v>
       </c>
     </row>
@@ -5351,22 +5741,27 @@
       <c r="N74" t="n">
         <v>11</v>
       </c>
-      <c r="O74" t="n">
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="n">
         <v>6</v>
       </c>
-      <c r="P74" t="n">
+      <c r="Q74" t="n">
         <v>11</v>
       </c>
-      <c r="Q74" t="n">
+      <c r="R74" t="n">
         <v>24</v>
       </c>
-      <c r="R74" t="n">
+      <c r="S74" t="n">
         <v>7</v>
       </c>
-      <c r="S74" t="n">
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr"/>
+      <c r="X74" t="n">
         <v>63.00083027612067</v>
       </c>
-      <c r="T74" t="n">
+      <c r="Y74" t="n">
         <v>19</v>
       </c>
     </row>
@@ -5417,22 +5812,27 @@
       <c r="N75" t="n">
         <v>16</v>
       </c>
-      <c r="O75" t="n">
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="n">
         <v>11</v>
       </c>
-      <c r="P75" t="n">
+      <c r="Q75" t="n">
         <v>16</v>
       </c>
-      <c r="Q75" t="n">
+      <c r="R75" t="n">
         <v>0</v>
       </c>
-      <c r="R75" t="n">
+      <c r="S75" t="n">
         <v>16</v>
       </c>
-      <c r="S75" t="n">
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr"/>
+      <c r="X75" t="n">
         <v>60.62083722943027</v>
       </c>
-      <c r="T75" t="n">
+      <c r="Y75" t="n">
         <v>19</v>
       </c>
     </row>
@@ -5483,22 +5883,27 @@
       <c r="N76" t="n">
         <v>18</v>
       </c>
-      <c r="O76" t="n">
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="n">
         <v>10</v>
       </c>
-      <c r="P76" t="n">
+      <c r="Q76" t="n">
         <v>18</v>
       </c>
-      <c r="Q76" t="n">
-        <v>5</v>
-      </c>
       <c r="R76" t="n">
+        <v>5</v>
+      </c>
+      <c r="S76" t="n">
         <v>11</v>
       </c>
-      <c r="S76" t="n">
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr"/>
+      <c r="X76" t="n">
         <v>61.57750132615346</v>
       </c>
-      <c r="T76" t="n">
+      <c r="Y76" t="n">
         <v>19</v>
       </c>
     </row>
@@ -5549,22 +5954,27 @@
       <c r="N77" t="n">
         <v>22</v>
       </c>
-      <c r="O77" t="n">
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="n">
         <v>3</v>
-      </c>
-      <c r="P77" t="n">
-        <v>11</v>
       </c>
       <c r="Q77" t="n">
         <v>11</v>
       </c>
       <c r="R77" t="n">
+        <v>11</v>
+      </c>
+      <c r="S77" t="n">
         <v>24</v>
       </c>
-      <c r="S77" t="n">
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr"/>
+      <c r="X77" t="n">
         <v>52.95821507321001</v>
       </c>
-      <c r="T77" t="n">
+      <c r="Y77" t="n">
         <v>19</v>
       </c>
     </row>
@@ -5615,22 +6025,27 @@
       <c r="N78" t="n">
         <v>25</v>
       </c>
-      <c r="O78" t="n">
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="n">
         <v>18</v>
       </c>
-      <c r="P78" t="n">
+      <c r="Q78" t="n">
         <v>23</v>
       </c>
-      <c r="Q78" t="n">
-        <v>19</v>
-      </c>
       <c r="R78" t="n">
         <v>19</v>
       </c>
       <c r="S78" t="n">
+        <v>19</v>
+      </c>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr"/>
+      <c r="X78" t="n">
         <v>65.57504291775645</v>
       </c>
-      <c r="T78" t="n">
+      <c r="Y78" t="n">
         <v>19</v>
       </c>
     </row>
@@ -5681,22 +6096,27 @@
       <c r="N79" t="n">
         <v>4</v>
       </c>
-      <c r="O79" t="n">
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="n">
         <v>22</v>
-      </c>
-      <c r="P79" t="n">
-        <v>27</v>
       </c>
       <c r="Q79" t="n">
         <v>27</v>
       </c>
       <c r="R79" t="n">
+        <v>27</v>
+      </c>
+      <c r="S79" t="n">
         <v>4</v>
       </c>
-      <c r="S79" t="n">
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr"/>
+      <c r="X79" t="n">
         <v>53.214548421417</v>
       </c>
-      <c r="T79" t="n">
+      <c r="Y79" t="n">
         <v>19</v>
       </c>
     </row>
@@ -5747,22 +6167,27 @@
       <c r="N80" t="n">
         <v>14</v>
       </c>
-      <c r="O80" t="n">
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="n">
         <v>14</v>
       </c>
-      <c r="P80" t="n">
-        <v>20</v>
-      </c>
       <c r="Q80" t="n">
+        <v>20</v>
+      </c>
+      <c r="R80" t="n">
         <v>14</v>
       </c>
-      <c r="R80" t="n">
-        <v>19</v>
-      </c>
       <c r="S80" t="n">
+        <v>19</v>
+      </c>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="n">
         <v>54.36714272975471</v>
       </c>
-      <c r="T80" t="n">
+      <c r="Y80" t="n">
         <v>19</v>
       </c>
     </row>
@@ -5813,22 +6238,27 @@
       <c r="N81" t="n">
         <v>19</v>
       </c>
-      <c r="O81" t="n">
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="n">
         <v>12</v>
-      </c>
-      <c r="P81" t="n">
-        <v>11</v>
       </c>
       <c r="Q81" t="n">
         <v>11</v>
       </c>
       <c r="R81" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="S81" t="n">
+        <v>19</v>
+      </c>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="n">
         <v>52.66665556473693</v>
       </c>
-      <c r="T81" t="n">
+      <c r="Y81" t="n">
         <v>19</v>
       </c>
     </row>
@@ -5879,22 +6309,27 @@
       <c r="N82" t="n">
         <v>7</v>
       </c>
-      <c r="O82" t="n">
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="n">
         <v>30</v>
-      </c>
-      <c r="P82" t="n">
-        <v>21</v>
       </c>
       <c r="Q82" t="n">
         <v>21</v>
       </c>
       <c r="R82" t="n">
+        <v>21</v>
+      </c>
+      <c r="S82" t="n">
         <v>9</v>
       </c>
-      <c r="S82" t="n">
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr"/>
+      <c r="X82" t="n">
         <v>53.02492447257619</v>
       </c>
-      <c r="T82" t="n">
+      <c r="Y82" t="n">
         <v>19</v>
       </c>
     </row>
@@ -5945,22 +6380,27 @@
       <c r="N83" t="n">
         <v>17</v>
       </c>
-      <c r="O83" t="n">
-        <v>16</v>
-      </c>
+      <c r="O83" t="inlineStr"/>
       <c r="P83" t="n">
         <v>16</v>
       </c>
       <c r="Q83" t="n">
+        <v>16</v>
+      </c>
+      <c r="R83" t="n">
         <v>4</v>
       </c>
-      <c r="R83" t="n">
+      <c r="S83" t="n">
         <v>18</v>
       </c>
-      <c r="S83" t="n">
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="inlineStr"/>
+      <c r="X83" t="n">
         <v>87.78701154945981</v>
       </c>
-      <c r="T83" t="n">
+      <c r="Y83" t="n">
         <v>19</v>
       </c>
     </row>
@@ -6011,22 +6451,27 @@
       <c r="N84" t="n">
         <v>2</v>
       </c>
-      <c r="O84" t="n">
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="n">
         <v>3</v>
-      </c>
-      <c r="P84" t="n">
-        <v>21</v>
       </c>
       <c r="Q84" t="n">
         <v>21</v>
       </c>
       <c r="R84" t="n">
+        <v>21</v>
+      </c>
+      <c r="S84" t="n">
         <v>4</v>
       </c>
-      <c r="S84" t="n">
+      <c r="T84" t="inlineStr"/>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
+      <c r="W84" t="inlineStr"/>
+      <c r="X84" t="n">
         <v>50.86900424344039</v>
       </c>
-      <c r="T84" t="n">
+      <c r="Y84" t="n">
         <v>19</v>
       </c>
     </row>
@@ -6077,22 +6522,27 @@
       <c r="N85" t="n">
         <v>12</v>
       </c>
-      <c r="O85" t="n">
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="n">
         <v>12</v>
       </c>
-      <c r="P85" t="n">
+      <c r="Q85" t="n">
         <v>17</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>12</v>
       </c>
       <c r="R85" t="n">
         <v>12</v>
       </c>
       <c r="S85" t="n">
+        <v>12</v>
+      </c>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
+      <c r="W85" t="inlineStr"/>
+      <c r="X85" t="n">
         <v>51.20496899610172</v>
       </c>
-      <c r="T85" t="n">
+      <c r="Y85" t="n">
         <v>19</v>
       </c>
     </row>
@@ -6143,22 +6593,27 @@
       <c r="N86" t="n">
         <v>26</v>
       </c>
-      <c r="O86" t="n">
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="n">
         <v>22</v>
-      </c>
-      <c r="P86" t="n">
-        <v>7</v>
       </c>
       <c r="Q86" t="n">
         <v>7</v>
       </c>
       <c r="R86" t="n">
+        <v>7</v>
+      </c>
+      <c r="S86" t="n">
         <v>23</v>
       </c>
-      <c r="S86" t="n">
+      <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
+      <c r="W86" t="inlineStr"/>
+      <c r="X86" t="n">
         <v>65.38790812898377</v>
       </c>
-      <c r="T86" t="n">
+      <c r="Y86" t="n">
         <v>19</v>
       </c>
     </row>
@@ -6209,22 +6664,27 @@
       <c r="N87" t="n">
         <v>21</v>
       </c>
-      <c r="O87" t="n">
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="n">
         <v>22</v>
-      </c>
-      <c r="P87" t="n">
-        <v>10</v>
       </c>
       <c r="Q87" t="n">
         <v>10</v>
       </c>
       <c r="R87" t="n">
+        <v>10</v>
+      </c>
+      <c r="S87" t="n">
         <v>21</v>
       </c>
-      <c r="S87" t="n">
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
+      <c r="W87" t="inlineStr"/>
+      <c r="X87" t="n">
         <v>50.86900424344032</v>
       </c>
-      <c r="T87" t="n">
+      <c r="Y87" t="n">
         <v>19</v>
       </c>
     </row>
@@ -6275,22 +6735,27 @@
       <c r="N88" t="n">
         <v>26</v>
       </c>
-      <c r="O88" t="n">
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="n">
         <v>21</v>
-      </c>
-      <c r="P88" t="n">
-        <v>10</v>
       </c>
       <c r="Q88" t="n">
         <v>10</v>
       </c>
       <c r="R88" t="n">
+        <v>10</v>
+      </c>
+      <c r="S88" t="n">
         <v>12</v>
       </c>
-      <c r="S88" t="n">
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
+      <c r="W88" t="inlineStr"/>
+      <c r="X88" t="n">
         <v>54.2011607968826</v>
       </c>
-      <c r="T88" t="n">
+      <c r="Y88" t="n">
         <v>19</v>
       </c>
     </row>
@@ -6341,22 +6806,27 @@
       <c r="N89" t="n">
         <v>30</v>
       </c>
-      <c r="O89" t="n">
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="n">
         <v>22</v>
       </c>
-      <c r="P89" t="n">
+      <c r="Q89" t="n">
         <v>3</v>
       </c>
-      <c r="Q89" t="n">
+      <c r="R89" t="n">
         <v>17</v>
       </c>
-      <c r="R89" t="n">
+      <c r="S89" t="n">
         <v>23</v>
       </c>
-      <c r="S89" t="n">
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr"/>
+      <c r="W89" t="inlineStr"/>
+      <c r="X89" t="n">
         <v>76.78382094285232</v>
       </c>
-      <c r="T89" t="n">
+      <c r="Y89" t="n">
         <v>19</v>
       </c>
     </row>
@@ -6407,22 +6877,27 @@
       <c r="N90" t="n">
         <v>13</v>
       </c>
-      <c r="O90" t="n">
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="n">
         <v>7</v>
       </c>
-      <c r="P90" t="n">
+      <c r="Q90" t="n">
         <v>14</v>
       </c>
-      <c r="Q90" t="n">
+      <c r="R90" t="n">
         <v>13</v>
       </c>
-      <c r="R90" t="n">
+      <c r="S90" t="n">
         <v>14</v>
       </c>
-      <c r="S90" t="n">
+      <c r="T90" t="inlineStr"/>
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" t="inlineStr"/>
+      <c r="W90" t="inlineStr"/>
+      <c r="X90" t="n">
         <v>65.2941798258715</v>
       </c>
-      <c r="T90" t="n">
+      <c r="Y90" t="n">
         <v>19</v>
       </c>
     </row>
@@ -6473,22 +6948,27 @@
       <c r="N91" t="n">
         <v>24</v>
       </c>
-      <c r="O91" t="n">
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="n">
         <v>25</v>
       </c>
-      <c r="P91" t="n">
+      <c r="Q91" t="n">
         <v>24</v>
       </c>
-      <c r="Q91" t="n">
-        <v>2</v>
-      </c>
       <c r="R91" t="n">
         <v>2</v>
       </c>
       <c r="S91" t="n">
+        <v>2</v>
+      </c>
+      <c r="T91" t="inlineStr"/>
+      <c r="U91" t="inlineStr"/>
+      <c r="V91" t="inlineStr"/>
+      <c r="W91" t="inlineStr"/>
+      <c r="X91" t="n">
         <v>67.71460284066265</v>
       </c>
-      <c r="T91" t="n">
+      <c r="Y91" t="n">
         <v>19</v>
       </c>
     </row>
@@ -6539,22 +7019,27 @@
       <c r="N92" t="n">
         <v>12</v>
       </c>
-      <c r="O92" t="n">
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="n">
         <v>12</v>
-      </c>
-      <c r="P92" t="n">
-        <v>24</v>
       </c>
       <c r="Q92" t="n">
         <v>24</v>
       </c>
       <c r="R92" t="n">
+        <v>24</v>
+      </c>
+      <c r="S92" t="n">
         <v>14</v>
       </c>
-      <c r="S92" t="n">
+      <c r="T92" t="inlineStr"/>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr"/>
+      <c r="W92" t="inlineStr"/>
+      <c r="X92" t="n">
         <v>51.16019157575865</v>
       </c>
-      <c r="T92" t="n">
+      <c r="Y92" t="n">
         <v>19</v>
       </c>
     </row>
@@ -6605,22 +7090,27 @@
       <c r="N93" t="n">
         <v>25</v>
       </c>
-      <c r="O93" t="n">
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="n">
         <v>26</v>
-      </c>
-      <c r="P93" t="n">
-        <v>18</v>
       </c>
       <c r="Q93" t="n">
         <v>18</v>
       </c>
       <c r="R93" t="n">
+        <v>18</v>
+      </c>
+      <c r="S93" t="n">
         <v>26</v>
       </c>
-      <c r="S93" t="n">
+      <c r="T93" t="inlineStr"/>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr"/>
+      <c r="W93" t="inlineStr"/>
+      <c r="X93" t="n">
         <v>50.86900424344039</v>
       </c>
-      <c r="T93" t="n">
+      <c r="Y93" t="n">
         <v>19</v>
       </c>
     </row>
@@ -6671,22 +7161,27 @@
       <c r="N94" t="n">
         <v>24</v>
       </c>
-      <c r="O94" t="n">
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="n">
         <v>0</v>
-      </c>
-      <c r="P94" t="n">
-        <v>24</v>
       </c>
       <c r="Q94" t="n">
         <v>24</v>
       </c>
       <c r="R94" t="n">
+        <v>24</v>
+      </c>
+      <c r="S94" t="n">
         <v>26</v>
       </c>
-      <c r="S94" t="n">
+      <c r="T94" t="inlineStr"/>
+      <c r="U94" t="inlineStr"/>
+      <c r="V94" t="inlineStr"/>
+      <c r="W94" t="inlineStr"/>
+      <c r="X94" t="n">
         <v>37.35402933294379</v>
       </c>
-      <c r="T94" t="n">
+      <c r="Y94" t="n">
         <v>19</v>
       </c>
     </row>
@@ -6737,22 +7232,27 @@
       <c r="N95" t="n">
         <v>29</v>
       </c>
-      <c r="O95" t="n">
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="n">
         <v>14</v>
       </c>
-      <c r="P95" t="n">
+      <c r="Q95" t="n">
         <v>23</v>
       </c>
-      <c r="Q95" t="n">
+      <c r="R95" t="n">
         <v>29</v>
       </c>
-      <c r="R95" t="n">
+      <c r="S95" t="n">
         <v>14</v>
       </c>
-      <c r="S95" t="n">
+      <c r="T95" t="inlineStr"/>
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="inlineStr"/>
+      <c r="W95" t="inlineStr"/>
+      <c r="X95" t="n">
         <v>54.43999870293894</v>
       </c>
-      <c r="T95" t="n">
+      <c r="Y95" t="n">
         <v>19</v>
       </c>
     </row>
@@ -6803,22 +7303,27 @@
       <c r="N96" t="n">
         <v>29</v>
       </c>
-      <c r="O96" t="n">
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="n">
         <v>12</v>
       </c>
-      <c r="P96" t="n">
+      <c r="Q96" t="n">
         <v>9</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>11</v>
       </c>
       <c r="R96" t="n">
         <v>11</v>
       </c>
       <c r="S96" t="n">
+        <v>11</v>
+      </c>
+      <c r="T96" t="inlineStr"/>
+      <c r="U96" t="inlineStr"/>
+      <c r="V96" t="inlineStr"/>
+      <c r="W96" t="inlineStr"/>
+      <c r="X96" t="n">
         <v>68.21884607629063</v>
       </c>
-      <c r="T96" t="n">
+      <c r="Y96" t="n">
         <v>19</v>
       </c>
     </row>
@@ -6869,22 +7374,27 @@
       <c r="N97" t="n">
         <v>2</v>
       </c>
-      <c r="O97" t="n">
-        <v>20</v>
-      </c>
+      <c r="O97" t="inlineStr"/>
       <c r="P97" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="Q97" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="R97" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="S97" t="n">
+        <v>2</v>
+      </c>
+      <c r="T97" t="inlineStr"/>
+      <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr"/>
+      <c r="W97" t="inlineStr"/>
+      <c r="X97" t="n">
         <v>59.3373858168374</v>
       </c>
-      <c r="T97" t="n">
+      <c r="Y97" t="n">
         <v>19</v>
       </c>
     </row>
@@ -6935,22 +7445,27 @@
       <c r="N98" t="n">
         <v>22</v>
       </c>
-      <c r="O98" t="n">
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="n">
         <v>30</v>
-      </c>
-      <c r="P98" t="n">
-        <v>22</v>
       </c>
       <c r="Q98" t="n">
         <v>22</v>
       </c>
       <c r="R98" t="n">
+        <v>22</v>
+      </c>
+      <c r="S98" t="n">
         <v>13</v>
       </c>
-      <c r="S98" t="n">
+      <c r="T98" t="inlineStr"/>
+      <c r="U98" t="inlineStr"/>
+      <c r="V98" t="inlineStr"/>
+      <c r="W98" t="inlineStr"/>
+      <c r="X98" t="n">
         <v>50.3210096574379</v>
       </c>
-      <c r="T98" t="n">
+      <c r="Y98" t="n">
         <v>19</v>
       </c>
     </row>
@@ -7001,22 +7516,27 @@
       <c r="N99" t="n">
         <v>2</v>
       </c>
-      <c r="O99" t="n">
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="n">
         <v>12</v>
       </c>
-      <c r="P99" t="n">
+      <c r="Q99" t="n">
         <v>22</v>
       </c>
-      <c r="Q99" t="n">
-        <v>2</v>
-      </c>
       <c r="R99" t="n">
+        <v>2</v>
+      </c>
+      <c r="S99" t="n">
         <v>12</v>
       </c>
-      <c r="S99" t="n">
+      <c r="T99" t="inlineStr"/>
+      <c r="U99" t="inlineStr"/>
+      <c r="V99" t="inlineStr"/>
+      <c r="W99" t="inlineStr"/>
+      <c r="X99" t="n">
         <v>54.43999870293889</v>
       </c>
-      <c r="T99" t="n">
+      <c r="Y99" t="n">
         <v>19</v>
       </c>
     </row>
@@ -7067,22 +7587,27 @@
       <c r="N100" t="n">
         <v>22</v>
       </c>
-      <c r="O100" t="n">
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="n">
         <v>10</v>
       </c>
-      <c r="P100" t="n">
+      <c r="Q100" t="n">
         <v>15</v>
-      </c>
-      <c r="Q100" t="n">
-        <v>22</v>
       </c>
       <c r="R100" t="n">
         <v>22</v>
       </c>
       <c r="S100" t="n">
+        <v>22</v>
+      </c>
+      <c r="T100" t="inlineStr"/>
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr"/>
+      <c r="W100" t="inlineStr"/>
+      <c r="X100" t="n">
         <v>53.74700036815332</v>
       </c>
-      <c r="T100" t="n">
+      <c r="Y100" t="n">
         <v>19</v>
       </c>
     </row>
@@ -7133,22 +7658,27 @@
       <c r="N101" t="n">
         <v>23</v>
       </c>
-      <c r="O101" t="n">
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="n">
         <v>3</v>
       </c>
-      <c r="P101" t="n">
+      <c r="Q101" t="n">
         <v>8</v>
       </c>
-      <c r="Q101" t="n">
+      <c r="R101" t="n">
         <v>3</v>
       </c>
-      <c r="R101" t="n">
-        <v>5</v>
-      </c>
       <c r="S101" t="n">
+        <v>5</v>
+      </c>
+      <c r="T101" t="inlineStr"/>
+      <c r="U101" t="inlineStr"/>
+      <c r="V101" t="inlineStr"/>
+      <c r="W101" t="inlineStr"/>
+      <c r="X101" t="n">
         <v>68.30712905157661</v>
       </c>
-      <c r="T101" t="n">
+      <c r="Y101" t="n">
         <v>19</v>
       </c>
     </row>
@@ -7199,22 +7729,27 @@
       <c r="N102" t="n">
         <v>31</v>
       </c>
-      <c r="O102" t="n">
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="n">
         <v>25</v>
       </c>
-      <c r="P102" t="n">
+      <c r="Q102" t="n">
         <v>4</v>
       </c>
-      <c r="Q102" t="n">
+      <c r="R102" t="n">
         <v>14</v>
       </c>
-      <c r="R102" t="n">
+      <c r="S102" t="n">
         <v>6</v>
       </c>
-      <c r="S102" t="n">
+      <c r="T102" t="inlineStr"/>
+      <c r="U102" t="inlineStr"/>
+      <c r="V102" t="inlineStr"/>
+      <c r="W102" t="inlineStr"/>
+      <c r="X102" t="n">
         <v>80.05270792571612</v>
       </c>
-      <c r="T102" t="n">
+      <c r="Y102" t="n">
         <v>19</v>
       </c>
     </row>
@@ -7265,22 +7800,27 @@
       <c r="N103" t="n">
         <v>22</v>
       </c>
-      <c r="O103" t="n">
-        <v>1</v>
-      </c>
+      <c r="O103" t="inlineStr"/>
       <c r="P103" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Q103" t="n">
         <v>11</v>
       </c>
       <c r="R103" t="n">
+        <v>11</v>
+      </c>
+      <c r="S103" t="n">
         <v>22</v>
       </c>
-      <c r="S103" t="n">
+      <c r="T103" t="inlineStr"/>
+      <c r="U103" t="inlineStr"/>
+      <c r="V103" t="inlineStr"/>
+      <c r="W103" t="inlineStr"/>
+      <c r="X103" t="n">
         <v>52.95821507321003</v>
       </c>
-      <c r="T103" t="n">
+      <c r="Y103" t="n">
         <v>19</v>
       </c>
     </row>
@@ -7331,22 +7871,27 @@
       <c r="N104" t="n">
         <v>17</v>
       </c>
-      <c r="O104" t="n">
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="n">
         <v>26</v>
       </c>
-      <c r="P104" t="n">
+      <c r="Q104" t="n">
         <v>24</v>
       </c>
-      <c r="Q104" t="n">
+      <c r="R104" t="n">
         <v>25</v>
       </c>
-      <c r="R104" t="n">
+      <c r="S104" t="n">
         <v>24</v>
       </c>
-      <c r="S104" t="n">
+      <c r="T104" t="inlineStr"/>
+      <c r="U104" t="inlineStr"/>
+      <c r="V104" t="inlineStr"/>
+      <c r="W104" t="inlineStr"/>
+      <c r="X104" t="n">
         <v>80.75688621642344</v>
       </c>
-      <c r="T104" t="n">
+      <c r="Y104" t="n">
         <v>19</v>
       </c>
     </row>
@@ -7397,22 +7942,27 @@
       <c r="N105" t="n">
         <v>23</v>
       </c>
-      <c r="O105" t="n">
-        <v>1</v>
-      </c>
+      <c r="O105" t="inlineStr"/>
       <c r="P105" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q105" t="n">
         <v>6</v>
       </c>
-      <c r="Q105" t="n">
-        <v>1</v>
-      </c>
       <c r="R105" t="n">
+        <v>1</v>
+      </c>
+      <c r="S105" t="n">
         <v>3</v>
       </c>
-      <c r="S105" t="n">
+      <c r="T105" t="inlineStr"/>
+      <c r="U105" t="inlineStr"/>
+      <c r="V105" t="inlineStr"/>
+      <c r="W105" t="inlineStr"/>
+      <c r="X105" t="n">
         <v>68.36719176659345</v>
       </c>
-      <c r="T105" t="n">
+      <c r="Y105" t="n">
         <v>19</v>
       </c>
     </row>
@@ -7463,22 +8013,27 @@
       <c r="N106" t="n">
         <v>0</v>
       </c>
-      <c r="O106" t="n">
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="n">
         <v>13</v>
-      </c>
-      <c r="P106" t="n">
-        <v>0</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
+        <v>2</v>
+      </c>
+      <c r="T106" t="inlineStr"/>
+      <c r="U106" t="inlineStr"/>
+      <c r="V106" t="inlineStr"/>
+      <c r="W106" t="inlineStr"/>
+      <c r="X106" t="n">
         <v>37.35402933294379</v>
       </c>
-      <c r="T106" t="n">
+      <c r="Y106" t="n">
         <v>19</v>
       </c>
     </row>
@@ -7529,22 +8084,27 @@
       <c r="N107" t="n">
         <v>7</v>
       </c>
-      <c r="O107" t="n">
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="n">
         <v>28</v>
       </c>
-      <c r="P107" t="n">
+      <c r="Q107" t="n">
         <v>7</v>
       </c>
-      <c r="Q107" t="n">
+      <c r="R107" t="n">
         <v>8</v>
       </c>
-      <c r="R107" t="n">
+      <c r="S107" t="n">
         <v>10</v>
       </c>
-      <c r="S107" t="n">
+      <c r="T107" t="inlineStr"/>
+      <c r="U107" t="inlineStr"/>
+      <c r="V107" t="inlineStr"/>
+      <c r="W107" t="inlineStr"/>
+      <c r="X107" t="n">
         <v>68.25142359906067</v>
       </c>
-      <c r="T107" t="n">
+      <c r="Y107" t="n">
         <v>19</v>
       </c>
     </row>
@@ -7595,22 +8155,27 @@
       <c r="N108" t="n">
         <v>29</v>
       </c>
-      <c r="O108" t="n">
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="n">
         <v>30</v>
       </c>
-      <c r="P108" t="n">
+      <c r="Q108" t="n">
         <v>22</v>
       </c>
-      <c r="Q108" t="n">
+      <c r="R108" t="n">
         <v>3</v>
       </c>
-      <c r="R108" t="n">
+      <c r="S108" t="n">
         <v>31</v>
       </c>
-      <c r="S108" t="n">
+      <c r="T108" t="inlineStr"/>
+      <c r="U108" t="inlineStr"/>
+      <c r="V108" t="inlineStr"/>
+      <c r="W108" t="inlineStr"/>
+      <c r="X108" t="n">
         <v>74.07780777305416</v>
       </c>
-      <c r="T108" t="n">
+      <c r="Y108" t="n">
         <v>19</v>
       </c>
     </row>
@@ -7661,9 +8226,7 @@
       <c r="N109" t="n">
         <v>4</v>
       </c>
-      <c r="O109" t="n">
-        <v>26</v>
-      </c>
+      <c r="O109" t="inlineStr"/>
       <c r="P109" t="n">
         <v>26</v>
       </c>
@@ -7674,9 +8237,16 @@
         <v>26</v>
       </c>
       <c r="S109" t="n">
+        <v>26</v>
+      </c>
+      <c r="T109" t="inlineStr"/>
+      <c r="U109" t="inlineStr"/>
+      <c r="V109" t="inlineStr"/>
+      <c r="W109" t="inlineStr"/>
+      <c r="X109" t="n">
         <v>52.9094208814944</v>
       </c>
-      <c r="T109" t="n">
+      <c r="Y109" t="n">
         <v>19</v>
       </c>
     </row>
@@ -7727,22 +8297,27 @@
       <c r="N110" t="n">
         <v>7</v>
       </c>
-      <c r="O110" t="n">
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="n">
         <v>28</v>
       </c>
-      <c r="P110" t="n">
+      <c r="Q110" t="n">
         <v>7</v>
       </c>
-      <c r="Q110" t="n">
+      <c r="R110" t="n">
         <v>18</v>
       </c>
-      <c r="R110" t="n">
-        <v>20</v>
-      </c>
       <c r="S110" t="n">
+        <v>20</v>
+      </c>
+      <c r="T110" t="inlineStr"/>
+      <c r="U110" t="inlineStr"/>
+      <c r="V110" t="inlineStr"/>
+      <c r="W110" t="inlineStr"/>
+      <c r="X110" t="n">
         <v>66.23680007452545</v>
       </c>
-      <c r="T110" t="n">
+      <c r="Y110" t="n">
         <v>19</v>
       </c>
     </row>
@@ -7793,22 +8368,27 @@
       <c r="N111" t="n">
         <v>24</v>
       </c>
-      <c r="O111" t="n">
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="n">
         <v>15</v>
       </c>
-      <c r="P111" t="n">
+      <c r="Q111" t="n">
         <v>10</v>
       </c>
-      <c r="Q111" t="n">
+      <c r="R111" t="n">
         <v>24</v>
       </c>
-      <c r="R111" t="n">
+      <c r="S111" t="n">
         <v>16</v>
       </c>
-      <c r="S111" t="n">
+      <c r="T111" t="inlineStr"/>
+      <c r="U111" t="inlineStr"/>
+      <c r="V111" t="inlineStr"/>
+      <c r="W111" t="inlineStr"/>
+      <c r="X111" t="n">
         <v>54.49533691903626</v>
       </c>
-      <c r="T111" t="n">
+      <c r="Y111" t="n">
         <v>19</v>
       </c>
     </row>
@@ -7859,9 +8439,7 @@
       <c r="N112" t="n">
         <v>5</v>
       </c>
-      <c r="O112" t="n">
-        <v>23</v>
-      </c>
+      <c r="O112" t="inlineStr"/>
       <c r="P112" t="n">
         <v>23</v>
       </c>
@@ -7869,12 +8447,19 @@
         <v>23</v>
       </c>
       <c r="R112" t="n">
+        <v>23</v>
+      </c>
+      <c r="S112" t="n">
         <v>25</v>
       </c>
-      <c r="S112" t="n">
+      <c r="T112" t="inlineStr"/>
+      <c r="U112" t="inlineStr"/>
+      <c r="V112" t="inlineStr"/>
+      <c r="W112" t="inlineStr"/>
+      <c r="X112" t="n">
         <v>52.33167472531786</v>
       </c>
-      <c r="T112" t="n">
+      <c r="Y112" t="n">
         <v>19</v>
       </c>
     </row>
@@ -7925,22 +8510,3915 @@
       <c r="N113" t="n">
         <v>12</v>
       </c>
-      <c r="O113" t="n">
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="n">
         <v>12</v>
       </c>
-      <c r="P113" t="n">
+      <c r="Q113" t="n">
         <v>3</v>
       </c>
-      <c r="Q113" t="n">
+      <c r="R113" t="n">
         <v>12</v>
       </c>
-      <c r="R113" t="n">
+      <c r="S113" t="n">
         <v>14</v>
       </c>
-      <c r="S113" t="n">
+      <c r="T113" t="inlineStr"/>
+      <c r="U113" t="inlineStr"/>
+      <c r="V113" t="inlineStr"/>
+      <c r="W113" t="inlineStr"/>
+      <c r="X113" t="n">
         <v>52.03405360298243</v>
       </c>
-      <c r="T113" t="n">
+      <c r="Y113" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_13-23-12</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>1</v>
+      </c>
+      <c r="D114" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F114" t="n">
+        <v>2</v>
+      </c>
+      <c r="G114" t="n">
+        <v>10</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I114" t="n">
+        <v>20</v>
+      </c>
+      <c r="J114" t="n">
+        <v>1</v>
+      </c>
+      <c r="K114" t="n">
+        <v>5</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M114" t="n">
+        <v>50</v>
+      </c>
+      <c r="N114" t="n">
+        <v>27</v>
+      </c>
+      <c r="O114" t="n">
+        <v>29</v>
+      </c>
+      <c r="P114" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>6</v>
+      </c>
+      <c r="R114" t="n">
+        <v>1</v>
+      </c>
+      <c r="S114" t="n">
+        <v>17</v>
+      </c>
+      <c r="T114" t="n">
+        <v>11</v>
+      </c>
+      <c r="U114" t="n">
+        <v>4</v>
+      </c>
+      <c r="V114" t="n">
+        <v>11</v>
+      </c>
+      <c r="W114" t="n">
+        <v>7</v>
+      </c>
+      <c r="X114" t="n">
+        <v>16.50189592933643</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_13-23-12</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>2</v>
+      </c>
+      <c r="D115" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F115" t="n">
+        <v>2</v>
+      </c>
+      <c r="G115" t="n">
+        <v>10</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I115" t="n">
+        <v>20</v>
+      </c>
+      <c r="J115" t="n">
+        <v>1</v>
+      </c>
+      <c r="K115" t="n">
+        <v>5</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M115" t="n">
+        <v>50</v>
+      </c>
+      <c r="N115" t="n">
+        <v>23</v>
+      </c>
+      <c r="O115" t="n">
+        <v>1</v>
+      </c>
+      <c r="P115" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>23</v>
+      </c>
+      <c r="R115" t="n">
+        <v>23</v>
+      </c>
+      <c r="S115" t="n">
+        <v>27</v>
+      </c>
+      <c r="T115" t="n">
+        <v>23</v>
+      </c>
+      <c r="U115" t="n">
+        <v>23</v>
+      </c>
+      <c r="V115" t="n">
+        <v>27</v>
+      </c>
+      <c r="W115" t="n">
+        <v>3</v>
+      </c>
+      <c r="X115" t="n">
+        <v>12.72755015482802</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_13-23-12</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>3</v>
+      </c>
+      <c r="D116" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F116" t="n">
+        <v>2</v>
+      </c>
+      <c r="G116" t="n">
+        <v>10</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I116" t="n">
+        <v>20</v>
+      </c>
+      <c r="J116" t="n">
+        <v>1</v>
+      </c>
+      <c r="K116" t="n">
+        <v>5</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M116" t="n">
+        <v>50</v>
+      </c>
+      <c r="N116" t="n">
+        <v>25</v>
+      </c>
+      <c r="O116" t="n">
+        <v>30</v>
+      </c>
+      <c r="P116" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>18</v>
+      </c>
+      <c r="R116" t="n">
+        <v>8</v>
+      </c>
+      <c r="S116" t="n">
+        <v>4</v>
+      </c>
+      <c r="T116" t="n">
+        <v>18</v>
+      </c>
+      <c r="U116" t="n">
+        <v>8</v>
+      </c>
+      <c r="V116" t="n">
+        <v>25</v>
+      </c>
+      <c r="W116" t="n">
+        <v>3</v>
+      </c>
+      <c r="X116" t="n">
+        <v>13.00752928396169</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_13-23-12</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>4</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F117" t="n">
+        <v>2</v>
+      </c>
+      <c r="G117" t="n">
+        <v>10</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I117" t="n">
+        <v>20</v>
+      </c>
+      <c r="J117" t="n">
+        <v>1</v>
+      </c>
+      <c r="K117" t="n">
+        <v>5</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M117" t="n">
+        <v>50</v>
+      </c>
+      <c r="N117" t="n">
+        <v>28</v>
+      </c>
+      <c r="O117" t="n">
+        <v>12</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>29</v>
+      </c>
+      <c r="R117" t="n">
+        <v>29</v>
+      </c>
+      <c r="S117" t="n">
+        <v>31</v>
+      </c>
+      <c r="T117" t="n">
+        <v>31</v>
+      </c>
+      <c r="U117" t="n">
+        <v>6</v>
+      </c>
+      <c r="V117" t="n">
+        <v>30</v>
+      </c>
+      <c r="W117" t="n">
+        <v>17</v>
+      </c>
+      <c r="X117" t="n">
+        <v>13.97422553021965</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_13-23-12</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>1</v>
+      </c>
+      <c r="D118" t="n">
+        <v>2</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F118" t="n">
+        <v>2</v>
+      </c>
+      <c r="G118" t="n">
+        <v>10</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I118" t="n">
+        <v>20</v>
+      </c>
+      <c r="J118" t="n">
+        <v>1</v>
+      </c>
+      <c r="K118" t="n">
+        <v>5</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M118" t="n">
+        <v>50</v>
+      </c>
+      <c r="N118" t="n">
+        <v>8</v>
+      </c>
+      <c r="O118" t="n">
+        <v>5</v>
+      </c>
+      <c r="P118" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>18</v>
+      </c>
+      <c r="R118" t="n">
+        <v>31</v>
+      </c>
+      <c r="S118" t="n">
+        <v>2</v>
+      </c>
+      <c r="T118" t="n">
+        <v>24</v>
+      </c>
+      <c r="U118" t="n">
+        <v>2</v>
+      </c>
+      <c r="V118" t="n">
+        <v>25</v>
+      </c>
+      <c r="W118" t="n">
+        <v>1</v>
+      </c>
+      <c r="X118" t="n">
+        <v>16.67080684394357</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_13-23-12</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>2</v>
+      </c>
+      <c r="D119" t="n">
+        <v>2</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F119" t="n">
+        <v>2</v>
+      </c>
+      <c r="G119" t="n">
+        <v>10</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I119" t="n">
+        <v>20</v>
+      </c>
+      <c r="J119" t="n">
+        <v>1</v>
+      </c>
+      <c r="K119" t="n">
+        <v>5</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M119" t="n">
+        <v>50</v>
+      </c>
+      <c r="N119" t="n">
+        <v>23</v>
+      </c>
+      <c r="O119" t="n">
+        <v>22</v>
+      </c>
+      <c r="P119" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>23</v>
+      </c>
+      <c r="R119" t="n">
+        <v>21</v>
+      </c>
+      <c r="S119" t="n">
+        <v>23</v>
+      </c>
+      <c r="T119" t="n">
+        <v>26</v>
+      </c>
+      <c r="U119" t="n">
+        <v>23</v>
+      </c>
+      <c r="V119" t="n">
+        <v>13</v>
+      </c>
+      <c r="W119" t="n">
+        <v>25</v>
+      </c>
+      <c r="X119" t="n">
+        <v>15.60413017271284</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_13-23-12</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>3</v>
+      </c>
+      <c r="D120" t="n">
+        <v>2</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F120" t="n">
+        <v>2</v>
+      </c>
+      <c r="G120" t="n">
+        <v>10</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I120" t="n">
+        <v>20</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1</v>
+      </c>
+      <c r="K120" t="n">
+        <v>5</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M120" t="n">
+        <v>50</v>
+      </c>
+      <c r="N120" t="n">
+        <v>22</v>
+      </c>
+      <c r="O120" t="n">
+        <v>3</v>
+      </c>
+      <c r="P120" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>10</v>
+      </c>
+      <c r="R120" t="n">
+        <v>30</v>
+      </c>
+      <c r="S120" t="n">
+        <v>17</v>
+      </c>
+      <c r="T120" t="n">
+        <v>3</v>
+      </c>
+      <c r="U120" t="n">
+        <v>10</v>
+      </c>
+      <c r="V120" t="n">
+        <v>13</v>
+      </c>
+      <c r="W120" t="n">
+        <v>12</v>
+      </c>
+      <c r="X120" t="n">
+        <v>16.94293634599591</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_13-23-12</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>4</v>
+      </c>
+      <c r="D121" t="n">
+        <v>2</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F121" t="n">
+        <v>2</v>
+      </c>
+      <c r="G121" t="n">
+        <v>10</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I121" t="n">
+        <v>20</v>
+      </c>
+      <c r="J121" t="n">
+        <v>1</v>
+      </c>
+      <c r="K121" t="n">
+        <v>5</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M121" t="n">
+        <v>50</v>
+      </c>
+      <c r="N121" t="n">
+        <v>31</v>
+      </c>
+      <c r="O121" t="n">
+        <v>1</v>
+      </c>
+      <c r="P121" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>31</v>
+      </c>
+      <c r="R121" t="n">
+        <v>18</v>
+      </c>
+      <c r="S121" t="n">
+        <v>9</v>
+      </c>
+      <c r="T121" t="n">
+        <v>13</v>
+      </c>
+      <c r="U121" t="n">
+        <v>11</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0</v>
+      </c>
+      <c r="W121" t="n">
+        <v>1</v>
+      </c>
+      <c r="X121" t="n">
+        <v>14.99491943110936</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_13-23-12</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>1</v>
+      </c>
+      <c r="D122" t="n">
+        <v>3</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F122" t="n">
+        <v>2</v>
+      </c>
+      <c r="G122" t="n">
+        <v>10</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I122" t="n">
+        <v>20</v>
+      </c>
+      <c r="J122" t="n">
+        <v>1</v>
+      </c>
+      <c r="K122" t="n">
+        <v>5</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M122" t="n">
+        <v>50</v>
+      </c>
+      <c r="N122" t="n">
+        <v>16</v>
+      </c>
+      <c r="O122" t="n">
+        <v>17</v>
+      </c>
+      <c r="P122" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>3</v>
+      </c>
+      <c r="R122" t="n">
+        <v>3</v>
+      </c>
+      <c r="S122" t="n">
+        <v>5</v>
+      </c>
+      <c r="T122" t="n">
+        <v>11</v>
+      </c>
+      <c r="U122" t="n">
+        <v>11</v>
+      </c>
+      <c r="V122" t="n">
+        <v>30</v>
+      </c>
+      <c r="W122" t="n">
+        <v>12</v>
+      </c>
+      <c r="X122" t="n">
+        <v>10.30310695298891</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_13-23-12</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>2</v>
+      </c>
+      <c r="D123" t="n">
+        <v>3</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F123" t="n">
+        <v>2</v>
+      </c>
+      <c r="G123" t="n">
+        <v>10</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I123" t="n">
+        <v>20</v>
+      </c>
+      <c r="J123" t="n">
+        <v>1</v>
+      </c>
+      <c r="K123" t="n">
+        <v>5</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M123" t="n">
+        <v>50</v>
+      </c>
+      <c r="N123" t="n">
+        <v>19</v>
+      </c>
+      <c r="O123" t="n">
+        <v>19</v>
+      </c>
+      <c r="P123" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>25</v>
+      </c>
+      <c r="R123" t="n">
+        <v>19</v>
+      </c>
+      <c r="S123" t="n">
+        <v>24</v>
+      </c>
+      <c r="T123" t="n">
+        <v>19</v>
+      </c>
+      <c r="U123" t="n">
+        <v>26</v>
+      </c>
+      <c r="V123" t="n">
+        <v>14</v>
+      </c>
+      <c r="W123" t="n">
+        <v>6</v>
+      </c>
+      <c r="X123" t="n">
+        <v>12.27866011108737</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_13-23-12</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>3</v>
+      </c>
+      <c r="D124" t="n">
+        <v>3</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F124" t="n">
+        <v>2</v>
+      </c>
+      <c r="G124" t="n">
+        <v>10</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I124" t="n">
+        <v>20</v>
+      </c>
+      <c r="J124" t="n">
+        <v>1</v>
+      </c>
+      <c r="K124" t="n">
+        <v>5</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M124" t="n">
+        <v>50</v>
+      </c>
+      <c r="N124" t="n">
+        <v>29</v>
+      </c>
+      <c r="O124" t="n">
+        <v>29</v>
+      </c>
+      <c r="P124" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>29</v>
+      </c>
+      <c r="R124" t="n">
+        <v>16</v>
+      </c>
+      <c r="S124" t="n">
+        <v>28</v>
+      </c>
+      <c r="T124" t="n">
+        <v>27</v>
+      </c>
+      <c r="U124" t="n">
+        <v>28</v>
+      </c>
+      <c r="V124" t="n">
+        <v>30</v>
+      </c>
+      <c r="W124" t="n">
+        <v>8</v>
+      </c>
+      <c r="X124" t="n">
+        <v>12.28479942364725</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_13-23-12</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>4</v>
+      </c>
+      <c r="D125" t="n">
+        <v>3</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F125" t="n">
+        <v>2</v>
+      </c>
+      <c r="G125" t="n">
+        <v>10</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I125" t="n">
+        <v>20</v>
+      </c>
+      <c r="J125" t="n">
+        <v>1</v>
+      </c>
+      <c r="K125" t="n">
+        <v>5</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M125" t="n">
+        <v>50</v>
+      </c>
+      <c r="N125" t="n">
+        <v>29</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>3</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6</v>
+      </c>
+      <c r="S125" t="n">
+        <v>5</v>
+      </c>
+      <c r="T125" t="n">
+        <v>15</v>
+      </c>
+      <c r="U125" t="n">
+        <v>5</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0</v>
+      </c>
+      <c r="W125" t="n">
+        <v>3</v>
+      </c>
+      <c r="X125" t="n">
+        <v>11.9986809819536</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_13-23-12</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>1</v>
+      </c>
+      <c r="D126" t="n">
+        <v>4</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F126" t="n">
+        <v>2</v>
+      </c>
+      <c r="G126" t="n">
+        <v>10</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I126" t="n">
+        <v>20</v>
+      </c>
+      <c r="J126" t="n">
+        <v>1</v>
+      </c>
+      <c r="K126" t="n">
+        <v>5</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M126" t="n">
+        <v>50</v>
+      </c>
+      <c r="N126" t="n">
+        <v>9</v>
+      </c>
+      <c r="O126" t="n">
+        <v>20</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>9</v>
+      </c>
+      <c r="R126" t="n">
+        <v>2</v>
+      </c>
+      <c r="S126" t="n">
+        <v>4</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" t="n">
+        <v>20</v>
+      </c>
+      <c r="V126" t="n">
+        <v>2</v>
+      </c>
+      <c r="W126" t="n">
+        <v>2</v>
+      </c>
+      <c r="X126" t="n">
+        <v>12.72755015482808</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_13-23-12</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>2</v>
+      </c>
+      <c r="D127" t="n">
+        <v>4</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F127" t="n">
+        <v>2</v>
+      </c>
+      <c r="G127" t="n">
+        <v>10</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I127" t="n">
+        <v>20</v>
+      </c>
+      <c r="J127" t="n">
+        <v>1</v>
+      </c>
+      <c r="K127" t="n">
+        <v>5</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M127" t="n">
+        <v>50</v>
+      </c>
+      <c r="N127" t="n">
+        <v>16</v>
+      </c>
+      <c r="O127" t="n">
+        <v>9</v>
+      </c>
+      <c r="P127" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>3</v>
+      </c>
+      <c r="R127" t="n">
+        <v>3</v>
+      </c>
+      <c r="S127" t="n">
+        <v>31</v>
+      </c>
+      <c r="T127" t="n">
+        <v>24</v>
+      </c>
+      <c r="U127" t="n">
+        <v>24</v>
+      </c>
+      <c r="V127" t="n">
+        <v>25</v>
+      </c>
+      <c r="W127" t="n">
+        <v>25</v>
+      </c>
+      <c r="X127" t="n">
+        <v>10.59093570920385</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_13-23-12</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>3</v>
+      </c>
+      <c r="D128" t="n">
+        <v>4</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F128" t="n">
+        <v>2</v>
+      </c>
+      <c r="G128" t="n">
+        <v>10</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I128" t="n">
+        <v>20</v>
+      </c>
+      <c r="J128" t="n">
+        <v>1</v>
+      </c>
+      <c r="K128" t="n">
+        <v>5</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M128" t="n">
+        <v>50</v>
+      </c>
+      <c r="N128" t="n">
+        <v>1</v>
+      </c>
+      <c r="O128" t="n">
+        <v>1</v>
+      </c>
+      <c r="P128" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>31</v>
+      </c>
+      <c r="R128" t="n">
+        <v>31</v>
+      </c>
+      <c r="S128" t="n">
+        <v>5</v>
+      </c>
+      <c r="T128" t="n">
+        <v>9</v>
+      </c>
+      <c r="U128" t="n">
+        <v>4</v>
+      </c>
+      <c r="V128" t="n">
+        <v>6</v>
+      </c>
+      <c r="W128" t="n">
+        <v>1</v>
+      </c>
+      <c r="X128" t="n">
+        <v>11.99868098195341</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_13-23-12</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>4</v>
+      </c>
+      <c r="D129" t="n">
+        <v>4</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F129" t="n">
+        <v>2</v>
+      </c>
+      <c r="G129" t="n">
+        <v>10</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I129" t="n">
+        <v>20</v>
+      </c>
+      <c r="J129" t="n">
+        <v>1</v>
+      </c>
+      <c r="K129" t="n">
+        <v>5</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M129" t="n">
+        <v>50</v>
+      </c>
+      <c r="N129" t="n">
+        <v>11</v>
+      </c>
+      <c r="O129" t="n">
+        <v>25</v>
+      </c>
+      <c r="P129" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>11</v>
+      </c>
+      <c r="R129" t="n">
+        <v>30</v>
+      </c>
+      <c r="S129" t="n">
+        <v>13</v>
+      </c>
+      <c r="T129" t="n">
+        <v>9</v>
+      </c>
+      <c r="U129" t="n">
+        <v>13</v>
+      </c>
+      <c r="V129" t="n">
+        <v>4</v>
+      </c>
+      <c r="W129" t="n">
+        <v>13</v>
+      </c>
+      <c r="X129" t="n">
+        <v>12.83861836935439</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_13-40-19</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>1</v>
+      </c>
+      <c r="D130" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F130" t="n">
+        <v>2</v>
+      </c>
+      <c r="G130" t="n">
+        <v>10</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I130" t="n">
+        <v>20</v>
+      </c>
+      <c r="J130" t="n">
+        <v>1</v>
+      </c>
+      <c r="K130" t="n">
+        <v>5</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M130" t="n">
+        <v>50</v>
+      </c>
+      <c r="N130" t="n">
+        <v>7</v>
+      </c>
+      <c r="O130" t="n">
+        <v>28</v>
+      </c>
+      <c r="P130" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>31</v>
+      </c>
+      <c r="R130" t="n">
+        <v>19</v>
+      </c>
+      <c r="S130" t="n">
+        <v>5</v>
+      </c>
+      <c r="T130" t="n">
+        <v>19</v>
+      </c>
+      <c r="U130" t="n">
+        <v>3</v>
+      </c>
+      <c r="V130" t="n">
+        <v>28</v>
+      </c>
+      <c r="W130" t="n">
+        <v>31</v>
+      </c>
+      <c r="X130" t="n">
+        <v>14.53419239831948</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_13-40-19</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>2</v>
+      </c>
+      <c r="D131" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F131" t="n">
+        <v>2</v>
+      </c>
+      <c r="G131" t="n">
+        <v>10</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I131" t="n">
+        <v>20</v>
+      </c>
+      <c r="J131" t="n">
+        <v>1</v>
+      </c>
+      <c r="K131" t="n">
+        <v>5</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M131" t="n">
+        <v>50</v>
+      </c>
+      <c r="N131" t="n">
+        <v>4</v>
+      </c>
+      <c r="O131" t="n">
+        <v>13</v>
+      </c>
+      <c r="P131" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>2</v>
+      </c>
+      <c r="R131" t="n">
+        <v>13</v>
+      </c>
+      <c r="S131" t="n">
+        <v>4</v>
+      </c>
+      <c r="T131" t="n">
+        <v>13</v>
+      </c>
+      <c r="U131" t="n">
+        <v>17</v>
+      </c>
+      <c r="V131" t="n">
+        <v>12</v>
+      </c>
+      <c r="W131" t="n">
+        <v>15</v>
+      </c>
+      <c r="X131" t="n">
+        <v>15.82897265222084</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_13-40-19</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>3</v>
+      </c>
+      <c r="D132" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F132" t="n">
+        <v>2</v>
+      </c>
+      <c r="G132" t="n">
+        <v>10</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I132" t="n">
+        <v>20</v>
+      </c>
+      <c r="J132" t="n">
+        <v>1</v>
+      </c>
+      <c r="K132" t="n">
+        <v>5</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M132" t="n">
+        <v>50</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" t="n">
+        <v>25</v>
+      </c>
+      <c r="P132" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>16</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" t="n">
+        <v>3</v>
+      </c>
+      <c r="T132" t="n">
+        <v>29</v>
+      </c>
+      <c r="U132" t="n">
+        <v>24</v>
+      </c>
+      <c r="V132" t="n">
+        <v>28</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0</v>
+      </c>
+      <c r="X132" t="n">
+        <v>15.38197941280165</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_13-40-19</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>4</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F133" t="n">
+        <v>2</v>
+      </c>
+      <c r="G133" t="n">
+        <v>10</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I133" t="n">
+        <v>20</v>
+      </c>
+      <c r="J133" t="n">
+        <v>1</v>
+      </c>
+      <c r="K133" t="n">
+        <v>5</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M133" t="n">
+        <v>50</v>
+      </c>
+      <c r="N133" t="n">
+        <v>4</v>
+      </c>
+      <c r="O133" t="n">
+        <v>26</v>
+      </c>
+      <c r="P133" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>30</v>
+      </c>
+      <c r="R133" t="n">
+        <v>13</v>
+      </c>
+      <c r="S133" t="n">
+        <v>5</v>
+      </c>
+      <c r="T133" t="n">
+        <v>26</v>
+      </c>
+      <c r="U133" t="n">
+        <v>19</v>
+      </c>
+      <c r="V133" t="n">
+        <v>7</v>
+      </c>
+      <c r="W133" t="n">
+        <v>3</v>
+      </c>
+      <c r="X133" t="n">
+        <v>14.53419239831951</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_13-40-19</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>1</v>
+      </c>
+      <c r="D134" t="n">
+        <v>2</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F134" t="n">
+        <v>2</v>
+      </c>
+      <c r="G134" t="n">
+        <v>10</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I134" t="n">
+        <v>20</v>
+      </c>
+      <c r="J134" t="n">
+        <v>1</v>
+      </c>
+      <c r="K134" t="n">
+        <v>5</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M134" t="n">
+        <v>50</v>
+      </c>
+      <c r="N134" t="n">
+        <v>8</v>
+      </c>
+      <c r="O134" t="n">
+        <v>25</v>
+      </c>
+      <c r="P134" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>1</v>
+      </c>
+      <c r="R134" t="n">
+        <v>1</v>
+      </c>
+      <c r="S134" t="n">
+        <v>30</v>
+      </c>
+      <c r="T134" t="n">
+        <v>8</v>
+      </c>
+      <c r="U134" t="n">
+        <v>27</v>
+      </c>
+      <c r="V134" t="n">
+        <v>26</v>
+      </c>
+      <c r="W134" t="n">
+        <v>31</v>
+      </c>
+      <c r="X134" t="n">
+        <v>14.81417152745302</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_13-40-19</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>2</v>
+      </c>
+      <c r="D135" t="n">
+        <v>2</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F135" t="n">
+        <v>2</v>
+      </c>
+      <c r="G135" t="n">
+        <v>10</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I135" t="n">
+        <v>20</v>
+      </c>
+      <c r="J135" t="n">
+        <v>1</v>
+      </c>
+      <c r="K135" t="n">
+        <v>5</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M135" t="n">
+        <v>50</v>
+      </c>
+      <c r="N135" t="n">
+        <v>15</v>
+      </c>
+      <c r="O135" t="n">
+        <v>7</v>
+      </c>
+      <c r="P135" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>29</v>
+      </c>
+      <c r="R135" t="n">
+        <v>29</v>
+      </c>
+      <c r="S135" t="n">
+        <v>26</v>
+      </c>
+      <c r="T135" t="n">
+        <v>25</v>
+      </c>
+      <c r="U135" t="n">
+        <v>1</v>
+      </c>
+      <c r="V135" t="n">
+        <v>15</v>
+      </c>
+      <c r="W135" t="n">
+        <v>9</v>
+      </c>
+      <c r="X135" t="n">
+        <v>15.82301982946126</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_13-40-19</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>3</v>
+      </c>
+      <c r="D136" t="n">
+        <v>2</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F136" t="n">
+        <v>2</v>
+      </c>
+      <c r="G136" t="n">
+        <v>10</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I136" t="n">
+        <v>20</v>
+      </c>
+      <c r="J136" t="n">
+        <v>1</v>
+      </c>
+      <c r="K136" t="n">
+        <v>5</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M136" t="n">
+        <v>50</v>
+      </c>
+      <c r="N136" t="n">
+        <v>9</v>
+      </c>
+      <c r="O136" t="n">
+        <v>23</v>
+      </c>
+      <c r="P136" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>7</v>
+      </c>
+      <c r="R136" t="n">
+        <v>27</v>
+      </c>
+      <c r="S136" t="n">
+        <v>7</v>
+      </c>
+      <c r="T136" t="n">
+        <v>23</v>
+      </c>
+      <c r="U136" t="n">
+        <v>5</v>
+      </c>
+      <c r="V136" t="n">
+        <v>28</v>
+      </c>
+      <c r="W136" t="n">
+        <v>11</v>
+      </c>
+      <c r="X136" t="n">
+        <v>15.44506274141657</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_13-40-19</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>4</v>
+      </c>
+      <c r="D137" t="n">
+        <v>2</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F137" t="n">
+        <v>2</v>
+      </c>
+      <c r="G137" t="n">
+        <v>10</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I137" t="n">
+        <v>20</v>
+      </c>
+      <c r="J137" t="n">
+        <v>1</v>
+      </c>
+      <c r="K137" t="n">
+        <v>5</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M137" t="n">
+        <v>50</v>
+      </c>
+      <c r="N137" t="n">
+        <v>24</v>
+      </c>
+      <c r="O137" t="n">
+        <v>12</v>
+      </c>
+      <c r="P137" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>21</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6</v>
+      </c>
+      <c r="S137" t="n">
+        <v>18</v>
+      </c>
+      <c r="T137" t="n">
+        <v>12</v>
+      </c>
+      <c r="U137" t="n">
+        <v>31</v>
+      </c>
+      <c r="V137" t="n">
+        <v>12</v>
+      </c>
+      <c r="W137" t="n">
+        <v>21</v>
+      </c>
+      <c r="X137" t="n">
+        <v>15.15116740014605</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_13-40-19</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>1</v>
+      </c>
+      <c r="D138" t="n">
+        <v>3</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F138" t="n">
+        <v>2</v>
+      </c>
+      <c r="G138" t="n">
+        <v>10</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I138" t="n">
+        <v>20</v>
+      </c>
+      <c r="J138" t="n">
+        <v>1</v>
+      </c>
+      <c r="K138" t="n">
+        <v>5</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M138" t="n">
+        <v>50</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
+        <v>5</v>
+      </c>
+      <c r="P138" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>5</v>
+      </c>
+      <c r="R138" t="n">
+        <v>11</v>
+      </c>
+      <c r="S138" t="n">
+        <v>17</v>
+      </c>
+      <c r="T138" t="n">
+        <v>12</v>
+      </c>
+      <c r="U138" t="n">
+        <v>5</v>
+      </c>
+      <c r="V138" t="n">
+        <v>31</v>
+      </c>
+      <c r="W138" t="n">
+        <v>5</v>
+      </c>
+      <c r="X138" t="n">
+        <v>12.55863924022089</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_13-40-19</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>2</v>
+      </c>
+      <c r="D139" t="n">
+        <v>3</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F139" t="n">
+        <v>2</v>
+      </c>
+      <c r="G139" t="n">
+        <v>10</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I139" t="n">
+        <v>20</v>
+      </c>
+      <c r="J139" t="n">
+        <v>1</v>
+      </c>
+      <c r="K139" t="n">
+        <v>5</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M139" t="n">
+        <v>50</v>
+      </c>
+      <c r="N139" t="n">
+        <v>28</v>
+      </c>
+      <c r="O139" t="n">
+        <v>28</v>
+      </c>
+      <c r="P139" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>1</v>
+      </c>
+      <c r="R139" t="n">
+        <v>14</v>
+      </c>
+      <c r="S139" t="n">
+        <v>1</v>
+      </c>
+      <c r="T139" t="n">
+        <v>7</v>
+      </c>
+      <c r="U139" t="n">
+        <v>1</v>
+      </c>
+      <c r="V139" t="n">
+        <v>28</v>
+      </c>
+      <c r="W139" t="n">
+        <v>30</v>
+      </c>
+      <c r="X139" t="n">
+        <v>9.749288007281555</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_13-40-19</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>3</v>
+      </c>
+      <c r="D140" t="n">
+        <v>3</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F140" t="n">
+        <v>2</v>
+      </c>
+      <c r="G140" t="n">
+        <v>10</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I140" t="n">
+        <v>20</v>
+      </c>
+      <c r="J140" t="n">
+        <v>1</v>
+      </c>
+      <c r="K140" t="n">
+        <v>5</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M140" t="n">
+        <v>50</v>
+      </c>
+      <c r="N140" t="n">
+        <v>22</v>
+      </c>
+      <c r="O140" t="n">
+        <v>1</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>14</v>
+      </c>
+      <c r="R140" t="n">
+        <v>1</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="n">
+        <v>15</v>
+      </c>
+      <c r="U140" t="n">
+        <v>1</v>
+      </c>
+      <c r="V140" t="n">
+        <v>10</v>
+      </c>
+      <c r="W140" t="n">
+        <v>10</v>
+      </c>
+      <c r="X140" t="n">
+        <v>12.43972139861296</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_13-40-19</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>4</v>
+      </c>
+      <c r="D141" t="n">
+        <v>3</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F141" t="n">
+        <v>2</v>
+      </c>
+      <c r="G141" t="n">
+        <v>10</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I141" t="n">
+        <v>20</v>
+      </c>
+      <c r="J141" t="n">
+        <v>1</v>
+      </c>
+      <c r="K141" t="n">
+        <v>5</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M141" t="n">
+        <v>50</v>
+      </c>
+      <c r="N141" t="n">
+        <v>27</v>
+      </c>
+      <c r="O141" t="n">
+        <v>15</v>
+      </c>
+      <c r="P141" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>5</v>
+      </c>
+      <c r="R141" t="n">
+        <v>24</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0</v>
+      </c>
+      <c r="T141" t="n">
+        <v>24</v>
+      </c>
+      <c r="U141" t="n">
+        <v>5</v>
+      </c>
+      <c r="V141" t="n">
+        <v>24</v>
+      </c>
+      <c r="W141" t="n">
+        <v>29</v>
+      </c>
+      <c r="X141" t="n">
+        <v>9.46316956558778</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_13-40-19</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>1</v>
+      </c>
+      <c r="D142" t="n">
+        <v>4</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F142" t="n">
+        <v>2</v>
+      </c>
+      <c r="G142" t="n">
+        <v>10</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I142" t="n">
+        <v>20</v>
+      </c>
+      <c r="J142" t="n">
+        <v>1</v>
+      </c>
+      <c r="K142" t="n">
+        <v>5</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M142" t="n">
+        <v>50</v>
+      </c>
+      <c r="N142" t="n">
+        <v>22</v>
+      </c>
+      <c r="O142" t="n">
+        <v>31</v>
+      </c>
+      <c r="P142" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>15</v>
+      </c>
+      <c r="R142" t="n">
+        <v>27</v>
+      </c>
+      <c r="S142" t="n">
+        <v>17</v>
+      </c>
+      <c r="T142" t="n">
+        <v>7</v>
+      </c>
+      <c r="U142" t="n">
+        <v>22</v>
+      </c>
+      <c r="V142" t="n">
+        <v>22</v>
+      </c>
+      <c r="W142" t="n">
+        <v>3</v>
+      </c>
+      <c r="X142" t="n">
+        <v>14.6952536858451</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_13-40-19</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>2</v>
+      </c>
+      <c r="D143" t="n">
+        <v>4</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F143" t="n">
+        <v>2</v>
+      </c>
+      <c r="G143" t="n">
+        <v>10</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I143" t="n">
+        <v>20</v>
+      </c>
+      <c r="J143" t="n">
+        <v>1</v>
+      </c>
+      <c r="K143" t="n">
+        <v>5</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M143" t="n">
+        <v>50</v>
+      </c>
+      <c r="N143" t="n">
+        <v>2</v>
+      </c>
+      <c r="O143" t="n">
+        <v>21</v>
+      </c>
+      <c r="P143" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>6</v>
+      </c>
+      <c r="R143" t="n">
+        <v>27</v>
+      </c>
+      <c r="S143" t="n">
+        <v>8</v>
+      </c>
+      <c r="T143" t="n">
+        <v>21</v>
+      </c>
+      <c r="U143" t="n">
+        <v>2</v>
+      </c>
+      <c r="V143" t="n">
+        <v>28</v>
+      </c>
+      <c r="W143" t="n">
+        <v>6</v>
+      </c>
+      <c r="X143" t="n">
+        <v>12.15974226947949</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_13-40-19</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>3</v>
+      </c>
+      <c r="D144" t="n">
+        <v>4</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F144" t="n">
+        <v>2</v>
+      </c>
+      <c r="G144" t="n">
+        <v>10</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I144" t="n">
+        <v>20</v>
+      </c>
+      <c r="J144" t="n">
+        <v>1</v>
+      </c>
+      <c r="K144" t="n">
+        <v>5</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M144" t="n">
+        <v>50</v>
+      </c>
+      <c r="N144" t="n">
+        <v>24</v>
+      </c>
+      <c r="O144" t="n">
+        <v>15</v>
+      </c>
+      <c r="P144" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>19</v>
+      </c>
+      <c r="R144" t="n">
+        <v>24</v>
+      </c>
+      <c r="S144" t="n">
+        <v>30</v>
+      </c>
+      <c r="T144" t="n">
+        <v>6</v>
+      </c>
+      <c r="U144" t="n">
+        <v>5</v>
+      </c>
+      <c r="V144" t="n">
+        <v>20</v>
+      </c>
+      <c r="W144" t="n">
+        <v>15</v>
+      </c>
+      <c r="X144" t="n">
+        <v>13.28750841309538</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_13-40-19</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>4</v>
+      </c>
+      <c r="D145" t="n">
+        <v>4</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F145" t="n">
+        <v>2</v>
+      </c>
+      <c r="G145" t="n">
+        <v>10</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I145" t="n">
+        <v>20</v>
+      </c>
+      <c r="J145" t="n">
+        <v>1</v>
+      </c>
+      <c r="K145" t="n">
+        <v>5</v>
+      </c>
+      <c r="L145" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M145" t="n">
+        <v>50</v>
+      </c>
+      <c r="N145" t="n">
+        <v>29</v>
+      </c>
+      <c r="O145" t="n">
+        <v>24</v>
+      </c>
+      <c r="P145" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>8</v>
+      </c>
+      <c r="R145" t="n">
+        <v>24</v>
+      </c>
+      <c r="S145" t="n">
+        <v>8</v>
+      </c>
+      <c r="T145" t="n">
+        <v>30</v>
+      </c>
+      <c r="U145" t="n">
+        <v>30</v>
+      </c>
+      <c r="V145" t="n">
+        <v>12</v>
+      </c>
+      <c r="W145" t="n">
+        <v>14</v>
+      </c>
+      <c r="X145" t="n">
+        <v>11.71869324298762</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_14-26-34</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>1</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F146" t="n">
+        <v>2</v>
+      </c>
+      <c r="G146" t="n">
+        <v>10</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I146" t="n">
+        <v>20</v>
+      </c>
+      <c r="J146" t="n">
+        <v>1</v>
+      </c>
+      <c r="K146" t="n">
+        <v>5</v>
+      </c>
+      <c r="L146" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M146" t="n">
+        <v>50</v>
+      </c>
+      <c r="N146" t="n">
+        <v>3</v>
+      </c>
+      <c r="O146" t="n">
+        <v>25</v>
+      </c>
+      <c r="P146" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>10</v>
+      </c>
+      <c r="R146" t="n">
+        <v>1</v>
+      </c>
+      <c r="S146" t="n">
+        <v>30</v>
+      </c>
+      <c r="T146" t="n">
+        <v>28</v>
+      </c>
+      <c r="U146" t="n">
+        <v>0</v>
+      </c>
+      <c r="V146" t="n">
+        <v>26</v>
+      </c>
+      <c r="W146" t="n">
+        <v>19</v>
+      </c>
+      <c r="X146" t="n">
+        <v>17.07754483193436</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_14-26-34</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>2</v>
+      </c>
+      <c r="D147" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F147" t="n">
+        <v>2</v>
+      </c>
+      <c r="G147" t="n">
+        <v>10</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I147" t="n">
+        <v>20</v>
+      </c>
+      <c r="J147" t="n">
+        <v>1</v>
+      </c>
+      <c r="K147" t="n">
+        <v>5</v>
+      </c>
+      <c r="L147" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M147" t="n">
+        <v>50</v>
+      </c>
+      <c r="N147" t="n">
+        <v>27</v>
+      </c>
+      <c r="O147" t="n">
+        <v>2</v>
+      </c>
+      <c r="P147" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>6</v>
+      </c>
+      <c r="R147" t="n">
+        <v>29</v>
+      </c>
+      <c r="S147" t="n">
+        <v>16</v>
+      </c>
+      <c r="T147" t="n">
+        <v>13</v>
+      </c>
+      <c r="U147" t="n">
+        <v>1</v>
+      </c>
+      <c r="V147" t="n">
+        <v>1</v>
+      </c>
+      <c r="W147" t="n">
+        <v>7</v>
+      </c>
+      <c r="X147" t="n">
+        <v>15.09415065658687</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_14-26-34</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>3</v>
+      </c>
+      <c r="D148" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F148" t="n">
+        <v>2</v>
+      </c>
+      <c r="G148" t="n">
+        <v>10</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I148" t="n">
+        <v>20</v>
+      </c>
+      <c r="J148" t="n">
+        <v>1</v>
+      </c>
+      <c r="K148" t="n">
+        <v>5</v>
+      </c>
+      <c r="L148" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M148" t="n">
+        <v>50</v>
+      </c>
+      <c r="N148" t="n">
+        <v>4</v>
+      </c>
+      <c r="O148" t="n">
+        <v>13</v>
+      </c>
+      <c r="P148" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>7</v>
+      </c>
+      <c r="R148" t="n">
+        <v>0</v>
+      </c>
+      <c r="S148" t="n">
+        <v>10</v>
+      </c>
+      <c r="T148" t="n">
+        <v>22</v>
+      </c>
+      <c r="U148" t="n">
+        <v>27</v>
+      </c>
+      <c r="V148" t="n">
+        <v>28</v>
+      </c>
+      <c r="W148" t="n">
+        <v>6</v>
+      </c>
+      <c r="X148" t="n">
+        <v>15.82301982946127</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_14-26-34</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>4</v>
+      </c>
+      <c r="D149" t="n">
+        <v>1</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F149" t="n">
+        <v>2</v>
+      </c>
+      <c r="G149" t="n">
+        <v>10</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I149" t="n">
+        <v>20</v>
+      </c>
+      <c r="J149" t="n">
+        <v>1</v>
+      </c>
+      <c r="K149" t="n">
+        <v>5</v>
+      </c>
+      <c r="L149" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M149" t="n">
+        <v>50</v>
+      </c>
+      <c r="N149" t="n">
+        <v>2</v>
+      </c>
+      <c r="O149" t="n">
+        <v>8</v>
+      </c>
+      <c r="P149" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>2</v>
+      </c>
+      <c r="R149" t="n">
+        <v>4</v>
+      </c>
+      <c r="S149" t="n">
+        <v>1</v>
+      </c>
+      <c r="T149" t="n">
+        <v>30</v>
+      </c>
+      <c r="U149" t="n">
+        <v>29</v>
+      </c>
+      <c r="V149" t="n">
+        <v>13</v>
+      </c>
+      <c r="W149" t="n">
+        <v>1</v>
+      </c>
+      <c r="X149" t="n">
+        <v>13.12644712556977</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_14-26-34</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>1</v>
+      </c>
+      <c r="D150" t="n">
+        <v>2</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F150" t="n">
+        <v>2</v>
+      </c>
+      <c r="G150" t="n">
+        <v>10</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I150" t="n">
+        <v>20</v>
+      </c>
+      <c r="J150" t="n">
+        <v>1</v>
+      </c>
+      <c r="K150" t="n">
+        <v>5</v>
+      </c>
+      <c r="L150" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M150" t="n">
+        <v>50</v>
+      </c>
+      <c r="N150" t="n">
+        <v>15</v>
+      </c>
+      <c r="O150" t="n">
+        <v>2</v>
+      </c>
+      <c r="P150" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>0</v>
+      </c>
+      <c r="R150" t="n">
+        <v>26</v>
+      </c>
+      <c r="S150" t="n">
+        <v>31</v>
+      </c>
+      <c r="T150" t="n">
+        <v>25</v>
+      </c>
+      <c r="U150" t="n">
+        <v>28</v>
+      </c>
+      <c r="V150" t="n">
+        <v>16</v>
+      </c>
+      <c r="W150" t="n">
+        <v>30</v>
+      </c>
+      <c r="X150" t="n">
+        <v>17.0697038146852</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_14-26-34</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>2</v>
+      </c>
+      <c r="D151" t="n">
+        <v>2</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F151" t="n">
+        <v>2</v>
+      </c>
+      <c r="G151" t="n">
+        <v>10</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I151" t="n">
+        <v>20</v>
+      </c>
+      <c r="J151" t="n">
+        <v>1</v>
+      </c>
+      <c r="K151" t="n">
+        <v>5</v>
+      </c>
+      <c r="L151" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M151" t="n">
+        <v>50</v>
+      </c>
+      <c r="N151" t="n">
+        <v>23</v>
+      </c>
+      <c r="O151" t="n">
+        <v>17</v>
+      </c>
+      <c r="P151" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>28</v>
+      </c>
+      <c r="R151" t="n">
+        <v>31</v>
+      </c>
+      <c r="S151" t="n">
+        <v>26</v>
+      </c>
+      <c r="T151" t="n">
+        <v>3</v>
+      </c>
+      <c r="U151" t="n">
+        <v>23</v>
+      </c>
+      <c r="V151" t="n">
+        <v>23</v>
+      </c>
+      <c r="W151" t="n">
+        <v>10</v>
+      </c>
+      <c r="X151" t="n">
+        <v>14.69525368584516</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_14-26-34</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>3</v>
+      </c>
+      <c r="D152" t="n">
+        <v>2</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F152" t="n">
+        <v>2</v>
+      </c>
+      <c r="G152" t="n">
+        <v>10</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I152" t="n">
+        <v>20</v>
+      </c>
+      <c r="J152" t="n">
+        <v>1</v>
+      </c>
+      <c r="K152" t="n">
+        <v>5</v>
+      </c>
+      <c r="L152" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M152" t="n">
+        <v>50</v>
+      </c>
+      <c r="N152" t="n">
+        <v>10</v>
+      </c>
+      <c r="O152" t="n">
+        <v>29</v>
+      </c>
+      <c r="P152" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>10</v>
+      </c>
+      <c r="R152" t="n">
+        <v>8</v>
+      </c>
+      <c r="S152" t="n">
+        <v>2</v>
+      </c>
+      <c r="T152" t="n">
+        <v>9</v>
+      </c>
+      <c r="U152" t="n">
+        <v>12</v>
+      </c>
+      <c r="V152" t="n">
+        <v>30</v>
+      </c>
+      <c r="W152" t="n">
+        <v>8</v>
+      </c>
+      <c r="X152" t="n">
+        <v>14.24636364210424</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_14-26-34</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>4</v>
+      </c>
+      <c r="D153" t="n">
+        <v>2</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F153" t="n">
+        <v>2</v>
+      </c>
+      <c r="G153" t="n">
+        <v>10</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I153" t="n">
+        <v>20</v>
+      </c>
+      <c r="J153" t="n">
+        <v>1</v>
+      </c>
+      <c r="K153" t="n">
+        <v>5</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M153" t="n">
+        <v>50</v>
+      </c>
+      <c r="N153" t="n">
+        <v>2</v>
+      </c>
+      <c r="O153" t="n">
+        <v>15</v>
+      </c>
+      <c r="P153" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>7</v>
+      </c>
+      <c r="R153" t="n">
+        <v>14</v>
+      </c>
+      <c r="S153" t="n">
+        <v>9</v>
+      </c>
+      <c r="T153" t="n">
+        <v>3</v>
+      </c>
+      <c r="U153" t="n">
+        <v>8</v>
+      </c>
+      <c r="V153" t="n">
+        <v>23</v>
+      </c>
+      <c r="W153" t="n">
+        <v>10</v>
+      </c>
+      <c r="X153" t="n">
+        <v>16.66907577972181</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_14-26-34</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>1</v>
+      </c>
+      <c r="D154" t="n">
+        <v>3</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F154" t="n">
+        <v>2</v>
+      </c>
+      <c r="G154" t="n">
+        <v>10</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I154" t="n">
+        <v>20</v>
+      </c>
+      <c r="J154" t="n">
+        <v>1</v>
+      </c>
+      <c r="K154" t="n">
+        <v>5</v>
+      </c>
+      <c r="L154" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M154" t="n">
+        <v>50</v>
+      </c>
+      <c r="N154" t="n">
+        <v>4</v>
+      </c>
+      <c r="O154" t="n">
+        <v>1</v>
+      </c>
+      <c r="P154" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>14</v>
+      </c>
+      <c r="R154" t="n">
+        <v>5</v>
+      </c>
+      <c r="S154" t="n">
+        <v>4</v>
+      </c>
+      <c r="T154" t="n">
+        <v>6</v>
+      </c>
+      <c r="U154" t="n">
+        <v>6</v>
+      </c>
+      <c r="V154" t="n">
+        <v>5</v>
+      </c>
+      <c r="W154" t="n">
+        <v>6</v>
+      </c>
+      <c r="X154" t="n">
+        <v>12.27866011108715</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_14-26-34</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>2</v>
+      </c>
+      <c r="D155" t="n">
+        <v>3</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F155" t="n">
+        <v>2</v>
+      </c>
+      <c r="G155" t="n">
+        <v>10</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I155" t="n">
+        <v>20</v>
+      </c>
+      <c r="J155" t="n">
+        <v>1</v>
+      </c>
+      <c r="K155" t="n">
+        <v>5</v>
+      </c>
+      <c r="L155" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M155" t="n">
+        <v>50</v>
+      </c>
+      <c r="N155" t="n">
+        <v>7</v>
+      </c>
+      <c r="O155" t="n">
+        <v>7</v>
+      </c>
+      <c r="P155" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>31</v>
+      </c>
+      <c r="R155" t="n">
+        <v>4</v>
+      </c>
+      <c r="S155" t="n">
+        <v>31</v>
+      </c>
+      <c r="T155" t="n">
+        <v>7</v>
+      </c>
+      <c r="U155" t="n">
+        <v>4</v>
+      </c>
+      <c r="V155" t="n">
+        <v>26</v>
+      </c>
+      <c r="W155" t="n">
+        <v>8</v>
+      </c>
+      <c r="X155" t="n">
+        <v>12.27866011108729</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_14-26-34</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>3</v>
+      </c>
+      <c r="D156" t="n">
+        <v>3</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F156" t="n">
+        <v>2</v>
+      </c>
+      <c r="G156" t="n">
+        <v>10</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I156" t="n">
+        <v>20</v>
+      </c>
+      <c r="J156" t="n">
+        <v>1</v>
+      </c>
+      <c r="K156" t="n">
+        <v>5</v>
+      </c>
+      <c r="L156" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M156" t="n">
+        <v>50</v>
+      </c>
+      <c r="N156" t="n">
+        <v>6</v>
+      </c>
+      <c r="O156" t="n">
+        <v>31</v>
+      </c>
+      <c r="P156" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>28</v>
+      </c>
+      <c r="R156" t="n">
+        <v>6</v>
+      </c>
+      <c r="S156" t="n">
+        <v>24</v>
+      </c>
+      <c r="T156" t="n">
+        <v>31</v>
+      </c>
+      <c r="U156" t="n">
+        <v>29</v>
+      </c>
+      <c r="V156" t="n">
+        <v>31</v>
+      </c>
+      <c r="W156" t="n">
+        <v>28</v>
+      </c>
+      <c r="X156" t="n">
+        <v>12.5649534206813</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_14-26-34</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>4</v>
+      </c>
+      <c r="D157" t="n">
+        <v>3</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F157" t="n">
+        <v>2</v>
+      </c>
+      <c r="G157" t="n">
+        <v>10</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I157" t="n">
+        <v>20</v>
+      </c>
+      <c r="J157" t="n">
+        <v>1</v>
+      </c>
+      <c r="K157" t="n">
+        <v>5</v>
+      </c>
+      <c r="L157" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M157" t="n">
+        <v>50</v>
+      </c>
+      <c r="N157" t="n">
+        <v>12</v>
+      </c>
+      <c r="O157" t="n">
+        <v>3</v>
+      </c>
+      <c r="P157" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>24</v>
+      </c>
+      <c r="R157" t="n">
+        <v>24</v>
+      </c>
+      <c r="S157" t="n">
+        <v>29</v>
+      </c>
+      <c r="T157" t="n">
+        <v>3</v>
+      </c>
+      <c r="U157" t="n">
+        <v>24</v>
+      </c>
+      <c r="V157" t="n">
+        <v>3</v>
+      </c>
+      <c r="W157" t="n">
+        <v>29</v>
+      </c>
+      <c r="X157" t="n">
+        <v>7.207637278355739</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_14-26-34</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>1</v>
+      </c>
+      <c r="D158" t="n">
+        <v>4</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F158" t="n">
+        <v>2</v>
+      </c>
+      <c r="G158" t="n">
+        <v>10</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I158" t="n">
+        <v>20</v>
+      </c>
+      <c r="J158" t="n">
+        <v>1</v>
+      </c>
+      <c r="K158" t="n">
+        <v>5</v>
+      </c>
+      <c r="L158" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M158" t="n">
+        <v>50</v>
+      </c>
+      <c r="N158" t="n">
+        <v>20</v>
+      </c>
+      <c r="O158" t="n">
+        <v>21</v>
+      </c>
+      <c r="P158" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>5</v>
+      </c>
+      <c r="R158" t="n">
+        <v>20</v>
+      </c>
+      <c r="S158" t="n">
+        <v>30</v>
+      </c>
+      <c r="T158" t="n">
+        <v>6</v>
+      </c>
+      <c r="U158" t="n">
+        <v>20</v>
+      </c>
+      <c r="V158" t="n">
+        <v>24</v>
+      </c>
+      <c r="W158" t="n">
+        <v>1</v>
+      </c>
+      <c r="X158" t="n">
+        <v>12.90140847861105</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_14-26-34</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>2</v>
+      </c>
+      <c r="D159" t="n">
+        <v>4</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F159" t="n">
+        <v>2</v>
+      </c>
+      <c r="G159" t="n">
+        <v>10</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I159" t="n">
+        <v>20</v>
+      </c>
+      <c r="J159" t="n">
+        <v>1</v>
+      </c>
+      <c r="K159" t="n">
+        <v>5</v>
+      </c>
+      <c r="L159" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M159" t="n">
+        <v>50</v>
+      </c>
+      <c r="N159" t="n">
+        <v>3</v>
+      </c>
+      <c r="O159" t="n">
+        <v>2</v>
+      </c>
+      <c r="P159" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>16</v>
+      </c>
+      <c r="R159" t="n">
+        <v>2</v>
+      </c>
+      <c r="S159" t="n">
+        <v>24</v>
+      </c>
+      <c r="T159" t="n">
+        <v>4</v>
+      </c>
+      <c r="U159" t="n">
+        <v>4</v>
+      </c>
+      <c r="V159" t="n">
+        <v>28</v>
+      </c>
+      <c r="W159" t="n">
+        <v>3</v>
+      </c>
+      <c r="X159" t="n">
+        <v>11.99868098195339</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_14-26-34</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>3</v>
+      </c>
+      <c r="D160" t="n">
+        <v>4</v>
+      </c>
+      <c r="E160" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F160" t="n">
+        <v>2</v>
+      </c>
+      <c r="G160" t="n">
+        <v>10</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I160" t="n">
+        <v>20</v>
+      </c>
+      <c r="J160" t="n">
+        <v>1</v>
+      </c>
+      <c r="K160" t="n">
+        <v>5</v>
+      </c>
+      <c r="L160" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M160" t="n">
+        <v>50</v>
+      </c>
+      <c r="N160" t="n">
+        <v>31</v>
+      </c>
+      <c r="O160" t="n">
+        <v>7</v>
+      </c>
+      <c r="P160" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>0</v>
+      </c>
+      <c r="R160" t="n">
+        <v>31</v>
+      </c>
+      <c r="S160" t="n">
+        <v>6</v>
+      </c>
+      <c r="T160" t="n">
+        <v>7</v>
+      </c>
+      <c r="U160" t="n">
+        <v>0</v>
+      </c>
+      <c r="V160" t="n">
+        <v>3</v>
+      </c>
+      <c r="W160" t="n">
+        <v>5</v>
+      </c>
+      <c r="X160" t="n">
+        <v>13.40642625470343</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_14-26-34</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>4</v>
+      </c>
+      <c r="D161" t="n">
+        <v>4</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F161" t="n">
+        <v>2</v>
+      </c>
+      <c r="G161" t="n">
+        <v>10</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I161" t="n">
+        <v>20</v>
+      </c>
+      <c r="J161" t="n">
+        <v>1</v>
+      </c>
+      <c r="K161" t="n">
+        <v>5</v>
+      </c>
+      <c r="L161" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M161" t="n">
+        <v>50</v>
+      </c>
+      <c r="N161" t="n">
+        <v>28</v>
+      </c>
+      <c r="O161" t="n">
+        <v>2</v>
+      </c>
+      <c r="P161" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>1</v>
+      </c>
+      <c r="R161" t="n">
+        <v>1</v>
+      </c>
+      <c r="S161" t="n">
+        <v>26</v>
+      </c>
+      <c r="T161" t="n">
+        <v>26</v>
+      </c>
+      <c r="U161" t="n">
+        <v>25</v>
+      </c>
+      <c r="V161" t="n">
+        <v>14</v>
+      </c>
+      <c r="W161" t="n">
+        <v>28</v>
+      </c>
+      <c r="X161" t="n">
+        <v>11.9986809819536</v>
+      </c>
+      <c r="Y161" t="n">
         <v>19</v>
       </c>
     </row>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y161"/>
+  <dimension ref="A1:Y170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -12422,6 +12422,735 @@
         <v>19</v>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_15-26-30</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>1</v>
+      </c>
+      <c r="D162" t="n">
+        <v>1</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F162" t="n">
+        <v>2</v>
+      </c>
+      <c r="G162" t="n">
+        <v>10</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I162" t="n">
+        <v>20</v>
+      </c>
+      <c r="J162" t="n">
+        <v>1</v>
+      </c>
+      <c r="K162" t="n">
+        <v>5</v>
+      </c>
+      <c r="L162" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M162" t="n">
+        <v>50</v>
+      </c>
+      <c r="N162" t="n">
+        <v>3</v>
+      </c>
+      <c r="O162" t="n">
+        <v>24</v>
+      </c>
+      <c r="P162" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>24</v>
+      </c>
+      <c r="R162" t="n">
+        <v>15</v>
+      </c>
+      <c r="S162" t="n">
+        <v>27</v>
+      </c>
+      <c r="T162" t="n">
+        <v>27</v>
+      </c>
+      <c r="U162" t="n">
+        <v>3</v>
+      </c>
+      <c r="V162" t="n">
+        <v>24</v>
+      </c>
+      <c r="W162" t="n">
+        <v>6</v>
+      </c>
+      <c r="X162" t="n">
+        <v>13.13258643812988</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_15-26-30</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>2</v>
+      </c>
+      <c r="D163" t="n">
+        <v>1</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F163" t="n">
+        <v>2</v>
+      </c>
+      <c r="G163" t="n">
+        <v>10</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I163" t="n">
+        <v>20</v>
+      </c>
+      <c r="J163" t="n">
+        <v>1</v>
+      </c>
+      <c r="K163" t="n">
+        <v>5</v>
+      </c>
+      <c r="L163" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M163" t="n">
+        <v>50</v>
+      </c>
+      <c r="N163" t="n">
+        <v>9</v>
+      </c>
+      <c r="O163" t="n">
+        <v>13</v>
+      </c>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>24</v>
+      </c>
+      <c r="R163" t="n">
+        <v>12</v>
+      </c>
+      <c r="S163" t="n">
+        <v>14</v>
+      </c>
+      <c r="T163" t="n">
+        <v>19</v>
+      </c>
+      <c r="U163" t="n">
+        <v>19</v>
+      </c>
+      <c r="V163" t="n">
+        <v>8</v>
+      </c>
+      <c r="W163" t="n">
+        <v>0</v>
+      </c>
+      <c r="X163" t="n">
+        <v>15.37412978572048</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_15-26-30</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>3</v>
+      </c>
+      <c r="D164" t="n">
+        <v>1</v>
+      </c>
+      <c r="E164" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F164" t="n">
+        <v>2</v>
+      </c>
+      <c r="G164" t="n">
+        <v>10</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I164" t="n">
+        <v>20</v>
+      </c>
+      <c r="J164" t="n">
+        <v>1</v>
+      </c>
+      <c r="K164" t="n">
+        <v>5</v>
+      </c>
+      <c r="L164" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M164" t="n">
+        <v>50</v>
+      </c>
+      <c r="N164" t="n">
+        <v>21</v>
+      </c>
+      <c r="O164" t="n">
+        <v>7</v>
+      </c>
+      <c r="P164" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>8</v>
+      </c>
+      <c r="R164" t="n">
+        <v>7</v>
+      </c>
+      <c r="S164" t="n">
+        <v>17</v>
+      </c>
+      <c r="T164" t="n">
+        <v>19</v>
+      </c>
+      <c r="U164" t="n">
+        <v>21</v>
+      </c>
+      <c r="V164" t="n">
+        <v>24</v>
+      </c>
+      <c r="W164" t="n">
+        <v>8</v>
+      </c>
+      <c r="X164" t="n">
+        <v>14.97523281497879</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_15-26-30</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>4</v>
+      </c>
+      <c r="D165" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F165" t="n">
+        <v>2</v>
+      </c>
+      <c r="G165" t="n">
+        <v>10</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I165" t="n">
+        <v>20</v>
+      </c>
+      <c r="J165" t="n">
+        <v>1</v>
+      </c>
+      <c r="K165" t="n">
+        <v>5</v>
+      </c>
+      <c r="L165" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M165" t="n">
+        <v>50</v>
+      </c>
+      <c r="N165" t="n">
+        <v>0</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0</v>
+      </c>
+      <c r="P165" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>27</v>
+      </c>
+      <c r="R165" t="n">
+        <v>0</v>
+      </c>
+      <c r="S165" t="n">
+        <v>3</v>
+      </c>
+      <c r="T165" t="n">
+        <v>20</v>
+      </c>
+      <c r="U165" t="n">
+        <v>9</v>
+      </c>
+      <c r="V165" t="n">
+        <v>21</v>
+      </c>
+      <c r="W165" t="n">
+        <v>15</v>
+      </c>
+      <c r="X165" t="n">
+        <v>16.83970914871843</v>
+      </c>
+      <c r="Y165" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_15-26-30</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>1</v>
+      </c>
+      <c r="D166" t="n">
+        <v>2</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F166" t="n">
+        <v>2</v>
+      </c>
+      <c r="G166" t="n">
+        <v>10</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I166" t="n">
+        <v>20</v>
+      </c>
+      <c r="J166" t="n">
+        <v>1</v>
+      </c>
+      <c r="K166" t="n">
+        <v>5</v>
+      </c>
+      <c r="L166" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M166" t="n">
+        <v>50</v>
+      </c>
+      <c r="N166" t="n">
+        <v>18</v>
+      </c>
+      <c r="O166" t="n">
+        <v>30</v>
+      </c>
+      <c r="P166" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>18</v>
+      </c>
+      <c r="R166" t="n">
+        <v>6</v>
+      </c>
+      <c r="S166" t="n">
+        <v>23</v>
+      </c>
+      <c r="T166" t="n">
+        <v>13</v>
+      </c>
+      <c r="U166" t="n">
+        <v>18</v>
+      </c>
+      <c r="V166" t="n">
+        <v>18</v>
+      </c>
+      <c r="W166" t="n">
+        <v>14</v>
+      </c>
+      <c r="X166" t="n">
+        <v>12.43972139861306</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_15-26-30</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>2</v>
+      </c>
+      <c r="D167" t="n">
+        <v>2</v>
+      </c>
+      <c r="E167" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F167" t="n">
+        <v>2</v>
+      </c>
+      <c r="G167" t="n">
+        <v>10</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I167" t="n">
+        <v>20</v>
+      </c>
+      <c r="J167" t="n">
+        <v>1</v>
+      </c>
+      <c r="K167" t="n">
+        <v>5</v>
+      </c>
+      <c r="L167" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M167" t="n">
+        <v>50</v>
+      </c>
+      <c r="N167" t="n">
+        <v>25</v>
+      </c>
+      <c r="O167" t="n">
+        <v>7</v>
+      </c>
+      <c r="P167" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>19</v>
+      </c>
+      <c r="R167" t="n">
+        <v>29</v>
+      </c>
+      <c r="S167" t="n">
+        <v>12</v>
+      </c>
+      <c r="T167" t="n">
+        <v>2</v>
+      </c>
+      <c r="U167" t="n">
+        <v>7</v>
+      </c>
+      <c r="V167" t="n">
+        <v>25</v>
+      </c>
+      <c r="W167" t="n">
+        <v>1</v>
+      </c>
+      <c r="X167" t="n">
+        <v>17.06970381468504</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_15-26-30</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>3</v>
+      </c>
+      <c r="D168" t="n">
+        <v>2</v>
+      </c>
+      <c r="E168" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F168" t="n">
+        <v>2</v>
+      </c>
+      <c r="G168" t="n">
+        <v>10</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I168" t="n">
+        <v>20</v>
+      </c>
+      <c r="J168" t="n">
+        <v>1</v>
+      </c>
+      <c r="K168" t="n">
+        <v>5</v>
+      </c>
+      <c r="L168" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M168" t="n">
+        <v>50</v>
+      </c>
+      <c r="N168" t="n">
+        <v>23</v>
+      </c>
+      <c r="O168" t="n">
+        <v>8</v>
+      </c>
+      <c r="P168" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>29</v>
+      </c>
+      <c r="R168" t="n">
+        <v>29</v>
+      </c>
+      <c r="S168" t="n">
+        <v>3</v>
+      </c>
+      <c r="T168" t="n">
+        <v>29</v>
+      </c>
+      <c r="U168" t="n">
+        <v>9</v>
+      </c>
+      <c r="V168" t="n">
+        <v>10</v>
+      </c>
+      <c r="W168" t="n">
+        <v>3</v>
+      </c>
+      <c r="X168" t="n">
+        <v>14.97523281497881</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_15-26-30</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>4</v>
+      </c>
+      <c r="D169" t="n">
+        <v>2</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F169" t="n">
+        <v>2</v>
+      </c>
+      <c r="G169" t="n">
+        <v>10</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I169" t="n">
+        <v>20</v>
+      </c>
+      <c r="J169" t="n">
+        <v>1</v>
+      </c>
+      <c r="K169" t="n">
+        <v>5</v>
+      </c>
+      <c r="L169" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M169" t="n">
+        <v>50</v>
+      </c>
+      <c r="N169" t="n">
+        <v>26</v>
+      </c>
+      <c r="O169" t="n">
+        <v>5</v>
+      </c>
+      <c r="P169" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>12</v>
+      </c>
+      <c r="R169" t="n">
+        <v>26</v>
+      </c>
+      <c r="S169" t="n">
+        <v>27</v>
+      </c>
+      <c r="T169" t="n">
+        <v>6</v>
+      </c>
+      <c r="U169" t="n">
+        <v>26</v>
+      </c>
+      <c r="V169" t="n">
+        <v>6</v>
+      </c>
+      <c r="W169" t="n">
+        <v>12</v>
+      </c>
+      <c r="X169" t="n">
+        <v>11.15089396747111</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_15-26-30</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>1</v>
+      </c>
+      <c r="D170" t="n">
+        <v>3</v>
+      </c>
+      <c r="E170" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F170" t="n">
+        <v>2</v>
+      </c>
+      <c r="G170" t="n">
+        <v>10</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I170" t="n">
+        <v>20</v>
+      </c>
+      <c r="J170" t="n">
+        <v>1</v>
+      </c>
+      <c r="K170" t="n">
+        <v>5</v>
+      </c>
+      <c r="L170" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M170" t="n">
+        <v>50</v>
+      </c>
+      <c r="N170" t="n">
+        <v>20</v>
+      </c>
+      <c r="O170" t="n">
+        <v>14</v>
+      </c>
+      <c r="P170" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>20</v>
+      </c>
+      <c r="R170" t="n">
+        <v>30</v>
+      </c>
+      <c r="S170" t="n">
+        <v>5</v>
+      </c>
+      <c r="T170" t="n">
+        <v>14</v>
+      </c>
+      <c r="U170" t="n">
+        <v>20</v>
+      </c>
+      <c r="V170" t="n">
+        <v>20</v>
+      </c>
+      <c r="W170" t="n">
+        <v>5</v>
+      </c>
+      <c r="X170" t="n">
+        <v>10.7519969967297</v>
+      </c>
+      <c r="Y170" t="n">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y170"/>
+  <dimension ref="A1:Y177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -13151,6 +13151,573 @@
         <v>19</v>
       </c>
     </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_15-26-30</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>2</v>
+      </c>
+      <c r="D171" t="n">
+        <v>3</v>
+      </c>
+      <c r="E171" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F171" t="n">
+        <v>2</v>
+      </c>
+      <c r="G171" t="n">
+        <v>10</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I171" t="n">
+        <v>20</v>
+      </c>
+      <c r="J171" t="n">
+        <v>1</v>
+      </c>
+      <c r="K171" t="n">
+        <v>5</v>
+      </c>
+      <c r="L171" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M171" t="n">
+        <v>50</v>
+      </c>
+      <c r="N171" t="n">
+        <v>2</v>
+      </c>
+      <c r="O171" t="n">
+        <v>6</v>
+      </c>
+      <c r="P171" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>3</v>
+      </c>
+      <c r="R171" t="n">
+        <v>2</v>
+      </c>
+      <c r="S171" t="n">
+        <v>13</v>
+      </c>
+      <c r="T171" t="n">
+        <v>3</v>
+      </c>
+      <c r="U171" t="n">
+        <v>2</v>
+      </c>
+      <c r="V171" t="n">
+        <v>6</v>
+      </c>
+      <c r="W171" t="n">
+        <v>2</v>
+      </c>
+      <c r="X171" t="n">
+        <v>8.615382551105476</v>
+      </c>
+      <c r="Y171" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_15-26-30</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>3</v>
+      </c>
+      <c r="D172" t="n">
+        <v>3</v>
+      </c>
+      <c r="E172" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F172" t="n">
+        <v>2</v>
+      </c>
+      <c r="G172" t="n">
+        <v>10</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I172" t="n">
+        <v>20</v>
+      </c>
+      <c r="J172" t="n">
+        <v>1</v>
+      </c>
+      <c r="K172" t="n">
+        <v>5</v>
+      </c>
+      <c r="L172" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M172" t="n">
+        <v>50</v>
+      </c>
+      <c r="N172" t="n">
+        <v>21</v>
+      </c>
+      <c r="O172" t="n">
+        <v>0</v>
+      </c>
+      <c r="P172" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>21</v>
+      </c>
+      <c r="R172" t="n">
+        <v>3</v>
+      </c>
+      <c r="S172" t="n">
+        <v>5</v>
+      </c>
+      <c r="T172" t="n">
+        <v>8</v>
+      </c>
+      <c r="U172" t="n">
+        <v>3</v>
+      </c>
+      <c r="V172" t="n">
+        <v>0</v>
+      </c>
+      <c r="W172" t="n">
+        <v>29</v>
+      </c>
+      <c r="X172" t="n">
+        <v>10.75199699672964</v>
+      </c>
+      <c r="Y172" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_15-26-30</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>4</v>
+      </c>
+      <c r="D173" t="n">
+        <v>3</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F173" t="n">
+        <v>2</v>
+      </c>
+      <c r="G173" t="n">
+        <v>10</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I173" t="n">
+        <v>20</v>
+      </c>
+      <c r="J173" t="n">
+        <v>1</v>
+      </c>
+      <c r="K173" t="n">
+        <v>5</v>
+      </c>
+      <c r="L173" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M173" t="n">
+        <v>50</v>
+      </c>
+      <c r="N173" t="n">
+        <v>0</v>
+      </c>
+      <c r="O173" t="n">
+        <v>17</v>
+      </c>
+      <c r="P173" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>16</v>
+      </c>
+      <c r="R173" t="n">
+        <v>1</v>
+      </c>
+      <c r="S173" t="n">
+        <v>17</v>
+      </c>
+      <c r="T173" t="n">
+        <v>29</v>
+      </c>
+      <c r="U173" t="n">
+        <v>0</v>
+      </c>
+      <c r="V173" t="n">
+        <v>29</v>
+      </c>
+      <c r="W173" t="n">
+        <v>17</v>
+      </c>
+      <c r="X173" t="n">
+        <v>12.45182992483245</v>
+      </c>
+      <c r="Y173" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_15-26-30</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>1</v>
+      </c>
+      <c r="D174" t="n">
+        <v>4</v>
+      </c>
+      <c r="E174" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F174" t="n">
+        <v>2</v>
+      </c>
+      <c r="G174" t="n">
+        <v>10</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I174" t="n">
+        <v>20</v>
+      </c>
+      <c r="J174" t="n">
+        <v>1</v>
+      </c>
+      <c r="K174" t="n">
+        <v>5</v>
+      </c>
+      <c r="L174" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M174" t="n">
+        <v>50</v>
+      </c>
+      <c r="N174" t="n">
+        <v>26</v>
+      </c>
+      <c r="O174" t="n">
+        <v>1</v>
+      </c>
+      <c r="P174" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>8</v>
+      </c>
+      <c r="R174" t="n">
+        <v>0</v>
+      </c>
+      <c r="S174" t="n">
+        <v>22</v>
+      </c>
+      <c r="T174" t="n">
+        <v>3</v>
+      </c>
+      <c r="U174" t="n">
+        <v>28</v>
+      </c>
+      <c r="V174" t="n">
+        <v>27</v>
+      </c>
+      <c r="W174" t="n">
+        <v>22</v>
+      </c>
+      <c r="X174" t="n">
+        <v>14.42309882366953</v>
+      </c>
+      <c r="Y174" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_15-26-30</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>2</v>
+      </c>
+      <c r="D175" t="n">
+        <v>4</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F175" t="n">
+        <v>2</v>
+      </c>
+      <c r="G175" t="n">
+        <v>10</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I175" t="n">
+        <v>20</v>
+      </c>
+      <c r="J175" t="n">
+        <v>1</v>
+      </c>
+      <c r="K175" t="n">
+        <v>5</v>
+      </c>
+      <c r="L175" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M175" t="n">
+        <v>50</v>
+      </c>
+      <c r="N175" t="n">
+        <v>10</v>
+      </c>
+      <c r="O175" t="n">
+        <v>5</v>
+      </c>
+      <c r="P175" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>10</v>
+      </c>
+      <c r="R175" t="n">
+        <v>15</v>
+      </c>
+      <c r="S175" t="n">
+        <v>1</v>
+      </c>
+      <c r="T175" t="n">
+        <v>10</v>
+      </c>
+      <c r="U175" t="n">
+        <v>25</v>
+      </c>
+      <c r="V175" t="n">
+        <v>29</v>
+      </c>
+      <c r="W175" t="n">
+        <v>15</v>
+      </c>
+      <c r="X175" t="n">
+        <v>12.56477855278127</v>
+      </c>
+      <c r="Y175" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_15-26-30</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>3</v>
+      </c>
+      <c r="D176" t="n">
+        <v>4</v>
+      </c>
+      <c r="E176" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F176" t="n">
+        <v>2</v>
+      </c>
+      <c r="G176" t="n">
+        <v>10</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I176" t="n">
+        <v>20</v>
+      </c>
+      <c r="J176" t="n">
+        <v>1</v>
+      </c>
+      <c r="K176" t="n">
+        <v>5</v>
+      </c>
+      <c r="L176" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M176" t="n">
+        <v>50</v>
+      </c>
+      <c r="N176" t="n">
+        <v>31</v>
+      </c>
+      <c r="O176" t="n">
+        <v>6</v>
+      </c>
+      <c r="P176" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>16</v>
+      </c>
+      <c r="R176" t="n">
+        <v>16</v>
+      </c>
+      <c r="S176" t="n">
+        <v>0</v>
+      </c>
+      <c r="T176" t="n">
+        <v>5</v>
+      </c>
+      <c r="U176" t="n">
+        <v>4</v>
+      </c>
+      <c r="V176" t="n">
+        <v>6</v>
+      </c>
+      <c r="W176" t="n">
+        <v>27</v>
+      </c>
+      <c r="X176" t="n">
+        <v>10.87708160122025</v>
+      </c>
+      <c r="Y176" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_15-26-30</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>4</v>
+      </c>
+      <c r="D177" t="n">
+        <v>4</v>
+      </c>
+      <c r="E177" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F177" t="n">
+        <v>2</v>
+      </c>
+      <c r="G177" t="n">
+        <v>10</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I177" t="n">
+        <v>20</v>
+      </c>
+      <c r="J177" t="n">
+        <v>1</v>
+      </c>
+      <c r="K177" t="n">
+        <v>5</v>
+      </c>
+      <c r="L177" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M177" t="n">
+        <v>50</v>
+      </c>
+      <c r="N177" t="n">
+        <v>31</v>
+      </c>
+      <c r="O177" t="n">
+        <v>12</v>
+      </c>
+      <c r="P177" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>24</v>
+      </c>
+      <c r="R177" t="n">
+        <v>31</v>
+      </c>
+      <c r="S177" t="n">
+        <v>24</v>
+      </c>
+      <c r="T177" t="n">
+        <v>12</v>
+      </c>
+      <c r="U177" t="n">
+        <v>31</v>
+      </c>
+      <c r="V177" t="n">
+        <v>1</v>
+      </c>
+      <c r="W177" t="n">
+        <v>5</v>
+      </c>
+      <c r="X177" t="n">
+        <v>9.463169565587837</v>
+      </c>
+      <c r="Y177" t="n">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y177"/>
+  <dimension ref="A1:Y187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -13718,6 +13718,816 @@
         <v>19</v>
       </c>
     </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_18-17-56</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>1</v>
+      </c>
+      <c r="D178" t="n">
+        <v>1</v>
+      </c>
+      <c r="E178" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F178" t="n">
+        <v>2</v>
+      </c>
+      <c r="G178" t="n">
+        <v>10</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I178" t="n">
+        <v>20</v>
+      </c>
+      <c r="J178" t="n">
+        <v>1</v>
+      </c>
+      <c r="K178" t="n">
+        <v>5</v>
+      </c>
+      <c r="L178" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M178" t="n">
+        <v>50</v>
+      </c>
+      <c r="N178" t="n">
+        <v>22</v>
+      </c>
+      <c r="O178" t="n">
+        <v>26</v>
+      </c>
+      <c r="P178" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>5</v>
+      </c>
+      <c r="R178" t="n">
+        <v>29</v>
+      </c>
+      <c r="S178" t="n">
+        <v>1</v>
+      </c>
+      <c r="T178" t="n">
+        <v>22</v>
+      </c>
+      <c r="U178" t="n">
+        <v>28</v>
+      </c>
+      <c r="V178" t="n">
+        <v>29</v>
+      </c>
+      <c r="W178" t="n">
+        <v>16</v>
+      </c>
+      <c r="X178" t="n">
+        <v>14.70309470309421</v>
+      </c>
+      <c r="Y178" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_18-17-56</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>2</v>
+      </c>
+      <c r="D179" t="n">
+        <v>1</v>
+      </c>
+      <c r="E179" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F179" t="n">
+        <v>2</v>
+      </c>
+      <c r="G179" t="n">
+        <v>10</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I179" t="n">
+        <v>20</v>
+      </c>
+      <c r="J179" t="n">
+        <v>1</v>
+      </c>
+      <c r="K179" t="n">
+        <v>5</v>
+      </c>
+      <c r="L179" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M179" t="n">
+        <v>50</v>
+      </c>
+      <c r="N179" t="n">
+        <v>17</v>
+      </c>
+      <c r="O179" t="n">
+        <v>16</v>
+      </c>
+      <c r="P179" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>17</v>
+      </c>
+      <c r="R179" t="n">
+        <v>7</v>
+      </c>
+      <c r="S179" t="n">
+        <v>14</v>
+      </c>
+      <c r="T179" t="n">
+        <v>3</v>
+      </c>
+      <c r="U179" t="n">
+        <v>17</v>
+      </c>
+      <c r="V179" t="n">
+        <v>2</v>
+      </c>
+      <c r="W179" t="n">
+        <v>3</v>
+      </c>
+      <c r="X179" t="n">
+        <v>16.26406024612064</v>
+      </c>
+      <c r="Y179" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_18-17-56</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>3</v>
+      </c>
+      <c r="D180" t="n">
+        <v>1</v>
+      </c>
+      <c r="E180" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F180" t="n">
+        <v>2</v>
+      </c>
+      <c r="G180" t="n">
+        <v>10</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I180" t="n">
+        <v>20</v>
+      </c>
+      <c r="J180" t="n">
+        <v>1</v>
+      </c>
+      <c r="K180" t="n">
+        <v>5</v>
+      </c>
+      <c r="L180" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M180" t="n">
+        <v>50</v>
+      </c>
+      <c r="N180" t="n">
+        <v>4</v>
+      </c>
+      <c r="O180" t="n">
+        <v>4</v>
+      </c>
+      <c r="P180" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>5</v>
+      </c>
+      <c r="R180" t="n">
+        <v>4</v>
+      </c>
+      <c r="S180" t="n">
+        <v>19</v>
+      </c>
+      <c r="T180" t="n">
+        <v>2</v>
+      </c>
+      <c r="U180" t="n">
+        <v>2</v>
+      </c>
+      <c r="V180" t="n">
+        <v>18</v>
+      </c>
+      <c r="W180" t="n">
+        <v>1</v>
+      </c>
+      <c r="X180" t="n">
+        <v>15.82301982946126</v>
+      </c>
+      <c r="Y180" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_18-17-56</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>4</v>
+      </c>
+      <c r="D181" t="n">
+        <v>1</v>
+      </c>
+      <c r="E181" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F181" t="n">
+        <v>2</v>
+      </c>
+      <c r="G181" t="n">
+        <v>10</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I181" t="n">
+        <v>20</v>
+      </c>
+      <c r="J181" t="n">
+        <v>1</v>
+      </c>
+      <c r="K181" t="n">
+        <v>5</v>
+      </c>
+      <c r="L181" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M181" t="n">
+        <v>50</v>
+      </c>
+      <c r="N181" t="n">
+        <v>0</v>
+      </c>
+      <c r="O181" t="n">
+        <v>25</v>
+      </c>
+      <c r="P181" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>10</v>
+      </c>
+      <c r="R181" t="n">
+        <v>12</v>
+      </c>
+      <c r="S181" t="n">
+        <v>24</v>
+      </c>
+      <c r="T181" t="n">
+        <v>12</v>
+      </c>
+      <c r="U181" t="n">
+        <v>10</v>
+      </c>
+      <c r="V181" t="n">
+        <v>5</v>
+      </c>
+      <c r="W181" t="n">
+        <v>0</v>
+      </c>
+      <c r="X181" t="n">
+        <v>16.23546410377331</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_18-17-56</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>1</v>
+      </c>
+      <c r="D182" t="n">
+        <v>2</v>
+      </c>
+      <c r="E182" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F182" t="n">
+        <v>2</v>
+      </c>
+      <c r="G182" t="n">
+        <v>10</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I182" t="n">
+        <v>20</v>
+      </c>
+      <c r="J182" t="n">
+        <v>1</v>
+      </c>
+      <c r="K182" t="n">
+        <v>5</v>
+      </c>
+      <c r="L182" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M182" t="n">
+        <v>50</v>
+      </c>
+      <c r="N182" t="n">
+        <v>16</v>
+      </c>
+      <c r="O182" t="n">
+        <v>14</v>
+      </c>
+      <c r="P182" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>26</v>
+      </c>
+      <c r="R182" t="n">
+        <v>25</v>
+      </c>
+      <c r="S182" t="n">
+        <v>22</v>
+      </c>
+      <c r="T182" t="n">
+        <v>19</v>
+      </c>
+      <c r="U182" t="n">
+        <v>25</v>
+      </c>
+      <c r="V182" t="n">
+        <v>11</v>
+      </c>
+      <c r="W182" t="n">
+        <v>2</v>
+      </c>
+      <c r="X182" t="n">
+        <v>14.97523281497877</v>
+      </c>
+      <c r="Y182" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_18-17-56</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>2</v>
+      </c>
+      <c r="D183" t="n">
+        <v>2</v>
+      </c>
+      <c r="E183" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F183" t="n">
+        <v>2</v>
+      </c>
+      <c r="G183" t="n">
+        <v>10</v>
+      </c>
+      <c r="H183" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I183" t="n">
+        <v>20</v>
+      </c>
+      <c r="J183" t="n">
+        <v>1</v>
+      </c>
+      <c r="K183" t="n">
+        <v>5</v>
+      </c>
+      <c r="L183" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M183" t="n">
+        <v>50</v>
+      </c>
+      <c r="N183" t="n">
+        <v>2</v>
+      </c>
+      <c r="O183" t="n">
+        <v>27</v>
+      </c>
+      <c r="P183" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>14</v>
+      </c>
+      <c r="R183" t="n">
+        <v>25</v>
+      </c>
+      <c r="S183" t="n">
+        <v>10</v>
+      </c>
+      <c r="T183" t="n">
+        <v>0</v>
+      </c>
+      <c r="U183" t="n">
+        <v>8</v>
+      </c>
+      <c r="V183" t="n">
+        <v>3</v>
+      </c>
+      <c r="W183" t="n">
+        <v>0</v>
+      </c>
+      <c r="X183" t="n">
+        <v>15.66195854193517</v>
+      </c>
+      <c r="Y183" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_18-17-56</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>3</v>
+      </c>
+      <c r="D184" t="n">
+        <v>2</v>
+      </c>
+      <c r="E184" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F184" t="n">
+        <v>2</v>
+      </c>
+      <c r="G184" t="n">
+        <v>10</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I184" t="n">
+        <v>20</v>
+      </c>
+      <c r="J184" t="n">
+        <v>1</v>
+      </c>
+      <c r="K184" t="n">
+        <v>5</v>
+      </c>
+      <c r="L184" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M184" t="n">
+        <v>50</v>
+      </c>
+      <c r="N184" t="n">
+        <v>27</v>
+      </c>
+      <c r="O184" t="n">
+        <v>0</v>
+      </c>
+      <c r="P184" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>9</v>
+      </c>
+      <c r="R184" t="n">
+        <v>27</v>
+      </c>
+      <c r="S184" t="n">
+        <v>14</v>
+      </c>
+      <c r="T184" t="n">
+        <v>9</v>
+      </c>
+      <c r="U184" t="n">
+        <v>5</v>
+      </c>
+      <c r="V184" t="n">
+        <v>14</v>
+      </c>
+      <c r="W184" t="n">
+        <v>11</v>
+      </c>
+      <c r="X184" t="n">
+        <v>12.83861836935484</v>
+      </c>
+      <c r="Y184" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_18-17-56</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>4</v>
+      </c>
+      <c r="D185" t="n">
+        <v>2</v>
+      </c>
+      <c r="E185" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F185" t="n">
+        <v>2</v>
+      </c>
+      <c r="G185" t="n">
+        <v>10</v>
+      </c>
+      <c r="H185" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I185" t="n">
+        <v>20</v>
+      </c>
+      <c r="J185" t="n">
+        <v>1</v>
+      </c>
+      <c r="K185" t="n">
+        <v>5</v>
+      </c>
+      <c r="L185" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M185" t="n">
+        <v>50</v>
+      </c>
+      <c r="N185" t="n">
+        <v>14</v>
+      </c>
+      <c r="O185" t="n">
+        <v>15</v>
+      </c>
+      <c r="P185" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>12</v>
+      </c>
+      <c r="R185" t="n">
+        <v>8</v>
+      </c>
+      <c r="S185" t="n">
+        <v>12</v>
+      </c>
+      <c r="T185" t="n">
+        <v>15</v>
+      </c>
+      <c r="U185" t="n">
+        <v>6</v>
+      </c>
+      <c r="V185" t="n">
+        <v>26</v>
+      </c>
+      <c r="W185" t="n">
+        <v>12</v>
+      </c>
+      <c r="X185" t="n">
+        <v>13.96638451297058</v>
+      </c>
+      <c r="Y185" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_18-17-56</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>1</v>
+      </c>
+      <c r="D186" t="n">
+        <v>3</v>
+      </c>
+      <c r="E186" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F186" t="n">
+        <v>2</v>
+      </c>
+      <c r="G186" t="n">
+        <v>10</v>
+      </c>
+      <c r="H186" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I186" t="n">
+        <v>20</v>
+      </c>
+      <c r="J186" t="n">
+        <v>1</v>
+      </c>
+      <c r="K186" t="n">
+        <v>5</v>
+      </c>
+      <c r="L186" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M186" t="n">
+        <v>50</v>
+      </c>
+      <c r="N186" t="n">
+        <v>4</v>
+      </c>
+      <c r="O186" t="n">
+        <v>29</v>
+      </c>
+      <c r="P186" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>19</v>
+      </c>
+      <c r="R186" t="n">
+        <v>4</v>
+      </c>
+      <c r="S186" t="n">
+        <v>31</v>
+      </c>
+      <c r="T186" t="n">
+        <v>30</v>
+      </c>
+      <c r="U186" t="n">
+        <v>29</v>
+      </c>
+      <c r="V186" t="n">
+        <v>9</v>
+      </c>
+      <c r="W186" t="n">
+        <v>0</v>
+      </c>
+      <c r="X186" t="n">
+        <v>12.27866011108733</v>
+      </c>
+      <c r="Y186" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_18-17-56</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>2</v>
+      </c>
+      <c r="D187" t="n">
+        <v>3</v>
+      </c>
+      <c r="E187" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F187" t="n">
+        <v>2</v>
+      </c>
+      <c r="G187" t="n">
+        <v>10</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I187" t="n">
+        <v>20</v>
+      </c>
+      <c r="J187" t="n">
+        <v>1</v>
+      </c>
+      <c r="K187" t="n">
+        <v>5</v>
+      </c>
+      <c r="L187" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M187" t="n">
+        <v>50</v>
+      </c>
+      <c r="N187" t="n">
+        <v>30</v>
+      </c>
+      <c r="O187" t="n">
+        <v>11</v>
+      </c>
+      <c r="P187" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>11</v>
+      </c>
+      <c r="R187" t="n">
+        <v>30</v>
+      </c>
+      <c r="S187" t="n">
+        <v>0</v>
+      </c>
+      <c r="T187" t="n">
+        <v>30</v>
+      </c>
+      <c r="U187" t="n">
+        <v>11</v>
+      </c>
+      <c r="V187" t="n">
+        <v>23</v>
+      </c>
+      <c r="W187" t="n">
+        <v>12</v>
+      </c>
+      <c r="X187" t="n">
+        <v>11.59193438413067</v>
+      </c>
+      <c r="Y187" t="n">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y187"/>
+  <dimension ref="A1:Y193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -14528,6 +14528,492 @@
         <v>19</v>
       </c>
     </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_18-17-56</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>3</v>
+      </c>
+      <c r="D188" t="n">
+        <v>3</v>
+      </c>
+      <c r="E188" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F188" t="n">
+        <v>2</v>
+      </c>
+      <c r="G188" t="n">
+        <v>10</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I188" t="n">
+        <v>20</v>
+      </c>
+      <c r="J188" t="n">
+        <v>1</v>
+      </c>
+      <c r="K188" t="n">
+        <v>5</v>
+      </c>
+      <c r="L188" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M188" t="n">
+        <v>50</v>
+      </c>
+      <c r="N188" t="n">
+        <v>28</v>
+      </c>
+      <c r="O188" t="n">
+        <v>18</v>
+      </c>
+      <c r="P188" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>7</v>
+      </c>
+      <c r="R188" t="n">
+        <v>17</v>
+      </c>
+      <c r="S188" t="n">
+        <v>4</v>
+      </c>
+      <c r="T188" t="n">
+        <v>2</v>
+      </c>
+      <c r="U188" t="n">
+        <v>2</v>
+      </c>
+      <c r="V188" t="n">
+        <v>18</v>
+      </c>
+      <c r="W188" t="n">
+        <v>2</v>
+      </c>
+      <c r="X188" t="n">
+        <v>10.88461081933012</v>
+      </c>
+      <c r="Y188" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_18-17-56</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>4</v>
+      </c>
+      <c r="D189" t="n">
+        <v>3</v>
+      </c>
+      <c r="E189" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F189" t="n">
+        <v>2</v>
+      </c>
+      <c r="G189" t="n">
+        <v>10</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I189" t="n">
+        <v>20</v>
+      </c>
+      <c r="J189" t="n">
+        <v>1</v>
+      </c>
+      <c r="K189" t="n">
+        <v>5</v>
+      </c>
+      <c r="L189" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M189" t="n">
+        <v>50</v>
+      </c>
+      <c r="N189" t="n">
+        <v>3</v>
+      </c>
+      <c r="O189" t="n">
+        <v>5</v>
+      </c>
+      <c r="P189" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>1</v>
+      </c>
+      <c r="R189" t="n">
+        <v>9</v>
+      </c>
+      <c r="S189" t="n">
+        <v>3</v>
+      </c>
+      <c r="T189" t="n">
+        <v>5</v>
+      </c>
+      <c r="U189" t="n">
+        <v>1</v>
+      </c>
+      <c r="V189" t="n">
+        <v>19</v>
+      </c>
+      <c r="W189" t="n">
+        <v>28</v>
+      </c>
+      <c r="X189" t="n">
+        <v>10.87091483833749</v>
+      </c>
+      <c r="Y189" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_18-17-56</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>1</v>
+      </c>
+      <c r="D190" t="n">
+        <v>4</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F190" t="n">
+        <v>2</v>
+      </c>
+      <c r="G190" t="n">
+        <v>10</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I190" t="n">
+        <v>20</v>
+      </c>
+      <c r="J190" t="n">
+        <v>1</v>
+      </c>
+      <c r="K190" t="n">
+        <v>5</v>
+      </c>
+      <c r="L190" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M190" t="n">
+        <v>50</v>
+      </c>
+      <c r="N190" t="n">
+        <v>19</v>
+      </c>
+      <c r="O190" t="n">
+        <v>12</v>
+      </c>
+      <c r="P190" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>2</v>
+      </c>
+      <c r="R190" t="n">
+        <v>30</v>
+      </c>
+      <c r="S190" t="n">
+        <v>26</v>
+      </c>
+      <c r="T190" t="n">
+        <v>10</v>
+      </c>
+      <c r="U190" t="n">
+        <v>11</v>
+      </c>
+      <c r="V190" t="n">
+        <v>10</v>
+      </c>
+      <c r="W190" t="n">
+        <v>26</v>
+      </c>
+      <c r="X190" t="n">
+        <v>11.71085222573857</v>
+      </c>
+      <c r="Y190" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_18-17-56</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>2</v>
+      </c>
+      <c r="D191" t="n">
+        <v>4</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F191" t="n">
+        <v>2</v>
+      </c>
+      <c r="G191" t="n">
+        <v>10</v>
+      </c>
+      <c r="H191" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I191" t="n">
+        <v>20</v>
+      </c>
+      <c r="J191" t="n">
+        <v>1</v>
+      </c>
+      <c r="K191" t="n">
+        <v>5</v>
+      </c>
+      <c r="L191" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M191" t="n">
+        <v>50</v>
+      </c>
+      <c r="N191" t="n">
+        <v>0</v>
+      </c>
+      <c r="O191" t="n">
+        <v>11</v>
+      </c>
+      <c r="P191" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>24</v>
+      </c>
+      <c r="R191" t="n">
+        <v>7</v>
+      </c>
+      <c r="S191" t="n">
+        <v>0</v>
+      </c>
+      <c r="T191" t="n">
+        <v>11</v>
+      </c>
+      <c r="U191" t="n">
+        <v>6</v>
+      </c>
+      <c r="V191" t="n">
+        <v>7</v>
+      </c>
+      <c r="W191" t="n">
+        <v>31</v>
+      </c>
+      <c r="X191" t="n">
+        <v>13.40642625470339</v>
+      </c>
+      <c r="Y191" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_18-17-56</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>3</v>
+      </c>
+      <c r="D192" t="n">
+        <v>4</v>
+      </c>
+      <c r="E192" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F192" t="n">
+        <v>2</v>
+      </c>
+      <c r="G192" t="n">
+        <v>10</v>
+      </c>
+      <c r="H192" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I192" t="n">
+        <v>20</v>
+      </c>
+      <c r="J192" t="n">
+        <v>1</v>
+      </c>
+      <c r="K192" t="n">
+        <v>5</v>
+      </c>
+      <c r="L192" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M192" t="n">
+        <v>50</v>
+      </c>
+      <c r="N192" t="n">
+        <v>2</v>
+      </c>
+      <c r="O192" t="n">
+        <v>0</v>
+      </c>
+      <c r="P192" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>15</v>
+      </c>
+      <c r="R192" t="n">
+        <v>28</v>
+      </c>
+      <c r="S192" t="n">
+        <v>4</v>
+      </c>
+      <c r="T192" t="n">
+        <v>0</v>
+      </c>
+      <c r="U192" t="n">
+        <v>26</v>
+      </c>
+      <c r="V192" t="n">
+        <v>2</v>
+      </c>
+      <c r="W192" t="n">
+        <v>28</v>
+      </c>
+      <c r="X192" t="n">
+        <v>11.99868098195354</v>
+      </c>
+      <c r="Y192" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_18-17-56</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>4</v>
+      </c>
+      <c r="D193" t="n">
+        <v>4</v>
+      </c>
+      <c r="E193" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F193" t="n">
+        <v>2</v>
+      </c>
+      <c r="G193" t="n">
+        <v>10</v>
+      </c>
+      <c r="H193" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I193" t="n">
+        <v>20</v>
+      </c>
+      <c r="J193" t="n">
+        <v>1</v>
+      </c>
+      <c r="K193" t="n">
+        <v>5</v>
+      </c>
+      <c r="L193" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M193" t="n">
+        <v>50</v>
+      </c>
+      <c r="N193" t="n">
+        <v>22</v>
+      </c>
+      <c r="O193" t="n">
+        <v>31</v>
+      </c>
+      <c r="P193" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>9</v>
+      </c>
+      <c r="R193" t="n">
+        <v>22</v>
+      </c>
+      <c r="S193" t="n">
+        <v>2</v>
+      </c>
+      <c r="T193" t="n">
+        <v>24</v>
+      </c>
+      <c r="U193" t="n">
+        <v>24</v>
+      </c>
+      <c r="V193" t="n">
+        <v>25</v>
+      </c>
+      <c r="W193" t="n">
+        <v>25</v>
+      </c>
+      <c r="X193" t="n">
+        <v>11.60609819167245</v>
+      </c>
+      <c r="Y193" t="n">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y193"/>
+  <dimension ref="A1:Y209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -15014,6 +15014,1302 @@
         <v>19</v>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_20-05-44</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>1</v>
+      </c>
+      <c r="D194" t="n">
+        <v>1</v>
+      </c>
+      <c r="E194" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F194" t="n">
+        <v>2</v>
+      </c>
+      <c r="G194" t="n">
+        <v>10</v>
+      </c>
+      <c r="H194" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I194" t="n">
+        <v>20</v>
+      </c>
+      <c r="J194" t="n">
+        <v>1</v>
+      </c>
+      <c r="K194" t="n">
+        <v>5</v>
+      </c>
+      <c r="L194" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M194" t="n">
+        <v>50</v>
+      </c>
+      <c r="N194" t="n">
+        <v>14</v>
+      </c>
+      <c r="O194" t="n">
+        <v>29</v>
+      </c>
+      <c r="P194" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>10</v>
+      </c>
+      <c r="R194" t="n">
+        <v>0</v>
+      </c>
+      <c r="S194" t="n">
+        <v>7</v>
+      </c>
+      <c r="T194" t="n">
+        <v>17</v>
+      </c>
+      <c r="U194" t="n">
+        <v>14</v>
+      </c>
+      <c r="V194" t="n">
+        <v>1</v>
+      </c>
+      <c r="W194" t="n">
+        <v>0</v>
+      </c>
+      <c r="X194" t="n">
+        <v>17.7907233604782</v>
+      </c>
+      <c r="Y194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_20-05-44</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>2</v>
+      </c>
+      <c r="D195" t="n">
+        <v>1</v>
+      </c>
+      <c r="E195" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F195" t="n">
+        <v>2</v>
+      </c>
+      <c r="G195" t="n">
+        <v>10</v>
+      </c>
+      <c r="H195" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I195" t="n">
+        <v>20</v>
+      </c>
+      <c r="J195" t="n">
+        <v>1</v>
+      </c>
+      <c r="K195" t="n">
+        <v>5</v>
+      </c>
+      <c r="L195" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M195" t="n">
+        <v>50</v>
+      </c>
+      <c r="N195" t="n">
+        <v>0</v>
+      </c>
+      <c r="O195" t="n">
+        <v>0</v>
+      </c>
+      <c r="P195" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q195" t="n">
+        <v>8</v>
+      </c>
+      <c r="R195" t="n">
+        <v>29</v>
+      </c>
+      <c r="S195" t="n">
+        <v>10</v>
+      </c>
+      <c r="T195" t="n">
+        <v>31</v>
+      </c>
+      <c r="U195" t="n">
+        <v>30</v>
+      </c>
+      <c r="V195" t="n">
+        <v>30</v>
+      </c>
+      <c r="W195" t="n">
+        <v>6</v>
+      </c>
+      <c r="X195" t="n">
+        <v>14.81417152745315</v>
+      </c>
+      <c r="Y195" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_20-05-44</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>3</v>
+      </c>
+      <c r="D196" t="n">
+        <v>1</v>
+      </c>
+      <c r="E196" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F196" t="n">
+        <v>2</v>
+      </c>
+      <c r="G196" t="n">
+        <v>10</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I196" t="n">
+        <v>20</v>
+      </c>
+      <c r="J196" t="n">
+        <v>1</v>
+      </c>
+      <c r="K196" t="n">
+        <v>5</v>
+      </c>
+      <c r="L196" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M196" t="n">
+        <v>50</v>
+      </c>
+      <c r="N196" t="n">
+        <v>17</v>
+      </c>
+      <c r="O196" t="n">
+        <v>19</v>
+      </c>
+      <c r="P196" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>28</v>
+      </c>
+      <c r="R196" t="n">
+        <v>19</v>
+      </c>
+      <c r="S196" t="n">
+        <v>19</v>
+      </c>
+      <c r="T196" t="n">
+        <v>25</v>
+      </c>
+      <c r="U196" t="n">
+        <v>22</v>
+      </c>
+      <c r="V196" t="n">
+        <v>30</v>
+      </c>
+      <c r="W196" t="n">
+        <v>0</v>
+      </c>
+      <c r="X196" t="n">
+        <v>17.13134665405862</v>
+      </c>
+      <c r="Y196" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_20-05-44</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>4</v>
+      </c>
+      <c r="D197" t="n">
+        <v>1</v>
+      </c>
+      <c r="E197" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F197" t="n">
+        <v>2</v>
+      </c>
+      <c r="G197" t="n">
+        <v>10</v>
+      </c>
+      <c r="H197" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I197" t="n">
+        <v>20</v>
+      </c>
+      <c r="J197" t="n">
+        <v>1</v>
+      </c>
+      <c r="K197" t="n">
+        <v>5</v>
+      </c>
+      <c r="L197" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M197" t="n">
+        <v>50</v>
+      </c>
+      <c r="N197" t="n">
+        <v>23</v>
+      </c>
+      <c r="O197" t="n">
+        <v>24</v>
+      </c>
+      <c r="P197" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q197" t="n">
+        <v>28</v>
+      </c>
+      <c r="R197" t="n">
+        <v>24</v>
+      </c>
+      <c r="S197" t="n">
+        <v>24</v>
+      </c>
+      <c r="T197" t="n">
+        <v>12</v>
+      </c>
+      <c r="U197" t="n">
+        <v>30</v>
+      </c>
+      <c r="V197" t="n">
+        <v>10</v>
+      </c>
+      <c r="W197" t="n">
+        <v>6</v>
+      </c>
+      <c r="X197" t="n">
+        <v>16.10299895859482</v>
+      </c>
+      <c r="Y197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_20-05-44</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>1</v>
+      </c>
+      <c r="D198" t="n">
+        <v>2</v>
+      </c>
+      <c r="E198" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F198" t="n">
+        <v>2</v>
+      </c>
+      <c r="G198" t="n">
+        <v>10</v>
+      </c>
+      <c r="H198" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I198" t="n">
+        <v>20</v>
+      </c>
+      <c r="J198" t="n">
+        <v>1</v>
+      </c>
+      <c r="K198" t="n">
+        <v>5</v>
+      </c>
+      <c r="L198" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M198" t="n">
+        <v>50</v>
+      </c>
+      <c r="N198" t="n">
+        <v>25</v>
+      </c>
+      <c r="O198" t="n">
+        <v>4</v>
+      </c>
+      <c r="P198" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q198" t="n">
+        <v>27</v>
+      </c>
+      <c r="R198" t="n">
+        <v>6</v>
+      </c>
+      <c r="S198" t="n">
+        <v>15</v>
+      </c>
+      <c r="T198" t="n">
+        <v>15</v>
+      </c>
+      <c r="U198" t="n">
+        <v>14</v>
+      </c>
+      <c r="V198" t="n">
+        <v>4</v>
+      </c>
+      <c r="W198" t="n">
+        <v>2</v>
+      </c>
+      <c r="X198" t="n">
+        <v>14.81417152745308</v>
+      </c>
+      <c r="Y198" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_20-05-44</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>2</v>
+      </c>
+      <c r="D199" t="n">
+        <v>2</v>
+      </c>
+      <c r="E199" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F199" t="n">
+        <v>2</v>
+      </c>
+      <c r="G199" t="n">
+        <v>10</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I199" t="n">
+        <v>20</v>
+      </c>
+      <c r="J199" t="n">
+        <v>1</v>
+      </c>
+      <c r="K199" t="n">
+        <v>5</v>
+      </c>
+      <c r="L199" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M199" t="n">
+        <v>50</v>
+      </c>
+      <c r="N199" t="n">
+        <v>6</v>
+      </c>
+      <c r="O199" t="n">
+        <v>12</v>
+      </c>
+      <c r="P199" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>3</v>
+      </c>
+      <c r="R199" t="n">
+        <v>31</v>
+      </c>
+      <c r="S199" t="n">
+        <v>31</v>
+      </c>
+      <c r="T199" t="n">
+        <v>19</v>
+      </c>
+      <c r="U199" t="n">
+        <v>11</v>
+      </c>
+      <c r="V199" t="n">
+        <v>14</v>
+      </c>
+      <c r="W199" t="n">
+        <v>8</v>
+      </c>
+      <c r="X199" t="n">
+        <v>16.78187505847015</v>
+      </c>
+      <c r="Y199" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_20-05-44</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>3</v>
+      </c>
+      <c r="D200" t="n">
+        <v>2</v>
+      </c>
+      <c r="E200" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F200" t="n">
+        <v>2</v>
+      </c>
+      <c r="G200" t="n">
+        <v>10</v>
+      </c>
+      <c r="H200" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I200" t="n">
+        <v>20</v>
+      </c>
+      <c r="J200" t="n">
+        <v>1</v>
+      </c>
+      <c r="K200" t="n">
+        <v>5</v>
+      </c>
+      <c r="L200" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M200" t="n">
+        <v>50</v>
+      </c>
+      <c r="N200" t="n">
+        <v>20</v>
+      </c>
+      <c r="O200" t="n">
+        <v>1</v>
+      </c>
+      <c r="P200" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>23</v>
+      </c>
+      <c r="R200" t="n">
+        <v>24</v>
+      </c>
+      <c r="S200" t="n">
+        <v>21</v>
+      </c>
+      <c r="T200" t="n">
+        <v>26</v>
+      </c>
+      <c r="U200" t="n">
+        <v>24</v>
+      </c>
+      <c r="V200" t="n">
+        <v>20</v>
+      </c>
+      <c r="W200" t="n">
+        <v>21</v>
+      </c>
+      <c r="X200" t="n">
+        <v>16.80540576064361</v>
+      </c>
+      <c r="Y200" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_20-05-44</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>4</v>
+      </c>
+      <c r="D201" t="n">
+        <v>2</v>
+      </c>
+      <c r="E201" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F201" t="n">
+        <v>2</v>
+      </c>
+      <c r="G201" t="n">
+        <v>10</v>
+      </c>
+      <c r="H201" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I201" t="n">
+        <v>20</v>
+      </c>
+      <c r="J201" t="n">
+        <v>1</v>
+      </c>
+      <c r="K201" t="n">
+        <v>5</v>
+      </c>
+      <c r="L201" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M201" t="n">
+        <v>50</v>
+      </c>
+      <c r="N201" t="n">
+        <v>1</v>
+      </c>
+      <c r="O201" t="n">
+        <v>18</v>
+      </c>
+      <c r="P201" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>27</v>
+      </c>
+      <c r="R201" t="n">
+        <v>11</v>
+      </c>
+      <c r="S201" t="n">
+        <v>0</v>
+      </c>
+      <c r="T201" t="n">
+        <v>28</v>
+      </c>
+      <c r="U201" t="n">
+        <v>11</v>
+      </c>
+      <c r="V201" t="n">
+        <v>20</v>
+      </c>
+      <c r="W201" t="n">
+        <v>1</v>
+      </c>
+      <c r="X201" t="n">
+        <v>15.70410198785326</v>
+      </c>
+      <c r="Y201" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_20-05-44</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>1</v>
+      </c>
+      <c r="D202" t="n">
+        <v>3</v>
+      </c>
+      <c r="E202" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F202" t="n">
+        <v>2</v>
+      </c>
+      <c r="G202" t="n">
+        <v>10</v>
+      </c>
+      <c r="H202" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I202" t="n">
+        <v>20</v>
+      </c>
+      <c r="J202" t="n">
+        <v>1</v>
+      </c>
+      <c r="K202" t="n">
+        <v>5</v>
+      </c>
+      <c r="L202" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M202" t="n">
+        <v>50</v>
+      </c>
+      <c r="N202" t="n">
+        <v>27</v>
+      </c>
+      <c r="O202" t="n">
+        <v>28</v>
+      </c>
+      <c r="P202" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>27</v>
+      </c>
+      <c r="R202" t="n">
+        <v>27</v>
+      </c>
+      <c r="S202" t="n">
+        <v>10</v>
+      </c>
+      <c r="T202" t="n">
+        <v>15</v>
+      </c>
+      <c r="U202" t="n">
+        <v>24</v>
+      </c>
+      <c r="V202" t="n">
+        <v>30</v>
+      </c>
+      <c r="W202" t="n">
+        <v>3</v>
+      </c>
+      <c r="X202" t="n">
+        <v>11.15089396747128</v>
+      </c>
+      <c r="Y202" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_20-05-44</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>2</v>
+      </c>
+      <c r="D203" t="n">
+        <v>3</v>
+      </c>
+      <c r="E203" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F203" t="n">
+        <v>2</v>
+      </c>
+      <c r="G203" t="n">
+        <v>10</v>
+      </c>
+      <c r="H203" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I203" t="n">
+        <v>20</v>
+      </c>
+      <c r="J203" t="n">
+        <v>1</v>
+      </c>
+      <c r="K203" t="n">
+        <v>5</v>
+      </c>
+      <c r="L203" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M203" t="n">
+        <v>50</v>
+      </c>
+      <c r="N203" t="n">
+        <v>12</v>
+      </c>
+      <c r="O203" t="n">
+        <v>2</v>
+      </c>
+      <c r="P203" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>7</v>
+      </c>
+      <c r="R203" t="n">
+        <v>29</v>
+      </c>
+      <c r="S203" t="n">
+        <v>31</v>
+      </c>
+      <c r="T203" t="n">
+        <v>2</v>
+      </c>
+      <c r="U203" t="n">
+        <v>18</v>
+      </c>
+      <c r="V203" t="n">
+        <v>20</v>
+      </c>
+      <c r="W203" t="n">
+        <v>31</v>
+      </c>
+      <c r="X203" t="n">
+        <v>13.56748754222904</v>
+      </c>
+      <c r="Y203" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_20-05-44</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>3</v>
+      </c>
+      <c r="D204" t="n">
+        <v>3</v>
+      </c>
+      <c r="E204" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F204" t="n">
+        <v>2</v>
+      </c>
+      <c r="G204" t="n">
+        <v>10</v>
+      </c>
+      <c r="H204" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I204" t="n">
+        <v>20</v>
+      </c>
+      <c r="J204" t="n">
+        <v>1</v>
+      </c>
+      <c r="K204" t="n">
+        <v>5</v>
+      </c>
+      <c r="L204" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M204" t="n">
+        <v>50</v>
+      </c>
+      <c r="N204" t="n">
+        <v>8</v>
+      </c>
+      <c r="O204" t="n">
+        <v>13</v>
+      </c>
+      <c r="P204" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>12</v>
+      </c>
+      <c r="R204" t="n">
+        <v>7</v>
+      </c>
+      <c r="S204" t="n">
+        <v>7</v>
+      </c>
+      <c r="T204" t="n">
+        <v>29</v>
+      </c>
+      <c r="U204" t="n">
+        <v>7</v>
+      </c>
+      <c r="V204" t="n">
+        <v>29</v>
+      </c>
+      <c r="W204" t="n">
+        <v>13</v>
+      </c>
+      <c r="X204" t="n">
+        <v>11.71085222573847</v>
+      </c>
+      <c r="Y204" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_20-05-44</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>4</v>
+      </c>
+      <c r="D205" t="n">
+        <v>3</v>
+      </c>
+      <c r="E205" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F205" t="n">
+        <v>2</v>
+      </c>
+      <c r="G205" t="n">
+        <v>10</v>
+      </c>
+      <c r="H205" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I205" t="n">
+        <v>20</v>
+      </c>
+      <c r="J205" t="n">
+        <v>1</v>
+      </c>
+      <c r="K205" t="n">
+        <v>5</v>
+      </c>
+      <c r="L205" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M205" t="n">
+        <v>50</v>
+      </c>
+      <c r="N205" t="n">
+        <v>9</v>
+      </c>
+      <c r="O205" t="n">
+        <v>3</v>
+      </c>
+      <c r="P205" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q205" t="n">
+        <v>13</v>
+      </c>
+      <c r="R205" t="n">
+        <v>3</v>
+      </c>
+      <c r="S205" t="n">
+        <v>9</v>
+      </c>
+      <c r="T205" t="n">
+        <v>3</v>
+      </c>
+      <c r="U205" t="n">
+        <v>7</v>
+      </c>
+      <c r="V205" t="n">
+        <v>15</v>
+      </c>
+      <c r="W205" t="n">
+        <v>3</v>
+      </c>
+      <c r="X205" t="n">
+        <v>10.30310695298883</v>
+      </c>
+      <c r="Y205" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_20-05-44</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>1</v>
+      </c>
+      <c r="D206" t="n">
+        <v>4</v>
+      </c>
+      <c r="E206" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F206" t="n">
+        <v>2</v>
+      </c>
+      <c r="G206" t="n">
+        <v>10</v>
+      </c>
+      <c r="H206" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I206" t="n">
+        <v>20</v>
+      </c>
+      <c r="J206" t="n">
+        <v>1</v>
+      </c>
+      <c r="K206" t="n">
+        <v>5</v>
+      </c>
+      <c r="L206" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M206" t="n">
+        <v>50</v>
+      </c>
+      <c r="N206" t="n">
+        <v>24</v>
+      </c>
+      <c r="O206" t="n">
+        <v>3</v>
+      </c>
+      <c r="P206" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>17</v>
+      </c>
+      <c r="R206" t="n">
+        <v>29</v>
+      </c>
+      <c r="S206" t="n">
+        <v>4</v>
+      </c>
+      <c r="T206" t="n">
+        <v>24</v>
+      </c>
+      <c r="U206" t="n">
+        <v>24</v>
+      </c>
+      <c r="V206" t="n">
+        <v>30</v>
+      </c>
+      <c r="W206" t="n">
+        <v>4</v>
+      </c>
+      <c r="X206" t="n">
+        <v>10.59093570920389</v>
+      </c>
+      <c r="Y206" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_20-05-44</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>2</v>
+      </c>
+      <c r="D207" t="n">
+        <v>4</v>
+      </c>
+      <c r="E207" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F207" t="n">
+        <v>2</v>
+      </c>
+      <c r="G207" t="n">
+        <v>10</v>
+      </c>
+      <c r="H207" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I207" t="n">
+        <v>20</v>
+      </c>
+      <c r="J207" t="n">
+        <v>1</v>
+      </c>
+      <c r="K207" t="n">
+        <v>5</v>
+      </c>
+      <c r="L207" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M207" t="n">
+        <v>50</v>
+      </c>
+      <c r="N207" t="n">
+        <v>30</v>
+      </c>
+      <c r="O207" t="n">
+        <v>28</v>
+      </c>
+      <c r="P207" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>24</v>
+      </c>
+      <c r="R207" t="n">
+        <v>30</v>
+      </c>
+      <c r="S207" t="n">
+        <v>24</v>
+      </c>
+      <c r="T207" t="n">
+        <v>19</v>
+      </c>
+      <c r="U207" t="n">
+        <v>24</v>
+      </c>
+      <c r="V207" t="n">
+        <v>28</v>
+      </c>
+      <c r="W207" t="n">
+        <v>30</v>
+      </c>
+      <c r="X207" t="n">
+        <v>8.615382551105444</v>
+      </c>
+      <c r="Y207" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_20-05-44</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>3</v>
+      </c>
+      <c r="D208" t="n">
+        <v>4</v>
+      </c>
+      <c r="E208" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F208" t="n">
+        <v>2</v>
+      </c>
+      <c r="G208" t="n">
+        <v>10</v>
+      </c>
+      <c r="H208" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I208" t="n">
+        <v>20</v>
+      </c>
+      <c r="J208" t="n">
+        <v>1</v>
+      </c>
+      <c r="K208" t="n">
+        <v>5</v>
+      </c>
+      <c r="L208" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M208" t="n">
+        <v>50</v>
+      </c>
+      <c r="N208" t="n">
+        <v>2</v>
+      </c>
+      <c r="O208" t="n">
+        <v>3</v>
+      </c>
+      <c r="P208" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>8</v>
+      </c>
+      <c r="R208" t="n">
+        <v>8</v>
+      </c>
+      <c r="S208" t="n">
+        <v>10</v>
+      </c>
+      <c r="T208" t="n">
+        <v>24</v>
+      </c>
+      <c r="U208" t="n">
+        <v>8</v>
+      </c>
+      <c r="V208" t="n">
+        <v>3</v>
+      </c>
+      <c r="W208" t="n">
+        <v>10</v>
+      </c>
+      <c r="X208" t="n">
+        <v>7.501294484291276</v>
+      </c>
+      <c r="Y208" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_20-05-44</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>4</v>
+      </c>
+      <c r="D209" t="n">
+        <v>4</v>
+      </c>
+      <c r="E209" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F209" t="n">
+        <v>2</v>
+      </c>
+      <c r="G209" t="n">
+        <v>10</v>
+      </c>
+      <c r="H209" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I209" t="n">
+        <v>20</v>
+      </c>
+      <c r="J209" t="n">
+        <v>1</v>
+      </c>
+      <c r="K209" t="n">
+        <v>5</v>
+      </c>
+      <c r="L209" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M209" t="n">
+        <v>50</v>
+      </c>
+      <c r="N209" t="n">
+        <v>25</v>
+      </c>
+      <c r="O209" t="n">
+        <v>25</v>
+      </c>
+      <c r="P209" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>20</v>
+      </c>
+      <c r="R209" t="n">
+        <v>25</v>
+      </c>
+      <c r="S209" t="n">
+        <v>31</v>
+      </c>
+      <c r="T209" t="n">
+        <v>30</v>
+      </c>
+      <c r="U209" t="n">
+        <v>20</v>
+      </c>
+      <c r="V209" t="n">
+        <v>24</v>
+      </c>
+      <c r="W209" t="n">
+        <v>31</v>
+      </c>
+      <c r="X209" t="n">
+        <v>9.183190436454158</v>
+      </c>
+      <c r="Y209" t="n">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y209"/>
+  <dimension ref="A1:Y216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -16310,6 +16310,573 @@
         <v>17</v>
       </c>
     </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_21-16-21</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>1</v>
+      </c>
+      <c r="D210" t="n">
+        <v>1</v>
+      </c>
+      <c r="E210" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F210" t="n">
+        <v>2</v>
+      </c>
+      <c r="G210" t="n">
+        <v>10</v>
+      </c>
+      <c r="H210" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I210" t="n">
+        <v>20</v>
+      </c>
+      <c r="J210" t="n">
+        <v>1</v>
+      </c>
+      <c r="K210" t="n">
+        <v>5</v>
+      </c>
+      <c r="L210" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M210" t="n">
+        <v>50</v>
+      </c>
+      <c r="N210" t="n">
+        <v>23</v>
+      </c>
+      <c r="O210" t="n">
+        <v>11</v>
+      </c>
+      <c r="P210" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>29</v>
+      </c>
+      <c r="R210" t="n">
+        <v>24</v>
+      </c>
+      <c r="S210" t="n">
+        <v>6</v>
+      </c>
+      <c r="T210" t="n">
+        <v>22</v>
+      </c>
+      <c r="U210" t="n">
+        <v>24</v>
+      </c>
+      <c r="V210" t="n">
+        <v>5</v>
+      </c>
+      <c r="W210" t="n">
+        <v>5</v>
+      </c>
+      <c r="X210" t="n">
+        <v>15.42412285871953</v>
+      </c>
+      <c r="Y210" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_21-16-21</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>2</v>
+      </c>
+      <c r="D211" t="n">
+        <v>1</v>
+      </c>
+      <c r="E211" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F211" t="n">
+        <v>2</v>
+      </c>
+      <c r="G211" t="n">
+        <v>10</v>
+      </c>
+      <c r="H211" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I211" t="n">
+        <v>20</v>
+      </c>
+      <c r="J211" t="n">
+        <v>1</v>
+      </c>
+      <c r="K211" t="n">
+        <v>5</v>
+      </c>
+      <c r="L211" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M211" t="n">
+        <v>50</v>
+      </c>
+      <c r="N211" t="n">
+        <v>22</v>
+      </c>
+      <c r="O211" t="n">
+        <v>6</v>
+      </c>
+      <c r="P211" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>21</v>
+      </c>
+      <c r="R211" t="n">
+        <v>30</v>
+      </c>
+      <c r="S211" t="n">
+        <v>1</v>
+      </c>
+      <c r="T211" t="n">
+        <v>6</v>
+      </c>
+      <c r="U211" t="n">
+        <v>30</v>
+      </c>
+      <c r="V211" t="n">
+        <v>22</v>
+      </c>
+      <c r="W211" t="n">
+        <v>22</v>
+      </c>
+      <c r="X211" t="n">
+        <v>12.51184159307749</v>
+      </c>
+      <c r="Y211" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_21-16-21</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>3</v>
+      </c>
+      <c r="D212" t="n">
+        <v>1</v>
+      </c>
+      <c r="E212" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F212" t="n">
+        <v>2</v>
+      </c>
+      <c r="G212" t="n">
+        <v>10</v>
+      </c>
+      <c r="H212" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I212" t="n">
+        <v>20</v>
+      </c>
+      <c r="J212" t="n">
+        <v>1</v>
+      </c>
+      <c r="K212" t="n">
+        <v>5</v>
+      </c>
+      <c r="L212" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M212" t="n">
+        <v>50</v>
+      </c>
+      <c r="N212" t="n">
+        <v>8</v>
+      </c>
+      <c r="O212" t="n">
+        <v>3</v>
+      </c>
+      <c r="P212" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>8</v>
+      </c>
+      <c r="R212" t="n">
+        <v>13</v>
+      </c>
+      <c r="S212" t="n">
+        <v>7</v>
+      </c>
+      <c r="T212" t="n">
+        <v>13</v>
+      </c>
+      <c r="U212" t="n">
+        <v>7</v>
+      </c>
+      <c r="V212" t="n">
+        <v>3</v>
+      </c>
+      <c r="W212" t="n">
+        <v>9</v>
+      </c>
+      <c r="X212" t="n">
+        <v>11.71699153829863</v>
+      </c>
+      <c r="Y212" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_21-16-21</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>4</v>
+      </c>
+      <c r="D213" t="n">
+        <v>1</v>
+      </c>
+      <c r="E213" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F213" t="n">
+        <v>2</v>
+      </c>
+      <c r="G213" t="n">
+        <v>10</v>
+      </c>
+      <c r="H213" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I213" t="n">
+        <v>20</v>
+      </c>
+      <c r="J213" t="n">
+        <v>1</v>
+      </c>
+      <c r="K213" t="n">
+        <v>5</v>
+      </c>
+      <c r="L213" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M213" t="n">
+        <v>50</v>
+      </c>
+      <c r="N213" t="n">
+        <v>4</v>
+      </c>
+      <c r="O213" t="n">
+        <v>31</v>
+      </c>
+      <c r="P213" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>4</v>
+      </c>
+      <c r="R213" t="n">
+        <v>20</v>
+      </c>
+      <c r="S213" t="n">
+        <v>14</v>
+      </c>
+      <c r="T213" t="n">
+        <v>9</v>
+      </c>
+      <c r="U213" t="n">
+        <v>20</v>
+      </c>
+      <c r="V213" t="n">
+        <v>11</v>
+      </c>
+      <c r="W213" t="n">
+        <v>7</v>
+      </c>
+      <c r="X213" t="n">
+        <v>14.98142278639315</v>
+      </c>
+      <c r="Y213" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_21-16-21</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>1</v>
+      </c>
+      <c r="D214" t="n">
+        <v>2</v>
+      </c>
+      <c r="E214" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F214" t="n">
+        <v>2</v>
+      </c>
+      <c r="G214" t="n">
+        <v>10</v>
+      </c>
+      <c r="H214" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I214" t="n">
+        <v>20</v>
+      </c>
+      <c r="J214" t="n">
+        <v>1</v>
+      </c>
+      <c r="K214" t="n">
+        <v>5</v>
+      </c>
+      <c r="L214" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M214" t="n">
+        <v>50</v>
+      </c>
+      <c r="N214" t="n">
+        <v>9</v>
+      </c>
+      <c r="O214" t="n">
+        <v>10</v>
+      </c>
+      <c r="P214" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>5</v>
+      </c>
+      <c r="R214" t="n">
+        <v>5</v>
+      </c>
+      <c r="S214" t="n">
+        <v>9</v>
+      </c>
+      <c r="T214" t="n">
+        <v>15</v>
+      </c>
+      <c r="U214" t="n">
+        <v>5</v>
+      </c>
+      <c r="V214" t="n">
+        <v>5</v>
+      </c>
+      <c r="W214" t="n">
+        <v>11</v>
+      </c>
+      <c r="X214" t="n">
+        <v>9.175340809372777</v>
+      </c>
+      <c r="Y214" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_21-16-21</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>2</v>
+      </c>
+      <c r="D215" t="n">
+        <v>2</v>
+      </c>
+      <c r="E215" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F215" t="n">
+        <v>2</v>
+      </c>
+      <c r="G215" t="n">
+        <v>10</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I215" t="n">
+        <v>20</v>
+      </c>
+      <c r="J215" t="n">
+        <v>1</v>
+      </c>
+      <c r="K215" t="n">
+        <v>5</v>
+      </c>
+      <c r="L215" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M215" t="n">
+        <v>50</v>
+      </c>
+      <c r="N215" t="n">
+        <v>31</v>
+      </c>
+      <c r="O215" t="n">
+        <v>6</v>
+      </c>
+      <c r="P215" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>2</v>
+      </c>
+      <c r="R215" t="n">
+        <v>1</v>
+      </c>
+      <c r="S215" t="n">
+        <v>7</v>
+      </c>
+      <c r="T215" t="n">
+        <v>11</v>
+      </c>
+      <c r="U215" t="n">
+        <v>9</v>
+      </c>
+      <c r="V215" t="n">
+        <v>1</v>
+      </c>
+      <c r="W215" t="n">
+        <v>31</v>
+      </c>
+      <c r="X215" t="n">
+        <v>15.09415065658671</v>
+      </c>
+      <c r="Y215" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_21-16-21</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>3</v>
+      </c>
+      <c r="D216" t="n">
+        <v>2</v>
+      </c>
+      <c r="E216" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F216" t="n">
+        <v>2</v>
+      </c>
+      <c r="G216" t="n">
+        <v>10</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I216" t="n">
+        <v>20</v>
+      </c>
+      <c r="J216" t="n">
+        <v>1</v>
+      </c>
+      <c r="K216" t="n">
+        <v>5</v>
+      </c>
+      <c r="L216" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M216" t="n">
+        <v>50</v>
+      </c>
+      <c r="N216" t="n">
+        <v>14</v>
+      </c>
+      <c r="O216" t="n">
+        <v>7</v>
+      </c>
+      <c r="P216" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>5</v>
+      </c>
+      <c r="R216" t="n">
+        <v>22</v>
+      </c>
+      <c r="S216" t="n">
+        <v>9</v>
+      </c>
+      <c r="T216" t="n">
+        <v>6</v>
+      </c>
+      <c r="U216" t="n">
+        <v>0</v>
+      </c>
+      <c r="V216" t="n">
+        <v>0</v>
+      </c>
+      <c r="W216" t="n">
+        <v>14</v>
+      </c>
+      <c r="X216" t="n">
+        <v>16.10913827115498</v>
+      </c>
+      <c r="Y216" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y216"/>
+  <dimension ref="A1:Y237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -16877,6 +16877,1707 @@
         <v>0</v>
       </c>
     </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_21-16-21</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>4</v>
+      </c>
+      <c r="D217" t="n">
+        <v>2</v>
+      </c>
+      <c r="E217" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F217" t="n">
+        <v>2</v>
+      </c>
+      <c r="G217" t="n">
+        <v>10</v>
+      </c>
+      <c r="H217" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I217" t="n">
+        <v>20</v>
+      </c>
+      <c r="J217" t="n">
+        <v>1</v>
+      </c>
+      <c r="K217" t="n">
+        <v>5</v>
+      </c>
+      <c r="L217" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M217" t="n">
+        <v>50</v>
+      </c>
+      <c r="N217" t="n">
+        <v>6</v>
+      </c>
+      <c r="O217" t="n">
+        <v>7</v>
+      </c>
+      <c r="P217" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>4</v>
+      </c>
+      <c r="R217" t="n">
+        <v>30</v>
+      </c>
+      <c r="S217" t="n">
+        <v>28</v>
+      </c>
+      <c r="T217" t="n">
+        <v>25</v>
+      </c>
+      <c r="U217" t="n">
+        <v>4</v>
+      </c>
+      <c r="V217" t="n">
+        <v>25</v>
+      </c>
+      <c r="W217" t="n">
+        <v>4</v>
+      </c>
+      <c r="X217" t="n">
+        <v>13.12644712556954</v>
+      </c>
+      <c r="Y217" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_21-16-21</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>1</v>
+      </c>
+      <c r="D218" t="n">
+        <v>3</v>
+      </c>
+      <c r="E218" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F218" t="n">
+        <v>2</v>
+      </c>
+      <c r="G218" t="n">
+        <v>10</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I218" t="n">
+        <v>20</v>
+      </c>
+      <c r="J218" t="n">
+        <v>1</v>
+      </c>
+      <c r="K218" t="n">
+        <v>5</v>
+      </c>
+      <c r="L218" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M218" t="n">
+        <v>50</v>
+      </c>
+      <c r="N218" t="n">
+        <v>0</v>
+      </c>
+      <c r="O218" t="n">
+        <v>7</v>
+      </c>
+      <c r="P218" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q218" t="n">
+        <v>0</v>
+      </c>
+      <c r="R218" t="n">
+        <v>6</v>
+      </c>
+      <c r="S218" t="n">
+        <v>7</v>
+      </c>
+      <c r="T218" t="n">
+        <v>6</v>
+      </c>
+      <c r="U218" t="n">
+        <v>30</v>
+      </c>
+      <c r="V218" t="n">
+        <v>1</v>
+      </c>
+      <c r="W218" t="n">
+        <v>7</v>
+      </c>
+      <c r="X218" t="n">
+        <v>8.341521984831523</v>
+      </c>
+      <c r="Y218" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_21-16-21</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>2</v>
+      </c>
+      <c r="D219" t="n">
+        <v>3</v>
+      </c>
+      <c r="E219" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F219" t="n">
+        <v>2</v>
+      </c>
+      <c r="G219" t="n">
+        <v>10</v>
+      </c>
+      <c r="H219" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I219" t="n">
+        <v>20</v>
+      </c>
+      <c r="J219" t="n">
+        <v>1</v>
+      </c>
+      <c r="K219" t="n">
+        <v>5</v>
+      </c>
+      <c r="L219" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M219" t="n">
+        <v>50</v>
+      </c>
+      <c r="N219" t="n">
+        <v>10</v>
+      </c>
+      <c r="O219" t="n">
+        <v>29</v>
+      </c>
+      <c r="P219" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>10</v>
+      </c>
+      <c r="R219" t="n">
+        <v>4</v>
+      </c>
+      <c r="S219" t="n">
+        <v>10</v>
+      </c>
+      <c r="T219" t="n">
+        <v>4</v>
+      </c>
+      <c r="U219" t="n">
+        <v>9</v>
+      </c>
+      <c r="V219" t="n">
+        <v>25</v>
+      </c>
+      <c r="W219" t="n">
+        <v>26</v>
+      </c>
+      <c r="X219" t="n">
+        <v>12.27866011108721</v>
+      </c>
+      <c r="Y219" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_21-16-21</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>3</v>
+      </c>
+      <c r="D220" t="n">
+        <v>3</v>
+      </c>
+      <c r="E220" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F220" t="n">
+        <v>2</v>
+      </c>
+      <c r="G220" t="n">
+        <v>10</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I220" t="n">
+        <v>20</v>
+      </c>
+      <c r="J220" t="n">
+        <v>1</v>
+      </c>
+      <c r="K220" t="n">
+        <v>5</v>
+      </c>
+      <c r="L220" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M220" t="n">
+        <v>50</v>
+      </c>
+      <c r="N220" t="n">
+        <v>9</v>
+      </c>
+      <c r="O220" t="n">
+        <v>2</v>
+      </c>
+      <c r="P220" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q220" t="n">
+        <v>1</v>
+      </c>
+      <c r="R220" t="n">
+        <v>28</v>
+      </c>
+      <c r="S220" t="n">
+        <v>26</v>
+      </c>
+      <c r="T220" t="n">
+        <v>1</v>
+      </c>
+      <c r="U220" t="n">
+        <v>9</v>
+      </c>
+      <c r="V220" t="n">
+        <v>25</v>
+      </c>
+      <c r="W220" t="n">
+        <v>30</v>
+      </c>
+      <c r="X220" t="n">
+        <v>10.31095658007025</v>
+      </c>
+      <c r="Y220" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_21-16-21</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>4</v>
+      </c>
+      <c r="D221" t="n">
+        <v>3</v>
+      </c>
+      <c r="E221" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F221" t="n">
+        <v>2</v>
+      </c>
+      <c r="G221" t="n">
+        <v>10</v>
+      </c>
+      <c r="H221" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I221" t="n">
+        <v>20</v>
+      </c>
+      <c r="J221" t="n">
+        <v>1</v>
+      </c>
+      <c r="K221" t="n">
+        <v>5</v>
+      </c>
+      <c r="L221" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M221" t="n">
+        <v>50</v>
+      </c>
+      <c r="N221" t="n">
+        <v>22</v>
+      </c>
+      <c r="O221" t="n">
+        <v>5</v>
+      </c>
+      <c r="P221" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>24</v>
+      </c>
+      <c r="R221" t="n">
+        <v>4</v>
+      </c>
+      <c r="S221" t="n">
+        <v>24</v>
+      </c>
+      <c r="T221" t="n">
+        <v>23</v>
+      </c>
+      <c r="U221" t="n">
+        <v>30</v>
+      </c>
+      <c r="V221" t="n">
+        <v>23</v>
+      </c>
+      <c r="W221" t="n">
+        <v>24</v>
+      </c>
+      <c r="X221" t="n">
+        <v>13.16859057148757</v>
+      </c>
+      <c r="Y221" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_21-49-56</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>1</v>
+      </c>
+      <c r="D222" t="n">
+        <v>1</v>
+      </c>
+      <c r="E222" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F222" t="n">
+        <v>2</v>
+      </c>
+      <c r="G222" t="n">
+        <v>10</v>
+      </c>
+      <c r="H222" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I222" t="n">
+        <v>50</v>
+      </c>
+      <c r="J222" t="n">
+        <v>1</v>
+      </c>
+      <c r="K222" t="n">
+        <v>5</v>
+      </c>
+      <c r="L222" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M222" t="n">
+        <v>50</v>
+      </c>
+      <c r="N222" t="n">
+        <v>8</v>
+      </c>
+      <c r="O222" t="n">
+        <v>8</v>
+      </c>
+      <c r="P222" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>22</v>
+      </c>
+      <c r="R222" t="n">
+        <v>0</v>
+      </c>
+      <c r="S222" t="n">
+        <v>9</v>
+      </c>
+      <c r="T222" t="n">
+        <v>18</v>
+      </c>
+      <c r="U222" t="n">
+        <v>4</v>
+      </c>
+      <c r="V222" t="n">
+        <v>2</v>
+      </c>
+      <c r="W222" t="n">
+        <v>3</v>
+      </c>
+      <c r="X222" t="n">
+        <v>1671</v>
+      </c>
+      <c r="Y222" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_21-49-56</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>2</v>
+      </c>
+      <c r="D223" t="n">
+        <v>1</v>
+      </c>
+      <c r="E223" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F223" t="n">
+        <v>2</v>
+      </c>
+      <c r="G223" t="n">
+        <v>10</v>
+      </c>
+      <c r="H223" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I223" t="n">
+        <v>50</v>
+      </c>
+      <c r="J223" t="n">
+        <v>1</v>
+      </c>
+      <c r="K223" t="n">
+        <v>5</v>
+      </c>
+      <c r="L223" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M223" t="n">
+        <v>50</v>
+      </c>
+      <c r="N223" t="n">
+        <v>14</v>
+      </c>
+      <c r="O223" t="n">
+        <v>1</v>
+      </c>
+      <c r="P223" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q223" t="n">
+        <v>4</v>
+      </c>
+      <c r="R223" t="n">
+        <v>8</v>
+      </c>
+      <c r="S223" t="n">
+        <v>10</v>
+      </c>
+      <c r="T223" t="n">
+        <v>4</v>
+      </c>
+      <c r="U223" t="n">
+        <v>10</v>
+      </c>
+      <c r="V223" t="n">
+        <v>2</v>
+      </c>
+      <c r="W223" t="n">
+        <v>8</v>
+      </c>
+      <c r="X223" t="n">
+        <v>561</v>
+      </c>
+      <c r="Y223" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_21-49-56</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>3</v>
+      </c>
+      <c r="D224" t="n">
+        <v>1</v>
+      </c>
+      <c r="E224" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F224" t="n">
+        <v>2</v>
+      </c>
+      <c r="G224" t="n">
+        <v>10</v>
+      </c>
+      <c r="H224" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I224" t="n">
+        <v>50</v>
+      </c>
+      <c r="J224" t="n">
+        <v>1</v>
+      </c>
+      <c r="K224" t="n">
+        <v>5</v>
+      </c>
+      <c r="L224" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M224" t="n">
+        <v>50</v>
+      </c>
+      <c r="N224" t="n">
+        <v>11</v>
+      </c>
+      <c r="O224" t="n">
+        <v>8</v>
+      </c>
+      <c r="P224" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>10</v>
+      </c>
+      <c r="R224" t="n">
+        <v>0</v>
+      </c>
+      <c r="S224" t="n">
+        <v>10</v>
+      </c>
+      <c r="T224" t="n">
+        <v>0</v>
+      </c>
+      <c r="U224" t="n">
+        <v>8</v>
+      </c>
+      <c r="V224" t="n">
+        <v>3</v>
+      </c>
+      <c r="W224" t="n">
+        <v>7</v>
+      </c>
+      <c r="X224" t="n">
+        <v>1468</v>
+      </c>
+      <c r="Y224" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_21-49-56</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>4</v>
+      </c>
+      <c r="D225" t="n">
+        <v>1</v>
+      </c>
+      <c r="E225" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F225" t="n">
+        <v>2</v>
+      </c>
+      <c r="G225" t="n">
+        <v>10</v>
+      </c>
+      <c r="H225" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I225" t="n">
+        <v>50</v>
+      </c>
+      <c r="J225" t="n">
+        <v>1</v>
+      </c>
+      <c r="K225" t="n">
+        <v>5</v>
+      </c>
+      <c r="L225" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M225" t="n">
+        <v>50</v>
+      </c>
+      <c r="N225" t="n">
+        <v>3</v>
+      </c>
+      <c r="O225" t="n">
+        <v>4</v>
+      </c>
+      <c r="P225" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q225" t="n">
+        <v>13</v>
+      </c>
+      <c r="R225" t="n">
+        <v>15</v>
+      </c>
+      <c r="S225" t="n">
+        <v>7</v>
+      </c>
+      <c r="T225" t="n">
+        <v>19</v>
+      </c>
+      <c r="U225" t="n">
+        <v>7</v>
+      </c>
+      <c r="V225" t="n">
+        <v>1</v>
+      </c>
+      <c r="W225" t="n">
+        <v>2</v>
+      </c>
+      <c r="X225" t="n">
+        <v>883</v>
+      </c>
+      <c r="Y225" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_21-49-56</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>1</v>
+      </c>
+      <c r="D226" t="n">
+        <v>2</v>
+      </c>
+      <c r="E226" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F226" t="n">
+        <v>2</v>
+      </c>
+      <c r="G226" t="n">
+        <v>10</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I226" t="n">
+        <v>50</v>
+      </c>
+      <c r="J226" t="n">
+        <v>1</v>
+      </c>
+      <c r="K226" t="n">
+        <v>5</v>
+      </c>
+      <c r="L226" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M226" t="n">
+        <v>50</v>
+      </c>
+      <c r="N226" t="n">
+        <v>8</v>
+      </c>
+      <c r="O226" t="n">
+        <v>3</v>
+      </c>
+      <c r="P226" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q226" t="n">
+        <v>1</v>
+      </c>
+      <c r="R226" t="n">
+        <v>4</v>
+      </c>
+      <c r="S226" t="n">
+        <v>6</v>
+      </c>
+      <c r="T226" t="n">
+        <v>22</v>
+      </c>
+      <c r="U226" t="n">
+        <v>3</v>
+      </c>
+      <c r="V226" t="n">
+        <v>6</v>
+      </c>
+      <c r="W226" t="n">
+        <v>2</v>
+      </c>
+      <c r="X226" t="n">
+        <v>659</v>
+      </c>
+      <c r="Y226" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_21-49-56</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>2</v>
+      </c>
+      <c r="D227" t="n">
+        <v>2</v>
+      </c>
+      <c r="E227" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F227" t="n">
+        <v>2</v>
+      </c>
+      <c r="G227" t="n">
+        <v>10</v>
+      </c>
+      <c r="H227" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I227" t="n">
+        <v>50</v>
+      </c>
+      <c r="J227" t="n">
+        <v>1</v>
+      </c>
+      <c r="K227" t="n">
+        <v>5</v>
+      </c>
+      <c r="L227" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M227" t="n">
+        <v>50</v>
+      </c>
+      <c r="N227" t="n">
+        <v>1</v>
+      </c>
+      <c r="O227" t="n">
+        <v>24</v>
+      </c>
+      <c r="P227" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>10</v>
+      </c>
+      <c r="R227" t="n">
+        <v>1</v>
+      </c>
+      <c r="S227" t="n">
+        <v>5</v>
+      </c>
+      <c r="T227" t="n">
+        <v>15</v>
+      </c>
+      <c r="U227" t="n">
+        <v>7</v>
+      </c>
+      <c r="V227" t="n">
+        <v>4</v>
+      </c>
+      <c r="W227" t="n">
+        <v>14</v>
+      </c>
+      <c r="X227" t="n">
+        <v>1270</v>
+      </c>
+      <c r="Y227" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_21-49-56</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>3</v>
+      </c>
+      <c r="D228" t="n">
+        <v>2</v>
+      </c>
+      <c r="E228" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F228" t="n">
+        <v>2</v>
+      </c>
+      <c r="G228" t="n">
+        <v>10</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I228" t="n">
+        <v>50</v>
+      </c>
+      <c r="J228" t="n">
+        <v>1</v>
+      </c>
+      <c r="K228" t="n">
+        <v>5</v>
+      </c>
+      <c r="L228" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M228" t="n">
+        <v>50</v>
+      </c>
+      <c r="N228" t="n">
+        <v>0</v>
+      </c>
+      <c r="O228" t="n">
+        <v>3</v>
+      </c>
+      <c r="P228" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q228" t="n">
+        <v>1</v>
+      </c>
+      <c r="R228" t="n">
+        <v>17</v>
+      </c>
+      <c r="S228" t="n">
+        <v>2</v>
+      </c>
+      <c r="T228" t="n">
+        <v>5</v>
+      </c>
+      <c r="U228" t="n">
+        <v>4</v>
+      </c>
+      <c r="V228" t="n">
+        <v>15</v>
+      </c>
+      <c r="W228" t="n">
+        <v>3</v>
+      </c>
+      <c r="X228" t="n">
+        <v>582</v>
+      </c>
+      <c r="Y228" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_21-49-56</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>4</v>
+      </c>
+      <c r="D229" t="n">
+        <v>2</v>
+      </c>
+      <c r="E229" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F229" t="n">
+        <v>2</v>
+      </c>
+      <c r="G229" t="n">
+        <v>10</v>
+      </c>
+      <c r="H229" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I229" t="n">
+        <v>50</v>
+      </c>
+      <c r="J229" t="n">
+        <v>1</v>
+      </c>
+      <c r="K229" t="n">
+        <v>5</v>
+      </c>
+      <c r="L229" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M229" t="n">
+        <v>50</v>
+      </c>
+      <c r="N229" t="n">
+        <v>6</v>
+      </c>
+      <c r="O229" t="n">
+        <v>11</v>
+      </c>
+      <c r="P229" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q229" t="n">
+        <v>1</v>
+      </c>
+      <c r="R229" t="n">
+        <v>16</v>
+      </c>
+      <c r="S229" t="n">
+        <v>11</v>
+      </c>
+      <c r="T229" t="n">
+        <v>0</v>
+      </c>
+      <c r="U229" t="n">
+        <v>7</v>
+      </c>
+      <c r="V229" t="n">
+        <v>1</v>
+      </c>
+      <c r="W229" t="n">
+        <v>4</v>
+      </c>
+      <c r="X229" t="n">
+        <v>1130</v>
+      </c>
+      <c r="Y229" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_21-49-56</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>1</v>
+      </c>
+      <c r="D230" t="n">
+        <v>3</v>
+      </c>
+      <c r="E230" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F230" t="n">
+        <v>2</v>
+      </c>
+      <c r="G230" t="n">
+        <v>10</v>
+      </c>
+      <c r="H230" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I230" t="n">
+        <v>50</v>
+      </c>
+      <c r="J230" t="n">
+        <v>1</v>
+      </c>
+      <c r="K230" t="n">
+        <v>5</v>
+      </c>
+      <c r="L230" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M230" t="n">
+        <v>50</v>
+      </c>
+      <c r="N230" t="n">
+        <v>0</v>
+      </c>
+      <c r="O230" t="n">
+        <v>4</v>
+      </c>
+      <c r="P230" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q230" t="n">
+        <v>4</v>
+      </c>
+      <c r="R230" t="n">
+        <v>3</v>
+      </c>
+      <c r="S230" t="n">
+        <v>1</v>
+      </c>
+      <c r="T230" t="n">
+        <v>1</v>
+      </c>
+      <c r="U230" t="n">
+        <v>2</v>
+      </c>
+      <c r="V230" t="n">
+        <v>0</v>
+      </c>
+      <c r="W230" t="n">
+        <v>14</v>
+      </c>
+      <c r="X230" t="n">
+        <v>244</v>
+      </c>
+      <c r="Y230" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_21-49-56</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>2</v>
+      </c>
+      <c r="D231" t="n">
+        <v>3</v>
+      </c>
+      <c r="E231" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F231" t="n">
+        <v>2</v>
+      </c>
+      <c r="G231" t="n">
+        <v>10</v>
+      </c>
+      <c r="H231" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I231" t="n">
+        <v>50</v>
+      </c>
+      <c r="J231" t="n">
+        <v>1</v>
+      </c>
+      <c r="K231" t="n">
+        <v>5</v>
+      </c>
+      <c r="L231" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M231" t="n">
+        <v>50</v>
+      </c>
+      <c r="N231" t="n">
+        <v>3</v>
+      </c>
+      <c r="O231" t="n">
+        <v>2</v>
+      </c>
+      <c r="P231" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q231" t="n">
+        <v>1</v>
+      </c>
+      <c r="R231" t="n">
+        <v>0</v>
+      </c>
+      <c r="S231" t="n">
+        <v>1</v>
+      </c>
+      <c r="T231" t="n">
+        <v>5</v>
+      </c>
+      <c r="U231" t="n">
+        <v>5</v>
+      </c>
+      <c r="V231" t="n">
+        <v>3</v>
+      </c>
+      <c r="W231" t="n">
+        <v>0</v>
+      </c>
+      <c r="X231" t="n">
+        <v>74</v>
+      </c>
+      <c r="Y231" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_21-49-56</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>3</v>
+      </c>
+      <c r="D232" t="n">
+        <v>3</v>
+      </c>
+      <c r="E232" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F232" t="n">
+        <v>2</v>
+      </c>
+      <c r="G232" t="n">
+        <v>10</v>
+      </c>
+      <c r="H232" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I232" t="n">
+        <v>50</v>
+      </c>
+      <c r="J232" t="n">
+        <v>1</v>
+      </c>
+      <c r="K232" t="n">
+        <v>5</v>
+      </c>
+      <c r="L232" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M232" t="n">
+        <v>50</v>
+      </c>
+      <c r="N232" t="n">
+        <v>1</v>
+      </c>
+      <c r="O232" t="n">
+        <v>7</v>
+      </c>
+      <c r="P232" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q232" t="n">
+        <v>1</v>
+      </c>
+      <c r="R232" t="n">
+        <v>2</v>
+      </c>
+      <c r="S232" t="n">
+        <v>9</v>
+      </c>
+      <c r="T232" t="n">
+        <v>3</v>
+      </c>
+      <c r="U232" t="n">
+        <v>0</v>
+      </c>
+      <c r="V232" t="n">
+        <v>1</v>
+      </c>
+      <c r="W232" t="n">
+        <v>1</v>
+      </c>
+      <c r="X232" t="n">
+        <v>147</v>
+      </c>
+      <c r="Y232" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_21-49-56</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>4</v>
+      </c>
+      <c r="D233" t="n">
+        <v>3</v>
+      </c>
+      <c r="E233" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F233" t="n">
+        <v>2</v>
+      </c>
+      <c r="G233" t="n">
+        <v>10</v>
+      </c>
+      <c r="H233" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I233" t="n">
+        <v>50</v>
+      </c>
+      <c r="J233" t="n">
+        <v>1</v>
+      </c>
+      <c r="K233" t="n">
+        <v>5</v>
+      </c>
+      <c r="L233" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M233" t="n">
+        <v>50</v>
+      </c>
+      <c r="N233" t="n">
+        <v>3</v>
+      </c>
+      <c r="O233" t="n">
+        <v>0</v>
+      </c>
+      <c r="P233" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>1</v>
+      </c>
+      <c r="R233" t="n">
+        <v>0</v>
+      </c>
+      <c r="S233" t="n">
+        <v>0</v>
+      </c>
+      <c r="T233" t="n">
+        <v>3</v>
+      </c>
+      <c r="U233" t="n">
+        <v>3</v>
+      </c>
+      <c r="V233" t="n">
+        <v>0</v>
+      </c>
+      <c r="W233" t="n">
+        <v>8</v>
+      </c>
+      <c r="X233" t="n">
+        <v>101</v>
+      </c>
+      <c r="Y233" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_21-49-56</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>1</v>
+      </c>
+      <c r="D234" t="n">
+        <v>4</v>
+      </c>
+      <c r="E234" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F234" t="n">
+        <v>2</v>
+      </c>
+      <c r="G234" t="n">
+        <v>10</v>
+      </c>
+      <c r="H234" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I234" t="n">
+        <v>50</v>
+      </c>
+      <c r="J234" t="n">
+        <v>1</v>
+      </c>
+      <c r="K234" t="n">
+        <v>5</v>
+      </c>
+      <c r="L234" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M234" t="n">
+        <v>50</v>
+      </c>
+      <c r="N234" t="n">
+        <v>1</v>
+      </c>
+      <c r="O234" t="n">
+        <v>5</v>
+      </c>
+      <c r="P234" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q234" t="n">
+        <v>7</v>
+      </c>
+      <c r="R234" t="n">
+        <v>3</v>
+      </c>
+      <c r="S234" t="n">
+        <v>1</v>
+      </c>
+      <c r="T234" t="n">
+        <v>2</v>
+      </c>
+      <c r="U234" t="n">
+        <v>0</v>
+      </c>
+      <c r="V234" t="n">
+        <v>3</v>
+      </c>
+      <c r="W234" t="n">
+        <v>2</v>
+      </c>
+      <c r="X234" t="n">
+        <v>127</v>
+      </c>
+      <c r="Y234" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_21-49-56</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>2</v>
+      </c>
+      <c r="D235" t="n">
+        <v>4</v>
+      </c>
+      <c r="E235" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F235" t="n">
+        <v>2</v>
+      </c>
+      <c r="G235" t="n">
+        <v>10</v>
+      </c>
+      <c r="H235" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I235" t="n">
+        <v>50</v>
+      </c>
+      <c r="J235" t="n">
+        <v>1</v>
+      </c>
+      <c r="K235" t="n">
+        <v>5</v>
+      </c>
+      <c r="L235" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M235" t="n">
+        <v>50</v>
+      </c>
+      <c r="N235" t="n">
+        <v>1</v>
+      </c>
+      <c r="O235" t="n">
+        <v>6</v>
+      </c>
+      <c r="P235" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q235" t="n">
+        <v>3</v>
+      </c>
+      <c r="R235" t="n">
+        <v>6</v>
+      </c>
+      <c r="S235" t="n">
+        <v>4</v>
+      </c>
+      <c r="T235" t="n">
+        <v>1</v>
+      </c>
+      <c r="U235" t="n">
+        <v>0</v>
+      </c>
+      <c r="V235" t="n">
+        <v>0</v>
+      </c>
+      <c r="W235" t="n">
+        <v>5</v>
+      </c>
+      <c r="X235" t="n">
+        <v>140</v>
+      </c>
+      <c r="Y235" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_21-49-56</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>3</v>
+      </c>
+      <c r="D236" t="n">
+        <v>4</v>
+      </c>
+      <c r="E236" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F236" t="n">
+        <v>2</v>
+      </c>
+      <c r="G236" t="n">
+        <v>10</v>
+      </c>
+      <c r="H236" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I236" t="n">
+        <v>50</v>
+      </c>
+      <c r="J236" t="n">
+        <v>1</v>
+      </c>
+      <c r="K236" t="n">
+        <v>5</v>
+      </c>
+      <c r="L236" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M236" t="n">
+        <v>50</v>
+      </c>
+      <c r="N236" t="n">
+        <v>1</v>
+      </c>
+      <c r="O236" t="n">
+        <v>2</v>
+      </c>
+      <c r="P236" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q236" t="n">
+        <v>3</v>
+      </c>
+      <c r="R236" t="n">
+        <v>1</v>
+      </c>
+      <c r="S236" t="n">
+        <v>4</v>
+      </c>
+      <c r="T236" t="n">
+        <v>0</v>
+      </c>
+      <c r="U236" t="n">
+        <v>1</v>
+      </c>
+      <c r="V236" t="n">
+        <v>4</v>
+      </c>
+      <c r="W236" t="n">
+        <v>0</v>
+      </c>
+      <c r="X236" t="n">
+        <v>73</v>
+      </c>
+      <c r="Y236" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_21-49-56</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>4</v>
+      </c>
+      <c r="D237" t="n">
+        <v>4</v>
+      </c>
+      <c r="E237" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F237" t="n">
+        <v>2</v>
+      </c>
+      <c r="G237" t="n">
+        <v>10</v>
+      </c>
+      <c r="H237" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I237" t="n">
+        <v>50</v>
+      </c>
+      <c r="J237" t="n">
+        <v>1</v>
+      </c>
+      <c r="K237" t="n">
+        <v>5</v>
+      </c>
+      <c r="L237" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M237" t="n">
+        <v>50</v>
+      </c>
+      <c r="N237" t="n">
+        <v>5</v>
+      </c>
+      <c r="O237" t="n">
+        <v>8</v>
+      </c>
+      <c r="P237" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q237" t="n">
+        <v>15</v>
+      </c>
+      <c r="R237" t="n">
+        <v>0</v>
+      </c>
+      <c r="S237" t="n">
+        <v>5</v>
+      </c>
+      <c r="T237" t="n">
+        <v>4</v>
+      </c>
+      <c r="U237" t="n">
+        <v>4</v>
+      </c>
+      <c r="V237" t="n">
+        <v>11</v>
+      </c>
+      <c r="W237" t="n">
+        <v>0</v>
+      </c>
+      <c r="X237" t="n">
+        <v>528</v>
+      </c>
+      <c r="Y237" t="n">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y237"/>
+  <dimension ref="A1:Y241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -17285,34 +17285,34 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>run_2025-08-26_21-49-56</t>
+          <t>run_2025-08-26_21-16-21</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>config_1</t>
+          <t>config_4</t>
         </is>
       </c>
       <c r="C222" t="n">
         <v>1</v>
       </c>
       <c r="D222" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E222" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F222" t="n">
+        <v>2</v>
+      </c>
+      <c r="G222" t="n">
+        <v>10</v>
+      </c>
+      <c r="H222" t="n">
         <v>0.9</v>
       </c>
-      <c r="F222" t="n">
-        <v>2</v>
-      </c>
-      <c r="G222" t="n">
-        <v>10</v>
-      </c>
-      <c r="H222" t="n">
-        <v>0.1</v>
-      </c>
       <c r="I222" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J222" t="n">
         <v>1</v>
@@ -17327,73 +17327,73 @@
         <v>50</v>
       </c>
       <c r="N222" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O222" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P222" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q222" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="R222" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S222" t="n">
+        <v>5</v>
+      </c>
+      <c r="T222" t="n">
+        <v>12</v>
+      </c>
+      <c r="U222" t="n">
+        <v>2</v>
+      </c>
+      <c r="V222" t="n">
+        <v>24</v>
+      </c>
+      <c r="W222" t="n">
+        <v>4</v>
+      </c>
+      <c r="X222" t="n">
+        <v>12.84646799643586</v>
+      </c>
+      <c r="Y222" t="n">
         <v>9</v>
-      </c>
-      <c r="T222" t="n">
-        <v>18</v>
-      </c>
-      <c r="U222" t="n">
-        <v>4</v>
-      </c>
-      <c r="V222" t="n">
-        <v>2</v>
-      </c>
-      <c r="W222" t="n">
-        <v>3</v>
-      </c>
-      <c r="X222" t="n">
-        <v>1671</v>
-      </c>
-      <c r="Y222" t="n">
-        <v>42</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>run_2025-08-26_21-49-56</t>
+          <t>run_2025-08-26_21-16-21</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>config_1</t>
+          <t>config_4</t>
         </is>
       </c>
       <c r="C223" t="n">
         <v>2</v>
       </c>
       <c r="D223" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E223" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F223" t="n">
+        <v>2</v>
+      </c>
+      <c r="G223" t="n">
+        <v>10</v>
+      </c>
+      <c r="H223" t="n">
         <v>0.9</v>
       </c>
-      <c r="F223" t="n">
-        <v>2</v>
-      </c>
-      <c r="G223" t="n">
-        <v>10</v>
-      </c>
-      <c r="H223" t="n">
-        <v>0.1</v>
-      </c>
       <c r="I223" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J223" t="n">
         <v>1</v>
@@ -17408,73 +17408,73 @@
         <v>50</v>
       </c>
       <c r="N223" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O223" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P223" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q223" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="R223" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S223" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T223" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U223" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="V223" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="W223" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="X223" t="n">
-        <v>561</v>
+        <v>12.27866011108725</v>
       </c>
       <c r="Y223" t="n">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>run_2025-08-26_21-49-56</t>
+          <t>run_2025-08-26_21-16-21</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>config_1</t>
+          <t>config_4</t>
         </is>
       </c>
       <c r="C224" t="n">
         <v>3</v>
       </c>
       <c r="D224" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E224" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F224" t="n">
+        <v>2</v>
+      </c>
+      <c r="G224" t="n">
+        <v>10</v>
+      </c>
+      <c r="H224" t="n">
         <v>0.9</v>
       </c>
-      <c r="F224" t="n">
-        <v>2</v>
-      </c>
-      <c r="G224" t="n">
-        <v>10</v>
-      </c>
-      <c r="H224" t="n">
-        <v>0.1</v>
-      </c>
       <c r="I224" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J224" t="n">
         <v>1</v>
@@ -17489,73 +17489,73 @@
         <v>50</v>
       </c>
       <c r="N224" t="n">
+        <v>31</v>
+      </c>
+      <c r="O224" t="n">
         <v>11</v>
       </c>
-      <c r="O224" t="n">
-        <v>8</v>
-      </c>
       <c r="P224" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q224" t="n">
         <v>31</v>
       </c>
-      <c r="Q224" t="n">
-        <v>10</v>
-      </c>
       <c r="R224" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="S224" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="T224" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="U224" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="V224" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="W224" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="X224" t="n">
-        <v>1468</v>
+        <v>11.15089396747112</v>
       </c>
       <c r="Y224" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>run_2025-08-26_21-49-56</t>
+          <t>run_2025-08-26_21-16-21</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>config_1</t>
+          <t>config_4</t>
         </is>
       </c>
       <c r="C225" t="n">
         <v>4</v>
       </c>
       <c r="D225" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E225" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F225" t="n">
+        <v>2</v>
+      </c>
+      <c r="G225" t="n">
+        <v>10</v>
+      </c>
+      <c r="H225" t="n">
         <v>0.9</v>
       </c>
-      <c r="F225" t="n">
-        <v>2</v>
-      </c>
-      <c r="G225" t="n">
-        <v>10</v>
-      </c>
-      <c r="H225" t="n">
-        <v>0.1</v>
-      </c>
       <c r="I225" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J225" t="n">
         <v>1</v>
@@ -17570,40 +17570,40 @@
         <v>50</v>
       </c>
       <c r="N225" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="O225" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="P225" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q225" t="n">
+        <v>29</v>
+      </c>
+      <c r="R225" t="n">
         <v>0</v>
       </c>
-      <c r="Q225" t="n">
-        <v>13</v>
-      </c>
-      <c r="R225" t="n">
-        <v>15</v>
-      </c>
       <c r="S225" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T225" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="U225" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V225" t="n">
         <v>1</v>
       </c>
       <c r="W225" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="X225" t="n">
-        <v>883</v>
+        <v>10.59093570920384</v>
       </c>
       <c r="Y225" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="226">
@@ -17614,17 +17614,17 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>config_2</t>
+          <t>config_1</t>
         </is>
       </c>
       <c r="C226" t="n">
         <v>1</v>
       </c>
       <c r="D226" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E226" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="F226" t="n">
         <v>2</v>
@@ -17654,37 +17654,37 @@
         <v>8</v>
       </c>
       <c r="O226" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P226" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q226" t="n">
+        <v>22</v>
+      </c>
+      <c r="R226" t="n">
         <v>0</v>
       </c>
-      <c r="Q226" t="n">
-        <v>1</v>
-      </c>
-      <c r="R226" t="n">
-        <v>4</v>
-      </c>
       <c r="S226" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T226" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="U226" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V226" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="W226" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X226" t="n">
-        <v>659</v>
+        <v>1671</v>
       </c>
       <c r="Y226" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="227">
@@ -17695,17 +17695,17 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>config_2</t>
+          <t>config_1</t>
         </is>
       </c>
       <c r="C227" t="n">
         <v>2</v>
       </c>
       <c r="D227" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E227" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="F227" t="n">
         <v>2</v>
@@ -17732,37 +17732,37 @@
         <v>50</v>
       </c>
       <c r="N227" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O227" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="P227" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q227" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="R227" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S227" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T227" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="U227" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V227" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W227" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="X227" t="n">
-        <v>1270</v>
+        <v>561</v>
       </c>
       <c r="Y227" t="n">
         <v>49</v>
@@ -17776,17 +17776,17 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>config_2</t>
+          <t>config_1</t>
         </is>
       </c>
       <c r="C228" t="n">
         <v>3</v>
       </c>
       <c r="D228" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E228" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="F228" t="n">
         <v>2</v>
@@ -17813,40 +17813,40 @@
         <v>50</v>
       </c>
       <c r="N228" t="n">
+        <v>11</v>
+      </c>
+      <c r="O228" t="n">
+        <v>8</v>
+      </c>
+      <c r="P228" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q228" t="n">
+        <v>10</v>
+      </c>
+      <c r="R228" t="n">
         <v>0</v>
       </c>
-      <c r="O228" t="n">
-        <v>3</v>
-      </c>
-      <c r="P228" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q228" t="n">
-        <v>1</v>
-      </c>
-      <c r="R228" t="n">
-        <v>17</v>
-      </c>
       <c r="S228" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T228" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U228" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V228" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="W228" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="X228" t="n">
-        <v>582</v>
+        <v>1468</v>
       </c>
       <c r="Y228" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="229">
@@ -17857,17 +17857,17 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>config_2</t>
+          <t>config_1</t>
         </is>
       </c>
       <c r="C229" t="n">
         <v>4</v>
       </c>
       <c r="D229" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E229" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="F229" t="n">
         <v>2</v>
@@ -17894,25 +17894,25 @@
         <v>50</v>
       </c>
       <c r="N229" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O229" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="P229" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Q229" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R229" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S229" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T229" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="U229" t="n">
         <v>7</v>
@@ -17921,13 +17921,13 @@
         <v>1</v>
       </c>
       <c r="W229" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X229" t="n">
-        <v>1130</v>
+        <v>883</v>
       </c>
       <c r="Y229" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
     </row>
     <row r="230">
@@ -17938,17 +17938,17 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>config_3</t>
+          <t>config_2</t>
         </is>
       </c>
       <c r="C230" t="n">
         <v>1</v>
       </c>
       <c r="D230" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E230" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="F230" t="n">
         <v>2</v>
@@ -17957,7 +17957,7 @@
         <v>10</v>
       </c>
       <c r="H230" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="I230" t="n">
         <v>50</v>
@@ -17975,40 +17975,40 @@
         <v>50</v>
       </c>
       <c r="N230" t="n">
+        <v>8</v>
+      </c>
+      <c r="O230" t="n">
+        <v>3</v>
+      </c>
+      <c r="P230" t="n">
         <v>0</v>
       </c>
-      <c r="O230" t="n">
-        <v>4</v>
-      </c>
-      <c r="P230" t="n">
-        <v>1</v>
-      </c>
       <c r="Q230" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R230" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S230" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T230" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="U230" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V230" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W230" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="X230" t="n">
-        <v>244</v>
+        <v>659</v>
       </c>
       <c r="Y230" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
     </row>
     <row r="231">
@@ -18019,17 +18019,17 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>config_3</t>
+          <t>config_2</t>
         </is>
       </c>
       <c r="C231" t="n">
         <v>2</v>
       </c>
       <c r="D231" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E231" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="F231" t="n">
         <v>2</v>
@@ -18038,7 +18038,7 @@
         <v>10</v>
       </c>
       <c r="H231" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="I231" t="n">
         <v>50</v>
@@ -18056,40 +18056,40 @@
         <v>50</v>
       </c>
       <c r="N231" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O231" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="P231" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q231" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S231" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T231" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="U231" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V231" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W231" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="X231" t="n">
-        <v>74</v>
+        <v>1270</v>
       </c>
       <c r="Y231" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="232">
@@ -18100,17 +18100,17 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>config_3</t>
+          <t>config_2</t>
         </is>
       </c>
       <c r="C232" t="n">
         <v>3</v>
       </c>
       <c r="D232" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E232" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="F232" t="n">
         <v>2</v>
@@ -18119,7 +18119,7 @@
         <v>10</v>
       </c>
       <c r="H232" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="I232" t="n">
         <v>50</v>
@@ -18137,40 +18137,40 @@
         <v>50</v>
       </c>
       <c r="N232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O232" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P232" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q232" t="n">
         <v>1</v>
       </c>
       <c r="R232" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="S232" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="T232" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U232" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V232" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="W232" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X232" t="n">
-        <v>147</v>
+        <v>582</v>
       </c>
       <c r="Y232" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="233">
@@ -18181,17 +18181,17 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>config_3</t>
+          <t>config_2</t>
         </is>
       </c>
       <c r="C233" t="n">
         <v>4</v>
       </c>
       <c r="D233" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E233" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="F233" t="n">
         <v>2</v>
@@ -18200,7 +18200,7 @@
         <v>10</v>
       </c>
       <c r="H233" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="I233" t="n">
         <v>50</v>
@@ -18218,40 +18218,40 @@
         <v>50</v>
       </c>
       <c r="N233" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O233" t="n">
+        <v>11</v>
+      </c>
+      <c r="P233" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>1</v>
+      </c>
+      <c r="R233" t="n">
+        <v>16</v>
+      </c>
+      <c r="S233" t="n">
+        <v>11</v>
+      </c>
+      <c r="T233" t="n">
         <v>0</v>
       </c>
-      <c r="P233" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q233" t="n">
-        <v>1</v>
-      </c>
-      <c r="R233" t="n">
-        <v>0</v>
-      </c>
-      <c r="S233" t="n">
-        <v>0</v>
-      </c>
-      <c r="T233" t="n">
-        <v>3</v>
-      </c>
       <c r="U233" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="V233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W233" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="X233" t="n">
-        <v>101</v>
+        <v>1130</v>
       </c>
       <c r="Y233" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="234">
@@ -18262,17 +18262,17 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>config_4</t>
+          <t>config_3</t>
         </is>
       </c>
       <c r="C234" t="n">
         <v>1</v>
       </c>
       <c r="D234" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E234" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="F234" t="n">
         <v>2</v>
@@ -18299,16 +18299,16 @@
         <v>50</v>
       </c>
       <c r="N234" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O234" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P234" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q234" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R234" t="n">
         <v>3</v>
@@ -18317,22 +18317,22 @@
         <v>1</v>
       </c>
       <c r="T234" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U234" t="n">
+        <v>2</v>
+      </c>
+      <c r="V234" t="n">
         <v>0</v>
       </c>
-      <c r="V234" t="n">
-        <v>3</v>
-      </c>
       <c r="W234" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="X234" t="n">
-        <v>127</v>
+        <v>244</v>
       </c>
       <c r="Y234" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="235">
@@ -18343,17 +18343,17 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>config_4</t>
+          <t>config_3</t>
         </is>
       </c>
       <c r="C235" t="n">
         <v>2</v>
       </c>
       <c r="D235" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E235" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="F235" t="n">
         <v>2</v>
@@ -18380,40 +18380,40 @@
         <v>50</v>
       </c>
       <c r="N235" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O235" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P235" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q235" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R235" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S235" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T235" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U235" t="n">
+        <v>5</v>
+      </c>
+      <c r="V235" t="n">
+        <v>3</v>
+      </c>
+      <c r="W235" t="n">
         <v>0</v>
       </c>
-      <c r="V235" t="n">
-        <v>0</v>
-      </c>
-      <c r="W235" t="n">
-        <v>5</v>
-      </c>
       <c r="X235" t="n">
-        <v>140</v>
+        <v>74</v>
       </c>
       <c r="Y235" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="236">
@@ -18424,17 +18424,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>config_4</t>
+          <t>config_3</t>
         </is>
       </c>
       <c r="C236" t="n">
         <v>3</v>
       </c>
       <c r="D236" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E236" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="F236" t="n">
         <v>2</v>
@@ -18464,37 +18464,37 @@
         <v>1</v>
       </c>
       <c r="O236" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P236" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q236" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R236" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S236" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T236" t="n">
+        <v>3</v>
+      </c>
+      <c r="U236" t="n">
         <v>0</v>
       </c>
-      <c r="U236" t="n">
-        <v>1</v>
-      </c>
       <c r="V236" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X236" t="n">
-        <v>73</v>
+        <v>147</v>
       </c>
       <c r="Y236" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="237">
@@ -18505,17 +18505,17 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>config_4</t>
+          <t>config_3</t>
         </is>
       </c>
       <c r="C237" t="n">
         <v>4</v>
       </c>
       <c r="D237" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E237" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="F237" t="n">
         <v>2</v>
@@ -18542,39 +18542,363 @@
         <v>50</v>
       </c>
       <c r="N237" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O237" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P237" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q237" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="R237" t="n">
         <v>0</v>
       </c>
       <c r="S237" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T237" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U237" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V237" t="n">
+        <v>0</v>
+      </c>
+      <c r="W237" t="n">
+        <v>8</v>
+      </c>
+      <c r="X237" t="n">
+        <v>101</v>
+      </c>
+      <c r="Y237" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_21-49-56</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>1</v>
+      </c>
+      <c r="D238" t="n">
+        <v>4</v>
+      </c>
+      <c r="E238" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F238" t="n">
+        <v>2</v>
+      </c>
+      <c r="G238" t="n">
+        <v>10</v>
+      </c>
+      <c r="H238" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I238" t="n">
+        <v>50</v>
+      </c>
+      <c r="J238" t="n">
+        <v>1</v>
+      </c>
+      <c r="K238" t="n">
+        <v>5</v>
+      </c>
+      <c r="L238" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M238" t="n">
+        <v>50</v>
+      </c>
+      <c r="N238" t="n">
+        <v>1</v>
+      </c>
+      <c r="O238" t="n">
+        <v>5</v>
+      </c>
+      <c r="P238" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q238" t="n">
+        <v>7</v>
+      </c>
+      <c r="R238" t="n">
+        <v>3</v>
+      </c>
+      <c r="S238" t="n">
+        <v>1</v>
+      </c>
+      <c r="T238" t="n">
+        <v>2</v>
+      </c>
+      <c r="U238" t="n">
+        <v>0</v>
+      </c>
+      <c r="V238" t="n">
+        <v>3</v>
+      </c>
+      <c r="W238" t="n">
+        <v>2</v>
+      </c>
+      <c r="X238" t="n">
+        <v>127</v>
+      </c>
+      <c r="Y238" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_21-49-56</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>2</v>
+      </c>
+      <c r="D239" t="n">
+        <v>4</v>
+      </c>
+      <c r="E239" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F239" t="n">
+        <v>2</v>
+      </c>
+      <c r="G239" t="n">
+        <v>10</v>
+      </c>
+      <c r="H239" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I239" t="n">
+        <v>50</v>
+      </c>
+      <c r="J239" t="n">
+        <v>1</v>
+      </c>
+      <c r="K239" t="n">
+        <v>5</v>
+      </c>
+      <c r="L239" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M239" t="n">
+        <v>50</v>
+      </c>
+      <c r="N239" t="n">
+        <v>1</v>
+      </c>
+      <c r="O239" t="n">
+        <v>6</v>
+      </c>
+      <c r="P239" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q239" t="n">
+        <v>3</v>
+      </c>
+      <c r="R239" t="n">
+        <v>6</v>
+      </c>
+      <c r="S239" t="n">
+        <v>4</v>
+      </c>
+      <c r="T239" t="n">
+        <v>1</v>
+      </c>
+      <c r="U239" t="n">
+        <v>0</v>
+      </c>
+      <c r="V239" t="n">
+        <v>0</v>
+      </c>
+      <c r="W239" t="n">
+        <v>5</v>
+      </c>
+      <c r="X239" t="n">
+        <v>140</v>
+      </c>
+      <c r="Y239" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_21-49-56</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>3</v>
+      </c>
+      <c r="D240" t="n">
+        <v>4</v>
+      </c>
+      <c r="E240" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F240" t="n">
+        <v>2</v>
+      </c>
+      <c r="G240" t="n">
+        <v>10</v>
+      </c>
+      <c r="H240" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I240" t="n">
+        <v>50</v>
+      </c>
+      <c r="J240" t="n">
+        <v>1</v>
+      </c>
+      <c r="K240" t="n">
+        <v>5</v>
+      </c>
+      <c r="L240" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M240" t="n">
+        <v>50</v>
+      </c>
+      <c r="N240" t="n">
+        <v>1</v>
+      </c>
+      <c r="O240" t="n">
+        <v>2</v>
+      </c>
+      <c r="P240" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q240" t="n">
+        <v>3</v>
+      </c>
+      <c r="R240" t="n">
+        <v>1</v>
+      </c>
+      <c r="S240" t="n">
+        <v>4</v>
+      </c>
+      <c r="T240" t="n">
+        <v>0</v>
+      </c>
+      <c r="U240" t="n">
+        <v>1</v>
+      </c>
+      <c r="V240" t="n">
+        <v>4</v>
+      </c>
+      <c r="W240" t="n">
+        <v>0</v>
+      </c>
+      <c r="X240" t="n">
+        <v>73</v>
+      </c>
+      <c r="Y240" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_21-49-56</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>4</v>
+      </c>
+      <c r="D241" t="n">
+        <v>4</v>
+      </c>
+      <c r="E241" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F241" t="n">
+        <v>2</v>
+      </c>
+      <c r="G241" t="n">
+        <v>10</v>
+      </c>
+      <c r="H241" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I241" t="n">
+        <v>50</v>
+      </c>
+      <c r="J241" t="n">
+        <v>1</v>
+      </c>
+      <c r="K241" t="n">
+        <v>5</v>
+      </c>
+      <c r="L241" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M241" t="n">
+        <v>50</v>
+      </c>
+      <c r="N241" t="n">
+        <v>5</v>
+      </c>
+      <c r="O241" t="n">
+        <v>8</v>
+      </c>
+      <c r="P241" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q241" t="n">
+        <v>15</v>
+      </c>
+      <c r="R241" t="n">
+        <v>0</v>
+      </c>
+      <c r="S241" t="n">
+        <v>5</v>
+      </c>
+      <c r="T241" t="n">
+        <v>4</v>
+      </c>
+      <c r="U241" t="n">
+        <v>4</v>
+      </c>
+      <c r="V241" t="n">
         <v>11</v>
       </c>
-      <c r="W237" t="n">
+      <c r="W241" t="n">
         <v>0</v>
       </c>
-      <c r="X237" t="n">
+      <c r="X241" t="n">
         <v>528</v>
       </c>
-      <c r="Y237" t="n">
+      <c r="Y241" t="n">
         <v>49</v>
       </c>
     </row>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y241"/>
+  <dimension ref="A1:Y245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -18902,6 +18902,330 @@
         <v>49</v>
       </c>
     </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_22-50-33</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>1</v>
+      </c>
+      <c r="D242" t="n">
+        <v>1</v>
+      </c>
+      <c r="E242" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F242" t="n">
+        <v>2</v>
+      </c>
+      <c r="G242" t="n">
+        <v>10</v>
+      </c>
+      <c r="H242" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I242" t="n">
+        <v>20</v>
+      </c>
+      <c r="J242" t="n">
+        <v>1</v>
+      </c>
+      <c r="K242" t="n">
+        <v>10</v>
+      </c>
+      <c r="L242" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M242" t="n">
+        <v>50</v>
+      </c>
+      <c r="N242" t="n">
+        <v>17</v>
+      </c>
+      <c r="O242" t="n">
+        <v>1</v>
+      </c>
+      <c r="P242" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q242" t="n">
+        <v>17</v>
+      </c>
+      <c r="R242" t="n">
+        <v>5</v>
+      </c>
+      <c r="S242" t="n">
+        <v>1</v>
+      </c>
+      <c r="T242" t="n">
+        <v>0</v>
+      </c>
+      <c r="U242" t="n">
+        <v>17</v>
+      </c>
+      <c r="V242" t="n">
+        <v>0</v>
+      </c>
+      <c r="W242" t="n">
+        <v>11</v>
+      </c>
+      <c r="X242" t="n">
+        <v>64.01356070820761</v>
+      </c>
+      <c r="Y242" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_23-01-40</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>1</v>
+      </c>
+      <c r="D243" t="n">
+        <v>1</v>
+      </c>
+      <c r="E243" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F243" t="n">
+        <v>2</v>
+      </c>
+      <c r="G243" t="n">
+        <v>10</v>
+      </c>
+      <c r="H243" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I243" t="n">
+        <v>20</v>
+      </c>
+      <c r="J243" t="n">
+        <v>1</v>
+      </c>
+      <c r="K243" t="n">
+        <v>10</v>
+      </c>
+      <c r="L243" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M243" t="n">
+        <v>50</v>
+      </c>
+      <c r="N243" t="n">
+        <v>9</v>
+      </c>
+      <c r="O243" t="n">
+        <v>0</v>
+      </c>
+      <c r="P243" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q243" t="n">
+        <v>11</v>
+      </c>
+      <c r="R243" t="n">
+        <v>15</v>
+      </c>
+      <c r="S243" t="n">
+        <v>11</v>
+      </c>
+      <c r="T243" t="n">
+        <v>27</v>
+      </c>
+      <c r="U243" t="n">
+        <v>11</v>
+      </c>
+      <c r="V243" t="n">
+        <v>0</v>
+      </c>
+      <c r="W243" t="n">
+        <v>23</v>
+      </c>
+      <c r="X243" t="n">
+        <v>70.03122164816341</v>
+      </c>
+      <c r="Y243" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_23-01-40</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>2</v>
+      </c>
+      <c r="D244" t="n">
+        <v>1</v>
+      </c>
+      <c r="E244" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F244" t="n">
+        <v>2</v>
+      </c>
+      <c r="G244" t="n">
+        <v>10</v>
+      </c>
+      <c r="H244" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I244" t="n">
+        <v>20</v>
+      </c>
+      <c r="J244" t="n">
+        <v>1</v>
+      </c>
+      <c r="K244" t="n">
+        <v>10</v>
+      </c>
+      <c r="L244" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M244" t="n">
+        <v>50</v>
+      </c>
+      <c r="N244" t="n">
+        <v>3</v>
+      </c>
+      <c r="O244" t="n">
+        <v>8</v>
+      </c>
+      <c r="P244" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q244" t="n">
+        <v>3</v>
+      </c>
+      <c r="R244" t="n">
+        <v>12</v>
+      </c>
+      <c r="S244" t="n">
+        <v>9</v>
+      </c>
+      <c r="T244" t="n">
+        <v>28</v>
+      </c>
+      <c r="U244" t="n">
+        <v>12</v>
+      </c>
+      <c r="V244" t="n">
+        <v>3</v>
+      </c>
+      <c r="W244" t="n">
+        <v>9</v>
+      </c>
+      <c r="X244" t="n">
+        <v>62.27399231295124</v>
+      </c>
+      <c r="Y244" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_23-10-44</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>1</v>
+      </c>
+      <c r="D245" t="n">
+        <v>1</v>
+      </c>
+      <c r="E245" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F245" t="n">
+        <v>2</v>
+      </c>
+      <c r="G245" t="n">
+        <v>10</v>
+      </c>
+      <c r="H245" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I245" t="n">
+        <v>20</v>
+      </c>
+      <c r="J245" t="n">
+        <v>1</v>
+      </c>
+      <c r="K245" t="n">
+        <v>10</v>
+      </c>
+      <c r="L245" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M245" t="n">
+        <v>50</v>
+      </c>
+      <c r="N245" t="n">
+        <v>3</v>
+      </c>
+      <c r="O245" t="n">
+        <v>11</v>
+      </c>
+      <c r="P245" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q245" t="n">
+        <v>3</v>
+      </c>
+      <c r="R245" t="n">
+        <v>24</v>
+      </c>
+      <c r="S245" t="n">
+        <v>25</v>
+      </c>
+      <c r="T245" t="n">
+        <v>3</v>
+      </c>
+      <c r="U245" t="n">
+        <v>3</v>
+      </c>
+      <c r="V245" t="n">
+        <v>18</v>
+      </c>
+      <c r="W245" t="n">
+        <v>3</v>
+      </c>
+      <c r="X245" t="n">
+        <v>10.87091483833755</v>
+      </c>
+      <c r="Y245" t="n">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y2"/>
+  <dimension ref="A1:Y7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -663,6 +663,413 @@
         <v>19</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_23-50-56</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I3" t="n">
+        <v>20</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>50</v>
+      </c>
+      <c r="N3" t="n">
+        <v>12</v>
+      </c>
+      <c r="O3" t="n">
+        <v>14</v>
+      </c>
+      <c r="P3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>12</v>
+      </c>
+      <c r="R3" t="n">
+        <v>20</v>
+      </c>
+      <c r="S3" t="n">
+        <v>14</v>
+      </c>
+      <c r="T3" t="n">
+        <v>14</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V3" t="n">
+        <v>6</v>
+      </c>
+      <c r="W3" t="n">
+        <v>14</v>
+      </c>
+      <c r="X3" t="n">
+        <v>56.64479768115913</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_23-50-56</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>50</v>
+      </c>
+      <c r="N4" t="n">
+        <v>31</v>
+      </c>
+      <c r="O4" t="n">
+        <v>30</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>31</v>
+      </c>
+      <c r="R4" t="n">
+        <v>17</v>
+      </c>
+      <c r="S4" t="n">
+        <v>13</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>31</v>
+      </c>
+      <c r="V4" t="n">
+        <v>30</v>
+      </c>
+      <c r="W4" t="n">
+        <v>24</v>
+      </c>
+      <c r="X4" t="n">
+        <v>44.76846039852396</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_23-50-56</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I5" t="n">
+        <v>20</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>50</v>
+      </c>
+      <c r="N5" t="n">
+        <v>31</v>
+      </c>
+      <c r="O5" t="n">
+        <v>22</v>
+      </c>
+      <c r="P5" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+      <c r="R5" t="n">
+        <v>15</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="n">
+        <v>16</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>3</v>
+      </c>
+      <c r="W5" t="n">
+        <v>22</v>
+      </c>
+      <c r="X5" t="n">
+        <v>63.3563177068533</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_23-50-56</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I6" t="n">
+        <v>20</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>10</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>50</v>
+      </c>
+      <c r="N6" t="n">
+        <v>30</v>
+      </c>
+      <c r="O6" t="n">
+        <v>31</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>30</v>
+      </c>
+      <c r="R6" t="n">
+        <v>22</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
+      </c>
+      <c r="V6" t="n">
+        <v>31</v>
+      </c>
+      <c r="W6" t="n">
+        <v>10</v>
+      </c>
+      <c r="X6" t="n">
+        <v>62.06612510097931</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>run_2025-08-26_23-50-56</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I7" t="n">
+        <v>20</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>50</v>
+      </c>
+      <c r="N7" t="n">
+        <v>24</v>
+      </c>
+      <c r="O7" t="n">
+        <v>15</v>
+      </c>
+      <c r="P7" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>10</v>
+      </c>
+      <c r="R7" t="n">
+        <v>31</v>
+      </c>
+      <c r="S7" t="n">
+        <v>22</v>
+      </c>
+      <c r="T7" t="n">
+        <v>25</v>
+      </c>
+      <c r="U7" t="n">
+        <v>21</v>
+      </c>
+      <c r="V7" t="n">
+        <v>9</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y7"/>
+  <dimension ref="A1:Y33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1070,6 +1070,2114 @@
         <v>0</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_11-05-00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I8" t="n">
+        <v>20</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>10</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>50</v>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>9</v>
+      </c>
+      <c r="R8" t="n">
+        <v>22</v>
+      </c>
+      <c r="S8" t="n">
+        <v>7</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>16</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>15</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_11-09-45</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I9" t="n">
+        <v>20</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>10</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>50</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>30</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>13</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>31</v>
+      </c>
+      <c r="T9" t="n">
+        <v>30</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>13</v>
+      </c>
+      <c r="W9" t="n">
+        <v>23</v>
+      </c>
+      <c r="X9" t="n">
+        <v>70.04860773670998</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_11-17-42</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I10" t="n">
+        <v>20</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>10</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N10" t="n">
+        <v>29</v>
+      </c>
+      <c r="O10" t="n">
+        <v>29</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6</v>
+      </c>
+      <c r="S10" t="n">
+        <v>30</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>29</v>
+      </c>
+      <c r="W10" t="n">
+        <v>8</v>
+      </c>
+      <c r="X10" t="n">
+        <v>79.98669109803332</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_11-17-42</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>10</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I11" t="n">
+        <v>20</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>10</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>50</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>31</v>
+      </c>
+      <c r="R11" t="n">
+        <v>10</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>31</v>
+      </c>
+      <c r="V11" t="n">
+        <v>11</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>89.84110741054994</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_11-17-42</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I12" t="n">
+        <v>20</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>50</v>
+      </c>
+      <c r="N12" t="n">
+        <v>24</v>
+      </c>
+      <c r="O12" t="n">
+        <v>8</v>
+      </c>
+      <c r="P12" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>24</v>
+      </c>
+      <c r="R12" t="n">
+        <v>16</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>16</v>
+      </c>
+      <c r="U12" t="n">
+        <v>16</v>
+      </c>
+      <c r="V12" t="n">
+        <v>24</v>
+      </c>
+      <c r="W12" t="n">
+        <v>26</v>
+      </c>
+      <c r="X12" t="n">
+        <v>69.60868196518105</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_12-07-08</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I13" t="n">
+        <v>20</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>10</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>50</v>
+      </c>
+      <c r="N13" t="n">
+        <v>26</v>
+      </c>
+      <c r="O13" t="n">
+        <v>11</v>
+      </c>
+      <c r="P13" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4</v>
+      </c>
+      <c r="R13" t="n">
+        <v>26</v>
+      </c>
+      <c r="S13" t="n">
+        <v>11</v>
+      </c>
+      <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>26</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>28</v>
+      </c>
+      <c r="X13" t="n">
+        <v>62.82579950473799</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_12-07-54</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>10</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I14" t="n">
+        <v>20</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>10</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>50</v>
+      </c>
+      <c r="N14" t="n">
+        <v>27</v>
+      </c>
+      <c r="O14" t="n">
+        <v>4</v>
+      </c>
+      <c r="P14" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>27</v>
+      </c>
+      <c r="R14" t="n">
+        <v>27</v>
+      </c>
+      <c r="S14" t="n">
+        <v>27</v>
+      </c>
+      <c r="T14" t="n">
+        <v>13</v>
+      </c>
+      <c r="U14" t="n">
+        <v>25</v>
+      </c>
+      <c r="V14" t="n">
+        <v>8</v>
+      </c>
+      <c r="W14" t="n">
+        <v>4</v>
+      </c>
+      <c r="X14" t="n">
+        <v>71.3219414105654</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_12-07-54</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>10</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I15" t="n">
+        <v>20</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>10</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>50</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>26</v>
+      </c>
+      <c r="P15" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>30</v>
+      </c>
+      <c r="R15" t="n">
+        <v>23</v>
+      </c>
+      <c r="S15" t="n">
+        <v>26</v>
+      </c>
+      <c r="T15" t="n">
+        <v>10</v>
+      </c>
+      <c r="U15" t="n">
+        <v>30</v>
+      </c>
+      <c r="V15" t="n">
+        <v>29</v>
+      </c>
+      <c r="W15" t="n">
+        <v>26</v>
+      </c>
+      <c r="X15" t="n">
+        <v>81.14711086205445</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_12-07-54</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>10</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I16" t="n">
+        <v>20</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>10</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>50</v>
+      </c>
+      <c r="N16" t="n">
+        <v>6</v>
+      </c>
+      <c r="O16" t="n">
+        <v>6</v>
+      </c>
+      <c r="P16" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>12</v>
+      </c>
+      <c r="R16" t="n">
+        <v>28</v>
+      </c>
+      <c r="S16" t="n">
+        <v>21</v>
+      </c>
+      <c r="T16" t="n">
+        <v>28</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>12</v>
+      </c>
+      <c r="W16" t="n">
+        <v>11</v>
+      </c>
+      <c r="X16" t="n">
+        <v>90.81424630863604</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_12-07-54</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I17" t="n">
+        <v>20</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>10</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>50</v>
+      </c>
+      <c r="N17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O17" t="n">
+        <v>23</v>
+      </c>
+      <c r="P17" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>26</v>
+      </c>
+      <c r="R17" t="n">
+        <v>11</v>
+      </c>
+      <c r="S17" t="n">
+        <v>28</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>26</v>
+      </c>
+      <c r="V17" t="n">
+        <v>11</v>
+      </c>
+      <c r="W17" t="n">
+        <v>28</v>
+      </c>
+      <c r="X17" t="n">
+        <v>63.52567745171968</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_12-07-54</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>10</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I18" t="n">
+        <v>20</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>50</v>
+      </c>
+      <c r="N18" t="n">
+        <v>12</v>
+      </c>
+      <c r="O18" t="n">
+        <v>30</v>
+      </c>
+      <c r="P18" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>12</v>
+      </c>
+      <c r="R18" t="n">
+        <v>12</v>
+      </c>
+      <c r="S18" t="n">
+        <v>14</v>
+      </c>
+      <c r="T18" t="n">
+        <v>30</v>
+      </c>
+      <c r="U18" t="n">
+        <v>14</v>
+      </c>
+      <c r="V18" t="n">
+        <v>30</v>
+      </c>
+      <c r="W18" t="n">
+        <v>14</v>
+      </c>
+      <c r="X18" t="n">
+        <v>50.58447819361012</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_12-07-54</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>10</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I19" t="n">
+        <v>20</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>50</v>
+      </c>
+      <c r="N19" t="n">
+        <v>30</v>
+      </c>
+      <c r="O19" t="n">
+        <v>22</v>
+      </c>
+      <c r="P19" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>27</v>
+      </c>
+      <c r="R19" t="n">
+        <v>27</v>
+      </c>
+      <c r="S19" t="n">
+        <v>30</v>
+      </c>
+      <c r="T19" t="n">
+        <v>7</v>
+      </c>
+      <c r="U19" t="n">
+        <v>7</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>9</v>
+      </c>
+      <c r="X19" t="n">
+        <v>90.71454400943628</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_12-07-54</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>10</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I20" t="n">
+        <v>20</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>10</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>50</v>
+      </c>
+      <c r="N20" t="n">
+        <v>22</v>
+      </c>
+      <c r="O20" t="n">
+        <v>30</v>
+      </c>
+      <c r="P20" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>28</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2</v>
+      </c>
+      <c r="S20" t="n">
+        <v>26</v>
+      </c>
+      <c r="T20" t="n">
+        <v>16</v>
+      </c>
+      <c r="U20" t="n">
+        <v>28</v>
+      </c>
+      <c r="V20" t="n">
+        <v>30</v>
+      </c>
+      <c r="W20" t="n">
+        <v>30</v>
+      </c>
+      <c r="X20" t="n">
+        <v>71.88394812573939</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_12-07-54</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I21" t="n">
+        <v>20</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>10</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>50</v>
+      </c>
+      <c r="N21" t="n">
+        <v>14</v>
+      </c>
+      <c r="O21" t="n">
+        <v>8</v>
+      </c>
+      <c r="P21" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>13</v>
+      </c>
+      <c r="R21" t="n">
+        <v>13</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="n">
+        <v>8</v>
+      </c>
+      <c r="U21" t="n">
+        <v>23</v>
+      </c>
+      <c r="V21" t="n">
+        <v>24</v>
+      </c>
+      <c r="W21" t="n">
+        <v>19</v>
+      </c>
+      <c r="X21" t="n">
+        <v>80.21186065863191</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_12-07-54</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>10</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I22" t="n">
+        <v>20</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>10</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M22" t="n">
+        <v>50</v>
+      </c>
+      <c r="N22" t="n">
+        <v>10</v>
+      </c>
+      <c r="O22" t="n">
+        <v>23</v>
+      </c>
+      <c r="P22" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>17</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>24</v>
+      </c>
+      <c r="T22" t="n">
+        <v>31</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>31</v>
+      </c>
+      <c r="W22" t="n">
+        <v>17</v>
+      </c>
+      <c r="X22" t="n">
+        <v>71.64900683348328</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_12-07-54</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>10</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I23" t="n">
+        <v>20</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>10</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M23" t="n">
+        <v>50</v>
+      </c>
+      <c r="N23" t="n">
+        <v>27</v>
+      </c>
+      <c r="O23" t="n">
+        <v>10</v>
+      </c>
+      <c r="P23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>28</v>
+      </c>
+      <c r="R23" t="n">
+        <v>28</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>10</v>
+      </c>
+      <c r="U23" t="n">
+        <v>10</v>
+      </c>
+      <c r="V23" t="n">
+        <v>28</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>60.44199631234798</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_12-07-54</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>10</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I24" t="n">
+        <v>20</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>10</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M24" t="n">
+        <v>50</v>
+      </c>
+      <c r="N24" t="n">
+        <v>7</v>
+      </c>
+      <c r="O24" t="n">
+        <v>7</v>
+      </c>
+      <c r="P24" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>30</v>
+      </c>
+      <c r="R24" t="n">
+        <v>30</v>
+      </c>
+      <c r="S24" t="n">
+        <v>19</v>
+      </c>
+      <c r="T24" t="n">
+        <v>13</v>
+      </c>
+      <c r="U24" t="n">
+        <v>31</v>
+      </c>
+      <c r="V24" t="n">
+        <v>7</v>
+      </c>
+      <c r="W24" t="n">
+        <v>7</v>
+      </c>
+      <c r="X24" t="n">
+        <v>81.09268309401315</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_12-07-54</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>10</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I25" t="n">
+        <v>20</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>10</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M25" t="n">
+        <v>50</v>
+      </c>
+      <c r="N25" t="n">
+        <v>6</v>
+      </c>
+      <c r="O25" t="n">
+        <v>24</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>12</v>
+      </c>
+      <c r="R25" t="n">
+        <v>12</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>24</v>
+      </c>
+      <c r="U25" t="n">
+        <v>12</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
+        <v>25</v>
+      </c>
+      <c r="X25" t="n">
+        <v>71.36676446325041</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_12-07-54</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" t="n">
+        <v>10</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I26" t="n">
+        <v>20</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>10</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M26" t="n">
+        <v>50</v>
+      </c>
+      <c r="N26" t="n">
+        <v>10</v>
+      </c>
+      <c r="O26" t="n">
+        <v>13</v>
+      </c>
+      <c r="P26" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>21</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2</v>
+      </c>
+      <c r="S26" t="n">
+        <v>17</v>
+      </c>
+      <c r="T26" t="n">
+        <v>13</v>
+      </c>
+      <c r="U26" t="n">
+        <v>21</v>
+      </c>
+      <c r="V26" t="n">
+        <v>30</v>
+      </c>
+      <c r="W26" t="n">
+        <v>13</v>
+      </c>
+      <c r="X26" t="n">
+        <v>79.69783946883608</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_12-07-54</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" t="n">
+        <v>10</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I27" t="n">
+        <v>20</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>10</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M27" t="n">
+        <v>50</v>
+      </c>
+      <c r="N27" t="n">
+        <v>6</v>
+      </c>
+      <c r="O27" t="n">
+        <v>10</v>
+      </c>
+      <c r="P27" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>6</v>
+      </c>
+      <c r="R27" t="n">
+        <v>17</v>
+      </c>
+      <c r="S27" t="n">
+        <v>23</v>
+      </c>
+      <c r="T27" t="n">
+        <v>23</v>
+      </c>
+      <c r="U27" t="n">
+        <v>30</v>
+      </c>
+      <c r="V27" t="n">
+        <v>12</v>
+      </c>
+      <c r="W27" t="n">
+        <v>6</v>
+      </c>
+      <c r="X27" t="n">
+        <v>81.08182666511398</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_12-07-54</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>5</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" t="n">
+        <v>10</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I28" t="n">
+        <v>20</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>10</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M28" t="n">
+        <v>50</v>
+      </c>
+      <c r="N28" t="n">
+        <v>20</v>
+      </c>
+      <c r="O28" t="n">
+        <v>30</v>
+      </c>
+      <c r="P28" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>12</v>
+      </c>
+      <c r="R28" t="n">
+        <v>24</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" t="n">
+        <v>27</v>
+      </c>
+      <c r="U28" t="n">
+        <v>30</v>
+      </c>
+      <c r="V28" t="n">
+        <v>27</v>
+      </c>
+      <c r="W28" t="n">
+        <v>26</v>
+      </c>
+      <c r="X28" t="n">
+        <v>98.43107781837801</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_12-07-54</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>10</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I29" t="n">
+        <v>20</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>10</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M29" t="n">
+        <v>50</v>
+      </c>
+      <c r="N29" t="n">
+        <v>9</v>
+      </c>
+      <c r="O29" t="n">
+        <v>29</v>
+      </c>
+      <c r="P29" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>29</v>
+      </c>
+      <c r="R29" t="n">
+        <v>29</v>
+      </c>
+      <c r="S29" t="n">
+        <v>20</v>
+      </c>
+      <c r="T29" t="n">
+        <v>10</v>
+      </c>
+      <c r="U29" t="n">
+        <v>9</v>
+      </c>
+      <c r="V29" t="n">
+        <v>29</v>
+      </c>
+      <c r="W29" t="n">
+        <v>31</v>
+      </c>
+      <c r="X29" t="n">
+        <v>74.00241605743199</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_12-07-54</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" t="n">
+        <v>10</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I30" t="n">
+        <v>20</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>10</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M30" t="n">
+        <v>50</v>
+      </c>
+      <c r="N30" t="n">
+        <v>26</v>
+      </c>
+      <c r="O30" t="n">
+        <v>26</v>
+      </c>
+      <c r="P30" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2</v>
+      </c>
+      <c r="T30" t="n">
+        <v>20</v>
+      </c>
+      <c r="U30" t="n">
+        <v>11</v>
+      </c>
+      <c r="V30" t="n">
+        <v>31</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2</v>
+      </c>
+      <c r="X30" t="n">
+        <v>71.13692263849397</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_12-07-54</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" t="n">
+        <v>10</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I31" t="n">
+        <v>20</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>10</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M31" t="n">
+        <v>50</v>
+      </c>
+      <c r="N31" t="n">
+        <v>16</v>
+      </c>
+      <c r="O31" t="n">
+        <v>28</v>
+      </c>
+      <c r="P31" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>16</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>11</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
+      </c>
+      <c r="V31" t="n">
+        <v>25</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1</v>
+      </c>
+      <c r="X31" t="n">
+        <v>70.78469326972854</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_12-07-54</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" t="n">
+        <v>10</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I32" t="n">
+        <v>20</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>10</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M32" t="n">
+        <v>50</v>
+      </c>
+      <c r="N32" t="n">
+        <v>7</v>
+      </c>
+      <c r="O32" t="n">
+        <v>30</v>
+      </c>
+      <c r="P32" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>7</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7</v>
+      </c>
+      <c r="S32" t="n">
+        <v>12</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>10</v>
+      </c>
+      <c r="V32" t="n">
+        <v>30</v>
+      </c>
+      <c r="W32" t="n">
+        <v>17</v>
+      </c>
+      <c r="X32" t="n">
+        <v>70.25909423750996</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_12-07-54</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>5</v>
+      </c>
+      <c r="D33" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" t="n">
+        <v>10</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I33" t="n">
+        <v>20</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>10</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M33" t="n">
+        <v>50</v>
+      </c>
+      <c r="N33" t="n">
+        <v>22</v>
+      </c>
+      <c r="O33" t="n">
+        <v>11</v>
+      </c>
+      <c r="P33" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>26</v>
+      </c>
+      <c r="R33" t="n">
+        <v>26</v>
+      </c>
+      <c r="S33" t="n">
+        <v>28</v>
+      </c>
+      <c r="T33" t="n">
+        <v>16</v>
+      </c>
+      <c r="U33" t="n">
+        <v>22</v>
+      </c>
+      <c r="V33" t="n">
+        <v>11</v>
+      </c>
+      <c r="W33" t="n">
+        <v>28</v>
+      </c>
+      <c r="X33" t="n">
+        <v>51.93248491785744</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y33"/>
+  <dimension ref="A1:Y38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -3178,6 +3178,411 @@
         <v>19</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_12-45-14</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" t="n">
+        <v>10</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I34" t="n">
+        <v>20</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>10</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M34" t="n">
+        <v>50</v>
+      </c>
+      <c r="N34" t="n">
+        <v>24</v>
+      </c>
+      <c r="O34" t="n">
+        <v>4</v>
+      </c>
+      <c r="P34" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>4</v>
+      </c>
+      <c r="R34" t="n">
+        <v>24</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>4</v>
+      </c>
+      <c r="V34" t="n">
+        <v>3</v>
+      </c>
+      <c r="W34" t="n">
+        <v>26</v>
+      </c>
+      <c r="X34" t="n">
+        <v>73.3884704842657</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_12-45-14</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" t="n">
+        <v>10</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I35" t="n">
+        <v>20</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>10</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M35" t="n">
+        <v>50</v>
+      </c>
+      <c r="N35" t="n">
+        <v>22</v>
+      </c>
+      <c r="O35" t="n">
+        <v>3</v>
+      </c>
+      <c r="P35" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>22</v>
+      </c>
+      <c r="R35" t="n">
+        <v>24</v>
+      </c>
+      <c r="S35" t="n">
+        <v>22</v>
+      </c>
+      <c r="T35" t="n">
+        <v>28</v>
+      </c>
+      <c r="U35" t="n">
+        <v>24</v>
+      </c>
+      <c r="V35" t="n">
+        <v>28</v>
+      </c>
+      <c r="W35" t="n">
+        <v>27</v>
+      </c>
+      <c r="X35" t="n">
+        <v>89.8477442977694</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_12-45-14</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" t="n">
+        <v>10</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I36" t="n">
+        <v>20</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>10</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M36" t="n">
+        <v>50</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>13</v>
+      </c>
+      <c r="P36" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2</v>
+      </c>
+      <c r="T36" t="n">
+        <v>20</v>
+      </c>
+      <c r="U36" t="n">
+        <v>29</v>
+      </c>
+      <c r="V36" t="n">
+        <v>3</v>
+      </c>
+      <c r="W36" t="n">
+        <v>29</v>
+      </c>
+      <c r="X36" t="n">
+        <v>80.89208475675144</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_12-45-14</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" t="n">
+        <v>10</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I37" t="n">
+        <v>20</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>10</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M37" t="n">
+        <v>50</v>
+      </c>
+      <c r="N37" t="n">
+        <v>27</v>
+      </c>
+      <c r="O37" t="n">
+        <v>17</v>
+      </c>
+      <c r="P37" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>10</v>
+      </c>
+      <c r="R37" t="n">
+        <v>23</v>
+      </c>
+      <c r="S37" t="n">
+        <v>29</v>
+      </c>
+      <c r="T37" t="n">
+        <v>10</v>
+      </c>
+      <c r="U37" t="n">
+        <v>23</v>
+      </c>
+      <c r="V37" t="n">
+        <v>4</v>
+      </c>
+      <c r="W37" t="n">
+        <v>17</v>
+      </c>
+      <c r="X37" t="n">
+        <v>89.85885743453213</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_12-45-14</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>5</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2</v>
+      </c>
+      <c r="G38" t="n">
+        <v>10</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I38" t="n">
+        <v>20</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>10</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M38" t="n">
+        <v>50</v>
+      </c>
+      <c r="N38" t="n">
+        <v>8</v>
+      </c>
+      <c r="O38" t="n">
+        <v>20</v>
+      </c>
+      <c r="P38" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>8</v>
+      </c>
+      <c r="R38" t="n">
+        <v>20</v>
+      </c>
+      <c r="S38" t="n">
+        <v>8</v>
+      </c>
+      <c r="T38" t="n">
+        <v>26</v>
+      </c>
+      <c r="U38" t="n">
+        <v>25</v>
+      </c>
+      <c r="V38" t="n">
+        <v>26</v>
+      </c>
+      <c r="W38" t="n">
+        <v>26</v>
+      </c>
+      <c r="X38" t="n">
+        <v>68.69336801194453</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y38"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -585,7 +585,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>run_2025-08-26_23-50-56</t>
+          <t>run_2025-08-27_12-07-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -627,37 +627,37 @@
         <v>50</v>
       </c>
       <c r="N2" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="O2" t="n">
+        <v>11</v>
+      </c>
+      <c r="P2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>4</v>
+      </c>
+      <c r="R2" t="n">
         <v>26</v>
       </c>
-      <c r="P2" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>12</v>
-      </c>
-      <c r="R2" t="n">
-        <v>18</v>
-      </c>
       <c r="S2" t="n">
+        <v>11</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U2" t="n">
         <v>26</v>
       </c>
-      <c r="T2" t="n">
-        <v>18</v>
-      </c>
-      <c r="U2" t="n">
-        <v>3</v>
-      </c>
       <c r="V2" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="W2" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="X2" t="n">
-        <v>58.95649025492629</v>
+        <v>62.82579950473799</v>
       </c>
       <c r="Y2" t="n">
         <v>19</v>
@@ -666,7 +666,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>run_2025-08-26_23-50-56</t>
+          <t>run_2025-08-27_12-07-54</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -708,46 +708,46 @@
         <v>50</v>
       </c>
       <c r="N3" t="n">
+        <v>27</v>
+      </c>
+      <c r="O3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>27</v>
+      </c>
+      <c r="R3" t="n">
+        <v>27</v>
+      </c>
+      <c r="S3" t="n">
+        <v>27</v>
+      </c>
+      <c r="T3" t="n">
+        <v>13</v>
+      </c>
+      <c r="U3" t="n">
+        <v>25</v>
+      </c>
+      <c r="V3" t="n">
+        <v>8</v>
+      </c>
+      <c r="W3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X3" t="n">
+        <v>71.3219414105654</v>
+      </c>
+      <c r="Y3" t="n">
         <v>12</v>
-      </c>
-      <c r="O3" t="n">
-        <v>14</v>
-      </c>
-      <c r="P3" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>12</v>
-      </c>
-      <c r="R3" t="n">
-        <v>20</v>
-      </c>
-      <c r="S3" t="n">
-        <v>14</v>
-      </c>
-      <c r="T3" t="n">
-        <v>14</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2</v>
-      </c>
-      <c r="V3" t="n">
-        <v>6</v>
-      </c>
-      <c r="W3" t="n">
-        <v>14</v>
-      </c>
-      <c r="X3" t="n">
-        <v>56.64479768115913</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>run_2025-08-26_23-50-56</t>
+          <t>run_2025-08-27_12-07-54</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -789,46 +789,46 @@
         <v>50</v>
       </c>
       <c r="N4" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
+        <v>26</v>
+      </c>
+      <c r="P4" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q4" t="n">
         <v>30</v>
       </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>31</v>
-      </c>
       <c r="R4" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="X4" t="n">
-        <v>44.76846039852396</v>
+        <v>81.14711086205445</v>
       </c>
       <c r="Y4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>run_2025-08-26_23-50-56</t>
+          <t>run_2025-08-27_12-07-54</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -870,46 +870,46 @@
         <v>50</v>
       </c>
       <c r="N5" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="P5" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="R5" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="T5" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="W5" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="X5" t="n">
-        <v>63.3563177068533</v>
+        <v>90.81424630863604</v>
       </c>
       <c r="Y5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>run_2025-08-26_23-50-56</t>
+          <t>run_2025-08-27_12-07-54</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
@@ -951,37 +951,37 @@
         <v>50</v>
       </c>
       <c r="N6" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="O6" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Q6" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="R6" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="T6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="V6" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="W6" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="X6" t="n">
-        <v>62.06612510097931</v>
+        <v>63.52567745171968</v>
       </c>
       <c r="Y6" t="n">
         <v>19</v>
@@ -990,22 +990,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>run_2025-08-26_23-50-56</t>
+          <t>run_2025-08-27_12-07-54</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>config_2</t>
+          <t>config_1</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -1032,63 +1032,61 @@
         <v>50</v>
       </c>
       <c r="N7" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="O7" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="P7" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="Q7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R7" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="S7" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="T7" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="U7" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="V7" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="X7" t="n">
+        <v>50.58447819361012</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>run_2025-08-27_11-05-00</t>
+          <t>run_2025-08-27_12-07-54</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>config_1</t>
+          <t>config_2</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -1115,63 +1113,61 @@
         <v>50</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="P8" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>27</v>
+      </c>
+      <c r="R8" t="n">
+        <v>27</v>
+      </c>
+      <c r="S8" t="n">
+        <v>30</v>
+      </c>
+      <c r="T8" t="n">
+        <v>7</v>
+      </c>
+      <c r="U8" t="n">
+        <v>7</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>9</v>
+      </c>
+      <c r="X8" t="n">
+        <v>90.71454400943628</v>
+      </c>
+      <c r="Y8" t="n">
         <v>14</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>9</v>
-      </c>
-      <c r="R8" t="n">
-        <v>22</v>
-      </c>
-      <c r="S8" t="n">
-        <v>7</v>
-      </c>
-      <c r="T8" t="n">
-        <v>4</v>
-      </c>
-      <c r="U8" t="n">
-        <v>16</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>15</v>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>run_2025-08-27_11-09-45</t>
+          <t>run_2025-08-27_12-07-54</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>config_1</t>
+          <t>config_2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
@@ -1198,61 +1194,61 @@
         <v>50</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O9" t="n">
         <v>30</v>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="Q9" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="T9" t="n">
+        <v>16</v>
+      </c>
+      <c r="U9" t="n">
+        <v>28</v>
+      </c>
+      <c r="V9" t="n">
         <v>30</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>13</v>
-      </c>
       <c r="W9" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="X9" t="n">
-        <v>70.04860773670998</v>
+        <v>71.88394812573939</v>
       </c>
       <c r="Y9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>run_2025-08-27_11-17-42</t>
+          <t>run_2025-08-27_12-07-54</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>config_1</t>
+          <t>config_2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -1279,61 +1275,61 @@
         <v>50</v>
       </c>
       <c r="N10" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="O10" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R10" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="S10" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="V10" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="W10" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="X10" t="n">
-        <v>79.98669109803332</v>
+        <v>80.21186065863191</v>
       </c>
       <c r="Y10" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>run_2025-08-27_11-17-42</t>
+          <t>run_2025-08-27_12-07-54</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>config_1</t>
+          <t>config_2</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="F11" t="n">
         <v>2</v>
@@ -1360,61 +1356,61 @@
         <v>50</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="P11" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="Q11" t="n">
+        <v>17</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>24</v>
+      </c>
+      <c r="T11" t="n">
         <v>31</v>
       </c>
-      <c r="R11" t="n">
-        <v>10</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="U11" t="n">
         <v>0</v>
       </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>31</v>
       </c>
-      <c r="V11" t="n">
-        <v>11</v>
-      </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="X11" t="n">
-        <v>89.84110741054994</v>
+        <v>71.64900683348328</v>
       </c>
       <c r="Y11" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>run_2025-08-27_11-17-42</t>
+          <t>run_2025-08-27_12-07-54</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>config_1</t>
+          <t>config_2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="F12" t="n">
         <v>2</v>
@@ -1441,58 +1437,58 @@
         <v>50</v>
       </c>
       <c r="N12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="O12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="R12" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="U12" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="V12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="W12" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>69.60868196518105</v>
+        <v>60.44199631234798</v>
       </c>
       <c r="Y12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>run_2025-08-27_12-07-08</t>
+          <t>run_2025-08-27_12-07-54</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>config_1</t>
+          <t>config_3</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
         <v>0.5</v>
@@ -1504,7 +1500,7 @@
         <v>10</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="I13" t="n">
         <v>20</v>
@@ -1522,37 +1518,37 @@
         <v>50</v>
       </c>
       <c r="N13" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="O13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="P13" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="R13" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="T13" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="U13" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="V13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="X13" t="n">
-        <v>62.82579950473799</v>
+        <v>81.09268309401315</v>
       </c>
       <c r="Y13" t="n">
         <v>19</v>
@@ -1566,14 +1562,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>config_1</t>
+          <t>config_3</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
         <v>0.5</v>
@@ -1585,7 +1581,7 @@
         <v>10</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="I14" t="n">
         <v>20</v>
@@ -1603,40 +1599,40 @@
         <v>50</v>
       </c>
       <c r="N14" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="P14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="R14" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="S14" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="U14" t="n">
+        <v>12</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="n">
         <v>25</v>
       </c>
-      <c r="V14" t="n">
-        <v>8</v>
-      </c>
-      <c r="W14" t="n">
-        <v>4</v>
-      </c>
       <c r="X14" t="n">
-        <v>71.3219414105654</v>
+        <v>71.36676446325041</v>
       </c>
       <c r="Y14" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -1647,14 +1643,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>config_1</t>
+          <t>config_3</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
         <v>0.5</v>
@@ -1666,7 +1662,7 @@
         <v>10</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="I15" t="n">
         <v>20</v>
@@ -1684,40 +1680,40 @@
         <v>50</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O15" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="P15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q15" t="n">
+        <v>21</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2</v>
+      </c>
+      <c r="S15" t="n">
+        <v>17</v>
+      </c>
+      <c r="T15" t="n">
+        <v>13</v>
+      </c>
+      <c r="U15" t="n">
+        <v>21</v>
+      </c>
+      <c r="V15" t="n">
         <v>30</v>
       </c>
-      <c r="R15" t="n">
-        <v>23</v>
-      </c>
-      <c r="S15" t="n">
-        <v>26</v>
-      </c>
-      <c r="T15" t="n">
-        <v>10</v>
-      </c>
-      <c r="U15" t="n">
-        <v>30</v>
-      </c>
-      <c r="V15" t="n">
-        <v>29</v>
-      </c>
       <c r="W15" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="X15" t="n">
-        <v>81.14711086205445</v>
+        <v>79.69783946883608</v>
       </c>
       <c r="Y15" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
@@ -1728,14 +1724,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>config_1</t>
+          <t>config_3</t>
         </is>
       </c>
       <c r="C16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" t="n">
         <v>3</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1</v>
       </c>
       <c r="E16" t="n">
         <v>0.5</v>
@@ -1747,7 +1743,7 @@
         <v>10</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="I16" t="n">
         <v>20</v>
@@ -1768,37 +1764,37 @@
         <v>6</v>
       </c>
       <c r="O16" t="n">
+        <v>10</v>
+      </c>
+      <c r="P16" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q16" t="n">
         <v>6</v>
       </c>
-      <c r="P16" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>12</v>
-      </c>
       <c r="R16" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="S16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="T16" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="V16" t="n">
         <v>12</v>
       </c>
       <c r="W16" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="X16" t="n">
-        <v>90.81424630863604</v>
+        <v>81.08182666511398</v>
       </c>
       <c r="Y16" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -1809,14 +1805,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>config_1</t>
+          <t>config_3</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
         <v>0.5</v>
@@ -1828,7 +1824,7 @@
         <v>10</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="I17" t="n">
         <v>20</v>
@@ -1846,40 +1842,40 @@
         <v>50</v>
       </c>
       <c r="N17" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="O17" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="P17" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="Q17" t="n">
+        <v>12</v>
+      </c>
+      <c r="R17" t="n">
+        <v>24</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="n">
+        <v>27</v>
+      </c>
+      <c r="U17" t="n">
+        <v>30</v>
+      </c>
+      <c r="V17" t="n">
+        <v>27</v>
+      </c>
+      <c r="W17" t="n">
         <v>26</v>
       </c>
-      <c r="R17" t="n">
-        <v>11</v>
-      </c>
-      <c r="S17" t="n">
-        <v>28</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>26</v>
-      </c>
-      <c r="V17" t="n">
-        <v>11</v>
-      </c>
-      <c r="W17" t="n">
-        <v>28</v>
-      </c>
       <c r="X17" t="n">
-        <v>63.52567745171968</v>
+        <v>98.43107781837801</v>
       </c>
       <c r="Y17" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -1890,26 +1886,26 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>config_1</t>
+          <t>config_4</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>10</v>
+      </c>
+      <c r="H18" t="n">
         <v>0.5</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" t="n">
-        <v>10</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.9</v>
       </c>
       <c r="I18" t="n">
         <v>20</v>
@@ -1927,37 +1923,37 @@
         <v>50</v>
       </c>
       <c r="N18" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="O18" t="n">
+        <v>29</v>
+      </c>
+      <c r="P18" t="n">
         <v>30</v>
       </c>
-      <c r="P18" t="n">
-        <v>14</v>
-      </c>
       <c r="Q18" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="R18" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="S18" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="T18" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="U18" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="V18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W18" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="X18" t="n">
-        <v>50.58447819361012</v>
+        <v>74.00241605743199</v>
       </c>
       <c r="Y18" t="n">
         <v>17</v>
@@ -1971,14 +1967,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>config_2</t>
+          <t>config_4</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
         <v>0.9</v>
@@ -1990,7 +1986,7 @@
         <v>10</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="I19" t="n">
         <v>20</v>
@@ -2008,40 +2004,40 @@
         <v>50</v>
       </c>
       <c r="N19" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="O19" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="P19" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="Q19" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="T19" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="U19" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="W19" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="X19" t="n">
-        <v>90.71454400943628</v>
+        <v>71.13692263849397</v>
       </c>
       <c r="Y19" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
@@ -2052,14 +2048,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>config_2</t>
+          <t>config_4</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
         <v>0.9</v>
@@ -2071,7 +2067,7 @@
         <v>10</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="I20" t="n">
         <v>20</v>
@@ -2089,40 +2085,40 @@
         <v>50</v>
       </c>
       <c r="N20" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O20" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P20" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="Q20" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="S20" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="U20" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="V20" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="W20" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="X20" t="n">
-        <v>71.88394812573939</v>
+        <v>70.78469326972854</v>
       </c>
       <c r="Y20" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -2133,14 +2129,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>config_2</t>
+          <t>config_4</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
         <v>0.9</v>
@@ -2152,7 +2148,7 @@
         <v>10</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="I21" t="n">
         <v>20</v>
@@ -2170,40 +2166,40 @@
         <v>50</v>
       </c>
       <c r="N21" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="O21" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="P21" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>7</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7</v>
+      </c>
+      <c r="S21" t="n">
+        <v>12</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>10</v>
+      </c>
+      <c r="V21" t="n">
+        <v>30</v>
+      </c>
+      <c r="W21" t="n">
+        <v>17</v>
+      </c>
+      <c r="X21" t="n">
+        <v>70.25909423750996</v>
+      </c>
+      <c r="Y21" t="n">
         <v>19</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>13</v>
-      </c>
-      <c r="R21" t="n">
-        <v>13</v>
-      </c>
-      <c r="S21" t="n">
-        <v>15</v>
-      </c>
-      <c r="T21" t="n">
-        <v>8</v>
-      </c>
-      <c r="U21" t="n">
-        <v>23</v>
-      </c>
-      <c r="V21" t="n">
-        <v>24</v>
-      </c>
-      <c r="W21" t="n">
-        <v>19</v>
-      </c>
-      <c r="X21" t="n">
-        <v>80.21186065863191</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="22">
@@ -2214,14 +2210,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>config_2</t>
+          <t>config_4</t>
         </is>
       </c>
       <c r="C22" t="n">
+        <v>5</v>
+      </c>
+      <c r="D22" t="n">
         <v>4</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2</v>
       </c>
       <c r="E22" t="n">
         <v>0.9</v>
@@ -2233,7 +2229,7 @@
         <v>10</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="I22" t="n">
         <v>20</v>
@@ -2251,61 +2247,61 @@
         <v>50</v>
       </c>
       <c r="N22" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="O22" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="P22" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="Q22" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="S22" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="T22" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="V22" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="W22" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="X22" t="n">
-        <v>71.64900683348328</v>
+        <v>51.93248491785744</v>
       </c>
       <c r="Y22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>run_2025-08-27_12-07-54</t>
+          <t>run_2025-08-27_12-45-14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>config_2</t>
+          <t>config_1</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="F23" t="n">
         <v>2</v>
@@ -2332,58 +2328,58 @@
         <v>50</v>
       </c>
       <c r="N23" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O23" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="P23" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="Q23" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T23" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U23" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="V23" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="W23" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="X23" t="n">
-        <v>60.44199631234798</v>
+        <v>73.3884704842657</v>
       </c>
       <c r="Y23" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>run_2025-08-27_12-07-54</t>
+          <t>run_2025-08-27_12-45-14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>config_3</t>
+          <t>config_1</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
         <v>0.5</v>
@@ -2395,7 +2391,7 @@
         <v>10</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="I24" t="n">
         <v>20</v>
@@ -2413,58 +2409,58 @@
         <v>50</v>
       </c>
       <c r="N24" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="O24" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="Q24" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="R24" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="S24" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T24" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="U24" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="V24" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="W24" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="X24" t="n">
-        <v>81.09268309401315</v>
+        <v>89.8477442977694</v>
       </c>
       <c r="Y24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>run_2025-08-27_12-07-54</t>
+          <t>run_2025-08-27_12-45-14</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>config_3</t>
+          <t>config_1</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>0.5</v>
@@ -2476,7 +2472,7 @@
         <v>10</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="I25" t="n">
         <v>20</v>
@@ -2494,58 +2490,58 @@
         <v>50</v>
       </c>
       <c r="N25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="P25" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2</v>
+      </c>
+      <c r="R25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>12</v>
-      </c>
-      <c r="R25" t="n">
-        <v>12</v>
-      </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T25" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="U25" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="V25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W25" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="X25" t="n">
-        <v>71.36676446325041</v>
+        <v>80.89208475675144</v>
       </c>
       <c r="Y25" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>run_2025-08-27_12-07-54</t>
+          <t>run_2025-08-27_12-45-14</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>config_3</t>
+          <t>config_1</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
         <v>0.5</v>
@@ -2557,7 +2553,7 @@
         <v>10</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="I26" t="n">
         <v>20</v>
@@ -2575,58 +2571,58 @@
         <v>50</v>
       </c>
       <c r="N26" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="O26" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P26" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="Q26" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="R26" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="S26" t="n">
+        <v>29</v>
+      </c>
+      <c r="T26" t="n">
+        <v>10</v>
+      </c>
+      <c r="U26" t="n">
+        <v>23</v>
+      </c>
+      <c r="V26" t="n">
+        <v>4</v>
+      </c>
+      <c r="W26" t="n">
         <v>17</v>
       </c>
-      <c r="T26" t="n">
-        <v>13</v>
-      </c>
-      <c r="U26" t="n">
-        <v>21</v>
-      </c>
-      <c r="V26" t="n">
-        <v>30</v>
-      </c>
-      <c r="W26" t="n">
-        <v>13</v>
-      </c>
       <c r="X26" t="n">
-        <v>79.69783946883608</v>
+        <v>89.85885743453213</v>
       </c>
       <c r="Y26" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>run_2025-08-27_12-07-54</t>
+          <t>run_2025-08-27_12-45-14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>config_3</t>
+          <t>config_1</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
         <v>0.5</v>
@@ -2638,7 +2634,7 @@
         <v>10</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="I27" t="n">
         <v>20</v>
@@ -2656,930 +2652,39 @@
         <v>50</v>
       </c>
       <c r="N27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="P27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="Q27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R27" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="S27" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="T27" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="U27" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="V27" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="W27" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="X27" t="n">
-        <v>81.08182666511398</v>
+        <v>68.69336801194453</v>
       </c>
       <c r="Y27" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>run_2025-08-27_12-07-54</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>config_3</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>5</v>
-      </c>
-      <c r="D28" t="n">
-        <v>3</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F28" t="n">
-        <v>2</v>
-      </c>
-      <c r="G28" t="n">
-        <v>10</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I28" t="n">
-        <v>20</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>10</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M28" t="n">
-        <v>50</v>
-      </c>
-      <c r="N28" t="n">
-        <v>20</v>
-      </c>
-      <c r="O28" t="n">
-        <v>30</v>
-      </c>
-      <c r="P28" t="n">
-        <v>31</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>12</v>
-      </c>
-      <c r="R28" t="n">
-        <v>24</v>
-      </c>
-      <c r="S28" t="n">
-        <v>20</v>
-      </c>
-      <c r="T28" t="n">
-        <v>27</v>
-      </c>
-      <c r="U28" t="n">
-        <v>30</v>
-      </c>
-      <c r="V28" t="n">
-        <v>27</v>
-      </c>
-      <c r="W28" t="n">
-        <v>26</v>
-      </c>
-      <c r="X28" t="n">
-        <v>98.43107781837801</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>run_2025-08-27_12-07-54</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>config_4</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" t="n">
-        <v>4</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F29" t="n">
-        <v>2</v>
-      </c>
-      <c r="G29" t="n">
-        <v>10</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I29" t="n">
-        <v>20</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>10</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M29" t="n">
-        <v>50</v>
-      </c>
-      <c r="N29" t="n">
-        <v>9</v>
-      </c>
-      <c r="O29" t="n">
-        <v>29</v>
-      </c>
-      <c r="P29" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>29</v>
-      </c>
-      <c r="R29" t="n">
-        <v>29</v>
-      </c>
-      <c r="S29" t="n">
-        <v>20</v>
-      </c>
-      <c r="T29" t="n">
-        <v>10</v>
-      </c>
-      <c r="U29" t="n">
-        <v>9</v>
-      </c>
-      <c r="V29" t="n">
-        <v>29</v>
-      </c>
-      <c r="W29" t="n">
-        <v>31</v>
-      </c>
-      <c r="X29" t="n">
-        <v>74.00241605743199</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>run_2025-08-27_12-07-54</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>config_4</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>2</v>
-      </c>
-      <c r="D30" t="n">
-        <v>4</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F30" t="n">
-        <v>2</v>
-      </c>
-      <c r="G30" t="n">
-        <v>10</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I30" t="n">
-        <v>20</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>10</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M30" t="n">
-        <v>50</v>
-      </c>
-      <c r="N30" t="n">
-        <v>26</v>
-      </c>
-      <c r="O30" t="n">
-        <v>26</v>
-      </c>
-      <c r="P30" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2</v>
-      </c>
-      <c r="R30" t="n">
-        <v>2</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2</v>
-      </c>
-      <c r="T30" t="n">
-        <v>20</v>
-      </c>
-      <c r="U30" t="n">
-        <v>11</v>
-      </c>
-      <c r="V30" t="n">
-        <v>31</v>
-      </c>
-      <c r="W30" t="n">
-        <v>2</v>
-      </c>
-      <c r="X30" t="n">
-        <v>71.13692263849397</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>run_2025-08-27_12-07-54</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>config_4</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>3</v>
-      </c>
-      <c r="D31" t="n">
-        <v>4</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F31" t="n">
-        <v>2</v>
-      </c>
-      <c r="G31" t="n">
-        <v>10</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I31" t="n">
-        <v>20</v>
-      </c>
-      <c r="J31" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" t="n">
-        <v>10</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M31" t="n">
-        <v>50</v>
-      </c>
-      <c r="N31" t="n">
-        <v>16</v>
-      </c>
-      <c r="O31" t="n">
-        <v>28</v>
-      </c>
-      <c r="P31" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1</v>
-      </c>
-      <c r="R31" t="n">
-        <v>16</v>
-      </c>
-      <c r="S31" t="n">
-        <v>1</v>
-      </c>
-      <c r="T31" t="n">
-        <v>11</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1</v>
-      </c>
-      <c r="V31" t="n">
-        <v>25</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1</v>
-      </c>
-      <c r="X31" t="n">
-        <v>70.78469326972854</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>run_2025-08-27_12-07-54</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>config_4</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>4</v>
-      </c>
-      <c r="D32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F32" t="n">
-        <v>2</v>
-      </c>
-      <c r="G32" t="n">
-        <v>10</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I32" t="n">
-        <v>20</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" t="n">
-        <v>10</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M32" t="n">
-        <v>50</v>
-      </c>
-      <c r="N32" t="n">
-        <v>7</v>
-      </c>
-      <c r="O32" t="n">
-        <v>30</v>
-      </c>
-      <c r="P32" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>7</v>
-      </c>
-      <c r="R32" t="n">
-        <v>7</v>
-      </c>
-      <c r="S32" t="n">
-        <v>12</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2</v>
-      </c>
-      <c r="U32" t="n">
-        <v>10</v>
-      </c>
-      <c r="V32" t="n">
-        <v>30</v>
-      </c>
-      <c r="W32" t="n">
-        <v>17</v>
-      </c>
-      <c r="X32" t="n">
-        <v>70.25909423750996</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>run_2025-08-27_12-07-54</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>config_4</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>5</v>
-      </c>
-      <c r="D33" t="n">
-        <v>4</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F33" t="n">
-        <v>2</v>
-      </c>
-      <c r="G33" t="n">
-        <v>10</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I33" t="n">
-        <v>20</v>
-      </c>
-      <c r="J33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>10</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M33" t="n">
-        <v>50</v>
-      </c>
-      <c r="N33" t="n">
-        <v>22</v>
-      </c>
-      <c r="O33" t="n">
-        <v>11</v>
-      </c>
-      <c r="P33" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>26</v>
-      </c>
-      <c r="R33" t="n">
-        <v>26</v>
-      </c>
-      <c r="S33" t="n">
-        <v>28</v>
-      </c>
-      <c r="T33" t="n">
-        <v>16</v>
-      </c>
-      <c r="U33" t="n">
-        <v>22</v>
-      </c>
-      <c r="V33" t="n">
-        <v>11</v>
-      </c>
-      <c r="W33" t="n">
-        <v>28</v>
-      </c>
-      <c r="X33" t="n">
-        <v>51.93248491785744</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>run_2025-08-27_12-45-14</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>config_1</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F34" t="n">
-        <v>2</v>
-      </c>
-      <c r="G34" t="n">
-        <v>10</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I34" t="n">
-        <v>20</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" t="n">
-        <v>10</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M34" t="n">
-        <v>50</v>
-      </c>
-      <c r="N34" t="n">
-        <v>24</v>
-      </c>
-      <c r="O34" t="n">
-        <v>4</v>
-      </c>
-      <c r="P34" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>4</v>
-      </c>
-      <c r="R34" t="n">
-        <v>24</v>
-      </c>
-      <c r="S34" t="n">
-        <v>4</v>
-      </c>
-      <c r="T34" t="n">
-        <v>3</v>
-      </c>
-      <c r="U34" t="n">
-        <v>4</v>
-      </c>
-      <c r="V34" t="n">
-        <v>3</v>
-      </c>
-      <c r="W34" t="n">
-        <v>26</v>
-      </c>
-      <c r="X34" t="n">
-        <v>73.3884704842657</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>run_2025-08-27_12-45-14</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>config_1</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>2</v>
-      </c>
-      <c r="D35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F35" t="n">
-        <v>2</v>
-      </c>
-      <c r="G35" t="n">
-        <v>10</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I35" t="n">
-        <v>20</v>
-      </c>
-      <c r="J35" t="n">
-        <v>1</v>
-      </c>
-      <c r="K35" t="n">
-        <v>10</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M35" t="n">
-        <v>50</v>
-      </c>
-      <c r="N35" t="n">
-        <v>22</v>
-      </c>
-      <c r="O35" t="n">
-        <v>3</v>
-      </c>
-      <c r="P35" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>22</v>
-      </c>
-      <c r="R35" t="n">
-        <v>24</v>
-      </c>
-      <c r="S35" t="n">
-        <v>22</v>
-      </c>
-      <c r="T35" t="n">
-        <v>28</v>
-      </c>
-      <c r="U35" t="n">
-        <v>24</v>
-      </c>
-      <c r="V35" t="n">
-        <v>28</v>
-      </c>
-      <c r="W35" t="n">
-        <v>27</v>
-      </c>
-      <c r="X35" t="n">
-        <v>89.8477442977694</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>run_2025-08-27_12-45-14</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>config_1</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>3</v>
-      </c>
-      <c r="D36" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F36" t="n">
-        <v>2</v>
-      </c>
-      <c r="G36" t="n">
-        <v>10</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I36" t="n">
-        <v>20</v>
-      </c>
-      <c r="J36" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" t="n">
-        <v>10</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M36" t="n">
-        <v>50</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>13</v>
-      </c>
-      <c r="P36" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>2</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2</v>
-      </c>
-      <c r="T36" t="n">
-        <v>20</v>
-      </c>
-      <c r="U36" t="n">
-        <v>29</v>
-      </c>
-      <c r="V36" t="n">
-        <v>3</v>
-      </c>
-      <c r="W36" t="n">
-        <v>29</v>
-      </c>
-      <c r="X36" t="n">
-        <v>80.89208475675144</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>run_2025-08-27_12-45-14</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>config_1</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>4</v>
-      </c>
-      <c r="D37" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F37" t="n">
-        <v>2</v>
-      </c>
-      <c r="G37" t="n">
-        <v>10</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I37" t="n">
-        <v>20</v>
-      </c>
-      <c r="J37" t="n">
-        <v>1</v>
-      </c>
-      <c r="K37" t="n">
-        <v>10</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M37" t="n">
-        <v>50</v>
-      </c>
-      <c r="N37" t="n">
-        <v>27</v>
-      </c>
-      <c r="O37" t="n">
-        <v>17</v>
-      </c>
-      <c r="P37" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>10</v>
-      </c>
-      <c r="R37" t="n">
-        <v>23</v>
-      </c>
-      <c r="S37" t="n">
-        <v>29</v>
-      </c>
-      <c r="T37" t="n">
-        <v>10</v>
-      </c>
-      <c r="U37" t="n">
-        <v>23</v>
-      </c>
-      <c r="V37" t="n">
-        <v>4</v>
-      </c>
-      <c r="W37" t="n">
-        <v>17</v>
-      </c>
-      <c r="X37" t="n">
-        <v>89.85885743453213</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>run_2025-08-27_12-45-14</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>config_1</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>5</v>
-      </c>
-      <c r="D38" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F38" t="n">
-        <v>2</v>
-      </c>
-      <c r="G38" t="n">
-        <v>10</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I38" t="n">
-        <v>20</v>
-      </c>
-      <c r="J38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" t="n">
-        <v>10</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M38" t="n">
-        <v>50</v>
-      </c>
-      <c r="N38" t="n">
-        <v>8</v>
-      </c>
-      <c r="O38" t="n">
-        <v>20</v>
-      </c>
-      <c r="P38" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>8</v>
-      </c>
-      <c r="R38" t="n">
-        <v>20</v>
-      </c>
-      <c r="S38" t="n">
-        <v>8</v>
-      </c>
-      <c r="T38" t="n">
-        <v>26</v>
-      </c>
-      <c r="U38" t="n">
-        <v>25</v>
-      </c>
-      <c r="V38" t="n">
-        <v>26</v>
-      </c>
-      <c r="W38" t="n">
-        <v>26</v>
-      </c>
-      <c r="X38" t="n">
-        <v>68.69336801194453</v>
-      </c>
-      <c r="Y38" t="n">
         <v>18</v>
       </c>
     </row>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y27"/>
+  <dimension ref="A1:Y35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -2688,6 +2688,654 @@
         <v>18</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_13-03-24</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" t="n">
+        <v>10</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I28" t="n">
+        <v>20</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>10</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M28" t="n">
+        <v>50</v>
+      </c>
+      <c r="N28" t="n">
+        <v>27</v>
+      </c>
+      <c r="O28" t="n">
+        <v>6</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>14</v>
+      </c>
+      <c r="R28" t="n">
+        <v>27</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="n">
+        <v>5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>5</v>
+      </c>
+      <c r="V28" t="n">
+        <v>27</v>
+      </c>
+      <c r="W28" t="n">
+        <v>21</v>
+      </c>
+      <c r="X28" t="n">
+        <v>89.85581179336344</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_13-06-06</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>10</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I29" t="n">
+        <v>20</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>10</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M29" t="n">
+        <v>50</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3</v>
+      </c>
+      <c r="O29" t="n">
+        <v>24</v>
+      </c>
+      <c r="P29" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>23</v>
+      </c>
+      <c r="R29" t="n">
+        <v>31</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="n">
+        <v>18</v>
+      </c>
+      <c r="U29" t="n">
+        <v>31</v>
+      </c>
+      <c r="V29" t="n">
+        <v>24</v>
+      </c>
+      <c r="W29" t="n">
+        <v>14</v>
+      </c>
+      <c r="X29" t="n">
+        <v>72.32166195869878</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_13-06-06</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" t="n">
+        <v>10</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I30" t="n">
+        <v>20</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>10</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M30" t="n">
+        <v>50</v>
+      </c>
+      <c r="N30" t="n">
+        <v>24</v>
+      </c>
+      <c r="O30" t="n">
+        <v>20</v>
+      </c>
+      <c r="P30" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>24</v>
+      </c>
+      <c r="R30" t="n">
+        <v>30</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>25</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>25</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>61.67168379107283</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_13-06-06</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" t="n">
+        <v>10</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I31" t="n">
+        <v>20</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>10</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M31" t="n">
+        <v>50</v>
+      </c>
+      <c r="N31" t="n">
+        <v>8</v>
+      </c>
+      <c r="O31" t="n">
+        <v>13</v>
+      </c>
+      <c r="P31" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>8</v>
+      </c>
+      <c r="R31" t="n">
+        <v>4</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4</v>
+      </c>
+      <c r="T31" t="n">
+        <v>14</v>
+      </c>
+      <c r="U31" t="n">
+        <v>23</v>
+      </c>
+      <c r="V31" t="n">
+        <v>31</v>
+      </c>
+      <c r="W31" t="n">
+        <v>4</v>
+      </c>
+      <c r="X31" t="n">
+        <v>80.66919979610719</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_13-06-06</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" t="n">
+        <v>10</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I32" t="n">
+        <v>20</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>10</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M32" t="n">
+        <v>50</v>
+      </c>
+      <c r="N32" t="n">
+        <v>19</v>
+      </c>
+      <c r="O32" t="n">
+        <v>25</v>
+      </c>
+      <c r="P32" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>19</v>
+      </c>
+      <c r="R32" t="n">
+        <v>31</v>
+      </c>
+      <c r="S32" t="n">
+        <v>7</v>
+      </c>
+      <c r="T32" t="n">
+        <v>31</v>
+      </c>
+      <c r="U32" t="n">
+        <v>19</v>
+      </c>
+      <c r="V32" t="n">
+        <v>12</v>
+      </c>
+      <c r="W32" t="n">
+        <v>7</v>
+      </c>
+      <c r="X32" t="n">
+        <v>62.02964425352365</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_13-06-06</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>5</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" t="n">
+        <v>10</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I33" t="n">
+        <v>20</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>10</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M33" t="n">
+        <v>50</v>
+      </c>
+      <c r="N33" t="n">
+        <v>16</v>
+      </c>
+      <c r="O33" t="n">
+        <v>18</v>
+      </c>
+      <c r="P33" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>29</v>
+      </c>
+      <c r="R33" t="n">
+        <v>29</v>
+      </c>
+      <c r="S33" t="n">
+        <v>22</v>
+      </c>
+      <c r="T33" t="n">
+        <v>29</v>
+      </c>
+      <c r="U33" t="n">
+        <v>23</v>
+      </c>
+      <c r="V33" t="n">
+        <v>24</v>
+      </c>
+      <c r="W33" t="n">
+        <v>18</v>
+      </c>
+      <c r="X33" t="n">
+        <v>81.09081591251483</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_13-06-06</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>6</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" t="n">
+        <v>10</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I34" t="n">
+        <v>20</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>10</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M34" t="n">
+        <v>50</v>
+      </c>
+      <c r="N34" t="n">
+        <v>4</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1</v>
+      </c>
+      <c r="P34" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>4</v>
+      </c>
+      <c r="R34" t="n">
+        <v>4</v>
+      </c>
+      <c r="S34" t="n">
+        <v>16</v>
+      </c>
+      <c r="T34" t="n">
+        <v>29</v>
+      </c>
+      <c r="U34" t="n">
+        <v>29</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>90.09717078433157</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_13-06-06</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>7</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" t="n">
+        <v>10</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I35" t="n">
+        <v>20</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>10</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M35" t="n">
+        <v>50</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>6</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6</v>
+      </c>
+      <c r="S35" t="n">
+        <v>12</v>
+      </c>
+      <c r="T35" t="n">
+        <v>6</v>
+      </c>
+      <c r="U35" t="n">
+        <v>19</v>
+      </c>
+      <c r="V35" t="n">
+        <v>30</v>
+      </c>
+      <c r="W35" t="n">
+        <v>12</v>
+      </c>
+      <c r="X35" t="n">
+        <v>73.29970650469733</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y35"/>
+  <dimension ref="A1:Y49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -3336,6 +3336,1140 @@
         <v>17</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_15-56-12</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" t="n">
+        <v>10</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I36" t="n">
+        <v>20</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>10</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M36" t="n">
+        <v>50</v>
+      </c>
+      <c r="N36" t="n">
+        <v>6</v>
+      </c>
+      <c r="O36" t="n">
+        <v>31</v>
+      </c>
+      <c r="P36" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>23</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6</v>
+      </c>
+      <c r="S36" t="n">
+        <v>13</v>
+      </c>
+      <c r="T36" t="n">
+        <v>31</v>
+      </c>
+      <c r="U36" t="n">
+        <v>23</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>31</v>
+      </c>
+      <c r="X36" t="n">
+        <v>69.75157096645847</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_15-56-12</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" t="n">
+        <v>10</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I37" t="n">
+        <v>20</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>10</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M37" t="n">
+        <v>50</v>
+      </c>
+      <c r="N37" t="n">
+        <v>31</v>
+      </c>
+      <c r="O37" t="n">
+        <v>16</v>
+      </c>
+      <c r="P37" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>23</v>
+      </c>
+      <c r="R37" t="n">
+        <v>31</v>
+      </c>
+      <c r="S37" t="n">
+        <v>31</v>
+      </c>
+      <c r="T37" t="n">
+        <v>9</v>
+      </c>
+      <c r="U37" t="n">
+        <v>31</v>
+      </c>
+      <c r="V37" t="n">
+        <v>2</v>
+      </c>
+      <c r="W37" t="n">
+        <v>9</v>
+      </c>
+      <c r="X37" t="n">
+        <v>70.13368377810761</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_15-56-12</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2</v>
+      </c>
+      <c r="G38" t="n">
+        <v>10</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I38" t="n">
+        <v>20</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>10</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M38" t="n">
+        <v>50</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="n">
+        <v>30</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>18</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1</v>
+      </c>
+      <c r="S38" t="n">
+        <v>11</v>
+      </c>
+      <c r="T38" t="n">
+        <v>30</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" t="n">
+        <v>30</v>
+      </c>
+      <c r="W38" t="n">
+        <v>11</v>
+      </c>
+      <c r="X38" t="n">
+        <v>51.06666042284164</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_15-56-12</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" t="n">
+        <v>10</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I39" t="n">
+        <v>20</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" t="n">
+        <v>10</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M39" t="n">
+        <v>50</v>
+      </c>
+      <c r="N39" t="n">
+        <v>4</v>
+      </c>
+      <c r="O39" t="n">
+        <v>25</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>7</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7</v>
+      </c>
+      <c r="S39" t="n">
+        <v>6</v>
+      </c>
+      <c r="T39" t="n">
+        <v>16</v>
+      </c>
+      <c r="U39" t="n">
+        <v>7</v>
+      </c>
+      <c r="V39" t="n">
+        <v>2</v>
+      </c>
+      <c r="W39" t="n">
+        <v>6</v>
+      </c>
+      <c r="X39" t="n">
+        <v>70.6710829216978</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_15-56-12</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>5</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" t="n">
+        <v>10</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I40" t="n">
+        <v>20</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>10</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M40" t="n">
+        <v>50</v>
+      </c>
+      <c r="N40" t="n">
+        <v>28</v>
+      </c>
+      <c r="O40" t="n">
+        <v>9</v>
+      </c>
+      <c r="P40" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>8</v>
+      </c>
+      <c r="R40" t="n">
+        <v>20</v>
+      </c>
+      <c r="S40" t="n">
+        <v>16</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>28</v>
+      </c>
+      <c r="V40" t="n">
+        <v>9</v>
+      </c>
+      <c r="W40" t="n">
+        <v>16</v>
+      </c>
+      <c r="X40" t="n">
+        <v>59.69563968076868</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_15-56-12</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>6</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2</v>
+      </c>
+      <c r="G41" t="n">
+        <v>10</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I41" t="n">
+        <v>20</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="n">
+        <v>10</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M41" t="n">
+        <v>50</v>
+      </c>
+      <c r="N41" t="n">
+        <v>23</v>
+      </c>
+      <c r="O41" t="n">
+        <v>12</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>12</v>
+      </c>
+      <c r="R41" t="n">
+        <v>23</v>
+      </c>
+      <c r="S41" t="n">
+        <v>19</v>
+      </c>
+      <c r="T41" t="n">
+        <v>12</v>
+      </c>
+      <c r="U41" t="n">
+        <v>5</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1</v>
+      </c>
+      <c r="X41" t="n">
+        <v>69.56951516478856</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_15-56-12</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>7</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" t="n">
+        <v>10</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I42" t="n">
+        <v>20</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" t="n">
+        <v>10</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M42" t="n">
+        <v>50</v>
+      </c>
+      <c r="N42" t="n">
+        <v>21</v>
+      </c>
+      <c r="O42" t="n">
+        <v>28</v>
+      </c>
+      <c r="P42" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2</v>
+      </c>
+      <c r="R42" t="n">
+        <v>27</v>
+      </c>
+      <c r="S42" t="n">
+        <v>19</v>
+      </c>
+      <c r="T42" t="n">
+        <v>23</v>
+      </c>
+      <c r="U42" t="n">
+        <v>21</v>
+      </c>
+      <c r="V42" t="n">
+        <v>2</v>
+      </c>
+      <c r="W42" t="n">
+        <v>19</v>
+      </c>
+      <c r="X42" t="n">
+        <v>73.42183868846176</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_16-13-16</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" t="n">
+        <v>10</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I43" t="n">
+        <v>20</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" t="n">
+        <v>10</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M43" t="n">
+        <v>50</v>
+      </c>
+      <c r="N43" t="n">
+        <v>21</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>27</v>
+      </c>
+      <c r="R43" t="n">
+        <v>21</v>
+      </c>
+      <c r="S43" t="n">
+        <v>14</v>
+      </c>
+      <c r="T43" t="n">
+        <v>14</v>
+      </c>
+      <c r="U43" t="n">
+        <v>27</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="n">
+        <v>9</v>
+      </c>
+      <c r="X43" t="n">
+        <v>60.32889335089057</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_16-13-16</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2</v>
+      </c>
+      <c r="G44" t="n">
+        <v>10</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I44" t="n">
+        <v>20</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>10</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M44" t="n">
+        <v>50</v>
+      </c>
+      <c r="N44" t="n">
+        <v>15</v>
+      </c>
+      <c r="O44" t="n">
+        <v>4</v>
+      </c>
+      <c r="P44" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>9</v>
+      </c>
+      <c r="R44" t="n">
+        <v>15</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>4</v>
+      </c>
+      <c r="V44" t="n">
+        <v>4</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>72.29519285335351</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_16-13-16</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2</v>
+      </c>
+      <c r="G45" t="n">
+        <v>10</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I45" t="n">
+        <v>20</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>10</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M45" t="n">
+        <v>50</v>
+      </c>
+      <c r="N45" t="n">
+        <v>31</v>
+      </c>
+      <c r="O45" t="n">
+        <v>24</v>
+      </c>
+      <c r="P45" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>23</v>
+      </c>
+      <c r="R45" t="n">
+        <v>31</v>
+      </c>
+      <c r="S45" t="n">
+        <v>12</v>
+      </c>
+      <c r="T45" t="n">
+        <v>24</v>
+      </c>
+      <c r="U45" t="n">
+        <v>31</v>
+      </c>
+      <c r="V45" t="n">
+        <v>4</v>
+      </c>
+      <c r="W45" t="n">
+        <v>16</v>
+      </c>
+      <c r="X45" t="n">
+        <v>60.15968895795001</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_16-13-16</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>4</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G46" t="n">
+        <v>10</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I46" t="n">
+        <v>20</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>10</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M46" t="n">
+        <v>50</v>
+      </c>
+      <c r="N46" t="n">
+        <v>4</v>
+      </c>
+      <c r="O46" t="n">
+        <v>11</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>11</v>
+      </c>
+      <c r="R46" t="n">
+        <v>4</v>
+      </c>
+      <c r="S46" t="n">
+        <v>21</v>
+      </c>
+      <c r="T46" t="n">
+        <v>11</v>
+      </c>
+      <c r="U46" t="n">
+        <v>10</v>
+      </c>
+      <c r="V46" t="n">
+        <v>2</v>
+      </c>
+      <c r="W46" t="n">
+        <v>7</v>
+      </c>
+      <c r="X46" t="n">
+        <v>69.85389860399302</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_16-13-16</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>5</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G47" t="n">
+        <v>10</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I47" t="n">
+        <v>20</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>10</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M47" t="n">
+        <v>50</v>
+      </c>
+      <c r="N47" t="n">
+        <v>28</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1</v>
+      </c>
+      <c r="P47" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1</v>
+      </c>
+      <c r="R47" t="n">
+        <v>28</v>
+      </c>
+      <c r="S47" t="n">
+        <v>18</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>29</v>
+      </c>
+      <c r="V47" t="n">
+        <v>11</v>
+      </c>
+      <c r="W47" t="n">
+        <v>29</v>
+      </c>
+      <c r="X47" t="n">
+        <v>80.23243610456481</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_16-13-16</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>6</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F48" t="n">
+        <v>2</v>
+      </c>
+      <c r="G48" t="n">
+        <v>10</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I48" t="n">
+        <v>20</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="n">
+        <v>10</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M48" t="n">
+        <v>50</v>
+      </c>
+      <c r="N48" t="n">
+        <v>5</v>
+      </c>
+      <c r="O48" t="n">
+        <v>6</v>
+      </c>
+      <c r="P48" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>5</v>
+      </c>
+      <c r="R48" t="n">
+        <v>5</v>
+      </c>
+      <c r="S48" t="n">
+        <v>6</v>
+      </c>
+      <c r="T48" t="n">
+        <v>17</v>
+      </c>
+      <c r="U48" t="n">
+        <v>5</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1</v>
+      </c>
+      <c r="W48" t="n">
+        <v>25</v>
+      </c>
+      <c r="X48" t="n">
+        <v>65.17106827556108</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_16-13-16</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>7</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F49" t="n">
+        <v>2</v>
+      </c>
+      <c r="G49" t="n">
+        <v>10</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I49" t="n">
+        <v>20</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" t="n">
+        <v>10</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M49" t="n">
+        <v>50</v>
+      </c>
+      <c r="N49" t="n">
+        <v>5</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1</v>
+      </c>
+      <c r="P49" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>30</v>
+      </c>
+      <c r="R49" t="n">
+        <v>30</v>
+      </c>
+      <c r="S49" t="n">
+        <v>26</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>30</v>
+      </c>
+      <c r="V49" t="n">
+        <v>6</v>
+      </c>
+      <c r="W49" t="n">
+        <v>26</v>
+      </c>
+      <c r="X49" t="n">
+        <v>61.24061453535801</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y49"/>
+  <dimension ref="A1:Y63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -4470,6 +4470,1140 @@
         <v>12</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_16-28-38</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G50" t="n">
+        <v>10</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I50" t="n">
+        <v>20</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>10</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M50" t="n">
+        <v>50</v>
+      </c>
+      <c r="N50" t="n">
+        <v>16</v>
+      </c>
+      <c r="O50" t="n">
+        <v>27</v>
+      </c>
+      <c r="P50" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>27</v>
+      </c>
+      <c r="R50" t="n">
+        <v>8</v>
+      </c>
+      <c r="S50" t="n">
+        <v>8</v>
+      </c>
+      <c r="T50" t="n">
+        <v>27</v>
+      </c>
+      <c r="U50" t="n">
+        <v>29</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>31</v>
+      </c>
+      <c r="X50" t="n">
+        <v>90.8994998302497</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_16-28-38</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2</v>
+      </c>
+      <c r="G51" t="n">
+        <v>10</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I51" t="n">
+        <v>20</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
+        <v>10</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M51" t="n">
+        <v>50</v>
+      </c>
+      <c r="N51" t="n">
+        <v>2</v>
+      </c>
+      <c r="O51" t="n">
+        <v>9</v>
+      </c>
+      <c r="P51" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>2</v>
+      </c>
+      <c r="R51" t="n">
+        <v>31</v>
+      </c>
+      <c r="S51" t="n">
+        <v>2</v>
+      </c>
+      <c r="T51" t="n">
+        <v>19</v>
+      </c>
+      <c r="U51" t="n">
+        <v>31</v>
+      </c>
+      <c r="V51" t="n">
+        <v>14</v>
+      </c>
+      <c r="W51" t="n">
+        <v>24</v>
+      </c>
+      <c r="X51" t="n">
+        <v>70.71698685237277</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_16-28-38</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>3</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2</v>
+      </c>
+      <c r="G52" t="n">
+        <v>10</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I52" t="n">
+        <v>20</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" t="n">
+        <v>10</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M52" t="n">
+        <v>50</v>
+      </c>
+      <c r="N52" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" t="n">
+        <v>11</v>
+      </c>
+      <c r="P52" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>28</v>
+      </c>
+      <c r="R52" t="n">
+        <v>28</v>
+      </c>
+      <c r="S52" t="n">
+        <v>18</v>
+      </c>
+      <c r="T52" t="n">
+        <v>28</v>
+      </c>
+      <c r="U52" t="n">
+        <v>28</v>
+      </c>
+      <c r="V52" t="n">
+        <v>29</v>
+      </c>
+      <c r="W52" t="n">
+        <v>29</v>
+      </c>
+      <c r="X52" t="n">
+        <v>71.57630668569244</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_16-28-38</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>4</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2</v>
+      </c>
+      <c r="G53" t="n">
+        <v>10</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I53" t="n">
+        <v>20</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" t="n">
+        <v>10</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M53" t="n">
+        <v>50</v>
+      </c>
+      <c r="N53" t="n">
+        <v>13</v>
+      </c>
+      <c r="O53" t="n">
+        <v>5</v>
+      </c>
+      <c r="P53" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>13</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>15</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>6</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>24</v>
+      </c>
+      <c r="X53" t="n">
+        <v>73.0804407688649</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_16-28-38</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>5</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G54" t="n">
+        <v>10</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I54" t="n">
+        <v>20</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" t="n">
+        <v>10</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M54" t="n">
+        <v>50</v>
+      </c>
+      <c r="N54" t="n">
+        <v>10</v>
+      </c>
+      <c r="O54" t="n">
+        <v>24</v>
+      </c>
+      <c r="P54" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>10</v>
+      </c>
+      <c r="R54" t="n">
+        <v>18</v>
+      </c>
+      <c r="S54" t="n">
+        <v>31</v>
+      </c>
+      <c r="T54" t="n">
+        <v>9</v>
+      </c>
+      <c r="U54" t="n">
+        <v>10</v>
+      </c>
+      <c r="V54" t="n">
+        <v>24</v>
+      </c>
+      <c r="W54" t="n">
+        <v>31</v>
+      </c>
+      <c r="X54" t="n">
+        <v>70.00079448098258</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_16-28-38</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>6</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F55" t="n">
+        <v>2</v>
+      </c>
+      <c r="G55" t="n">
+        <v>10</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I55" t="n">
+        <v>20</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" t="n">
+        <v>10</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M55" t="n">
+        <v>50</v>
+      </c>
+      <c r="N55" t="n">
+        <v>28</v>
+      </c>
+      <c r="O55" t="n">
+        <v>28</v>
+      </c>
+      <c r="P55" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>28</v>
+      </c>
+      <c r="R55" t="n">
+        <v>22</v>
+      </c>
+      <c r="S55" t="n">
+        <v>28</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>22</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1</v>
+      </c>
+      <c r="W55" t="n">
+        <v>16</v>
+      </c>
+      <c r="X55" t="n">
+        <v>72.32713719607064</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_16-28-38</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>7</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F56" t="n">
+        <v>2</v>
+      </c>
+      <c r="G56" t="n">
+        <v>10</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I56" t="n">
+        <v>20</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>10</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M56" t="n">
+        <v>50</v>
+      </c>
+      <c r="N56" t="n">
+        <v>3</v>
+      </c>
+      <c r="O56" t="n">
+        <v>30</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>3</v>
+      </c>
+      <c r="R56" t="n">
+        <v>16</v>
+      </c>
+      <c r="S56" t="n">
+        <v>2</v>
+      </c>
+      <c r="T56" t="n">
+        <v>30</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>2</v>
+      </c>
+      <c r="W56" t="n">
+        <v>5</v>
+      </c>
+      <c r="X56" t="n">
+        <v>80.38269937855587</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_16-40-27</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F57" t="n">
+        <v>2</v>
+      </c>
+      <c r="G57" t="n">
+        <v>10</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I57" t="n">
+        <v>20</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="n">
+        <v>10</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M57" t="n">
+        <v>50</v>
+      </c>
+      <c r="N57" t="n">
+        <v>21</v>
+      </c>
+      <c r="O57" t="n">
+        <v>21</v>
+      </c>
+      <c r="P57" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>21</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1</v>
+      </c>
+      <c r="S57" t="n">
+        <v>16</v>
+      </c>
+      <c r="T57" t="n">
+        <v>20</v>
+      </c>
+      <c r="U57" t="n">
+        <v>27</v>
+      </c>
+      <c r="V57" t="n">
+        <v>25</v>
+      </c>
+      <c r="W57" t="n">
+        <v>26</v>
+      </c>
+      <c r="X57" t="n">
+        <v>89.43218022307984</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_16-40-27</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2</v>
+      </c>
+      <c r="G58" t="n">
+        <v>10</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I58" t="n">
+        <v>20</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" t="n">
+        <v>10</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M58" t="n">
+        <v>50</v>
+      </c>
+      <c r="N58" t="n">
+        <v>11</v>
+      </c>
+      <c r="O58" t="n">
+        <v>29</v>
+      </c>
+      <c r="P58" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>11</v>
+      </c>
+      <c r="R58" t="n">
+        <v>25</v>
+      </c>
+      <c r="S58" t="n">
+        <v>31</v>
+      </c>
+      <c r="T58" t="n">
+        <v>31</v>
+      </c>
+      <c r="U58" t="n">
+        <v>29</v>
+      </c>
+      <c r="V58" t="n">
+        <v>29</v>
+      </c>
+      <c r="W58" t="n">
+        <v>31</v>
+      </c>
+      <c r="X58" t="n">
+        <v>72.7201620013243</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_16-40-27</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>3</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F59" t="n">
+        <v>2</v>
+      </c>
+      <c r="G59" t="n">
+        <v>10</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I59" t="n">
+        <v>20</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" t="n">
+        <v>10</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M59" t="n">
+        <v>50</v>
+      </c>
+      <c r="N59" t="n">
+        <v>18</v>
+      </c>
+      <c r="O59" t="n">
+        <v>19</v>
+      </c>
+      <c r="P59" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>4</v>
+      </c>
+      <c r="R59" t="n">
+        <v>13</v>
+      </c>
+      <c r="S59" t="n">
+        <v>13</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>13</v>
+      </c>
+      <c r="V59" t="n">
+        <v>2</v>
+      </c>
+      <c r="W59" t="n">
+        <v>18</v>
+      </c>
+      <c r="X59" t="n">
+        <v>93.22656316473359</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_16-40-27</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>4</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F60" t="n">
+        <v>2</v>
+      </c>
+      <c r="G60" t="n">
+        <v>10</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I60" t="n">
+        <v>20</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" t="n">
+        <v>10</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M60" t="n">
+        <v>50</v>
+      </c>
+      <c r="N60" t="n">
+        <v>27</v>
+      </c>
+      <c r="O60" t="n">
+        <v>11</v>
+      </c>
+      <c r="P60" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>28</v>
+      </c>
+      <c r="R60" t="n">
+        <v>27</v>
+      </c>
+      <c r="S60" t="n">
+        <v>17</v>
+      </c>
+      <c r="T60" t="n">
+        <v>11</v>
+      </c>
+      <c r="U60" t="n">
+        <v>28</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1</v>
+      </c>
+      <c r="W60" t="n">
+        <v>22</v>
+      </c>
+      <c r="X60" t="n">
+        <v>70.7113925024574</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_16-40-27</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>5</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2</v>
+      </c>
+      <c r="G61" t="n">
+        <v>10</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I61" t="n">
+        <v>20</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="n">
+        <v>10</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M61" t="n">
+        <v>50</v>
+      </c>
+      <c r="N61" t="n">
+        <v>20</v>
+      </c>
+      <c r="O61" t="n">
+        <v>26</v>
+      </c>
+      <c r="P61" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>20</v>
+      </c>
+      <c r="R61" t="n">
+        <v>14</v>
+      </c>
+      <c r="S61" t="n">
+        <v>22</v>
+      </c>
+      <c r="T61" t="n">
+        <v>26</v>
+      </c>
+      <c r="U61" t="n">
+        <v>20</v>
+      </c>
+      <c r="V61" t="n">
+        <v>26</v>
+      </c>
+      <c r="W61" t="n">
+        <v>3</v>
+      </c>
+      <c r="X61" t="n">
+        <v>51.58379116276597</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_16-40-27</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>6</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F62" t="n">
+        <v>2</v>
+      </c>
+      <c r="G62" t="n">
+        <v>10</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I62" t="n">
+        <v>20</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" t="n">
+        <v>10</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M62" t="n">
+        <v>50</v>
+      </c>
+      <c r="N62" t="n">
+        <v>23</v>
+      </c>
+      <c r="O62" t="n">
+        <v>19</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>8</v>
+      </c>
+      <c r="R62" t="n">
+        <v>23</v>
+      </c>
+      <c r="S62" t="n">
+        <v>19</v>
+      </c>
+      <c r="T62" t="n">
+        <v>29</v>
+      </c>
+      <c r="U62" t="n">
+        <v>23</v>
+      </c>
+      <c r="V62" t="n">
+        <v>29</v>
+      </c>
+      <c r="W62" t="n">
+        <v>19</v>
+      </c>
+      <c r="X62" t="n">
+        <v>66.9701332876583</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_16-40-27</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>7</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F63" t="n">
+        <v>2</v>
+      </c>
+      <c r="G63" t="n">
+        <v>10</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I63" t="n">
+        <v>20</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" t="n">
+        <v>10</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M63" t="n">
+        <v>50</v>
+      </c>
+      <c r="N63" t="n">
+        <v>7</v>
+      </c>
+      <c r="O63" t="n">
+        <v>23</v>
+      </c>
+      <c r="P63" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>14</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7</v>
+      </c>
+      <c r="S63" t="n">
+        <v>23</v>
+      </c>
+      <c r="T63" t="n">
+        <v>8</v>
+      </c>
+      <c r="U63" t="n">
+        <v>13</v>
+      </c>
+      <c r="V63" t="n">
+        <v>14</v>
+      </c>
+      <c r="W63" t="n">
+        <v>23</v>
+      </c>
+      <c r="X63" t="n">
+        <v>76.19436102454603</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y63"/>
+  <dimension ref="A1:Y70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -5604,6 +5604,573 @@
         <v>19</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_16-50-50</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F64" t="n">
+        <v>2</v>
+      </c>
+      <c r="G64" t="n">
+        <v>10</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I64" t="n">
+        <v>20</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" t="n">
+        <v>10</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M64" t="n">
+        <v>50</v>
+      </c>
+      <c r="N64" t="n">
+        <v>16</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>16</v>
+      </c>
+      <c r="R64" t="n">
+        <v>8</v>
+      </c>
+      <c r="S64" t="n">
+        <v>19</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>8</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1</v>
+      </c>
+      <c r="W64" t="n">
+        <v>30</v>
+      </c>
+      <c r="X64" t="n">
+        <v>82.58358565461631</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_16-50-50</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>2</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F65" t="n">
+        <v>2</v>
+      </c>
+      <c r="G65" t="n">
+        <v>10</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I65" t="n">
+        <v>20</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" t="n">
+        <v>10</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M65" t="n">
+        <v>50</v>
+      </c>
+      <c r="N65" t="n">
+        <v>24</v>
+      </c>
+      <c r="O65" t="n">
+        <v>24</v>
+      </c>
+      <c r="P65" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>29</v>
+      </c>
+      <c r="R65" t="n">
+        <v>29</v>
+      </c>
+      <c r="S65" t="n">
+        <v>12</v>
+      </c>
+      <c r="T65" t="n">
+        <v>24</v>
+      </c>
+      <c r="U65" t="n">
+        <v>24</v>
+      </c>
+      <c r="V65" t="n">
+        <v>4</v>
+      </c>
+      <c r="W65" t="n">
+        <v>12</v>
+      </c>
+      <c r="X65" t="n">
+        <v>50.11746936808142</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_16-50-50</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>3</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F66" t="n">
+        <v>2</v>
+      </c>
+      <c r="G66" t="n">
+        <v>10</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I66" t="n">
+        <v>20</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" t="n">
+        <v>10</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M66" t="n">
+        <v>50</v>
+      </c>
+      <c r="N66" t="n">
+        <v>2</v>
+      </c>
+      <c r="O66" t="n">
+        <v>29</v>
+      </c>
+      <c r="P66" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>2</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1</v>
+      </c>
+      <c r="S66" t="n">
+        <v>7</v>
+      </c>
+      <c r="T66" t="n">
+        <v>8</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
+      </c>
+      <c r="V66" t="n">
+        <v>2</v>
+      </c>
+      <c r="W66" t="n">
+        <v>29</v>
+      </c>
+      <c r="X66" t="n">
+        <v>70.71294748531726</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_16-50-50</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>4</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F67" t="n">
+        <v>2</v>
+      </c>
+      <c r="G67" t="n">
+        <v>10</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I67" t="n">
+        <v>20</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1</v>
+      </c>
+      <c r="K67" t="n">
+        <v>10</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M67" t="n">
+        <v>50</v>
+      </c>
+      <c r="N67" t="n">
+        <v>16</v>
+      </c>
+      <c r="O67" t="n">
+        <v>8</v>
+      </c>
+      <c r="P67" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>20</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7</v>
+      </c>
+      <c r="S67" t="n">
+        <v>21</v>
+      </c>
+      <c r="T67" t="n">
+        <v>16</v>
+      </c>
+      <c r="U67" t="n">
+        <v>21</v>
+      </c>
+      <c r="V67" t="n">
+        <v>25</v>
+      </c>
+      <c r="W67" t="n">
+        <v>26</v>
+      </c>
+      <c r="X67" t="n">
+        <v>92.80726619934072</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_16-50-50</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>5</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F68" t="n">
+        <v>2</v>
+      </c>
+      <c r="G68" t="n">
+        <v>10</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I68" t="n">
+        <v>20</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1</v>
+      </c>
+      <c r="K68" t="n">
+        <v>10</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M68" t="n">
+        <v>50</v>
+      </c>
+      <c r="N68" t="n">
+        <v>19</v>
+      </c>
+      <c r="O68" t="n">
+        <v>7</v>
+      </c>
+      <c r="P68" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>19</v>
+      </c>
+      <c r="R68" t="n">
+        <v>27</v>
+      </c>
+      <c r="S68" t="n">
+        <v>6</v>
+      </c>
+      <c r="T68" t="n">
+        <v>6</v>
+      </c>
+      <c r="U68" t="n">
+        <v>19</v>
+      </c>
+      <c r="V68" t="n">
+        <v>11</v>
+      </c>
+      <c r="W68" t="n">
+        <v>6</v>
+      </c>
+      <c r="X68" t="n">
+        <v>70.30467147188583</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_16-50-50</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>6</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F69" t="n">
+        <v>2</v>
+      </c>
+      <c r="G69" t="n">
+        <v>10</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I69" t="n">
+        <v>20</v>
+      </c>
+      <c r="J69" t="n">
+        <v>1</v>
+      </c>
+      <c r="K69" t="n">
+        <v>10</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M69" t="n">
+        <v>50</v>
+      </c>
+      <c r="N69" t="n">
+        <v>23</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>16</v>
+      </c>
+      <c r="R69" t="n">
+        <v>16</v>
+      </c>
+      <c r="S69" t="n">
+        <v>6</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>16</v>
+      </c>
+      <c r="V69" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" t="n">
+        <v>0</v>
+      </c>
+      <c r="X69" t="n">
+        <v>55.05240209631094</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_16-50-50</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>7</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F70" t="n">
+        <v>2</v>
+      </c>
+      <c r="G70" t="n">
+        <v>10</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I70" t="n">
+        <v>20</v>
+      </c>
+      <c r="J70" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" t="n">
+        <v>10</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M70" t="n">
+        <v>50</v>
+      </c>
+      <c r="N70" t="n">
+        <v>21</v>
+      </c>
+      <c r="O70" t="n">
+        <v>12</v>
+      </c>
+      <c r="P70" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>30</v>
+      </c>
+      <c r="R70" t="n">
+        <v>30</v>
+      </c>
+      <c r="S70" t="n">
+        <v>12</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>30</v>
+      </c>
+      <c r="V70" t="n">
+        <v>12</v>
+      </c>
+      <c r="W70" t="n">
+        <v>17</v>
+      </c>
+      <c r="X70" t="n">
+        <v>61.51231560729596</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y70"/>
+  <dimension ref="A1:Y84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -6171,6 +6171,1140 @@
         <v>13</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_17-01-02</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F71" t="n">
+        <v>2</v>
+      </c>
+      <c r="G71" t="n">
+        <v>10</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I71" t="n">
+        <v>20</v>
+      </c>
+      <c r="J71" t="n">
+        <v>1</v>
+      </c>
+      <c r="K71" t="n">
+        <v>10</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M71" t="n">
+        <v>50</v>
+      </c>
+      <c r="N71" t="n">
+        <v>15</v>
+      </c>
+      <c r="O71" t="n">
+        <v>7</v>
+      </c>
+      <c r="P71" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>3</v>
+      </c>
+      <c r="R71" t="n">
+        <v>9</v>
+      </c>
+      <c r="S71" t="n">
+        <v>3</v>
+      </c>
+      <c r="T71" t="n">
+        <v>21</v>
+      </c>
+      <c r="U71" t="n">
+        <v>3</v>
+      </c>
+      <c r="V71" t="n">
+        <v>7</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0</v>
+      </c>
+      <c r="X71" t="n">
+        <v>82.68584192279398</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_17-01-02</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>2</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F72" t="n">
+        <v>2</v>
+      </c>
+      <c r="G72" t="n">
+        <v>10</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I72" t="n">
+        <v>20</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1</v>
+      </c>
+      <c r="K72" t="n">
+        <v>10</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M72" t="n">
+        <v>50</v>
+      </c>
+      <c r="N72" t="n">
+        <v>17</v>
+      </c>
+      <c r="O72" t="n">
+        <v>31</v>
+      </c>
+      <c r="P72" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>12</v>
+      </c>
+      <c r="R72" t="n">
+        <v>14</v>
+      </c>
+      <c r="S72" t="n">
+        <v>14</v>
+      </c>
+      <c r="T72" t="n">
+        <v>23</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
+      </c>
+      <c r="V72" t="n">
+        <v>12</v>
+      </c>
+      <c r="W72" t="n">
+        <v>14</v>
+      </c>
+      <c r="X72" t="n">
+        <v>81.12302620632943</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_17-01-02</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>3</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F73" t="n">
+        <v>2</v>
+      </c>
+      <c r="G73" t="n">
+        <v>10</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I73" t="n">
+        <v>20</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1</v>
+      </c>
+      <c r="K73" t="n">
+        <v>10</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M73" t="n">
+        <v>50</v>
+      </c>
+      <c r="N73" t="n">
+        <v>23</v>
+      </c>
+      <c r="O73" t="n">
+        <v>29</v>
+      </c>
+      <c r="P73" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>27</v>
+      </c>
+      <c r="R73" t="n">
+        <v>27</v>
+      </c>
+      <c r="S73" t="n">
+        <v>23</v>
+      </c>
+      <c r="T73" t="n">
+        <v>13</v>
+      </c>
+      <c r="U73" t="n">
+        <v>23</v>
+      </c>
+      <c r="V73" t="n">
+        <v>29</v>
+      </c>
+      <c r="W73" t="n">
+        <v>15</v>
+      </c>
+      <c r="X73" t="n">
+        <v>70.73403290374708</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_17-01-02</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>4</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F74" t="n">
+        <v>2</v>
+      </c>
+      <c r="G74" t="n">
+        <v>10</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I74" t="n">
+        <v>20</v>
+      </c>
+      <c r="J74" t="n">
+        <v>1</v>
+      </c>
+      <c r="K74" t="n">
+        <v>10</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M74" t="n">
+        <v>50</v>
+      </c>
+      <c r="N74" t="n">
+        <v>29</v>
+      </c>
+      <c r="O74" t="n">
+        <v>13</v>
+      </c>
+      <c r="P74" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>29</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>22</v>
+      </c>
+      <c r="T74" t="n">
+        <v>21</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" t="n">
+        <v>31</v>
+      </c>
+      <c r="W74" t="n">
+        <v>31</v>
+      </c>
+      <c r="X74" t="n">
+        <v>70.24904301012094</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_17-01-02</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>5</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2</v>
+      </c>
+      <c r="G75" t="n">
+        <v>10</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I75" t="n">
+        <v>20</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1</v>
+      </c>
+      <c r="K75" t="n">
+        <v>10</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M75" t="n">
+        <v>50</v>
+      </c>
+      <c r="N75" t="n">
+        <v>30</v>
+      </c>
+      <c r="O75" t="n">
+        <v>6</v>
+      </c>
+      <c r="P75" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>11</v>
+      </c>
+      <c r="R75" t="n">
+        <v>24</v>
+      </c>
+      <c r="S75" t="n">
+        <v>30</v>
+      </c>
+      <c r="T75" t="n">
+        <v>30</v>
+      </c>
+      <c r="U75" t="n">
+        <v>26</v>
+      </c>
+      <c r="V75" t="n">
+        <v>24</v>
+      </c>
+      <c r="W75" t="n">
+        <v>26</v>
+      </c>
+      <c r="X75" t="n">
+        <v>90.60278541737854</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_17-01-02</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>6</v>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F76" t="n">
+        <v>2</v>
+      </c>
+      <c r="G76" t="n">
+        <v>10</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I76" t="n">
+        <v>20</v>
+      </c>
+      <c r="J76" t="n">
+        <v>1</v>
+      </c>
+      <c r="K76" t="n">
+        <v>10</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M76" t="n">
+        <v>50</v>
+      </c>
+      <c r="N76" t="n">
+        <v>24</v>
+      </c>
+      <c r="O76" t="n">
+        <v>30</v>
+      </c>
+      <c r="P76" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>12</v>
+      </c>
+      <c r="R76" t="n">
+        <v>12</v>
+      </c>
+      <c r="S76" t="n">
+        <v>7</v>
+      </c>
+      <c r="T76" t="n">
+        <v>18</v>
+      </c>
+      <c r="U76" t="n">
+        <v>24</v>
+      </c>
+      <c r="V76" t="n">
+        <v>24</v>
+      </c>
+      <c r="W76" t="n">
+        <v>30</v>
+      </c>
+      <c r="X76" t="n">
+        <v>71.92019429031519</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_17-01-02</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>7</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F77" t="n">
+        <v>2</v>
+      </c>
+      <c r="G77" t="n">
+        <v>10</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I77" t="n">
+        <v>20</v>
+      </c>
+      <c r="J77" t="n">
+        <v>1</v>
+      </c>
+      <c r="K77" t="n">
+        <v>10</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M77" t="n">
+        <v>50</v>
+      </c>
+      <c r="N77" t="n">
+        <v>2</v>
+      </c>
+      <c r="O77" t="n">
+        <v>9</v>
+      </c>
+      <c r="P77" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>2</v>
+      </c>
+      <c r="R77" t="n">
+        <v>3</v>
+      </c>
+      <c r="S77" t="n">
+        <v>14</v>
+      </c>
+      <c r="T77" t="n">
+        <v>9</v>
+      </c>
+      <c r="U77" t="n">
+        <v>28</v>
+      </c>
+      <c r="V77" t="n">
+        <v>3</v>
+      </c>
+      <c r="W77" t="n">
+        <v>14</v>
+      </c>
+      <c r="X77" t="n">
+        <v>70.26224935786232</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_17-13-48</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F78" t="n">
+        <v>2</v>
+      </c>
+      <c r="G78" t="n">
+        <v>10</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I78" t="n">
+        <v>20</v>
+      </c>
+      <c r="J78" t="n">
+        <v>1</v>
+      </c>
+      <c r="K78" t="n">
+        <v>10</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M78" t="n">
+        <v>50</v>
+      </c>
+      <c r="N78" t="n">
+        <v>19</v>
+      </c>
+      <c r="O78" t="n">
+        <v>17</v>
+      </c>
+      <c r="P78" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>17</v>
+      </c>
+      <c r="R78" t="n">
+        <v>2</v>
+      </c>
+      <c r="S78" t="n">
+        <v>19</v>
+      </c>
+      <c r="T78" t="n">
+        <v>31</v>
+      </c>
+      <c r="U78" t="n">
+        <v>10</v>
+      </c>
+      <c r="V78" t="n">
+        <v>31</v>
+      </c>
+      <c r="W78" t="n">
+        <v>19</v>
+      </c>
+      <c r="X78" t="n">
+        <v>70.40081404647938</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_17-13-48</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>2</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F79" t="n">
+        <v>2</v>
+      </c>
+      <c r="G79" t="n">
+        <v>10</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I79" t="n">
+        <v>20</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" t="n">
+        <v>10</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M79" t="n">
+        <v>50</v>
+      </c>
+      <c r="N79" t="n">
+        <v>26</v>
+      </c>
+      <c r="O79" t="n">
+        <v>5</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>15</v>
+      </c>
+      <c r="R79" t="n">
+        <v>5</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="n">
+        <v>26</v>
+      </c>
+      <c r="V79" t="n">
+        <v>5</v>
+      </c>
+      <c r="W79" t="n">
+        <v>26</v>
+      </c>
+      <c r="X79" t="n">
+        <v>71.16143209221531</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_17-13-48</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>3</v>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F80" t="n">
+        <v>2</v>
+      </c>
+      <c r="G80" t="n">
+        <v>10</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I80" t="n">
+        <v>20</v>
+      </c>
+      <c r="J80" t="n">
+        <v>1</v>
+      </c>
+      <c r="K80" t="n">
+        <v>10</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M80" t="n">
+        <v>50</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>30</v>
+      </c>
+      <c r="P80" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>29</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
+        <v>15</v>
+      </c>
+      <c r="T80" t="n">
+        <v>23</v>
+      </c>
+      <c r="U80" t="n">
+        <v>23</v>
+      </c>
+      <c r="V80" t="n">
+        <v>24</v>
+      </c>
+      <c r="W80" t="n">
+        <v>20</v>
+      </c>
+      <c r="X80" t="n">
+        <v>84.3462365771817</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_17-13-48</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>4</v>
+      </c>
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F81" t="n">
+        <v>2</v>
+      </c>
+      <c r="G81" t="n">
+        <v>10</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I81" t="n">
+        <v>20</v>
+      </c>
+      <c r="J81" t="n">
+        <v>1</v>
+      </c>
+      <c r="K81" t="n">
+        <v>10</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M81" t="n">
+        <v>50</v>
+      </c>
+      <c r="N81" t="n">
+        <v>27</v>
+      </c>
+      <c r="O81" t="n">
+        <v>9</v>
+      </c>
+      <c r="P81" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>17</v>
+      </c>
+      <c r="R81" t="n">
+        <v>27</v>
+      </c>
+      <c r="S81" t="n">
+        <v>17</v>
+      </c>
+      <c r="T81" t="n">
+        <v>3</v>
+      </c>
+      <c r="U81" t="n">
+        <v>27</v>
+      </c>
+      <c r="V81" t="n">
+        <v>3</v>
+      </c>
+      <c r="W81" t="n">
+        <v>17</v>
+      </c>
+      <c r="X81" t="n">
+        <v>60.30921031948485</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_17-13-48</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>5</v>
+      </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F82" t="n">
+        <v>2</v>
+      </c>
+      <c r="G82" t="n">
+        <v>10</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I82" t="n">
+        <v>20</v>
+      </c>
+      <c r="J82" t="n">
+        <v>1</v>
+      </c>
+      <c r="K82" t="n">
+        <v>10</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M82" t="n">
+        <v>50</v>
+      </c>
+      <c r="N82" t="n">
+        <v>2</v>
+      </c>
+      <c r="O82" t="n">
+        <v>3</v>
+      </c>
+      <c r="P82" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>16</v>
+      </c>
+      <c r="R82" t="n">
+        <v>10</v>
+      </c>
+      <c r="S82" t="n">
+        <v>16</v>
+      </c>
+      <c r="T82" t="n">
+        <v>30</v>
+      </c>
+      <c r="U82" t="n">
+        <v>2</v>
+      </c>
+      <c r="V82" t="n">
+        <v>3</v>
+      </c>
+      <c r="W82" t="n">
+        <v>30</v>
+      </c>
+      <c r="X82" t="n">
+        <v>70.38398548871506</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_17-13-48</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>6</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F83" t="n">
+        <v>2</v>
+      </c>
+      <c r="G83" t="n">
+        <v>10</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I83" t="n">
+        <v>20</v>
+      </c>
+      <c r="J83" t="n">
+        <v>1</v>
+      </c>
+      <c r="K83" t="n">
+        <v>10</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M83" t="n">
+        <v>50</v>
+      </c>
+      <c r="N83" t="n">
+        <v>28</v>
+      </c>
+      <c r="O83" t="n">
+        <v>23</v>
+      </c>
+      <c r="P83" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>17</v>
+      </c>
+      <c r="R83" t="n">
+        <v>28</v>
+      </c>
+      <c r="S83" t="n">
+        <v>9</v>
+      </c>
+      <c r="T83" t="n">
+        <v>9</v>
+      </c>
+      <c r="U83" t="n">
+        <v>28</v>
+      </c>
+      <c r="V83" t="n">
+        <v>4</v>
+      </c>
+      <c r="W83" t="n">
+        <v>19</v>
+      </c>
+      <c r="X83" t="n">
+        <v>69.9518714826707</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>run_2025-08-27_17-13-48</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>7</v>
+      </c>
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F84" t="n">
+        <v>2</v>
+      </c>
+      <c r="G84" t="n">
+        <v>10</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I84" t="n">
+        <v>20</v>
+      </c>
+      <c r="J84" t="n">
+        <v>1</v>
+      </c>
+      <c r="K84" t="n">
+        <v>10</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M84" t="n">
+        <v>50</v>
+      </c>
+      <c r="N84" t="n">
+        <v>3</v>
+      </c>
+      <c r="O84" t="n">
+        <v>7</v>
+      </c>
+      <c r="P84" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>3</v>
+      </c>
+      <c r="R84" t="n">
+        <v>15</v>
+      </c>
+      <c r="S84" t="n">
+        <v>3</v>
+      </c>
+      <c r="T84" t="n">
+        <v>21</v>
+      </c>
+      <c r="U84" t="n">
+        <v>3</v>
+      </c>
+      <c r="V84" t="n">
+        <v>9</v>
+      </c>
+      <c r="W84" t="n">
+        <v>15</v>
+      </c>
+      <c r="X84" t="n">
+        <v>71.46426030057391</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y15"/>
+  <dimension ref="A1:Y22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1716,6 +1716,573 @@
         <v>14</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>run_2025-08-28_10-09-59</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>10</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>15</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>50</v>
+      </c>
+      <c r="N16" t="n">
+        <v>15</v>
+      </c>
+      <c r="O16" t="n">
+        <v>25</v>
+      </c>
+      <c r="P16" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>15</v>
+      </c>
+      <c r="R16" t="n">
+        <v>9</v>
+      </c>
+      <c r="S16" t="n">
+        <v>29</v>
+      </c>
+      <c r="T16" t="n">
+        <v>24</v>
+      </c>
+      <c r="U16" t="n">
+        <v>15</v>
+      </c>
+      <c r="V16" t="n">
+        <v>13</v>
+      </c>
+      <c r="W16" t="n">
+        <v>9</v>
+      </c>
+      <c r="X16" t="n">
+        <v>11.15089396747124</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>run_2025-08-28_10-09-59</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>15</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>50</v>
+      </c>
+      <c r="N17" t="n">
+        <v>24</v>
+      </c>
+      <c r="O17" t="n">
+        <v>8</v>
+      </c>
+      <c r="P17" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>23</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>8</v>
+      </c>
+      <c r="V17" t="n">
+        <v>15</v>
+      </c>
+      <c r="W17" t="n">
+        <v>15</v>
+      </c>
+      <c r="X17" t="n">
+        <v>15.82301982946113</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>run_2025-08-28_10-09-59</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>10</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>15</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>50</v>
+      </c>
+      <c r="N18" t="n">
+        <v>24</v>
+      </c>
+      <c r="O18" t="n">
+        <v>9</v>
+      </c>
+      <c r="P18" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>12</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7</v>
+      </c>
+      <c r="S18" t="n">
+        <v>9</v>
+      </c>
+      <c r="T18" t="n">
+        <v>28</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>7</v>
+      </c>
+      <c r="W18" t="n">
+        <v>29</v>
+      </c>
+      <c r="X18" t="n">
+        <v>13.40642625470327</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>run_2025-08-28_10-09-59</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>10</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>15</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>50</v>
+      </c>
+      <c r="N19" t="n">
+        <v>19</v>
+      </c>
+      <c r="O19" t="n">
+        <v>15</v>
+      </c>
+      <c r="P19" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>24</v>
+      </c>
+      <c r="R19" t="n">
+        <v>24</v>
+      </c>
+      <c r="S19" t="n">
+        <v>7</v>
+      </c>
+      <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5</v>
+      </c>
+      <c r="V19" t="n">
+        <v>19</v>
+      </c>
+      <c r="W19" t="n">
+        <v>11</v>
+      </c>
+      <c r="X19" t="n">
+        <v>15.25521194411239</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>run_2025-08-28_10-09-59</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>10</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>15</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>50</v>
+      </c>
+      <c r="N20" t="n">
+        <v>12</v>
+      </c>
+      <c r="O20" t="n">
+        <v>28</v>
+      </c>
+      <c r="P20" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>13</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>30</v>
+      </c>
+      <c r="T20" t="n">
+        <v>6</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>7</v>
+      </c>
+      <c r="X20" t="n">
+        <v>14.81417152745293</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>run_2025-08-28_10-09-59</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>6</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>15</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>50</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4</v>
+      </c>
+      <c r="O21" t="n">
+        <v>16</v>
+      </c>
+      <c r="P21" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>27</v>
+      </c>
+      <c r="R21" t="n">
+        <v>24</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4</v>
+      </c>
+      <c r="T21" t="n">
+        <v>30</v>
+      </c>
+      <c r="U21" t="n">
+        <v>5</v>
+      </c>
+      <c r="V21" t="n">
+        <v>3</v>
+      </c>
+      <c r="W21" t="n">
+        <v>4</v>
+      </c>
+      <c r="X21" t="n">
+        <v>13.40642625470323</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>run_2025-08-28_10-09-59</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>7</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>10</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>15</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M22" t="n">
+        <v>50</v>
+      </c>
+      <c r="N22" t="n">
+        <v>29</v>
+      </c>
+      <c r="O22" t="n">
+        <v>12</v>
+      </c>
+      <c r="P22" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3</v>
+      </c>
+      <c r="R22" t="n">
+        <v>3</v>
+      </c>
+      <c r="S22" t="n">
+        <v>13</v>
+      </c>
+      <c r="T22" t="n">
+        <v>17</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
+      </c>
+      <c r="V22" t="n">
+        <v>12</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1</v>
+      </c>
+      <c r="X22" t="n">
+        <v>10.02312782385509</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y22"/>
+  <dimension ref="A1:Y36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -2283,6 +2283,1140 @@
         <v>13</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>run_2025-08-28_13-06-48</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>10</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>15</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>5</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M23" t="n">
+        <v>50</v>
+      </c>
+      <c r="N23" t="n">
+        <v>25</v>
+      </c>
+      <c r="O23" t="n">
+        <v>30</v>
+      </c>
+      <c r="P23" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>31</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>7</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>20</v>
+      </c>
+      <c r="W23" t="n">
+        <v>11</v>
+      </c>
+      <c r="X23" t="n">
+        <v>128.3056883336597</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>run_2025-08-28_13-06-48</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>10</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>15</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>5</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M24" t="n">
+        <v>50</v>
+      </c>
+      <c r="N24" t="n">
+        <v>10</v>
+      </c>
+      <c r="O24" t="n">
+        <v>22</v>
+      </c>
+      <c r="P24" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>10</v>
+      </c>
+      <c r="R24" t="n">
+        <v>26</v>
+      </c>
+      <c r="S24" t="n">
+        <v>7</v>
+      </c>
+      <c r="T24" t="n">
+        <v>10</v>
+      </c>
+      <c r="U24" t="n">
+        <v>26</v>
+      </c>
+      <c r="V24" t="n">
+        <v>16</v>
+      </c>
+      <c r="W24" t="n">
+        <v>5</v>
+      </c>
+      <c r="X24" t="n">
+        <v>112.8998086994584</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>run_2025-08-28_13-06-48</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>10</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>15</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>5</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M25" t="n">
+        <v>50</v>
+      </c>
+      <c r="N25" t="n">
+        <v>15</v>
+      </c>
+      <c r="O25" t="n">
+        <v>28</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>28</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>22</v>
+      </c>
+      <c r="T25" t="n">
+        <v>21</v>
+      </c>
+      <c r="U25" t="n">
+        <v>22</v>
+      </c>
+      <c r="V25" t="n">
+        <v>13</v>
+      </c>
+      <c r="W25" t="n">
+        <v>18</v>
+      </c>
+      <c r="X25" t="n">
+        <v>102.5655634473235</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>run_2025-08-28_13-06-48</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" t="n">
+        <v>10</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>15</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>5</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M26" t="n">
+        <v>50</v>
+      </c>
+      <c r="N26" t="n">
+        <v>7</v>
+      </c>
+      <c r="O26" t="n">
+        <v>4</v>
+      </c>
+      <c r="P26" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>25</v>
+      </c>
+      <c r="R26" t="n">
+        <v>10</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2</v>
+      </c>
+      <c r="T26" t="n">
+        <v>20</v>
+      </c>
+      <c r="U26" t="n">
+        <v>25</v>
+      </c>
+      <c r="V26" t="n">
+        <v>2</v>
+      </c>
+      <c r="W26" t="n">
+        <v>13</v>
+      </c>
+      <c r="X26" t="n">
+        <v>111.529189969701</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>run_2025-08-28_13-06-48</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" t="n">
+        <v>10</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>15</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M27" t="n">
+        <v>50</v>
+      </c>
+      <c r="N27" t="n">
+        <v>15</v>
+      </c>
+      <c r="O27" t="n">
+        <v>24</v>
+      </c>
+      <c r="P27" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>21</v>
+      </c>
+      <c r="R27" t="n">
+        <v>3</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="n">
+        <v>20</v>
+      </c>
+      <c r="U27" t="n">
+        <v>15</v>
+      </c>
+      <c r="V27" t="n">
+        <v>9</v>
+      </c>
+      <c r="W27" t="n">
+        <v>27</v>
+      </c>
+      <c r="X27" t="n">
+        <v>97.32804085492451</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>run_2025-08-28_13-06-48</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>6</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" t="n">
+        <v>10</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>15</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>5</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M28" t="n">
+        <v>50</v>
+      </c>
+      <c r="N28" t="n">
+        <v>4</v>
+      </c>
+      <c r="O28" t="n">
+        <v>31</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>7</v>
+      </c>
+      <c r="R28" t="n">
+        <v>22</v>
+      </c>
+      <c r="S28" t="n">
+        <v>24</v>
+      </c>
+      <c r="T28" t="n">
+        <v>5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>4</v>
+      </c>
+      <c r="V28" t="n">
+        <v>31</v>
+      </c>
+      <c r="W28" t="n">
+        <v>9</v>
+      </c>
+      <c r="X28" t="n">
+        <v>91.05274688294004</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>run_2025-08-28_13-06-48</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>7</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>10</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>15</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>5</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M29" t="n">
+        <v>50</v>
+      </c>
+      <c r="N29" t="n">
+        <v>29</v>
+      </c>
+      <c r="O29" t="n">
+        <v>20</v>
+      </c>
+      <c r="P29" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3</v>
+      </c>
+      <c r="R29" t="n">
+        <v>29</v>
+      </c>
+      <c r="S29" t="n">
+        <v>21</v>
+      </c>
+      <c r="T29" t="n">
+        <v>7</v>
+      </c>
+      <c r="U29" t="n">
+        <v>26</v>
+      </c>
+      <c r="V29" t="n">
+        <v>12</v>
+      </c>
+      <c r="W29" t="n">
+        <v>17</v>
+      </c>
+      <c r="X29" t="n">
+        <v>111.7445520787406</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>run_2025-08-28_14-11-19</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" t="n">
+        <v>10</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>15</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>5</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M30" t="n">
+        <v>50</v>
+      </c>
+      <c r="N30" t="n">
+        <v>18</v>
+      </c>
+      <c r="O30" t="n">
+        <v>8</v>
+      </c>
+      <c r="P30" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>15</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
+      <c r="S30" t="n">
+        <v>31</v>
+      </c>
+      <c r="T30" t="n">
+        <v>16</v>
+      </c>
+      <c r="U30" t="n">
+        <v>16</v>
+      </c>
+      <c r="V30" t="n">
+        <v>11</v>
+      </c>
+      <c r="W30" t="n">
+        <v>8</v>
+      </c>
+      <c r="X30" t="n">
+        <v>117.0129093827633</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>run_2025-08-28_14-11-19</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" t="n">
+        <v>10</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>15</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>5</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M31" t="n">
+        <v>50</v>
+      </c>
+      <c r="N31" t="n">
+        <v>14</v>
+      </c>
+      <c r="O31" t="n">
+        <v>5</v>
+      </c>
+      <c r="P31" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>30</v>
+      </c>
+      <c r="R31" t="n">
+        <v>18</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="n">
+        <v>30</v>
+      </c>
+      <c r="U31" t="n">
+        <v>20</v>
+      </c>
+      <c r="V31" t="n">
+        <v>31</v>
+      </c>
+      <c r="W31" t="n">
+        <v>11</v>
+      </c>
+      <c r="X31" t="n">
+        <v>113.178432176553</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>run_2025-08-28_14-11-19</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" t="n">
+        <v>10</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>15</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>5</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M32" t="n">
+        <v>50</v>
+      </c>
+      <c r="N32" t="n">
+        <v>26</v>
+      </c>
+      <c r="O32" t="n">
+        <v>3</v>
+      </c>
+      <c r="P32" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>4</v>
+      </c>
+      <c r="R32" t="n">
+        <v>3</v>
+      </c>
+      <c r="S32" t="n">
+        <v>28</v>
+      </c>
+      <c r="T32" t="n">
+        <v>28</v>
+      </c>
+      <c r="U32" t="n">
+        <v>4</v>
+      </c>
+      <c r="V32" t="n">
+        <v>4</v>
+      </c>
+      <c r="W32" t="n">
+        <v>29</v>
+      </c>
+      <c r="X32" t="n">
+        <v>91.4425151636582</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>run_2025-08-28_14-11-19</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" t="n">
+        <v>10</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>15</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>5</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M33" t="n">
+        <v>50</v>
+      </c>
+      <c r="N33" t="n">
+        <v>30</v>
+      </c>
+      <c r="O33" t="n">
+        <v>12</v>
+      </c>
+      <c r="P33" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>23</v>
+      </c>
+      <c r="R33" t="n">
+        <v>30</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>19</v>
+      </c>
+      <c r="U33" t="n">
+        <v>30</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>4</v>
+      </c>
+      <c r="X33" t="n">
+        <v>112.7488876821949</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>run_2025-08-28_14-11-19</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" t="n">
+        <v>10</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>15</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>5</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M34" t="n">
+        <v>50</v>
+      </c>
+      <c r="N34" t="n">
+        <v>19</v>
+      </c>
+      <c r="O34" t="n">
+        <v>7</v>
+      </c>
+      <c r="P34" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>9</v>
+      </c>
+      <c r="R34" t="n">
+        <v>19</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>11</v>
+      </c>
+      <c r="U34" t="n">
+        <v>29</v>
+      </c>
+      <c r="V34" t="n">
+        <v>29</v>
+      </c>
+      <c r="W34" t="n">
+        <v>21</v>
+      </c>
+      <c r="X34" t="n">
+        <v>101.1008977213279</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>run_2025-08-28_14-11-19</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>6</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" t="n">
+        <v>10</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>15</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>5</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M35" t="n">
+        <v>50</v>
+      </c>
+      <c r="N35" t="n">
+        <v>5</v>
+      </c>
+      <c r="O35" t="n">
+        <v>17</v>
+      </c>
+      <c r="P35" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>25</v>
+      </c>
+      <c r="R35" t="n">
+        <v>25</v>
+      </c>
+      <c r="S35" t="n">
+        <v>19</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>9</v>
+      </c>
+      <c r="V35" t="n">
+        <v>12</v>
+      </c>
+      <c r="W35" t="n">
+        <v>19</v>
+      </c>
+      <c r="X35" t="n">
+        <v>110.3247173888242</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>run_2025-08-28_14-11-19</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>7</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" t="n">
+        <v>10</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>15</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>5</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M36" t="n">
+        <v>50</v>
+      </c>
+      <c r="N36" t="n">
+        <v>5</v>
+      </c>
+      <c r="O36" t="n">
+        <v>27</v>
+      </c>
+      <c r="P36" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>17</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
+      <c r="S36" t="n">
+        <v>20</v>
+      </c>
+      <c r="T36" t="n">
+        <v>10</v>
+      </c>
+      <c r="U36" t="n">
+        <v>17</v>
+      </c>
+      <c r="V36" t="n">
+        <v>2</v>
+      </c>
+      <c r="W36" t="n">
+        <v>20</v>
+      </c>
+      <c r="X36" t="n">
+        <v>100.5366308809948</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y36"/>
+  <dimension ref="A1:Y43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -3417,6 +3417,573 @@
         <v>9</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>run_2025-08-28_14-38-39</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" t="n">
+        <v>10</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>15</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>5</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M37" t="n">
+        <v>50</v>
+      </c>
+      <c r="N37" t="n">
+        <v>22</v>
+      </c>
+      <c r="O37" t="n">
+        <v>28</v>
+      </c>
+      <c r="P37" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>20</v>
+      </c>
+      <c r="R37" t="n">
+        <v>20</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="n">
+        <v>29</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>5</v>
+      </c>
+      <c r="W37" t="n">
+        <v>22</v>
+      </c>
+      <c r="X37" t="n">
+        <v>115.2924362933609</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>run_2025-08-28_14-38-39</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2</v>
+      </c>
+      <c r="G38" t="n">
+        <v>10</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>15</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>5</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M38" t="n">
+        <v>50</v>
+      </c>
+      <c r="N38" t="n">
+        <v>16</v>
+      </c>
+      <c r="O38" t="n">
+        <v>11</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>9</v>
+      </c>
+      <c r="R38" t="n">
+        <v>25</v>
+      </c>
+      <c r="S38" t="n">
+        <v>29</v>
+      </c>
+      <c r="T38" t="n">
+        <v>4</v>
+      </c>
+      <c r="U38" t="n">
+        <v>25</v>
+      </c>
+      <c r="V38" t="n">
+        <v>11</v>
+      </c>
+      <c r="W38" t="n">
+        <v>25</v>
+      </c>
+      <c r="X38" t="n">
+        <v>102.3106153695511</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>run_2025-08-28_14-38-39</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>3</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" t="n">
+        <v>10</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>15</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" t="n">
+        <v>5</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M39" t="n">
+        <v>50</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="n">
+        <v>4</v>
+      </c>
+      <c r="P39" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>30</v>
+      </c>
+      <c r="R39" t="n">
+        <v>24</v>
+      </c>
+      <c r="S39" t="n">
+        <v>11</v>
+      </c>
+      <c r="T39" t="n">
+        <v>4</v>
+      </c>
+      <c r="U39" t="n">
+        <v>9</v>
+      </c>
+      <c r="V39" t="n">
+        <v>24</v>
+      </c>
+      <c r="W39" t="n">
+        <v>10</v>
+      </c>
+      <c r="X39" t="n">
+        <v>101.0176639522709</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>run_2025-08-28_14-38-39</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>4</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" t="n">
+        <v>10</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>15</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>5</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M40" t="n">
+        <v>50</v>
+      </c>
+      <c r="N40" t="n">
+        <v>28</v>
+      </c>
+      <c r="O40" t="n">
+        <v>25</v>
+      </c>
+      <c r="P40" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>24</v>
+      </c>
+      <c r="R40" t="n">
+        <v>31</v>
+      </c>
+      <c r="S40" t="n">
+        <v>8</v>
+      </c>
+      <c r="T40" t="n">
+        <v>28</v>
+      </c>
+      <c r="U40" t="n">
+        <v>28</v>
+      </c>
+      <c r="V40" t="n">
+        <v>2</v>
+      </c>
+      <c r="W40" t="n">
+        <v>29</v>
+      </c>
+      <c r="X40" t="n">
+        <v>111.8448635651264</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>run_2025-08-28_14-38-39</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2</v>
+      </c>
+      <c r="G41" t="n">
+        <v>10</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>15</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="n">
+        <v>5</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M41" t="n">
+        <v>50</v>
+      </c>
+      <c r="N41" t="n">
+        <v>4</v>
+      </c>
+      <c r="O41" t="n">
+        <v>22</v>
+      </c>
+      <c r="P41" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>22</v>
+      </c>
+      <c r="R41" t="n">
+        <v>8</v>
+      </c>
+      <c r="S41" t="n">
+        <v>31</v>
+      </c>
+      <c r="T41" t="n">
+        <v>12</v>
+      </c>
+      <c r="U41" t="n">
+        <v>4</v>
+      </c>
+      <c r="V41" t="n">
+        <v>28</v>
+      </c>
+      <c r="W41" t="n">
+        <v>10</v>
+      </c>
+      <c r="X41" t="n">
+        <v>114.1314815981396</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>run_2025-08-28_14-38-39</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>6</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" t="n">
+        <v>10</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I42" t="n">
+        <v>15</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" t="n">
+        <v>5</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M42" t="n">
+        <v>50</v>
+      </c>
+      <c r="N42" t="n">
+        <v>21</v>
+      </c>
+      <c r="O42" t="n">
+        <v>18</v>
+      </c>
+      <c r="P42" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>17</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S42" t="n">
+        <v>18</v>
+      </c>
+      <c r="T42" t="n">
+        <v>30</v>
+      </c>
+      <c r="U42" t="n">
+        <v>30</v>
+      </c>
+      <c r="V42" t="n">
+        <v>11</v>
+      </c>
+      <c r="W42" t="n">
+        <v>11</v>
+      </c>
+      <c r="X42" t="n">
+        <v>114.160710859693</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>run_2025-08-28_14-38-39</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>7</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" t="n">
+        <v>10</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>15</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" t="n">
+        <v>5</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M43" t="n">
+        <v>50</v>
+      </c>
+      <c r="N43" t="n">
+        <v>8</v>
+      </c>
+      <c r="O43" t="n">
+        <v>8</v>
+      </c>
+      <c r="P43" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>24</v>
+      </c>
+      <c r="R43" t="n">
+        <v>21</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2</v>
+      </c>
+      <c r="T43" t="n">
+        <v>14</v>
+      </c>
+      <c r="U43" t="n">
+        <v>19</v>
+      </c>
+      <c r="V43" t="n">
+        <v>29</v>
+      </c>
+      <c r="W43" t="n">
+        <v>30</v>
+      </c>
+      <c r="X43" t="n">
+        <v>112.59804608922</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y6"/>
+  <dimension ref="A1:Y10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -987,6 +987,330 @@
         <v>14</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_00-20-45</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I7" t="n">
+        <v>20</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>50</v>
+      </c>
+      <c r="N7" t="n">
+        <v>10</v>
+      </c>
+      <c r="O7" t="n">
+        <v>10</v>
+      </c>
+      <c r="P7" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>10</v>
+      </c>
+      <c r="R7" t="n">
+        <v>9</v>
+      </c>
+      <c r="S7" t="n">
+        <v>19</v>
+      </c>
+      <c r="T7" t="n">
+        <v>24</v>
+      </c>
+      <c r="U7" t="n">
+        <v>9</v>
+      </c>
+      <c r="V7" t="n">
+        <v>5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>19</v>
+      </c>
+      <c r="X7" t="n">
+        <v>61.62924010615293</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_00-20-45</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I8" t="n">
+        <v>20</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>10</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>50</v>
+      </c>
+      <c r="N8" t="n">
+        <v>15</v>
+      </c>
+      <c r="O8" t="n">
+        <v>6</v>
+      </c>
+      <c r="P8" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>30</v>
+      </c>
+      <c r="R8" t="n">
+        <v>23</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="n">
+        <v>17</v>
+      </c>
+      <c r="U8" t="n">
+        <v>30</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6</v>
+      </c>
+      <c r="W8" t="n">
+        <v>17</v>
+      </c>
+      <c r="X8" t="n">
+        <v>74.78321484913504</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_00-20-45</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I9" t="n">
+        <v>20</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>10</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>50</v>
+      </c>
+      <c r="N9" t="n">
+        <v>8</v>
+      </c>
+      <c r="O9" t="n">
+        <v>30</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>8</v>
+      </c>
+      <c r="R9" t="n">
+        <v>29</v>
+      </c>
+      <c r="S9" t="n">
+        <v>21</v>
+      </c>
+      <c r="T9" t="n">
+        <v>9</v>
+      </c>
+      <c r="U9" t="n">
+        <v>29</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>29</v>
+      </c>
+      <c r="X9" t="n">
+        <v>72.08207694486565</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_00-20-45</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I10" t="n">
+        <v>20</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>10</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N10" t="n">
+        <v>31</v>
+      </c>
+      <c r="O10" t="n">
+        <v>30</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>24</v>
+      </c>
+      <c r="R10" t="n">
+        <v>29</v>
+      </c>
+      <c r="S10" t="n">
+        <v>9</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>29</v>
+      </c>
+      <c r="V10" t="n">
+        <v>24</v>
+      </c>
+      <c r="W10" t="n">
+        <v>31</v>
+      </c>
+      <c r="X10" t="n">
+        <v>71.4117285109498</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y10"/>
+  <dimension ref="A1:Y12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1311,6 +1311,168 @@
         <v>19</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_00-20-45</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>10</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I11" t="n">
+        <v>20</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>10</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>50</v>
+      </c>
+      <c r="N11" t="n">
+        <v>10</v>
+      </c>
+      <c r="O11" t="n">
+        <v>29</v>
+      </c>
+      <c r="P11" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>10</v>
+      </c>
+      <c r="R11" t="n">
+        <v>29</v>
+      </c>
+      <c r="S11" t="n">
+        <v>13</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>20</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>13</v>
+      </c>
+      <c r="X11" t="n">
+        <v>80.31392829193935</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_00-20-45</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I12" t="n">
+        <v>20</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>50</v>
+      </c>
+      <c r="N12" t="n">
+        <v>7</v>
+      </c>
+      <c r="O12" t="n">
+        <v>5</v>
+      </c>
+      <c r="P12" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>7</v>
+      </c>
+      <c r="T12" t="n">
+        <v>28</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>29</v>
+      </c>
+      <c r="W12" t="n">
+        <v>7</v>
+      </c>
+      <c r="X12" t="n">
+        <v>81.11904902908648</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y50"/>
+  <dimension ref="A1:AC53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -433,26 +433,30 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="19" customWidth="1" min="12" max="12"/>
-    <col width="36" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="15" max="15"/>
+    <col width="36" customWidth="1" min="16" max="16"/>
+    <col width="28" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="20" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="20" customWidth="1" min="28" max="28"/>
+    <col width="14" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -483,100 +487,120 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>param_CRUZAMENTO</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>param_DELTA_MIN</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>param_IND_SIZE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>param_MUTACAO</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>param_MUTAÇÃO</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>param_NUM_GENERATIONS</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>param_NUM_VAR_DIFERENTES</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>param_NÚMERO DE GERAÇÕES</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>param_POP_SIZE</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>param_PORCENTAGEM</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>param_RCE_REPOPULATION_GENERATIONS</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>param_TAMANHO DA POPULAÇÃO</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>best_var_1</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>best_var_10</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>best_var_2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>best_var_3</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>best_var_4</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>best_var_5</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>best_var_6</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>best_var_7</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>best_var_8</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>best_var_9</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>best_fitness</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>best_gen_idx</t>
         </is>
@@ -602,64 +626,68 @@
       <c r="E2" t="n">
         <v>0.9</v>
       </c>
-      <c r="F2" t="n">
-        <v>2</v>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M2" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
+        <v>10</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P2" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="n">
         <v>9</v>
-      </c>
-      <c r="O2" t="n">
-        <v>17</v>
-      </c>
-      <c r="P2" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>11</v>
-      </c>
-      <c r="R2" t="n">
-        <v>11</v>
       </c>
       <c r="S2" t="n">
         <v>17</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="U2" t="n">
+        <v>11</v>
+      </c>
+      <c r="V2" t="n">
+        <v>11</v>
+      </c>
+      <c r="W2" t="n">
+        <v>17</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="n">
         <v>15</v>
       </c>
-      <c r="V2" t="n">
+      <c r="Z2" t="n">
         <v>25</v>
       </c>
-      <c r="W2" t="n">
+      <c r="AA2" t="n">
         <v>11</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AB2" t="n">
         <v>69.94115870034361</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AC2" t="n">
         <v>18</v>
       </c>
     </row>
@@ -683,64 +711,68 @@
       <c r="E3" t="n">
         <v>0.9</v>
       </c>
-      <c r="F3" t="n">
-        <v>2</v>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I3" t="n">
-        <v>20</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M3" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" t="n">
         <v>9</v>
-      </c>
-      <c r="P3" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>18</v>
-      </c>
-      <c r="R3" t="n">
-        <v>29</v>
-      </c>
-      <c r="S3" t="n">
-        <v>16</v>
       </c>
       <c r="T3" t="n">
         <v>24</v>
       </c>
       <c r="U3" t="n">
+        <v>18</v>
+      </c>
+      <c r="V3" t="n">
         <v>29</v>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
+        <v>16</v>
+      </c>
+      <c r="X3" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z3" t="n">
         <v>9</v>
       </c>
-      <c r="W3" t="n">
-        <v>20</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="AA3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB3" t="n">
         <v>70.44028319168333</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AC3" t="n">
         <v>17</v>
       </c>
     </row>
@@ -764,64 +796,68 @@
       <c r="E4" t="n">
         <v>0.9</v>
       </c>
-      <c r="F4" t="n">
-        <v>2</v>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>20</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M4" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
+        <v>10</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P4" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="n">
         <v>3</v>
       </c>
-      <c r="O4" t="n">
+      <c r="S4" t="n">
         <v>4</v>
-      </c>
-      <c r="P4" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>13</v>
-      </c>
-      <c r="R4" t="n">
-        <v>14</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
       </c>
       <c r="T4" t="n">
         <v>9</v>
       </c>
       <c r="U4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="V4" t="n">
         <v>14</v>
       </c>
       <c r="W4" t="n">
+        <v>10</v>
+      </c>
+      <c r="X4" t="n">
         <v>9</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB4" t="n">
         <v>69.88838027870801</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AC4" t="n">
         <v>17</v>
       </c>
     </row>
@@ -845,64 +881,68 @@
       <c r="E5" t="n">
         <v>0.9</v>
       </c>
-      <c r="F5" t="n">
-        <v>2</v>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
         <v>7</v>
-      </c>
-      <c r="P5" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>19</v>
-      </c>
-      <c r="S5" t="n">
-        <v>12</v>
       </c>
       <c r="T5" t="n">
         <v>14</v>
       </c>
       <c r="U5" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="W5" t="n">
         <v>12</v>
       </c>
       <c r="X5" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB5" t="n">
         <v>80.09991729036848</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AC5" t="n">
         <v>18</v>
       </c>
     </row>
@@ -926,64 +966,68 @@
       <c r="E6" t="n">
         <v>0.9</v>
       </c>
-      <c r="F6" t="n">
-        <v>2</v>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I6" t="n">
-        <v>20</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M6" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="O6" t="n">
-        <v>11</v>
+        <v>0.2</v>
       </c>
       <c r="P6" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>17</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
         <v>29</v>
       </c>
       <c r="S6" t="n">
+        <v>11</v>
+      </c>
+      <c r="T6" t="n">
+        <v>24</v>
+      </c>
+      <c r="U6" t="n">
+        <v>17</v>
+      </c>
+      <c r="V6" t="n">
+        <v>29</v>
+      </c>
+      <c r="W6" t="n">
         <v>19</v>
       </c>
-      <c r="T6" t="n">
+      <c r="X6" t="n">
         <v>23</v>
       </c>
-      <c r="U6" t="n">
+      <c r="Y6" t="n">
         <v>29</v>
       </c>
-      <c r="V6" t="n">
+      <c r="Z6" t="n">
         <v>11</v>
       </c>
-      <c r="W6" t="n">
+      <c r="AA6" t="n">
         <v>25</v>
       </c>
-      <c r="X6" t="n">
+      <c r="AB6" t="n">
         <v>79.73330625432395</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AC6" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1007,64 +1051,68 @@
       <c r="E7" t="n">
         <v>0.9</v>
       </c>
-      <c r="F7" t="n">
-        <v>2</v>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>20</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
+        <v>10</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P7" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="n">
         <v>27</v>
       </c>
-      <c r="O7" t="n">
+      <c r="S7" t="n">
         <v>14</v>
       </c>
-      <c r="P7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
         <v>12</v>
       </c>
-      <c r="R7" t="n">
+      <c r="V7" t="n">
         <v>12</v>
       </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
+        <v>10</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y7" t="n">
         <v>15</v>
       </c>
-      <c r="V7" t="n">
-        <v>10</v>
-      </c>
-      <c r="W7" t="n">
+      <c r="Z7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA7" t="n">
         <v>15</v>
       </c>
-      <c r="X7" t="n">
+      <c r="AB7" t="n">
         <v>83.64113262599737</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AC7" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1088,64 +1136,68 @@
       <c r="E8" t="n">
         <v>0.9</v>
       </c>
-      <c r="F8" t="n">
-        <v>2</v>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I8" t="n">
-        <v>20</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M8" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O8" t="n">
-        <v>9</v>
+        <v>0.2</v>
       </c>
       <c r="P8" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>7</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
         <v>12</v>
       </c>
       <c r="S8" t="n">
+        <v>9</v>
+      </c>
+      <c r="T8" t="n">
+        <v>9</v>
+      </c>
+      <c r="U8" t="n">
+        <v>7</v>
+      </c>
+      <c r="V8" t="n">
+        <v>12</v>
+      </c>
+      <c r="W8" t="n">
         <v>14</v>
       </c>
-      <c r="T8" t="n">
+      <c r="X8" t="n">
         <v>21</v>
       </c>
-      <c r="U8" t="n">
+      <c r="Y8" t="n">
         <v>12</v>
       </c>
-      <c r="V8" t="n">
+      <c r="Z8" t="n">
         <v>7</v>
       </c>
-      <c r="W8" t="n">
+      <c r="AA8" t="n">
         <v>22</v>
       </c>
-      <c r="X8" t="n">
+      <c r="AB8" t="n">
         <v>74.55891978956514</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AC8" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1169,64 +1221,68 @@
       <c r="E9" t="n">
         <v>0.9</v>
       </c>
-      <c r="F9" t="n">
-        <v>2</v>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I9" t="n">
-        <v>20</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M9" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O9" t="n">
-        <v>19</v>
+        <v>0.2</v>
       </c>
       <c r="P9" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>11</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
         <v>8</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="T9" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="U9" t="n">
         <v>11</v>
       </c>
       <c r="V9" t="n">
+        <v>8</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z9" t="n">
         <v>29</v>
       </c>
-      <c r="W9" t="n">
+      <c r="AA9" t="n">
         <v>12</v>
       </c>
-      <c r="X9" t="n">
+      <c r="AB9" t="n">
         <v>72.87472010697184</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AC9" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1250,64 +1306,68 @@
       <c r="E10" t="n">
         <v>0.9</v>
       </c>
-      <c r="F10" t="n">
-        <v>2</v>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I10" t="n">
-        <v>20</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
+        <v>10</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P10" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="n">
         <v>29</v>
       </c>
-      <c r="O10" t="n">
+      <c r="S10" t="n">
         <v>5</v>
       </c>
-      <c r="P10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
         <v>7</v>
       </c>
-      <c r="R10" t="n">
+      <c r="V10" t="n">
         <v>7</v>
       </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
         <v>23</v>
       </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1</v>
-      </c>
-      <c r="W10" t="n">
-        <v>10</v>
-      </c>
-      <c r="X10" t="n">
+      <c r="Y10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB10" t="n">
         <v>80.8756117910568</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AC10" t="n">
         <v>16</v>
       </c>
     </row>
@@ -1331,42 +1391,34 @@
       <c r="E11" t="n">
         <v>0.9</v>
       </c>
-      <c r="F11" t="n">
-        <v>2</v>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I11" t="n">
-        <v>20</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>0.2</v>
       </c>
       <c r="P11" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>10</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="n">
         <v>24</v>
       </c>
@@ -1374,21 +1426,33 @@
         <v>4</v>
       </c>
       <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>10</v>
+      </c>
+      <c r="V11" t="n">
+        <v>24</v>
+      </c>
+      <c r="W11" t="n">
+        <v>4</v>
+      </c>
+      <c r="X11" t="n">
         <v>11</v>
       </c>
-      <c r="U11" t="n">
-        <v>2</v>
-      </c>
-      <c r="V11" t="n">
+      <c r="Y11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z11" t="n">
         <v>11</v>
       </c>
-      <c r="W11" t="n">
+      <c r="AA11" t="n">
         <v>18</v>
       </c>
-      <c r="X11" t="n">
+      <c r="AB11" t="n">
         <v>72.66151212808893</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AC11" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1412,64 +1476,68 @@
       <c r="E12" t="n">
         <v>0.9</v>
       </c>
-      <c r="F12" t="n">
-        <v>2</v>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I12" t="n">
-        <v>20</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M12" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O12" t="n">
-        <v>12</v>
+        <v>0.2</v>
       </c>
       <c r="P12" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>5</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="n">
         <v>5</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T12" t="n">
         <v>11</v>
       </c>
       <c r="U12" t="n">
+        <v>5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>20</v>
+      </c>
+      <c r="X12" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y12" t="n">
         <v>29</v>
       </c>
-      <c r="V12" t="n">
+      <c r="Z12" t="n">
         <v>29</v>
       </c>
-      <c r="W12" t="n">
+      <c r="AA12" t="n">
         <v>13</v>
       </c>
-      <c r="X12" t="n">
+      <c r="AB12" t="n">
         <v>79.56772804901573</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AC12" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1493,64 +1561,68 @@
       <c r="E13" t="n">
         <v>0.9</v>
       </c>
-      <c r="F13" t="n">
-        <v>2</v>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I13" t="n">
-        <v>20</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M13" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
+        <v>10</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P13" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="n">
         <v>29</v>
       </c>
-      <c r="O13" t="n">
+      <c r="S13" t="n">
         <v>5</v>
       </c>
-      <c r="P13" t="n">
+      <c r="T13" t="n">
         <v>11</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="U13" t="n">
         <v>5</v>
       </c>
-      <c r="R13" t="n">
-        <v>10</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="V13" t="n">
+        <v>10</v>
+      </c>
+      <c r="W13" t="n">
         <v>11</v>
       </c>
-      <c r="T13" t="n">
+      <c r="X13" t="n">
         <v>29</v>
       </c>
-      <c r="U13" t="n">
-        <v>10</v>
-      </c>
-      <c r="V13" t="n">
+      <c r="Y13" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z13" t="n">
         <v>5</v>
       </c>
-      <c r="W13" t="n">
+      <c r="AA13" t="n">
         <v>5</v>
       </c>
-      <c r="X13" t="n">
+      <c r="AB13" t="n">
         <v>71.23685913823019</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AC13" t="n">
         <v>19</v>
       </c>
     </row>
@@ -1574,47 +1646,39 @@
       <c r="E14" t="n">
         <v>0.9</v>
       </c>
-      <c r="F14" t="n">
-        <v>2</v>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I14" t="n">
-        <v>20</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M14" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
+        <v>10</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P14" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="n">
         <v>23</v>
       </c>
-      <c r="O14" t="n">
-        <v>2</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>7</v>
-      </c>
-      <c r="R14" t="n">
-        <v>13</v>
-      </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T14" t="n">
         <v>2</v>
@@ -1623,15 +1687,27 @@
         <v>7</v>
       </c>
       <c r="V14" t="n">
+        <v>13</v>
+      </c>
+      <c r="W14" t="n">
+        <v>25</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z14" t="n">
         <v>30</v>
       </c>
-      <c r="W14" t="n">
+      <c r="AA14" t="n">
         <v>30</v>
       </c>
-      <c r="X14" t="n">
+      <c r="AB14" t="n">
         <v>70.02954178562373</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AC14" t="n">
         <v>19</v>
       </c>
     </row>
@@ -1655,64 +1731,68 @@
       <c r="E15" t="n">
         <v>0.9</v>
       </c>
-      <c r="F15" t="n">
-        <v>2</v>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I15" t="n">
-        <v>20</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M15" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P15" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>18</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="n">
         <v>9</v>
       </c>
       <c r="S15" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U15" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W15" t="n">
         <v>11</v>
       </c>
       <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB15" t="n">
         <v>60.71285467694437</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AC15" t="n">
         <v>16</v>
       </c>
     </row>
@@ -1736,64 +1816,68 @@
       <c r="E16" t="n">
         <v>0.9</v>
       </c>
-      <c r="F16" t="n">
-        <v>2</v>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I16" t="n">
-        <v>20</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
+        <v>10</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P16" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="n">
         <v>26</v>
       </c>
-      <c r="O16" t="n">
+      <c r="S16" t="n">
         <v>27</v>
-      </c>
-      <c r="P16" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>26</v>
-      </c>
-      <c r="R16" t="n">
-        <v>21</v>
-      </c>
-      <c r="S16" t="n">
-        <v>6</v>
       </c>
       <c r="T16" t="n">
         <v>27</v>
       </c>
       <c r="U16" t="n">
+        <v>26</v>
+      </c>
+      <c r="V16" t="n">
+        <v>21</v>
+      </c>
+      <c r="W16" t="n">
+        <v>6</v>
+      </c>
+      <c r="X16" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y16" t="n">
         <v>28</v>
       </c>
-      <c r="V16" t="n">
+      <c r="Z16" t="n">
         <v>27</v>
       </c>
-      <c r="W16" t="n">
-        <v>10</v>
-      </c>
-      <c r="X16" t="n">
+      <c r="AA16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB16" t="n">
         <v>79.17852733107715</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AC16" t="n">
         <v>16</v>
       </c>
     </row>
@@ -1817,50 +1901,42 @@
       <c r="E17" t="n">
         <v>0.9</v>
       </c>
-      <c r="F17" t="n">
-        <v>2</v>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I17" t="n">
-        <v>20</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P17" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>30</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="n">
         <v>30</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="U17" t="n">
         <v>30</v>
@@ -1869,12 +1945,24 @@
         <v>30</v>
       </c>
       <c r="W17" t="n">
+        <v>11</v>
+      </c>
+      <c r="X17" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA17" t="n">
         <v>22</v>
       </c>
-      <c r="X17" t="n">
+      <c r="AB17" t="n">
         <v>60.35310418134321</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AC17" t="n">
         <v>18</v>
       </c>
     </row>
@@ -1898,64 +1986,68 @@
       <c r="E18" t="n">
         <v>0.9</v>
       </c>
-      <c r="F18" t="n">
-        <v>2</v>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M18" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
+        <v>10</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="n">
         <v>19</v>
       </c>
-      <c r="O18" t="n">
+      <c r="S18" t="n">
         <v>13</v>
       </c>
-      <c r="P18" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="T18" t="n">
+        <v>20</v>
+      </c>
+      <c r="U18" t="n">
         <v>19</v>
       </c>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" t="n">
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="n">
         <v>19</v>
       </c>
-      <c r="T18" t="n">
+      <c r="X18" t="n">
         <v>13</v>
       </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" t="n">
-        <v>2</v>
-      </c>
-      <c r="W18" t="n">
+      <c r="Y18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA18" t="n">
         <v>23</v>
       </c>
-      <c r="X18" t="n">
+      <c r="AB18" t="n">
         <v>71.38425443533653</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AC18" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1979,64 +2071,68 @@
       <c r="E19" t="n">
         <v>0.9</v>
       </c>
-      <c r="F19" t="n">
-        <v>2</v>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I19" t="n">
-        <v>20</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M19" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
+        <v>10</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P19" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="n">
         <v>18</v>
       </c>
-      <c r="O19" t="n">
+      <c r="S19" t="n">
         <v>15</v>
       </c>
-      <c r="P19" t="n">
+      <c r="T19" t="n">
         <v>15</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="U19" t="n">
         <v>13</v>
       </c>
-      <c r="R19" t="n">
+      <c r="V19" t="n">
         <v>5</v>
       </c>
-      <c r="S19" t="n">
-        <v>20</v>
-      </c>
-      <c r="T19" t="n">
+      <c r="W19" t="n">
+        <v>20</v>
+      </c>
+      <c r="X19" t="n">
         <v>24</v>
       </c>
-      <c r="U19" t="n">
+      <c r="Y19" t="n">
         <v>18</v>
       </c>
-      <c r="V19" t="n">
+      <c r="Z19" t="n">
         <v>24</v>
       </c>
-      <c r="W19" t="n">
+      <c r="AA19" t="n">
         <v>15</v>
       </c>
-      <c r="X19" t="n">
+      <c r="AB19" t="n">
         <v>70.50937698867091</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AC19" t="n">
         <v>17</v>
       </c>
     </row>
@@ -2060,64 +2156,68 @@
       <c r="E20" t="n">
         <v>0.9</v>
       </c>
-      <c r="F20" t="n">
-        <v>2</v>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I20" t="n">
-        <v>20</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M20" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
+        <v>10</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P20" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="n">
         <v>4</v>
       </c>
-      <c r="O20" t="n">
-        <v>2</v>
-      </c>
-      <c r="P20" t="n">
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
         <v>8</v>
       </c>
-      <c r="Q20" t="n">
-        <v>20</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="U20" t="n">
+        <v>20</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="n">
         <v>4</v>
       </c>
-      <c r="T20" t="n">
+      <c r="X20" t="n">
         <v>7</v>
       </c>
-      <c r="U20" t="n">
+      <c r="Y20" t="n">
         <v>12</v>
       </c>
-      <c r="V20" t="n">
-        <v>2</v>
-      </c>
-      <c r="W20" t="n">
+      <c r="Z20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA20" t="n">
         <v>8</v>
       </c>
-      <c r="X20" t="n">
+      <c r="AB20" t="n">
         <v>91.12290480750639</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AC20" t="n">
         <v>19</v>
       </c>
     </row>
@@ -2141,64 +2241,68 @@
       <c r="E21" t="n">
         <v>0.9</v>
       </c>
-      <c r="F21" t="n">
-        <v>2</v>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M21" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
+        <v>10</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P21" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="n">
         <v>9</v>
       </c>
-      <c r="O21" t="n">
-        <v>10</v>
-      </c>
-      <c r="P21" t="n">
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="U21" t="n">
         <v>21</v>
       </c>
-      <c r="R21" t="n">
+      <c r="V21" t="n">
         <v>28</v>
       </c>
-      <c r="S21" t="n">
+      <c r="W21" t="n">
         <v>19</v>
       </c>
-      <c r="T21" t="n">
-        <v>10</v>
-      </c>
-      <c r="U21" t="n">
+      <c r="X21" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y21" t="n">
         <v>9</v>
       </c>
-      <c r="V21" t="n">
-        <v>10</v>
-      </c>
-      <c r="W21" t="n">
+      <c r="Z21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA21" t="n">
         <v>23</v>
       </c>
-      <c r="X21" t="n">
+      <c r="AB21" t="n">
         <v>76.74823935932713</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="AC21" t="n">
         <v>14</v>
       </c>
     </row>
@@ -2222,64 +2326,68 @@
       <c r="E22" t="n">
         <v>0.9</v>
       </c>
-      <c r="F22" t="n">
-        <v>2</v>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I22" t="n">
-        <v>20</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M22" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
+        <v>10</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P22" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="n">
         <v>3</v>
       </c>
-      <c r="O22" t="n">
+      <c r="S22" t="n">
         <v>12</v>
       </c>
-      <c r="P22" t="n">
+      <c r="T22" t="n">
         <v>5</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="U22" t="n">
         <v>5</v>
       </c>
-      <c r="R22" t="n">
+      <c r="V22" t="n">
         <v>19</v>
       </c>
-      <c r="S22" t="n">
+      <c r="W22" t="n">
         <v>5</v>
       </c>
-      <c r="T22" t="n">
+      <c r="X22" t="n">
         <v>3</v>
       </c>
-      <c r="U22" t="n">
+      <c r="Y22" t="n">
         <v>3</v>
       </c>
-      <c r="V22" t="n">
+      <c r="Z22" t="n">
         <v>12</v>
       </c>
-      <c r="W22" t="n">
+      <c r="AA22" t="n">
         <v>3</v>
       </c>
-      <c r="X22" t="n">
+      <c r="AB22" t="n">
         <v>79.43852682603794</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AC22" t="n">
         <v>19</v>
       </c>
     </row>
@@ -2303,64 +2411,68 @@
       <c r="E23" t="n">
         <v>0.9</v>
       </c>
-      <c r="F23" t="n">
-        <v>2</v>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I23" t="n">
-        <v>20</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M23" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O23" t="n">
-        <v>13</v>
+        <v>0.2</v>
       </c>
       <c r="P23" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>7</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
         <v>12</v>
       </c>
       <c r="S23" t="n">
+        <v>13</v>
+      </c>
+      <c r="T23" t="n">
         <v>7</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
+        <v>7</v>
+      </c>
+      <c r="V23" t="n">
+        <v>12</v>
+      </c>
+      <c r="W23" t="n">
+        <v>7</v>
+      </c>
+      <c r="X23" t="n">
         <v>19</v>
       </c>
-      <c r="U23" t="n">
+      <c r="Y23" t="n">
         <v>19</v>
       </c>
-      <c r="V23" t="n">
+      <c r="Z23" t="n">
         <v>7</v>
       </c>
-      <c r="W23" t="n">
+      <c r="AA23" t="n">
         <v>28</v>
       </c>
-      <c r="X23" t="n">
+      <c r="AB23" t="n">
         <v>71.95842575032354</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AC23" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2384,64 +2496,68 @@
       <c r="E24" t="n">
         <v>0.9</v>
       </c>
-      <c r="F24" t="n">
-        <v>2</v>
-      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I24" t="n">
-        <v>20</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M24" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="O24" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="P24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="n">
         <v>31</v>
       </c>
       <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" t="n">
+        <v>31</v>
+      </c>
+      <c r="W24" t="n">
         <v>18</v>
       </c>
-      <c r="T24" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" t="n">
+      <c r="X24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y24" t="n">
         <v>26</v>
       </c>
-      <c r="V24" t="n">
+      <c r="Z24" t="n">
         <v>26</v>
       </c>
-      <c r="W24" t="n">
-        <v>1</v>
-      </c>
-      <c r="X24" t="n">
+      <c r="AA24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB24" t="n">
         <v>69.97195716876267</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="AC24" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2465,64 +2581,68 @@
       <c r="E25" t="n">
         <v>0.9</v>
       </c>
-      <c r="F25" t="n">
-        <v>2</v>
-      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I25" t="n">
-        <v>20</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M25" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P25" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="n">
+        <v>20</v>
+      </c>
+      <c r="S25" t="n">
         <v>3</v>
-      </c>
-      <c r="P25" t="n">
-        <v>31</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>20</v>
-      </c>
-      <c r="R25" t="n">
-        <v>24</v>
-      </c>
-      <c r="S25" t="n">
-        <v>20</v>
       </c>
       <c r="T25" t="n">
         <v>31</v>
       </c>
       <c r="U25" t="n">
+        <v>20</v>
+      </c>
+      <c r="V25" t="n">
+        <v>24</v>
+      </c>
+      <c r="W25" t="n">
+        <v>20</v>
+      </c>
+      <c r="X25" t="n">
+        <v>31</v>
+      </c>
+      <c r="Y25" t="n">
         <v>8</v>
       </c>
-      <c r="V25" t="n">
+      <c r="Z25" t="n">
         <v>3</v>
       </c>
-      <c r="W25" t="n">
-        <v>20</v>
-      </c>
-      <c r="X25" t="n">
+      <c r="AA25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB25" t="n">
         <v>60.60760785077801</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="AC25" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2546,64 +2666,68 @@
       <c r="E26" t="n">
         <v>0.9</v>
       </c>
-      <c r="F26" t="n">
-        <v>2</v>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I26" t="n">
-        <v>20</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M26" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
+        <v>10</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P26" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="n">
         <v>5</v>
       </c>
-      <c r="O26" t="n">
+      <c r="S26" t="n">
         <v>11</v>
       </c>
-      <c r="P26" t="n">
+      <c r="T26" t="n">
         <v>26</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="U26" t="n">
         <v>19</v>
       </c>
-      <c r="R26" t="n">
+      <c r="V26" t="n">
         <v>19</v>
       </c>
-      <c r="S26" t="n">
-        <v>10</v>
-      </c>
-      <c r="T26" t="n">
+      <c r="W26" t="n">
+        <v>10</v>
+      </c>
+      <c r="X26" t="n">
         <v>14</v>
       </c>
-      <c r="U26" t="n">
+      <c r="Y26" t="n">
         <v>5</v>
       </c>
-      <c r="V26" t="n">
+      <c r="Z26" t="n">
         <v>26</v>
       </c>
-      <c r="W26" t="n">
-        <v>10</v>
-      </c>
-      <c r="X26" t="n">
+      <c r="AA26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB26" t="n">
         <v>70.38614837988442</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AC26" t="n">
         <v>17</v>
       </c>
     </row>
@@ -2627,64 +2751,68 @@
       <c r="E27" t="n">
         <v>0.9</v>
       </c>
-      <c r="F27" t="n">
-        <v>2</v>
-      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I27" t="n">
-        <v>20</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L27" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M27" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O27" t="n">
-        <v>10</v>
+        <v>0.2</v>
       </c>
       <c r="P27" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>9</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="n">
         <v>1</v>
       </c>
       <c r="S27" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T27" t="n">
         <v>9</v>
       </c>
       <c r="U27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W27" t="n">
+        <v>16</v>
+      </c>
+      <c r="X27" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA27" t="n">
         <v>12</v>
       </c>
-      <c r="X27" t="n">
+      <c r="AB27" t="n">
         <v>79.75716111099894</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="AC27" t="n">
         <v>19</v>
       </c>
     </row>
@@ -2708,64 +2836,68 @@
       <c r="E28" t="n">
         <v>0.9</v>
       </c>
-      <c r="F28" t="n">
-        <v>2</v>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L28" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M28" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O28" t="n">
-        <v>30</v>
+        <v>0.2</v>
       </c>
       <c r="P28" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="n">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="U28" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
       </c>
       <c r="W28" t="n">
+        <v>24</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
         <v>14</v>
       </c>
-      <c r="X28" t="n">
+      <c r="AB28" t="n">
         <v>78.75647691026845</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="AC28" t="n">
         <v>16</v>
       </c>
     </row>
@@ -2789,64 +2921,68 @@
       <c r="E29" t="n">
         <v>0.9</v>
       </c>
-      <c r="F29" t="n">
-        <v>2</v>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I29" t="n">
-        <v>20</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M29" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P29" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="n">
+        <v>1</v>
+      </c>
+      <c r="S29" t="n">
         <v>30</v>
       </c>
-      <c r="P29" t="n">
+      <c r="T29" t="n">
         <v>30</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="U29" t="n">
         <v>13</v>
       </c>
-      <c r="R29" t="n">
+      <c r="V29" t="n">
         <v>13</v>
       </c>
-      <c r="S29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1</v>
-      </c>
-      <c r="V29" t="n">
-        <v>2</v>
-      </c>
       <c r="W29" t="n">
+        <v>2</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA29" t="n">
         <v>7</v>
       </c>
-      <c r="X29" t="n">
+      <c r="AB29" t="n">
         <v>63.32957635020941</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="AC29" t="n">
         <v>16</v>
       </c>
     </row>
@@ -2870,47 +3006,39 @@
       <c r="E30" t="n">
         <v>0.9</v>
       </c>
-      <c r="F30" t="n">
-        <v>2</v>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I30" t="n">
-        <v>20</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L30" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M30" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="O30" t="n">
-        <v>21</v>
+        <v>0.2</v>
       </c>
       <c r="P30" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>31</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="n">
         <v>31</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="T30" t="n">
         <v>15</v>
@@ -2919,15 +3047,27 @@
         <v>31</v>
       </c>
       <c r="V30" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="W30" t="n">
         <v>3</v>
       </c>
       <c r="X30" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>31</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB30" t="n">
         <v>62.03940216509471</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="AC30" t="n">
         <v>19</v>
       </c>
     </row>
@@ -2951,64 +3091,68 @@
       <c r="E31" t="n">
         <v>0.9</v>
       </c>
-      <c r="F31" t="n">
-        <v>2</v>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I31" t="n">
-        <v>20</v>
-      </c>
-      <c r="J31" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M31" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
+        <v>10</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P31" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="n">
         <v>7</v>
       </c>
-      <c r="O31" t="n">
+      <c r="S31" t="n">
         <v>28</v>
       </c>
-      <c r="P31" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q31" t="n">
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
         <v>7</v>
       </c>
-      <c r="R31" t="n">
+      <c r="V31" t="n">
         <v>22</v>
       </c>
-      <c r="S31" t="n">
+      <c r="W31" t="n">
         <v>13</v>
       </c>
-      <c r="T31" t="n">
-        <v>2</v>
-      </c>
-      <c r="U31" t="n">
+      <c r="X31" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y31" t="n">
         <v>28</v>
       </c>
-      <c r="V31" t="n">
-        <v>2</v>
-      </c>
-      <c r="W31" t="n">
+      <c r="Z31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA31" t="n">
         <v>22</v>
       </c>
-      <c r="X31" t="n">
+      <c r="AB31" t="n">
         <v>71.56128516447409</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="AC31" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3032,64 +3176,68 @@
       <c r="E32" t="n">
         <v>0.9</v>
       </c>
-      <c r="F32" t="n">
-        <v>2</v>
-      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I32" t="n">
-        <v>20</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M32" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
+        <v>10</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P32" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="n">
         <v>3</v>
       </c>
-      <c r="O32" t="n">
+      <c r="S32" t="n">
         <v>7</v>
-      </c>
-      <c r="P32" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>5</v>
-      </c>
-      <c r="R32" t="n">
-        <v>11</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3</v>
       </c>
       <c r="T32" t="n">
         <v>21</v>
       </c>
       <c r="U32" t="n">
+        <v>5</v>
+      </c>
+      <c r="V32" t="n">
+        <v>11</v>
+      </c>
+      <c r="W32" t="n">
         <v>3</v>
       </c>
-      <c r="V32" t="n">
+      <c r="X32" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z32" t="n">
         <v>5</v>
       </c>
-      <c r="W32" t="n">
+      <c r="AA32" t="n">
         <v>7</v>
       </c>
-      <c r="X32" t="n">
+      <c r="AB32" t="n">
         <v>81.60143934007365</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="AC32" t="n">
         <v>16</v>
       </c>
     </row>
@@ -3113,64 +3261,68 @@
       <c r="E33" t="n">
         <v>0.9</v>
       </c>
-      <c r="F33" t="n">
-        <v>2</v>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I33" t="n">
-        <v>20</v>
-      </c>
-      <c r="J33" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M33" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O33" t="n">
-        <v>26</v>
+        <v>0.2</v>
       </c>
       <c r="P33" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>25</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="n">
         <v>6</v>
       </c>
       <c r="S33" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="T33" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="U33" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="V33" t="n">
         <v>6</v>
       </c>
       <c r="W33" t="n">
+        <v>22</v>
+      </c>
+      <c r="X33" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA33" t="n">
         <v>12</v>
       </c>
-      <c r="X33" t="n">
+      <c r="AB33" t="n">
         <v>62.69663633888545</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="AC33" t="n">
         <v>18</v>
       </c>
     </row>
@@ -3194,64 +3346,68 @@
       <c r="E34" t="n">
         <v>0.9</v>
       </c>
-      <c r="F34" t="n">
-        <v>2</v>
-      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I34" t="n">
-        <v>20</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L34" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M34" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
+        <v>10</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P34" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="n">
         <v>31</v>
       </c>
-      <c r="O34" t="n">
-        <v>20</v>
-      </c>
-      <c r="P34" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q34" t="n">
+      <c r="S34" t="n">
+        <v>20</v>
+      </c>
+      <c r="T34" t="n">
+        <v>10</v>
+      </c>
+      <c r="U34" t="n">
         <v>25</v>
       </c>
-      <c r="R34" t="n">
+      <c r="V34" t="n">
         <v>25</v>
       </c>
-      <c r="S34" t="n">
+      <c r="W34" t="n">
         <v>16</v>
       </c>
-      <c r="T34" t="n">
+      <c r="X34" t="n">
         <v>16</v>
       </c>
-      <c r="U34" t="n">
+      <c r="Y34" t="n">
         <v>31</v>
       </c>
-      <c r="V34" t="n">
+      <c r="Z34" t="n">
         <v>31</v>
       </c>
-      <c r="W34" t="n">
+      <c r="AA34" t="n">
         <v>21</v>
       </c>
-      <c r="X34" t="n">
+      <c r="AB34" t="n">
         <v>73.17415864238353</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="AC34" t="n">
         <v>14</v>
       </c>
     </row>
@@ -3275,47 +3431,39 @@
       <c r="E35" t="n">
         <v>0.9</v>
       </c>
-      <c r="F35" t="n">
-        <v>2</v>
-      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I35" t="n">
-        <v>20</v>
-      </c>
-      <c r="J35" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M35" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P35" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="n">
+        <v>2</v>
+      </c>
+      <c r="S35" t="n">
         <v>9</v>
-      </c>
-      <c r="P35" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2</v>
-      </c>
-      <c r="R35" t="n">
-        <v>2</v>
-      </c>
-      <c r="S35" t="n">
-        <v>4</v>
       </c>
       <c r="T35" t="n">
         <v>29</v>
@@ -3324,15 +3472,27 @@
         <v>2</v>
       </c>
       <c r="V35" t="n">
+        <v>2</v>
+      </c>
+      <c r="W35" t="n">
+        <v>4</v>
+      </c>
+      <c r="X35" t="n">
         <v>29</v>
       </c>
-      <c r="W35" t="n">
+      <c r="Y35" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA35" t="n">
         <v>14</v>
       </c>
-      <c r="X35" t="n">
+      <c r="AB35" t="n">
         <v>51.36860285855139</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="AC35" t="n">
         <v>19</v>
       </c>
     </row>
@@ -3356,64 +3516,68 @@
       <c r="E36" t="n">
         <v>0.9</v>
       </c>
-      <c r="F36" t="n">
-        <v>2</v>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I36" t="n">
-        <v>20</v>
-      </c>
-      <c r="J36" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L36" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M36" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O36" t="n">
-        <v>18</v>
+        <v>0.2</v>
       </c>
       <c r="P36" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>23</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="n">
         <v>3</v>
       </c>
       <c r="S36" t="n">
+        <v>18</v>
+      </c>
+      <c r="T36" t="n">
+        <v>18</v>
+      </c>
+      <c r="U36" t="n">
+        <v>23</v>
+      </c>
+      <c r="V36" t="n">
+        <v>3</v>
+      </c>
+      <c r="W36" t="n">
         <v>11</v>
       </c>
-      <c r="T36" t="n">
-        <v>10</v>
-      </c>
-      <c r="U36" t="n">
-        <v>10</v>
-      </c>
-      <c r="V36" t="n">
+      <c r="X36" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z36" t="n">
         <v>11</v>
       </c>
-      <c r="W36" t="n">
+      <c r="AA36" t="n">
         <v>3</v>
       </c>
-      <c r="X36" t="n">
+      <c r="AB36" t="n">
         <v>74.71387324321469</v>
       </c>
-      <c r="Y36" t="n">
+      <c r="AC36" t="n">
         <v>19</v>
       </c>
     </row>
@@ -3437,47 +3601,39 @@
       <c r="E37" t="n">
         <v>0.9</v>
       </c>
-      <c r="F37" t="n">
-        <v>2</v>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I37" t="n">
-        <v>20</v>
-      </c>
-      <c r="J37" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L37" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M37" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P37" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="n">
+        <v>20</v>
+      </c>
+      <c r="S37" t="n">
         <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>18</v>
-      </c>
-      <c r="R37" t="n">
-        <v>31</v>
-      </c>
-      <c r="S37" t="n">
-        <v>20</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3486,15 +3642,27 @@
         <v>18</v>
       </c>
       <c r="V37" t="n">
+        <v>31</v>
+      </c>
+      <c r="W37" t="n">
+        <v>20</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z37" t="n">
         <v>8</v>
       </c>
-      <c r="W37" t="n">
-        <v>20</v>
-      </c>
-      <c r="X37" t="n">
+      <c r="AA37" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB37" t="n">
         <v>60.12465299051002</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="AC37" t="n">
         <v>16</v>
       </c>
     </row>
@@ -3518,64 +3686,68 @@
       <c r="E38" t="n">
         <v>0.9</v>
       </c>
-      <c r="F38" t="n">
-        <v>2</v>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I38" t="n">
-        <v>20</v>
-      </c>
-      <c r="J38" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L38" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M38" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P38" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="n">
+        <v>1</v>
+      </c>
+      <c r="S38" t="n">
         <v>29</v>
       </c>
-      <c r="P38" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q38" t="n">
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
         <v>17</v>
       </c>
-      <c r="R38" t="n">
+      <c r="V38" t="n">
         <v>6</v>
       </c>
-      <c r="S38" t="n">
+      <c r="W38" t="n">
         <v>17</v>
       </c>
-      <c r="T38" t="n">
+      <c r="X38" t="n">
         <v>24</v>
       </c>
-      <c r="U38" t="n">
+      <c r="Y38" t="n">
         <v>6</v>
       </c>
-      <c r="V38" t="n">
-        <v>1</v>
-      </c>
-      <c r="W38" t="n">
+      <c r="Z38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA38" t="n">
         <v>24</v>
       </c>
-      <c r="X38" t="n">
+      <c r="AB38" t="n">
         <v>90.22154010305432</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="AC38" t="n">
         <v>18</v>
       </c>
     </row>
@@ -3599,64 +3771,68 @@
       <c r="E39" t="n">
         <v>0.9</v>
       </c>
-      <c r="F39" t="n">
-        <v>2</v>
-      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H39" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I39" t="n">
-        <v>20</v>
-      </c>
-      <c r="J39" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L39" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M39" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="n">
+        <v>10</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P39" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="n">
         <v>14</v>
       </c>
-      <c r="O39" t="n">
+      <c r="S39" t="n">
         <v>9</v>
       </c>
-      <c r="P39" t="n">
+      <c r="T39" t="n">
         <v>9</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="U39" t="n">
         <v>8</v>
       </c>
-      <c r="R39" t="n">
+      <c r="V39" t="n">
         <v>29</v>
       </c>
-      <c r="S39" t="n">
+      <c r="W39" t="n">
         <v>8</v>
       </c>
-      <c r="T39" t="n">
+      <c r="X39" t="n">
         <v>14</v>
       </c>
-      <c r="U39" t="n">
+      <c r="Y39" t="n">
         <v>14</v>
       </c>
-      <c r="V39" t="n">
-        <v>2</v>
-      </c>
-      <c r="W39" t="n">
+      <c r="Z39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA39" t="n">
         <v>22</v>
       </c>
-      <c r="X39" t="n">
+      <c r="AB39" t="n">
         <v>81.03923045560538</v>
       </c>
-      <c r="Y39" t="n">
+      <c r="AC39" t="n">
         <v>16</v>
       </c>
     </row>
@@ -3680,64 +3856,68 @@
       <c r="E40" t="n">
         <v>0.9</v>
       </c>
-      <c r="F40" t="n">
-        <v>2</v>
-      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I40" t="n">
-        <v>20</v>
-      </c>
-      <c r="J40" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L40" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M40" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="n">
+        <v>10</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P40" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="n">
         <v>13</v>
       </c>
-      <c r="O40" t="n">
+      <c r="S40" t="n">
         <v>23</v>
       </c>
-      <c r="P40" t="n">
+      <c r="T40" t="n">
         <v>23</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="U40" t="n">
         <v>13</v>
       </c>
-      <c r="R40" t="n">
+      <c r="V40" t="n">
         <v>7</v>
-      </c>
-      <c r="S40" t="n">
-        <v>12</v>
-      </c>
-      <c r="T40" t="n">
-        <v>29</v>
-      </c>
-      <c r="U40" t="n">
-        <v>10</v>
-      </c>
-      <c r="V40" t="n">
-        <v>29</v>
       </c>
       <c r="W40" t="n">
         <v>12</v>
       </c>
       <c r="X40" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB40" t="n">
         <v>71.48759872863228</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="AC40" t="n">
         <v>17</v>
       </c>
     </row>
@@ -3761,42 +3941,34 @@
       <c r="E41" t="n">
         <v>0.9</v>
       </c>
-      <c r="F41" t="n">
-        <v>2</v>
-      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H41" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I41" t="n">
-        <v>20</v>
-      </c>
-      <c r="J41" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M41" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="O41" t="n">
-        <v>11</v>
+        <v>0.2</v>
       </c>
       <c r="P41" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>15</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="n">
         <v>24</v>
       </c>
@@ -3804,21 +3976,33 @@
         <v>11</v>
       </c>
       <c r="T41" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="U41" t="n">
+        <v>15</v>
+      </c>
+      <c r="V41" t="n">
+        <v>24</v>
+      </c>
+      <c r="W41" t="n">
+        <v>11</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y41" t="n">
         <v>16</v>
       </c>
-      <c r="V41" t="n">
+      <c r="Z41" t="n">
         <v>11</v>
       </c>
-      <c r="W41" t="n">
+      <c r="AA41" t="n">
         <v>6</v>
       </c>
-      <c r="X41" t="n">
+      <c r="AB41" t="n">
         <v>70.46373966882555</v>
       </c>
-      <c r="Y41" t="n">
+      <c r="AC41" t="n">
         <v>17</v>
       </c>
     </row>
@@ -3842,64 +4026,68 @@
       <c r="E42" t="n">
         <v>0.9</v>
       </c>
-      <c r="F42" t="n">
-        <v>2</v>
-      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H42" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I42" t="n">
-        <v>20</v>
-      </c>
-      <c r="J42" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L42" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M42" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="n">
+        <v>10</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P42" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="n">
         <v>18</v>
       </c>
-      <c r="O42" t="n">
+      <c r="S42" t="n">
         <v>0</v>
       </c>
-      <c r="P42" t="n">
+      <c r="T42" t="n">
         <v>9</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>12</v>
-      </c>
-      <c r="R42" t="n">
-        <v>12</v>
-      </c>
-      <c r="S42" t="n">
-        <v>14</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
       </c>
       <c r="U42" t="n">
         <v>12</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W42" t="n">
         <v>14</v>
       </c>
       <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB42" t="n">
         <v>51.25417116186403</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="AC42" t="n">
         <v>19</v>
       </c>
     </row>
@@ -3923,64 +4111,68 @@
       <c r="E43" t="n">
         <v>0.9</v>
       </c>
-      <c r="F43" t="n">
-        <v>2</v>
-      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I43" t="n">
-        <v>20</v>
-      </c>
-      <c r="J43" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L43" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M43" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="n">
+        <v>10</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P43" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="n">
         <v>16</v>
       </c>
-      <c r="O43" t="n">
-        <v>1</v>
-      </c>
-      <c r="P43" t="n">
+      <c r="S43" t="n">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
         <v>17</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="U43" t="n">
         <v>16</v>
       </c>
-      <c r="R43" t="n">
+      <c r="V43" t="n">
         <v>22</v>
-      </c>
-      <c r="S43" t="n">
-        <v>18</v>
-      </c>
-      <c r="T43" t="n">
-        <v>1</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1</v>
-      </c>
-      <c r="V43" t="n">
-        <v>11</v>
       </c>
       <c r="W43" t="n">
         <v>18</v>
       </c>
       <c r="X43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB43" t="n">
         <v>69.49805135065665</v>
       </c>
-      <c r="Y43" t="n">
+      <c r="AC43" t="n">
         <v>18</v>
       </c>
     </row>
@@ -4004,64 +4196,68 @@
       <c r="E44" t="n">
         <v>0.9</v>
       </c>
-      <c r="F44" t="n">
-        <v>2</v>
-      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H44" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I44" t="n">
-        <v>20</v>
-      </c>
-      <c r="J44" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L44" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M44" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P44" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="n">
+        <v>20</v>
+      </c>
+      <c r="S44" t="n">
         <v>26</v>
       </c>
-      <c r="P44" t="n">
+      <c r="T44" t="n">
         <v>26</v>
       </c>
-      <c r="Q44" t="n">
-        <v>20</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1</v>
-      </c>
-      <c r="S44" t="n">
+      <c r="U44" t="n">
+        <v>20</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" t="n">
         <v>14</v>
       </c>
-      <c r="T44" t="n">
-        <v>1</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1</v>
-      </c>
-      <c r="V44" t="n">
+      <c r="X44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z44" t="n">
         <v>26</v>
       </c>
-      <c r="W44" t="n">
-        <v>20</v>
-      </c>
-      <c r="X44" t="n">
+      <c r="AA44" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB44" t="n">
         <v>60.39690286379585</v>
       </c>
-      <c r="Y44" t="n">
+      <c r="AC44" t="n">
         <v>19</v>
       </c>
     </row>
@@ -4085,50 +4281,42 @@
       <c r="E45" t="n">
         <v>0.9</v>
       </c>
-      <c r="F45" t="n">
-        <v>2</v>
-      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H45" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I45" t="n">
-        <v>20</v>
-      </c>
-      <c r="J45" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L45" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M45" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="n">
+        <v>10</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P45" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="n">
         <v>29</v>
       </c>
-      <c r="O45" t="n">
+      <c r="S45" t="n">
         <v>0</v>
       </c>
-      <c r="P45" t="n">
+      <c r="T45" t="n">
         <v>30</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>29</v>
-      </c>
-      <c r="R45" t="n">
-        <v>24</v>
-      </c>
-      <c r="S45" t="n">
-        <v>30</v>
-      </c>
-      <c r="T45" t="n">
-        <v>16</v>
       </c>
       <c r="U45" t="n">
         <v>29</v>
@@ -4137,12 +4325,24 @@
         <v>24</v>
       </c>
       <c r="W45" t="n">
+        <v>30</v>
+      </c>
+      <c r="X45" t="n">
         <v>16</v>
       </c>
-      <c r="X45" t="n">
+      <c r="Y45" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB45" t="n">
         <v>70.33344619037086</v>
       </c>
-      <c r="Y45" t="n">
+      <c r="AC45" t="n">
         <v>15</v>
       </c>
     </row>
@@ -4166,66 +4366,70 @@
       <c r="E46" t="n">
         <v>0.9</v>
       </c>
-      <c r="F46" t="n">
-        <v>2</v>
-      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H46" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I46" t="n">
-        <v>20</v>
-      </c>
-      <c r="J46" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L46" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M46" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="n">
+        <v>10</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P46" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="n">
         <v>27</v>
       </c>
-      <c r="O46" t="n">
+      <c r="S46" t="n">
         <v>24</v>
       </c>
-      <c r="P46" t="n">
+      <c r="T46" t="n">
         <v>29</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="U46" t="n">
         <v>27</v>
       </c>
-      <c r="R46" t="n">
+      <c r="V46" t="n">
         <v>14</v>
-      </c>
-      <c r="S46" t="n">
-        <v>29</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>14</v>
-      </c>
-      <c r="V46" t="n">
-        <v>29</v>
       </c>
       <c r="W46" t="n">
         <v>29</v>
       </c>
       <c r="X46" t="n">
-        <v>60.65079914243123</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
         <v>14</v>
       </c>
+      <c r="Z46" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>60.65079914243123</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4247,64 +4451,68 @@
       <c r="E47" t="n">
         <v>0.9</v>
       </c>
-      <c r="F47" t="n">
-        <v>2</v>
-      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I47" t="n">
-        <v>20</v>
-      </c>
-      <c r="J47" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L47" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M47" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="O47" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="P47" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>27</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="n">
         <v>27</v>
       </c>
       <c r="S47" t="n">
+        <v>3</v>
+      </c>
+      <c r="T47" t="n">
+        <v>27</v>
+      </c>
+      <c r="U47" t="n">
+        <v>27</v>
+      </c>
+      <c r="V47" t="n">
+        <v>27</v>
+      </c>
+      <c r="W47" t="n">
         <v>14</v>
       </c>
-      <c r="T47" t="n">
+      <c r="X47" t="n">
         <v>3</v>
       </c>
-      <c r="U47" t="n">
+      <c r="Y47" t="n">
         <v>6</v>
       </c>
-      <c r="V47" t="n">
+      <c r="Z47" t="n">
         <v>8</v>
       </c>
-      <c r="W47" t="n">
-        <v>20</v>
-      </c>
-      <c r="X47" t="n">
+      <c r="AA47" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB47" t="n">
         <v>79.77175775525258</v>
       </c>
-      <c r="Y47" t="n">
+      <c r="AC47" t="n">
         <v>14</v>
       </c>
     </row>
@@ -4328,64 +4536,68 @@
       <c r="E48" t="n">
         <v>0.9</v>
       </c>
-      <c r="F48" t="n">
-        <v>2</v>
-      </c>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H48" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I48" t="n">
-        <v>20</v>
-      </c>
-      <c r="J48" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L48" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M48" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="n">
+        <v>10</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P48" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="n">
         <v>3</v>
       </c>
-      <c r="O48" t="n">
+      <c r="S48" t="n">
         <v>5</v>
       </c>
-      <c r="P48" t="n">
+      <c r="T48" t="n">
         <v>7</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="U48" t="n">
         <v>12</v>
       </c>
-      <c r="R48" t="n">
+      <c r="V48" t="n">
         <v>12</v>
       </c>
-      <c r="S48" t="n">
+      <c r="W48" t="n">
         <v>3</v>
       </c>
-      <c r="T48" t="n">
+      <c r="X48" t="n">
         <v>31</v>
       </c>
-      <c r="U48" t="n">
+      <c r="Y48" t="n">
         <v>4</v>
       </c>
-      <c r="V48" t="n">
+      <c r="Z48" t="n">
         <v>5</v>
       </c>
-      <c r="W48" t="n">
+      <c r="AA48" t="n">
         <v>31</v>
       </c>
-      <c r="X48" t="n">
+      <c r="AB48" t="n">
         <v>93.21828656950322</v>
       </c>
-      <c r="Y48" t="n">
+      <c r="AC48" t="n">
         <v>17</v>
       </c>
     </row>
@@ -4409,64 +4621,68 @@
       <c r="E49" t="n">
         <v>0.9</v>
       </c>
-      <c r="F49" t="n">
-        <v>2</v>
-      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H49" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I49" t="n">
-        <v>20</v>
-      </c>
-      <c r="J49" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L49" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M49" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="O49" t="n">
-        <v>11</v>
+        <v>0.2</v>
       </c>
       <c r="P49" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>24</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="n">
         <v>16</v>
       </c>
       <c r="S49" t="n">
+        <v>11</v>
+      </c>
+      <c r="T49" t="n">
         <v>24</v>
       </c>
-      <c r="T49" t="n">
+      <c r="U49" t="n">
+        <v>24</v>
+      </c>
+      <c r="V49" t="n">
+        <v>16</v>
+      </c>
+      <c r="W49" t="n">
+        <v>24</v>
+      </c>
+      <c r="X49" t="n">
         <v>3</v>
       </c>
-      <c r="U49" t="n">
+      <c r="Y49" t="n">
         <v>22</v>
       </c>
-      <c r="V49" t="n">
+      <c r="Z49" t="n">
         <v>3</v>
       </c>
-      <c r="W49" t="n">
+      <c r="AA49" t="n">
         <v>11</v>
       </c>
-      <c r="X49" t="n">
+      <c r="AB49" t="n">
         <v>83.30591760243827</v>
       </c>
-      <c r="Y49" t="n">
+      <c r="AC49" t="n">
         <v>18</v>
       </c>
     </row>
@@ -4490,64 +4706,347 @@
       <c r="E50" t="n">
         <v>0.9</v>
       </c>
-      <c r="F50" t="n">
-        <v>2</v>
-      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H50" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="I50" t="n">
-        <v>20</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L50" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M50" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="n">
+        <v>10</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P50" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="n">
         <v>13</v>
       </c>
-      <c r="O50" t="n">
-        <v>2</v>
-      </c>
-      <c r="P50" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>2</v>
-      </c>
-      <c r="R50" t="n">
+      <c r="S50" t="n">
+        <v>2</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
+      </c>
+      <c r="V50" t="n">
         <v>7</v>
-      </c>
-      <c r="S50" t="n">
-        <v>22</v>
-      </c>
-      <c r="T50" t="n">
-        <v>27</v>
-      </c>
-      <c r="U50" t="n">
-        <v>2</v>
-      </c>
-      <c r="V50" t="n">
-        <v>2</v>
       </c>
       <c r="W50" t="n">
         <v>22</v>
       </c>
       <c r="X50" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB50" t="n">
         <v>60.75436103269089</v>
       </c>
-      <c r="Y50" t="n">
+      <c r="AC50" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_09-31-38</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2</v>
+      </c>
+      <c r="H51" t="n">
+        <v>10</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>20</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" t="n">
+        <v>20</v>
+      </c>
+      <c r="N51" t="n">
+        <v>10</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P51" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>10</v>
+      </c>
+      <c r="R51" t="n">
+        <v>18</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>11</v>
+      </c>
+      <c r="U51" t="n">
+        <v>4</v>
+      </c>
+      <c r="V51" t="n">
+        <v>18</v>
+      </c>
+      <c r="W51" t="n">
+        <v>6</v>
+      </c>
+      <c r="X51" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>83.62958536688184</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_09-31-38</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2</v>
+      </c>
+      <c r="H52" t="n">
+        <v>10</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>20</v>
+      </c>
+      <c r="L52" t="n">
+        <v>1</v>
+      </c>
+      <c r="M52" t="n">
+        <v>20</v>
+      </c>
+      <c r="N52" t="n">
+        <v>10</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P52" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>10</v>
+      </c>
+      <c r="R52" t="n">
+        <v>2</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2</v>
+      </c>
+      <c r="T52" t="n">
+        <v>9</v>
+      </c>
+      <c r="U52" t="n">
+        <v>9</v>
+      </c>
+      <c r="V52" t="n">
+        <v>26</v>
+      </c>
+      <c r="W52" t="n">
+        <v>22</v>
+      </c>
+      <c r="X52" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>70.28350465061963</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_09-31-38</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>2</v>
+      </c>
+      <c r="H53" t="n">
+        <v>10</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>20</v>
+      </c>
+      <c r="L53" t="n">
+        <v>1</v>
+      </c>
+      <c r="M53" t="n">
+        <v>20</v>
+      </c>
+      <c r="N53" t="n">
+        <v>10</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P53" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>10</v>
+      </c>
+      <c r="R53" t="n">
+        <v>20</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="n">
+        <v>10</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
+      </c>
+      <c r="V53" t="n">
+        <v>18</v>
+      </c>
+      <c r="W53" t="n">
+        <v>20</v>
+      </c>
+      <c r="X53" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>81.5538916534439</v>
+      </c>
+      <c r="AC53" t="n">
         <v>19</v>
       </c>
     </row>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC53"/>
+  <dimension ref="A1:AC74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -5050,6 +5050,1959 @@
         <v>19</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_09-31-38</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>4</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2</v>
+      </c>
+      <c r="H54" t="n">
+        <v>10</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>20</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1</v>
+      </c>
+      <c r="M54" t="n">
+        <v>20</v>
+      </c>
+      <c r="N54" t="n">
+        <v>10</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P54" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>10</v>
+      </c>
+      <c r="R54" t="n">
+        <v>14</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>5</v>
+      </c>
+      <c r="U54" t="n">
+        <v>11</v>
+      </c>
+      <c r="V54" t="n">
+        <v>14</v>
+      </c>
+      <c r="W54" t="n">
+        <v>20</v>
+      </c>
+      <c r="X54" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>69.96481884499433</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_09-31-38</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>5</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2</v>
+      </c>
+      <c r="H55" t="n">
+        <v>10</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>20</v>
+      </c>
+      <c r="L55" t="n">
+        <v>1</v>
+      </c>
+      <c r="M55" t="n">
+        <v>20</v>
+      </c>
+      <c r="N55" t="n">
+        <v>10</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P55" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>10</v>
+      </c>
+      <c r="R55" t="n">
+        <v>2</v>
+      </c>
+      <c r="S55" t="n">
+        <v>3</v>
+      </c>
+      <c r="T55" t="n">
+        <v>31</v>
+      </c>
+      <c r="U55" t="n">
+        <v>23</v>
+      </c>
+      <c r="V55" t="n">
+        <v>2</v>
+      </c>
+      <c r="W55" t="n">
+        <v>3</v>
+      </c>
+      <c r="X55" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>31</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>91.23074538392875</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_09-31-38</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>6</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2</v>
+      </c>
+      <c r="H56" t="n">
+        <v>10</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>20</v>
+      </c>
+      <c r="L56" t="n">
+        <v>1</v>
+      </c>
+      <c r="M56" t="n">
+        <v>20</v>
+      </c>
+      <c r="N56" t="n">
+        <v>10</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P56" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>10</v>
+      </c>
+      <c r="R56" t="n">
+        <v>5</v>
+      </c>
+      <c r="S56" t="n">
+        <v>11</v>
+      </c>
+      <c r="T56" t="n">
+        <v>5</v>
+      </c>
+      <c r="U56" t="n">
+        <v>21</v>
+      </c>
+      <c r="V56" t="n">
+        <v>25</v>
+      </c>
+      <c r="W56" t="n">
+        <v>21</v>
+      </c>
+      <c r="X56" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>77.91403492021858</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_09-31-38</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>7</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>2</v>
+      </c>
+      <c r="H57" t="n">
+        <v>10</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>20</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M57" t="n">
+        <v>20</v>
+      </c>
+      <c r="N57" t="n">
+        <v>10</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P57" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>10</v>
+      </c>
+      <c r="R57" t="n">
+        <v>25</v>
+      </c>
+      <c r="S57" t="n">
+        <v>11</v>
+      </c>
+      <c r="T57" t="n">
+        <v>21</v>
+      </c>
+      <c r="U57" t="n">
+        <v>25</v>
+      </c>
+      <c r="V57" t="n">
+        <v>21</v>
+      </c>
+      <c r="W57" t="n">
+        <v>7</v>
+      </c>
+      <c r="X57" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>31</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>90.3892695833925</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_09-31-38</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2</v>
+      </c>
+      <c r="H58" t="n">
+        <v>10</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>20</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1</v>
+      </c>
+      <c r="M58" t="n">
+        <v>20</v>
+      </c>
+      <c r="N58" t="n">
+        <v>10</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P58" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>10</v>
+      </c>
+      <c r="R58" t="n">
+        <v>31</v>
+      </c>
+      <c r="S58" t="n">
+        <v>18</v>
+      </c>
+      <c r="T58" t="n">
+        <v>18</v>
+      </c>
+      <c r="U58" t="n">
+        <v>31</v>
+      </c>
+      <c r="V58" t="n">
+        <v>24</v>
+      </c>
+      <c r="W58" t="n">
+        <v>30</v>
+      </c>
+      <c r="X58" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>71.03936704629072</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_09-31-38</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" t="n">
+        <v>2</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2</v>
+      </c>
+      <c r="H59" t="n">
+        <v>10</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>20</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1</v>
+      </c>
+      <c r="M59" t="n">
+        <v>20</v>
+      </c>
+      <c r="N59" t="n">
+        <v>10</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P59" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>10</v>
+      </c>
+      <c r="R59" t="n">
+        <v>23</v>
+      </c>
+      <c r="S59" t="n">
+        <v>12</v>
+      </c>
+      <c r="T59" t="n">
+        <v>29</v>
+      </c>
+      <c r="U59" t="n">
+        <v>28</v>
+      </c>
+      <c r="V59" t="n">
+        <v>23</v>
+      </c>
+      <c r="W59" t="n">
+        <v>29</v>
+      </c>
+      <c r="X59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>70.29502002498131</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_09-31-38</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>3</v>
+      </c>
+      <c r="D60" t="n">
+        <v>2</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>2</v>
+      </c>
+      <c r="H60" t="n">
+        <v>10</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>20</v>
+      </c>
+      <c r="L60" t="n">
+        <v>1</v>
+      </c>
+      <c r="M60" t="n">
+        <v>20</v>
+      </c>
+      <c r="N60" t="n">
+        <v>10</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P60" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>10</v>
+      </c>
+      <c r="R60" t="n">
+        <v>25</v>
+      </c>
+      <c r="S60" t="n">
+        <v>8</v>
+      </c>
+      <c r="T60" t="n">
+        <v>8</v>
+      </c>
+      <c r="U60" t="n">
+        <v>31</v>
+      </c>
+      <c r="V60" t="n">
+        <v>8</v>
+      </c>
+      <c r="W60" t="n">
+        <v>21</v>
+      </c>
+      <c r="X60" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>90.61766048075884</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_09-31-38</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>4</v>
+      </c>
+      <c r="D61" t="n">
+        <v>2</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>2</v>
+      </c>
+      <c r="H61" t="n">
+        <v>10</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>20</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1</v>
+      </c>
+      <c r="M61" t="n">
+        <v>20</v>
+      </c>
+      <c r="N61" t="n">
+        <v>10</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P61" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>10</v>
+      </c>
+      <c r="R61" t="n">
+        <v>26</v>
+      </c>
+      <c r="S61" t="n">
+        <v>9</v>
+      </c>
+      <c r="T61" t="n">
+        <v>17</v>
+      </c>
+      <c r="U61" t="n">
+        <v>17</v>
+      </c>
+      <c r="V61" t="n">
+        <v>27</v>
+      </c>
+      <c r="W61" t="n">
+        <v>18</v>
+      </c>
+      <c r="X61" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>80.10815500375237</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_09-31-38</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>5</v>
+      </c>
+      <c r="D62" t="n">
+        <v>2</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>2</v>
+      </c>
+      <c r="H62" t="n">
+        <v>10</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>20</v>
+      </c>
+      <c r="L62" t="n">
+        <v>1</v>
+      </c>
+      <c r="M62" t="n">
+        <v>20</v>
+      </c>
+      <c r="N62" t="n">
+        <v>10</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P62" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>10</v>
+      </c>
+      <c r="R62" t="n">
+        <v>15</v>
+      </c>
+      <c r="S62" t="n">
+        <v>16</v>
+      </c>
+      <c r="T62" t="n">
+        <v>10</v>
+      </c>
+      <c r="U62" t="n">
+        <v>10</v>
+      </c>
+      <c r="V62" t="n">
+        <v>26</v>
+      </c>
+      <c r="W62" t="n">
+        <v>26</v>
+      </c>
+      <c r="X62" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>76.10668818897702</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_09-31-38</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>6</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>2</v>
+      </c>
+      <c r="H63" t="n">
+        <v>10</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>20</v>
+      </c>
+      <c r="L63" t="n">
+        <v>1</v>
+      </c>
+      <c r="M63" t="n">
+        <v>20</v>
+      </c>
+      <c r="N63" t="n">
+        <v>10</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P63" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>10</v>
+      </c>
+      <c r="R63" t="n">
+        <v>29</v>
+      </c>
+      <c r="S63" t="n">
+        <v>30</v>
+      </c>
+      <c r="T63" t="n">
+        <v>28</v>
+      </c>
+      <c r="U63" t="n">
+        <v>7</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1</v>
+      </c>
+      <c r="W63" t="n">
+        <v>7</v>
+      </c>
+      <c r="X63" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>83.95485074397826</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_09-31-38</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>7</v>
+      </c>
+      <c r="D64" t="n">
+        <v>2</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>2</v>
+      </c>
+      <c r="H64" t="n">
+        <v>10</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>20</v>
+      </c>
+      <c r="L64" t="n">
+        <v>1</v>
+      </c>
+      <c r="M64" t="n">
+        <v>20</v>
+      </c>
+      <c r="N64" t="n">
+        <v>10</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P64" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>10</v>
+      </c>
+      <c r="R64" t="n">
+        <v>27</v>
+      </c>
+      <c r="S64" t="n">
+        <v>22</v>
+      </c>
+      <c r="T64" t="n">
+        <v>10</v>
+      </c>
+      <c r="U64" t="n">
+        <v>31</v>
+      </c>
+      <c r="V64" t="n">
+        <v>31</v>
+      </c>
+      <c r="W64" t="n">
+        <v>27</v>
+      </c>
+      <c r="X64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>72.34833197231806</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_09-31-38</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="n">
+        <v>3</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="n">
+        <v>2</v>
+      </c>
+      <c r="H65" t="n">
+        <v>10</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>20</v>
+      </c>
+      <c r="L65" t="n">
+        <v>1</v>
+      </c>
+      <c r="M65" t="n">
+        <v>20</v>
+      </c>
+      <c r="N65" t="n">
+        <v>10</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P65" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>10</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7</v>
+      </c>
+      <c r="S65" t="n">
+        <v>26</v>
+      </c>
+      <c r="T65" t="n">
+        <v>26</v>
+      </c>
+      <c r="U65" t="n">
+        <v>7</v>
+      </c>
+      <c r="V65" t="n">
+        <v>20</v>
+      </c>
+      <c r="W65" t="n">
+        <v>8</v>
+      </c>
+      <c r="X65" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>31</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>79.6032091818544</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_09-31-38</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" t="n">
+        <v>3</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2</v>
+      </c>
+      <c r="H66" t="n">
+        <v>10</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>20</v>
+      </c>
+      <c r="L66" t="n">
+        <v>1</v>
+      </c>
+      <c r="M66" t="n">
+        <v>20</v>
+      </c>
+      <c r="N66" t="n">
+        <v>10</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P66" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>10</v>
+      </c>
+      <c r="R66" t="n">
+        <v>10</v>
+      </c>
+      <c r="S66" t="n">
+        <v>9</v>
+      </c>
+      <c r="T66" t="n">
+        <v>7</v>
+      </c>
+      <c r="U66" t="n">
+        <v>3</v>
+      </c>
+      <c r="V66" t="n">
+        <v>3</v>
+      </c>
+      <c r="W66" t="n">
+        <v>12</v>
+      </c>
+      <c r="X66" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>80.6576796606395</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_09-31-38</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>3</v>
+      </c>
+      <c r="D67" t="n">
+        <v>3</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2</v>
+      </c>
+      <c r="H67" t="n">
+        <v>10</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>20</v>
+      </c>
+      <c r="L67" t="n">
+        <v>1</v>
+      </c>
+      <c r="M67" t="n">
+        <v>20</v>
+      </c>
+      <c r="N67" t="n">
+        <v>10</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P67" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>10</v>
+      </c>
+      <c r="R67" t="n">
+        <v>28</v>
+      </c>
+      <c r="S67" t="n">
+        <v>15</v>
+      </c>
+      <c r="T67" t="n">
+        <v>28</v>
+      </c>
+      <c r="U67" t="n">
+        <v>13</v>
+      </c>
+      <c r="V67" t="n">
+        <v>30</v>
+      </c>
+      <c r="W67" t="n">
+        <v>15</v>
+      </c>
+      <c r="X67" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>94.35191265863823</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_09-31-38</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>4</v>
+      </c>
+      <c r="D68" t="n">
+        <v>3</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
+        <v>2</v>
+      </c>
+      <c r="H68" t="n">
+        <v>10</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>20</v>
+      </c>
+      <c r="L68" t="n">
+        <v>1</v>
+      </c>
+      <c r="M68" t="n">
+        <v>20</v>
+      </c>
+      <c r="N68" t="n">
+        <v>10</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P68" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>10</v>
+      </c>
+      <c r="R68" t="n">
+        <v>11</v>
+      </c>
+      <c r="S68" t="n">
+        <v>30</v>
+      </c>
+      <c r="T68" t="n">
+        <v>30</v>
+      </c>
+      <c r="U68" t="n">
+        <v>11</v>
+      </c>
+      <c r="V68" t="n">
+        <v>17</v>
+      </c>
+      <c r="W68" t="n">
+        <v>6</v>
+      </c>
+      <c r="X68" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>91.22155975665849</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_09-31-38</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>5</v>
+      </c>
+      <c r="D69" t="n">
+        <v>3</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>2</v>
+      </c>
+      <c r="H69" t="n">
+        <v>10</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>20</v>
+      </c>
+      <c r="L69" t="n">
+        <v>1</v>
+      </c>
+      <c r="M69" t="n">
+        <v>20</v>
+      </c>
+      <c r="N69" t="n">
+        <v>10</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P69" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>10</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1</v>
+      </c>
+      <c r="S69" t="n">
+        <v>22</v>
+      </c>
+      <c r="T69" t="n">
+        <v>21</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
+      </c>
+      <c r="V69" t="n">
+        <v>28</v>
+      </c>
+      <c r="W69" t="n">
+        <v>22</v>
+      </c>
+      <c r="X69" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>85.92082288136916</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_09-31-38</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>6</v>
+      </c>
+      <c r="D70" t="n">
+        <v>3</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>2</v>
+      </c>
+      <c r="H70" t="n">
+        <v>10</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>20</v>
+      </c>
+      <c r="L70" t="n">
+        <v>1</v>
+      </c>
+      <c r="M70" t="n">
+        <v>20</v>
+      </c>
+      <c r="N70" t="n">
+        <v>10</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P70" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>10</v>
+      </c>
+      <c r="R70" t="n">
+        <v>12</v>
+      </c>
+      <c r="S70" t="n">
+        <v>4</v>
+      </c>
+      <c r="T70" t="n">
+        <v>9</v>
+      </c>
+      <c r="U70" t="n">
+        <v>12</v>
+      </c>
+      <c r="V70" t="n">
+        <v>19</v>
+      </c>
+      <c r="W70" t="n">
+        <v>10</v>
+      </c>
+      <c r="X70" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>100.9821152014726</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_09-31-38</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>7</v>
+      </c>
+      <c r="D71" t="n">
+        <v>3</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>2</v>
+      </c>
+      <c r="H71" t="n">
+        <v>10</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>20</v>
+      </c>
+      <c r="L71" t="n">
+        <v>1</v>
+      </c>
+      <c r="M71" t="n">
+        <v>20</v>
+      </c>
+      <c r="N71" t="n">
+        <v>10</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P71" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>10</v>
+      </c>
+      <c r="R71" t="n">
+        <v>13</v>
+      </c>
+      <c r="S71" t="n">
+        <v>21</v>
+      </c>
+      <c r="T71" t="n">
+        <v>20</v>
+      </c>
+      <c r="U71" t="n">
+        <v>14</v>
+      </c>
+      <c r="V71" t="n">
+        <v>28</v>
+      </c>
+      <c r="W71" t="n">
+        <v>21</v>
+      </c>
+      <c r="X71" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>82.94329206738793</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_09-31-38</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="n">
+        <v>4</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="n">
+        <v>2</v>
+      </c>
+      <c r="H72" t="n">
+        <v>10</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>20</v>
+      </c>
+      <c r="L72" t="n">
+        <v>1</v>
+      </c>
+      <c r="M72" t="n">
+        <v>20</v>
+      </c>
+      <c r="N72" t="n">
+        <v>10</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P72" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>10</v>
+      </c>
+      <c r="R72" t="n">
+        <v>8</v>
+      </c>
+      <c r="S72" t="n">
+        <v>14</v>
+      </c>
+      <c r="T72" t="n">
+        <v>28</v>
+      </c>
+      <c r="U72" t="n">
+        <v>20</v>
+      </c>
+      <c r="V72" t="n">
+        <v>8</v>
+      </c>
+      <c r="W72" t="n">
+        <v>29</v>
+      </c>
+      <c r="X72" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>89.95663958569145</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_09-31-38</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>2</v>
+      </c>
+      <c r="D73" t="n">
+        <v>4</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>2</v>
+      </c>
+      <c r="H73" t="n">
+        <v>10</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>20</v>
+      </c>
+      <c r="L73" t="n">
+        <v>1</v>
+      </c>
+      <c r="M73" t="n">
+        <v>20</v>
+      </c>
+      <c r="N73" t="n">
+        <v>10</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P73" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>10</v>
+      </c>
+      <c r="R73" t="n">
+        <v>24</v>
+      </c>
+      <c r="S73" t="n">
+        <v>25</v>
+      </c>
+      <c r="T73" t="n">
+        <v>25</v>
+      </c>
+      <c r="U73" t="n">
+        <v>13</v>
+      </c>
+      <c r="V73" t="n">
+        <v>2</v>
+      </c>
+      <c r="W73" t="n">
+        <v>31</v>
+      </c>
+      <c r="X73" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>70.72014930294843</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_09-31-38</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>3</v>
+      </c>
+      <c r="D74" t="n">
+        <v>4</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>2</v>
+      </c>
+      <c r="H74" t="n">
+        <v>10</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>20</v>
+      </c>
+      <c r="L74" t="n">
+        <v>1</v>
+      </c>
+      <c r="M74" t="n">
+        <v>20</v>
+      </c>
+      <c r="N74" t="n">
+        <v>10</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P74" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>10</v>
+      </c>
+      <c r="R74" t="n">
+        <v>10</v>
+      </c>
+      <c r="S74" t="n">
+        <v>19</v>
+      </c>
+      <c r="T74" t="n">
+        <v>25</v>
+      </c>
+      <c r="U74" t="n">
+        <v>24</v>
+      </c>
+      <c r="V74" t="n">
+        <v>24</v>
+      </c>
+      <c r="W74" t="n">
+        <v>26</v>
+      </c>
+      <c r="X74" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>64.36583496108256</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC74"/>
+  <dimension ref="A1:AC92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -7003,6 +7003,1680 @@
         <v>16</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_12-36-25</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2</v>
+      </c>
+      <c r="H75" t="n">
+        <v>10</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>20</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1</v>
+      </c>
+      <c r="M75" t="n">
+        <v>20</v>
+      </c>
+      <c r="N75" t="n">
+        <v>10</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P75" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>10</v>
+      </c>
+      <c r="R75" t="n">
+        <v>3</v>
+      </c>
+      <c r="S75" t="n">
+        <v>3</v>
+      </c>
+      <c r="T75" t="n">
+        <v>3</v>
+      </c>
+      <c r="U75" t="n">
+        <v>3</v>
+      </c>
+      <c r="V75" t="n">
+        <v>11</v>
+      </c>
+      <c r="W75" t="n">
+        <v>26</v>
+      </c>
+      <c r="X75" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>73.78724275057083</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_12-36-25</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>2</v>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>2</v>
+      </c>
+      <c r="H76" t="n">
+        <v>10</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>20</v>
+      </c>
+      <c r="L76" t="n">
+        <v>1</v>
+      </c>
+      <c r="M76" t="n">
+        <v>20</v>
+      </c>
+      <c r="N76" t="n">
+        <v>10</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P76" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>10</v>
+      </c>
+      <c r="R76" t="n">
+        <v>28</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="n">
+        <v>10</v>
+      </c>
+      <c r="U76" t="n">
+        <v>28</v>
+      </c>
+      <c r="V76" t="n">
+        <v>28</v>
+      </c>
+      <c r="W76" t="n">
+        <v>26</v>
+      </c>
+      <c r="X76" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>76.17908603751954</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_12-36-25</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>3</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>2</v>
+      </c>
+      <c r="H77" t="n">
+        <v>10</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>20</v>
+      </c>
+      <c r="L77" t="n">
+        <v>1</v>
+      </c>
+      <c r="M77" t="n">
+        <v>20</v>
+      </c>
+      <c r="N77" t="n">
+        <v>10</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P77" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>10</v>
+      </c>
+      <c r="R77" t="n">
+        <v>5</v>
+      </c>
+      <c r="S77" t="n">
+        <v>29</v>
+      </c>
+      <c r="T77" t="n">
+        <v>5</v>
+      </c>
+      <c r="U77" t="n">
+        <v>10</v>
+      </c>
+      <c r="V77" t="n">
+        <v>16</v>
+      </c>
+      <c r="W77" t="n">
+        <v>25</v>
+      </c>
+      <c r="X77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>70.77780894915028</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_12-36-25</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>4</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>2</v>
+      </c>
+      <c r="H78" t="n">
+        <v>10</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>20</v>
+      </c>
+      <c r="L78" t="n">
+        <v>1</v>
+      </c>
+      <c r="M78" t="n">
+        <v>20</v>
+      </c>
+      <c r="N78" t="n">
+        <v>10</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P78" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>10</v>
+      </c>
+      <c r="R78" t="n">
+        <v>2</v>
+      </c>
+      <c r="S78" t="n">
+        <v>19</v>
+      </c>
+      <c r="T78" t="n">
+        <v>19</v>
+      </c>
+      <c r="U78" t="n">
+        <v>11</v>
+      </c>
+      <c r="V78" t="n">
+        <v>2</v>
+      </c>
+      <c r="W78" t="n">
+        <v>2</v>
+      </c>
+      <c r="X78" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>79.43102267615259</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_12-36-25</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>5</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
+        <v>2</v>
+      </c>
+      <c r="H79" t="n">
+        <v>10</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>20</v>
+      </c>
+      <c r="L79" t="n">
+        <v>1</v>
+      </c>
+      <c r="M79" t="n">
+        <v>20</v>
+      </c>
+      <c r="N79" t="n">
+        <v>10</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P79" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>10</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7</v>
+      </c>
+      <c r="S79" t="n">
+        <v>4</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2</v>
+      </c>
+      <c r="U79" t="n">
+        <v>2</v>
+      </c>
+      <c r="V79" t="n">
+        <v>23</v>
+      </c>
+      <c r="W79" t="n">
+        <v>16</v>
+      </c>
+      <c r="X79" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>82.43808998802103</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_12-36-25</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>6</v>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>2</v>
+      </c>
+      <c r="H80" t="n">
+        <v>10</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>20</v>
+      </c>
+      <c r="L80" t="n">
+        <v>1</v>
+      </c>
+      <c r="M80" t="n">
+        <v>20</v>
+      </c>
+      <c r="N80" t="n">
+        <v>10</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P80" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>10</v>
+      </c>
+      <c r="R80" t="n">
+        <v>13</v>
+      </c>
+      <c r="S80" t="n">
+        <v>14</v>
+      </c>
+      <c r="T80" t="n">
+        <v>8</v>
+      </c>
+      <c r="U80" t="n">
+        <v>9</v>
+      </c>
+      <c r="V80" t="n">
+        <v>20</v>
+      </c>
+      <c r="W80" t="n">
+        <v>13</v>
+      </c>
+      <c r="X80" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>87.32889206035736</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_12-36-25</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>7</v>
+      </c>
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>2</v>
+      </c>
+      <c r="H81" t="n">
+        <v>10</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>20</v>
+      </c>
+      <c r="L81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M81" t="n">
+        <v>20</v>
+      </c>
+      <c r="N81" t="n">
+        <v>10</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P81" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>10</v>
+      </c>
+      <c r="R81" t="n">
+        <v>24</v>
+      </c>
+      <c r="S81" t="n">
+        <v>24</v>
+      </c>
+      <c r="T81" t="n">
+        <v>25</v>
+      </c>
+      <c r="U81" t="n">
+        <v>18</v>
+      </c>
+      <c r="V81" t="n">
+        <v>29</v>
+      </c>
+      <c r="W81" t="n">
+        <v>0</v>
+      </c>
+      <c r="X81" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>71.85081189465204</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_12-36-25</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>8</v>
+      </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>2</v>
+      </c>
+      <c r="H82" t="n">
+        <v>10</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>20</v>
+      </c>
+      <c r="L82" t="n">
+        <v>1</v>
+      </c>
+      <c r="M82" t="n">
+        <v>20</v>
+      </c>
+      <c r="N82" t="n">
+        <v>10</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P82" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>10</v>
+      </c>
+      <c r="R82" t="n">
+        <v>18</v>
+      </c>
+      <c r="S82" t="n">
+        <v>28</v>
+      </c>
+      <c r="T82" t="n">
+        <v>28</v>
+      </c>
+      <c r="U82" t="n">
+        <v>28</v>
+      </c>
+      <c r="V82" t="n">
+        <v>28</v>
+      </c>
+      <c r="W82" t="n">
+        <v>8</v>
+      </c>
+      <c r="X82" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>72.03163115364866</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_12-36-25</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>9</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>2</v>
+      </c>
+      <c r="H83" t="n">
+        <v>10</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>20</v>
+      </c>
+      <c r="L83" t="n">
+        <v>1</v>
+      </c>
+      <c r="M83" t="n">
+        <v>20</v>
+      </c>
+      <c r="N83" t="n">
+        <v>10</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P83" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>10</v>
+      </c>
+      <c r="R83" t="n">
+        <v>15</v>
+      </c>
+      <c r="S83" t="n">
+        <v>24</v>
+      </c>
+      <c r="T83" t="n">
+        <v>14</v>
+      </c>
+      <c r="U83" t="n">
+        <v>7</v>
+      </c>
+      <c r="V83" t="n">
+        <v>29</v>
+      </c>
+      <c r="W83" t="n">
+        <v>1</v>
+      </c>
+      <c r="X83" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>81.80476421593224</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_12-56-14</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>2</v>
+      </c>
+      <c r="H84" t="n">
+        <v>10</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>20</v>
+      </c>
+      <c r="L84" t="n">
+        <v>1</v>
+      </c>
+      <c r="M84" t="n">
+        <v>20</v>
+      </c>
+      <c r="N84" t="n">
+        <v>10</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P84" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>10</v>
+      </c>
+      <c r="R84" t="n">
+        <v>15</v>
+      </c>
+      <c r="S84" t="n">
+        <v>4</v>
+      </c>
+      <c r="T84" t="n">
+        <v>4</v>
+      </c>
+      <c r="U84" t="n">
+        <v>4</v>
+      </c>
+      <c r="V84" t="n">
+        <v>15</v>
+      </c>
+      <c r="W84" t="n">
+        <v>31</v>
+      </c>
+      <c r="X84" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>31</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>80.66023053161592</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_12-56-14</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>2</v>
+      </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>2</v>
+      </c>
+      <c r="H85" t="n">
+        <v>10</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>20</v>
+      </c>
+      <c r="L85" t="n">
+        <v>1</v>
+      </c>
+      <c r="M85" t="n">
+        <v>20</v>
+      </c>
+      <c r="N85" t="n">
+        <v>10</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P85" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>10</v>
+      </c>
+      <c r="R85" t="n">
+        <v>10</v>
+      </c>
+      <c r="S85" t="n">
+        <v>12</v>
+      </c>
+      <c r="T85" t="n">
+        <v>11</v>
+      </c>
+      <c r="U85" t="n">
+        <v>10</v>
+      </c>
+      <c r="V85" t="n">
+        <v>0</v>
+      </c>
+      <c r="W85" t="n">
+        <v>12</v>
+      </c>
+      <c r="X85" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>70.14666828285621</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_12-56-14</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>3</v>
+      </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>2</v>
+      </c>
+      <c r="H86" t="n">
+        <v>10</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>20</v>
+      </c>
+      <c r="L86" t="n">
+        <v>1</v>
+      </c>
+      <c r="M86" t="n">
+        <v>20</v>
+      </c>
+      <c r="N86" t="n">
+        <v>10</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P86" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>10</v>
+      </c>
+      <c r="R86" t="n">
+        <v>5</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="n">
+        <v>5</v>
+      </c>
+      <c r="U86" t="n">
+        <v>4</v>
+      </c>
+      <c r="V86" t="n">
+        <v>5</v>
+      </c>
+      <c r="W86" t="n">
+        <v>12</v>
+      </c>
+      <c r="X86" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>71.89511224673814</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_12-56-14</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>4</v>
+      </c>
+      <c r="D87" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>2</v>
+      </c>
+      <c r="H87" t="n">
+        <v>10</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>20</v>
+      </c>
+      <c r="L87" t="n">
+        <v>1</v>
+      </c>
+      <c r="M87" t="n">
+        <v>20</v>
+      </c>
+      <c r="N87" t="n">
+        <v>10</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P87" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>10</v>
+      </c>
+      <c r="R87" t="n">
+        <v>25</v>
+      </c>
+      <c r="S87" t="n">
+        <v>26</v>
+      </c>
+      <c r="T87" t="n">
+        <v>26</v>
+      </c>
+      <c r="U87" t="n">
+        <v>25</v>
+      </c>
+      <c r="V87" t="n">
+        <v>17</v>
+      </c>
+      <c r="W87" t="n">
+        <v>11</v>
+      </c>
+      <c r="X87" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>80.3040159455697</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_12-56-14</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>5</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>2</v>
+      </c>
+      <c r="H88" t="n">
+        <v>10</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>20</v>
+      </c>
+      <c r="L88" t="n">
+        <v>1</v>
+      </c>
+      <c r="M88" t="n">
+        <v>20</v>
+      </c>
+      <c r="N88" t="n">
+        <v>10</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P88" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>10</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7</v>
+      </c>
+      <c r="S88" t="n">
+        <v>14</v>
+      </c>
+      <c r="T88" t="n">
+        <v>2</v>
+      </c>
+      <c r="U88" t="n">
+        <v>26</v>
+      </c>
+      <c r="V88" t="n">
+        <v>26</v>
+      </c>
+      <c r="W88" t="n">
+        <v>20</v>
+      </c>
+      <c r="X88" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>91.43248535301586</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_12-56-14</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>6</v>
+      </c>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>2</v>
+      </c>
+      <c r="H89" t="n">
+        <v>10</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>20</v>
+      </c>
+      <c r="L89" t="n">
+        <v>1</v>
+      </c>
+      <c r="M89" t="n">
+        <v>20</v>
+      </c>
+      <c r="N89" t="n">
+        <v>10</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P89" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>10</v>
+      </c>
+      <c r="R89" t="n">
+        <v>27</v>
+      </c>
+      <c r="S89" t="n">
+        <v>27</v>
+      </c>
+      <c r="T89" t="n">
+        <v>31</v>
+      </c>
+      <c r="U89" t="n">
+        <v>27</v>
+      </c>
+      <c r="V89" t="n">
+        <v>21</v>
+      </c>
+      <c r="W89" t="n">
+        <v>5</v>
+      </c>
+      <c r="X89" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>31</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>90.09116093324292</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_12-56-14</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>7</v>
+      </c>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>2</v>
+      </c>
+      <c r="H90" t="n">
+        <v>10</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>20</v>
+      </c>
+      <c r="L90" t="n">
+        <v>1</v>
+      </c>
+      <c r="M90" t="n">
+        <v>20</v>
+      </c>
+      <c r="N90" t="n">
+        <v>10</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P90" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>10</v>
+      </c>
+      <c r="R90" t="n">
+        <v>29</v>
+      </c>
+      <c r="S90" t="n">
+        <v>30</v>
+      </c>
+      <c r="T90" t="n">
+        <v>29</v>
+      </c>
+      <c r="U90" t="n">
+        <v>24</v>
+      </c>
+      <c r="V90" t="n">
+        <v>20</v>
+      </c>
+      <c r="W90" t="n">
+        <v>14</v>
+      </c>
+      <c r="X90" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA90" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>84.270182858442</v>
+      </c>
+      <c r="AC90" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_12-56-14</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>8</v>
+      </c>
+      <c r="D91" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>2</v>
+      </c>
+      <c r="H91" t="n">
+        <v>10</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>20</v>
+      </c>
+      <c r="L91" t="n">
+        <v>1</v>
+      </c>
+      <c r="M91" t="n">
+        <v>20</v>
+      </c>
+      <c r="N91" t="n">
+        <v>10</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P91" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>10</v>
+      </c>
+      <c r="R91" t="n">
+        <v>30</v>
+      </c>
+      <c r="S91" t="n">
+        <v>5</v>
+      </c>
+      <c r="T91" t="n">
+        <v>6</v>
+      </c>
+      <c r="U91" t="n">
+        <v>30</v>
+      </c>
+      <c r="V91" t="n">
+        <v>19</v>
+      </c>
+      <c r="W91" t="n">
+        <v>7</v>
+      </c>
+      <c r="X91" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>79.57624366224009</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_12-56-14</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>9</v>
+      </c>
+      <c r="D92" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>2</v>
+      </c>
+      <c r="H92" t="n">
+        <v>10</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>20</v>
+      </c>
+      <c r="L92" t="n">
+        <v>1</v>
+      </c>
+      <c r="M92" t="n">
+        <v>20</v>
+      </c>
+      <c r="N92" t="n">
+        <v>10</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P92" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>10</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="n">
+        <v>1</v>
+      </c>
+      <c r="T92" t="n">
+        <v>1</v>
+      </c>
+      <c r="U92" t="n">
+        <v>16</v>
+      </c>
+      <c r="V92" t="n">
+        <v>25</v>
+      </c>
+      <c r="W92" t="n">
+        <v>27</v>
+      </c>
+      <c r="X92" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>71.90706968461106</v>
+      </c>
+      <c r="AC92" t="n">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC92"/>
+  <dimension ref="A1:AC101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -8677,6 +8677,843 @@
         <v>12</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-11-59</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>2</v>
+      </c>
+      <c r="H93" t="n">
+        <v>10</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
+        <v>20</v>
+      </c>
+      <c r="L93" t="n">
+        <v>1</v>
+      </c>
+      <c r="M93" t="n">
+        <v>20</v>
+      </c>
+      <c r="N93" t="n">
+        <v>10</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P93" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>10</v>
+      </c>
+      <c r="R93" t="n">
+        <v>9</v>
+      </c>
+      <c r="S93" t="n">
+        <v>11</v>
+      </c>
+      <c r="T93" t="n">
+        <v>1</v>
+      </c>
+      <c r="U93" t="n">
+        <v>26</v>
+      </c>
+      <c r="V93" t="n">
+        <v>9</v>
+      </c>
+      <c r="W93" t="n">
+        <v>21</v>
+      </c>
+      <c r="X93" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>81.59929238614657</v>
+      </c>
+      <c r="AC93" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-11-59</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>2</v>
+      </c>
+      <c r="D94" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>2</v>
+      </c>
+      <c r="H94" t="n">
+        <v>10</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>20</v>
+      </c>
+      <c r="L94" t="n">
+        <v>1</v>
+      </c>
+      <c r="M94" t="n">
+        <v>20</v>
+      </c>
+      <c r="N94" t="n">
+        <v>10</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P94" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>10</v>
+      </c>
+      <c r="R94" t="n">
+        <v>19</v>
+      </c>
+      <c r="S94" t="n">
+        <v>1</v>
+      </c>
+      <c r="T94" t="n">
+        <v>30</v>
+      </c>
+      <c r="U94" t="n">
+        <v>25</v>
+      </c>
+      <c r="V94" t="n">
+        <v>21</v>
+      </c>
+      <c r="W94" t="n">
+        <v>31</v>
+      </c>
+      <c r="X94" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>31</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>91.20370300559101</v>
+      </c>
+      <c r="AC94" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-11-59</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>3</v>
+      </c>
+      <c r="D95" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>2</v>
+      </c>
+      <c r="H95" t="n">
+        <v>10</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
+        <v>20</v>
+      </c>
+      <c r="L95" t="n">
+        <v>1</v>
+      </c>
+      <c r="M95" t="n">
+        <v>20</v>
+      </c>
+      <c r="N95" t="n">
+        <v>10</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P95" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>10</v>
+      </c>
+      <c r="R95" t="n">
+        <v>17</v>
+      </c>
+      <c r="S95" t="n">
+        <v>0</v>
+      </c>
+      <c r="T95" t="n">
+        <v>3</v>
+      </c>
+      <c r="U95" t="n">
+        <v>11</v>
+      </c>
+      <c r="V95" t="n">
+        <v>27</v>
+      </c>
+      <c r="W95" t="n">
+        <v>5</v>
+      </c>
+      <c r="X95" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA95" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>91.50992383097463</v>
+      </c>
+      <c r="AC95" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-11-59</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>4</v>
+      </c>
+      <c r="D96" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>2</v>
+      </c>
+      <c r="H96" t="n">
+        <v>10</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>20</v>
+      </c>
+      <c r="L96" t="n">
+        <v>1</v>
+      </c>
+      <c r="M96" t="n">
+        <v>20</v>
+      </c>
+      <c r="N96" t="n">
+        <v>10</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P96" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>10</v>
+      </c>
+      <c r="R96" t="n">
+        <v>12</v>
+      </c>
+      <c r="S96" t="n">
+        <v>5</v>
+      </c>
+      <c r="T96" t="n">
+        <v>29</v>
+      </c>
+      <c r="U96" t="n">
+        <v>7</v>
+      </c>
+      <c r="V96" t="n">
+        <v>10</v>
+      </c>
+      <c r="W96" t="n">
+        <v>16</v>
+      </c>
+      <c r="X96" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>83.51597533576862</v>
+      </c>
+      <c r="AC96" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-11-59</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>5</v>
+      </c>
+      <c r="D97" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>2</v>
+      </c>
+      <c r="H97" t="n">
+        <v>10</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>20</v>
+      </c>
+      <c r="L97" t="n">
+        <v>1</v>
+      </c>
+      <c r="M97" t="n">
+        <v>20</v>
+      </c>
+      <c r="N97" t="n">
+        <v>10</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P97" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>10</v>
+      </c>
+      <c r="R97" t="n">
+        <v>31</v>
+      </c>
+      <c r="S97" t="n">
+        <v>15</v>
+      </c>
+      <c r="T97" t="n">
+        <v>10</v>
+      </c>
+      <c r="U97" t="n">
+        <v>29</v>
+      </c>
+      <c r="V97" t="n">
+        <v>29</v>
+      </c>
+      <c r="W97" t="n">
+        <v>10</v>
+      </c>
+      <c r="X97" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z97" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA97" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>83.39607650522957</v>
+      </c>
+      <c r="AC97" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-11-59</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>6</v>
+      </c>
+      <c r="D98" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" t="n">
+        <v>2</v>
+      </c>
+      <c r="H98" t="n">
+        <v>10</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>20</v>
+      </c>
+      <c r="L98" t="n">
+        <v>1</v>
+      </c>
+      <c r="M98" t="n">
+        <v>20</v>
+      </c>
+      <c r="N98" t="n">
+        <v>10</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P98" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>10</v>
+      </c>
+      <c r="R98" t="n">
+        <v>1</v>
+      </c>
+      <c r="S98" t="n">
+        <v>31</v>
+      </c>
+      <c r="T98" t="n">
+        <v>31</v>
+      </c>
+      <c r="U98" t="n">
+        <v>1</v>
+      </c>
+      <c r="V98" t="n">
+        <v>7</v>
+      </c>
+      <c r="W98" t="n">
+        <v>3</v>
+      </c>
+      <c r="X98" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z98" t="n">
+        <v>31</v>
+      </c>
+      <c r="AA98" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB98" t="n">
+        <v>60.36298738026565</v>
+      </c>
+      <c r="AC98" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-11-59</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>7</v>
+      </c>
+      <c r="D99" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="n">
+        <v>2</v>
+      </c>
+      <c r="H99" t="n">
+        <v>10</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
+        <v>20</v>
+      </c>
+      <c r="L99" t="n">
+        <v>1</v>
+      </c>
+      <c r="M99" t="n">
+        <v>20</v>
+      </c>
+      <c r="N99" t="n">
+        <v>10</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P99" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>10</v>
+      </c>
+      <c r="R99" t="n">
+        <v>16</v>
+      </c>
+      <c r="S99" t="n">
+        <v>14</v>
+      </c>
+      <c r="T99" t="n">
+        <v>14</v>
+      </c>
+      <c r="U99" t="n">
+        <v>31</v>
+      </c>
+      <c r="V99" t="n">
+        <v>0</v>
+      </c>
+      <c r="W99" t="n">
+        <v>19</v>
+      </c>
+      <c r="X99" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA99" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>81.33401170113055</v>
+      </c>
+      <c r="AC99" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-11-59</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>8</v>
+      </c>
+      <c r="D100" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>2</v>
+      </c>
+      <c r="H100" t="n">
+        <v>10</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>20</v>
+      </c>
+      <c r="L100" t="n">
+        <v>1</v>
+      </c>
+      <c r="M100" t="n">
+        <v>20</v>
+      </c>
+      <c r="N100" t="n">
+        <v>10</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P100" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>10</v>
+      </c>
+      <c r="R100" t="n">
+        <v>12</v>
+      </c>
+      <c r="S100" t="n">
+        <v>14</v>
+      </c>
+      <c r="T100" t="n">
+        <v>13</v>
+      </c>
+      <c r="U100" t="n">
+        <v>13</v>
+      </c>
+      <c r="V100" t="n">
+        <v>1</v>
+      </c>
+      <c r="W100" t="n">
+        <v>21</v>
+      </c>
+      <c r="X100" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA100" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>94.24221039560808</v>
+      </c>
+      <c r="AC100" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-11-59</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>9</v>
+      </c>
+      <c r="D101" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>2</v>
+      </c>
+      <c r="H101" t="n">
+        <v>10</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>20</v>
+      </c>
+      <c r="L101" t="n">
+        <v>1</v>
+      </c>
+      <c r="M101" t="n">
+        <v>20</v>
+      </c>
+      <c r="N101" t="n">
+        <v>10</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P101" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>10</v>
+      </c>
+      <c r="R101" t="n">
+        <v>8</v>
+      </c>
+      <c r="S101" t="n">
+        <v>18</v>
+      </c>
+      <c r="T101" t="n">
+        <v>14</v>
+      </c>
+      <c r="U101" t="n">
+        <v>12</v>
+      </c>
+      <c r="V101" t="n">
+        <v>8</v>
+      </c>
+      <c r="W101" t="n">
+        <v>14</v>
+      </c>
+      <c r="X101" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>70.05807245169061</v>
+      </c>
+      <c r="AC101" t="n">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC101"/>
+  <dimension ref="A1:AC119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -9514,6 +9514,1680 @@
         <v>14</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-27-48</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>1</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="n">
+        <v>2</v>
+      </c>
+      <c r="H102" t="n">
+        <v>10</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>20</v>
+      </c>
+      <c r="L102" t="n">
+        <v>1</v>
+      </c>
+      <c r="M102" t="n">
+        <v>20</v>
+      </c>
+      <c r="N102" t="n">
+        <v>10</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P102" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>10</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6</v>
+      </c>
+      <c r="S102" t="n">
+        <v>11</v>
+      </c>
+      <c r="T102" t="n">
+        <v>1</v>
+      </c>
+      <c r="U102" t="n">
+        <v>10</v>
+      </c>
+      <c r="V102" t="n">
+        <v>12</v>
+      </c>
+      <c r="W102" t="n">
+        <v>6</v>
+      </c>
+      <c r="X102" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>71.27083524782145</v>
+      </c>
+      <c r="AC102" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-27-48</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>2</v>
+      </c>
+      <c r="D103" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" t="n">
+        <v>2</v>
+      </c>
+      <c r="H103" t="n">
+        <v>10</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>20</v>
+      </c>
+      <c r="L103" t="n">
+        <v>1</v>
+      </c>
+      <c r="M103" t="n">
+        <v>20</v>
+      </c>
+      <c r="N103" t="n">
+        <v>10</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P103" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>10</v>
+      </c>
+      <c r="R103" t="n">
+        <v>31</v>
+      </c>
+      <c r="S103" t="n">
+        <v>16</v>
+      </c>
+      <c r="T103" t="n">
+        <v>16</v>
+      </c>
+      <c r="U103" t="n">
+        <v>17</v>
+      </c>
+      <c r="V103" t="n">
+        <v>0</v>
+      </c>
+      <c r="W103" t="n">
+        <v>17</v>
+      </c>
+      <c r="X103" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA103" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>80.32374204294429</v>
+      </c>
+      <c r="AC103" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-27-48</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>3</v>
+      </c>
+      <c r="D104" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="n">
+        <v>2</v>
+      </c>
+      <c r="H104" t="n">
+        <v>10</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>20</v>
+      </c>
+      <c r="L104" t="n">
+        <v>1</v>
+      </c>
+      <c r="M104" t="n">
+        <v>20</v>
+      </c>
+      <c r="N104" t="n">
+        <v>10</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P104" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>10</v>
+      </c>
+      <c r="R104" t="n">
+        <v>11</v>
+      </c>
+      <c r="S104" t="n">
+        <v>17</v>
+      </c>
+      <c r="T104" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" t="n">
+        <v>17</v>
+      </c>
+      <c r="V104" t="n">
+        <v>5</v>
+      </c>
+      <c r="W104" t="n">
+        <v>17</v>
+      </c>
+      <c r="X104" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>90.15308331915274</v>
+      </c>
+      <c r="AC104" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-27-48</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>4</v>
+      </c>
+      <c r="D105" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" t="n">
+        <v>2</v>
+      </c>
+      <c r="H105" t="n">
+        <v>10</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>20</v>
+      </c>
+      <c r="L105" t="n">
+        <v>1</v>
+      </c>
+      <c r="M105" t="n">
+        <v>20</v>
+      </c>
+      <c r="N105" t="n">
+        <v>10</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P105" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>10</v>
+      </c>
+      <c r="R105" t="n">
+        <v>19</v>
+      </c>
+      <c r="S105" t="n">
+        <v>5</v>
+      </c>
+      <c r="T105" t="n">
+        <v>5</v>
+      </c>
+      <c r="U105" t="n">
+        <v>19</v>
+      </c>
+      <c r="V105" t="n">
+        <v>31</v>
+      </c>
+      <c r="W105" t="n">
+        <v>20</v>
+      </c>
+      <c r="X105" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>31</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA105" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>71.27131843280721</v>
+      </c>
+      <c r="AC105" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-27-48</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>5</v>
+      </c>
+      <c r="D106" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" t="n">
+        <v>2</v>
+      </c>
+      <c r="H106" t="n">
+        <v>10</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>20</v>
+      </c>
+      <c r="L106" t="n">
+        <v>1</v>
+      </c>
+      <c r="M106" t="n">
+        <v>20</v>
+      </c>
+      <c r="N106" t="n">
+        <v>10</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P106" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>10</v>
+      </c>
+      <c r="R106" t="n">
+        <v>5</v>
+      </c>
+      <c r="S106" t="n">
+        <v>31</v>
+      </c>
+      <c r="T106" t="n">
+        <v>27</v>
+      </c>
+      <c r="U106" t="n">
+        <v>25</v>
+      </c>
+      <c r="V106" t="n">
+        <v>25</v>
+      </c>
+      <c r="W106" t="n">
+        <v>7</v>
+      </c>
+      <c r="X106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>81.00982443887447</v>
+      </c>
+      <c r="AC106" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-27-48</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>6</v>
+      </c>
+      <c r="D107" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" t="n">
+        <v>2</v>
+      </c>
+      <c r="H107" t="n">
+        <v>10</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>20</v>
+      </c>
+      <c r="L107" t="n">
+        <v>1</v>
+      </c>
+      <c r="M107" t="n">
+        <v>20</v>
+      </c>
+      <c r="N107" t="n">
+        <v>10</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P107" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>10</v>
+      </c>
+      <c r="R107" t="n">
+        <v>14</v>
+      </c>
+      <c r="S107" t="n">
+        <v>31</v>
+      </c>
+      <c r="T107" t="n">
+        <v>7</v>
+      </c>
+      <c r="U107" t="n">
+        <v>14</v>
+      </c>
+      <c r="V107" t="n">
+        <v>14</v>
+      </c>
+      <c r="W107" t="n">
+        <v>1</v>
+      </c>
+      <c r="X107" t="n">
+        <v>31</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>62.05937180723794</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-27-48</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>7</v>
+      </c>
+      <c r="D108" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" t="n">
+        <v>2</v>
+      </c>
+      <c r="H108" t="n">
+        <v>10</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>20</v>
+      </c>
+      <c r="L108" t="n">
+        <v>1</v>
+      </c>
+      <c r="M108" t="n">
+        <v>20</v>
+      </c>
+      <c r="N108" t="n">
+        <v>10</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P108" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>10</v>
+      </c>
+      <c r="R108" t="n">
+        <v>26</v>
+      </c>
+      <c r="S108" t="n">
+        <v>27</v>
+      </c>
+      <c r="T108" t="n">
+        <v>27</v>
+      </c>
+      <c r="U108" t="n">
+        <v>18</v>
+      </c>
+      <c r="V108" t="n">
+        <v>26</v>
+      </c>
+      <c r="W108" t="n">
+        <v>1</v>
+      </c>
+      <c r="X108" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB108" t="n">
+        <v>80.6920425387038</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-27-48</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>8</v>
+      </c>
+      <c r="D109" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="n">
+        <v>2</v>
+      </c>
+      <c r="H109" t="n">
+        <v>10</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>20</v>
+      </c>
+      <c r="L109" t="n">
+        <v>1</v>
+      </c>
+      <c r="M109" t="n">
+        <v>20</v>
+      </c>
+      <c r="N109" t="n">
+        <v>10</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P109" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>10</v>
+      </c>
+      <c r="R109" t="n">
+        <v>30</v>
+      </c>
+      <c r="S109" t="n">
+        <v>2</v>
+      </c>
+      <c r="T109" t="n">
+        <v>9</v>
+      </c>
+      <c r="U109" t="n">
+        <v>18</v>
+      </c>
+      <c r="V109" t="n">
+        <v>3</v>
+      </c>
+      <c r="W109" t="n">
+        <v>7</v>
+      </c>
+      <c r="X109" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB109" t="n">
+        <v>81.80934525964373</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-27-48</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>9</v>
+      </c>
+      <c r="D110" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" t="n">
+        <v>2</v>
+      </c>
+      <c r="H110" t="n">
+        <v>10</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="n">
+        <v>20</v>
+      </c>
+      <c r="L110" t="n">
+        <v>1</v>
+      </c>
+      <c r="M110" t="n">
+        <v>20</v>
+      </c>
+      <c r="N110" t="n">
+        <v>10</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P110" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>10</v>
+      </c>
+      <c r="R110" t="n">
+        <v>2</v>
+      </c>
+      <c r="S110" t="n">
+        <v>24</v>
+      </c>
+      <c r="T110" t="n">
+        <v>24</v>
+      </c>
+      <c r="U110" t="n">
+        <v>6</v>
+      </c>
+      <c r="V110" t="n">
+        <v>6</v>
+      </c>
+      <c r="W110" t="n">
+        <v>2</v>
+      </c>
+      <c r="X110" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA110" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB110" t="n">
+        <v>70.76923618861733</v>
+      </c>
+      <c r="AC110" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-30-50</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>1</v>
+      </c>
+      <c r="D111" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" t="n">
+        <v>2</v>
+      </c>
+      <c r="H111" t="n">
+        <v>10</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="n">
+        <v>20</v>
+      </c>
+      <c r="L111" t="n">
+        <v>1</v>
+      </c>
+      <c r="M111" t="n">
+        <v>20</v>
+      </c>
+      <c r="N111" t="n">
+        <v>10</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P111" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>10</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6</v>
+      </c>
+      <c r="S111" t="n">
+        <v>30</v>
+      </c>
+      <c r="T111" t="n">
+        <v>10</v>
+      </c>
+      <c r="U111" t="n">
+        <v>6</v>
+      </c>
+      <c r="V111" t="n">
+        <v>6</v>
+      </c>
+      <c r="W111" t="n">
+        <v>11</v>
+      </c>
+      <c r="X111" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB111" t="n">
+        <v>79.58882563455383</v>
+      </c>
+      <c r="AC111" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-30-50</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>2</v>
+      </c>
+      <c r="D112" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" t="n">
+        <v>2</v>
+      </c>
+      <c r="H112" t="n">
+        <v>10</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="n">
+        <v>20</v>
+      </c>
+      <c r="L112" t="n">
+        <v>1</v>
+      </c>
+      <c r="M112" t="n">
+        <v>20</v>
+      </c>
+      <c r="N112" t="n">
+        <v>10</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P112" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>10</v>
+      </c>
+      <c r="R112" t="n">
+        <v>10</v>
+      </c>
+      <c r="S112" t="n">
+        <v>20</v>
+      </c>
+      <c r="T112" t="n">
+        <v>17</v>
+      </c>
+      <c r="U112" t="n">
+        <v>10</v>
+      </c>
+      <c r="V112" t="n">
+        <v>10</v>
+      </c>
+      <c r="W112" t="n">
+        <v>16</v>
+      </c>
+      <c r="X112" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>90.63036269288629</v>
+      </c>
+      <c r="AC112" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-30-50</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>3</v>
+      </c>
+      <c r="D113" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" t="n">
+        <v>2</v>
+      </c>
+      <c r="H113" t="n">
+        <v>10</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="n">
+        <v>20</v>
+      </c>
+      <c r="L113" t="n">
+        <v>1</v>
+      </c>
+      <c r="M113" t="n">
+        <v>20</v>
+      </c>
+      <c r="N113" t="n">
+        <v>10</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P113" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>10</v>
+      </c>
+      <c r="R113" t="n">
+        <v>4</v>
+      </c>
+      <c r="S113" t="n">
+        <v>26</v>
+      </c>
+      <c r="T113" t="n">
+        <v>14</v>
+      </c>
+      <c r="U113" t="n">
+        <v>13</v>
+      </c>
+      <c r="V113" t="n">
+        <v>13</v>
+      </c>
+      <c r="W113" t="n">
+        <v>14</v>
+      </c>
+      <c r="X113" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB113" t="n">
+        <v>81.6938423034044</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-30-50</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>4</v>
+      </c>
+      <c r="D114" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" t="n">
+        <v>2</v>
+      </c>
+      <c r="H114" t="n">
+        <v>10</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" t="n">
+        <v>20</v>
+      </c>
+      <c r="L114" t="n">
+        <v>1</v>
+      </c>
+      <c r="M114" t="n">
+        <v>20</v>
+      </c>
+      <c r="N114" t="n">
+        <v>10</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P114" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>10</v>
+      </c>
+      <c r="R114" t="n">
+        <v>7</v>
+      </c>
+      <c r="S114" t="n">
+        <v>15</v>
+      </c>
+      <c r="T114" t="n">
+        <v>15</v>
+      </c>
+      <c r="U114" t="n">
+        <v>22</v>
+      </c>
+      <c r="V114" t="n">
+        <v>0</v>
+      </c>
+      <c r="W114" t="n">
+        <v>9</v>
+      </c>
+      <c r="X114" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA114" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB114" t="n">
+        <v>80.57308327777891</v>
+      </c>
+      <c r="AC114" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-30-50</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>5</v>
+      </c>
+      <c r="D115" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" t="n">
+        <v>2</v>
+      </c>
+      <c r="H115" t="n">
+        <v>10</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="n">
+        <v>20</v>
+      </c>
+      <c r="L115" t="n">
+        <v>1</v>
+      </c>
+      <c r="M115" t="n">
+        <v>20</v>
+      </c>
+      <c r="N115" t="n">
+        <v>10</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P115" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>10</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="n">
+        <v>12</v>
+      </c>
+      <c r="T115" t="n">
+        <v>12</v>
+      </c>
+      <c r="U115" t="n">
+        <v>0</v>
+      </c>
+      <c r="V115" t="n">
+        <v>23</v>
+      </c>
+      <c r="W115" t="n">
+        <v>7</v>
+      </c>
+      <c r="X115" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA115" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB115" t="n">
+        <v>89.80479047587292</v>
+      </c>
+      <c r="AC115" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-30-50</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>6</v>
+      </c>
+      <c r="D116" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" t="n">
+        <v>2</v>
+      </c>
+      <c r="H116" t="n">
+        <v>10</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="n">
+        <v>20</v>
+      </c>
+      <c r="L116" t="n">
+        <v>1</v>
+      </c>
+      <c r="M116" t="n">
+        <v>20</v>
+      </c>
+      <c r="N116" t="n">
+        <v>10</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P116" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>10</v>
+      </c>
+      <c r="R116" t="n">
+        <v>2</v>
+      </c>
+      <c r="S116" t="n">
+        <v>25</v>
+      </c>
+      <c r="T116" t="n">
+        <v>22</v>
+      </c>
+      <c r="U116" t="n">
+        <v>11</v>
+      </c>
+      <c r="V116" t="n">
+        <v>11</v>
+      </c>
+      <c r="W116" t="n">
+        <v>3</v>
+      </c>
+      <c r="X116" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB116" t="n">
+        <v>80.23246595137162</v>
+      </c>
+      <c r="AC116" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-30-50</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>7</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" t="n">
+        <v>2</v>
+      </c>
+      <c r="H117" t="n">
+        <v>10</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="n">
+        <v>20</v>
+      </c>
+      <c r="L117" t="n">
+        <v>1</v>
+      </c>
+      <c r="M117" t="n">
+        <v>20</v>
+      </c>
+      <c r="N117" t="n">
+        <v>10</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P117" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>10</v>
+      </c>
+      <c r="R117" t="n">
+        <v>27</v>
+      </c>
+      <c r="S117" t="n">
+        <v>21</v>
+      </c>
+      <c r="T117" t="n">
+        <v>5</v>
+      </c>
+      <c r="U117" t="n">
+        <v>21</v>
+      </c>
+      <c r="V117" t="n">
+        <v>14</v>
+      </c>
+      <c r="W117" t="n">
+        <v>24</v>
+      </c>
+      <c r="X117" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>82.01234191803778</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-30-50</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>8</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" t="n">
+        <v>2</v>
+      </c>
+      <c r="H118" t="n">
+        <v>10</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="n">
+        <v>20</v>
+      </c>
+      <c r="L118" t="n">
+        <v>1</v>
+      </c>
+      <c r="M118" t="n">
+        <v>20</v>
+      </c>
+      <c r="N118" t="n">
+        <v>10</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P118" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>10</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="n">
+        <v>31</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0</v>
+      </c>
+      <c r="V118" t="n">
+        <v>6</v>
+      </c>
+      <c r="W118" t="n">
+        <v>5</v>
+      </c>
+      <c r="X118" t="n">
+        <v>31</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>31</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>62.3788851875768</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-30-50</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>9</v>
+      </c>
+      <c r="D119" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" t="n">
+        <v>2</v>
+      </c>
+      <c r="H119" t="n">
+        <v>10</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
+        <v>20</v>
+      </c>
+      <c r="L119" t="n">
+        <v>1</v>
+      </c>
+      <c r="M119" t="n">
+        <v>20</v>
+      </c>
+      <c r="N119" t="n">
+        <v>10</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P119" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>10</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6</v>
+      </c>
+      <c r="S119" t="n">
+        <v>7</v>
+      </c>
+      <c r="T119" t="n">
+        <v>16</v>
+      </c>
+      <c r="U119" t="n">
+        <v>4</v>
+      </c>
+      <c r="V119" t="n">
+        <v>21</v>
+      </c>
+      <c r="W119" t="n">
+        <v>3</v>
+      </c>
+      <c r="X119" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>91.0656006181139</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC119"/>
+  <dimension ref="A1:AC164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -11188,6 +11188,4191 @@
         <v>11</v>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-54-29</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>1</v>
+      </c>
+      <c r="D120" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" t="n">
+        <v>2</v>
+      </c>
+      <c r="H120" t="n">
+        <v>10</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>20</v>
+      </c>
+      <c r="L120" t="n">
+        <v>1</v>
+      </c>
+      <c r="M120" t="n">
+        <v>20</v>
+      </c>
+      <c r="N120" t="n">
+        <v>10</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P120" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>10</v>
+      </c>
+      <c r="R120" t="n">
+        <v>29</v>
+      </c>
+      <c r="S120" t="n">
+        <v>29</v>
+      </c>
+      <c r="T120" t="n">
+        <v>20</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0</v>
+      </c>
+      <c r="W120" t="n">
+        <v>31</v>
+      </c>
+      <c r="X120" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>81.47216319261737</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-54-29</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>2</v>
+      </c>
+      <c r="D121" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" t="n">
+        <v>2</v>
+      </c>
+      <c r="H121" t="n">
+        <v>10</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="n">
+        <v>20</v>
+      </c>
+      <c r="L121" t="n">
+        <v>1</v>
+      </c>
+      <c r="M121" t="n">
+        <v>20</v>
+      </c>
+      <c r="N121" t="n">
+        <v>10</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P121" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>10</v>
+      </c>
+      <c r="R121" t="n">
+        <v>2</v>
+      </c>
+      <c r="S121" t="n">
+        <v>29</v>
+      </c>
+      <c r="T121" t="n">
+        <v>13</v>
+      </c>
+      <c r="U121" t="n">
+        <v>29</v>
+      </c>
+      <c r="V121" t="n">
+        <v>29</v>
+      </c>
+      <c r="W121" t="n">
+        <v>4</v>
+      </c>
+      <c r="X121" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>81.55536181276165</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-54-29</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>3</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" t="n">
+        <v>2</v>
+      </c>
+      <c r="H122" t="n">
+        <v>10</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="n">
+        <v>20</v>
+      </c>
+      <c r="L122" t="n">
+        <v>1</v>
+      </c>
+      <c r="M122" t="n">
+        <v>20</v>
+      </c>
+      <c r="N122" t="n">
+        <v>10</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P122" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>10</v>
+      </c>
+      <c r="R122" t="n">
+        <v>15</v>
+      </c>
+      <c r="S122" t="n">
+        <v>15</v>
+      </c>
+      <c r="T122" t="n">
+        <v>2</v>
+      </c>
+      <c r="U122" t="n">
+        <v>16</v>
+      </c>
+      <c r="V122" t="n">
+        <v>27</v>
+      </c>
+      <c r="W122" t="n">
+        <v>20</v>
+      </c>
+      <c r="X122" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>80.10897673681087</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-54-29</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>4</v>
+      </c>
+      <c r="D123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" t="n">
+        <v>2</v>
+      </c>
+      <c r="H123" t="n">
+        <v>10</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
+        <v>20</v>
+      </c>
+      <c r="L123" t="n">
+        <v>1</v>
+      </c>
+      <c r="M123" t="n">
+        <v>20</v>
+      </c>
+      <c r="N123" t="n">
+        <v>10</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P123" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>10</v>
+      </c>
+      <c r="R123" t="n">
+        <v>13</v>
+      </c>
+      <c r="S123" t="n">
+        <v>28</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U123" t="n">
+        <v>11</v>
+      </c>
+      <c r="V123" t="n">
+        <v>13</v>
+      </c>
+      <c r="W123" t="n">
+        <v>19</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>65.35592171292812</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-54-29</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>5</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" t="n">
+        <v>2</v>
+      </c>
+      <c r="H124" t="n">
+        <v>10</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="n">
+        <v>20</v>
+      </c>
+      <c r="L124" t="n">
+        <v>1</v>
+      </c>
+      <c r="M124" t="n">
+        <v>20</v>
+      </c>
+      <c r="N124" t="n">
+        <v>10</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P124" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>10</v>
+      </c>
+      <c r="R124" t="n">
+        <v>3</v>
+      </c>
+      <c r="S124" t="n">
+        <v>11</v>
+      </c>
+      <c r="T124" t="n">
+        <v>27</v>
+      </c>
+      <c r="U124" t="n">
+        <v>3</v>
+      </c>
+      <c r="V124" t="n">
+        <v>28</v>
+      </c>
+      <c r="W124" t="n">
+        <v>3</v>
+      </c>
+      <c r="X124" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>74.94005679061841</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-54-29</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>6</v>
+      </c>
+      <c r="D125" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" t="n">
+        <v>2</v>
+      </c>
+      <c r="H125" t="n">
+        <v>10</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
+        <v>20</v>
+      </c>
+      <c r="L125" t="n">
+        <v>1</v>
+      </c>
+      <c r="M125" t="n">
+        <v>20</v>
+      </c>
+      <c r="N125" t="n">
+        <v>10</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P125" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>10</v>
+      </c>
+      <c r="R125" t="n">
+        <v>27</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0</v>
+      </c>
+      <c r="T125" t="n">
+        <v>13</v>
+      </c>
+      <c r="U125" t="n">
+        <v>20</v>
+      </c>
+      <c r="V125" t="n">
+        <v>20</v>
+      </c>
+      <c r="W125" t="n">
+        <v>26</v>
+      </c>
+      <c r="X125" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>72.64593956338219</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-54-29</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>7</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" t="n">
+        <v>2</v>
+      </c>
+      <c r="H126" t="n">
+        <v>10</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
+        <v>20</v>
+      </c>
+      <c r="L126" t="n">
+        <v>1</v>
+      </c>
+      <c r="M126" t="n">
+        <v>20</v>
+      </c>
+      <c r="N126" t="n">
+        <v>10</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P126" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>10</v>
+      </c>
+      <c r="R126" t="n">
+        <v>30</v>
+      </c>
+      <c r="S126" t="n">
+        <v>25</v>
+      </c>
+      <c r="T126" t="n">
+        <v>30</v>
+      </c>
+      <c r="U126" t="n">
+        <v>26</v>
+      </c>
+      <c r="V126" t="n">
+        <v>6</v>
+      </c>
+      <c r="W126" t="n">
+        <v>26</v>
+      </c>
+      <c r="X126" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>70.49185363842115</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-54-29</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>8</v>
+      </c>
+      <c r="D127" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" t="n">
+        <v>2</v>
+      </c>
+      <c r="H127" t="n">
+        <v>10</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
+        <v>20</v>
+      </c>
+      <c r="L127" t="n">
+        <v>1</v>
+      </c>
+      <c r="M127" t="n">
+        <v>20</v>
+      </c>
+      <c r="N127" t="n">
+        <v>10</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P127" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>10</v>
+      </c>
+      <c r="R127" t="n">
+        <v>3</v>
+      </c>
+      <c r="S127" t="n">
+        <v>17</v>
+      </c>
+      <c r="T127" t="n">
+        <v>17</v>
+      </c>
+      <c r="U127" t="n">
+        <v>3</v>
+      </c>
+      <c r="V127" t="n">
+        <v>2</v>
+      </c>
+      <c r="W127" t="n">
+        <v>18</v>
+      </c>
+      <c r="X127" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>70.5534269836413</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_13-54-29</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>9</v>
+      </c>
+      <c r="D128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" t="n">
+        <v>2</v>
+      </c>
+      <c r="H128" t="n">
+        <v>10</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="n">
+        <v>20</v>
+      </c>
+      <c r="L128" t="n">
+        <v>1</v>
+      </c>
+      <c r="M128" t="n">
+        <v>20</v>
+      </c>
+      <c r="N128" t="n">
+        <v>10</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P128" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>10</v>
+      </c>
+      <c r="R128" t="n">
+        <v>11</v>
+      </c>
+      <c r="S128" t="n">
+        <v>25</v>
+      </c>
+      <c r="T128" t="n">
+        <v>25</v>
+      </c>
+      <c r="U128" t="n">
+        <v>11</v>
+      </c>
+      <c r="V128" t="n">
+        <v>14</v>
+      </c>
+      <c r="W128" t="n">
+        <v>23</v>
+      </c>
+      <c r="X128" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>79.92269374411791</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_14-44-12</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>1</v>
+      </c>
+      <c r="D129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" t="n">
+        <v>2</v>
+      </c>
+      <c r="H129" t="n">
+        <v>10</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="n">
+        <v>20</v>
+      </c>
+      <c r="L129" t="n">
+        <v>1</v>
+      </c>
+      <c r="M129" t="n">
+        <v>20</v>
+      </c>
+      <c r="N129" t="n">
+        <v>10</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P129" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>10</v>
+      </c>
+      <c r="R129" t="n">
+        <v>1</v>
+      </c>
+      <c r="S129" t="n">
+        <v>16</v>
+      </c>
+      <c r="T129" t="n">
+        <v>1</v>
+      </c>
+      <c r="U129" t="n">
+        <v>1</v>
+      </c>
+      <c r="V129" t="n">
+        <v>1</v>
+      </c>
+      <c r="W129" t="n">
+        <v>1</v>
+      </c>
+      <c r="X129" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>62.84529003892763</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_14-44-12</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>2</v>
+      </c>
+      <c r="D130" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" t="n">
+        <v>2</v>
+      </c>
+      <c r="H130" t="n">
+        <v>10</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="n">
+        <v>20</v>
+      </c>
+      <c r="L130" t="n">
+        <v>1</v>
+      </c>
+      <c r="M130" t="n">
+        <v>20</v>
+      </c>
+      <c r="N130" t="n">
+        <v>10</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P130" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>10</v>
+      </c>
+      <c r="R130" t="n">
+        <v>11</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="n">
+        <v>6</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0</v>
+      </c>
+      <c r="V130" t="n">
+        <v>11</v>
+      </c>
+      <c r="W130" t="n">
+        <v>25</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>72.34863445397022</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_14-44-12</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>3</v>
+      </c>
+      <c r="D131" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" t="n">
+        <v>2</v>
+      </c>
+      <c r="H131" t="n">
+        <v>10</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="n">
+        <v>20</v>
+      </c>
+      <c r="L131" t="n">
+        <v>1</v>
+      </c>
+      <c r="M131" t="n">
+        <v>20</v>
+      </c>
+      <c r="N131" t="n">
+        <v>10</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P131" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>10</v>
+      </c>
+      <c r="R131" t="n">
+        <v>11</v>
+      </c>
+      <c r="S131" t="n">
+        <v>1</v>
+      </c>
+      <c r="T131" t="n">
+        <v>31</v>
+      </c>
+      <c r="U131" t="n">
+        <v>10</v>
+      </c>
+      <c r="V131" t="n">
+        <v>11</v>
+      </c>
+      <c r="W131" t="n">
+        <v>16</v>
+      </c>
+      <c r="X131" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>80.13127376050605</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_14-44-12</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>4</v>
+      </c>
+      <c r="D132" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" t="n">
+        <v>2</v>
+      </c>
+      <c r="H132" t="n">
+        <v>10</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="n">
+        <v>20</v>
+      </c>
+      <c r="L132" t="n">
+        <v>1</v>
+      </c>
+      <c r="M132" t="n">
+        <v>20</v>
+      </c>
+      <c r="N132" t="n">
+        <v>10</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P132" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>10</v>
+      </c>
+      <c r="R132" t="n">
+        <v>31</v>
+      </c>
+      <c r="S132" t="n">
+        <v>9</v>
+      </c>
+      <c r="T132" t="n">
+        <v>3</v>
+      </c>
+      <c r="U132" t="n">
+        <v>26</v>
+      </c>
+      <c r="V132" t="n">
+        <v>31</v>
+      </c>
+      <c r="W132" t="n">
+        <v>28</v>
+      </c>
+      <c r="X132" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>92.392785348302</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_14-44-12</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>5</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" t="n">
+        <v>2</v>
+      </c>
+      <c r="H133" t="n">
+        <v>10</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="n">
+        <v>20</v>
+      </c>
+      <c r="L133" t="n">
+        <v>1</v>
+      </c>
+      <c r="M133" t="n">
+        <v>20</v>
+      </c>
+      <c r="N133" t="n">
+        <v>10</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P133" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>10</v>
+      </c>
+      <c r="R133" t="n">
+        <v>3</v>
+      </c>
+      <c r="S133" t="n">
+        <v>16</v>
+      </c>
+      <c r="T133" t="n">
+        <v>3</v>
+      </c>
+      <c r="U133" t="n">
+        <v>19</v>
+      </c>
+      <c r="V133" t="n">
+        <v>3</v>
+      </c>
+      <c r="W133" t="n">
+        <v>19</v>
+      </c>
+      <c r="X133" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>73.06558769841936</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_14-44-12</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>6</v>
+      </c>
+      <c r="D134" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" t="n">
+        <v>2</v>
+      </c>
+      <c r="H134" t="n">
+        <v>10</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="n">
+        <v>20</v>
+      </c>
+      <c r="L134" t="n">
+        <v>1</v>
+      </c>
+      <c r="M134" t="n">
+        <v>20</v>
+      </c>
+      <c r="N134" t="n">
+        <v>10</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P134" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>10</v>
+      </c>
+      <c r="R134" t="n">
+        <v>14</v>
+      </c>
+      <c r="S134" t="n">
+        <v>15</v>
+      </c>
+      <c r="T134" t="n">
+        <v>8</v>
+      </c>
+      <c r="U134" t="n">
+        <v>31</v>
+      </c>
+      <c r="V134" t="n">
+        <v>31</v>
+      </c>
+      <c r="W134" t="n">
+        <v>31</v>
+      </c>
+      <c r="X134" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>31</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>31</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>71.39688765768912</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_14-44-12</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>7</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" t="n">
+        <v>2</v>
+      </c>
+      <c r="H135" t="n">
+        <v>10</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="n">
+        <v>20</v>
+      </c>
+      <c r="L135" t="n">
+        <v>1</v>
+      </c>
+      <c r="M135" t="n">
+        <v>20</v>
+      </c>
+      <c r="N135" t="n">
+        <v>10</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P135" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>10</v>
+      </c>
+      <c r="R135" t="n">
+        <v>8</v>
+      </c>
+      <c r="S135" t="n">
+        <v>3</v>
+      </c>
+      <c r="T135" t="n">
+        <v>15</v>
+      </c>
+      <c r="U135" t="n">
+        <v>8</v>
+      </c>
+      <c r="V135" t="n">
+        <v>2</v>
+      </c>
+      <c r="W135" t="n">
+        <v>22</v>
+      </c>
+      <c r="X135" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>81.44583189661856</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_14-44-12</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>8</v>
+      </c>
+      <c r="D136" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" t="n">
+        <v>2</v>
+      </c>
+      <c r="H136" t="n">
+        <v>10</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="n">
+        <v>20</v>
+      </c>
+      <c r="L136" t="n">
+        <v>1</v>
+      </c>
+      <c r="M136" t="n">
+        <v>20</v>
+      </c>
+      <c r="N136" t="n">
+        <v>10</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P136" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>10</v>
+      </c>
+      <c r="R136" t="n">
+        <v>25</v>
+      </c>
+      <c r="S136" t="n">
+        <v>26</v>
+      </c>
+      <c r="T136" t="n">
+        <v>29</v>
+      </c>
+      <c r="U136" t="n">
+        <v>25</v>
+      </c>
+      <c r="V136" t="n">
+        <v>25</v>
+      </c>
+      <c r="W136" t="n">
+        <v>20</v>
+      </c>
+      <c r="X136" t="n">
+        <v>31</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>80.18576770428342</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_14-44-12</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>9</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" t="n">
+        <v>2</v>
+      </c>
+      <c r="H137" t="n">
+        <v>10</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="n">
+        <v>20</v>
+      </c>
+      <c r="L137" t="n">
+        <v>1</v>
+      </c>
+      <c r="M137" t="n">
+        <v>20</v>
+      </c>
+      <c r="N137" t="n">
+        <v>10</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P137" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>10</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" t="n">
+        <v>14</v>
+      </c>
+      <c r="T137" t="n">
+        <v>3</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0</v>
+      </c>
+      <c r="V137" t="n">
+        <v>19</v>
+      </c>
+      <c r="W137" t="n">
+        <v>6</v>
+      </c>
+      <c r="X137" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>31</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>31</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>90.61505075197732</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_15-03-54</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>1</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" t="n">
+        <v>2</v>
+      </c>
+      <c r="H138" t="n">
+        <v>10</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
+        <v>20</v>
+      </c>
+      <c r="L138" t="n">
+        <v>1</v>
+      </c>
+      <c r="M138" t="n">
+        <v>20</v>
+      </c>
+      <c r="N138" t="n">
+        <v>10</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P138" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>10</v>
+      </c>
+      <c r="R138" t="n">
+        <v>30</v>
+      </c>
+      <c r="S138" t="n">
+        <v>6</v>
+      </c>
+      <c r="T138" t="n">
+        <v>2</v>
+      </c>
+      <c r="U138" t="n">
+        <v>4</v>
+      </c>
+      <c r="V138" t="n">
+        <v>17</v>
+      </c>
+      <c r="W138" t="n">
+        <v>23</v>
+      </c>
+      <c r="X138" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>89.31863232503748</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_15-03-54</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>2</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" t="n">
+        <v>2</v>
+      </c>
+      <c r="H139" t="n">
+        <v>10</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="n">
+        <v>20</v>
+      </c>
+      <c r="L139" t="n">
+        <v>1</v>
+      </c>
+      <c r="M139" t="n">
+        <v>20</v>
+      </c>
+      <c r="N139" t="n">
+        <v>10</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P139" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>10</v>
+      </c>
+      <c r="R139" t="n">
+        <v>22</v>
+      </c>
+      <c r="S139" t="n">
+        <v>23</v>
+      </c>
+      <c r="T139" t="n">
+        <v>5</v>
+      </c>
+      <c r="U139" t="n">
+        <v>22</v>
+      </c>
+      <c r="V139" t="n">
+        <v>29</v>
+      </c>
+      <c r="W139" t="n">
+        <v>18</v>
+      </c>
+      <c r="X139" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>85.15060400596124</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_15-03-54</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>3</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" t="n">
+        <v>2</v>
+      </c>
+      <c r="H140" t="n">
+        <v>10</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
+        <v>20</v>
+      </c>
+      <c r="L140" t="n">
+        <v>1</v>
+      </c>
+      <c r="M140" t="n">
+        <v>20</v>
+      </c>
+      <c r="N140" t="n">
+        <v>10</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P140" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>10</v>
+      </c>
+      <c r="R140" t="n">
+        <v>5</v>
+      </c>
+      <c r="S140" t="n">
+        <v>27</v>
+      </c>
+      <c r="T140" t="n">
+        <v>6</v>
+      </c>
+      <c r="U140" t="n">
+        <v>6</v>
+      </c>
+      <c r="V140" t="n">
+        <v>6</v>
+      </c>
+      <c r="W140" t="n">
+        <v>15</v>
+      </c>
+      <c r="X140" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>76.96367567049279</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_15-03-54</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>4</v>
+      </c>
+      <c r="D141" t="n">
+        <v>1</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" t="n">
+        <v>2</v>
+      </c>
+      <c r="H141" t="n">
+        <v>10</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="n">
+        <v>20</v>
+      </c>
+      <c r="L141" t="n">
+        <v>1</v>
+      </c>
+      <c r="M141" t="n">
+        <v>20</v>
+      </c>
+      <c r="N141" t="n">
+        <v>10</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P141" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>10</v>
+      </c>
+      <c r="R141" t="n">
+        <v>15</v>
+      </c>
+      <c r="S141" t="n">
+        <v>7</v>
+      </c>
+      <c r="T141" t="n">
+        <v>30</v>
+      </c>
+      <c r="U141" t="n">
+        <v>4</v>
+      </c>
+      <c r="V141" t="n">
+        <v>21</v>
+      </c>
+      <c r="W141" t="n">
+        <v>23</v>
+      </c>
+      <c r="X141" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>81.51582784301205</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_15-03-54</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>5</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" t="n">
+        <v>2</v>
+      </c>
+      <c r="H142" t="n">
+        <v>10</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
+        <v>20</v>
+      </c>
+      <c r="L142" t="n">
+        <v>1</v>
+      </c>
+      <c r="M142" t="n">
+        <v>20</v>
+      </c>
+      <c r="N142" t="n">
+        <v>10</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P142" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>10</v>
+      </c>
+      <c r="R142" t="n">
+        <v>12</v>
+      </c>
+      <c r="S142" t="n">
+        <v>13</v>
+      </c>
+      <c r="T142" t="n">
+        <v>7</v>
+      </c>
+      <c r="U142" t="n">
+        <v>20</v>
+      </c>
+      <c r="V142" t="n">
+        <v>7</v>
+      </c>
+      <c r="W142" t="n">
+        <v>22</v>
+      </c>
+      <c r="X142" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>31</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>74.30036657653909</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_15-03-54</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>6</v>
+      </c>
+      <c r="D143" t="n">
+        <v>1</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" t="n">
+        <v>2</v>
+      </c>
+      <c r="H143" t="n">
+        <v>10</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
+        <v>20</v>
+      </c>
+      <c r="L143" t="n">
+        <v>1</v>
+      </c>
+      <c r="M143" t="n">
+        <v>20</v>
+      </c>
+      <c r="N143" t="n">
+        <v>10</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P143" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>10</v>
+      </c>
+      <c r="R143" t="n">
+        <v>11</v>
+      </c>
+      <c r="S143" t="n">
+        <v>2</v>
+      </c>
+      <c r="T143" t="n">
+        <v>25</v>
+      </c>
+      <c r="U143" t="n">
+        <v>30</v>
+      </c>
+      <c r="V143" t="n">
+        <v>17</v>
+      </c>
+      <c r="W143" t="n">
+        <v>11</v>
+      </c>
+      <c r="X143" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>101.2003392277212</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_15-03-54</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>7</v>
+      </c>
+      <c r="D144" t="n">
+        <v>1</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" t="n">
+        <v>2</v>
+      </c>
+      <c r="H144" t="n">
+        <v>10</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
+        <v>20</v>
+      </c>
+      <c r="L144" t="n">
+        <v>1</v>
+      </c>
+      <c r="M144" t="n">
+        <v>20</v>
+      </c>
+      <c r="N144" t="n">
+        <v>10</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P144" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>10</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0</v>
+      </c>
+      <c r="S144" t="n">
+        <v>6</v>
+      </c>
+      <c r="T144" t="n">
+        <v>0</v>
+      </c>
+      <c r="U144" t="n">
+        <v>0</v>
+      </c>
+      <c r="V144" t="n">
+        <v>21</v>
+      </c>
+      <c r="W144" t="n">
+        <v>23</v>
+      </c>
+      <c r="X144" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB144" t="n">
+        <v>70.80993599454636</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_15-03-54</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>8</v>
+      </c>
+      <c r="D145" t="n">
+        <v>1</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" t="n">
+        <v>2</v>
+      </c>
+      <c r="H145" t="n">
+        <v>10</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="n">
+        <v>20</v>
+      </c>
+      <c r="L145" t="n">
+        <v>1</v>
+      </c>
+      <c r="M145" t="n">
+        <v>20</v>
+      </c>
+      <c r="N145" t="n">
+        <v>10</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P145" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>10</v>
+      </c>
+      <c r="R145" t="n">
+        <v>29</v>
+      </c>
+      <c r="S145" t="n">
+        <v>11</v>
+      </c>
+      <c r="T145" t="n">
+        <v>25</v>
+      </c>
+      <c r="U145" t="n">
+        <v>31</v>
+      </c>
+      <c r="V145" t="n">
+        <v>31</v>
+      </c>
+      <c r="W145" t="n">
+        <v>20</v>
+      </c>
+      <c r="X145" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA145" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB145" t="n">
+        <v>90.43446652667252</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_15-03-54</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>9</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0</v>
+      </c>
+      <c r="G146" t="n">
+        <v>2</v>
+      </c>
+      <c r="H146" t="n">
+        <v>10</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="n">
+        <v>20</v>
+      </c>
+      <c r="L146" t="n">
+        <v>1</v>
+      </c>
+      <c r="M146" t="n">
+        <v>20</v>
+      </c>
+      <c r="N146" t="n">
+        <v>10</v>
+      </c>
+      <c r="O146" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P146" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>10</v>
+      </c>
+      <c r="R146" t="n">
+        <v>11</v>
+      </c>
+      <c r="S146" t="n">
+        <v>5</v>
+      </c>
+      <c r="T146" t="n">
+        <v>30</v>
+      </c>
+      <c r="U146" t="n">
+        <v>22</v>
+      </c>
+      <c r="V146" t="n">
+        <v>11</v>
+      </c>
+      <c r="W146" t="n">
+        <v>30</v>
+      </c>
+      <c r="X146" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB146" t="n">
+        <v>90.87278521924063</v>
+      </c>
+      <c r="AC146" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_15-22-28</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>1</v>
+      </c>
+      <c r="D147" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0</v>
+      </c>
+      <c r="G147" t="n">
+        <v>2</v>
+      </c>
+      <c r="H147" t="n">
+        <v>10</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="n">
+        <v>20</v>
+      </c>
+      <c r="L147" t="n">
+        <v>1</v>
+      </c>
+      <c r="M147" t="n">
+        <v>20</v>
+      </c>
+      <c r="N147" t="n">
+        <v>10</v>
+      </c>
+      <c r="O147" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P147" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>10</v>
+      </c>
+      <c r="R147" t="n">
+        <v>15</v>
+      </c>
+      <c r="S147" t="n">
+        <v>5</v>
+      </c>
+      <c r="T147" t="n">
+        <v>5</v>
+      </c>
+      <c r="U147" t="n">
+        <v>4</v>
+      </c>
+      <c r="V147" t="n">
+        <v>15</v>
+      </c>
+      <c r="W147" t="n">
+        <v>25</v>
+      </c>
+      <c r="X147" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>92.04388657092042</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_15-22-28</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>2</v>
+      </c>
+      <c r="D148" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" t="n">
+        <v>2</v>
+      </c>
+      <c r="H148" t="n">
+        <v>10</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="n">
+        <v>20</v>
+      </c>
+      <c r="L148" t="n">
+        <v>1</v>
+      </c>
+      <c r="M148" t="n">
+        <v>20</v>
+      </c>
+      <c r="N148" t="n">
+        <v>10</v>
+      </c>
+      <c r="O148" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P148" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>10</v>
+      </c>
+      <c r="R148" t="n">
+        <v>28</v>
+      </c>
+      <c r="S148" t="n">
+        <v>28</v>
+      </c>
+      <c r="T148" t="n">
+        <v>28</v>
+      </c>
+      <c r="U148" t="n">
+        <v>25</v>
+      </c>
+      <c r="V148" t="n">
+        <v>4</v>
+      </c>
+      <c r="W148" t="n">
+        <v>29</v>
+      </c>
+      <c r="X148" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB148" t="n">
+        <v>89.87952977081328</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_15-22-28</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>3</v>
+      </c>
+      <c r="D149" t="n">
+        <v>1</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0</v>
+      </c>
+      <c r="G149" t="n">
+        <v>2</v>
+      </c>
+      <c r="H149" t="n">
+        <v>10</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" t="n">
+        <v>20</v>
+      </c>
+      <c r="L149" t="n">
+        <v>1</v>
+      </c>
+      <c r="M149" t="n">
+        <v>20</v>
+      </c>
+      <c r="N149" t="n">
+        <v>10</v>
+      </c>
+      <c r="O149" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P149" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>10</v>
+      </c>
+      <c r="R149" t="n">
+        <v>22</v>
+      </c>
+      <c r="S149" t="n">
+        <v>31</v>
+      </c>
+      <c r="T149" t="n">
+        <v>2</v>
+      </c>
+      <c r="U149" t="n">
+        <v>18</v>
+      </c>
+      <c r="V149" t="n">
+        <v>8</v>
+      </c>
+      <c r="W149" t="n">
+        <v>8</v>
+      </c>
+      <c r="X149" t="n">
+        <v>31</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>80.68961751417656</v>
+      </c>
+      <c r="AC149" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_15-22-28</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>4</v>
+      </c>
+      <c r="D150" t="n">
+        <v>1</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0</v>
+      </c>
+      <c r="G150" t="n">
+        <v>2</v>
+      </c>
+      <c r="H150" t="n">
+        <v>10</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" t="n">
+        <v>20</v>
+      </c>
+      <c r="L150" t="n">
+        <v>1</v>
+      </c>
+      <c r="M150" t="n">
+        <v>20</v>
+      </c>
+      <c r="N150" t="n">
+        <v>10</v>
+      </c>
+      <c r="O150" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P150" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>10</v>
+      </c>
+      <c r="R150" t="n">
+        <v>20</v>
+      </c>
+      <c r="S150" t="n">
+        <v>14</v>
+      </c>
+      <c r="T150" t="n">
+        <v>1</v>
+      </c>
+      <c r="U150" t="n">
+        <v>20</v>
+      </c>
+      <c r="V150" t="n">
+        <v>7</v>
+      </c>
+      <c r="W150" t="n">
+        <v>9</v>
+      </c>
+      <c r="X150" t="n">
+        <v>31</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>81.11048398111619</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_15-22-28</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>5</v>
+      </c>
+      <c r="D151" t="n">
+        <v>1</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0</v>
+      </c>
+      <c r="G151" t="n">
+        <v>2</v>
+      </c>
+      <c r="H151" t="n">
+        <v>10</v>
+      </c>
+      <c r="I151" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" t="n">
+        <v>20</v>
+      </c>
+      <c r="L151" t="n">
+        <v>1</v>
+      </c>
+      <c r="M151" t="n">
+        <v>20</v>
+      </c>
+      <c r="N151" t="n">
+        <v>10</v>
+      </c>
+      <c r="O151" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P151" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>10</v>
+      </c>
+      <c r="R151" t="n">
+        <v>3</v>
+      </c>
+      <c r="S151" t="n">
+        <v>27</v>
+      </c>
+      <c r="T151" t="n">
+        <v>16</v>
+      </c>
+      <c r="U151" t="n">
+        <v>3</v>
+      </c>
+      <c r="V151" t="n">
+        <v>3</v>
+      </c>
+      <c r="W151" t="n">
+        <v>22</v>
+      </c>
+      <c r="X151" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA151" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB151" t="n">
+        <v>71.34994177819186</v>
+      </c>
+      <c r="AC151" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_15-22-28</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>6</v>
+      </c>
+      <c r="D152" t="n">
+        <v>1</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0</v>
+      </c>
+      <c r="G152" t="n">
+        <v>2</v>
+      </c>
+      <c r="H152" t="n">
+        <v>10</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K152" t="n">
+        <v>20</v>
+      </c>
+      <c r="L152" t="n">
+        <v>1</v>
+      </c>
+      <c r="M152" t="n">
+        <v>20</v>
+      </c>
+      <c r="N152" t="n">
+        <v>10</v>
+      </c>
+      <c r="O152" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P152" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>10</v>
+      </c>
+      <c r="R152" t="n">
+        <v>13</v>
+      </c>
+      <c r="S152" t="n">
+        <v>18</v>
+      </c>
+      <c r="T152" t="n">
+        <v>25</v>
+      </c>
+      <c r="U152" t="n">
+        <v>12</v>
+      </c>
+      <c r="V152" t="n">
+        <v>12</v>
+      </c>
+      <c r="W152" t="n">
+        <v>19</v>
+      </c>
+      <c r="X152" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z152" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA152" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB152" t="n">
+        <v>80.40397373810325</v>
+      </c>
+      <c r="AC152" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_15-22-28</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>7</v>
+      </c>
+      <c r="D153" t="n">
+        <v>1</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0</v>
+      </c>
+      <c r="G153" t="n">
+        <v>2</v>
+      </c>
+      <c r="H153" t="n">
+        <v>10</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" t="n">
+        <v>20</v>
+      </c>
+      <c r="L153" t="n">
+        <v>1</v>
+      </c>
+      <c r="M153" t="n">
+        <v>20</v>
+      </c>
+      <c r="N153" t="n">
+        <v>10</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P153" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>10</v>
+      </c>
+      <c r="R153" t="n">
+        <v>7</v>
+      </c>
+      <c r="S153" t="n">
+        <v>7</v>
+      </c>
+      <c r="T153" t="n">
+        <v>13</v>
+      </c>
+      <c r="U153" t="n">
+        <v>12</v>
+      </c>
+      <c r="V153" t="n">
+        <v>27</v>
+      </c>
+      <c r="W153" t="n">
+        <v>14</v>
+      </c>
+      <c r="X153" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z153" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA153" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB153" t="n">
+        <v>70.30942543578827</v>
+      </c>
+      <c r="AC153" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_15-22-28</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>8</v>
+      </c>
+      <c r="D154" t="n">
+        <v>1</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0</v>
+      </c>
+      <c r="G154" t="n">
+        <v>2</v>
+      </c>
+      <c r="H154" t="n">
+        <v>10</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K154" t="n">
+        <v>20</v>
+      </c>
+      <c r="L154" t="n">
+        <v>1</v>
+      </c>
+      <c r="M154" t="n">
+        <v>20</v>
+      </c>
+      <c r="N154" t="n">
+        <v>10</v>
+      </c>
+      <c r="O154" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P154" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>10</v>
+      </c>
+      <c r="R154" t="n">
+        <v>11</v>
+      </c>
+      <c r="S154" t="n">
+        <v>11</v>
+      </c>
+      <c r="T154" t="n">
+        <v>24</v>
+      </c>
+      <c r="U154" t="n">
+        <v>24</v>
+      </c>
+      <c r="V154" t="n">
+        <v>11</v>
+      </c>
+      <c r="W154" t="n">
+        <v>25</v>
+      </c>
+      <c r="X154" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA154" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB154" t="n">
+        <v>71.10660191434498</v>
+      </c>
+      <c r="AC154" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_15-22-28</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>9</v>
+      </c>
+      <c r="D155" t="n">
+        <v>1</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0</v>
+      </c>
+      <c r="G155" t="n">
+        <v>2</v>
+      </c>
+      <c r="H155" t="n">
+        <v>10</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155" t="n">
+        <v>20</v>
+      </c>
+      <c r="L155" t="n">
+        <v>1</v>
+      </c>
+      <c r="M155" t="n">
+        <v>20</v>
+      </c>
+      <c r="N155" t="n">
+        <v>10</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P155" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>10</v>
+      </c>
+      <c r="R155" t="n">
+        <v>21</v>
+      </c>
+      <c r="S155" t="n">
+        <v>28</v>
+      </c>
+      <c r="T155" t="n">
+        <v>10</v>
+      </c>
+      <c r="U155" t="n">
+        <v>10</v>
+      </c>
+      <c r="V155" t="n">
+        <v>2</v>
+      </c>
+      <c r="W155" t="n">
+        <v>22</v>
+      </c>
+      <c r="X155" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA155" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB155" t="n">
+        <v>79.90178127964363</v>
+      </c>
+      <c r="AC155" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_15-42-33</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>1</v>
+      </c>
+      <c r="D156" t="n">
+        <v>1</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" t="n">
+        <v>2</v>
+      </c>
+      <c r="H156" t="n">
+        <v>10</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" t="n">
+        <v>20</v>
+      </c>
+      <c r="L156" t="n">
+        <v>1</v>
+      </c>
+      <c r="M156" t="n">
+        <v>20</v>
+      </c>
+      <c r="N156" t="n">
+        <v>10</v>
+      </c>
+      <c r="O156" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P156" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>10</v>
+      </c>
+      <c r="R156" t="n">
+        <v>27</v>
+      </c>
+      <c r="S156" t="n">
+        <v>10</v>
+      </c>
+      <c r="T156" t="n">
+        <v>5</v>
+      </c>
+      <c r="U156" t="n">
+        <v>29</v>
+      </c>
+      <c r="V156" t="n">
+        <v>29</v>
+      </c>
+      <c r="W156" t="n">
+        <v>16</v>
+      </c>
+      <c r="X156" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z156" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA156" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB156" t="n">
+        <v>80.30494722259486</v>
+      </c>
+      <c r="AC156" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_15-42-33</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>2</v>
+      </c>
+      <c r="D157" t="n">
+        <v>1</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" t="n">
+        <v>2</v>
+      </c>
+      <c r="H157" t="n">
+        <v>10</v>
+      </c>
+      <c r="I157" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" t="n">
+        <v>20</v>
+      </c>
+      <c r="L157" t="n">
+        <v>1</v>
+      </c>
+      <c r="M157" t="n">
+        <v>20</v>
+      </c>
+      <c r="N157" t="n">
+        <v>10</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P157" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>10</v>
+      </c>
+      <c r="R157" t="n">
+        <v>6</v>
+      </c>
+      <c r="S157" t="n">
+        <v>0</v>
+      </c>
+      <c r="T157" t="n">
+        <v>3</v>
+      </c>
+      <c r="U157" t="n">
+        <v>0</v>
+      </c>
+      <c r="V157" t="n">
+        <v>0</v>
+      </c>
+      <c r="W157" t="n">
+        <v>8</v>
+      </c>
+      <c r="X157" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA157" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB157" t="n">
+        <v>80.70044621807986</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_15-42-33</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>3</v>
+      </c>
+      <c r="D158" t="n">
+        <v>1</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0</v>
+      </c>
+      <c r="G158" t="n">
+        <v>2</v>
+      </c>
+      <c r="H158" t="n">
+        <v>10</v>
+      </c>
+      <c r="I158" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" t="n">
+        <v>20</v>
+      </c>
+      <c r="L158" t="n">
+        <v>1</v>
+      </c>
+      <c r="M158" t="n">
+        <v>20</v>
+      </c>
+      <c r="N158" t="n">
+        <v>10</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P158" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>10</v>
+      </c>
+      <c r="R158" t="n">
+        <v>6</v>
+      </c>
+      <c r="S158" t="n">
+        <v>9</v>
+      </c>
+      <c r="T158" t="n">
+        <v>9</v>
+      </c>
+      <c r="U158" t="n">
+        <v>6</v>
+      </c>
+      <c r="V158" t="n">
+        <v>6</v>
+      </c>
+      <c r="W158" t="n">
+        <v>0</v>
+      </c>
+      <c r="X158" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z158" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA158" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB158" t="n">
+        <v>81.62597023710038</v>
+      </c>
+      <c r="AC158" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_15-42-33</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>4</v>
+      </c>
+      <c r="D159" t="n">
+        <v>1</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" t="n">
+        <v>2</v>
+      </c>
+      <c r="H159" t="n">
+        <v>10</v>
+      </c>
+      <c r="I159" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" t="n">
+        <v>20</v>
+      </c>
+      <c r="L159" t="n">
+        <v>1</v>
+      </c>
+      <c r="M159" t="n">
+        <v>20</v>
+      </c>
+      <c r="N159" t="n">
+        <v>10</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P159" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>10</v>
+      </c>
+      <c r="R159" t="n">
+        <v>10</v>
+      </c>
+      <c r="S159" t="n">
+        <v>23</v>
+      </c>
+      <c r="T159" t="n">
+        <v>31</v>
+      </c>
+      <c r="U159" t="n">
+        <v>10</v>
+      </c>
+      <c r="V159" t="n">
+        <v>10</v>
+      </c>
+      <c r="W159" t="n">
+        <v>12</v>
+      </c>
+      <c r="X159" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z159" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA159" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB159" t="n">
+        <v>81.69389017988638</v>
+      </c>
+      <c r="AC159" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_15-42-33</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>5</v>
+      </c>
+      <c r="D160" t="n">
+        <v>1</v>
+      </c>
+      <c r="E160" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0</v>
+      </c>
+      <c r="G160" t="n">
+        <v>2</v>
+      </c>
+      <c r="H160" t="n">
+        <v>10</v>
+      </c>
+      <c r="I160" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" t="n">
+        <v>20</v>
+      </c>
+      <c r="L160" t="n">
+        <v>1</v>
+      </c>
+      <c r="M160" t="n">
+        <v>20</v>
+      </c>
+      <c r="N160" t="n">
+        <v>10</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P160" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>10</v>
+      </c>
+      <c r="R160" t="n">
+        <v>13</v>
+      </c>
+      <c r="S160" t="n">
+        <v>3</v>
+      </c>
+      <c r="T160" t="n">
+        <v>14</v>
+      </c>
+      <c r="U160" t="n">
+        <v>28</v>
+      </c>
+      <c r="V160" t="n">
+        <v>28</v>
+      </c>
+      <c r="W160" t="n">
+        <v>3</v>
+      </c>
+      <c r="X160" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z160" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA160" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB160" t="n">
+        <v>82.57435723404583</v>
+      </c>
+      <c r="AC160" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_15-42-33</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>6</v>
+      </c>
+      <c r="D161" t="n">
+        <v>1</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0</v>
+      </c>
+      <c r="G161" t="n">
+        <v>2</v>
+      </c>
+      <c r="H161" t="n">
+        <v>10</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="n">
+        <v>20</v>
+      </c>
+      <c r="L161" t="n">
+        <v>1</v>
+      </c>
+      <c r="M161" t="n">
+        <v>20</v>
+      </c>
+      <c r="N161" t="n">
+        <v>10</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P161" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>10</v>
+      </c>
+      <c r="R161" t="n">
+        <v>1</v>
+      </c>
+      <c r="S161" t="n">
+        <v>9</v>
+      </c>
+      <c r="T161" t="n">
+        <v>22</v>
+      </c>
+      <c r="U161" t="n">
+        <v>9</v>
+      </c>
+      <c r="V161" t="n">
+        <v>9</v>
+      </c>
+      <c r="W161" t="n">
+        <v>9</v>
+      </c>
+      <c r="X161" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>73.89686564372616</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_15-42-33</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>7</v>
+      </c>
+      <c r="D162" t="n">
+        <v>1</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F162" t="n">
+        <v>0</v>
+      </c>
+      <c r="G162" t="n">
+        <v>2</v>
+      </c>
+      <c r="H162" t="n">
+        <v>10</v>
+      </c>
+      <c r="I162" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" t="n">
+        <v>20</v>
+      </c>
+      <c r="L162" t="n">
+        <v>1</v>
+      </c>
+      <c r="M162" t="n">
+        <v>20</v>
+      </c>
+      <c r="N162" t="n">
+        <v>10</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P162" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>10</v>
+      </c>
+      <c r="R162" t="n">
+        <v>24</v>
+      </c>
+      <c r="S162" t="n">
+        <v>29</v>
+      </c>
+      <c r="T162" t="n">
+        <v>11</v>
+      </c>
+      <c r="U162" t="n">
+        <v>23</v>
+      </c>
+      <c r="V162" t="n">
+        <v>9</v>
+      </c>
+      <c r="W162" t="n">
+        <v>30</v>
+      </c>
+      <c r="X162" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA162" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB162" t="n">
+        <v>100.7472646202053</v>
+      </c>
+      <c r="AC162" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_15-42-33</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>8</v>
+      </c>
+      <c r="D163" t="n">
+        <v>1</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F163" t="n">
+        <v>0</v>
+      </c>
+      <c r="G163" t="n">
+        <v>2</v>
+      </c>
+      <c r="H163" t="n">
+        <v>10</v>
+      </c>
+      <c r="I163" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" t="n">
+        <v>20</v>
+      </c>
+      <c r="L163" t="n">
+        <v>1</v>
+      </c>
+      <c r="M163" t="n">
+        <v>20</v>
+      </c>
+      <c r="N163" t="n">
+        <v>10</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P163" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>10</v>
+      </c>
+      <c r="R163" t="n">
+        <v>14</v>
+      </c>
+      <c r="S163" t="n">
+        <v>1</v>
+      </c>
+      <c r="T163" t="n">
+        <v>3</v>
+      </c>
+      <c r="U163" t="n">
+        <v>8</v>
+      </c>
+      <c r="V163" t="n">
+        <v>8</v>
+      </c>
+      <c r="W163" t="n">
+        <v>20</v>
+      </c>
+      <c r="X163" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA163" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB163" t="n">
+        <v>72.32486835524847</v>
+      </c>
+      <c r="AC163" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_15-42-33</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>9</v>
+      </c>
+      <c r="D164" t="n">
+        <v>1</v>
+      </c>
+      <c r="E164" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F164" t="n">
+        <v>0</v>
+      </c>
+      <c r="G164" t="n">
+        <v>2</v>
+      </c>
+      <c r="H164" t="n">
+        <v>10</v>
+      </c>
+      <c r="I164" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" t="n">
+        <v>20</v>
+      </c>
+      <c r="L164" t="n">
+        <v>1</v>
+      </c>
+      <c r="M164" t="n">
+        <v>20</v>
+      </c>
+      <c r="N164" t="n">
+        <v>10</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P164" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>10</v>
+      </c>
+      <c r="R164" t="n">
+        <v>22</v>
+      </c>
+      <c r="S164" t="n">
+        <v>22</v>
+      </c>
+      <c r="T164" t="n">
+        <v>2</v>
+      </c>
+      <c r="U164" t="n">
+        <v>2</v>
+      </c>
+      <c r="V164" t="n">
+        <v>14</v>
+      </c>
+      <c r="W164" t="n">
+        <v>3</v>
+      </c>
+      <c r="X164" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z164" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA164" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB164" t="n">
+        <v>80.67645214337233</v>
+      </c>
+      <c r="AC164" t="n">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC164"/>
+  <dimension ref="A1:AC178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -15373,6 +15373,1336 @@
         <v>17</v>
       </c>
     </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_17-08-22</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>1</v>
+      </c>
+      <c r="D165" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F165" t="n">
+        <v>0</v>
+      </c>
+      <c r="G165" t="n">
+        <v>2</v>
+      </c>
+      <c r="H165" t="n">
+        <v>10</v>
+      </c>
+      <c r="I165" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" t="n">
+        <v>20</v>
+      </c>
+      <c r="L165" t="n">
+        <v>1</v>
+      </c>
+      <c r="M165" t="n">
+        <v>20</v>
+      </c>
+      <c r="N165" t="n">
+        <v>10</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P165" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>10</v>
+      </c>
+      <c r="R165" t="n">
+        <v>18</v>
+      </c>
+      <c r="S165" t="n">
+        <v>12</v>
+      </c>
+      <c r="T165" t="n">
+        <v>17</v>
+      </c>
+      <c r="U165" t="n">
+        <v>12</v>
+      </c>
+      <c r="V165" t="n">
+        <v>15</v>
+      </c>
+      <c r="W165" t="n">
+        <v>1</v>
+      </c>
+      <c r="X165" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y165" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z165" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA165" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_17-08-22</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>2</v>
+      </c>
+      <c r="D166" t="n">
+        <v>1</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F166" t="n">
+        <v>0</v>
+      </c>
+      <c r="G166" t="n">
+        <v>2</v>
+      </c>
+      <c r="H166" t="n">
+        <v>10</v>
+      </c>
+      <c r="I166" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="n">
+        <v>20</v>
+      </c>
+      <c r="L166" t="n">
+        <v>1</v>
+      </c>
+      <c r="M166" t="n">
+        <v>20</v>
+      </c>
+      <c r="N166" t="n">
+        <v>10</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P166" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>10</v>
+      </c>
+      <c r="R166" t="n">
+        <v>26</v>
+      </c>
+      <c r="S166" t="n">
+        <v>21</v>
+      </c>
+      <c r="T166" t="n">
+        <v>1</v>
+      </c>
+      <c r="U166" t="n">
+        <v>8</v>
+      </c>
+      <c r="V166" t="n">
+        <v>23</v>
+      </c>
+      <c r="W166" t="n">
+        <v>13</v>
+      </c>
+      <c r="X166" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z166" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA166" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_17-08-22</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>3</v>
+      </c>
+      <c r="D167" t="n">
+        <v>1</v>
+      </c>
+      <c r="E167" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F167" t="n">
+        <v>0</v>
+      </c>
+      <c r="G167" t="n">
+        <v>2</v>
+      </c>
+      <c r="H167" t="n">
+        <v>10</v>
+      </c>
+      <c r="I167" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="n">
+        <v>20</v>
+      </c>
+      <c r="L167" t="n">
+        <v>1</v>
+      </c>
+      <c r="M167" t="n">
+        <v>20</v>
+      </c>
+      <c r="N167" t="n">
+        <v>10</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P167" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>10</v>
+      </c>
+      <c r="R167" t="n">
+        <v>7</v>
+      </c>
+      <c r="S167" t="n">
+        <v>16</v>
+      </c>
+      <c r="T167" t="n">
+        <v>28</v>
+      </c>
+      <c r="U167" t="n">
+        <v>27</v>
+      </c>
+      <c r="V167" t="n">
+        <v>14</v>
+      </c>
+      <c r="W167" t="n">
+        <v>16</v>
+      </c>
+      <c r="X167" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z167" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA167" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_17-08-22</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>4</v>
+      </c>
+      <c r="D168" t="n">
+        <v>1</v>
+      </c>
+      <c r="E168" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F168" t="n">
+        <v>0</v>
+      </c>
+      <c r="G168" t="n">
+        <v>2</v>
+      </c>
+      <c r="H168" t="n">
+        <v>10</v>
+      </c>
+      <c r="I168" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="n">
+        <v>20</v>
+      </c>
+      <c r="L168" t="n">
+        <v>1</v>
+      </c>
+      <c r="M168" t="n">
+        <v>20</v>
+      </c>
+      <c r="N168" t="n">
+        <v>10</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P168" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>10</v>
+      </c>
+      <c r="R168" t="n">
+        <v>23</v>
+      </c>
+      <c r="S168" t="n">
+        <v>18</v>
+      </c>
+      <c r="T168" t="n">
+        <v>7</v>
+      </c>
+      <c r="U168" t="n">
+        <v>0</v>
+      </c>
+      <c r="V168" t="n">
+        <v>13</v>
+      </c>
+      <c r="W168" t="n">
+        <v>18</v>
+      </c>
+      <c r="X168" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z168" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA168" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_17-08-22</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>5</v>
+      </c>
+      <c r="D169" t="n">
+        <v>1</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F169" t="n">
+        <v>0</v>
+      </c>
+      <c r="G169" t="n">
+        <v>2</v>
+      </c>
+      <c r="H169" t="n">
+        <v>10</v>
+      </c>
+      <c r="I169" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" t="n">
+        <v>20</v>
+      </c>
+      <c r="L169" t="n">
+        <v>1</v>
+      </c>
+      <c r="M169" t="n">
+        <v>20</v>
+      </c>
+      <c r="N169" t="n">
+        <v>10</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P169" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>10</v>
+      </c>
+      <c r="R169" t="n">
+        <v>8</v>
+      </c>
+      <c r="S169" t="n">
+        <v>5</v>
+      </c>
+      <c r="T169" t="n">
+        <v>18</v>
+      </c>
+      <c r="U169" t="n">
+        <v>6</v>
+      </c>
+      <c r="V169" t="n">
+        <v>25</v>
+      </c>
+      <c r="W169" t="n">
+        <v>19</v>
+      </c>
+      <c r="X169" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z169" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA169" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_17-08-22</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>6</v>
+      </c>
+      <c r="D170" t="n">
+        <v>1</v>
+      </c>
+      <c r="E170" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F170" t="n">
+        <v>0</v>
+      </c>
+      <c r="G170" t="n">
+        <v>2</v>
+      </c>
+      <c r="H170" t="n">
+        <v>10</v>
+      </c>
+      <c r="I170" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" t="n">
+        <v>20</v>
+      </c>
+      <c r="L170" t="n">
+        <v>1</v>
+      </c>
+      <c r="M170" t="n">
+        <v>20</v>
+      </c>
+      <c r="N170" t="n">
+        <v>10</v>
+      </c>
+      <c r="O170" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P170" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>10</v>
+      </c>
+      <c r="R170" t="n">
+        <v>30</v>
+      </c>
+      <c r="S170" t="n">
+        <v>21</v>
+      </c>
+      <c r="T170" t="n">
+        <v>6</v>
+      </c>
+      <c r="U170" t="n">
+        <v>4</v>
+      </c>
+      <c r="V170" t="n">
+        <v>24</v>
+      </c>
+      <c r="W170" t="n">
+        <v>15</v>
+      </c>
+      <c r="X170" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y170" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z170" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA170" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_17-08-22</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>7</v>
+      </c>
+      <c r="D171" t="n">
+        <v>1</v>
+      </c>
+      <c r="E171" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0</v>
+      </c>
+      <c r="G171" t="n">
+        <v>2</v>
+      </c>
+      <c r="H171" t="n">
+        <v>10</v>
+      </c>
+      <c r="I171" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" t="n">
+        <v>20</v>
+      </c>
+      <c r="L171" t="n">
+        <v>1</v>
+      </c>
+      <c r="M171" t="n">
+        <v>20</v>
+      </c>
+      <c r="N171" t="n">
+        <v>10</v>
+      </c>
+      <c r="O171" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P171" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>10</v>
+      </c>
+      <c r="R171" t="n">
+        <v>6</v>
+      </c>
+      <c r="S171" t="n">
+        <v>1</v>
+      </c>
+      <c r="T171" t="n">
+        <v>12</v>
+      </c>
+      <c r="U171" t="n">
+        <v>29</v>
+      </c>
+      <c r="V171" t="n">
+        <v>16</v>
+      </c>
+      <c r="W171" t="n">
+        <v>31</v>
+      </c>
+      <c r="X171" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y171" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z171" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA171" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_17-08-22</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>1</v>
+      </c>
+      <c r="D172" t="n">
+        <v>2</v>
+      </c>
+      <c r="E172" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0</v>
+      </c>
+      <c r="G172" t="n">
+        <v>2</v>
+      </c>
+      <c r="H172" t="n">
+        <v>10</v>
+      </c>
+      <c r="I172" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" t="n">
+        <v>20</v>
+      </c>
+      <c r="L172" t="n">
+        <v>1</v>
+      </c>
+      <c r="M172" t="n">
+        <v>20</v>
+      </c>
+      <c r="N172" t="n">
+        <v>10</v>
+      </c>
+      <c r="O172" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P172" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>10</v>
+      </c>
+      <c r="R172" t="n">
+        <v>29</v>
+      </c>
+      <c r="S172" t="n">
+        <v>4</v>
+      </c>
+      <c r="T172" t="n">
+        <v>27</v>
+      </c>
+      <c r="U172" t="n">
+        <v>28</v>
+      </c>
+      <c r="V172" t="n">
+        <v>26</v>
+      </c>
+      <c r="W172" t="n">
+        <v>23</v>
+      </c>
+      <c r="X172" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y172" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z172" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA172" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_17-08-22</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>2</v>
+      </c>
+      <c r="D173" t="n">
+        <v>2</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0</v>
+      </c>
+      <c r="G173" t="n">
+        <v>2</v>
+      </c>
+      <c r="H173" t="n">
+        <v>10</v>
+      </c>
+      <c r="I173" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K173" t="n">
+        <v>20</v>
+      </c>
+      <c r="L173" t="n">
+        <v>1</v>
+      </c>
+      <c r="M173" t="n">
+        <v>20</v>
+      </c>
+      <c r="N173" t="n">
+        <v>10</v>
+      </c>
+      <c r="O173" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P173" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>10</v>
+      </c>
+      <c r="R173" t="n">
+        <v>27</v>
+      </c>
+      <c r="S173" t="n">
+        <v>12</v>
+      </c>
+      <c r="T173" t="n">
+        <v>18</v>
+      </c>
+      <c r="U173" t="n">
+        <v>22</v>
+      </c>
+      <c r="V173" t="n">
+        <v>19</v>
+      </c>
+      <c r="W173" t="n">
+        <v>9</v>
+      </c>
+      <c r="X173" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y173" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z173" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA173" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_17-08-22</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>3</v>
+      </c>
+      <c r="D174" t="n">
+        <v>2</v>
+      </c>
+      <c r="E174" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0</v>
+      </c>
+      <c r="G174" t="n">
+        <v>2</v>
+      </c>
+      <c r="H174" t="n">
+        <v>10</v>
+      </c>
+      <c r="I174" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J174" t="n">
+        <v>0</v>
+      </c>
+      <c r="K174" t="n">
+        <v>20</v>
+      </c>
+      <c r="L174" t="n">
+        <v>1</v>
+      </c>
+      <c r="M174" t="n">
+        <v>20</v>
+      </c>
+      <c r="N174" t="n">
+        <v>10</v>
+      </c>
+      <c r="O174" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P174" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>10</v>
+      </c>
+      <c r="R174" t="n">
+        <v>13</v>
+      </c>
+      <c r="S174" t="n">
+        <v>12</v>
+      </c>
+      <c r="T174" t="n">
+        <v>16</v>
+      </c>
+      <c r="U174" t="n">
+        <v>8</v>
+      </c>
+      <c r="V174" t="n">
+        <v>28</v>
+      </c>
+      <c r="W174" t="n">
+        <v>18</v>
+      </c>
+      <c r="X174" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y174" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z174" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA174" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB174" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_17-08-22</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>4</v>
+      </c>
+      <c r="D175" t="n">
+        <v>2</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" t="n">
+        <v>2</v>
+      </c>
+      <c r="H175" t="n">
+        <v>10</v>
+      </c>
+      <c r="I175" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J175" t="n">
+        <v>0</v>
+      </c>
+      <c r="K175" t="n">
+        <v>20</v>
+      </c>
+      <c r="L175" t="n">
+        <v>1</v>
+      </c>
+      <c r="M175" t="n">
+        <v>20</v>
+      </c>
+      <c r="N175" t="n">
+        <v>10</v>
+      </c>
+      <c r="O175" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P175" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>10</v>
+      </c>
+      <c r="R175" t="n">
+        <v>27</v>
+      </c>
+      <c r="S175" t="n">
+        <v>24</v>
+      </c>
+      <c r="T175" t="n">
+        <v>4</v>
+      </c>
+      <c r="U175" t="n">
+        <v>16</v>
+      </c>
+      <c r="V175" t="n">
+        <v>14</v>
+      </c>
+      <c r="W175" t="n">
+        <v>16</v>
+      </c>
+      <c r="X175" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y175" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z175" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA175" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_17-08-22</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>5</v>
+      </c>
+      <c r="D176" t="n">
+        <v>2</v>
+      </c>
+      <c r="E176" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F176" t="n">
+        <v>0</v>
+      </c>
+      <c r="G176" t="n">
+        <v>2</v>
+      </c>
+      <c r="H176" t="n">
+        <v>10</v>
+      </c>
+      <c r="I176" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J176" t="n">
+        <v>0</v>
+      </c>
+      <c r="K176" t="n">
+        <v>20</v>
+      </c>
+      <c r="L176" t="n">
+        <v>1</v>
+      </c>
+      <c r="M176" t="n">
+        <v>20</v>
+      </c>
+      <c r="N176" t="n">
+        <v>10</v>
+      </c>
+      <c r="O176" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P176" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>10</v>
+      </c>
+      <c r="R176" t="n">
+        <v>23</v>
+      </c>
+      <c r="S176" t="n">
+        <v>18</v>
+      </c>
+      <c r="T176" t="n">
+        <v>19</v>
+      </c>
+      <c r="U176" t="n">
+        <v>15</v>
+      </c>
+      <c r="V176" t="n">
+        <v>27</v>
+      </c>
+      <c r="W176" t="n">
+        <v>24</v>
+      </c>
+      <c r="X176" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y176" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z176" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA176" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_17-08-22</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>6</v>
+      </c>
+      <c r="D177" t="n">
+        <v>2</v>
+      </c>
+      <c r="E177" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F177" t="n">
+        <v>0</v>
+      </c>
+      <c r="G177" t="n">
+        <v>2</v>
+      </c>
+      <c r="H177" t="n">
+        <v>10</v>
+      </c>
+      <c r="I177" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
+      <c r="K177" t="n">
+        <v>20</v>
+      </c>
+      <c r="L177" t="n">
+        <v>1</v>
+      </c>
+      <c r="M177" t="n">
+        <v>20</v>
+      </c>
+      <c r="N177" t="n">
+        <v>10</v>
+      </c>
+      <c r="O177" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P177" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>10</v>
+      </c>
+      <c r="R177" t="n">
+        <v>16</v>
+      </c>
+      <c r="S177" t="n">
+        <v>1</v>
+      </c>
+      <c r="T177" t="n">
+        <v>28</v>
+      </c>
+      <c r="U177" t="n">
+        <v>8</v>
+      </c>
+      <c r="V177" t="n">
+        <v>4</v>
+      </c>
+      <c r="W177" t="n">
+        <v>22</v>
+      </c>
+      <c r="X177" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y177" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z177" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA177" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>run_2025-08-29_17-08-22</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>7</v>
+      </c>
+      <c r="D178" t="n">
+        <v>2</v>
+      </c>
+      <c r="E178" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F178" t="n">
+        <v>0</v>
+      </c>
+      <c r="G178" t="n">
+        <v>2</v>
+      </c>
+      <c r="H178" t="n">
+        <v>10</v>
+      </c>
+      <c r="I178" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J178" t="n">
+        <v>0</v>
+      </c>
+      <c r="K178" t="n">
+        <v>20</v>
+      </c>
+      <c r="L178" t="n">
+        <v>1</v>
+      </c>
+      <c r="M178" t="n">
+        <v>20</v>
+      </c>
+      <c r="N178" t="n">
+        <v>10</v>
+      </c>
+      <c r="O178" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P178" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>10</v>
+      </c>
+      <c r="R178" t="n">
+        <v>7</v>
+      </c>
+      <c r="S178" t="n">
+        <v>21</v>
+      </c>
+      <c r="T178" t="n">
+        <v>1</v>
+      </c>
+      <c r="U178" t="n">
+        <v>25</v>
+      </c>
+      <c r="V178" t="n">
+        <v>14</v>
+      </c>
+      <c r="W178" t="n">
+        <v>24</v>
+      </c>
+      <c r="X178" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y178" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z178" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA178" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC178" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC471"/>
+  <dimension ref="A1:AC483"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -42136,6 +42136,1050 @@
         <v>0</v>
       </c>
     </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>run_2025-08-30_09-01-27</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C472" t="n">
+        <v>1</v>
+      </c>
+      <c r="D472" t="n">
+        <v>1</v>
+      </c>
+      <c r="E472" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F472" t="inlineStr"/>
+      <c r="G472" t="n">
+        <v>2</v>
+      </c>
+      <c r="H472" t="n">
+        <v>10</v>
+      </c>
+      <c r="I472" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J472" t="inlineStr"/>
+      <c r="K472" t="n">
+        <v>20</v>
+      </c>
+      <c r="L472" t="n">
+        <v>1</v>
+      </c>
+      <c r="M472" t="inlineStr"/>
+      <c r="N472" t="n">
+        <v>10</v>
+      </c>
+      <c r="O472" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P472" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q472" t="inlineStr"/>
+      <c r="R472" t="n">
+        <v>30</v>
+      </c>
+      <c r="S472" t="n">
+        <v>24</v>
+      </c>
+      <c r="T472" t="n">
+        <v>5</v>
+      </c>
+      <c r="U472" t="n">
+        <v>2</v>
+      </c>
+      <c r="V472" t="n">
+        <v>28</v>
+      </c>
+      <c r="W472" t="n">
+        <v>20</v>
+      </c>
+      <c r="X472" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y472" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z472" t="n">
+        <v>31</v>
+      </c>
+      <c r="AA472" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB472" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC472" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>run_2025-08-30_09-01-27</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C473" t="n">
+        <v>2</v>
+      </c>
+      <c r="D473" t="n">
+        <v>1</v>
+      </c>
+      <c r="E473" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F473" t="inlineStr"/>
+      <c r="G473" t="n">
+        <v>2</v>
+      </c>
+      <c r="H473" t="n">
+        <v>10</v>
+      </c>
+      <c r="I473" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J473" t="inlineStr"/>
+      <c r="K473" t="n">
+        <v>20</v>
+      </c>
+      <c r="L473" t="n">
+        <v>1</v>
+      </c>
+      <c r="M473" t="inlineStr"/>
+      <c r="N473" t="n">
+        <v>10</v>
+      </c>
+      <c r="O473" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P473" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q473" t="inlineStr"/>
+      <c r="R473" t="n">
+        <v>1</v>
+      </c>
+      <c r="S473" t="n">
+        <v>29</v>
+      </c>
+      <c r="T473" t="n">
+        <v>7</v>
+      </c>
+      <c r="U473" t="n">
+        <v>24</v>
+      </c>
+      <c r="V473" t="n">
+        <v>18</v>
+      </c>
+      <c r="W473" t="n">
+        <v>22</v>
+      </c>
+      <c r="X473" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y473" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z473" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA473" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB473" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC473" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>run_2025-08-30_09-01-27</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C474" t="n">
+        <v>3</v>
+      </c>
+      <c r="D474" t="n">
+        <v>1</v>
+      </c>
+      <c r="E474" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F474" t="inlineStr"/>
+      <c r="G474" t="n">
+        <v>2</v>
+      </c>
+      <c r="H474" t="n">
+        <v>10</v>
+      </c>
+      <c r="I474" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J474" t="inlineStr"/>
+      <c r="K474" t="n">
+        <v>20</v>
+      </c>
+      <c r="L474" t="n">
+        <v>1</v>
+      </c>
+      <c r="M474" t="inlineStr"/>
+      <c r="N474" t="n">
+        <v>10</v>
+      </c>
+      <c r="O474" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P474" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q474" t="inlineStr"/>
+      <c r="R474" t="n">
+        <v>3</v>
+      </c>
+      <c r="S474" t="n">
+        <v>3</v>
+      </c>
+      <c r="T474" t="n">
+        <v>27</v>
+      </c>
+      <c r="U474" t="n">
+        <v>6</v>
+      </c>
+      <c r="V474" t="n">
+        <v>15</v>
+      </c>
+      <c r="W474" t="n">
+        <v>7</v>
+      </c>
+      <c r="X474" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y474" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z474" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA474" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB474" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC474" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>run_2025-08-30_09-01-27</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C475" t="n">
+        <v>1</v>
+      </c>
+      <c r="D475" t="n">
+        <v>2</v>
+      </c>
+      <c r="E475" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F475" t="inlineStr"/>
+      <c r="G475" t="n">
+        <v>2</v>
+      </c>
+      <c r="H475" t="n">
+        <v>10</v>
+      </c>
+      <c r="I475" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J475" t="inlineStr"/>
+      <c r="K475" t="n">
+        <v>20</v>
+      </c>
+      <c r="L475" t="n">
+        <v>1</v>
+      </c>
+      <c r="M475" t="inlineStr"/>
+      <c r="N475" t="n">
+        <v>10</v>
+      </c>
+      <c r="O475" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P475" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q475" t="inlineStr"/>
+      <c r="R475" t="n">
+        <v>20</v>
+      </c>
+      <c r="S475" t="n">
+        <v>30</v>
+      </c>
+      <c r="T475" t="n">
+        <v>16</v>
+      </c>
+      <c r="U475" t="n">
+        <v>26</v>
+      </c>
+      <c r="V475" t="n">
+        <v>28</v>
+      </c>
+      <c r="W475" t="n">
+        <v>8</v>
+      </c>
+      <c r="X475" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y475" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z475" t="n">
+        <v>31</v>
+      </c>
+      <c r="AA475" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB475" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC475" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>run_2025-08-30_09-01-27</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C476" t="n">
+        <v>2</v>
+      </c>
+      <c r="D476" t="n">
+        <v>2</v>
+      </c>
+      <c r="E476" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F476" t="inlineStr"/>
+      <c r="G476" t="n">
+        <v>2</v>
+      </c>
+      <c r="H476" t="n">
+        <v>10</v>
+      </c>
+      <c r="I476" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J476" t="inlineStr"/>
+      <c r="K476" t="n">
+        <v>20</v>
+      </c>
+      <c r="L476" t="n">
+        <v>1</v>
+      </c>
+      <c r="M476" t="inlineStr"/>
+      <c r="N476" t="n">
+        <v>10</v>
+      </c>
+      <c r="O476" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P476" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q476" t="inlineStr"/>
+      <c r="R476" t="n">
+        <v>22</v>
+      </c>
+      <c r="S476" t="n">
+        <v>10</v>
+      </c>
+      <c r="T476" t="n">
+        <v>20</v>
+      </c>
+      <c r="U476" t="n">
+        <v>3</v>
+      </c>
+      <c r="V476" t="n">
+        <v>3</v>
+      </c>
+      <c r="W476" t="n">
+        <v>5</v>
+      </c>
+      <c r="X476" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y476" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z476" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA476" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB476" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC476" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>run_2025-08-30_09-01-27</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>config_2</t>
+        </is>
+      </c>
+      <c r="C477" t="n">
+        <v>3</v>
+      </c>
+      <c r="D477" t="n">
+        <v>2</v>
+      </c>
+      <c r="E477" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F477" t="inlineStr"/>
+      <c r="G477" t="n">
+        <v>2</v>
+      </c>
+      <c r="H477" t="n">
+        <v>10</v>
+      </c>
+      <c r="I477" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J477" t="inlineStr"/>
+      <c r="K477" t="n">
+        <v>20</v>
+      </c>
+      <c r="L477" t="n">
+        <v>1</v>
+      </c>
+      <c r="M477" t="inlineStr"/>
+      <c r="N477" t="n">
+        <v>10</v>
+      </c>
+      <c r="O477" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P477" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q477" t="inlineStr"/>
+      <c r="R477" t="n">
+        <v>5</v>
+      </c>
+      <c r="S477" t="n">
+        <v>29</v>
+      </c>
+      <c r="T477" t="n">
+        <v>8</v>
+      </c>
+      <c r="U477" t="n">
+        <v>8</v>
+      </c>
+      <c r="V477" t="n">
+        <v>28</v>
+      </c>
+      <c r="W477" t="n">
+        <v>29</v>
+      </c>
+      <c r="X477" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y477" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z477" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA477" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB477" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC477" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>run_2025-08-30_09-01-27</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C478" t="n">
+        <v>1</v>
+      </c>
+      <c r="D478" t="n">
+        <v>3</v>
+      </c>
+      <c r="E478" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F478" t="inlineStr"/>
+      <c r="G478" t="n">
+        <v>2</v>
+      </c>
+      <c r="H478" t="n">
+        <v>10</v>
+      </c>
+      <c r="I478" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J478" t="inlineStr"/>
+      <c r="K478" t="n">
+        <v>20</v>
+      </c>
+      <c r="L478" t="n">
+        <v>1</v>
+      </c>
+      <c r="M478" t="inlineStr"/>
+      <c r="N478" t="n">
+        <v>10</v>
+      </c>
+      <c r="O478" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P478" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q478" t="inlineStr"/>
+      <c r="R478" t="n">
+        <v>27</v>
+      </c>
+      <c r="S478" t="n">
+        <v>2</v>
+      </c>
+      <c r="T478" t="n">
+        <v>29</v>
+      </c>
+      <c r="U478" t="n">
+        <v>20</v>
+      </c>
+      <c r="V478" t="n">
+        <v>10</v>
+      </c>
+      <c r="W478" t="n">
+        <v>14</v>
+      </c>
+      <c r="X478" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y478" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z478" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA478" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB478" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC478" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>run_2025-08-30_09-01-27</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C479" t="n">
+        <v>2</v>
+      </c>
+      <c r="D479" t="n">
+        <v>3</v>
+      </c>
+      <c r="E479" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F479" t="inlineStr"/>
+      <c r="G479" t="n">
+        <v>2</v>
+      </c>
+      <c r="H479" t="n">
+        <v>10</v>
+      </c>
+      <c r="I479" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J479" t="inlineStr"/>
+      <c r="K479" t="n">
+        <v>20</v>
+      </c>
+      <c r="L479" t="n">
+        <v>1</v>
+      </c>
+      <c r="M479" t="inlineStr"/>
+      <c r="N479" t="n">
+        <v>10</v>
+      </c>
+      <c r="O479" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P479" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q479" t="inlineStr"/>
+      <c r="R479" t="n">
+        <v>11</v>
+      </c>
+      <c r="S479" t="n">
+        <v>12</v>
+      </c>
+      <c r="T479" t="n">
+        <v>11</v>
+      </c>
+      <c r="U479" t="n">
+        <v>1</v>
+      </c>
+      <c r="V479" t="n">
+        <v>17</v>
+      </c>
+      <c r="W479" t="n">
+        <v>17</v>
+      </c>
+      <c r="X479" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y479" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z479" t="n">
+        <v>31</v>
+      </c>
+      <c r="AA479" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB479" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC479" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>run_2025-08-30_09-01-27</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>config_3</t>
+        </is>
+      </c>
+      <c r="C480" t="n">
+        <v>3</v>
+      </c>
+      <c r="D480" t="n">
+        <v>3</v>
+      </c>
+      <c r="E480" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F480" t="inlineStr"/>
+      <c r="G480" t="n">
+        <v>2</v>
+      </c>
+      <c r="H480" t="n">
+        <v>10</v>
+      </c>
+      <c r="I480" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J480" t="inlineStr"/>
+      <c r="K480" t="n">
+        <v>20</v>
+      </c>
+      <c r="L480" t="n">
+        <v>1</v>
+      </c>
+      <c r="M480" t="inlineStr"/>
+      <c r="N480" t="n">
+        <v>10</v>
+      </c>
+      <c r="O480" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P480" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q480" t="inlineStr"/>
+      <c r="R480" t="n">
+        <v>31</v>
+      </c>
+      <c r="S480" t="n">
+        <v>25</v>
+      </c>
+      <c r="T480" t="n">
+        <v>23</v>
+      </c>
+      <c r="U480" t="n">
+        <v>11</v>
+      </c>
+      <c r="V480" t="n">
+        <v>29</v>
+      </c>
+      <c r="W480" t="n">
+        <v>13</v>
+      </c>
+      <c r="X480" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y480" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z480" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA480" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB480" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC480" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>run_2025-08-30_09-01-27</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C481" t="n">
+        <v>1</v>
+      </c>
+      <c r="D481" t="n">
+        <v>4</v>
+      </c>
+      <c r="E481" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F481" t="inlineStr"/>
+      <c r="G481" t="n">
+        <v>2</v>
+      </c>
+      <c r="H481" t="n">
+        <v>10</v>
+      </c>
+      <c r="I481" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J481" t="inlineStr"/>
+      <c r="K481" t="n">
+        <v>20</v>
+      </c>
+      <c r="L481" t="n">
+        <v>1</v>
+      </c>
+      <c r="M481" t="inlineStr"/>
+      <c r="N481" t="n">
+        <v>10</v>
+      </c>
+      <c r="O481" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P481" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q481" t="inlineStr"/>
+      <c r="R481" t="n">
+        <v>12</v>
+      </c>
+      <c r="S481" t="n">
+        <v>16</v>
+      </c>
+      <c r="T481" t="n">
+        <v>25</v>
+      </c>
+      <c r="U481" t="n">
+        <v>8</v>
+      </c>
+      <c r="V481" t="n">
+        <v>30</v>
+      </c>
+      <c r="W481" t="n">
+        <v>19</v>
+      </c>
+      <c r="X481" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y481" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z481" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA481" t="n">
+        <v>31</v>
+      </c>
+      <c r="AB481" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC481" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>run_2025-08-30_09-01-27</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C482" t="n">
+        <v>2</v>
+      </c>
+      <c r="D482" t="n">
+        <v>4</v>
+      </c>
+      <c r="E482" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F482" t="inlineStr"/>
+      <c r="G482" t="n">
+        <v>2</v>
+      </c>
+      <c r="H482" t="n">
+        <v>10</v>
+      </c>
+      <c r="I482" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J482" t="inlineStr"/>
+      <c r="K482" t="n">
+        <v>20</v>
+      </c>
+      <c r="L482" t="n">
+        <v>1</v>
+      </c>
+      <c r="M482" t="inlineStr"/>
+      <c r="N482" t="n">
+        <v>10</v>
+      </c>
+      <c r="O482" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P482" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q482" t="inlineStr"/>
+      <c r="R482" t="n">
+        <v>8</v>
+      </c>
+      <c r="S482" t="n">
+        <v>19</v>
+      </c>
+      <c r="T482" t="n">
+        <v>17</v>
+      </c>
+      <c r="U482" t="n">
+        <v>0</v>
+      </c>
+      <c r="V482" t="n">
+        <v>2</v>
+      </c>
+      <c r="W482" t="n">
+        <v>8</v>
+      </c>
+      <c r="X482" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y482" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z482" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA482" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB482" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC482" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>run_2025-08-30_09-01-27</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>config_4</t>
+        </is>
+      </c>
+      <c r="C483" t="n">
+        <v>3</v>
+      </c>
+      <c r="D483" t="n">
+        <v>4</v>
+      </c>
+      <c r="E483" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F483" t="inlineStr"/>
+      <c r="G483" t="n">
+        <v>2</v>
+      </c>
+      <c r="H483" t="n">
+        <v>10</v>
+      </c>
+      <c r="I483" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J483" t="inlineStr"/>
+      <c r="K483" t="n">
+        <v>20</v>
+      </c>
+      <c r="L483" t="n">
+        <v>1</v>
+      </c>
+      <c r="M483" t="inlineStr"/>
+      <c r="N483" t="n">
+        <v>10</v>
+      </c>
+      <c r="O483" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P483" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q483" t="inlineStr"/>
+      <c r="R483" t="n">
+        <v>28</v>
+      </c>
+      <c r="S483" t="n">
+        <v>25</v>
+      </c>
+      <c r="T483" t="n">
+        <v>18</v>
+      </c>
+      <c r="U483" t="n">
+        <v>17</v>
+      </c>
+      <c r="V483" t="n">
+        <v>29</v>
+      </c>
+      <c r="W483" t="n">
+        <v>18</v>
+      </c>
+      <c r="X483" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y483" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z483" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA483" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB483" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="AC483" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y42"/>
+  <dimension ref="A1:Y59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -3565,83 +3565,1364 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>run_2025-09-03_11-08-09</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" t="n">
+        <v>10</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I42" t="n">
+        <v>20</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" t="n">
+        <v>10</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M42" t="n">
+        <v>50</v>
+      </c>
+      <c r="N42" t="n">
+        <v>22</v>
+      </c>
+      <c r="O42" t="n">
+        <v>22</v>
+      </c>
+      <c r="P42" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>26</v>
+      </c>
+      <c r="R42" t="n">
+        <v>9</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>9</v>
+      </c>
+      <c r="V42" t="n">
+        <v>27</v>
+      </c>
+      <c r="W42" t="n">
+        <v>28</v>
+      </c>
+      <c r="X42" t="n">
+        <v>70.15734629485078</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>run_2025-09-03_11-08-09</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" t="n">
+        <v>10</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I43" t="n">
+        <v>20</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" t="n">
+        <v>10</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M43" t="n">
+        <v>50</v>
+      </c>
+      <c r="N43" t="n">
+        <v>14</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>28</v>
+      </c>
+      <c r="R43" t="n">
+        <v>14</v>
+      </c>
+      <c r="S43" t="n">
+        <v>14</v>
+      </c>
+      <c r="T43" t="n">
+        <v>20</v>
+      </c>
+      <c r="U43" t="n">
+        <v>28</v>
+      </c>
+      <c r="V43" t="n">
+        <v>29</v>
+      </c>
+      <c r="W43" t="n">
+        <v>20</v>
+      </c>
+      <c r="X43" t="n">
+        <v>70.64819670052827</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>run_2025-09-03_11-08-09</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>6</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2</v>
+      </c>
+      <c r="G44" t="n">
+        <v>10</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I44" t="n">
+        <v>20</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>10</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M44" t="n">
+        <v>50</v>
+      </c>
+      <c r="N44" t="n">
+        <v>16</v>
+      </c>
+      <c r="O44" t="n">
+        <v>22</v>
+      </c>
+      <c r="P44" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1</v>
+      </c>
+      <c r="S44" t="n">
+        <v>18</v>
+      </c>
+      <c r="T44" t="n">
+        <v>7</v>
+      </c>
+      <c r="U44" t="n">
+        <v>16</v>
+      </c>
+      <c r="V44" t="n">
+        <v>28</v>
+      </c>
+      <c r="W44" t="n">
+        <v>16</v>
+      </c>
+      <c r="X44" t="n">
+        <v>70.1317495509584</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>run_2025-09-03_11-08-09</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>7</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2</v>
+      </c>
+      <c r="G45" t="n">
+        <v>10</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I45" t="n">
+        <v>20</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>10</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M45" t="n">
+        <v>50</v>
+      </c>
+      <c r="N45" t="n">
+        <v>20</v>
+      </c>
+      <c r="O45" t="n">
+        <v>8</v>
+      </c>
+      <c r="P45" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>28</v>
+      </c>
+      <c r="R45" t="n">
+        <v>16</v>
+      </c>
+      <c r="S45" t="n">
+        <v>22</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>20</v>
+      </c>
+      <c r="V45" t="n">
+        <v>4</v>
+      </c>
+      <c r="W45" t="n">
+        <v>22</v>
+      </c>
+      <c r="X45" t="n">
+        <v>77.00629571209467</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>run_2025-09-03_11-08-09</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>8</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G46" t="n">
+        <v>10</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I46" t="n">
+        <v>20</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>10</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M46" t="n">
+        <v>50</v>
+      </c>
+      <c r="N46" t="n">
+        <v>26</v>
+      </c>
+      <c r="O46" t="n">
+        <v>2</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>26</v>
+      </c>
+      <c r="R46" t="n">
+        <v>20</v>
+      </c>
+      <c r="S46" t="n">
+        <v>7</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>26</v>
+      </c>
+      <c r="V46" t="n">
+        <v>2</v>
+      </c>
+      <c r="W46" t="n">
+        <v>22</v>
+      </c>
+      <c r="X46" t="n">
+        <v>51.57911230025218</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>run_2025-09-03_11-08-09</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>9</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G47" t="n">
+        <v>10</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I47" t="n">
+        <v>20</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>10</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M47" t="n">
+        <v>50</v>
+      </c>
+      <c r="N47" t="n">
+        <v>28</v>
+      </c>
+      <c r="O47" t="n">
+        <v>2</v>
+      </c>
+      <c r="P47" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>28</v>
+      </c>
+      <c r="R47" t="n">
+        <v>18</v>
+      </c>
+      <c r="S47" t="n">
+        <v>12</v>
+      </c>
+      <c r="T47" t="n">
+        <v>25</v>
+      </c>
+      <c r="U47" t="n">
+        <v>28</v>
+      </c>
+      <c r="V47" t="n">
+        <v>2</v>
+      </c>
+      <c r="W47" t="n">
+        <v>12</v>
+      </c>
+      <c r="X47" t="n">
+        <v>61.11561142227013</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>run_2025-09-03_11-08-09</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>10</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F48" t="n">
+        <v>2</v>
+      </c>
+      <c r="G48" t="n">
+        <v>10</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I48" t="n">
+        <v>20</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="n">
+        <v>10</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M48" t="n">
+        <v>50</v>
+      </c>
+      <c r="N48" t="n">
+        <v>11</v>
+      </c>
+      <c r="O48" t="n">
+        <v>6</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>11</v>
+      </c>
+      <c r="R48" t="n">
+        <v>11</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>6</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1</v>
+      </c>
+      <c r="X48" t="n">
+        <v>61.31103474784234</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>run_2025-09-03_11-08-09</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>11</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F49" t="n">
+        <v>2</v>
+      </c>
+      <c r="G49" t="n">
+        <v>10</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I49" t="n">
+        <v>20</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" t="n">
+        <v>10</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M49" t="n">
+        <v>50</v>
+      </c>
+      <c r="N49" t="n">
+        <v>1</v>
+      </c>
+      <c r="O49" t="n">
+        <v>2</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>20</v>
+      </c>
+      <c r="R49" t="n">
+        <v>10</v>
+      </c>
+      <c r="S49" t="n">
+        <v>16</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>10</v>
+      </c>
+      <c r="V49" t="n">
+        <v>29</v>
+      </c>
+      <c r="W49" t="n">
+        <v>16</v>
+      </c>
+      <c r="X49" t="n">
+        <v>69.99642346510838</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>run_2025-09-03_11-08-09</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>12</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G50" t="n">
+        <v>10</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I50" t="n">
+        <v>20</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>10</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M50" t="n">
+        <v>50</v>
+      </c>
+      <c r="N50" t="n">
+        <v>17</v>
+      </c>
+      <c r="O50" t="n">
+        <v>18</v>
+      </c>
+      <c r="P50" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>17</v>
+      </c>
+      <c r="R50" t="n">
+        <v>17</v>
+      </c>
+      <c r="S50" t="n">
+        <v>14</v>
+      </c>
+      <c r="T50" t="n">
+        <v>28</v>
+      </c>
+      <c r="U50" t="n">
+        <v>17</v>
+      </c>
+      <c r="V50" t="n">
+        <v>28</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>63.47602549898684</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>run_2025-09-03_11-08-09</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>13</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2</v>
+      </c>
+      <c r="G51" t="n">
+        <v>10</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I51" t="n">
+        <v>20</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
+        <v>10</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M51" t="n">
+        <v>50</v>
+      </c>
+      <c r="N51" t="n">
+        <v>24</v>
+      </c>
+      <c r="O51" t="n">
+        <v>25</v>
+      </c>
+      <c r="P51" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>19</v>
+      </c>
+      <c r="R51" t="n">
+        <v>19</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>7</v>
+      </c>
+      <c r="U51" t="n">
+        <v>12</v>
+      </c>
+      <c r="V51" t="n">
+        <v>7</v>
+      </c>
+      <c r="W51" t="n">
+        <v>25</v>
+      </c>
+      <c r="X51" t="n">
+        <v>76.46719317601173</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>run_2025-09-03_11-13-10</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>config_1</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F42" t="n">
-        <v>2</v>
-      </c>
-      <c r="G42" t="n">
-        <v>10</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I42" t="n">
-        <v>20</v>
-      </c>
-      <c r="J42" t="n">
-        <v>1</v>
-      </c>
-      <c r="K42" t="n">
-        <v>10</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M42" t="n">
-        <v>50</v>
-      </c>
-      <c r="N42" t="n">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2</v>
+      </c>
+      <c r="G52" t="n">
+        <v>10</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I52" t="n">
+        <v>20</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" t="n">
+        <v>10</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M52" t="n">
+        <v>50</v>
+      </c>
+      <c r="N52" t="n">
         <v>19</v>
       </c>
-      <c r="O42" t="n">
+      <c r="O52" t="n">
         <v>29</v>
       </c>
-      <c r="P42" t="n">
+      <c r="P52" t="n">
         <v>24</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="Q52" t="n">
         <v>6</v>
       </c>
-      <c r="R42" t="n">
+      <c r="R52" t="n">
         <v>31</v>
       </c>
-      <c r="S42" t="n">
+      <c r="S52" t="n">
         <v>19</v>
       </c>
-      <c r="T42" t="n">
+      <c r="T52" t="n">
         <v>19</v>
       </c>
-      <c r="U42" t="n">
+      <c r="U52" t="n">
         <v>21</v>
       </c>
-      <c r="V42" t="n">
+      <c r="V52" t="n">
         <v>4</v>
       </c>
-      <c r="W42" t="n">
+      <c r="W52" t="n">
         <v>30</v>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>inf</t>
         </is>
       </c>
-      <c r="Y42" t="n">
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>run_agendamento_2025-09-03_11-37-07</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2</v>
+      </c>
+      <c r="G53" t="n">
+        <v>5</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I53" t="n">
+        <v>20</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" t="n">
+        <v>10</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M53" t="n">
+        <v>50</v>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="n">
+        <v>50.57577825945867</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>run_agendamento_2025-09-03_11-37-07</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>2</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G54" t="n">
+        <v>5</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I54" t="n">
+        <v>20</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" t="n">
+        <v>10</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M54" t="n">
+        <v>50</v>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="n">
+        <v>50.63540522778682</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>run_agendamento_2025-09-03_11-37-07</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>3</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F55" t="n">
+        <v>2</v>
+      </c>
+      <c r="G55" t="n">
+        <v>5</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I55" t="n">
+        <v>20</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" t="n">
+        <v>10</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M55" t="n">
+        <v>50</v>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="n">
+        <v>53.63218834744396</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>run_agendamento_2025-09-03_11-37-07</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>4</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F56" t="n">
+        <v>2</v>
+      </c>
+      <c r="G56" t="n">
+        <v>5</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I56" t="n">
+        <v>20</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>10</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M56" t="n">
+        <v>50</v>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="n">
+        <v>51.02421332433355</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>run_agendamento_2025-09-03_11-37-07</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>5</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F57" t="n">
+        <v>2</v>
+      </c>
+      <c r="G57" t="n">
+        <v>5</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I57" t="n">
+        <v>20</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="n">
+        <v>10</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M57" t="n">
+        <v>50</v>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="n">
+        <v>50.92435253976513</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>run_2025-09-03_11-38-51</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2</v>
+      </c>
+      <c r="G58" t="n">
+        <v>10</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I58" t="n">
+        <v>20</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" t="n">
+        <v>10</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M58" t="n">
+        <v>50</v>
+      </c>
+      <c r="N58" t="n">
+        <v>30</v>
+      </c>
+      <c r="O58" t="n">
+        <v>22</v>
+      </c>
+      <c r="P58" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>31</v>
+      </c>
+      <c r="R58" t="n">
+        <v>11</v>
+      </c>
+      <c r="S58" t="n">
+        <v>3</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>23</v>
+      </c>
+      <c r="V58" t="n">
+        <v>13</v>
+      </c>
+      <c r="W58" t="n">
+        <v>7</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="Y58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>run_2025-09-03_11-38-51</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F59" t="n">
+        <v>2</v>
+      </c>
+      <c r="G59" t="n">
+        <v>10</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I59" t="n">
+        <v>20</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" t="n">
+        <v>10</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M59" t="n">
+        <v>50</v>
+      </c>
+      <c r="N59" t="n">
+        <v>4</v>
+      </c>
+      <c r="O59" t="n">
+        <v>26</v>
+      </c>
+      <c r="P59" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>27</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>10</v>
+      </c>
+      <c r="U59" t="n">
+        <v>4</v>
+      </c>
+      <c r="V59" t="n">
+        <v>11</v>
+      </c>
+      <c r="W59" t="n">
+        <v>16</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="Y59" t="n">
         <v>0</v>
       </c>
     </row>

--- a/src/output/resultados_consolidados.xlsx
+++ b/src/output/resultados_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y59"/>
+  <dimension ref="A1:Y67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -4763,7 +4763,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>run_2025-09-03_11-38-51</t>
+          <t>run_agendamento_2025-09-03_11-37-07</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4772,7 +4772,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D58" t="n">
         <v>1</v>
@@ -4784,7 +4784,7 @@
         <v>2</v>
       </c>
       <c r="G58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H58" t="n">
         <v>0.9</v>
@@ -4804,125 +4804,613 @@
       <c r="M58" t="n">
         <v>50</v>
       </c>
-      <c r="N58" t="n">
-        <v>30</v>
-      </c>
-      <c r="O58" t="n">
-        <v>22</v>
-      </c>
-      <c r="P58" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>31</v>
-      </c>
-      <c r="R58" t="n">
-        <v>11</v>
-      </c>
-      <c r="S58" t="n">
-        <v>3</v>
-      </c>
-      <c r="T58" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" t="n">
-        <v>23</v>
-      </c>
-      <c r="V58" t="n">
-        <v>13</v>
-      </c>
-      <c r="W58" t="n">
-        <v>7</v>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="n">
+        <v>41.61301147209014</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>run_agendamento_2025-09-03_11-37-07</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>7</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F59" t="n">
+        <v>2</v>
+      </c>
+      <c r="G59" t="n">
+        <v>5</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I59" t="n">
+        <v>20</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" t="n">
+        <v>10</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M59" t="n">
+        <v>50</v>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
+      <c r="X59" t="n">
+        <v>52.14556034566393</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>run_agendamento_2025-09-03_11-37-07</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>8</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F60" t="n">
+        <v>2</v>
+      </c>
+      <c r="G60" t="n">
+        <v>5</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I60" t="n">
+        <v>20</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" t="n">
+        <v>10</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M60" t="n">
+        <v>50</v>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="n">
+        <v>60.64886384813624</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>run_agendamento_2025-09-03_11-37-07</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>9</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2</v>
+      </c>
+      <c r="G61" t="n">
+        <v>5</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I61" t="n">
+        <v>20</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="n">
+        <v>10</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M61" t="n">
+        <v>50</v>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="n">
+        <v>51.65197017531482</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>run_agendamento_2025-09-03_11-37-07</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>10</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F62" t="n">
+        <v>2</v>
+      </c>
+      <c r="G62" t="n">
+        <v>5</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I62" t="n">
+        <v>20</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" t="n">
+        <v>10</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M62" t="n">
+        <v>50</v>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="n">
+        <v>49.59999708396475</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>run_agendamento_2025-09-03_11-37-07</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>11</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F63" t="n">
+        <v>2</v>
+      </c>
+      <c r="G63" t="n">
+        <v>5</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I63" t="n">
+        <v>20</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" t="n">
+        <v>10</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M63" t="n">
+        <v>50</v>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
+      <c r="X63" t="n">
+        <v>41.61301147209014</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>run_agendamento_2025-09-03_11-37-07</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>12</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F64" t="n">
+        <v>2</v>
+      </c>
+      <c r="G64" t="n">
+        <v>5</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I64" t="n">
+        <v>20</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" t="n">
+        <v>10</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M64" t="n">
+        <v>50</v>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
+      <c r="X64" t="n">
+        <v>51.65197017531484</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>run_agendamento_2025-09-03_11-37-07</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>13</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F65" t="n">
+        <v>2</v>
+      </c>
+      <c r="G65" t="n">
+        <v>5</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I65" t="n">
+        <v>20</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" t="n">
+        <v>10</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M65" t="n">
+        <v>50</v>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="n">
+        <v>49.5999970839648</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>run_2025-09-03_11-38-51</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>config_1</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>2</v>
-      </c>
-      <c r="D59" t="n">
-        <v>1</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F59" t="n">
-        <v>2</v>
-      </c>
-      <c r="G59" t="n">
-        <v>10</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I59" t="n">
-        <v>20</v>
-      </c>
-      <c r="J59" t="n">
-        <v>1</v>
-      </c>
-      <c r="K59" t="n">
-        <v>10</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M59" t="n">
-        <v>50</v>
-      </c>
-      <c r="N59" t="n">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F66" t="n">
+        <v>2</v>
+      </c>
+      <c r="G66" t="n">
+        <v>10</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I66" t="n">
+        <v>20</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" t="n">
+        <v>10</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M66" t="n">
+        <v>50</v>
+      </c>
+      <c r="N66" t="n">
+        <v>30</v>
+      </c>
+      <c r="O66" t="n">
+        <v>22</v>
+      </c>
+      <c r="P66" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>31</v>
+      </c>
+      <c r="R66" t="n">
+        <v>11</v>
+      </c>
+      <c r="S66" t="n">
+        <v>3</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>23</v>
+      </c>
+      <c r="V66" t="n">
+        <v>13</v>
+      </c>
+      <c r="W66" t="n">
+        <v>7</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="Y66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>run_2025-09-03_11-38-51</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>config_1</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>2</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F67" t="n">
+        <v>2</v>
+      </c>
+      <c r="G67" t="n">
+        <v>10</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I67" t="n">
+        <v>20</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1</v>
+      </c>
+      <c r="K67" t="n">
+        <v>10</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M67" t="n">
+        <v>50</v>
+      </c>
+      <c r="N67" t="n">
         <v>4</v>
       </c>
-      <c r="O59" t="n">
+      <c r="O67" t="n">
         <v>26</v>
       </c>
-      <c r="P59" t="n">
+      <c r="P67" t="n">
         <v>14</v>
       </c>
-      <c r="Q59" t="n">
+      <c r="Q67" t="n">
         <v>27</v>
       </c>
-      <c r="R59" t="n">
+      <c r="R67" t="n">
         <v>6</v>
       </c>
-      <c r="S59" t="n">
+      <c r="S67" t="n">
         <v>0</v>
       </c>
-      <c r="T59" t="n">
-        <v>10</v>
-      </c>
-      <c r="U59" t="n">
+      <c r="T67" t="n">
+        <v>10</v>
+      </c>
+      <c r="U67" t="n">
         <v>4</v>
       </c>
-      <c r="V59" t="n">
+      <c r="V67" t="n">
         <v>11</v>
       </c>
-      <c r="W59" t="n">
+      <c r="W67" t="n">
         <v>16</v>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>inf</t>
         </is>
       </c>
-      <c r="Y59" t="n">
+      <c r="Y67" t="n">
         <v>0</v>
       </c>
     </row>
